--- a/2026 IMI Golf League.xlsx
+++ b/2026 IMI Golf League.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://imicompanies-my.sharepoint.com/personal/ehigh_iengtobuild_com/Documents/Documents/Golf League/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="36" documentId="11_D9EC364B3004BA1E50EC54C5330225D83B9958DC" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8C87053C-6A65-4940-B147-FE5ED176DC15}"/>
+  <xr:revisionPtr revIDLastSave="13" documentId="11_8C2FB78B39C5EBC2F08C2CBAA07C8ED351C78C31" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{04FE213B-4E9E-42DB-95C5-672B9A58F09F}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="714" firstSheet="5" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="714" firstSheet="5" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Scores 2024" sheetId="1" state="hidden" r:id="rId1"/>
@@ -33,11 +33,8 @@
     <definedName name="Highland_Creek">Helper!$D$3:$D$5</definedName>
     <definedName name="Skybrook">Helper!$C$3:$C$5</definedName>
   </definedNames>
-  <calcPr calcId="191028"/>
+  <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -54,14 +51,152 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="552" uniqueCount="263">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="556" uniqueCount="265">
+  <si>
+    <t>Fill in the course, your name, tees, front/back and gross scores in the grey boxes</t>
+  </si>
+  <si>
+    <t>Points</t>
+  </si>
+  <si>
+    <t>Skybrook</t>
+  </si>
+  <si>
+    <t>First 3</t>
+  </si>
+  <si>
+    <t>Middle 3</t>
+  </si>
+  <si>
+    <t>Final 3</t>
+  </si>
+  <si>
+    <t>Overall</t>
+  </si>
+  <si>
+    <t>Net Score</t>
+  </si>
+  <si>
+    <t>Holes Won</t>
+  </si>
+  <si>
+    <t>PTS</t>
+  </si>
+  <si>
+    <t>Highland Creek</t>
+  </si>
+  <si>
+    <t>Brian Wojcio</t>
+  </si>
+  <si>
+    <t>Handicap:</t>
+  </si>
+  <si>
+    <t>Tees:</t>
+  </si>
+  <si>
+    <t>Blue</t>
+  </si>
+  <si>
+    <t>Holes:</t>
+  </si>
+  <si>
+    <t>Front 9</t>
+  </si>
+  <si>
+    <t>#</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Handicap</t>
+  </si>
+  <si>
+    <t>HC's by Tees</t>
+  </si>
+  <si>
+    <t>Back 9</t>
+  </si>
+  <si>
+    <t>HOLE</t>
+  </si>
+  <si>
+    <t>PAR</t>
+  </si>
+  <si>
+    <t>Ethan High</t>
+  </si>
+  <si>
+    <t>Green</t>
+  </si>
+  <si>
+    <t>White</t>
+  </si>
+  <si>
+    <t>HC</t>
+  </si>
+  <si>
+    <t>Rob Bass</t>
+  </si>
+  <si>
+    <t>Red</t>
+  </si>
+  <si>
+    <t>GROSS</t>
+  </si>
+  <si>
+    <t>Carson Bass</t>
+  </si>
+  <si>
+    <t>Par</t>
+  </si>
+  <si>
+    <t>Strokes</t>
+  </si>
+  <si>
+    <t>Michael McHugh</t>
+  </si>
+  <si>
+    <t>NET</t>
+  </si>
+  <si>
+    <t>Bruce Atkins</t>
+  </si>
+  <si>
+    <t>Wins Hole</t>
+  </si>
+  <si>
+    <t>Alex Palmer</t>
+  </si>
+  <si>
+    <t>Curtis Lynn</t>
+  </si>
+  <si>
+    <t>Ben Linck</t>
+  </si>
+  <si>
+    <t>Charlotte Hayes</t>
+  </si>
+  <si>
+    <t>David Maddox</t>
+  </si>
+  <si>
+    <t>Jerome Martin</t>
+  </si>
+  <si>
+    <t>Kaylan Adams</t>
+  </si>
+  <si>
+    <t>Megan Serian</t>
+  </si>
+  <si>
+    <t>Nick Coglianese</t>
+  </si>
   <si>
     <t>Tiebreaker</t>
   </si>
   <si>
-    <t>Name</t>
-  </si>
-  <si>
     <t>Week 1</t>
   </si>
   <si>
@@ -111,9 +246,6 @@
   </si>
   <si>
     <t>Stephen Keeler</t>
-  </si>
-  <si>
-    <t>Ethan High</t>
   </si>
   <si>
     <t>David Hughes</t>
@@ -463,9 +595,6 @@
     <t>7, 8, 9</t>
   </si>
   <si>
-    <t>#</t>
-  </si>
-  <si>
     <t>Players</t>
   </si>
   <si>
@@ -478,60 +607,18 @@
     <t>Paid?</t>
   </si>
   <si>
-    <t>Brian Wojcio</t>
-  </si>
-  <si>
     <t>Mens</t>
   </si>
   <si>
-    <t>Rob Bass</t>
-  </si>
-  <si>
-    <t>Carson Bass</t>
+    <t>Yes - Cash</t>
   </si>
   <si>
     <t>Yes - Venmo</t>
   </si>
   <si>
-    <t>Michael McHugh</t>
-  </si>
-  <si>
-    <t>Bruce Atkins</t>
-  </si>
-  <si>
-    <t>Alex Palmer</t>
-  </si>
-  <si>
-    <t>Curtis Lynn</t>
-  </si>
-  <si>
-    <t>Ben Linck</t>
-  </si>
-  <si>
-    <t>Yes - Cash</t>
-  </si>
-  <si>
-    <t>Charlotte Hayes</t>
-  </si>
-  <si>
-    <t>David Maddox</t>
-  </si>
-  <si>
-    <t>Jerome Martin</t>
-  </si>
-  <si>
-    <t>Kaylan Adams</t>
-  </si>
-  <si>
-    <t>Megan Serian</t>
-  </si>
-  <si>
     <t>Womens</t>
   </si>
   <si>
-    <t>Nick Coglianese</t>
-  </si>
-  <si>
     <t>Reston National</t>
   </si>
   <si>
@@ -604,18 +691,12 @@
     <t>Ethan</t>
   </si>
   <si>
-    <t>Blue</t>
-  </si>
-  <si>
     <t>USGA Diff.</t>
   </si>
   <si>
     <t>Blue/White</t>
   </si>
   <si>
-    <t>White</t>
-  </si>
-  <si>
     <t># of Score Differentials</t>
   </si>
   <si>
@@ -673,6 +754,9 @@
     <t>Average NET Score</t>
   </si>
   <si>
+    <t>0-1-0</t>
+  </si>
+  <si>
     <t>Playoffs</t>
   </si>
   <si>
@@ -688,15 +772,12 @@
     <t>Total Score</t>
   </si>
   <si>
+    <t>1-0-0</t>
+  </si>
+  <si>
     <t>Playoff Matchups</t>
   </si>
   <si>
-    <t>Front 9</t>
-  </si>
-  <si>
-    <t>Back 9</t>
-  </si>
-  <si>
     <t>Winner of each</t>
   </si>
   <si>
@@ -721,24 +802,6 @@
     <t>Fill in your name, tees, front/back 9, and gross scores in the grey boxes</t>
   </si>
   <si>
-    <t>Points</t>
-  </si>
-  <si>
-    <t>First 3</t>
-  </si>
-  <si>
-    <t>Middle 3</t>
-  </si>
-  <si>
-    <t>Final 3</t>
-  </si>
-  <si>
-    <t>Overall</t>
-  </si>
-  <si>
-    <t>Net Score</t>
-  </si>
-  <si>
     <t>Full Name</t>
   </si>
   <si>
@@ -748,79 +811,19 @@
     <t>Last Name</t>
   </si>
   <si>
-    <t>HC</t>
-  </si>
-  <si>
-    <t>Holes Won</t>
-  </si>
-  <si>
-    <t>PTS</t>
-  </si>
-  <si>
     <t>Brian Bencal</t>
   </si>
   <si>
-    <t>Handicap:</t>
-  </si>
-  <si>
-    <t>Tees:</t>
-  </si>
-  <si>
-    <t>Holes:</t>
-  </si>
-  <si>
-    <t>HC's by Tees</t>
-  </si>
-  <si>
-    <t>HOLE</t>
-  </si>
-  <si>
-    <t>PAR</t>
-  </si>
-  <si>
     <t>Blue / White</t>
   </si>
   <si>
     <t>Katherine Plasket</t>
   </si>
   <si>
-    <t>GROSS</t>
-  </si>
-  <si>
-    <t>Strokes</t>
-  </si>
-  <si>
-    <t>NET</t>
-  </si>
-  <si>
-    <t>Wins Hole</t>
-  </si>
-  <si>
     <t>Oscar Velasquez</t>
   </si>
   <si>
     <t>William Plasket</t>
-  </si>
-  <si>
-    <t>Fill in the course, your name, tees, front/back and gross scores in the grey boxes</t>
-  </si>
-  <si>
-    <t>Skybrook</t>
-  </si>
-  <si>
-    <t>Highland Creek</t>
-  </si>
-  <si>
-    <t>Handicap</t>
-  </si>
-  <si>
-    <t>Green</t>
-  </si>
-  <si>
-    <t>Red</t>
-  </si>
-  <si>
-    <t>Par</t>
   </si>
   <si>
     <t>Highland_Creek</t>
@@ -2195,36 +2198,36 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="17" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="19" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="5" borderId="25" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="17" fillId="5" borderId="25" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="17" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="5" borderId="19" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="19" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2237,16 +2240,19 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2262,9 +2268,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2304,39 +2307,39 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="19" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="19" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="2" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="2" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="17" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="19" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="2" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="5" borderId="25" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="5" borderId="25" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="17" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="19" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -2722,50 +2725,50 @@
     <col min="3" max="3" width="12.140625" style="12" bestFit="1" customWidth="1"/>
     <col min="4" max="11" width="9.140625" style="12" customWidth="1"/>
     <col min="12" max="13" width="11.5703125" style="12" customWidth="1"/>
-    <col min="14" max="19" width="9.140625" style="12" customWidth="1"/>
-    <col min="20" max="16384" width="9.140625" style="12"/>
+    <col min="14" max="20" width="9.140625" style="12" customWidth="1"/>
+    <col min="21" max="16384" width="9.140625" style="12"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="M1" s="27" t="s">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="N1" s="21"/>
     </row>
     <row r="2" spans="1:14" ht="41.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B2" s="20" t="s">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="C2" s="22"/>
       <c r="D2" s="19" t="s">
-        <v>2</v>
+        <v>48</v>
       </c>
       <c r="E2" s="18" t="s">
-        <v>3</v>
+        <v>49</v>
       </c>
       <c r="F2" s="18" t="s">
-        <v>4</v>
+        <v>50</v>
       </c>
       <c r="G2" s="18" t="s">
-        <v>5</v>
+        <v>51</v>
       </c>
       <c r="H2" s="18" t="s">
-        <v>6</v>
+        <v>52</v>
       </c>
       <c r="I2" s="18" t="s">
-        <v>7</v>
+        <v>53</v>
       </c>
       <c r="J2" s="18" t="s">
-        <v>8</v>
+        <v>54</v>
       </c>
       <c r="K2" s="17" t="s">
-        <v>9</v>
+        <v>55</v>
       </c>
       <c r="L2" s="16" t="s">
-        <v>10</v>
+        <v>56</v>
       </c>
       <c r="M2" s="15" t="s">
-        <v>11</v>
+        <v>57</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="12.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
@@ -2773,10 +2776,10 @@
         <v>1</v>
       </c>
       <c r="B3" s="25" t="s">
-        <v>12</v>
+        <v>58</v>
       </c>
       <c r="C3" s="24" t="s">
-        <v>13</v>
+        <v>59</v>
       </c>
       <c r="D3" s="23">
         <v>8</v>
@@ -2810,10 +2813,10 @@
         <v>2</v>
       </c>
       <c r="B4" s="25" t="s">
-        <v>14</v>
+        <v>60</v>
       </c>
       <c r="C4" s="24" t="s">
-        <v>13</v>
+        <v>59</v>
       </c>
       <c r="D4" s="23">
         <v>0</v>
@@ -2847,10 +2850,10 @@
         <v>3</v>
       </c>
       <c r="B5" s="25" t="s">
-        <v>15</v>
+        <v>61</v>
       </c>
       <c r="C5" s="24" t="s">
-        <v>13</v>
+        <v>59</v>
       </c>
       <c r="D5" s="23"/>
       <c r="E5" s="14">
@@ -2884,10 +2887,10 @@
         <v>4</v>
       </c>
       <c r="B6" s="25" t="s">
-        <v>16</v>
+        <v>62</v>
       </c>
       <c r="C6" s="24" t="s">
-        <v>13</v>
+        <v>59</v>
       </c>
       <c r="D6" s="23"/>
       <c r="E6" s="14">
@@ -2919,10 +2922,10 @@
         <v>5</v>
       </c>
       <c r="B7" s="25" t="s">
-        <v>17</v>
+        <v>63</v>
       </c>
       <c r="C7" s="24" t="s">
-        <v>13</v>
+        <v>59</v>
       </c>
       <c r="D7" s="23">
         <v>6</v>
@@ -2958,10 +2961,10 @@
         <v>6</v>
       </c>
       <c r="B8" s="25" t="s">
-        <v>18</v>
+        <v>64</v>
       </c>
       <c r="C8" s="24" t="s">
-        <v>13</v>
+        <v>59</v>
       </c>
       <c r="D8" s="23">
         <v>2</v>
@@ -2995,10 +2998,10 @@
         <v>7</v>
       </c>
       <c r="B9" s="25" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="C9" s="24" t="s">
-        <v>13</v>
+        <v>59</v>
       </c>
       <c r="D9" s="23">
         <v>2.5</v>
@@ -3030,10 +3033,10 @@
         <v>8</v>
       </c>
       <c r="B10" s="25" t="s">
-        <v>20</v>
+        <v>65</v>
       </c>
       <c r="C10" s="24" t="s">
-        <v>13</v>
+        <v>59</v>
       </c>
       <c r="D10" s="23">
         <v>5.5</v>
@@ -3067,10 +3070,10 @@
         <v>9</v>
       </c>
       <c r="B11" s="25" t="s">
-        <v>21</v>
+        <v>66</v>
       </c>
       <c r="C11" s="24" t="s">
-        <v>13</v>
+        <v>59</v>
       </c>
       <c r="D11" s="23">
         <v>5</v>
@@ -3104,10 +3107,10 @@
         <v>10</v>
       </c>
       <c r="B12" s="25" t="s">
-        <v>22</v>
+        <v>67</v>
       </c>
       <c r="C12" s="24" t="s">
-        <v>13</v>
+        <v>59</v>
       </c>
       <c r="D12" s="23">
         <v>3</v>
@@ -3143,10 +3146,10 @@
         <v>11</v>
       </c>
       <c r="B13" s="25" t="s">
-        <v>23</v>
+        <v>68</v>
       </c>
       <c r="C13" s="24" t="s">
-        <v>13</v>
+        <v>59</v>
       </c>
       <c r="D13" s="23">
         <v>2</v>
@@ -3178,10 +3181,10 @@
         <v>12</v>
       </c>
       <c r="B14" s="25" t="s">
-        <v>24</v>
+        <v>69</v>
       </c>
       <c r="C14" s="24" t="s">
-        <v>13</v>
+        <v>59</v>
       </c>
       <c r="D14" s="23">
         <v>6</v>
@@ -3215,10 +3218,10 @@
         <v>13</v>
       </c>
       <c r="B15" s="25" t="s">
-        <v>25</v>
+        <v>70</v>
       </c>
       <c r="C15" s="24" t="s">
-        <v>13</v>
+        <v>59</v>
       </c>
       <c r="D15" s="23">
         <v>3</v>
@@ -3252,10 +3255,10 @@
         <v>14</v>
       </c>
       <c r="B16" s="25" t="s">
-        <v>26</v>
+        <v>71</v>
       </c>
       <c r="C16" s="24" t="s">
-        <v>13</v>
+        <v>59</v>
       </c>
       <c r="D16" s="23">
         <v>5</v>
@@ -3289,10 +3292,10 @@
         <v>15</v>
       </c>
       <c r="B17" s="25" t="s">
-        <v>27</v>
+        <v>72</v>
       </c>
       <c r="C17" s="24" t="s">
-        <v>13</v>
+        <v>59</v>
       </c>
       <c r="D17" s="23">
         <v>3.5</v>
@@ -3324,10 +3327,10 @@
         <v>16</v>
       </c>
       <c r="B18" s="25" t="s">
-        <v>28</v>
+        <v>73</v>
       </c>
       <c r="C18" s="24" t="s">
-        <v>13</v>
+        <v>59</v>
       </c>
       <c r="D18" s="23">
         <v>4.5</v>
@@ -3363,10 +3366,10 @@
         <v>17</v>
       </c>
       <c r="B19" s="25" t="s">
-        <v>29</v>
+        <v>74</v>
       </c>
       <c r="C19" s="24" t="s">
-        <v>13</v>
+        <v>59</v>
       </c>
       <c r="D19" s="23">
         <v>7</v>
@@ -3400,10 +3403,10 @@
         <v>18</v>
       </c>
       <c r="B20" s="25" t="s">
-        <v>30</v>
+        <v>75</v>
       </c>
       <c r="C20" s="24" t="s">
-        <v>13</v>
+        <v>59</v>
       </c>
       <c r="D20" s="23">
         <v>1</v>
@@ -3461,59 +3464,59 @@
     <col min="41" max="49" width="4" style="117" customWidth="1"/>
     <col min="50" max="50" width="10.42578125" style="117" bestFit="1" customWidth="1"/>
     <col min="51" max="59" width="4" style="117" customWidth="1"/>
-    <col min="60" max="65" width="9.85546875" style="117" customWidth="1"/>
-    <col min="66" max="16384" width="9.85546875" style="117"/>
+    <col min="60" max="66" width="9.85546875" style="117" customWidth="1"/>
+    <col min="67" max="16384" width="9.85546875" style="117"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:59" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B1" s="116" t="s">
-        <v>248</v>
-      </c>
-      <c r="J1" s="182" t="s">
-        <v>221</v>
-      </c>
-      <c r="K1" s="183"/>
-      <c r="L1" s="183"/>
-      <c r="M1" s="183"/>
+        <v>0</v>
+      </c>
+      <c r="J1" s="190" t="s">
+        <v>1</v>
+      </c>
+      <c r="K1" s="191"/>
+      <c r="L1" s="191"/>
+      <c r="M1" s="191"/>
     </row>
     <row r="2" spans="2:59" ht="24.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B2" s="172" t="s">
-        <v>249</v>
+        <v>10</v>
       </c>
       <c r="D2" s="118" t="s">
-        <v>222</v>
+        <v>3</v>
       </c>
       <c r="E2" s="118" t="s">
-        <v>223</v>
+        <v>4</v>
       </c>
       <c r="F2" s="118" t="s">
-        <v>224</v>
+        <v>5</v>
       </c>
       <c r="G2" s="118" t="s">
-        <v>225</v>
+        <v>6</v>
       </c>
       <c r="H2" s="118" t="s">
-        <v>226</v>
+        <v>7</v>
       </c>
       <c r="I2" s="119"/>
-      <c r="J2" s="189" t="str">
+      <c r="J2" s="188" t="str">
         <f>B8</f>
-        <v>Curtis Lynn</v>
-      </c>
-      <c r="K2" s="190"/>
-      <c r="L2" s="192" t="str">
+        <v>Jerome Martin</v>
+      </c>
+      <c r="K2" s="179"/>
+      <c r="L2" s="178" t="str">
         <f>B17</f>
-        <v>Nick Coglianese</v>
-      </c>
-      <c r="M2" s="190"/>
+        <v>Kaylan Adams</v>
+      </c>
+      <c r="M2" s="179"/>
     </row>
     <row r="3" spans="2:59" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="178" t="str">
+      <c r="B3" s="189" t="str">
         <f>J2</f>
-        <v>Curtis Lynn</v>
+        <v>Jerome Martin</v>
       </c>
       <c r="C3" s="120" t="s">
-        <v>231</v>
+        <v>8</v>
       </c>
       <c r="D3" s="121">
         <f>SUM(C15:E15)</f>
@@ -3525,31 +3528,31 @@
       </c>
       <c r="F3" s="121">
         <f>SUM(I15:K15)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G3" s="121">
         <f>SUM(C15:K15)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H3" s="121">
         <f>SUM(C14:K14)</f>
-        <v>25</v>
-      </c>
-      <c r="J3" s="184">
+        <v>54</v>
+      </c>
+      <c r="J3" s="182">
         <f>SUM(D4:H4)</f>
-        <v>3</v>
-      </c>
-      <c r="K3" s="185"/>
-      <c r="L3" s="191">
+        <v>4</v>
+      </c>
+      <c r="K3" s="183"/>
+      <c r="L3" s="192">
         <f>SUM(D6:H6)</f>
-        <v>5</v>
-      </c>
-      <c r="M3" s="185"/>
+        <v>4</v>
+      </c>
+      <c r="M3" s="183"/>
     </row>
     <row r="4" spans="2:59" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="179"/>
+      <c r="B4" s="186"/>
       <c r="C4" s="125" t="s">
-        <v>232</v>
+        <v>9</v>
       </c>
       <c r="D4" s="126">
         <f>IF(D3&gt;D5,2,IF(D3=D5,1,0))</f>
@@ -3557,32 +3560,32 @@
       </c>
       <c r="E4" s="126">
         <f>IF(E3&gt;E5,2,IF(E3=E5,1,0))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F4" s="126">
         <f>IF(F3&gt;F5,2,IF(F3=F5,1,0))</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G4" s="126">
         <f>IF(G3&gt;G5,1,IF(G3=G5,0.5,0))</f>
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="H4" s="126">
         <f>IF(H3&lt;H5,1,IF(H3=H5,0.5,0))</f>
-        <v>0</v>
-      </c>
-      <c r="J4" s="186"/>
-      <c r="K4" s="187"/>
+        <v>0.5</v>
+      </c>
+      <c r="J4" s="184"/>
+      <c r="K4" s="185"/>
       <c r="L4" s="181"/>
-      <c r="M4" s="187"/>
+      <c r="M4" s="185"/>
     </row>
     <row r="5" spans="2:59" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="178" t="str">
+      <c r="B5" s="189" t="str">
         <f>L2</f>
-        <v>Nick Coglianese</v>
+        <v>Kaylan Adams</v>
       </c>
       <c r="C5" s="127" t="s">
-        <v>231</v>
+        <v>8</v>
       </c>
       <c r="D5" s="128">
         <f>SUM(C24:E24)</f>
@@ -3590,29 +3593,29 @@
       </c>
       <c r="E5" s="128">
         <f>SUM(F24:H24)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F5" s="128">
         <f>SUM(I24:K24)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G5" s="128">
         <f>SUM(C24:K24)</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H5" s="128">
         <f>SUM(C23:K23)</f>
-        <v>23</v>
-      </c>
-      <c r="J5" s="179"/>
-      <c r="K5" s="188"/>
-      <c r="L5" s="183"/>
-      <c r="M5" s="188"/>
+        <v>54</v>
+      </c>
+      <c r="J5" s="186"/>
+      <c r="K5" s="187"/>
+      <c r="L5" s="191"/>
+      <c r="M5" s="187"/>
     </row>
     <row r="6" spans="2:59" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="179"/>
+      <c r="B6" s="186"/>
       <c r="C6" s="125" t="s">
-        <v>232</v>
+        <v>9</v>
       </c>
       <c r="D6" s="126">
         <f>IF(D5&gt;D3,2,IF(D5=D3,1,0))</f>
@@ -3620,19 +3623,19 @@
       </c>
       <c r="E6" s="126">
         <f>IF(E5&gt;E3,2,IF(E5=E3,1,0))</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F6" s="126">
         <f>IF(F5&gt;F3,2,IF(F5=F3,1,0))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G6" s="126">
         <f>IF(G5&gt;G3,1,IF(G5=G3,0.5,0))</f>
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="H6" s="126">
         <f>IF(H5&lt;H3,1,IF(H5=H3,0.5,0))</f>
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J6" s="129"/>
       <c r="K6" s="129"/>
@@ -3651,7 +3654,7 @@
       <c r="K7" s="129"/>
       <c r="L7" s="129"/>
       <c r="T7" s="180" t="s">
-        <v>249</v>
+        <v>2</v>
       </c>
       <c r="U7" s="181"/>
       <c r="V7" s="181"/>
@@ -3673,7 +3676,7 @@
       <c r="AL7" s="181"/>
       <c r="AM7" s="181"/>
       <c r="AN7" s="180" t="s">
-        <v>250</v>
+        <v>10</v>
       </c>
       <c r="AO7" s="181"/>
       <c r="AP7" s="181"/>
@@ -3697,45 +3700,45 @@
     </row>
     <row r="8" spans="2:59" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B8" s="145" t="s">
-        <v>148</v>
+        <v>43</v>
       </c>
       <c r="C8" s="130" t="s">
-        <v>234</v>
+        <v>12</v>
       </c>
       <c r="D8" s="129">
         <f>_xlfn.XLOOKUP(B8,$P$9:$P$23,$Q$9:$Q$23)</f>
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="E8" s="129"/>
       <c r="F8" s="129" t="s">
-        <v>235</v>
+        <v>13</v>
       </c>
       <c r="G8" s="173" t="s">
-        <v>182</v>
+        <v>14</v>
       </c>
       <c r="H8" s="129"/>
       <c r="I8" s="129" t="s">
-        <v>236</v>
+        <v>15</v>
       </c>
       <c r="J8" s="149" t="s">
-        <v>211</v>
+        <v>16</v>
       </c>
       <c r="K8" s="129"/>
       <c r="L8" s="129"/>
       <c r="O8" s="143" t="s">
-        <v>135</v>
+        <v>17</v>
       </c>
       <c r="P8" s="143" t="s">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="Q8" s="143" t="s">
-        <v>251</v>
+        <v>19</v>
       </c>
       <c r="T8" s="117" t="s">
-        <v>237</v>
+        <v>20</v>
       </c>
       <c r="U8" s="180" t="s">
-        <v>211</v>
+        <v>16</v>
       </c>
       <c r="V8" s="181"/>
       <c r="W8" s="181"/>
@@ -3746,7 +3749,7 @@
       <c r="AB8" s="181"/>
       <c r="AC8" s="181"/>
       <c r="AD8" s="180" t="s">
-        <v>212</v>
+        <v>21</v>
       </c>
       <c r="AE8" s="181"/>
       <c r="AF8" s="181"/>
@@ -3758,10 +3761,10 @@
       <c r="AL8" s="181"/>
       <c r="AM8" s="181"/>
       <c r="AN8" s="117" t="s">
-        <v>237</v>
+        <v>20</v>
       </c>
       <c r="AO8" s="180" t="s">
-        <v>211</v>
+        <v>16</v>
       </c>
       <c r="AP8" s="181"/>
       <c r="AQ8" s="181"/>
@@ -3772,7 +3775,7 @@
       <c r="AV8" s="181"/>
       <c r="AW8" s="181"/>
       <c r="AX8" s="180" t="s">
-        <v>212</v>
+        <v>21</v>
       </c>
       <c r="AY8" s="181"/>
       <c r="AZ8" s="181"/>
@@ -3786,7 +3789,7 @@
     </row>
     <row r="9" spans="2:59" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="131" t="s">
-        <v>238</v>
+        <v>22</v>
       </c>
       <c r="C9" s="132">
         <v>1</v>
@@ -3820,14 +3823,14 @@
         <v>1</v>
       </c>
       <c r="P9" s="123" t="s">
-        <v>140</v>
+        <v>11</v>
       </c>
       <c r="Q9" s="153">
         <f>Schedule!D15</f>
         <v>12</v>
       </c>
       <c r="T9" s="117" t="s">
-        <v>182</v>
+        <v>14</v>
       </c>
       <c r="U9" s="129">
         <v>7</v>
@@ -3857,7 +3860,7 @@
         <v>1</v>
       </c>
       <c r="AD9" s="117" t="s">
-        <v>182</v>
+        <v>14</v>
       </c>
       <c r="AE9" s="129">
         <v>4</v>
@@ -3887,7 +3890,7 @@
         <v>10</v>
       </c>
       <c r="AN9" s="117" t="s">
-        <v>182</v>
+        <v>14</v>
       </c>
       <c r="AO9" s="129">
         <v>7</v>
@@ -3917,7 +3920,7 @@
         <v>3</v>
       </c>
       <c r="AX9" s="117" t="s">
-        <v>182</v>
+        <v>14</v>
       </c>
       <c r="AY9" s="129">
         <v>14</v>
@@ -3949,7 +3952,7 @@
     </row>
     <row r="10" spans="2:59" x14ac:dyDescent="0.25">
       <c r="B10" s="135" t="s">
-        <v>239</v>
+        <v>23</v>
       </c>
       <c r="C10" s="129">
         <f t="array" ref="C10">IF($B$2="Skybrook",
@@ -3975,7 +3978,7 @@
       $J8="Front 9",INDEX($AO$12:$AW$12,1,D9)
    )
 )</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E10" s="137">
         <f t="array" ref="E10">IF($B$2="Skybrook",
@@ -3988,7 +3991,7 @@
       $J8="Front 9",INDEX($AO$12:$AW$12,1,E9)
    )
 )</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F10" s="136">
         <f t="array" ref="F10">IF($B$2="Skybrook",
@@ -4001,7 +4004,7 @@
       $J8="Front 9",INDEX($AO$12:$AW$12,1,F9)
    )
 )</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G10" s="129">
         <f t="array" ref="G10">IF($B$2="Skybrook",
@@ -4027,7 +4030,7 @@
       $J8="Front 9",INDEX($AO$12:$AW$12,1,H9)
    )
 )</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I10" s="136">
         <f t="array" ref="I10">IF($B$2="Skybrook",
@@ -4040,7 +4043,7 @@
       $J8="Front 9",INDEX($AO$12:$AW$12,1,I9)
    )
 )</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J10" s="129">
         <f t="array" ref="J10">IF($B$2="Skybrook",
@@ -4053,7 +4056,7 @@
       $J8="Front 9",INDEX($AO$12:$AW$12,1,J9)
    )
 )</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K10" s="137">
         <f t="array" ref="K10">IF($B$2="Skybrook",
@@ -4076,14 +4079,14 @@
         <v>2</v>
       </c>
       <c r="P10" s="123" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="Q10" s="153">
         <f>Schedule!D16</f>
         <v>12</v>
       </c>
       <c r="T10" s="117" t="s">
-        <v>252</v>
+        <v>25</v>
       </c>
       <c r="U10" s="129">
         <v>7</v>
@@ -4113,7 +4116,7 @@
         <v>1</v>
       </c>
       <c r="AD10" s="117" t="s">
-        <v>252</v>
+        <v>25</v>
       </c>
       <c r="AE10" s="129">
         <v>4</v>
@@ -4143,7 +4146,7 @@
         <v>10</v>
       </c>
       <c r="AN10" s="117" t="s">
-        <v>185</v>
+        <v>26</v>
       </c>
       <c r="AO10" s="129">
         <v>7</v>
@@ -4173,7 +4176,7 @@
         <v>3</v>
       </c>
       <c r="AX10" s="117" t="s">
-        <v>185</v>
+        <v>26</v>
       </c>
       <c r="AY10" s="129">
         <v>14</v>
@@ -4205,7 +4208,7 @@
     </row>
     <row r="11" spans="2:59" x14ac:dyDescent="0.25">
       <c r="B11" s="135" t="s">
-        <v>230</v>
+        <v>27</v>
       </c>
       <c r="C11" s="129">
         <f t="array" ref="C11">IF($B$2="Skybrook",
@@ -4231,7 +4234,7 @@
       $J8="Front 9",VLOOKUP($G8,$AN$9:$AW$11,COLUMN()-1,0)
    )
 )</f>
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E11" s="137">
         <f t="array" ref="E11">IF($B$2="Skybrook",
@@ -4244,7 +4247,7 @@
       $J8="Front 9",VLOOKUP($G8,$AN$9:$AW$11,COLUMN()-1,0)
    )
 )</f>
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="F11" s="136">
         <f t="array" ref="F11">IF($B$2="Skybrook",
@@ -4257,7 +4260,7 @@
       $J8="Front 9",VLOOKUP($G8,$AN$9:$AW$11,COLUMN()-1,0)
    )
 )</f>
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="G11" s="129">
         <f t="array" ref="G11">IF($B$2="Skybrook",
@@ -4270,7 +4273,7 @@
       $J8="Front 9",VLOOKUP($G8,$AN$9:$AW$11,COLUMN()-1,0)
    )
 )</f>
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="H11" s="137">
         <f t="array" ref="H11">IF($B$2="Skybrook",
@@ -4283,7 +4286,7 @@
       $J8="Front 9",VLOOKUP($G8,$AN$9:$AW$11,COLUMN()-1,0)
    )
 )</f>
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="I11" s="136">
         <f t="array" ref="I11">IF($B$2="Skybrook",
@@ -4296,7 +4299,7 @@
       $J8="Front 9",VLOOKUP($G8,$AN$9:$AW$11,COLUMN()-1,0)
    )
 )</f>
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="J11" s="129">
         <f t="array" ref="J11">IF($B$2="Skybrook",
@@ -4309,7 +4312,7 @@
       $J8="Front 9",VLOOKUP($G8,$AN$9:$AW$11,COLUMN()-1,0)
    )
 )</f>
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="K11" s="137">
         <f t="array" ref="K11">IF($B$2="Skybrook",
@@ -4322,7 +4325,7 @@
       $J8="Front 9",VLOOKUP($G8,$AN$9:$AW$11,COLUMN()-1,0)
    )
 )</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L11" s="129"/>
       <c r="O11" s="122">
@@ -4330,14 +4333,14 @@
         <v>3</v>
       </c>
       <c r="P11" s="123" t="s">
-        <v>142</v>
+        <v>28</v>
       </c>
       <c r="Q11" s="153">
         <f>Schedule!D17</f>
         <v>15</v>
       </c>
       <c r="T11" s="117" t="s">
-        <v>253</v>
+        <v>29</v>
       </c>
       <c r="U11" s="129">
         <v>17</v>
@@ -4367,7 +4370,7 @@
         <v>1</v>
       </c>
       <c r="AD11" s="117" t="s">
-        <v>253</v>
+        <v>29</v>
       </c>
       <c r="AE11" s="129">
         <v>4</v>
@@ -4397,7 +4400,7 @@
         <v>8</v>
       </c>
       <c r="AN11" s="117" t="s">
-        <v>253</v>
+        <v>29</v>
       </c>
       <c r="AO11" s="129">
         <v>7</v>
@@ -4427,7 +4430,7 @@
         <v>3</v>
       </c>
       <c r="AX11" s="117" t="s">
-        <v>253</v>
+        <v>29</v>
       </c>
       <c r="AY11" s="129">
         <v>14</v>
@@ -4459,55 +4462,55 @@
     </row>
     <row r="12" spans="2:59" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="138" t="s">
-        <v>242</v>
+        <v>30</v>
       </c>
       <c r="C12" s="146">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D12" s="147">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E12" s="148">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F12" s="146">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G12" s="147">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H12" s="148">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I12" s="146">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J12" s="147">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="K12" s="148">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="L12" s="129">
         <f>SUM(C12:K12)</f>
-        <v>39</v>
+        <v>72</v>
       </c>
       <c r="M12" s="139">
         <f>SUM(C12:K12)-SUM(C$10:K$10)</f>
-        <v>3</v>
+        <v>36</v>
       </c>
       <c r="O12" s="122">
         <v>4</v>
       </c>
       <c r="P12" s="123" t="s">
-        <v>143</v>
+        <v>31</v>
       </c>
       <c r="Q12" s="153">
         <f>Schedule!D18</f>
         <v>20</v>
       </c>
       <c r="T12" s="117" t="s">
-        <v>254</v>
+        <v>32</v>
       </c>
       <c r="U12" s="144">
         <v>4</v>
@@ -4537,7 +4540,7 @@
         <v>4</v>
       </c>
       <c r="AD12" s="117" t="s">
-        <v>254</v>
+        <v>32</v>
       </c>
       <c r="AE12" s="144">
         <v>4</v>
@@ -4567,7 +4570,7 @@
         <v>5</v>
       </c>
       <c r="AN12" s="117" t="s">
-        <v>254</v>
+        <v>32</v>
       </c>
       <c r="AO12" s="144">
         <v>4</v>
@@ -4597,7 +4600,7 @@
         <v>4</v>
       </c>
       <c r="AX12" s="117" t="s">
-        <v>254</v>
+        <v>32</v>
       </c>
       <c r="AY12" s="144">
         <v>4</v>
@@ -4629,7 +4632,7 @@
     </row>
     <row r="13" spans="2:59" x14ac:dyDescent="0.25">
       <c r="B13" s="135" t="s">
-        <v>243</v>
+        <v>33</v>
       </c>
       <c r="C13" s="136">
         <f t="shared" ref="C13:K13" si="0">INT($D$8/18)+IF(C11&lt;=MOD($D$8,18),1,0)</f>
@@ -4637,7 +4640,7 @@
       </c>
       <c r="D13" s="129">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E13" s="137">
         <f t="shared" si="0"/>
@@ -4645,7 +4648,7 @@
       </c>
       <c r="F13" s="136">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G13" s="129">
         <f t="shared" si="0"/>
@@ -4653,11 +4656,11 @@
       </c>
       <c r="H13" s="137">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I13" s="136">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J13" s="129">
         <f t="shared" si="0"/>
@@ -4672,7 +4675,7 @@
         <v>5</v>
       </c>
       <c r="P13" s="123" t="s">
-        <v>145</v>
+        <v>34</v>
       </c>
       <c r="Q13" s="153">
         <f>Schedule!D19</f>
@@ -4681,11 +4684,11 @@
     </row>
     <row r="14" spans="2:59" x14ac:dyDescent="0.25">
       <c r="B14" s="135" t="s">
-        <v>244</v>
+        <v>35</v>
       </c>
       <c r="C14" s="136">
         <f>C12-C13</f>
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D14" s="129">
         <f t="shared" ref="D14:K14" si="1">D12-INT($D$8/18)-IF(D11&lt;=MOD($D$8,18),1,0)</f>
@@ -4693,45 +4696,45 @@
       </c>
       <c r="E14" s="137">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F14" s="136">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G14" s="129">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H14" s="137">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I14" s="136">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J14" s="129">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="K14" s="137">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="L14" s="155">
         <f>SUM(C14:K14)</f>
-        <v>25</v>
+        <v>54</v>
       </c>
       <c r="M14" s="139">
         <f>SUM(C14:K14)-SUM(C$10:K$10)</f>
-        <v>-11</v>
+        <v>18</v>
       </c>
       <c r="O14" s="122">
         <v>6</v>
       </c>
       <c r="P14" s="123" t="s">
-        <v>146</v>
+        <v>36</v>
       </c>
       <c r="Q14" s="153">
         <f>Schedule!D20</f>
@@ -4740,7 +4743,7 @@
     </row>
     <row r="15" spans="2:59" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B15" s="140" t="s">
-        <v>245</v>
+        <v>37</v>
       </c>
       <c r="C15" s="124">
         <f t="shared" ref="C15:K15" si="2">IF(C14&lt;C23,1,0)</f>
@@ -4772,11 +4775,11 @@
       </c>
       <c r="J15" s="141">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K15" s="142">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L15" s="129"/>
       <c r="O15" s="122">
@@ -4784,7 +4787,7 @@
         <v>7</v>
       </c>
       <c r="P15" s="123" t="s">
-        <v>147</v>
+        <v>38</v>
       </c>
       <c r="Q15" s="153">
         <f>Schedule!D21</f>
@@ -4806,7 +4809,7 @@
         <v>8</v>
       </c>
       <c r="P16" s="123" t="s">
-        <v>148</v>
+        <v>39</v>
       </c>
       <c r="Q16" s="153">
         <f>Schedule!D22</f>
@@ -4815,10 +4818,10 @@
     </row>
     <row r="17" spans="2:17" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B17" s="145" t="s">
-        <v>157</v>
+        <v>44</v>
       </c>
       <c r="C17" s="130" t="s">
-        <v>234</v>
+        <v>12</v>
       </c>
       <c r="D17" s="129">
         <f>_xlfn.XLOOKUP(B17,$P$9:$P$23,$Q$9:$Q$23)</f>
@@ -4826,14 +4829,14 @@
       </c>
       <c r="E17" s="129"/>
       <c r="F17" s="129" t="s">
-        <v>235</v>
+        <v>13</v>
       </c>
       <c r="G17" s="173" t="s">
-        <v>182</v>
+        <v>14</v>
       </c>
       <c r="H17" s="129"/>
       <c r="I17" s="129" t="s">
-        <v>236</v>
+        <v>15</v>
       </c>
       <c r="J17" s="129" t="str">
         <f>J8</f>
@@ -4845,7 +4848,7 @@
         <v>9</v>
       </c>
       <c r="P17" s="123" t="s">
-        <v>149</v>
+        <v>40</v>
       </c>
       <c r="Q17" s="153">
         <f>Schedule!D23</f>
@@ -4854,7 +4857,7 @@
     </row>
     <row r="18" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B18" s="131" t="s">
-        <v>238</v>
+        <v>22</v>
       </c>
       <c r="C18" s="132">
         <v>1</v>
@@ -4889,7 +4892,7 @@
         <v>10</v>
       </c>
       <c r="P18" s="123" t="s">
-        <v>151</v>
+        <v>41</v>
       </c>
       <c r="Q18" s="153">
         <f>Schedule!D24</f>
@@ -4898,7 +4901,7 @@
     </row>
     <row r="19" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B19" s="135" t="s">
-        <v>239</v>
+        <v>23</v>
       </c>
       <c r="C19" s="129">
         <f t="array" ref="C19">IF($B$2="Skybrook",
@@ -4924,7 +4927,7 @@
       $J17="Front 9",INDEX($AO$12:$AW$12,1,D18)
    )
 )</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E19" s="137">
         <f t="array" ref="E19">IF($B$2="Skybrook",
@@ -4937,7 +4940,7 @@
       $J17="Front 9",INDEX($AO$12:$AW$12,1,E18)
    )
 )</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F19" s="136">
         <f t="array" ref="F19">IF($B$2="Skybrook",
@@ -4950,7 +4953,7 @@
       $J17="Front 9",INDEX($AO$12:$AW$12,1,F18)
    )
 )</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G19" s="129">
         <f t="array" ref="G19">IF($B$2="Skybrook",
@@ -4976,7 +4979,7 @@
       $J17="Front 9",INDEX($AO$12:$AW$12,1,H18)
    )
 )</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I19" s="136">
         <f t="array" ref="I19">IF($B$2="Skybrook",
@@ -4989,7 +4992,7 @@
       $J17="Front 9",INDEX($AO$12:$AW$12,1,I18)
    )
 )</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J19" s="129">
         <f t="array" ref="J19">IF($B$2="Skybrook",
@@ -5002,7 +5005,7 @@
       $J17="Front 9",INDEX($AO$12:$AW$12,1,J18)
    )
 )</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K19" s="137">
         <f t="array" ref="K19">IF($B$2="Skybrook",
@@ -5026,7 +5029,7 @@
         <v>11</v>
       </c>
       <c r="P19" s="123" t="s">
-        <v>152</v>
+        <v>42</v>
       </c>
       <c r="Q19" s="153">
         <f>Schedule!D25</f>
@@ -5035,7 +5038,7 @@
     </row>
     <row r="20" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B20" s="135" t="s">
-        <v>230</v>
+        <v>27</v>
       </c>
       <c r="C20" s="129">
         <f t="array" ref="C20">IF($B$2="Skybrook",
@@ -5061,7 +5064,7 @@
       $J17="Front 9",VLOOKUP($G17,$AN$9:$AW$11,COLUMN()-1,0)
    )
 )</f>
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E20" s="137">
         <f t="array" ref="E20">IF($B$2="Skybrook",
@@ -5074,7 +5077,7 @@
       $J17="Front 9",VLOOKUP($G17,$AN$9:$AW$11,COLUMN()-1,0)
    )
 )</f>
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="F20" s="136">
         <f t="array" ref="F20">IF($B$2="Skybrook",
@@ -5087,7 +5090,7 @@
       $J17="Front 9",VLOOKUP($G17,$AN$9:$AW$11,COLUMN()-1,0)
    )
 )</f>
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="G20" s="129">
         <f t="array" ref="G20">IF($B$2="Skybrook",
@@ -5100,7 +5103,7 @@
       $J17="Front 9",VLOOKUP($G17,$AN$9:$AW$11,COLUMN()-1,0)
    )
 )</f>
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="H20" s="137">
         <f t="array" ref="H20">IF($B$2="Skybrook",
@@ -5113,7 +5116,7 @@
       $J17="Front 9",VLOOKUP($G17,$AN$9:$AW$11,COLUMN()-1,0)
    )
 )</f>
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="I20" s="136">
         <f t="array" ref="I20">IF($B$2="Skybrook",
@@ -5126,7 +5129,7 @@
       $J17="Front 9",VLOOKUP($G17,$AN$9:$AW$11,COLUMN()-1,0)
    )
 )</f>
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="J20" s="129">
         <f t="array" ref="J20">IF($B$2="Skybrook",
@@ -5139,7 +5142,7 @@
       $J17="Front 9",VLOOKUP($G17,$AN$9:$AW$11,COLUMN()-1,0)
    )
 )</f>
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="K20" s="137">
         <f t="array" ref="K20">IF($B$2="Skybrook",
@@ -5152,14 +5155,14 @@
       $J17="Front 9",VLOOKUP($G17,$AN$9:$AW$11,COLUMN()-1,0)
    )
 )</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L20" s="129"/>
       <c r="O20" s="122">
         <v>12</v>
       </c>
       <c r="P20" s="123" t="s">
-        <v>153</v>
+        <v>43</v>
       </c>
       <c r="Q20" s="153">
         <f>Schedule!D26</f>
@@ -5168,48 +5171,48 @@
     </row>
     <row r="21" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B21" s="138" t="s">
-        <v>242</v>
+        <v>30</v>
       </c>
       <c r="C21" s="146">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D21" s="147">
         <v>6</v>
       </c>
       <c r="E21" s="148">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F21" s="146">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G21" s="147">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H21" s="148">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="I21" s="146">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J21" s="147">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="K21" s="148">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="L21" s="129">
         <f>SUM(C21:K21)</f>
-        <v>41</v>
+        <v>72</v>
       </c>
       <c r="M21" s="139">
         <f>SUM(C21:K21)-SUM(C$10:K$10)</f>
-        <v>5</v>
+        <v>36</v>
       </c>
       <c r="O21" s="122">
         <v>13</v>
       </c>
       <c r="P21" s="123" t="s">
-        <v>154</v>
+        <v>44</v>
       </c>
       <c r="Q21" s="153">
         <f>Schedule!D27</f>
@@ -5218,7 +5221,7 @@
     </row>
     <row r="22" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B22" s="135" t="s">
-        <v>243</v>
+        <v>33</v>
       </c>
       <c r="C22" s="136">
         <f t="shared" ref="C22:K22" si="3">INT($D$17/18)+IF(C20&lt;=MOD($D$17,18),1,0)</f>
@@ -5261,7 +5264,7 @@
         <v>14</v>
       </c>
       <c r="P22" s="123" t="s">
-        <v>155</v>
+        <v>45</v>
       </c>
       <c r="Q22" s="153">
         <f>Schedule!D28</f>
@@ -5270,11 +5273,11 @@
     </row>
     <row r="23" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B23" s="135" t="s">
-        <v>244</v>
+        <v>35</v>
       </c>
       <c r="C23" s="136">
         <f t="shared" ref="C23:K23" si="4">C21-C22</f>
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D23" s="129">
         <f t="shared" si="4"/>
@@ -5282,45 +5285,45 @@
       </c>
       <c r="E23" s="137">
         <f t="shared" si="4"/>
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F23" s="136">
         <f t="shared" si="4"/>
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="G23" s="129">
         <f t="shared" si="4"/>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H23" s="137">
         <f t="shared" si="4"/>
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I23" s="136">
         <f t="shared" si="4"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J23" s="129">
         <f t="shared" si="4"/>
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="K23" s="137">
         <f t="shared" si="4"/>
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="L23" s="155">
         <f>SUM(C23:K23)</f>
-        <v>23</v>
+        <v>54</v>
       </c>
       <c r="M23" s="139">
         <f>SUM(C23:K23)-SUM(C$10:K$10)</f>
-        <v>-13</v>
+        <v>18</v>
       </c>
       <c r="O23" s="122">
         <v>15</v>
       </c>
       <c r="P23" s="123" t="s">
-        <v>157</v>
+        <v>46</v>
       </c>
       <c r="Q23" s="153">
         <f>Schedule!D29</f>
@@ -5329,7 +5332,7 @@
     </row>
     <row r="24" spans="2:17" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B24" s="140" t="s">
-        <v>245</v>
+        <v>37</v>
       </c>
       <c r="C24" s="124">
         <f t="shared" ref="C24:K24" si="5">IF(C23&lt;C14,1,0)</f>
@@ -5345,7 +5348,7 @@
       </c>
       <c r="F24" s="124">
         <f t="shared" si="5"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G24" s="141">
         <f t="shared" si="5"/>
@@ -5353,11 +5356,11 @@
       </c>
       <c r="H24" s="142">
         <f t="shared" si="5"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I24" s="124">
         <f t="shared" si="5"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J24" s="141">
         <f t="shared" si="5"/>
@@ -5371,19 +5374,19 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="AD8:AM8"/>
     <mergeCell ref="AX8:BG8"/>
     <mergeCell ref="AN7:BG7"/>
     <mergeCell ref="L3:M5"/>
     <mergeCell ref="U8:AC8"/>
     <mergeCell ref="L2:M2"/>
     <mergeCell ref="AO8:AW8"/>
+    <mergeCell ref="J3:K5"/>
+    <mergeCell ref="J2:K2"/>
     <mergeCell ref="B3:B4"/>
     <mergeCell ref="T7:AM7"/>
     <mergeCell ref="B5:B6"/>
-    <mergeCell ref="J1:M1"/>
-    <mergeCell ref="AD8:AM8"/>
-    <mergeCell ref="J3:K5"/>
-    <mergeCell ref="J2:K2"/>
   </mergeCells>
   <conditionalFormatting sqref="C15:K15 C24:K24">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="greaterThan">
@@ -5419,34 +5422,34 @@
   <sheetData>
     <row r="2" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C2" t="s">
-        <v>249</v>
+        <v>2</v>
       </c>
       <c r="D2" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
     </row>
     <row r="3" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C3" t="s">
-        <v>182</v>
+        <v>14</v>
       </c>
       <c r="D3" t="s">
-        <v>182</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C4" t="s">
-        <v>252</v>
+        <v>25</v>
       </c>
       <c r="D4" t="s">
-        <v>185</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C5" t="s">
-        <v>253</v>
+        <v>29</v>
       </c>
       <c r="D5" t="s">
-        <v>253</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -5477,7 +5480,7 @@
   <sheetData>
     <row r="1" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="193" t="s">
-        <v>31</v>
+        <v>76</v>
       </c>
       <c r="B1" s="194"/>
       <c r="C1" s="194"/>
@@ -5494,7 +5497,7 @@
     </row>
     <row r="2" spans="1:13" s="12" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="10" t="s">
-        <v>32</v>
+        <v>77</v>
       </c>
       <c r="B2" s="11">
         <v>45551</v>
@@ -5573,10 +5576,10 @@
       </c>
       <c r="B5" s="9"/>
       <c r="C5" s="9" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="E5" s="9"/>
       <c r="F5" s="9"/>
@@ -5600,7 +5603,7 @@
       <c r="G6" s="9"/>
       <c r="H6" s="9"/>
       <c r="I6" s="9" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="J6" s="9"/>
       <c r="K6" s="9"/>
@@ -5791,7 +5794,7 @@
   <sheetData>
     <row r="1" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="193" t="s">
-        <v>31</v>
+        <v>76</v>
       </c>
       <c r="B1" s="194"/>
       <c r="C1" s="194"/>
@@ -5808,7 +5811,7 @@
     </row>
     <row r="2" spans="1:13" s="12" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="10" t="s">
-        <v>32</v>
+        <v>77</v>
       </c>
       <c r="B2" s="11">
         <v>45565</v>
@@ -5862,7 +5865,7 @@
       <c r="J3" s="9"/>
       <c r="K3" s="9"/>
       <c r="L3" s="9" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="M3" s="9"/>
     </row>
@@ -6118,7 +6121,7 @@
   <sheetData>
     <row r="1" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="193" t="s">
-        <v>31</v>
+        <v>76</v>
       </c>
       <c r="B1" s="194"/>
       <c r="C1" s="194"/>
@@ -6135,7 +6138,7 @@
     </row>
     <row r="2" spans="1:13" s="12" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="10" t="s">
-        <v>32</v>
+        <v>77</v>
       </c>
       <c r="B2" s="11">
         <v>45579</v>
@@ -6180,10 +6183,10 @@
       </c>
       <c r="B3" s="30"/>
       <c r="C3" s="30" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="E3" s="30"/>
       <c r="F3" s="30"/>
@@ -6192,7 +6195,7 @@
       <c r="I3" s="30"/>
       <c r="J3" s="30"/>
       <c r="K3" s="30" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="L3" s="30"/>
       <c r="M3" s="30"/>
@@ -6449,7 +6452,7 @@
   <sheetData>
     <row r="1" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="193" t="s">
-        <v>31</v>
+        <v>76</v>
       </c>
       <c r="B1" s="194"/>
       <c r="C1" s="194"/>
@@ -6466,7 +6469,7 @@
     </row>
     <row r="2" spans="1:13" s="12" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="10" t="s">
-        <v>32</v>
+        <v>77</v>
       </c>
       <c r="B2" s="11">
         <v>45537</v>
@@ -6512,7 +6515,7 @@
       <c r="B3" s="9"/>
       <c r="C3" s="9"/>
       <c r="D3" s="9" t="s">
-        <v>33</v>
+        <v>78</v>
       </c>
       <c r="E3" s="9"/>
       <c r="F3" s="9"/>
@@ -6548,7 +6551,7 @@
       <c r="B5" s="9"/>
       <c r="C5" s="9"/>
       <c r="D5" s="9" t="s">
-        <v>34</v>
+        <v>79</v>
       </c>
       <c r="E5" s="9"/>
       <c r="F5" s="9"/>
@@ -6572,7 +6575,7 @@
       <c r="G6" s="9"/>
       <c r="H6" s="9"/>
       <c r="I6" s="9" t="s">
-        <v>35</v>
+        <v>80</v>
       </c>
       <c r="J6" s="9"/>
       <c r="K6" s="9"/>
@@ -6587,7 +6590,7 @@
       <c r="C7" s="9"/>
       <c r="D7" s="9"/>
       <c r="E7" s="9" t="s">
-        <v>36</v>
+        <v>81</v>
       </c>
       <c r="F7" s="9"/>
       <c r="G7" s="9"/>
@@ -6765,7 +6768,7 @@
   <sheetData>
     <row r="1" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="193" t="s">
-        <v>31</v>
+        <v>76</v>
       </c>
       <c r="B1" s="194"/>
       <c r="C1" s="194"/>
@@ -6782,7 +6785,7 @@
     </row>
     <row r="2" spans="1:13" s="12" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="10" t="s">
-        <v>32</v>
+        <v>77</v>
       </c>
       <c r="B2" s="11">
         <v>45495</v>
@@ -6834,7 +6837,7 @@
       <c r="H3" s="9"/>
       <c r="I3" s="9"/>
       <c r="J3" s="9" t="s">
-        <v>37</v>
+        <v>82</v>
       </c>
       <c r="K3" s="9"/>
       <c r="L3" s="9"/>
@@ -6881,7 +6884,7 @@
       <c r="B6" s="9"/>
       <c r="C6" s="9"/>
       <c r="D6" s="9" t="s">
-        <v>38</v>
+        <v>83</v>
       </c>
       <c r="E6" s="9"/>
       <c r="F6" s="9"/>
@@ -6890,7 +6893,7 @@
       <c r="I6" s="9"/>
       <c r="J6" s="9"/>
       <c r="K6" s="9" t="s">
-        <v>39</v>
+        <v>84</v>
       </c>
       <c r="L6" s="9"/>
       <c r="M6" s="9"/>
@@ -6901,11 +6904,11 @@
       </c>
       <c r="B7" s="9"/>
       <c r="C7" s="9" t="s">
-        <v>40</v>
+        <v>85</v>
       </c>
       <c r="D7" s="9"/>
       <c r="E7" s="9" t="s">
-        <v>41</v>
+        <v>86</v>
       </c>
       <c r="F7" s="9"/>
       <c r="G7" s="9"/>
@@ -7073,7 +7076,7 @@
   <sheetData>
     <row r="1" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="193" t="s">
-        <v>31</v>
+        <v>76</v>
       </c>
       <c r="B1" s="194"/>
       <c r="C1" s="194"/>
@@ -7090,7 +7093,7 @@
     </row>
     <row r="2" spans="1:13" s="12" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="10" t="s">
-        <v>32</v>
+        <v>77</v>
       </c>
       <c r="B2" s="11">
         <v>45509</v>
@@ -7143,7 +7146,7 @@
       <c r="I3" s="9"/>
       <c r="J3" s="9"/>
       <c r="K3" s="9" t="s">
-        <v>42</v>
+        <v>87</v>
       </c>
       <c r="L3" s="9"/>
       <c r="M3" s="9"/>
@@ -7178,7 +7181,7 @@
       <c r="H5" s="9"/>
       <c r="I5" s="9"/>
       <c r="J5" s="9" t="s">
-        <v>43</v>
+        <v>88</v>
       </c>
       <c r="K5" s="9"/>
       <c r="L5" s="9"/>
@@ -7197,7 +7200,7 @@
       <c r="H6" s="9"/>
       <c r="I6" s="9"/>
       <c r="J6" s="9" t="s">
-        <v>44</v>
+        <v>89</v>
       </c>
       <c r="K6" s="9"/>
       <c r="L6" s="9"/>
@@ -7209,7 +7212,7 @@
       </c>
       <c r="B7" s="9"/>
       <c r="C7" s="9" t="s">
-        <v>45</v>
+        <v>90</v>
       </c>
       <c r="D7" s="9"/>
       <c r="E7" s="9"/>
@@ -7218,7 +7221,7 @@
       <c r="H7" s="9"/>
       <c r="I7" s="9"/>
       <c r="J7" s="9" t="s">
-        <v>46</v>
+        <v>91</v>
       </c>
       <c r="K7" s="9"/>
       <c r="L7" s="9"/>
@@ -7391,7 +7394,7 @@
   <sheetData>
     <row r="1" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="193" t="s">
-        <v>31</v>
+        <v>76</v>
       </c>
       <c r="B1" s="194"/>
       <c r="C1" s="194"/>
@@ -7408,7 +7411,7 @@
     </row>
     <row r="2" spans="1:13" s="12" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="10" t="s">
-        <v>32</v>
+        <v>77</v>
       </c>
       <c r="B2" s="11">
         <v>45523</v>
@@ -7503,14 +7506,14 @@
         <v>0.6875</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>47</v>
+        <v>92</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>48</v>
+        <v>93</v>
       </c>
       <c r="D6" s="9"/>
       <c r="E6" s="9" t="s">
-        <v>49</v>
+        <v>94</v>
       </c>
       <c r="F6" s="9"/>
       <c r="G6" s="9"/>
@@ -7527,7 +7530,7 @@
       <c r="B7" s="9"/>
       <c r="C7" s="9"/>
       <c r="D7" s="9" t="s">
-        <v>50</v>
+        <v>95</v>
       </c>
       <c r="E7" s="9"/>
       <c r="F7" s="9"/>
@@ -7536,7 +7539,7 @@
       <c r="I7" s="9"/>
       <c r="J7" s="9"/>
       <c r="K7" s="9" t="s">
-        <v>51</v>
+        <v>96</v>
       </c>
       <c r="L7" s="9"/>
       <c r="M7" s="9"/>
@@ -7704,7 +7707,7 @@
   <sheetData>
     <row r="1" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B1" s="195" t="s">
-        <v>52</v>
+        <v>97</v>
       </c>
       <c r="C1" s="194"/>
       <c r="D1" s="194"/>
@@ -7717,274 +7720,274 @@
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B2" s="6" t="s">
-        <v>53</v>
+        <v>98</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>54</v>
+        <v>99</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>55</v>
+        <v>100</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>56</v>
+        <v>101</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>57</v>
+        <v>102</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>58</v>
+        <v>103</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>59</v>
+        <v>104</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>60</v>
+        <v>105</v>
       </c>
       <c r="J2" s="6" t="s">
-        <v>61</v>
+        <v>106</v>
       </c>
       <c r="K2" s="176"/>
       <c r="L2" s="177"/>
       <c r="M2" s="150" t="s">
-        <v>62</v>
+        <v>107</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A3" s="103" t="s">
-        <v>63</v>
+        <v>108</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>64</v>
+        <v>109</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>65</v>
+        <v>110</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>66</v>
+        <v>111</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>67</v>
+        <v>112</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>68</v>
+        <v>113</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>69</v>
+        <v>114</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>70</v>
+        <v>115</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>71</v>
+        <v>116</v>
       </c>
       <c r="J3" s="6" t="s">
-        <v>72</v>
+        <v>117</v>
       </c>
       <c r="L3" s="156"/>
       <c r="M3" s="150" t="s">
-        <v>73</v>
+        <v>118</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B4" s="175" t="s">
-        <v>74</v>
+        <v>119</v>
       </c>
       <c r="C4" s="175" t="s">
-        <v>75</v>
+        <v>120</v>
       </c>
       <c r="D4" s="175" t="s">
-        <v>76</v>
+        <v>121</v>
       </c>
       <c r="E4" s="175" t="s">
-        <v>77</v>
+        <v>122</v>
       </c>
       <c r="F4" s="175" t="s">
-        <v>78</v>
+        <v>123</v>
       </c>
       <c r="G4" s="175" t="s">
-        <v>79</v>
+        <v>124</v>
       </c>
       <c r="H4" s="175" t="s">
-        <v>80</v>
+        <v>125</v>
       </c>
       <c r="I4" s="175" t="s">
-        <v>81</v>
+        <v>126</v>
       </c>
       <c r="J4" s="175" t="s">
-        <v>82</v>
+        <v>127</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B5" s="1" t="s">
-        <v>83</v>
+        <v>128</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>41</v>
+        <v>86</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>84</v>
+        <v>129</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>85</v>
+        <v>130</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>86</v>
+        <v>131</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>87</v>
+        <v>132</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>88</v>
+        <v>133</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>89</v>
+        <v>134</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>90</v>
+        <v>135</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
-        <v>91</v>
+        <v>136</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>92</v>
+        <v>137</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>93</v>
+        <v>138</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>94</v>
+        <v>139</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>95</v>
+        <v>140</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>96</v>
+        <v>141</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>97</v>
+        <v>142</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>98</v>
+        <v>143</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>99</v>
+        <v>144</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B7" s="1" t="s">
-        <v>100</v>
+        <v>145</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>101</v>
+        <v>146</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>102</v>
+        <v>147</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>103</v>
+        <v>148</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>42</v>
+        <v>87</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>104</v>
+        <v>149</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>105</v>
+        <v>150</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>106</v>
+        <v>151</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>107</v>
+        <v>152</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B8" s="1" t="s">
-        <v>108</v>
+        <v>153</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>109</v>
+        <v>154</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>110</v>
+        <v>155</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>111</v>
+        <v>156</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>112</v>
+        <v>157</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>113</v>
+        <v>158</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>114</v>
+        <v>159</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>115</v>
+        <v>160</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>116</v>
+        <v>161</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B9" s="1" t="s">
-        <v>117</v>
+        <v>162</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>118</v>
+        <v>163</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>119</v>
+        <v>164</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>120</v>
+        <v>165</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>121</v>
+        <v>166</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>39</v>
+        <v>84</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>122</v>
+        <v>167</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>123</v>
+        <v>168</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>124</v>
+        <v>169</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B10" s="1" t="s">
-        <v>125</v>
+        <v>170</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>126</v>
+        <v>171</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>127</v>
+        <v>172</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>128</v>
+        <v>173</v>
       </c>
       <c r="F10" s="1"/>
       <c r="G10" s="3"/>
       <c r="H10" s="1"/>
       <c r="I10" s="3" t="s">
-        <v>129</v>
+        <v>174</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>130</v>
+        <v>175</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A11" s="103" t="s">
-        <v>131</v>
+        <v>176</v>
       </c>
       <c r="B11" s="3">
         <v>11</v>
@@ -7999,13 +8002,13 @@
         <v>12</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>132</v>
+        <v>177</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>133</v>
+        <v>178</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>134</v>
+        <v>179</v>
       </c>
       <c r="I11" s="3">
         <v>13</v>
@@ -8020,19 +8023,19 @@
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B14" s="2" t="s">
-        <v>135</v>
+        <v>17</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>136</v>
+        <v>180</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>137</v>
+        <v>181</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>138</v>
+        <v>182</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>139</v>
+        <v>183</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.2">
@@ -8040,13 +8043,13 @@
         <v>1</v>
       </c>
       <c r="C15" s="53" t="s">
-        <v>140</v>
+        <v>11</v>
       </c>
       <c r="D15" s="73">
         <v>12</v>
       </c>
       <c r="E15" s="106" t="s">
-        <v>141</v>
+        <v>184</v>
       </c>
       <c r="F15" s="3"/>
     </row>
@@ -8055,16 +8058,16 @@
         <v>2</v>
       </c>
       <c r="C16" s="104" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D16" s="105">
         <v>12</v>
       </c>
       <c r="E16" s="106" t="s">
-        <v>141</v>
+        <v>184</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>150</v>
+        <v>185</v>
       </c>
     </row>
     <row r="17" spans="2:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -8073,13 +8076,13 @@
         <v>3</v>
       </c>
       <c r="C17" s="53" t="s">
-        <v>142</v>
+        <v>28</v>
       </c>
       <c r="D17" s="105">
         <v>15</v>
       </c>
       <c r="E17" s="106" t="s">
-        <v>141</v>
+        <v>184</v>
       </c>
       <c r="F17" s="3"/>
     </row>
@@ -8089,16 +8092,16 @@
         <v>4</v>
       </c>
       <c r="C18" s="53" t="s">
-        <v>143</v>
+        <v>31</v>
       </c>
       <c r="D18" s="105">
         <v>20</v>
       </c>
       <c r="E18" s="106" t="s">
-        <v>141</v>
+        <v>184</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>144</v>
+        <v>186</v>
       </c>
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.2">
@@ -8107,13 +8110,13 @@
         <v>5</v>
       </c>
       <c r="C19" s="107" t="s">
-        <v>145</v>
+        <v>34</v>
       </c>
       <c r="D19" s="108">
         <v>22</v>
       </c>
       <c r="E19" s="106" t="s">
-        <v>141</v>
+        <v>184</v>
       </c>
       <c r="F19" s="3"/>
     </row>
@@ -8123,16 +8126,16 @@
         <v>6</v>
       </c>
       <c r="C20" s="53" t="s">
-        <v>146</v>
+        <v>36</v>
       </c>
       <c r="D20" s="105">
         <v>24</v>
       </c>
       <c r="E20" s="106" t="s">
-        <v>141</v>
+        <v>184</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>144</v>
+        <v>186</v>
       </c>
       <c r="G20" s="4"/>
     </row>
@@ -8142,16 +8145,16 @@
         <v>7</v>
       </c>
       <c r="C21" s="53" t="s">
-        <v>147</v>
+        <v>38</v>
       </c>
       <c r="D21" s="105">
         <v>27</v>
       </c>
       <c r="E21" s="106" t="s">
-        <v>141</v>
+        <v>184</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>144</v>
+        <v>186</v>
       </c>
     </row>
     <row r="22" spans="2:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -8160,16 +8163,16 @@
         <v>8</v>
       </c>
       <c r="C22" s="53" t="s">
-        <v>148</v>
+        <v>39</v>
       </c>
       <c r="D22" s="105">
         <v>28</v>
       </c>
       <c r="E22" s="106" t="s">
-        <v>141</v>
+        <v>184</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>150</v>
+        <v>185</v>
       </c>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.2">
@@ -8178,16 +8181,16 @@
         <v>9</v>
       </c>
       <c r="C23" s="53" t="s">
-        <v>149</v>
+        <v>40</v>
       </c>
       <c r="D23" s="73">
         <v>30</v>
       </c>
       <c r="E23" s="106" t="s">
-        <v>141</v>
+        <v>184</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>150</v>
+        <v>185</v>
       </c>
     </row>
     <row r="24" spans="2:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -8196,13 +8199,13 @@
         <v>10</v>
       </c>
       <c r="C24" s="53" t="s">
-        <v>151</v>
+        <v>41</v>
       </c>
       <c r="D24" s="105">
         <v>36</v>
       </c>
       <c r="E24" s="106" t="s">
-        <v>141</v>
+        <v>184</v>
       </c>
       <c r="F24" s="3"/>
       <c r="G24" s="4"/>
@@ -8213,16 +8216,16 @@
         <v>11</v>
       </c>
       <c r="C25" s="107" t="s">
-        <v>152</v>
+        <v>42</v>
       </c>
       <c r="D25" s="108">
         <v>36</v>
       </c>
       <c r="E25" s="106" t="s">
-        <v>141</v>
+        <v>184</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>144</v>
+        <v>186</v>
       </c>
     </row>
     <row r="26" spans="2:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -8231,16 +8234,16 @@
         <v>12</v>
       </c>
       <c r="C26" s="53" t="s">
-        <v>153</v>
+        <v>43</v>
       </c>
       <c r="D26" s="105">
         <v>36</v>
       </c>
       <c r="E26" s="106" t="s">
-        <v>141</v>
+        <v>184</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>144</v>
+        <v>186</v>
       </c>
     </row>
     <row r="27" spans="2:7" x14ac:dyDescent="0.2">
@@ -8249,16 +8252,16 @@
         <v>13</v>
       </c>
       <c r="C27" s="53" t="s">
-        <v>154</v>
+        <v>44</v>
       </c>
       <c r="D27" s="73">
         <v>36</v>
       </c>
       <c r="E27" s="106" t="s">
-        <v>141</v>
+        <v>184</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>144</v>
+        <v>186</v>
       </c>
     </row>
     <row r="28" spans="2:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -8267,16 +8270,16 @@
         <v>14</v>
       </c>
       <c r="C28" s="53" t="s">
-        <v>155</v>
+        <v>45</v>
       </c>
       <c r="D28" s="105">
         <v>36</v>
       </c>
       <c r="E28" s="106" t="s">
-        <v>156</v>
+        <v>187</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>144</v>
+        <v>186</v>
       </c>
     </row>
     <row r="29" spans="2:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -8285,13 +8288,13 @@
         <v>15</v>
       </c>
       <c r="C29" s="53" t="s">
-        <v>157</v>
+        <v>46</v>
       </c>
       <c r="D29" s="105">
         <v>36</v>
       </c>
       <c r="E29" s="106" t="s">
-        <v>141</v>
+        <v>184</v>
       </c>
       <c r="F29" s="3"/>
     </row>
@@ -8340,8 +8343,8 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:35" x14ac:dyDescent="0.2">
-      <c r="P1" s="208" t="s">
-        <v>158</v>
+      <c r="P1" s="209" t="s">
+        <v>188</v>
       </c>
       <c r="Q1" s="197"/>
       <c r="R1" s="197"/>
@@ -8353,168 +8356,168 @@
     </row>
     <row r="2" spans="2:35" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="P2" s="46" t="s">
-        <v>53</v>
+        <v>98</v>
       </c>
       <c r="Q2" s="46" t="s">
-        <v>54</v>
+        <v>99</v>
       </c>
       <c r="R2" s="46" t="s">
-        <v>55</v>
+        <v>100</v>
       </c>
       <c r="S2" s="46" t="s">
-        <v>56</v>
+        <v>101</v>
       </c>
       <c r="T2" s="46" t="s">
-        <v>57</v>
+        <v>102</v>
       </c>
       <c r="U2" s="46" t="s">
-        <v>58</v>
+        <v>103</v>
       </c>
       <c r="V2" s="46" t="s">
-        <v>59</v>
+        <v>104</v>
       </c>
       <c r="W2" s="46" t="s">
-        <v>60</v>
+        <v>105</v>
       </c>
       <c r="X2" s="46" t="s">
-        <v>61</v>
+        <v>106</v>
       </c>
       <c r="Y2" s="46" t="s">
-        <v>159</v>
+        <v>189</v>
       </c>
       <c r="Z2" s="46" t="s">
-        <v>160</v>
+        <v>190</v>
       </c>
       <c r="AA2" s="46" t="s">
-        <v>161</v>
+        <v>191</v>
       </c>
       <c r="AB2" s="46" t="s">
-        <v>162</v>
+        <v>192</v>
       </c>
       <c r="AC2" s="46" t="s">
-        <v>163</v>
+        <v>193</v>
       </c>
       <c r="AD2" s="46" t="s">
-        <v>164</v>
+        <v>194</v>
       </c>
       <c r="AE2" s="46" t="s">
-        <v>165</v>
+        <v>195</v>
       </c>
       <c r="AF2" s="46" t="s">
-        <v>166</v>
+        <v>196</v>
       </c>
       <c r="AG2" s="46" t="s">
-        <v>167</v>
+        <v>197</v>
       </c>
       <c r="AH2" s="46" t="s">
-        <v>168</v>
+        <v>198</v>
       </c>
       <c r="AI2" s="46" t="s">
-        <v>169</v>
+        <v>199</v>
       </c>
     </row>
     <row r="3" spans="2:35" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B3" s="2" t="s">
-        <v>141</v>
+        <v>184</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>170</v>
+        <v>200</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>171</v>
+        <v>201</v>
       </c>
       <c r="F3" s="79" t="s">
-        <v>1</v>
-      </c>
-      <c r="G3" s="209" t="s">
-        <v>138</v>
-      </c>
-      <c r="H3" s="210"/>
+        <v>18</v>
+      </c>
+      <c r="G3" s="210" t="s">
+        <v>182</v>
+      </c>
+      <c r="H3" s="211"/>
       <c r="I3" s="80" t="s">
-        <v>172</v>
+        <v>202</v>
       </c>
       <c r="J3" s="80" t="s">
-        <v>173</v>
+        <v>203</v>
       </c>
       <c r="K3" s="80" t="s">
-        <v>174</v>
+        <v>204</v>
       </c>
       <c r="L3" s="80" t="s">
-        <v>175</v>
+        <v>205</v>
       </c>
       <c r="M3" s="80" t="s">
-        <v>176</v>
+        <v>206</v>
       </c>
       <c r="N3" s="99" t="s">
-        <v>177</v>
+        <v>207</v>
       </c>
       <c r="O3" s="81" t="s">
-        <v>178</v>
+        <v>208</v>
       </c>
       <c r="P3" s="94" t="s">
-        <v>179</v>
+        <v>209</v>
       </c>
       <c r="Q3" s="94" t="s">
-        <v>179</v>
+        <v>209</v>
       </c>
       <c r="R3" s="94" t="s">
-        <v>179</v>
+        <v>209</v>
       </c>
       <c r="S3" s="94" t="s">
-        <v>179</v>
+        <v>209</v>
       </c>
       <c r="T3" s="94" t="s">
-        <v>179</v>
+        <v>209</v>
       </c>
       <c r="U3" s="94" t="s">
-        <v>179</v>
+        <v>209</v>
       </c>
       <c r="V3" s="94" t="s">
-        <v>179</v>
+        <v>209</v>
       </c>
       <c r="W3" s="94" t="s">
-        <v>179</v>
+        <v>209</v>
       </c>
       <c r="X3" s="94" t="s">
-        <v>179</v>
+        <v>209</v>
       </c>
       <c r="Y3" s="94" t="s">
-        <v>179</v>
+        <v>209</v>
       </c>
       <c r="Z3" s="94" t="s">
-        <v>179</v>
+        <v>209</v>
       </c>
       <c r="AA3" s="94" t="s">
-        <v>179</v>
+        <v>209</v>
       </c>
       <c r="AB3" s="94" t="s">
-        <v>179</v>
+        <v>209</v>
       </c>
       <c r="AC3" s="94" t="s">
-        <v>179</v>
+        <v>209</v>
       </c>
       <c r="AD3" s="94" t="s">
-        <v>179</v>
+        <v>209</v>
       </c>
       <c r="AE3" s="94" t="s">
-        <v>179</v>
+        <v>209</v>
       </c>
       <c r="AF3" s="94" t="s">
-        <v>179</v>
+        <v>209</v>
       </c>
       <c r="AG3" s="94" t="s">
-        <v>179</v>
+        <v>209</v>
       </c>
       <c r="AH3" s="94" t="s">
-        <v>179</v>
+        <v>209</v>
       </c>
       <c r="AI3" s="94" t="s">
-        <v>179</v>
+        <v>209</v>
       </c>
     </row>
     <row r="4" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B4" s="42" t="s">
-        <v>180</v>
+        <v>210</v>
       </c>
       <c r="C4" s="43">
         <v>70.099999999999994</v>
@@ -8522,21 +8525,21 @@
       <c r="D4" s="43">
         <v>130</v>
       </c>
-      <c r="F4" s="204" t="s">
-        <v>181</v>
-      </c>
-      <c r="G4" s="211" t="str">
+      <c r="F4" s="205" t="s">
+        <v>211</v>
+      </c>
+      <c r="G4" s="198" t="str">
         <f>VLOOKUP($F4,Schedule!$C$15:$E$29,3)</f>
         <v>Mens</v>
       </c>
-      <c r="H4" s="211" t="e">
+      <c r="H4" s="198" t="e">
         <f>VLOOKUP($F4,Schedule!$C$15:$E$29,4)</f>
         <v>#REF!</v>
       </c>
-      <c r="I4" s="207">
+      <c r="I4" s="208">
         <v>13</v>
       </c>
-      <c r="J4" s="211">
+      <c r="J4" s="198">
         <f>I4+36</f>
         <v>49</v>
       </c>
@@ -8555,7 +8558,7 @@
         <f t="array" ref="N4">ROUNDUP(_xlfn.IFS($G4="Mens",ROUNDUP(M4*(VLOOKUP($H4,$B$4:$D$7,3)/113),1),$G4="Womens",ROUNDUP(M4*(VLOOKUP($H4,$B$10:$D$12,3)/113),1)),0)</f>
         <v>#REF!</v>
       </c>
-      <c r="O4" s="198">
+      <c r="O4" s="202">
         <f>COUNT(P4:AI4)</f>
         <v>8</v>
       </c>
@@ -8598,7 +8601,7 @@
     </row>
     <row r="5" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B5" s="44" t="s">
-        <v>182</v>
+        <v>14</v>
       </c>
       <c r="C5" s="43">
         <v>68.099999999999994</v>
@@ -8606,80 +8609,80 @@
       <c r="D5" s="43">
         <v>126</v>
       </c>
-      <c r="F5" s="205"/>
-      <c r="G5" s="202"/>
-      <c r="H5" s="202"/>
-      <c r="I5" s="202"/>
-      <c r="J5" s="202"/>
-      <c r="K5" s="202"/>
-      <c r="L5" s="202"/>
-      <c r="M5" s="202"/>
-      <c r="N5" s="202"/>
-      <c r="O5" s="199"/>
+      <c r="F5" s="206"/>
+      <c r="G5" s="199"/>
+      <c r="H5" s="199"/>
+      <c r="I5" s="199"/>
+      <c r="J5" s="199"/>
+      <c r="K5" s="199"/>
+      <c r="L5" s="199"/>
+      <c r="M5" s="199"/>
+      <c r="N5" s="199"/>
+      <c r="O5" s="203"/>
       <c r="P5" s="96" t="s">
-        <v>183</v>
+        <v>212</v>
       </c>
       <c r="Q5" s="96" t="s">
-        <v>183</v>
+        <v>212</v>
       </c>
       <c r="R5" s="96" t="s">
-        <v>183</v>
+        <v>212</v>
       </c>
       <c r="S5" s="96" t="s">
-        <v>183</v>
+        <v>212</v>
       </c>
       <c r="T5" s="96" t="s">
-        <v>183</v>
+        <v>212</v>
       </c>
       <c r="U5" s="96" t="s">
-        <v>183</v>
+        <v>212</v>
       </c>
       <c r="V5" s="96" t="s">
-        <v>183</v>
+        <v>212</v>
       </c>
       <c r="W5" s="96" t="s">
-        <v>183</v>
+        <v>212</v>
       </c>
       <c r="X5" s="96" t="s">
-        <v>183</v>
+        <v>212</v>
       </c>
       <c r="Y5" s="96" t="s">
-        <v>183</v>
+        <v>212</v>
       </c>
       <c r="Z5" s="96" t="s">
-        <v>183</v>
+        <v>212</v>
       </c>
       <c r="AA5" s="96" t="s">
-        <v>183</v>
+        <v>212</v>
       </c>
       <c r="AB5" s="96" t="s">
-        <v>183</v>
+        <v>212</v>
       </c>
       <c r="AC5" s="96" t="s">
-        <v>183</v>
+        <v>212</v>
       </c>
       <c r="AD5" s="96" t="s">
-        <v>183</v>
+        <v>212</v>
       </c>
       <c r="AE5" s="96" t="s">
-        <v>183</v>
+        <v>212</v>
       </c>
       <c r="AF5" s="96" t="s">
-        <v>183</v>
+        <v>212</v>
       </c>
       <c r="AG5" s="96" t="s">
-        <v>183</v>
+        <v>212</v>
       </c>
       <c r="AH5" s="96" t="s">
-        <v>183</v>
+        <v>212</v>
       </c>
       <c r="AI5" s="96" t="s">
-        <v>183</v>
+        <v>212</v>
       </c>
     </row>
     <row r="6" spans="2:35" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B6" s="42" t="s">
-        <v>184</v>
+        <v>213</v>
       </c>
       <c r="C6" s="43">
         <v>65.5</v>
@@ -8687,16 +8690,16 @@
       <c r="D6" s="43">
         <v>120</v>
       </c>
-      <c r="F6" s="206"/>
-      <c r="G6" s="203"/>
-      <c r="H6" s="203"/>
-      <c r="I6" s="203"/>
-      <c r="J6" s="203"/>
-      <c r="K6" s="203"/>
-      <c r="L6" s="203"/>
-      <c r="M6" s="203"/>
-      <c r="N6" s="203"/>
-      <c r="O6" s="200"/>
+      <c r="F6" s="207"/>
+      <c r="G6" s="200"/>
+      <c r="H6" s="200"/>
+      <c r="I6" s="200"/>
+      <c r="J6" s="200"/>
+      <c r="K6" s="200"/>
+      <c r="L6" s="200"/>
+      <c r="M6" s="200"/>
+      <c r="N6" s="200"/>
+      <c r="O6" s="204"/>
       <c r="P6" s="97" t="e">
         <f t="array" ref="P6">IF(P4="","",_xlfn.IFS($G4="Mens",(P4-(VLOOKUP($H4,$B$4:$D$7,2)/2))/VLOOKUP($H4,$B$4:$D$7,3)*113,$G4="Womens",(P4-(VLOOKUP($H4,$B$10:$D$12,2)/2))/VLOOKUP($H4,$B$10:$D$12,3)*113))</f>
         <v>#REF!</v>
@@ -8780,7 +8783,7 @@
     </row>
     <row r="7" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B7" s="45" t="s">
-        <v>185</v>
+        <v>26</v>
       </c>
       <c r="C7" s="43">
         <v>64</v>
@@ -8797,18 +8800,18 @@
     </row>
     <row r="9" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B9" s="2" t="s">
-        <v>156</v>
+        <v>187</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>170</v>
+        <v>200</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>171</v>
+        <v>201</v>
       </c>
     </row>
     <row r="10" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B10" s="44" t="s">
-        <v>182</v>
+        <v>14</v>
       </c>
       <c r="C10" s="43">
         <v>73.400000000000006</v>
@@ -8819,7 +8822,7 @@
     </row>
     <row r="11" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B11" s="42" t="s">
-        <v>184</v>
+        <v>213</v>
       </c>
       <c r="C11" s="43">
         <v>70.2</v>
@@ -8830,7 +8833,7 @@
     </row>
     <row r="12" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B12" s="45" t="s">
-        <v>185</v>
+        <v>26</v>
       </c>
       <c r="C12" s="43">
         <v>68.3</v>
@@ -8842,13 +8845,13 @@
     <row r="14" spans="2:35" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="15" spans="2:35" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B15" s="82" t="s">
-        <v>186</v>
+        <v>214</v>
       </c>
       <c r="C15" s="83" t="s">
-        <v>187</v>
+        <v>215</v>
       </c>
       <c r="D15" s="84" t="s">
-        <v>188</v>
+        <v>216</v>
       </c>
     </row>
     <row r="16" spans="2:35" x14ac:dyDescent="0.2">
@@ -8856,7 +8859,7 @@
         <v>1</v>
       </c>
       <c r="C16" s="77" t="s">
-        <v>189</v>
+        <v>217</v>
       </c>
       <c r="D16" s="38">
         <v>-2</v>
@@ -8867,7 +8870,7 @@
         <v>2</v>
       </c>
       <c r="C17" s="77" t="s">
-        <v>189</v>
+        <v>217</v>
       </c>
       <c r="D17" s="38">
         <v>-2</v>
@@ -8878,7 +8881,7 @@
         <v>3</v>
       </c>
       <c r="C18" s="77" t="s">
-        <v>189</v>
+        <v>217</v>
       </c>
       <c r="D18" s="38">
         <v>-2</v>
@@ -8889,7 +8892,7 @@
         <v>4</v>
       </c>
       <c r="C19" s="77" t="s">
-        <v>189</v>
+        <v>217</v>
       </c>
       <c r="D19" s="38">
         <v>-1</v>
@@ -8900,7 +8903,7 @@
         <v>5</v>
       </c>
       <c r="C20" s="85" t="s">
-        <v>189</v>
+        <v>217</v>
       </c>
       <c r="D20" s="41">
         <v>0</v>
@@ -8911,7 +8914,7 @@
         <v>6</v>
       </c>
       <c r="C21" s="87" t="s">
-        <v>190</v>
+        <v>218</v>
       </c>
       <c r="D21" s="88">
         <v>-1</v>
@@ -8922,7 +8925,7 @@
         <v>7</v>
       </c>
       <c r="C22" s="77" t="s">
-        <v>190</v>
+        <v>218</v>
       </c>
       <c r="D22" s="38">
         <v>0</v>
@@ -8933,7 +8936,7 @@
         <v>8</v>
       </c>
       <c r="C23" s="85" t="s">
-        <v>190</v>
+        <v>218</v>
       </c>
       <c r="D23" s="41">
         <v>0</v>
@@ -8944,7 +8947,7 @@
         <v>9</v>
       </c>
       <c r="C24" s="87" t="s">
-        <v>191</v>
+        <v>219</v>
       </c>
       <c r="D24" s="88">
         <v>0</v>
@@ -8955,7 +8958,7 @@
         <v>10</v>
       </c>
       <c r="C25" s="77" t="s">
-        <v>191</v>
+        <v>219</v>
       </c>
       <c r="D25" s="38">
         <v>0</v>
@@ -8967,7 +8970,7 @@
         <v>11</v>
       </c>
       <c r="C26" s="85" t="s">
-        <v>191</v>
+        <v>219</v>
       </c>
       <c r="D26" s="41">
         <v>0</v>
@@ -8978,7 +8981,7 @@
         <v>12</v>
       </c>
       <c r="C27" s="87" t="s">
-        <v>192</v>
+        <v>220</v>
       </c>
       <c r="D27" s="88">
         <v>0</v>
@@ -8989,7 +8992,7 @@
         <v>13</v>
       </c>
       <c r="C28" s="77" t="s">
-        <v>192</v>
+        <v>220</v>
       </c>
       <c r="D28" s="38">
         <v>0</v>
@@ -9000,7 +9003,7 @@
         <v>14</v>
       </c>
       <c r="C29" s="85" t="s">
-        <v>192</v>
+        <v>220</v>
       </c>
       <c r="D29" s="41">
         <v>0</v>
@@ -9011,7 +9014,7 @@
         <v>15</v>
       </c>
       <c r="C30" s="87" t="s">
-        <v>193</v>
+        <v>221</v>
       </c>
       <c r="D30" s="88">
         <v>0</v>
@@ -9022,7 +9025,7 @@
         <v>16</v>
       </c>
       <c r="C31" s="85" t="s">
-        <v>193</v>
+        <v>221</v>
       </c>
       <c r="D31" s="41">
         <v>0</v>
@@ -9033,7 +9036,7 @@
         <v>17</v>
       </c>
       <c r="C32" s="87" t="s">
-        <v>194</v>
+        <v>222</v>
       </c>
       <c r="D32" s="88">
         <v>0</v>
@@ -9044,7 +9047,7 @@
         <v>18</v>
       </c>
       <c r="C33" s="85" t="s">
-        <v>194</v>
+        <v>222</v>
       </c>
       <c r="D33" s="41">
         <v>0</v>
@@ -9055,7 +9058,7 @@
         <v>19</v>
       </c>
       <c r="C34" s="92" t="s">
-        <v>195</v>
+        <v>223</v>
       </c>
       <c r="D34" s="93">
         <v>0</v>
@@ -9066,7 +9069,7 @@
         <v>20</v>
       </c>
       <c r="C35" s="90" t="s">
-        <v>196</v>
+        <v>224</v>
       </c>
       <c r="D35" s="78">
         <v>0</v>
@@ -9074,7 +9077,7 @@
     </row>
     <row r="38" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B38" s="100" t="s">
-        <v>197</v>
+        <v>225</v>
       </c>
       <c r="C38" s="102" t="str">
         <f>IF(O4&lt;=$B$20,MIN(P6:AI6),"N/A")</f>
@@ -9083,7 +9086,7 @@
     </row>
     <row r="39" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B39" s="100" t="s">
-        <v>198</v>
+        <v>226</v>
       </c>
       <c r="C39" t="e">
         <f t="array" ref="C39">IF(AND(O4&gt;=$B$21,O4&lt;=$B$23),AVERAGE(SMALL(P6:AI6,{1,2})),"N/A")</f>
@@ -9092,7 +9095,7 @@
     </row>
     <row r="40" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B40" s="100" t="s">
-        <v>199</v>
+        <v>227</v>
       </c>
       <c r="C40" t="str">
         <f t="array" ref="C40">IF(AND(O4&gt;=$B$24,O4&lt;=$B$26),AVERAGE(SMALL(P6:AI6,{1,2,3})),"N/A")</f>
@@ -9101,7 +9104,7 @@
     </row>
     <row r="41" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B41" s="100" t="s">
-        <v>200</v>
+        <v>228</v>
       </c>
       <c r="C41" t="str">
         <f t="array" ref="C41">IF(AND(O4&gt;=$B$27,O4&lt;=$B$29),AVERAGE(SMALL(P6:AI6,{1,2,3,4})),"N/A")</f>
@@ -9110,7 +9113,7 @@
     </row>
     <row r="42" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B42" s="100" t="s">
-        <v>201</v>
+        <v>229</v>
       </c>
       <c r="C42" t="str">
         <f t="array" ref="C42">IF(AND(O4&gt;=$B$30,O4&lt;=$B$31),AVERAGE(SMALL(P6:AI6,{1,2,3,4,5})),"N/A")</f>
@@ -9119,7 +9122,7 @@
     </row>
     <row r="43" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B43" s="100" t="s">
-        <v>202</v>
+        <v>230</v>
       </c>
       <c r="C43" t="str">
         <f t="array" ref="C43">IF(AND(O4&gt;=$B$32,O4&lt;=$B$33),AVERAGE(SMALL(P6:AI6,{1,2,3,4,5,6})),"N/A")</f>
@@ -9146,7 +9149,7 @@
     </row>
     <row r="46" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B46" s="101" t="s">
-        <v>188</v>
+        <v>216</v>
       </c>
       <c r="C46">
         <f>VLOOKUP(O4,$B$16:$D$35,3)</f>
@@ -9187,57 +9190,57 @@
     <col min="13" max="15" width="11.5703125" style="12" customWidth="1"/>
     <col min="16" max="17" width="9.140625" style="12" customWidth="1"/>
     <col min="18" max="19" width="14.85546875" style="12" customWidth="1"/>
-    <col min="20" max="25" width="9.140625" style="12" customWidth="1"/>
-    <col min="26" max="16384" width="9.140625" style="12"/>
+    <col min="20" max="26" width="9.140625" style="12" customWidth="1"/>
+    <col min="27" max="16384" width="9.140625" style="12"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="N1" s="230" t="s">
-        <v>203</v>
-      </c>
-      <c r="O1" s="183"/>
+      <c r="N1" s="229" t="s">
+        <v>231</v>
+      </c>
+      <c r="O1" s="191"/>
       <c r="P1" s="21"/>
     </row>
     <row r="2" spans="1:19" ht="41.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B2" s="20" t="s">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="C2" s="22"/>
       <c r="D2" s="28" t="s">
-        <v>53</v>
+        <v>98</v>
       </c>
       <c r="E2" s="152" t="s">
-        <v>54</v>
+        <v>99</v>
       </c>
       <c r="F2" s="152" t="s">
-        <v>55</v>
+        <v>100</v>
       </c>
       <c r="G2" s="152" t="s">
+        <v>101</v>
+      </c>
+      <c r="H2" s="152" t="s">
+        <v>102</v>
+      </c>
+      <c r="I2" s="152" t="s">
+        <v>103</v>
+      </c>
+      <c r="J2" s="152" t="s">
+        <v>104</v>
+      </c>
+      <c r="K2" s="152" t="s">
+        <v>105</v>
+      </c>
+      <c r="L2" s="174" t="s">
+        <v>106</v>
+      </c>
+      <c r="M2" s="151" t="s">
         <v>56</v>
       </c>
-      <c r="H2" s="152" t="s">
+      <c r="N2" s="15" t="s">
         <v>57</v>
       </c>
-      <c r="I2" s="152" t="s">
-        <v>58</v>
-      </c>
-      <c r="J2" s="152" t="s">
-        <v>59</v>
-      </c>
-      <c r="K2" s="152" t="s">
-        <v>60</v>
-      </c>
-      <c r="L2" s="174" t="s">
-        <v>61</v>
-      </c>
-      <c r="M2" s="151" t="s">
-        <v>10</v>
-      </c>
-      <c r="N2" s="15" t="s">
-        <v>11</v>
-      </c>
       <c r="O2" s="29" t="s">
-        <v>204</v>
+        <v>232</v>
       </c>
     </row>
     <row r="3" spans="1:19" ht="12.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
@@ -9249,9 +9252,11 @@
         <v>Brian Wojcio</v>
       </c>
       <c r="C3" s="157" t="s">
-        <v>13</v>
-      </c>
-      <c r="D3" s="158"/>
+        <v>59</v>
+      </c>
+      <c r="D3" s="158">
+        <v>2</v>
+      </c>
       <c r="E3" s="159"/>
       <c r="F3" s="159"/>
       <c r="G3" s="159"/>
@@ -9260,21 +9265,29 @@
       <c r="J3" s="159"/>
       <c r="K3" s="159"/>
       <c r="L3" s="160"/>
-      <c r="M3" s="222"/>
-      <c r="N3" s="220"/>
-      <c r="O3" s="229"/>
+      <c r="M3" s="222">
+        <v>2</v>
+      </c>
+      <c r="N3" s="220" t="s">
+        <v>233</v>
+      </c>
+      <c r="O3" s="230">
+        <v>43</v>
+      </c>
       <c r="Q3" s="231" t="s">
-        <v>205</v>
+        <v>234</v>
       </c>
       <c r="R3" s="232"/>
-      <c r="S3" s="190"/>
+      <c r="S3" s="179"/>
     </row>
     <row r="4" spans="1:19" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B4" s="217"/>
       <c r="C4" s="161" t="s">
-        <v>206</v>
-      </c>
-      <c r="D4" s="162"/>
+        <v>235</v>
+      </c>
+      <c r="D4" s="162">
+        <v>43</v>
+      </c>
       <c r="E4" s="163"/>
       <c r="F4" s="163"/>
       <c r="G4" s="163"/>
@@ -9287,13 +9300,13 @@
       <c r="N4" s="219"/>
       <c r="O4" s="213"/>
       <c r="Q4" s="31" t="s">
-        <v>207</v>
+        <v>236</v>
       </c>
       <c r="R4" s="26" t="s">
-        <v>208</v>
+        <v>237</v>
       </c>
       <c r="S4" s="32" t="s">
-        <v>209</v>
+        <v>238</v>
       </c>
     </row>
     <row r="5" spans="1:19" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -9305,9 +9318,11 @@
         <v>Ethan High</v>
       </c>
       <c r="C5" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="D5" s="165"/>
+        <v>59</v>
+      </c>
+      <c r="D5" s="165">
+        <v>6</v>
+      </c>
       <c r="E5" s="166"/>
       <c r="F5" s="166"/>
       <c r="G5" s="166"/>
@@ -9316,9 +9331,15 @@
       <c r="J5" s="166"/>
       <c r="K5" s="166"/>
       <c r="L5" s="167"/>
-      <c r="M5" s="226"/>
-      <c r="N5" s="218"/>
-      <c r="O5" s="212"/>
+      <c r="M5" s="226">
+        <v>6</v>
+      </c>
+      <c r="N5" s="218" t="s">
+        <v>239</v>
+      </c>
+      <c r="O5" s="212">
+        <v>39</v>
+      </c>
       <c r="Q5" s="33">
         <v>1</v>
       </c>
@@ -9328,9 +9349,11 @@
     <row r="6" spans="1:19" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B6" s="215"/>
       <c r="C6" s="168" t="s">
-        <v>206</v>
-      </c>
-      <c r="D6" s="169"/>
+        <v>235</v>
+      </c>
+      <c r="D6" s="169">
+        <v>39</v>
+      </c>
       <c r="E6" s="170"/>
       <c r="F6" s="170"/>
       <c r="G6" s="170"/>
@@ -9357,9 +9380,11 @@
         <v>Rob Bass</v>
       </c>
       <c r="C7" s="157" t="s">
-        <v>13</v>
-      </c>
-      <c r="D7" s="158"/>
+        <v>59</v>
+      </c>
+      <c r="D7" s="158">
+        <v>1</v>
+      </c>
       <c r="E7" s="159"/>
       <c r="F7" s="159"/>
       <c r="G7" s="159"/>
@@ -9368,9 +9393,15 @@
       <c r="J7" s="159"/>
       <c r="K7" s="159"/>
       <c r="L7" s="160"/>
-      <c r="M7" s="222"/>
-      <c r="N7" s="220"/>
-      <c r="O7" s="229"/>
+      <c r="M7" s="222">
+        <v>1</v>
+      </c>
+      <c r="N7" s="220" t="s">
+        <v>233</v>
+      </c>
+      <c r="O7" s="230">
+        <v>43</v>
+      </c>
       <c r="Q7" s="33">
         <v>3</v>
       </c>
@@ -9380,9 +9411,11 @@
     <row r="8" spans="1:19" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B8" s="215"/>
       <c r="C8" s="161" t="s">
-        <v>206</v>
-      </c>
-      <c r="D8" s="162"/>
+        <v>235</v>
+      </c>
+      <c r="D8" s="162">
+        <v>43</v>
+      </c>
       <c r="E8" s="163"/>
       <c r="F8" s="163"/>
       <c r="G8" s="163"/>
@@ -9409,9 +9442,11 @@
         <v>Carson Bass</v>
       </c>
       <c r="C9" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="D9" s="165"/>
+        <v>59</v>
+      </c>
+      <c r="D9" s="165">
+        <v>7</v>
+      </c>
       <c r="E9" s="166"/>
       <c r="F9" s="166"/>
       <c r="G9" s="166"/>
@@ -9420,16 +9455,24 @@
       <c r="J9" s="166"/>
       <c r="K9" s="166"/>
       <c r="L9" s="167"/>
-      <c r="M9" s="226"/>
-      <c r="N9" s="218"/>
-      <c r="O9" s="212"/>
+      <c r="M9" s="226">
+        <v>7</v>
+      </c>
+      <c r="N9" s="218" t="s">
+        <v>239</v>
+      </c>
+      <c r="O9" s="212">
+        <v>38</v>
+      </c>
     </row>
     <row r="10" spans="1:19" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B10" s="215"/>
       <c r="C10" s="168" t="s">
-        <v>206</v>
-      </c>
-      <c r="D10" s="169"/>
+        <v>235</v>
+      </c>
+      <c r="D10" s="169">
+        <v>38</v>
+      </c>
       <c r="E10" s="170"/>
       <c r="F10" s="170"/>
       <c r="G10" s="170"/>
@@ -9442,7 +9485,7 @@
       <c r="N10" s="219"/>
       <c r="O10" s="213"/>
       <c r="R10" s="224" t="s">
-        <v>210</v>
+        <v>240</v>
       </c>
       <c r="S10" s="225"/>
     </row>
@@ -9455,7 +9498,7 @@
         <v>Michael McHugh</v>
       </c>
       <c r="C11" s="157" t="s">
-        <v>13</v>
+        <v>59</v>
       </c>
       <c r="D11" s="158"/>
       <c r="E11" s="159"/>
@@ -9468,18 +9511,18 @@
       <c r="L11" s="160"/>
       <c r="M11" s="222"/>
       <c r="N11" s="220"/>
-      <c r="O11" s="229"/>
+      <c r="O11" s="230"/>
       <c r="R11" s="36" t="s">
-        <v>211</v>
+        <v>16</v>
       </c>
       <c r="S11" s="38" t="s">
-        <v>212</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12" spans="1:19" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B12" s="215"/>
       <c r="C12" s="161" t="s">
-        <v>206</v>
+        <v>235</v>
       </c>
       <c r="D12" s="162"/>
       <c r="E12" s="163"/>
@@ -9494,10 +9537,10 @@
       <c r="N12" s="219"/>
       <c r="O12" s="213"/>
       <c r="R12" s="36" t="s">
-        <v>76</v>
+        <v>121</v>
       </c>
       <c r="S12" s="38" t="s">
-        <v>213</v>
+        <v>241</v>
       </c>
     </row>
     <row r="13" spans="1:19" ht="12.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
@@ -9509,7 +9552,7 @@
         <v>Bruce Atkins</v>
       </c>
       <c r="C13" s="24" t="s">
-        <v>13</v>
+        <v>59</v>
       </c>
       <c r="D13" s="165"/>
       <c r="E13" s="166"/>
@@ -9524,16 +9567,16 @@
       <c r="N13" s="218"/>
       <c r="O13" s="212"/>
       <c r="R13" s="39" t="s">
-        <v>87</v>
+        <v>132</v>
       </c>
       <c r="S13" s="41" t="s">
-        <v>214</v>
+        <v>242</v>
       </c>
     </row>
     <row r="14" spans="1:19" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B14" s="215"/>
       <c r="C14" s="168" t="s">
-        <v>206</v>
+        <v>235</v>
       </c>
       <c r="D14" s="169"/>
       <c r="E14" s="170"/>
@@ -9557,7 +9600,7 @@
         <v>Alex Palmer</v>
       </c>
       <c r="C15" s="157" t="s">
-        <v>13</v>
+        <v>59</v>
       </c>
       <c r="D15" s="158"/>
       <c r="E15" s="159"/>
@@ -9570,12 +9613,12 @@
       <c r="L15" s="160"/>
       <c r="M15" s="222"/>
       <c r="N15" s="220"/>
-      <c r="O15" s="229"/>
+      <c r="O15" s="230"/>
     </row>
     <row r="16" spans="1:19" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B16" s="215"/>
       <c r="C16" s="161" t="s">
-        <v>206</v>
+        <v>235</v>
       </c>
       <c r="D16" s="162"/>
       <c r="E16" s="163"/>
@@ -9599,7 +9642,7 @@
         <v>Curtis Lynn</v>
       </c>
       <c r="C17" s="24" t="s">
-        <v>13</v>
+        <v>59</v>
       </c>
       <c r="D17" s="165"/>
       <c r="E17" s="166"/>
@@ -9614,7 +9657,7 @@
       <c r="N17" s="218"/>
       <c r="O17" s="212"/>
       <c r="Q17" s="227" t="s">
-        <v>215</v>
+        <v>243</v>
       </c>
       <c r="R17" s="228"/>
       <c r="S17" s="228"/>
@@ -9622,7 +9665,7 @@
     <row r="18" spans="1:19" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B18" s="215"/>
       <c r="C18" s="168" t="s">
-        <v>206</v>
+        <v>235</v>
       </c>
       <c r="D18" s="169"/>
       <c r="E18" s="170"/>
@@ -9637,7 +9680,7 @@
       <c r="N18" s="219"/>
       <c r="O18" s="213"/>
       <c r="Q18" s="154" t="s">
-        <v>216</v>
+        <v>244</v>
       </c>
       <c r="R18" s="21"/>
     </row>
@@ -9650,7 +9693,7 @@
         <v>Ben Linck</v>
       </c>
       <c r="C19" s="157" t="s">
-        <v>13</v>
+        <v>59</v>
       </c>
       <c r="D19" s="158"/>
       <c r="E19" s="159"/>
@@ -9663,15 +9706,15 @@
       <c r="L19" s="160"/>
       <c r="M19" s="222"/>
       <c r="N19" s="220"/>
-      <c r="O19" s="229"/>
+      <c r="O19" s="230"/>
       <c r="Q19" s="154" t="s">
-        <v>217</v>
+        <v>245</v>
       </c>
     </row>
     <row r="20" spans="1:19" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B20" s="215"/>
       <c r="C20" s="161" t="s">
-        <v>206</v>
+        <v>235</v>
       </c>
       <c r="D20" s="162"/>
       <c r="E20" s="163"/>
@@ -9686,7 +9729,7 @@
       <c r="N20" s="219"/>
       <c r="O20" s="213"/>
       <c r="Q20" s="154" t="s">
-        <v>218</v>
+        <v>246</v>
       </c>
       <c r="R20" s="21"/>
     </row>
@@ -9699,7 +9742,7 @@
         <v>Charlotte Hayes</v>
       </c>
       <c r="C21" s="24" t="s">
-        <v>13</v>
+        <v>59</v>
       </c>
       <c r="D21" s="165"/>
       <c r="E21" s="166"/>
@@ -9714,14 +9757,14 @@
       <c r="N21" s="218"/>
       <c r="O21" s="212"/>
       <c r="Q21" s="154" t="s">
-        <v>219</v>
+        <v>247</v>
       </c>
       <c r="R21" s="21"/>
     </row>
     <row r="22" spans="1:19" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B22" s="215"/>
       <c r="C22" s="168" t="s">
-        <v>206</v>
+        <v>235</v>
       </c>
       <c r="D22" s="169"/>
       <c r="E22" s="170"/>
@@ -9745,7 +9788,7 @@
         <v>David Maddox</v>
       </c>
       <c r="C23" s="157" t="s">
-        <v>13</v>
+        <v>59</v>
       </c>
       <c r="D23" s="158"/>
       <c r="E23" s="159"/>
@@ -9758,12 +9801,12 @@
       <c r="L23" s="160"/>
       <c r="M23" s="222"/>
       <c r="N23" s="220"/>
-      <c r="O23" s="229"/>
+      <c r="O23" s="230"/>
     </row>
     <row r="24" spans="1:19" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B24" s="215"/>
       <c r="C24" s="161" t="s">
-        <v>206</v>
+        <v>235</v>
       </c>
       <c r="D24" s="162"/>
       <c r="E24" s="163"/>
@@ -9787,7 +9830,7 @@
         <v>Jerome Martin</v>
       </c>
       <c r="C25" s="24" t="s">
-        <v>13</v>
+        <v>59</v>
       </c>
       <c r="D25" s="165"/>
       <c r="E25" s="166"/>
@@ -9805,7 +9848,7 @@
     <row r="26" spans="1:19" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B26" s="215"/>
       <c r="C26" s="168" t="s">
-        <v>206</v>
+        <v>235</v>
       </c>
       <c r="D26" s="169"/>
       <c r="E26" s="170"/>
@@ -9829,7 +9872,7 @@
         <v>Kaylan Adams</v>
       </c>
       <c r="C27" s="157" t="s">
-        <v>13</v>
+        <v>59</v>
       </c>
       <c r="D27" s="158"/>
       <c r="E27" s="159"/>
@@ -9842,12 +9885,12 @@
       <c r="L27" s="160"/>
       <c r="M27" s="222"/>
       <c r="N27" s="220"/>
-      <c r="O27" s="229"/>
+      <c r="O27" s="230"/>
     </row>
     <row r="28" spans="1:19" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B28" s="215"/>
       <c r="C28" s="161" t="s">
-        <v>206</v>
+        <v>235</v>
       </c>
       <c r="D28" s="162"/>
       <c r="E28" s="163"/>
@@ -9871,7 +9914,7 @@
         <v>Megan Serian</v>
       </c>
       <c r="C29" s="24" t="s">
-        <v>13</v>
+        <v>59</v>
       </c>
       <c r="D29" s="165"/>
       <c r="E29" s="166"/>
@@ -9889,7 +9932,7 @@
     <row r="30" spans="1:19" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B30" s="215"/>
       <c r="C30" s="168" t="s">
-        <v>206</v>
+        <v>235</v>
       </c>
       <c r="D30" s="169"/>
       <c r="E30" s="170"/>
@@ -9913,7 +9956,7 @@
         <v>Nick Coglianese</v>
       </c>
       <c r="C31" s="157" t="s">
-        <v>13</v>
+        <v>59</v>
       </c>
       <c r="D31" s="158"/>
       <c r="E31" s="159"/>
@@ -9926,12 +9969,12 @@
       <c r="L31" s="160"/>
       <c r="M31" s="222"/>
       <c r="N31" s="220"/>
-      <c r="O31" s="229"/>
+      <c r="O31" s="230"/>
     </row>
     <row r="32" spans="1:19" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B32" s="215"/>
       <c r="C32" s="161" t="s">
-        <v>206</v>
+        <v>235</v>
       </c>
       <c r="D32" s="162"/>
       <c r="E32" s="163"/>
@@ -9949,22 +9992,22 @@
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="Y3y62YBPDCQhqKgsSl1/iH5xODfF8lm4IgTCoiweq2jLnTBBsjKN4ZDmcY+ulNgK91riyyuYS5VZZqKHpfKB8g==" saltValue="kkQ/PatKpMHBAJY782mRBw==" spinCount="100000" sheet="1"/>
   <mergeCells count="64">
-    <mergeCell ref="B31:B32"/>
     <mergeCell ref="Q3:S3"/>
     <mergeCell ref="N11:N12"/>
     <mergeCell ref="O19:O20"/>
     <mergeCell ref="N27:N28"/>
+    <mergeCell ref="B31:B32"/>
     <mergeCell ref="O13:O14"/>
+    <mergeCell ref="M29:M30"/>
+    <mergeCell ref="M9:M10"/>
     <mergeCell ref="O3:O4"/>
     <mergeCell ref="O9:O10"/>
+    <mergeCell ref="M19:M20"/>
+    <mergeCell ref="B7:B8"/>
+    <mergeCell ref="B25:B26"/>
     <mergeCell ref="N7:N8"/>
+    <mergeCell ref="B21:B22"/>
     <mergeCell ref="O15:O16"/>
-    <mergeCell ref="M31:M32"/>
-    <mergeCell ref="B13:B14"/>
-    <mergeCell ref="N17:N18"/>
-    <mergeCell ref="M25:M26"/>
-    <mergeCell ref="M3:M4"/>
-    <mergeCell ref="M5:M6"/>
     <mergeCell ref="N1:O1"/>
     <mergeCell ref="N23:N24"/>
     <mergeCell ref="O31:O32"/>
@@ -9981,12 +10024,16 @@
     <mergeCell ref="N31:N32"/>
     <mergeCell ref="O11:O12"/>
     <mergeCell ref="O27:O28"/>
-    <mergeCell ref="M29:M30"/>
-    <mergeCell ref="M9:M10"/>
-    <mergeCell ref="M19:M20"/>
-    <mergeCell ref="B7:B8"/>
-    <mergeCell ref="B25:B26"/>
-    <mergeCell ref="B21:B22"/>
+    <mergeCell ref="M31:M32"/>
+    <mergeCell ref="B13:B14"/>
+    <mergeCell ref="N17:N18"/>
+    <mergeCell ref="M25:M26"/>
+    <mergeCell ref="O25:O26"/>
+    <mergeCell ref="O21:O22"/>
+    <mergeCell ref="N29:N30"/>
+    <mergeCell ref="N15:N16"/>
+    <mergeCell ref="M23:M24"/>
+    <mergeCell ref="O23:O24"/>
     <mergeCell ref="R10:S10"/>
     <mergeCell ref="B11:B12"/>
     <mergeCell ref="N21:N22"/>
@@ -9996,13 +10043,8 @@
     <mergeCell ref="M15:M16"/>
     <mergeCell ref="M13:M14"/>
     <mergeCell ref="O29:O30"/>
-    <mergeCell ref="O25:O26"/>
     <mergeCell ref="Q17:S17"/>
-    <mergeCell ref="O21:O22"/>
     <mergeCell ref="O7:O8"/>
-    <mergeCell ref="O23:O24"/>
-    <mergeCell ref="N29:N30"/>
-    <mergeCell ref="N15:N16"/>
     <mergeCell ref="O5:O6"/>
     <mergeCell ref="B27:B28"/>
     <mergeCell ref="B3:B4"/>
@@ -10011,8 +10053,9 @@
     <mergeCell ref="B17:B18"/>
     <mergeCell ref="M11:M12"/>
     <mergeCell ref="N5:N6"/>
-    <mergeCell ref="M23:M24"/>
+    <mergeCell ref="M3:M4"/>
     <mergeCell ref="B5:B6"/>
+    <mergeCell ref="M5:M6"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="3" orientation="landscape" horizontalDpi="300" verticalDpi="300"/>
@@ -10038,71 +10081,71 @@
     <col min="26" max="27" width="9.85546875" style="48" customWidth="1"/>
     <col min="28" max="28" width="16.42578125" style="48" bestFit="1" customWidth="1"/>
     <col min="29" max="30" width="12.7109375" style="48" customWidth="1"/>
-    <col min="31" max="36" width="9.85546875" style="48" customWidth="1"/>
-    <col min="37" max="16384" width="9.85546875" style="48"/>
+    <col min="31" max="37" width="9.85546875" style="48" customWidth="1"/>
+    <col min="38" max="16384" width="9.85546875" style="48"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:31" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B1" s="47" t="s">
-        <v>220</v>
-      </c>
-      <c r="J1" s="233" t="s">
-        <v>221</v>
-      </c>
-      <c r="K1" s="183"/>
-      <c r="L1" s="183"/>
-      <c r="M1" s="183"/>
+        <v>248</v>
+      </c>
+      <c r="J1" s="240" t="s">
+        <v>1</v>
+      </c>
+      <c r="K1" s="191"/>
+      <c r="L1" s="191"/>
+      <c r="M1" s="191"/>
     </row>
     <row r="2" spans="2:31" ht="24.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="D2" s="49" t="s">
-        <v>222</v>
+        <v>3</v>
       </c>
       <c r="E2" s="49" t="s">
-        <v>223</v>
+        <v>4</v>
       </c>
       <c r="F2" s="49" t="s">
-        <v>224</v>
+        <v>5</v>
       </c>
       <c r="G2" s="49" t="s">
-        <v>225</v>
+        <v>6</v>
       </c>
       <c r="H2" s="49" t="s">
-        <v>226</v>
+        <v>7</v>
       </c>
       <c r="I2" s="50"/>
-      <c r="J2" s="240" t="str">
+      <c r="J2" s="237" t="str">
         <f>B8</f>
         <v>Ethan High</v>
       </c>
-      <c r="K2" s="190"/>
-      <c r="L2" s="237" t="str">
+      <c r="K2" s="179"/>
+      <c r="L2" s="233" t="str">
         <f>B17</f>
         <v>Bruce Dubovecky</v>
       </c>
-      <c r="M2" s="190"/>
+      <c r="M2" s="179"/>
       <c r="AA2" s="112" t="s">
-        <v>135</v>
+        <v>17</v>
       </c>
       <c r="AB2" s="112" t="s">
-        <v>227</v>
+        <v>249</v>
       </c>
       <c r="AC2" s="110" t="s">
-        <v>228</v>
+        <v>250</v>
       </c>
       <c r="AD2" s="110" t="s">
-        <v>229</v>
+        <v>251</v>
       </c>
       <c r="AE2" s="112" t="s">
-        <v>230</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3" spans="2:31" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="236" t="str">
+      <c r="B3" s="238" t="str">
         <f>B8</f>
         <v>Ethan High</v>
       </c>
       <c r="C3" s="51" t="s">
-        <v>231</v>
+        <v>8</v>
       </c>
       <c r="D3" s="52">
         <f>SUM(C15:E15)</f>
@@ -10124,21 +10167,21 @@
         <f>SUM(C14:K14)</f>
         <v>33</v>
       </c>
-      <c r="J3" s="239">
+      <c r="J3" s="236">
         <f>SUM(D4:H4)</f>
         <v>0</v>
       </c>
-      <c r="K3" s="185"/>
-      <c r="L3" s="234">
+      <c r="K3" s="183"/>
+      <c r="L3" s="239">
         <f>SUM(D6:H6)</f>
         <v>8</v>
       </c>
-      <c r="M3" s="185"/>
+      <c r="M3" s="183"/>
       <c r="AA3" s="110">
         <v>13</v>
       </c>
       <c r="AB3" s="111" t="s">
-        <v>25</v>
+        <v>70</v>
       </c>
       <c r="AC3" s="54" t="str">
         <f t="shared" ref="AC3:AC21" si="0">LEFT(AB3,SEARCH(" ",AB3)-1)</f>
@@ -10153,9 +10196,9 @@
       </c>
     </row>
     <row r="4" spans="2:31" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="179"/>
+      <c r="B4" s="186"/>
       <c r="C4" s="57" t="s">
-        <v>232</v>
+        <v>9</v>
       </c>
       <c r="D4" s="58">
         <f>IF(D3&gt;D5,2,IF(D3=D5,1,0))</f>
@@ -10177,15 +10220,15 @@
         <f>IF(H3&lt;H5,1,IF(H3=H5,0.5,0))</f>
         <v>0</v>
       </c>
-      <c r="J4" s="186"/>
-      <c r="K4" s="187"/>
+      <c r="J4" s="184"/>
+      <c r="K4" s="185"/>
       <c r="L4" s="235"/>
-      <c r="M4" s="187"/>
+      <c r="M4" s="185"/>
       <c r="AA4" s="110">
         <v>17</v>
       </c>
       <c r="AB4" s="111" t="s">
-        <v>29</v>
+        <v>74</v>
       </c>
       <c r="AC4" s="54" t="str">
         <f t="shared" si="0"/>
@@ -10200,12 +10243,12 @@
       </c>
     </row>
     <row r="5" spans="2:31" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="236" t="str">
+      <c r="B5" s="238" t="str">
         <f>B17</f>
         <v>Bruce Dubovecky</v>
       </c>
       <c r="C5" s="59" t="s">
-        <v>231</v>
+        <v>8</v>
       </c>
       <c r="D5" s="60">
         <f>SUM(C24:E24)</f>
@@ -10227,15 +10270,15 @@
         <f>SUM(C23:K23)</f>
         <v>0</v>
       </c>
-      <c r="J5" s="179"/>
-      <c r="K5" s="188"/>
-      <c r="L5" s="183"/>
-      <c r="M5" s="188"/>
+      <c r="J5" s="186"/>
+      <c r="K5" s="187"/>
+      <c r="L5" s="191"/>
+      <c r="M5" s="187"/>
       <c r="AA5" s="110">
         <v>4</v>
       </c>
       <c r="AB5" s="111" t="s">
-        <v>233</v>
+        <v>252</v>
       </c>
       <c r="AC5" s="54" t="str">
         <f t="shared" si="0"/>
@@ -10250,9 +10293,9 @@
       </c>
     </row>
     <row r="6" spans="2:31" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="179"/>
+      <c r="B6" s="186"/>
       <c r="C6" s="57" t="s">
-        <v>232</v>
+        <v>9</v>
       </c>
       <c r="D6" s="58">
         <f>IF(D5&gt;D3,2,IF(D5=D3,1,0))</f>
@@ -10282,7 +10325,7 @@
         <v>11</v>
       </c>
       <c r="AB6" s="111" t="s">
-        <v>24</v>
+        <v>69</v>
       </c>
       <c r="AC6" s="54" t="str">
         <f t="shared" si="0"/>
@@ -10311,7 +10354,7 @@
         <v>5</v>
       </c>
       <c r="AB7" s="111" t="s">
-        <v>20</v>
+        <v>65</v>
       </c>
       <c r="AC7" s="54" t="str">
         <f t="shared" si="0"/>
@@ -10327,10 +10370,10 @@
     </row>
     <row r="8" spans="2:31" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B8" s="109" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="C8" s="62" t="s">
-        <v>234</v>
+        <v>12</v>
       </c>
       <c r="D8" s="61">
         <f>IFERROR(VLOOKUP(B8,$AB$3:$AE$21,4,0),0)</f>
@@ -10338,25 +10381,25 @@
       </c>
       <c r="E8" s="61"/>
       <c r="F8" s="61" t="s">
-        <v>235</v>
+        <v>13</v>
       </c>
       <c r="G8" s="63" t="s">
-        <v>180</v>
+        <v>210</v>
       </c>
       <c r="H8" s="61"/>
       <c r="I8" s="61" t="s">
-        <v>236</v>
+        <v>15</v>
       </c>
       <c r="J8" s="63" t="s">
-        <v>211</v>
+        <v>16</v>
       </c>
       <c r="K8" s="61"/>
       <c r="L8" s="61"/>
       <c r="O8" s="48" t="s">
-        <v>237</v>
-      </c>
-      <c r="P8" s="238" t="s">
-        <v>211</v>
+        <v>20</v>
+      </c>
+      <c r="P8" s="234" t="s">
+        <v>16</v>
       </c>
       <c r="Q8" s="235"/>
       <c r="R8" s="235"/>
@@ -10370,7 +10413,7 @@
         <v>6</v>
       </c>
       <c r="AB8" s="111" t="s">
-        <v>21</v>
+        <v>66</v>
       </c>
       <c r="AC8" s="54" t="str">
         <f t="shared" si="0"/>
@@ -10386,7 +10429,7 @@
     </row>
     <row r="9" spans="2:31" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B9" s="64" t="s">
-        <v>238</v>
+        <v>22</v>
       </c>
       <c r="C9" s="65">
         <v>1</v>
@@ -10417,7 +10460,7 @@
       </c>
       <c r="L9" s="61"/>
       <c r="O9" s="48" t="s">
-        <v>180</v>
+        <v>210</v>
       </c>
       <c r="P9" s="61">
         <v>1</v>
@@ -10450,7 +10493,7 @@
         <v>7</v>
       </c>
       <c r="AB9" s="111" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="AC9" s="54" t="str">
         <f t="shared" si="0"/>
@@ -10466,7 +10509,7 @@
     </row>
     <row r="10" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B10" s="68" t="s">
-        <v>239</v>
+        <v>23</v>
       </c>
       <c r="C10" s="69">
         <v>4</v>
@@ -10500,7 +10543,7 @@
         <v>36</v>
       </c>
       <c r="O10" s="48" t="s">
-        <v>182</v>
+        <v>14</v>
       </c>
       <c r="P10" s="61">
         <v>1</v>
@@ -10533,7 +10576,7 @@
         <v>15</v>
       </c>
       <c r="AB10" s="111" t="s">
-        <v>22</v>
+        <v>67</v>
       </c>
       <c r="AC10" s="54" t="str">
         <f t="shared" si="0"/>
@@ -10549,7 +10592,7 @@
     </row>
     <row r="11" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B11" s="68" t="s">
-        <v>230</v>
+        <v>27</v>
       </c>
       <c r="C11" s="69">
         <f t="array" ref="C11">_xlfn.IFS($J8="Back 9",VLOOKUP($G8,$O$15:$X$18,COLUMN()-1,0),$J8="Front 9",VLOOKUP($G8,$O$9:$X$12,COLUMN()-1,0))</f>
@@ -10589,7 +10632,7 @@
       </c>
       <c r="L11" s="61"/>
       <c r="O11" s="48" t="s">
-        <v>240</v>
+        <v>253</v>
       </c>
       <c r="P11" s="61">
         <v>3</v>
@@ -10622,7 +10665,7 @@
         <v>18</v>
       </c>
       <c r="AB11" s="111" t="s">
-        <v>241</v>
+        <v>254</v>
       </c>
       <c r="AC11" s="54" t="str">
         <f t="shared" si="0"/>
@@ -10638,7 +10681,7 @@
     </row>
     <row r="12" spans="2:31" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B12" s="71" t="s">
-        <v>242</v>
+        <v>30</v>
       </c>
       <c r="C12" s="113">
         <v>5</v>
@@ -10676,7 +10719,7 @@
         <v>9</v>
       </c>
       <c r="O12" s="48" t="s">
-        <v>185</v>
+        <v>26</v>
       </c>
       <c r="P12" s="61">
         <v>1</v>
@@ -10709,7 +10752,7 @@
         <v>14</v>
       </c>
       <c r="AB12" s="111" t="s">
-        <v>27</v>
+        <v>72</v>
       </c>
       <c r="AC12" s="54" t="str">
         <f t="shared" si="0"/>
@@ -10725,7 +10768,7 @@
     </row>
     <row r="13" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B13" s="68" t="s">
-        <v>243</v>
+        <v>33</v>
       </c>
       <c r="C13" s="69">
         <v>5</v>
@@ -10759,7 +10802,7 @@
         <v>8</v>
       </c>
       <c r="AB13" s="111" t="s">
-        <v>17</v>
+        <v>63</v>
       </c>
       <c r="AC13" s="54" t="str">
         <f t="shared" si="0"/>
@@ -10775,7 +10818,7 @@
     </row>
     <row r="14" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B14" s="68" t="s">
-        <v>244</v>
+        <v>35</v>
       </c>
       <c r="C14" s="69">
         <f>C12-C13</f>
@@ -10821,8 +10864,8 @@
         <f>SUM(C14:K14)-SUM(C$10:K$10)</f>
         <v>-3</v>
       </c>
-      <c r="O14" s="238" t="s">
-        <v>212</v>
+      <c r="O14" s="234" t="s">
+        <v>21</v>
       </c>
       <c r="P14" s="235"/>
       <c r="Q14" s="235"/>
@@ -10837,7 +10880,7 @@
         <v>12</v>
       </c>
       <c r="AB14" s="111" t="s">
-        <v>26</v>
+        <v>71</v>
       </c>
       <c r="AC14" s="54" t="str">
         <f t="shared" si="0"/>
@@ -10853,7 +10896,7 @@
     </row>
     <row r="15" spans="2:31" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B15" s="74" t="s">
-        <v>245</v>
+        <v>37</v>
       </c>
       <c r="C15" s="56">
         <f t="shared" ref="C15:K15" si="3">IF(C14&lt;C23,1,0)</f>
@@ -10893,7 +10936,7 @@
       </c>
       <c r="L15" s="61"/>
       <c r="O15" s="48" t="s">
-        <v>180</v>
+        <v>210</v>
       </c>
       <c r="P15" s="61">
         <v>12</v>
@@ -10926,7 +10969,7 @@
         <v>19</v>
       </c>
       <c r="AB15" s="111" t="s">
-        <v>246</v>
+        <v>255</v>
       </c>
       <c r="AC15" s="54" t="str">
         <f t="shared" si="0"/>
@@ -10952,7 +10995,7 @@
       <c r="K16" s="61"/>
       <c r="L16" s="61"/>
       <c r="O16" s="48" t="s">
-        <v>182</v>
+        <v>14</v>
       </c>
       <c r="P16" s="61">
         <v>12</v>
@@ -10985,7 +11028,7 @@
         <v>10</v>
       </c>
       <c r="AB16" s="111" t="s">
-        <v>23</v>
+        <v>68</v>
       </c>
       <c r="AC16" s="54" t="str">
         <f t="shared" si="0"/>
@@ -11001,10 +11044,10 @@
     </row>
     <row r="17" spans="2:31" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B17" s="109" t="s">
-        <v>24</v>
+        <v>69</v>
       </c>
       <c r="C17" s="62" t="s">
-        <v>234</v>
+        <v>12</v>
       </c>
       <c r="D17" s="61">
         <f>IFERROR(VLOOKUP(B17,$AB$3:$AE$21,4,0),0)</f>
@@ -11012,22 +11055,22 @@
       </c>
       <c r="E17" s="61"/>
       <c r="F17" s="61" t="s">
-        <v>235</v>
+        <v>13</v>
       </c>
       <c r="G17" s="63" t="s">
-        <v>180</v>
+        <v>210</v>
       </c>
       <c r="H17" s="61"/>
       <c r="I17" s="61" t="s">
-        <v>236</v>
+        <v>15</v>
       </c>
       <c r="J17" s="63" t="s">
-        <v>211</v>
+        <v>16</v>
       </c>
       <c r="K17" s="61"/>
       <c r="L17" s="61"/>
       <c r="O17" s="48" t="s">
-        <v>240</v>
+        <v>253</v>
       </c>
       <c r="P17" s="61">
         <v>12</v>
@@ -11060,7 +11103,7 @@
         <v>9</v>
       </c>
       <c r="AB17" s="111" t="s">
-        <v>18</v>
+        <v>64</v>
       </c>
       <c r="AC17" s="54" t="str">
         <f t="shared" si="0"/>
@@ -11076,7 +11119,7 @@
     </row>
     <row r="18" spans="2:31" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B18" s="64" t="s">
-        <v>238</v>
+        <v>22</v>
       </c>
       <c r="C18" s="65">
         <v>1</v>
@@ -11108,7 +11151,7 @@
       <c r="L18" s="61"/>
       <c r="M18" s="72"/>
       <c r="O18" s="48" t="s">
-        <v>185</v>
+        <v>26</v>
       </c>
       <c r="P18" s="61">
         <v>10</v>
@@ -11141,7 +11184,7 @@
         <v>1</v>
       </c>
       <c r="AB18" s="111" t="s">
-        <v>12</v>
+        <v>58</v>
       </c>
       <c r="AC18" s="54" t="str">
         <f t="shared" si="0"/>
@@ -11157,7 +11200,7 @@
     </row>
     <row r="19" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B19" s="68" t="s">
-        <v>239</v>
+        <v>23</v>
       </c>
       <c r="C19" s="69">
         <v>4</v>
@@ -11194,7 +11237,7 @@
         <v>3</v>
       </c>
       <c r="AB19" s="111" t="s">
-        <v>15</v>
+        <v>61</v>
       </c>
       <c r="AC19" s="54" t="str">
         <f t="shared" si="0"/>
@@ -11210,7 +11253,7 @@
     </row>
     <row r="20" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B20" s="68" t="s">
-        <v>230</v>
+        <v>27</v>
       </c>
       <c r="C20" s="69">
         <f t="array" ref="C20">_xlfn.IFS($J17="Back 9",VLOOKUP($G17,$O$15:$X$18,COLUMN()-1,0),$J17="Front 9",VLOOKUP($G17,$O$9:$X$12,COLUMN()-1,0))</f>
@@ -11253,7 +11296,7 @@
         <v>16</v>
       </c>
       <c r="AB20" s="111" t="s">
-        <v>28</v>
+        <v>73</v>
       </c>
       <c r="AC20" s="54" t="str">
         <f t="shared" si="0"/>
@@ -11269,7 +11312,7 @@
     </row>
     <row r="21" spans="2:31" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B21" s="71" t="s">
-        <v>242</v>
+        <v>30</v>
       </c>
       <c r="C21" s="113">
         <v>5</v>
@@ -11310,7 +11353,7 @@
         <v>2</v>
       </c>
       <c r="AB21" s="111" t="s">
-        <v>247</v>
+        <v>256</v>
       </c>
       <c r="AC21" s="54" t="str">
         <f t="shared" si="0"/>
@@ -11326,7 +11369,7 @@
     </row>
     <row r="22" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B22" s="68" t="s">
-        <v>243</v>
+        <v>33</v>
       </c>
       <c r="C22" s="69">
         <v>5</v>
@@ -11359,7 +11402,7 @@
     </row>
     <row r="23" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B23" s="68" t="s">
-        <v>244</v>
+        <v>35</v>
       </c>
       <c r="C23" s="69">
         <f t="shared" ref="C23:K23" si="4">C21-C22</f>
@@ -11408,7 +11451,7 @@
     </row>
     <row r="24" spans="2:31" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B24" s="74" t="s">
-        <v>245</v>
+        <v>37</v>
       </c>
       <c r="C24" s="56">
         <f t="shared" ref="C24:K24" si="5">IF(C23&lt;C14,1,0)</f>
@@ -11455,15 +11498,15 @@
     </sortState>
   </autoFilter>
   <mergeCells count="9">
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="L3:M5"/>
     <mergeCell ref="J1:M1"/>
-    <mergeCell ref="L3:M5"/>
-    <mergeCell ref="B5:B6"/>
     <mergeCell ref="L2:M2"/>
     <mergeCell ref="O14:X14"/>
+    <mergeCell ref="P8:X8"/>
     <mergeCell ref="J3:K5"/>
-    <mergeCell ref="P8:X8"/>
     <mergeCell ref="J2:K2"/>
-    <mergeCell ref="B3:B4"/>
   </mergeCells>
   <conditionalFormatting sqref="C15:K15 C24:K24">
     <cfRule type="cellIs" dxfId="1" priority="1" operator="greaterThan">

--- a/2026 IMI Golf League.xlsx
+++ b/2026 IMI Golf League.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="714" firstSheet="5" activeTab="9" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="714" firstSheet="5" activeTab="9" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scores 2024" sheetId="1" state="hidden" r:id="rId1"/>
@@ -1385,17 +1385,106 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="49" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="48" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="2" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="26" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -1403,6 +1492,30 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="29" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="30" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="33" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="17" fillId="5" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1412,120 +1525,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="13" fillId="5" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="49" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="48" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="2" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1966,26 +1966,26 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:N20"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9.140625" defaultRowHeight="12.75"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9.109375" defaultRowHeight="13.2"/>
   <cols>
-    <col width="3.140625" customWidth="1" style="228" min="1" max="1"/>
-    <col width="18" bestFit="1" customWidth="1" style="228" min="2" max="2"/>
-    <col width="12.140625" bestFit="1" customWidth="1" style="228" min="3" max="3"/>
-    <col width="9.140625" customWidth="1" style="228" min="4" max="11"/>
-    <col width="11.5703125" customWidth="1" style="228" min="12" max="13"/>
-    <col width="9.140625" customWidth="1" style="228" min="14" max="20"/>
-    <col width="9.140625" customWidth="1" style="228" min="21" max="16384"/>
+    <col width="3.109375" customWidth="1" style="213" min="1" max="1"/>
+    <col width="18" bestFit="1" customWidth="1" style="213" min="2" max="2"/>
+    <col width="12.109375" bestFit="1" customWidth="1" style="213" min="3" max="3"/>
+    <col width="9.109375" customWidth="1" style="213" min="4" max="11"/>
+    <col width="11.5546875" customWidth="1" style="213" min="12" max="13"/>
+    <col width="9.109375" customWidth="1" style="213" min="14" max="26"/>
+    <col width="9.109375" customWidth="1" style="213" min="27" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1" ht="13.5" customHeight="1" s="197" thickBot="1">
-      <c r="M1" s="229" t="inlineStr">
+    <row r="1" ht="13.5" customHeight="1" s="181" thickBot="1">
+      <c r="M1" s="214" t="inlineStr">
         <is>
           <t>Tiebreaker</t>
         </is>
       </c>
       <c r="N1" s="21" t="n"/>
     </row>
-    <row r="2" ht="41.45" customHeight="1" s="197" thickBot="1">
+    <row r="2" ht="41.4" customHeight="1" s="181" thickBot="1">
       <c r="B2" s="20" t="inlineStr">
         <is>
           <t>Name</t>
@@ -2043,8 +2043,8 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="12.95" customHeight="1" s="197" thickBot="1">
-      <c r="A3" s="228" t="n">
+    <row r="3" ht="12.9" customHeight="1" s="181" thickBot="1">
+      <c r="A3" s="213" t="n">
         <v>1</v>
       </c>
       <c r="B3" s="25" t="inlineStr">
@@ -2084,8 +2084,8 @@
         <v/>
       </c>
     </row>
-    <row r="4" ht="12.95" customHeight="1" s="197" thickBot="1">
-      <c r="A4" s="228" t="n">
+    <row r="4" ht="12.9" customHeight="1" s="181" thickBot="1">
+      <c r="A4" s="213" t="n">
         <v>2</v>
       </c>
       <c r="B4" s="25" t="inlineStr">
@@ -2125,8 +2125,8 @@
         <v/>
       </c>
     </row>
-    <row r="5" ht="12.95" customHeight="1" s="197" thickBot="1">
-      <c r="A5" s="228" t="n">
+    <row r="5" ht="12.9" customHeight="1" s="181" thickBot="1">
+      <c r="A5" s="213" t="n">
         <v>3</v>
       </c>
       <c r="B5" s="25" t="inlineStr">
@@ -2166,8 +2166,8 @@
         <v/>
       </c>
     </row>
-    <row r="6" ht="12.95" customHeight="1" s="197" thickBot="1">
-      <c r="A6" s="228" t="n">
+    <row r="6" ht="12.9" customHeight="1" s="181" thickBot="1">
+      <c r="A6" s="213" t="n">
         <v>4</v>
       </c>
       <c r="B6" s="25" t="inlineStr">
@@ -2205,8 +2205,8 @@
         <v/>
       </c>
     </row>
-    <row r="7" ht="12.95" customHeight="1" s="197" thickBot="1">
-      <c r="A7" s="228" t="n">
+    <row r="7" ht="12.9" customHeight="1" s="181" thickBot="1">
+      <c r="A7" s="213" t="n">
         <v>5</v>
       </c>
       <c r="B7" s="25" t="inlineStr">
@@ -2248,8 +2248,8 @@
         <v/>
       </c>
     </row>
-    <row r="8" ht="12.95" customHeight="1" s="197" thickBot="1">
-      <c r="A8" s="228" t="n">
+    <row r="8" ht="12.9" customHeight="1" s="181" thickBot="1">
+      <c r="A8" s="213" t="n">
         <v>6</v>
       </c>
       <c r="B8" s="25" t="inlineStr">
@@ -2289,8 +2289,8 @@
         <v/>
       </c>
     </row>
-    <row r="9" ht="12.95" customHeight="1" s="197" thickBot="1">
-      <c r="A9" s="228" t="n">
+    <row r="9" ht="12.9" customHeight="1" s="181" thickBot="1">
+      <c r="A9" s="213" t="n">
         <v>7</v>
       </c>
       <c r="B9" s="25" t="inlineStr">
@@ -2328,8 +2328,8 @@
         <v/>
       </c>
     </row>
-    <row r="10" ht="12.95" customHeight="1" s="197" thickBot="1">
-      <c r="A10" s="228" t="n">
+    <row r="10" ht="12.9" customHeight="1" s="181" thickBot="1">
+      <c r="A10" s="213" t="n">
         <v>8</v>
       </c>
       <c r="B10" s="25" t="inlineStr">
@@ -2369,8 +2369,8 @@
         <v/>
       </c>
     </row>
-    <row r="11" ht="12.95" customHeight="1" s="197" thickBot="1">
-      <c r="A11" s="228" t="n">
+    <row r="11" ht="12.9" customHeight="1" s="181" thickBot="1">
+      <c r="A11" s="213" t="n">
         <v>9</v>
       </c>
       <c r="B11" s="25" t="inlineStr">
@@ -2410,8 +2410,8 @@
         <v/>
       </c>
     </row>
-    <row r="12" ht="12.95" customHeight="1" s="197" thickBot="1">
-      <c r="A12" s="228" t="n">
+    <row r="12" ht="12.9" customHeight="1" s="181" thickBot="1">
+      <c r="A12" s="213" t="n">
         <v>10</v>
       </c>
       <c r="B12" s="25" t="inlineStr">
@@ -2453,8 +2453,8 @@
         <v/>
       </c>
     </row>
-    <row r="13" ht="12.95" customHeight="1" s="197" thickBot="1">
-      <c r="A13" s="228" t="n">
+    <row r="13" ht="12.9" customHeight="1" s="181" thickBot="1">
+      <c r="A13" s="213" t="n">
         <v>11</v>
       </c>
       <c r="B13" s="25" t="inlineStr">
@@ -2492,8 +2492,8 @@
         <v/>
       </c>
     </row>
-    <row r="14" ht="12.95" customHeight="1" s="197" thickBot="1">
-      <c r="A14" s="228" t="n">
+    <row r="14" ht="12.9" customHeight="1" s="181" thickBot="1">
+      <c r="A14" s="213" t="n">
         <v>12</v>
       </c>
       <c r="B14" s="25" t="inlineStr">
@@ -2533,8 +2533,8 @@
         <v/>
       </c>
     </row>
-    <row r="15" ht="12.95" customHeight="1" s="197" thickBot="1">
-      <c r="A15" s="228" t="n">
+    <row r="15" ht="12.9" customHeight="1" s="181" thickBot="1">
+      <c r="A15" s="213" t="n">
         <v>13</v>
       </c>
       <c r="B15" s="25" t="inlineStr">
@@ -2574,8 +2574,8 @@
         <v/>
       </c>
     </row>
-    <row r="16" ht="12.95" customHeight="1" s="197" thickBot="1">
-      <c r="A16" s="228" t="n">
+    <row r="16" ht="12.9" customHeight="1" s="181" thickBot="1">
+      <c r="A16" s="213" t="n">
         <v>14</v>
       </c>
       <c r="B16" s="25" t="inlineStr">
@@ -2615,8 +2615,8 @@
         <v/>
       </c>
     </row>
-    <row r="17" ht="12.95" customHeight="1" s="197" thickBot="1">
-      <c r="A17" s="228" t="n">
+    <row r="17" ht="12.9" customHeight="1" s="181" thickBot="1">
+      <c r="A17" s="213" t="n">
         <v>15</v>
       </c>
       <c r="B17" s="25" t="inlineStr">
@@ -2654,8 +2654,8 @@
         <v/>
       </c>
     </row>
-    <row r="18" ht="12.95" customHeight="1" s="197" thickBot="1">
-      <c r="A18" s="228" t="n">
+    <row r="18" ht="12.9" customHeight="1" s="181" thickBot="1">
+      <c r="A18" s="213" t="n">
         <v>16</v>
       </c>
       <c r="B18" s="25" t="inlineStr">
@@ -2697,8 +2697,8 @@
         <v/>
       </c>
     </row>
-    <row r="19" ht="12.95" customHeight="1" s="197" thickBot="1">
-      <c r="A19" s="228" t="n">
+    <row r="19" ht="12.9" customHeight="1" s="181" thickBot="1">
+      <c r="A19" s="213" t="n">
         <v>17</v>
       </c>
       <c r="B19" s="25" t="inlineStr">
@@ -2738,8 +2738,8 @@
         <v/>
       </c>
     </row>
-    <row r="20" ht="12.95" customHeight="1" s="197">
-      <c r="A20" s="228" t="n">
+    <row r="20" ht="12.9" customHeight="1" s="181">
+      <c r="A20" s="213" t="n">
         <v>18</v>
       </c>
       <c r="B20" s="25" t="inlineStr">
@@ -2791,50 +2791,50 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="B1:BG24"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9.85546875" defaultRowHeight="13.5"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9.88671875" defaultRowHeight="13.8"/>
   <cols>
-    <col width="2.5703125" customWidth="1" style="181" min="1" max="1"/>
-    <col width="20.7109375" customWidth="1" style="181" min="2" max="2"/>
-    <col width="9.85546875" customWidth="1" style="181" min="3" max="8"/>
-    <col width="10.7109375" bestFit="1" customWidth="1" style="181" min="9" max="9"/>
-    <col width="10.5703125" customWidth="1" style="181" min="10" max="11"/>
-    <col width="10.85546875" customWidth="1" style="181" min="12" max="13"/>
-    <col width="5.7109375" customWidth="1" style="181" min="14" max="14"/>
-    <col width="11" bestFit="1" customWidth="1" style="181" min="15" max="15"/>
-    <col width="16.5703125" bestFit="1" customWidth="1" style="181" min="16" max="16"/>
-    <col width="8.85546875" bestFit="1" customWidth="1" style="181" min="17" max="17"/>
-    <col width="4.5703125" customWidth="1" style="181" min="18" max="19"/>
-    <col width="11" bestFit="1" customWidth="1" style="181" min="20" max="20"/>
-    <col width="4" customWidth="1" style="181" min="21" max="29"/>
-    <col width="10.42578125" bestFit="1" customWidth="1" style="181" min="30" max="30"/>
-    <col width="4" customWidth="1" style="181" min="31" max="39"/>
-    <col width="11" bestFit="1" customWidth="1" style="181" min="40" max="40"/>
-    <col width="4" customWidth="1" style="181" min="41" max="49"/>
-    <col width="10.42578125" bestFit="1" customWidth="1" style="181" min="50" max="50"/>
-    <col width="4" customWidth="1" style="181" min="51" max="59"/>
-    <col width="9.85546875" customWidth="1" style="181" min="60" max="66"/>
-    <col width="9.85546875" customWidth="1" style="181" min="67" max="16384"/>
+    <col width="2.5546875" customWidth="1" style="235" min="1" max="1"/>
+    <col width="20.6640625" customWidth="1" style="235" min="2" max="2"/>
+    <col width="9.88671875" customWidth="1" style="235" min="3" max="8"/>
+    <col width="10.6640625" bestFit="1" customWidth="1" style="235" min="9" max="9"/>
+    <col width="10.5546875" customWidth="1" style="235" min="10" max="11"/>
+    <col width="10.88671875" customWidth="1" style="235" min="12" max="13"/>
+    <col width="5.6640625" customWidth="1" style="235" min="14" max="14"/>
+    <col width="11" bestFit="1" customWidth="1" style="235" min="15" max="15"/>
+    <col width="16.5546875" bestFit="1" customWidth="1" style="235" min="16" max="16"/>
+    <col width="8.88671875" bestFit="1" customWidth="1" style="235" min="17" max="17"/>
+    <col width="4.5546875" customWidth="1" style="235" min="18" max="19"/>
+    <col width="11" bestFit="1" customWidth="1" style="235" min="20" max="20"/>
+    <col width="4" customWidth="1" style="235" min="21" max="29"/>
+    <col width="10.44140625" bestFit="1" customWidth="1" style="235" min="30" max="30"/>
+    <col width="4" customWidth="1" style="235" min="31" max="39"/>
+    <col width="11" bestFit="1" customWidth="1" style="235" min="40" max="40"/>
+    <col width="4" customWidth="1" style="235" min="41" max="49"/>
+    <col width="10.44140625" bestFit="1" customWidth="1" style="235" min="50" max="50"/>
+    <col width="4" customWidth="1" style="235" min="51" max="59"/>
+    <col width="9.88671875" customWidth="1" style="235" min="60" max="72"/>
+    <col width="9.88671875" customWidth="1" style="235" min="73" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.25" customHeight="1" s="197" thickBot="1">
+    <row r="1" ht="14.25" customHeight="1" s="181" thickBot="1">
       <c r="B1" s="116" t="inlineStr">
         <is>
           <t>Fill in the course, your name, tees, front/back and gross scores in the grey boxes</t>
         </is>
       </c>
-      <c r="J1" s="190" t="inlineStr">
+      <c r="J1" s="239" t="inlineStr">
         <is>
           <t>Points</t>
         </is>
       </c>
-      <c r="K1" s="191" t="n"/>
-      <c r="L1" s="191" t="n"/>
-      <c r="M1" s="191" t="n"/>
-    </row>
-    <row r="2" ht="24.95" customHeight="1" s="197" thickBot="1">
+      <c r="K1" s="215" t="n"/>
+      <c r="L1" s="215" t="n"/>
+      <c r="M1" s="215" t="n"/>
+    </row>
+    <row r="2" ht="24.9" customHeight="1" s="181" thickBot="1">
       <c r="B2" s="172" t="inlineStr">
         <is>
-          <t>Highland Creek</t>
+          <t>Skybrook</t>
         </is>
       </c>
       <c r="D2" s="118" t="inlineStr">
@@ -2863,19 +2863,19 @@
         </is>
       </c>
       <c r="I2" s="119" t="n"/>
-      <c r="J2" s="188">
+      <c r="J2" s="237">
         <f>B8</f>
         <v/>
       </c>
-      <c r="K2" s="179" t="n"/>
-      <c r="L2" s="178">
+      <c r="K2" s="219" t="n"/>
+      <c r="L2" s="233">
         <f>B17</f>
         <v/>
       </c>
-      <c r="M2" s="179" t="n"/>
-    </row>
-    <row r="3" ht="14.25" customHeight="1" s="197" thickBot="1">
-      <c r="B3" s="189">
+      <c r="M2" s="219" t="n"/>
+    </row>
+    <row r="3" ht="14.25" customHeight="1" s="181" thickBot="1">
+      <c r="B3" s="238">
         <f>J2</f>
         <v/>
       </c>
@@ -2904,19 +2904,19 @@
         <f>SUM(C14:K14)</f>
         <v/>
       </c>
-      <c r="J3" s="182">
+      <c r="J3" s="236">
         <f>SUM(D4:H4)</f>
         <v/>
       </c>
-      <c r="K3" s="183" t="n"/>
-      <c r="L3" s="192">
+      <c r="K3" s="224" t="n"/>
+      <c r="L3" s="240">
         <f>SUM(D6:H6)</f>
         <v/>
       </c>
-      <c r="M3" s="183" t="n"/>
-    </row>
-    <row r="4" ht="14.25" customHeight="1" s="197" thickBot="1">
-      <c r="B4" s="186" t="n"/>
+      <c r="M3" s="224" t="n"/>
+    </row>
+    <row r="4" ht="14.25" customHeight="1" s="181" thickBot="1">
+      <c r="B4" s="227" t="n"/>
       <c r="C4" s="125" t="inlineStr">
         <is>
           <t>PTS</t>
@@ -2942,12 +2942,12 @@
         <f>IF(H3&lt;H5,1,IF(H3=H5,0.5,0))</f>
         <v/>
       </c>
-      <c r="J4" s="184" t="n"/>
-      <c r="K4" s="185" t="n"/>
-      <c r="M4" s="185" t="n"/>
-    </row>
-    <row r="5" ht="14.25" customHeight="1" s="197" thickBot="1">
-      <c r="B5" s="189">
+      <c r="J4" s="225" t="n"/>
+      <c r="K4" s="226" t="n"/>
+      <c r="M4" s="226" t="n"/>
+    </row>
+    <row r="5" ht="14.25" customHeight="1" s="181" thickBot="1">
+      <c r="B5" s="238">
         <f>L2</f>
         <v/>
       </c>
@@ -2976,13 +2976,13 @@
         <f>SUM(C23:K23)</f>
         <v/>
       </c>
-      <c r="J5" s="186" t="n"/>
-      <c r="K5" s="187" t="n"/>
-      <c r="L5" s="191" t="n"/>
-      <c r="M5" s="187" t="n"/>
-    </row>
-    <row r="6" ht="14.25" customHeight="1" s="197" thickBot="1">
-      <c r="B6" s="186" t="n"/>
+      <c r="J5" s="227" t="n"/>
+      <c r="K5" s="228" t="n"/>
+      <c r="L5" s="215" t="n"/>
+      <c r="M5" s="228" t="n"/>
+    </row>
+    <row r="6" ht="14.25" customHeight="1" s="181" thickBot="1">
+      <c r="B6" s="227" t="n"/>
       <c r="C6" s="125" t="inlineStr">
         <is>
           <t>PTS</t>
@@ -3008,37 +3008,37 @@
         <f>IF(H5&lt;H3,1,IF(H5=H3,0.5,0))</f>
         <v/>
       </c>
-      <c r="J6" s="180" t="n"/>
-      <c r="K6" s="180" t="n"/>
-      <c r="L6" s="180" t="n"/>
-      <c r="M6" s="180" t="n"/>
+      <c r="J6" s="234" t="n"/>
+      <c r="K6" s="234" t="n"/>
+      <c r="L6" s="234" t="n"/>
+      <c r="M6" s="234" t="n"/>
     </row>
     <row r="7">
-      <c r="C7" s="180" t="n"/>
-      <c r="D7" s="180" t="n"/>
-      <c r="E7" s="180" t="n"/>
-      <c r="F7" s="180" t="n"/>
-      <c r="G7" s="180" t="n"/>
-      <c r="H7" s="180" t="n"/>
-      <c r="I7" s="180" t="n"/>
-      <c r="J7" s="180" t="n"/>
-      <c r="K7" s="180" t="n"/>
-      <c r="L7" s="180" t="n"/>
-      <c r="T7" s="180" t="inlineStr">
+      <c r="C7" s="234" t="n"/>
+      <c r="D7" s="234" t="n"/>
+      <c r="E7" s="234" t="n"/>
+      <c r="F7" s="234" t="n"/>
+      <c r="G7" s="234" t="n"/>
+      <c r="H7" s="234" t="n"/>
+      <c r="I7" s="234" t="n"/>
+      <c r="J7" s="234" t="n"/>
+      <c r="K7" s="234" t="n"/>
+      <c r="L7" s="234" t="n"/>
+      <c r="T7" s="234" t="inlineStr">
         <is>
           <t>Skybrook</t>
         </is>
       </c>
-      <c r="AN7" s="180" t="inlineStr">
+      <c r="AN7" s="234" t="inlineStr">
         <is>
           <t>Highland Creek</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="16.5" customHeight="1" s="197" thickBot="1">
+    <row r="8" ht="16.5" customHeight="1" s="181" thickBot="1">
       <c r="B8" s="145" t="inlineStr">
         <is>
-          <t>Jerome Martin</t>
+          <t>Ben Linck</t>
         </is>
       </c>
       <c r="C8" s="130" t="inlineStr">
@@ -3046,12 +3046,12 @@
           <t>Handicap:</t>
         </is>
       </c>
-      <c r="D8" s="180">
+      <c r="D8" s="234">
         <f>_xlfn.XLOOKUP(B8,$P$9:$P$23,$Q$9:$Q$23)</f>
         <v/>
       </c>
-      <c r="E8" s="180" t="n"/>
-      <c r="F8" s="180" t="inlineStr">
+      <c r="E8" s="234" t="n"/>
+      <c r="F8" s="234" t="inlineStr">
         <is>
           <t>Tees:</t>
         </is>
@@ -3061,8 +3061,8 @@
           <t>Blue</t>
         </is>
       </c>
-      <c r="H8" s="180" t="n"/>
-      <c r="I8" s="180" t="inlineStr">
+      <c r="H8" s="234" t="n"/>
+      <c r="I8" s="234" t="inlineStr">
         <is>
           <t>Holes:</t>
         </is>
@@ -3072,8 +3072,8 @@
           <t>Front 9</t>
         </is>
       </c>
-      <c r="K8" s="180" t="n"/>
-      <c r="L8" s="180" t="n"/>
+      <c r="K8" s="234" t="n"/>
+      <c r="L8" s="234" t="n"/>
       <c r="O8" s="143" t="inlineStr">
         <is>
           <t>#</t>
@@ -3089,38 +3089,38 @@
           <t>Handicap</t>
         </is>
       </c>
-      <c r="T8" s="181" t="inlineStr">
+      <c r="T8" s="235" t="inlineStr">
         <is>
           <t>HC's by Tees</t>
         </is>
       </c>
-      <c r="U8" s="180" t="inlineStr">
+      <c r="U8" s="234" t="inlineStr">
         <is>
           <t>Front 9</t>
         </is>
       </c>
-      <c r="AD8" s="180" t="inlineStr">
+      <c r="AD8" s="234" t="inlineStr">
         <is>
           <t>Back 9</t>
         </is>
       </c>
-      <c r="AN8" s="181" t="inlineStr">
+      <c r="AN8" s="235" t="inlineStr">
         <is>
           <t>HC's by Tees</t>
         </is>
       </c>
-      <c r="AO8" s="180" t="inlineStr">
+      <c r="AO8" s="234" t="inlineStr">
         <is>
           <t>Front 9</t>
         </is>
       </c>
-      <c r="AX8" s="180" t="inlineStr">
+      <c r="AX8" s="234" t="inlineStr">
         <is>
           <t>Back 9</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" s="197">
+    <row r="9" ht="15" customHeight="1" s="181">
       <c r="B9" s="131" t="inlineStr">
         <is>
           <t>HOLE</t>
@@ -3153,7 +3153,7 @@
       <c r="K9" s="134" t="n">
         <v>9</v>
       </c>
-      <c r="L9" s="180" t="n"/>
+      <c r="L9" s="234" t="n"/>
       <c r="O9" s="122" t="n">
         <v>1</v>
       </c>
@@ -3166,132 +3166,132 @@
         <f>Schedule!D15</f>
         <v/>
       </c>
-      <c r="T9" s="181" t="inlineStr">
+      <c r="T9" s="235" t="inlineStr">
         <is>
           <t>Blue</t>
         </is>
       </c>
-      <c r="U9" s="180" t="n">
+      <c r="U9" s="234" t="n">
         <v>7</v>
       </c>
-      <c r="V9" s="180" t="n">
+      <c r="V9" s="234" t="n">
         <v>15</v>
       </c>
-      <c r="W9" s="180" t="n">
+      <c r="W9" s="234" t="n">
         <v>5</v>
       </c>
-      <c r="X9" s="180" t="n">
+      <c r="X9" s="234" t="n">
         <v>13</v>
       </c>
-      <c r="Y9" s="180" t="n">
+      <c r="Y9" s="234" t="n">
         <v>3</v>
       </c>
-      <c r="Z9" s="180" t="n">
+      <c r="Z9" s="234" t="n">
         <v>11</v>
       </c>
-      <c r="AA9" s="180" t="n">
+      <c r="AA9" s="234" t="n">
         <v>17</v>
       </c>
-      <c r="AB9" s="180" t="n">
+      <c r="AB9" s="234" t="n">
         <v>9</v>
       </c>
-      <c r="AC9" s="180" t="n">
+      <c r="AC9" s="234" t="n">
         <v>1</v>
       </c>
-      <c r="AD9" s="181" t="inlineStr">
+      <c r="AD9" s="235" t="inlineStr">
         <is>
           <t>Blue</t>
         </is>
       </c>
-      <c r="AE9" s="180" t="n">
+      <c r="AE9" s="234" t="n">
         <v>4</v>
       </c>
-      <c r="AF9" s="180" t="n">
+      <c r="AF9" s="234" t="n">
         <v>12</v>
       </c>
-      <c r="AG9" s="180" t="n">
+      <c r="AG9" s="234" t="n">
         <v>14</v>
       </c>
-      <c r="AH9" s="180" t="n">
+      <c r="AH9" s="234" t="n">
         <v>6</v>
       </c>
-      <c r="AI9" s="180" t="n">
+      <c r="AI9" s="234" t="n">
         <v>16</v>
       </c>
-      <c r="AJ9" s="180" t="n">
+      <c r="AJ9" s="234" t="n">
         <v>8</v>
       </c>
-      <c r="AK9" s="180" t="n">
+      <c r="AK9" s="234" t="n">
         <v>18</v>
       </c>
-      <c r="AL9" s="180" t="n">
+      <c r="AL9" s="234" t="n">
         <v>2</v>
       </c>
-      <c r="AM9" s="180" t="n">
+      <c r="AM9" s="234" t="n">
         <v>10</v>
       </c>
-      <c r="AN9" s="181" t="inlineStr">
+      <c r="AN9" s="235" t="inlineStr">
         <is>
           <t>Blue</t>
         </is>
       </c>
-      <c r="AO9" s="180" t="n">
+      <c r="AO9" s="234" t="n">
         <v>7</v>
       </c>
-      <c r="AP9" s="180" t="n">
+      <c r="AP9" s="234" t="n">
         <v>17</v>
       </c>
-      <c r="AQ9" s="180" t="n">
+      <c r="AQ9" s="234" t="n">
         <v>15</v>
       </c>
-      <c r="AR9" s="180" t="n">
+      <c r="AR9" s="234" t="n">
         <v>1</v>
       </c>
-      <c r="AS9" s="180" t="n">
+      <c r="AS9" s="234" t="n">
         <v>11</v>
       </c>
-      <c r="AT9" s="180" t="n">
+      <c r="AT9" s="234" t="n">
         <v>9</v>
       </c>
-      <c r="AU9" s="180" t="n">
+      <c r="AU9" s="234" t="n">
         <v>13</v>
       </c>
-      <c r="AV9" s="180" t="n">
+      <c r="AV9" s="234" t="n">
         <v>5</v>
       </c>
-      <c r="AW9" s="180" t="n">
+      <c r="AW9" s="234" t="n">
         <v>3</v>
       </c>
-      <c r="AX9" s="181" t="inlineStr">
+      <c r="AX9" s="235" t="inlineStr">
         <is>
           <t>Blue</t>
         </is>
       </c>
-      <c r="AY9" s="180" t="n">
+      <c r="AY9" s="234" t="n">
         <v>14</v>
       </c>
-      <c r="AZ9" s="180" t="n">
+      <c r="AZ9" s="234" t="n">
         <v>8</v>
       </c>
-      <c r="BA9" s="180" t="n">
+      <c r="BA9" s="234" t="n">
         <v>6</v>
       </c>
-      <c r="BB9" s="180" t="n">
+      <c r="BB9" s="234" t="n">
         <v>4</v>
       </c>
-      <c r="BC9" s="180" t="n">
+      <c r="BC9" s="234" t="n">
         <v>16</v>
       </c>
-      <c r="BD9" s="180" t="n">
+      <c r="BD9" s="234" t="n">
         <v>2</v>
       </c>
-      <c r="BE9" s="180" t="n">
+      <c r="BE9" s="234" t="n">
         <v>10</v>
       </c>
-      <c r="BF9" s="180" t="n">
+      <c r="BF9" s="234" t="n">
         <v>12</v>
       </c>
-      <c r="BG9" s="180" t="n">
+      <c r="BG9" s="234" t="n">
         <v>18</v>
       </c>
     </row>
@@ -3301,7 +3301,7 @@
           <t>PAR</t>
         </is>
       </c>
-      <c r="C10" s="180">
+      <c r="C10" s="234">
         <f t="array" ref="C10">IF($B$2="Skybrook",
    _xlfn.IFS(
       $J8="Back 9",INDEX($AE$12:$AM$12,1,C9),
@@ -3314,7 +3314,7 @@
 )</f>
         <v/>
       </c>
-      <c r="D10" s="180">
+      <c r="D10" s="234">
         <f t="array" ref="D10">IF($B$2="Skybrook",
    _xlfn.IFS(
       $J8="Back 9",INDEX($AE$12:$AM$12,1,D9),
@@ -3353,7 +3353,7 @@
 )</f>
         <v/>
       </c>
-      <c r="G10" s="180">
+      <c r="G10" s="234">
         <f t="array" ref="G10">IF($B$2="Skybrook",
    _xlfn.IFS(
       $J8="Back 9",INDEX($AE$12:$AM$12,1,G9),
@@ -3392,7 +3392,7 @@
 )</f>
         <v/>
       </c>
-      <c r="J10" s="180">
+      <c r="J10" s="234">
         <f t="array" ref="J10">IF($B$2="Skybrook",
    _xlfn.IFS(
       $J8="Back 9",INDEX($AE$12:$AM$12,1,J9),
@@ -3418,7 +3418,7 @@
 )</f>
         <v/>
       </c>
-      <c r="L10" s="180">
+      <c r="L10" s="234">
         <f>SUM(C10:K10)</f>
         <v/>
       </c>
@@ -3434,132 +3434,132 @@
         <f>Schedule!D16</f>
         <v/>
       </c>
-      <c r="T10" s="181" t="inlineStr">
+      <c r="T10" s="235" t="inlineStr">
         <is>
           <t>Green</t>
         </is>
       </c>
-      <c r="U10" s="180" t="n">
+      <c r="U10" s="234" t="n">
         <v>7</v>
       </c>
-      <c r="V10" s="180" t="n">
+      <c r="V10" s="234" t="n">
         <v>15</v>
       </c>
-      <c r="W10" s="180" t="n">
+      <c r="W10" s="234" t="n">
         <v>5</v>
       </c>
-      <c r="X10" s="180" t="n">
+      <c r="X10" s="234" t="n">
         <v>13</v>
       </c>
-      <c r="Y10" s="180" t="n">
+      <c r="Y10" s="234" t="n">
         <v>3</v>
       </c>
-      <c r="Z10" s="180" t="n">
+      <c r="Z10" s="234" t="n">
         <v>11</v>
       </c>
-      <c r="AA10" s="180" t="n">
+      <c r="AA10" s="234" t="n">
         <v>17</v>
       </c>
-      <c r="AB10" s="180" t="n">
+      <c r="AB10" s="234" t="n">
         <v>9</v>
       </c>
-      <c r="AC10" s="180" t="n">
+      <c r="AC10" s="234" t="n">
         <v>1</v>
       </c>
-      <c r="AD10" s="181" t="inlineStr">
+      <c r="AD10" s="235" t="inlineStr">
         <is>
           <t>Green</t>
         </is>
       </c>
-      <c r="AE10" s="180" t="n">
+      <c r="AE10" s="234" t="n">
         <v>4</v>
       </c>
-      <c r="AF10" s="180" t="n">
+      <c r="AF10" s="234" t="n">
         <v>12</v>
       </c>
-      <c r="AG10" s="180" t="n">
+      <c r="AG10" s="234" t="n">
         <v>14</v>
       </c>
-      <c r="AH10" s="180" t="n">
+      <c r="AH10" s="234" t="n">
         <v>6</v>
       </c>
-      <c r="AI10" s="180" t="n">
+      <c r="AI10" s="234" t="n">
         <v>16</v>
       </c>
-      <c r="AJ10" s="180" t="n">
+      <c r="AJ10" s="234" t="n">
         <v>8</v>
       </c>
-      <c r="AK10" s="180" t="n">
+      <c r="AK10" s="234" t="n">
         <v>18</v>
       </c>
-      <c r="AL10" s="180" t="n">
+      <c r="AL10" s="234" t="n">
         <v>2</v>
       </c>
-      <c r="AM10" s="180" t="n">
+      <c r="AM10" s="234" t="n">
         <v>10</v>
       </c>
-      <c r="AN10" s="181" t="inlineStr">
+      <c r="AN10" s="235" t="inlineStr">
         <is>
           <t>White</t>
         </is>
       </c>
-      <c r="AO10" s="180" t="n">
+      <c r="AO10" s="234" t="n">
         <v>7</v>
       </c>
-      <c r="AP10" s="180" t="n">
+      <c r="AP10" s="234" t="n">
         <v>17</v>
       </c>
-      <c r="AQ10" s="180" t="n">
+      <c r="AQ10" s="234" t="n">
         <v>15</v>
       </c>
-      <c r="AR10" s="180" t="n">
+      <c r="AR10" s="234" t="n">
         <v>1</v>
       </c>
-      <c r="AS10" s="180" t="n">
+      <c r="AS10" s="234" t="n">
         <v>11</v>
       </c>
-      <c r="AT10" s="180" t="n">
+      <c r="AT10" s="234" t="n">
         <v>9</v>
       </c>
-      <c r="AU10" s="180" t="n">
+      <c r="AU10" s="234" t="n">
         <v>13</v>
       </c>
-      <c r="AV10" s="180" t="n">
+      <c r="AV10" s="234" t="n">
         <v>5</v>
       </c>
-      <c r="AW10" s="180" t="n">
+      <c r="AW10" s="234" t="n">
         <v>3</v>
       </c>
-      <c r="AX10" s="181" t="inlineStr">
+      <c r="AX10" s="235" t="inlineStr">
         <is>
           <t>White</t>
         </is>
       </c>
-      <c r="AY10" s="180" t="n">
+      <c r="AY10" s="234" t="n">
         <v>14</v>
       </c>
-      <c r="AZ10" s="180" t="n">
+      <c r="AZ10" s="234" t="n">
         <v>8</v>
       </c>
-      <c r="BA10" s="180" t="n">
+      <c r="BA10" s="234" t="n">
         <v>6</v>
       </c>
-      <c r="BB10" s="180" t="n">
+      <c r="BB10" s="234" t="n">
         <v>4</v>
       </c>
-      <c r="BC10" s="180" t="n">
+      <c r="BC10" s="234" t="n">
         <v>16</v>
       </c>
-      <c r="BD10" s="180" t="n">
+      <c r="BD10" s="234" t="n">
         <v>2</v>
       </c>
-      <c r="BE10" s="180" t="n">
+      <c r="BE10" s="234" t="n">
         <v>10</v>
       </c>
-      <c r="BF10" s="180" t="n">
+      <c r="BF10" s="234" t="n">
         <v>12</v>
       </c>
-      <c r="BG10" s="180" t="n">
+      <c r="BG10" s="234" t="n">
         <v>18</v>
       </c>
     </row>
@@ -3569,7 +3569,7 @@
           <t>HC</t>
         </is>
       </c>
-      <c r="C11" s="180">
+      <c r="C11" s="234">
         <f t="array" ref="C11">IF($B$2="Skybrook",
    _xlfn.IFS(
       $J8="Back 9",VLOOKUP($G8,$AD$9:$AM$11,COLUMN()-1,0),
@@ -3582,7 +3582,7 @@
 )</f>
         <v/>
       </c>
-      <c r="D11" s="180">
+      <c r="D11" s="234">
         <f t="array" ref="D11">IF($B$2="Skybrook",
    _xlfn.IFS(
       $J8="Back 9",VLOOKUP($G8,$AD$9:$AM$11,COLUMN()-1,0),
@@ -3621,7 +3621,7 @@
 )</f>
         <v/>
       </c>
-      <c r="G11" s="180">
+      <c r="G11" s="234">
         <f t="array" ref="G11">IF($B$2="Skybrook",
    _xlfn.IFS(
       $J8="Back 9",VLOOKUP($G8,$AD$9:$AM$11,COLUMN()-1,0),
@@ -3660,7 +3660,7 @@
 )</f>
         <v/>
       </c>
-      <c r="J11" s="180">
+      <c r="J11" s="234">
         <f t="array" ref="J11">IF($B$2="Skybrook",
    _xlfn.IFS(
       $J8="Back 9",VLOOKUP($G8,$AD$9:$AM$11,COLUMN()-1,0),
@@ -3686,7 +3686,7 @@
 )</f>
         <v/>
       </c>
-      <c r="L11" s="180" t="n"/>
+      <c r="L11" s="234" t="n"/>
       <c r="O11" s="122">
         <f>O10+1</f>
         <v/>
@@ -3700,169 +3700,169 @@
         <f>Schedule!D17</f>
         <v/>
       </c>
-      <c r="T11" s="181" t="inlineStr">
+      <c r="T11" s="235" t="inlineStr">
         <is>
           <t>Red</t>
         </is>
       </c>
-      <c r="U11" s="180" t="n">
+      <c r="U11" s="234" t="n">
         <v>17</v>
       </c>
-      <c r="V11" s="180" t="n">
+      <c r="V11" s="234" t="n">
         <v>9</v>
       </c>
-      <c r="W11" s="180" t="n">
+      <c r="W11" s="234" t="n">
         <v>5</v>
       </c>
-      <c r="X11" s="180" t="n">
+      <c r="X11" s="234" t="n">
         <v>7</v>
       </c>
-      <c r="Y11" s="180" t="n">
+      <c r="Y11" s="234" t="n">
         <v>3</v>
       </c>
-      <c r="Z11" s="180" t="n">
+      <c r="Z11" s="234" t="n">
         <v>15</v>
       </c>
-      <c r="AA11" s="180" t="n">
+      <c r="AA11" s="234" t="n">
         <v>11</v>
       </c>
-      <c r="AB11" s="180" t="n">
+      <c r="AB11" s="234" t="n">
         <v>13</v>
       </c>
-      <c r="AC11" s="180" t="n">
+      <c r="AC11" s="234" t="n">
         <v>1</v>
       </c>
-      <c r="AD11" s="181" t="inlineStr">
+      <c r="AD11" s="235" t="inlineStr">
         <is>
           <t>Red</t>
         </is>
       </c>
-      <c r="AE11" s="180" t="n">
+      <c r="AE11" s="234" t="n">
         <v>4</v>
       </c>
-      <c r="AF11" s="180" t="n">
+      <c r="AF11" s="234" t="n">
         <v>10</v>
       </c>
-      <c r="AG11" s="180" t="n">
+      <c r="AG11" s="234" t="n">
         <v>14</v>
       </c>
-      <c r="AH11" s="180" t="n">
+      <c r="AH11" s="234" t="n">
         <v>6</v>
       </c>
-      <c r="AI11" s="180" t="n">
+      <c r="AI11" s="234" t="n">
         <v>16</v>
       </c>
-      <c r="AJ11" s="180" t="n">
+      <c r="AJ11" s="234" t="n">
         <v>12</v>
       </c>
-      <c r="AK11" s="180" t="n">
+      <c r="AK11" s="234" t="n">
         <v>18</v>
       </c>
-      <c r="AL11" s="180" t="n">
+      <c r="AL11" s="234" t="n">
         <v>2</v>
       </c>
-      <c r="AM11" s="180" t="n">
+      <c r="AM11" s="234" t="n">
         <v>8</v>
       </c>
-      <c r="AN11" s="181" t="inlineStr">
+      <c r="AN11" s="235" t="inlineStr">
         <is>
           <t>Red</t>
         </is>
       </c>
-      <c r="AO11" s="180" t="n">
+      <c r="AO11" s="234" t="n">
         <v>7</v>
       </c>
-      <c r="AP11" s="180" t="n">
+      <c r="AP11" s="234" t="n">
         <v>17</v>
       </c>
-      <c r="AQ11" s="180" t="n">
+      <c r="AQ11" s="234" t="n">
         <v>15</v>
       </c>
-      <c r="AR11" s="180" t="n">
+      <c r="AR11" s="234" t="n">
         <v>1</v>
       </c>
-      <c r="AS11" s="180" t="n">
+      <c r="AS11" s="234" t="n">
         <v>11</v>
       </c>
-      <c r="AT11" s="180" t="n">
+      <c r="AT11" s="234" t="n">
         <v>9</v>
       </c>
-      <c r="AU11" s="180" t="n">
+      <c r="AU11" s="234" t="n">
         <v>13</v>
       </c>
-      <c r="AV11" s="180" t="n">
+      <c r="AV11" s="234" t="n">
         <v>5</v>
       </c>
-      <c r="AW11" s="180" t="n">
+      <c r="AW11" s="234" t="n">
         <v>3</v>
       </c>
-      <c r="AX11" s="181" t="inlineStr">
+      <c r="AX11" s="235" t="inlineStr">
         <is>
           <t>Red</t>
         </is>
       </c>
-      <c r="AY11" s="180" t="n">
+      <c r="AY11" s="234" t="n">
         <v>14</v>
       </c>
-      <c r="AZ11" s="180" t="n">
+      <c r="AZ11" s="234" t="n">
         <v>8</v>
       </c>
-      <c r="BA11" s="180" t="n">
+      <c r="BA11" s="234" t="n">
         <v>6</v>
       </c>
-      <c r="BB11" s="180" t="n">
+      <c r="BB11" s="234" t="n">
         <v>4</v>
       </c>
-      <c r="BC11" s="180" t="n">
+      <c r="BC11" s="234" t="n">
         <v>16</v>
       </c>
-      <c r="BD11" s="180" t="n">
+      <c r="BD11" s="234" t="n">
         <v>2</v>
       </c>
-      <c r="BE11" s="180" t="n">
+      <c r="BE11" s="234" t="n">
         <v>10</v>
       </c>
-      <c r="BF11" s="180" t="n">
+      <c r="BF11" s="234" t="n">
         <v>12</v>
       </c>
-      <c r="BG11" s="180" t="n">
+      <c r="BG11" s="234" t="n">
         <v>18</v>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1" s="197">
+    <row r="12" ht="15" customHeight="1" s="181">
       <c r="B12" s="138" t="inlineStr">
         <is>
           <t>GROSS</t>
         </is>
       </c>
       <c r="C12" s="146" t="n">
+        <v>7</v>
+      </c>
+      <c r="D12" s="147" t="n">
         <v>8</v>
       </c>
-      <c r="D12" s="147" t="n">
+      <c r="E12" s="148" t="n">
+        <v>5</v>
+      </c>
+      <c r="F12" s="146" t="n">
+        <v>5</v>
+      </c>
+      <c r="G12" s="147" t="n">
         <v>6</v>
       </c>
-      <c r="E12" s="148" t="n">
-        <v>8</v>
-      </c>
-      <c r="F12" s="146" t="n">
-        <v>10</v>
-      </c>
-      <c r="G12" s="147" t="n">
-        <v>8</v>
-      </c>
       <c r="H12" s="148" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I12" s="146" t="n">
         <v>6</v>
       </c>
       <c r="J12" s="147" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="K12" s="148" t="n">
-        <v>8</v>
-      </c>
-      <c r="L12" s="180">
+        <v>6</v>
+      </c>
+      <c r="L12" s="234">
         <f>SUM(C12:K12)</f>
         <v/>
       </c>
@@ -3882,7 +3882,7 @@
         <f>Schedule!D18</f>
         <v/>
       </c>
-      <c r="T12" s="181" t="inlineStr">
+      <c r="T12" s="235" t="inlineStr">
         <is>
           <t>Par</t>
         </is>
@@ -3914,7 +3914,7 @@
       <c r="AC12" s="144" t="n">
         <v>4</v>
       </c>
-      <c r="AD12" s="181" t="inlineStr">
+      <c r="AD12" s="235" t="inlineStr">
         <is>
           <t>Par</t>
         </is>
@@ -3946,7 +3946,7 @@
       <c r="AM12" s="144" t="n">
         <v>5</v>
       </c>
-      <c r="AN12" s="181" t="inlineStr">
+      <c r="AN12" s="235" t="inlineStr">
         <is>
           <t>Par</t>
         </is>
@@ -3978,7 +3978,7 @@
       <c r="AW12" s="144" t="n">
         <v>4</v>
       </c>
-      <c r="AX12" s="181" t="inlineStr">
+      <c r="AX12" s="235" t="inlineStr">
         <is>
           <t>Par</t>
         </is>
@@ -4021,7 +4021,7 @@
         <f>INT($D$8/18)+IF(C11&lt;=MOD($D$8,18),1,0)</f>
         <v/>
       </c>
-      <c r="D13" s="180">
+      <c r="D13" s="234">
         <f>INT($D$8/18)+IF(D11&lt;=MOD($D$8,18),1,0)</f>
         <v/>
       </c>
@@ -4033,7 +4033,7 @@
         <f>INT($D$8/18)+IF(F11&lt;=MOD($D$8,18),1,0)</f>
         <v/>
       </c>
-      <c r="G13" s="180">
+      <c r="G13" s="234">
         <f>INT($D$8/18)+IF(G11&lt;=MOD($D$8,18),1,0)</f>
         <v/>
       </c>
@@ -4045,7 +4045,7 @@
         <f>INT($D$8/18)+IF(I11&lt;=MOD($D$8,18),1,0)</f>
         <v/>
       </c>
-      <c r="J13" s="180">
+      <c r="J13" s="234">
         <f>INT($D$8/18)+IF(J11&lt;=MOD($D$8,18),1,0)</f>
         <v/>
       </c>
@@ -4077,7 +4077,7 @@
         <f>C12-C13</f>
         <v/>
       </c>
-      <c r="D14" s="180">
+      <c r="D14" s="234">
         <f>D12-INT($D$8/18)-IF(D11&lt;=MOD($D$8,18),1,0)</f>
         <v/>
       </c>
@@ -4089,7 +4089,7 @@
         <f>F12-INT($D$8/18)-IF(F11&lt;=MOD($D$8,18),1,0)</f>
         <v/>
       </c>
-      <c r="G14" s="180">
+      <c r="G14" s="234">
         <f>G12-INT($D$8/18)-IF(G11&lt;=MOD($D$8,18),1,0)</f>
         <v/>
       </c>
@@ -4101,7 +4101,7 @@
         <f>I12-INT($D$8/18)-IF(I11&lt;=MOD($D$8,18),1,0)</f>
         <v/>
       </c>
-      <c r="J14" s="180">
+      <c r="J14" s="234">
         <f>J12-INT($D$8/18)-IF(J11&lt;=MOD($D$8,18),1,0)</f>
         <v/>
       </c>
@@ -4130,7 +4130,7 @@
         <v/>
       </c>
     </row>
-    <row r="15" ht="14.25" customHeight="1" s="197" thickBot="1">
+    <row r="15" ht="14.25" customHeight="1" s="181" thickBot="1">
       <c r="B15" s="140" t="inlineStr">
         <is>
           <t>Wins Hole</t>
@@ -4172,7 +4172,7 @@
         <f>IF(K14&lt;K23,1,0)</f>
         <v/>
       </c>
-      <c r="L15" s="180" t="n"/>
+      <c r="L15" s="234" t="n"/>
       <c r="O15" s="122">
         <f>O14+1</f>
         <v/>
@@ -4188,16 +4188,16 @@
       </c>
     </row>
     <row r="16">
-      <c r="C16" s="180" t="n"/>
-      <c r="D16" s="180" t="n"/>
-      <c r="E16" s="180" t="n"/>
-      <c r="F16" s="180" t="n"/>
-      <c r="G16" s="180" t="n"/>
-      <c r="H16" s="180" t="n"/>
-      <c r="I16" s="180" t="n"/>
-      <c r="J16" s="180" t="n"/>
-      <c r="K16" s="180" t="n"/>
-      <c r="L16" s="180" t="n"/>
+      <c r="C16" s="234" t="n"/>
+      <c r="D16" s="234" t="n"/>
+      <c r="E16" s="234" t="n"/>
+      <c r="F16" s="234" t="n"/>
+      <c r="G16" s="234" t="n"/>
+      <c r="H16" s="234" t="n"/>
+      <c r="I16" s="234" t="n"/>
+      <c r="J16" s="234" t="n"/>
+      <c r="K16" s="234" t="n"/>
+      <c r="L16" s="234" t="n"/>
       <c r="O16" s="122" t="n">
         <v>8</v>
       </c>
@@ -4211,10 +4211,10 @@
         <v/>
       </c>
     </row>
-    <row r="17" ht="16.5" customHeight="1" s="197" thickBot="1">
+    <row r="17" ht="16.5" customHeight="1" s="181" thickBot="1">
       <c r="B17" s="145" t="inlineStr">
         <is>
-          <t>Kaylan Adams</t>
+          <t>Charlotte Hayes</t>
         </is>
       </c>
       <c r="C17" s="130" t="inlineStr">
@@ -4222,12 +4222,12 @@
           <t>Handicap:</t>
         </is>
       </c>
-      <c r="D17" s="180">
+      <c r="D17" s="234">
         <f>_xlfn.XLOOKUP(B17,$P$9:$P$23,$Q$9:$Q$23)</f>
         <v/>
       </c>
-      <c r="E17" s="180" t="n"/>
-      <c r="F17" s="180" t="inlineStr">
+      <c r="E17" s="234" t="n"/>
+      <c r="F17" s="234" t="inlineStr">
         <is>
           <t>Tees:</t>
         </is>
@@ -4237,18 +4237,18 @@
           <t>Blue</t>
         </is>
       </c>
-      <c r="H17" s="180" t="n"/>
-      <c r="I17" s="180" t="inlineStr">
+      <c r="H17" s="234" t="n"/>
+      <c r="I17" s="234" t="inlineStr">
         <is>
           <t>Holes:</t>
         </is>
       </c>
-      <c r="J17" s="180">
+      <c r="J17" s="234">
         <f>J8</f>
         <v/>
       </c>
-      <c r="K17" s="180" t="n"/>
-      <c r="L17" s="180" t="n"/>
+      <c r="K17" s="234" t="n"/>
+      <c r="L17" s="234" t="n"/>
       <c r="O17" s="122" t="n">
         <v>9</v>
       </c>
@@ -4262,7 +4262,7 @@
         <v/>
       </c>
     </row>
-    <row r="18" ht="15" customHeight="1" s="197">
+    <row r="18" ht="15" customHeight="1" s="181">
       <c r="B18" s="131" t="inlineStr">
         <is>
           <t>HOLE</t>
@@ -4295,7 +4295,7 @@
       <c r="K18" s="134" t="n">
         <v>9</v>
       </c>
-      <c r="L18" s="180" t="n"/>
+      <c r="L18" s="234" t="n"/>
       <c r="M18" s="139" t="n"/>
       <c r="O18" s="122" t="n">
         <v>10</v>
@@ -4316,7 +4316,7 @@
           <t>PAR</t>
         </is>
       </c>
-      <c r="C19" s="180">
+      <c r="C19" s="234">
         <f t="array" ref="C19">IF($B$2="Skybrook",
    _xlfn.IFS(
       $J17="Back 9",INDEX($AE$12:$AM$12,1,C18),
@@ -4329,7 +4329,7 @@
 )</f>
         <v/>
       </c>
-      <c r="D19" s="180">
+      <c r="D19" s="234">
         <f t="array" ref="D19">IF($B$2="Skybrook",
    _xlfn.IFS(
       $J17="Back 9",INDEX($AE$12:$AM$12,1,D18),
@@ -4368,7 +4368,7 @@
 )</f>
         <v/>
       </c>
-      <c r="G19" s="180">
+      <c r="G19" s="234">
         <f t="array" ref="G19">IF($B$2="Skybrook",
    _xlfn.IFS(
       $J17="Back 9",INDEX($AE$12:$AM$12,1,G18),
@@ -4407,7 +4407,7 @@
 )</f>
         <v/>
       </c>
-      <c r="J19" s="180">
+      <c r="J19" s="234">
         <f t="array" ref="J19">IF($B$2="Skybrook",
    _xlfn.IFS(
       $J17="Back 9",INDEX($AE$12:$AM$12,1,J18),
@@ -4433,7 +4433,7 @@
 )</f>
         <v/>
       </c>
-      <c r="L19" s="180">
+      <c r="L19" s="234">
         <f>SUM(C19:K19)</f>
         <v/>
       </c>
@@ -4457,7 +4457,7 @@
           <t>HC</t>
         </is>
       </c>
-      <c r="C20" s="180">
+      <c r="C20" s="234">
         <f t="array" ref="C20">IF($B$2="Skybrook",
    _xlfn.IFS(
       $J17="Back 9",VLOOKUP($G17,$AD$9:$AM$11,COLUMN()-1,0),
@@ -4470,7 +4470,7 @@
 )</f>
         <v/>
       </c>
-      <c r="D20" s="180">
+      <c r="D20" s="234">
         <f t="array" ref="D20">IF($B$2="Skybrook",
    _xlfn.IFS(
       $J17="Back 9",VLOOKUP($G17,$AD$9:$AM$11,COLUMN()-1,0),
@@ -4509,7 +4509,7 @@
 )</f>
         <v/>
       </c>
-      <c r="G20" s="180">
+      <c r="G20" s="234">
         <f t="array" ref="G20">IF($B$2="Skybrook",
    _xlfn.IFS(
       $J17="Back 9",VLOOKUP($G17,$AD$9:$AM$11,COLUMN()-1,0),
@@ -4548,7 +4548,7 @@
 )</f>
         <v/>
       </c>
-      <c r="J20" s="180">
+      <c r="J20" s="234">
         <f t="array" ref="J20">IF($B$2="Skybrook",
    _xlfn.IFS(
       $J17="Back 9",VLOOKUP($G17,$AD$9:$AM$11,COLUMN()-1,0),
@@ -4574,7 +4574,7 @@
 )</f>
         <v/>
       </c>
-      <c r="L20" s="180" t="n"/>
+      <c r="L20" s="234" t="n"/>
       <c r="O20" s="122" t="n">
         <v>12</v>
       </c>
@@ -4588,40 +4588,40 @@
         <v/>
       </c>
     </row>
-    <row r="21" ht="15" customHeight="1" s="197">
+    <row r="21" ht="15" customHeight="1" s="181">
       <c r="B21" s="138" t="inlineStr">
         <is>
           <t>GROSS</t>
         </is>
       </c>
       <c r="C21" s="146" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D21" s="147" t="n">
         <v>6</v>
       </c>
       <c r="E21" s="148" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F21" s="146" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G21" s="147" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H21" s="148" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="I21" s="146" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J21" s="147" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="K21" s="148" t="n">
-        <v>8</v>
-      </c>
-      <c r="L21" s="180">
+        <v>7</v>
+      </c>
+      <c r="L21" s="234">
         <f>SUM(C21:K21)</f>
         <v/>
       </c>
@@ -4652,7 +4652,7 @@
         <f>INT($D$17/18)+IF(C20&lt;=MOD($D$17,18),1,0)</f>
         <v/>
       </c>
-      <c r="D22" s="180">
+      <c r="D22" s="234">
         <f>INT($D$17/18)+IF(D20&lt;=MOD($D$17,18),1,0)</f>
         <v/>
       </c>
@@ -4664,7 +4664,7 @@
         <f>INT($D$17/18)+IF(F20&lt;=MOD($D$17,18),1,0)</f>
         <v/>
       </c>
-      <c r="G22" s="180">
+      <c r="G22" s="234">
         <f>INT($D$17/18)+IF(G20&lt;=MOD($D$17,18),1,0)</f>
         <v/>
       </c>
@@ -4676,7 +4676,7 @@
         <f>INT($D$17/18)+IF(I20&lt;=MOD($D$17,18),1,0)</f>
         <v/>
       </c>
-      <c r="J22" s="180">
+      <c r="J22" s="234">
         <f>INT($D$17/18)+IF(J20&lt;=MOD($D$17,18),1,0)</f>
         <v/>
       </c>
@@ -4708,7 +4708,7 @@
         <f>C21-C22</f>
         <v/>
       </c>
-      <c r="D23" s="180">
+      <c r="D23" s="234">
         <f>D21-D22</f>
         <v/>
       </c>
@@ -4720,7 +4720,7 @@
         <f>F21-F22</f>
         <v/>
       </c>
-      <c r="G23" s="180">
+      <c r="G23" s="234">
         <f>G21-G22</f>
         <v/>
       </c>
@@ -4732,7 +4732,7 @@
         <f>I21-I22</f>
         <v/>
       </c>
-      <c r="J23" s="180">
+      <c r="J23" s="234">
         <f>J21-J22</f>
         <v/>
       </c>
@@ -4761,7 +4761,7 @@
         <v/>
       </c>
     </row>
-    <row r="24" ht="14.25" customHeight="1" s="197" thickBot="1">
+    <row r="24" ht="14.25" customHeight="1" s="181" thickBot="1">
       <c r="B24" s="140" t="inlineStr">
         <is>
           <t>Wins Hole</t>
@@ -4803,7 +4803,7 @@
         <f>IF(K23&lt;K14,1,0)</f>
         <v/>
       </c>
-      <c r="L24" s="180" t="n"/>
+      <c r="L24" s="234" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="13">
@@ -4851,10 +4851,10 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="C2:D5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="12.75"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="13.2"/>
   <cols>
-    <col width="8.85546875" bestFit="1" customWidth="1" style="197" min="3" max="3"/>
-    <col width="14.140625" bestFit="1" customWidth="1" style="197" min="4" max="4"/>
+    <col width="8.88671875" bestFit="1" customWidth="1" style="181" min="3" max="3"/>
+    <col width="14.109375" bestFit="1" customWidth="1" style="181" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="2">
@@ -4917,43 +4917,43 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:M15"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="12.75"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="13.2"/>
   <cols>
-    <col width="18" bestFit="1" customWidth="1" style="197" min="1" max="1"/>
-    <col width="28" bestFit="1" customWidth="1" style="196" min="2" max="2"/>
-    <col width="28.5703125" bestFit="1" customWidth="1" style="197" min="3" max="3"/>
-    <col width="31.7109375" bestFit="1" customWidth="1" style="197" min="4" max="4"/>
-    <col width="29.42578125" bestFit="1" customWidth="1" style="197" min="5" max="5"/>
-    <col width="26.42578125" bestFit="1" customWidth="1" style="197" min="6" max="6"/>
-    <col width="28.85546875" bestFit="1" customWidth="1" style="197" min="7" max="7"/>
-    <col width="27.7109375" bestFit="1" customWidth="1" style="197" min="8" max="8"/>
-    <col width="28" bestFit="1" customWidth="1" style="197" min="9" max="9"/>
-    <col width="28.5703125" bestFit="1" customWidth="1" style="197" min="10" max="10"/>
-    <col width="31.7109375" bestFit="1" customWidth="1" style="197" min="11" max="11"/>
-    <col width="29.42578125" bestFit="1" customWidth="1" style="197" min="12" max="12"/>
-    <col width="26.42578125" bestFit="1" customWidth="1" style="197" min="13" max="13"/>
+    <col width="18" bestFit="1" customWidth="1" style="181" min="1" max="1"/>
+    <col width="28" bestFit="1" customWidth="1" style="180" min="2" max="2"/>
+    <col width="28.5546875" bestFit="1" customWidth="1" style="181" min="3" max="3"/>
+    <col width="31.6640625" bestFit="1" customWidth="1" style="181" min="4" max="4"/>
+    <col width="29.44140625" bestFit="1" customWidth="1" style="181" min="5" max="5"/>
+    <col width="26.44140625" bestFit="1" customWidth="1" style="181" min="6" max="6"/>
+    <col width="28.88671875" bestFit="1" customWidth="1" style="181" min="7" max="7"/>
+    <col width="27.6640625" bestFit="1" customWidth="1" style="181" min="8" max="8"/>
+    <col width="28" bestFit="1" customWidth="1" style="181" min="9" max="9"/>
+    <col width="28.5546875" bestFit="1" customWidth="1" style="181" min="10" max="10"/>
+    <col width="31.6640625" bestFit="1" customWidth="1" style="181" min="11" max="11"/>
+    <col width="29.44140625" bestFit="1" customWidth="1" style="181" min="12" max="12"/>
+    <col width="26.44140625" bestFit="1" customWidth="1" style="181" min="13" max="13"/>
   </cols>
   <sheetData>
-    <row r="1" ht="23.25" customHeight="1" s="197">
-      <c r="A1" s="193" t="inlineStr">
+    <row r="1" ht="23.25" customHeight="1" s="181">
+      <c r="A1" s="182" t="inlineStr">
         <is>
           <t>2024 Bechtel Golf League Schedule Tee Time</t>
         </is>
       </c>
-      <c r="B1" s="194" t="n"/>
-      <c r="C1" s="194" t="n"/>
-      <c r="D1" s="194" t="n"/>
-      <c r="E1" s="194" t="n"/>
-      <c r="F1" s="194" t="n"/>
-      <c r="G1" s="194" t="n"/>
-      <c r="H1" s="194" t="n"/>
-      <c r="I1" s="194" t="n"/>
-      <c r="J1" s="194" t="n"/>
-      <c r="K1" s="194" t="n"/>
-      <c r="L1" s="194" t="n"/>
-      <c r="M1" s="194" t="n"/>
-    </row>
-    <row r="2" ht="30" customFormat="1" customHeight="1" s="228">
+      <c r="B1" s="179" t="n"/>
+      <c r="C1" s="179" t="n"/>
+      <c r="D1" s="179" t="n"/>
+      <c r="E1" s="179" t="n"/>
+      <c r="F1" s="179" t="n"/>
+      <c r="G1" s="179" t="n"/>
+      <c r="H1" s="179" t="n"/>
+      <c r="I1" s="179" t="n"/>
+      <c r="J1" s="179" t="n"/>
+      <c r="K1" s="179" t="n"/>
+      <c r="L1" s="179" t="n"/>
+      <c r="M1" s="179" t="n"/>
+    </row>
+    <row r="2" ht="30" customFormat="1" customHeight="1" s="213">
       <c r="A2" s="10" t="inlineStr">
         <is>
           <t>TEE TIME</t>
@@ -4996,7 +4996,7 @@
         <v>45562</v>
       </c>
     </row>
-    <row r="3" ht="30" customHeight="1" s="197">
+    <row r="3" ht="30" customHeight="1" s="181">
       <c r="A3" s="8" t="n">
         <v>0.6666666666666666</v>
       </c>
@@ -5013,7 +5013,7 @@
       <c r="L3" s="9" t="n"/>
       <c r="M3" s="9" t="n"/>
     </row>
-    <row r="4" ht="30" customHeight="1" s="197">
+    <row r="4" ht="30" customHeight="1" s="181">
       <c r="A4" s="8" t="n">
         <v>0.6736111111111112</v>
       </c>
@@ -5030,7 +5030,7 @@
       <c r="L4" s="9" t="n"/>
       <c r="M4" s="9" t="n"/>
     </row>
-    <row r="5" ht="30" customHeight="1" s="197">
+    <row r="5" ht="30" customHeight="1" s="181">
       <c r="A5" s="8" t="n">
         <v>0.6805555555555556</v>
       </c>
@@ -5055,7 +5055,7 @@
       <c r="L5" s="9" t="n"/>
       <c r="M5" s="9" t="n"/>
     </row>
-    <row r="6" ht="30" customHeight="1" s="197">
+    <row r="6" ht="30" customHeight="1" s="181">
       <c r="A6" s="8" t="n">
         <v>0.6875</v>
       </c>
@@ -5076,7 +5076,7 @@
       <c r="L6" s="9" t="n"/>
       <c r="M6" s="9" t="n"/>
     </row>
-    <row r="7" ht="30" customHeight="1" s="197">
+    <row r="7" ht="30" customHeight="1" s="181">
       <c r="A7" s="8" t="n">
         <v>0.6944444444444444</v>
       </c>
@@ -5093,7 +5093,7 @@
       <c r="L7" s="9" t="n"/>
       <c r="M7" s="9" t="n"/>
     </row>
-    <row r="8" ht="30" customHeight="1" s="197">
+    <row r="8" ht="30" customHeight="1" s="181">
       <c r="A8" s="8" t="n">
         <v>0.7013888888888888</v>
       </c>
@@ -5110,7 +5110,7 @@
       <c r="L8" s="9" t="n"/>
       <c r="M8" s="9" t="n"/>
     </row>
-    <row r="9" ht="30" customHeight="1" s="197">
+    <row r="9" ht="30" customHeight="1" s="181">
       <c r="A9" s="8" t="n">
         <v>0.7083333333333334</v>
       </c>
@@ -5127,7 +5127,7 @@
       <c r="L9" s="9" t="n"/>
       <c r="M9" s="9" t="n"/>
     </row>
-    <row r="10" ht="30" customHeight="1" s="197">
+    <row r="10" ht="30" customHeight="1" s="181">
       <c r="A10" s="8" t="n">
         <v>0.7152777777777778</v>
       </c>
@@ -5144,7 +5144,7 @@
       <c r="L10" s="9" t="n"/>
       <c r="M10" s="9" t="n"/>
     </row>
-    <row r="11" ht="30" customHeight="1" s="197">
+    <row r="11" ht="30" customHeight="1" s="181">
       <c r="A11" s="8" t="n">
         <v>0.7222222222222222</v>
       </c>
@@ -5161,7 +5161,7 @@
       <c r="L11" s="9" t="n"/>
       <c r="M11" s="9" t="n"/>
     </row>
-    <row r="12" ht="30" customHeight="1" s="197">
+    <row r="12" ht="30" customHeight="1" s="181">
       <c r="A12" s="8" t="n">
         <v>0.7291666666666666</v>
       </c>
@@ -5178,7 +5178,7 @@
       <c r="L12" s="9" t="n"/>
       <c r="M12" s="9" t="n"/>
     </row>
-    <row r="13" ht="30" customHeight="1" s="197">
+    <row r="13" ht="30" customHeight="1" s="181">
       <c r="A13" s="8" t="n">
         <v>0.7361111111111112</v>
       </c>
@@ -5195,7 +5195,7 @@
       <c r="L13" s="9" t="n"/>
       <c r="M13" s="9" t="n"/>
     </row>
-    <row r="14" ht="30" customHeight="1" s="197">
+    <row r="14" ht="30" customHeight="1" s="181">
       <c r="A14" s="8" t="n">
         <v>0.7430555555555556</v>
       </c>
@@ -5212,7 +5212,7 @@
       <c r="L14" s="9" t="n"/>
       <c r="M14" s="9" t="n"/>
     </row>
-    <row r="15" ht="30" customHeight="1" s="197">
+    <row r="15" ht="30" customHeight="1" s="181">
       <c r="A15" s="8" t="n">
         <v>0.75</v>
       </c>
@@ -5244,43 +5244,43 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:M16"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="12.75"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="13.2"/>
   <cols>
-    <col width="24.5703125" bestFit="1" customWidth="1" style="197" min="1" max="1"/>
-    <col width="26.28515625" bestFit="1" customWidth="1" style="196" min="2" max="2"/>
-    <col width="27.140625" bestFit="1" customWidth="1" style="197" min="3" max="3"/>
-    <col width="30" bestFit="1" customWidth="1" style="197" min="4" max="4"/>
-    <col width="27.85546875" bestFit="1" customWidth="1" style="197" min="5" max="5"/>
-    <col width="24.85546875" bestFit="1" customWidth="1" style="197" min="6" max="6"/>
-    <col hidden="1" width="26.28515625" customWidth="1" style="197" min="7" max="7"/>
-    <col hidden="1" width="24.85546875" customWidth="1" style="197" min="8" max="8"/>
-    <col width="26.28515625" bestFit="1" customWidth="1" style="197" min="9" max="9"/>
-    <col width="27.140625" bestFit="1" customWidth="1" style="197" min="10" max="10"/>
-    <col width="30" bestFit="1" customWidth="1" style="197" min="11" max="11"/>
-    <col width="27.85546875" bestFit="1" customWidth="1" style="197" min="12" max="12"/>
-    <col width="24.85546875" bestFit="1" customWidth="1" style="197" min="13" max="13"/>
+    <col width="24.5546875" bestFit="1" customWidth="1" style="181" min="1" max="1"/>
+    <col width="26.33203125" bestFit="1" customWidth="1" style="180" min="2" max="2"/>
+    <col width="27.109375" bestFit="1" customWidth="1" style="181" min="3" max="3"/>
+    <col width="30" bestFit="1" customWidth="1" style="181" min="4" max="4"/>
+    <col width="27.88671875" bestFit="1" customWidth="1" style="181" min="5" max="5"/>
+    <col width="24.88671875" bestFit="1" customWidth="1" style="181" min="6" max="6"/>
+    <col hidden="1" width="26.33203125" customWidth="1" style="181" min="7" max="7"/>
+    <col hidden="1" width="24.88671875" customWidth="1" style="181" min="8" max="8"/>
+    <col width="26.33203125" bestFit="1" customWidth="1" style="181" min="9" max="9"/>
+    <col width="27.109375" bestFit="1" customWidth="1" style="181" min="10" max="10"/>
+    <col width="30" bestFit="1" customWidth="1" style="181" min="11" max="11"/>
+    <col width="27.88671875" bestFit="1" customWidth="1" style="181" min="12" max="12"/>
+    <col width="24.88671875" bestFit="1" customWidth="1" style="181" min="13" max="13"/>
   </cols>
   <sheetData>
-    <row r="1" ht="23.25" customHeight="1" s="197">
-      <c r="A1" s="193" t="inlineStr">
+    <row r="1" ht="23.25" customHeight="1" s="181">
+      <c r="A1" s="182" t="inlineStr">
         <is>
           <t>2024 Bechtel Golf League Schedule Tee Time</t>
         </is>
       </c>
-      <c r="B1" s="194" t="n"/>
-      <c r="C1" s="194" t="n"/>
-      <c r="D1" s="194" t="n"/>
-      <c r="E1" s="194" t="n"/>
-      <c r="F1" s="194" t="n"/>
-      <c r="G1" s="194" t="n"/>
-      <c r="H1" s="194" t="n"/>
-      <c r="I1" s="194" t="n"/>
-      <c r="J1" s="194" t="n"/>
-      <c r="K1" s="194" t="n"/>
-      <c r="L1" s="194" t="n"/>
-      <c r="M1" s="194" t="n"/>
-    </row>
-    <row r="2" ht="30" customFormat="1" customHeight="1" s="228">
+      <c r="B1" s="179" t="n"/>
+      <c r="C1" s="179" t="n"/>
+      <c r="D1" s="179" t="n"/>
+      <c r="E1" s="179" t="n"/>
+      <c r="F1" s="179" t="n"/>
+      <c r="G1" s="179" t="n"/>
+      <c r="H1" s="179" t="n"/>
+      <c r="I1" s="179" t="n"/>
+      <c r="J1" s="179" t="n"/>
+      <c r="K1" s="179" t="n"/>
+      <c r="L1" s="179" t="n"/>
+      <c r="M1" s="179" t="n"/>
+    </row>
+    <row r="2" ht="30" customFormat="1" customHeight="1" s="213">
       <c r="A2" s="10" t="inlineStr">
         <is>
           <t>TEE TIME</t>
@@ -5323,7 +5323,7 @@
         <v>45576</v>
       </c>
     </row>
-    <row r="3" ht="30" customHeight="1" s="197">
+    <row r="3" ht="30" customHeight="1" s="181">
       <c r="A3" s="8" t="n">
         <v>0.6597222222222222</v>
       </c>
@@ -5344,7 +5344,7 @@
       </c>
       <c r="M3" s="9" t="n"/>
     </row>
-    <row r="4" ht="30" customHeight="1" s="197">
+    <row r="4" ht="30" customHeight="1" s="181">
       <c r="A4" s="8" t="n">
         <v>0.6666666666666666</v>
       </c>
@@ -5361,7 +5361,7 @@
       <c r="L4" s="9" t="n"/>
       <c r="M4" s="9" t="n"/>
     </row>
-    <row r="5" ht="30" customHeight="1" s="197">
+    <row r="5" ht="30" customHeight="1" s="181">
       <c r="A5" s="8" t="n">
         <v>0.6736111111111112</v>
       </c>
@@ -5378,7 +5378,7 @@
       <c r="L5" s="9" t="n"/>
       <c r="M5" s="9" t="n"/>
     </row>
-    <row r="6" ht="30" customHeight="1" s="197">
+    <row r="6" ht="30" customHeight="1" s="181">
       <c r="A6" s="8" t="n">
         <v>0.6805555555555556</v>
       </c>
@@ -5395,7 +5395,7 @@
       <c r="L6" s="9" t="n"/>
       <c r="M6" s="9" t="n"/>
     </row>
-    <row r="7" ht="30" customHeight="1" s="197">
+    <row r="7" ht="30" customHeight="1" s="181">
       <c r="A7" s="8" t="n">
         <v>0.6875</v>
       </c>
@@ -5412,7 +5412,7 @@
       <c r="L7" s="9" t="n"/>
       <c r="M7" s="9" t="n"/>
     </row>
-    <row r="8" ht="30" customHeight="1" s="197">
+    <row r="8" ht="30" customHeight="1" s="181">
       <c r="A8" s="8" t="n">
         <v>0.6944444444444444</v>
       </c>
@@ -5429,7 +5429,7 @@
       <c r="L8" s="9" t="n"/>
       <c r="M8" s="9" t="n"/>
     </row>
-    <row r="9" ht="30" customHeight="1" s="197">
+    <row r="9" ht="30" customHeight="1" s="181">
       <c r="A9" s="8" t="n">
         <v>0.7013888888888888</v>
       </c>
@@ -5446,7 +5446,7 @@
       <c r="L9" s="9" t="n"/>
       <c r="M9" s="9" t="n"/>
     </row>
-    <row r="10" ht="30" customHeight="1" s="197">
+    <row r="10" ht="30" customHeight="1" s="181">
       <c r="A10" s="8" t="n">
         <v>0.7083333333333334</v>
       </c>
@@ -5463,7 +5463,7 @@
       <c r="L10" s="9" t="n"/>
       <c r="M10" s="9" t="n"/>
     </row>
-    <row r="11" ht="30" customHeight="1" s="197">
+    <row r="11" ht="30" customHeight="1" s="181">
       <c r="A11" s="8" t="n">
         <v>0.7152777777777778</v>
       </c>
@@ -5480,7 +5480,7 @@
       <c r="L11" s="9" t="n"/>
       <c r="M11" s="9" t="n"/>
     </row>
-    <row r="12" ht="30" customHeight="1" s="197">
+    <row r="12" ht="30" customHeight="1" s="181">
       <c r="A12" s="8" t="n">
         <v>0.7222222222222222</v>
       </c>
@@ -5497,7 +5497,7 @@
       <c r="L12" s="9" t="n"/>
       <c r="M12" s="9" t="n"/>
     </row>
-    <row r="13" ht="30" customHeight="1" s="197">
+    <row r="13" ht="30" customHeight="1" s="181">
       <c r="A13" s="8" t="n">
         <v>0.7291666666666666</v>
       </c>
@@ -5514,7 +5514,7 @@
       <c r="L13" s="9" t="n"/>
       <c r="M13" s="9" t="n"/>
     </row>
-    <row r="14" ht="30" customHeight="1" s="197">
+    <row r="14" ht="30" customHeight="1" s="181">
       <c r="A14" s="8" t="n">
         <v>0.7361111111111112</v>
       </c>
@@ -5531,7 +5531,7 @@
       <c r="L14" s="9" t="n"/>
       <c r="M14" s="9" t="n"/>
     </row>
-    <row r="15" ht="30" customHeight="1" s="197">
+    <row r="15" ht="30" customHeight="1" s="181">
       <c r="A15" s="8" t="n">
         <v>0.7430555555555556</v>
       </c>
@@ -5548,7 +5548,7 @@
       <c r="L15" s="9" t="n"/>
       <c r="M15" s="9" t="n"/>
     </row>
-    <row r="16" ht="30" customHeight="1" s="197">
+    <row r="16" ht="30" customHeight="1" s="181">
       <c r="A16" s="8" t="n">
         <v>0.75</v>
       </c>
@@ -5580,43 +5580,43 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:M16"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="12.75"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="13.2"/>
   <cols>
-    <col width="24.5703125" bestFit="1" customWidth="1" style="197" min="1" max="1"/>
-    <col width="26.28515625" bestFit="1" customWidth="1" style="196" min="2" max="2"/>
-    <col width="27.140625" bestFit="1" customWidth="1" style="197" min="3" max="3"/>
-    <col width="30" bestFit="1" customWidth="1" style="197" min="4" max="4"/>
-    <col width="27.85546875" bestFit="1" customWidth="1" style="197" min="5" max="5"/>
-    <col width="24.85546875" bestFit="1" customWidth="1" style="197" min="6" max="6"/>
-    <col hidden="1" width="26.28515625" customWidth="1" style="197" min="7" max="7"/>
-    <col hidden="1" width="24.85546875" customWidth="1" style="197" min="8" max="8"/>
-    <col width="26.28515625" bestFit="1" customWidth="1" style="197" min="9" max="9"/>
-    <col width="27.140625" bestFit="1" customWidth="1" style="197" min="10" max="10"/>
-    <col width="30" bestFit="1" customWidth="1" style="197" min="11" max="11"/>
-    <col width="27.85546875" customWidth="1" style="197" min="12" max="12"/>
-    <col width="24.85546875" bestFit="1" customWidth="1" style="197" min="13" max="13"/>
+    <col width="24.5546875" bestFit="1" customWidth="1" style="181" min="1" max="1"/>
+    <col width="26.33203125" bestFit="1" customWidth="1" style="180" min="2" max="2"/>
+    <col width="27.109375" bestFit="1" customWidth="1" style="181" min="3" max="3"/>
+    <col width="30" bestFit="1" customWidth="1" style="181" min="4" max="4"/>
+    <col width="27.88671875" bestFit="1" customWidth="1" style="181" min="5" max="5"/>
+    <col width="24.88671875" bestFit="1" customWidth="1" style="181" min="6" max="6"/>
+    <col hidden="1" width="26.33203125" customWidth="1" style="181" min="7" max="7"/>
+    <col hidden="1" width="24.88671875" customWidth="1" style="181" min="8" max="8"/>
+    <col width="26.33203125" bestFit="1" customWidth="1" style="181" min="9" max="9"/>
+    <col width="27.109375" bestFit="1" customWidth="1" style="181" min="10" max="10"/>
+    <col width="30" bestFit="1" customWidth="1" style="181" min="11" max="11"/>
+    <col width="27.88671875" customWidth="1" style="181" min="12" max="12"/>
+    <col width="24.88671875" bestFit="1" customWidth="1" style="181" min="13" max="13"/>
   </cols>
   <sheetData>
-    <row r="1" ht="23.25" customHeight="1" s="197">
-      <c r="A1" s="193" t="inlineStr">
+    <row r="1" ht="23.25" customHeight="1" s="181">
+      <c r="A1" s="182" t="inlineStr">
         <is>
           <t>2024 Bechtel Golf League Schedule Tee Time</t>
         </is>
       </c>
-      <c r="B1" s="194" t="n"/>
-      <c r="C1" s="194" t="n"/>
-      <c r="D1" s="194" t="n"/>
-      <c r="E1" s="194" t="n"/>
-      <c r="F1" s="194" t="n"/>
-      <c r="G1" s="194" t="n"/>
-      <c r="H1" s="194" t="n"/>
-      <c r="I1" s="194" t="n"/>
-      <c r="J1" s="194" t="n"/>
-      <c r="K1" s="194" t="n"/>
-      <c r="L1" s="194" t="n"/>
-      <c r="M1" s="194" t="n"/>
-    </row>
-    <row r="2" ht="30" customFormat="1" customHeight="1" s="228">
+      <c r="B1" s="179" t="n"/>
+      <c r="C1" s="179" t="n"/>
+      <c r="D1" s="179" t="n"/>
+      <c r="E1" s="179" t="n"/>
+      <c r="F1" s="179" t="n"/>
+      <c r="G1" s="179" t="n"/>
+      <c r="H1" s="179" t="n"/>
+      <c r="I1" s="179" t="n"/>
+      <c r="J1" s="179" t="n"/>
+      <c r="K1" s="179" t="n"/>
+      <c r="L1" s="179" t="n"/>
+      <c r="M1" s="179" t="n"/>
+    </row>
+    <row r="2" ht="30" customFormat="1" customHeight="1" s="213">
       <c r="A2" s="10" t="inlineStr">
         <is>
           <t>TEE TIME</t>
@@ -5659,7 +5659,7 @@
         <v>45590</v>
       </c>
     </row>
-    <row r="3" ht="30" customFormat="1" customHeight="1" s="228">
+    <row r="3" ht="30" customFormat="1" customHeight="1" s="213">
       <c r="A3" s="8" t="n">
         <v>0.6597222222222222</v>
       </c>
@@ -5688,7 +5688,7 @@
       <c r="L3" s="30" t="n"/>
       <c r="M3" s="30" t="n"/>
     </row>
-    <row r="4" ht="30" customHeight="1" s="197">
+    <row r="4" ht="30" customHeight="1" s="181">
       <c r="A4" s="8" t="n">
         <v>0.6666666666666666</v>
       </c>
@@ -5705,7 +5705,7 @@
       <c r="L4" s="9" t="n"/>
       <c r="M4" s="9" t="n"/>
     </row>
-    <row r="5" ht="30" customHeight="1" s="197">
+    <row r="5" ht="30" customHeight="1" s="181">
       <c r="A5" s="8" t="n">
         <v>0.6736111111111112</v>
       </c>
@@ -5722,7 +5722,7 @@
       <c r="L5" s="9" t="n"/>
       <c r="M5" s="9" t="n"/>
     </row>
-    <row r="6" ht="30" customHeight="1" s="197">
+    <row r="6" ht="30" customHeight="1" s="181">
       <c r="A6" s="8" t="n">
         <v>0.6805555555555556</v>
       </c>
@@ -5739,7 +5739,7 @@
       <c r="L6" s="9" t="n"/>
       <c r="M6" s="9" t="n"/>
     </row>
-    <row r="7" ht="30" customHeight="1" s="197">
+    <row r="7" ht="30" customHeight="1" s="181">
       <c r="A7" s="8" t="n">
         <v>0.6875</v>
       </c>
@@ -5756,7 +5756,7 @@
       <c r="L7" s="9" t="n"/>
       <c r="M7" s="9" t="n"/>
     </row>
-    <row r="8" ht="30" customHeight="1" s="197">
+    <row r="8" ht="30" customHeight="1" s="181">
       <c r="A8" s="8" t="n">
         <v>0.6944444444444444</v>
       </c>
@@ -5773,7 +5773,7 @@
       <c r="L8" s="9" t="n"/>
       <c r="M8" s="9" t="n"/>
     </row>
-    <row r="9" ht="30" customHeight="1" s="197">
+    <row r="9" ht="30" customHeight="1" s="181">
       <c r="A9" s="8" t="n">
         <v>0.7013888888888888</v>
       </c>
@@ -5790,7 +5790,7 @@
       <c r="L9" s="9" t="n"/>
       <c r="M9" s="9" t="n"/>
     </row>
-    <row r="10" ht="30" customHeight="1" s="197">
+    <row r="10" ht="30" customHeight="1" s="181">
       <c r="A10" s="8" t="n">
         <v>0.7083333333333334</v>
       </c>
@@ -5807,7 +5807,7 @@
       <c r="L10" s="9" t="n"/>
       <c r="M10" s="9" t="n"/>
     </row>
-    <row r="11" ht="30" customHeight="1" s="197">
+    <row r="11" ht="30" customHeight="1" s="181">
       <c r="A11" s="8" t="n">
         <v>0.7152777777777778</v>
       </c>
@@ -5824,7 +5824,7 @@
       <c r="L11" s="9" t="n"/>
       <c r="M11" s="9" t="n"/>
     </row>
-    <row r="12" ht="30" customHeight="1" s="197">
+    <row r="12" ht="30" customHeight="1" s="181">
       <c r="A12" s="8" t="n">
         <v>0.7222222222222222</v>
       </c>
@@ -5841,7 +5841,7 @@
       <c r="L12" s="9" t="n"/>
       <c r="M12" s="9" t="n"/>
     </row>
-    <row r="13" ht="30" customHeight="1" s="197">
+    <row r="13" ht="30" customHeight="1" s="181">
       <c r="A13" s="8" t="n">
         <v>0.7291666666666666</v>
       </c>
@@ -5858,7 +5858,7 @@
       <c r="L13" s="9" t="n"/>
       <c r="M13" s="9" t="n"/>
     </row>
-    <row r="14" ht="30" customHeight="1" s="197">
+    <row r="14" ht="30" customHeight="1" s="181">
       <c r="A14" s="8" t="n">
         <v>0.7361111111111112</v>
       </c>
@@ -5875,7 +5875,7 @@
       <c r="L14" s="9" t="n"/>
       <c r="M14" s="9" t="n"/>
     </row>
-    <row r="15" ht="30" customHeight="1" s="197">
+    <row r="15" ht="30" customHeight="1" s="181">
       <c r="A15" s="8" t="n">
         <v>0.7430555555555556</v>
       </c>
@@ -5892,7 +5892,7 @@
       <c r="L15" s="9" t="n"/>
       <c r="M15" s="9" t="n"/>
     </row>
-    <row r="16" ht="30" customHeight="1" s="197">
+    <row r="16" ht="30" customHeight="1" s="181">
       <c r="A16" s="8" t="n">
         <v>0.75</v>
       </c>
@@ -5924,43 +5924,43 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:M15"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="12.75"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="13.2"/>
   <cols>
-    <col width="18" bestFit="1" customWidth="1" style="197" min="1" max="1"/>
-    <col width="27" bestFit="1" customWidth="1" style="196" min="2" max="2"/>
-    <col width="27.7109375" bestFit="1" customWidth="1" style="197" min="3" max="3"/>
-    <col width="30.7109375" bestFit="1" customWidth="1" style="197" min="4" max="4"/>
-    <col width="28.5703125" bestFit="1" customWidth="1" style="197" min="5" max="5"/>
-    <col width="25.140625" bestFit="1" customWidth="1" style="197" min="6" max="6"/>
-    <col width="27.85546875" bestFit="1" customWidth="1" style="197" min="7" max="7"/>
-    <col width="26.5703125" bestFit="1" customWidth="1" style="197" min="8" max="8"/>
-    <col width="27" bestFit="1" customWidth="1" style="197" min="9" max="9"/>
-    <col width="28.7109375" bestFit="1" customWidth="1" style="197" min="10" max="10"/>
-    <col width="31.7109375" bestFit="1" customWidth="1" style="197" min="11" max="11"/>
-    <col width="29.5703125" bestFit="1" customWidth="1" style="197" min="12" max="12"/>
-    <col width="26.42578125" bestFit="1" customWidth="1" style="197" min="13" max="13"/>
+    <col width="18" bestFit="1" customWidth="1" style="181" min="1" max="1"/>
+    <col width="27" bestFit="1" customWidth="1" style="180" min="2" max="2"/>
+    <col width="27.6640625" bestFit="1" customWidth="1" style="181" min="3" max="3"/>
+    <col width="30.6640625" bestFit="1" customWidth="1" style="181" min="4" max="4"/>
+    <col width="28.5546875" bestFit="1" customWidth="1" style="181" min="5" max="5"/>
+    <col width="25.109375" bestFit="1" customWidth="1" style="181" min="6" max="6"/>
+    <col width="27.88671875" bestFit="1" customWidth="1" style="181" min="7" max="7"/>
+    <col width="26.5546875" bestFit="1" customWidth="1" style="181" min="8" max="8"/>
+    <col width="27" bestFit="1" customWidth="1" style="181" min="9" max="9"/>
+    <col width="28.6640625" bestFit="1" customWidth="1" style="181" min="10" max="10"/>
+    <col width="31.6640625" bestFit="1" customWidth="1" style="181" min="11" max="11"/>
+    <col width="29.5546875" bestFit="1" customWidth="1" style="181" min="12" max="12"/>
+    <col width="26.44140625" bestFit="1" customWidth="1" style="181" min="13" max="13"/>
   </cols>
   <sheetData>
-    <row r="1" ht="23.25" customHeight="1" s="197">
-      <c r="A1" s="193" t="inlineStr">
+    <row r="1" ht="23.25" customHeight="1" s="181">
+      <c r="A1" s="182" t="inlineStr">
         <is>
           <t>2024 Bechtel Golf League Schedule Tee Time</t>
         </is>
       </c>
-      <c r="B1" s="194" t="n"/>
-      <c r="C1" s="194" t="n"/>
-      <c r="D1" s="194" t="n"/>
-      <c r="E1" s="194" t="n"/>
-      <c r="F1" s="194" t="n"/>
-      <c r="G1" s="194" t="n"/>
-      <c r="H1" s="194" t="n"/>
-      <c r="I1" s="194" t="n"/>
-      <c r="J1" s="194" t="n"/>
-      <c r="K1" s="194" t="n"/>
-      <c r="L1" s="194" t="n"/>
-      <c r="M1" s="194" t="n"/>
-    </row>
-    <row r="2" ht="30" customFormat="1" customHeight="1" s="228">
+      <c r="B1" s="179" t="n"/>
+      <c r="C1" s="179" t="n"/>
+      <c r="D1" s="179" t="n"/>
+      <c r="E1" s="179" t="n"/>
+      <c r="F1" s="179" t="n"/>
+      <c r="G1" s="179" t="n"/>
+      <c r="H1" s="179" t="n"/>
+      <c r="I1" s="179" t="n"/>
+      <c r="J1" s="179" t="n"/>
+      <c r="K1" s="179" t="n"/>
+      <c r="L1" s="179" t="n"/>
+      <c r="M1" s="179" t="n"/>
+    </row>
+    <row r="2" ht="30" customFormat="1" customHeight="1" s="213">
       <c r="A2" s="10" t="inlineStr">
         <is>
           <t>TEE TIME</t>
@@ -6003,7 +6003,7 @@
         <v>45548</v>
       </c>
     </row>
-    <row r="3" ht="15" customHeight="1" s="197">
+    <row r="3" ht="15" customHeight="1" s="181">
       <c r="A3" s="8" t="n">
         <v>0.6666666666666666</v>
       </c>
@@ -6024,7 +6024,7 @@
       <c r="L3" s="9" t="n"/>
       <c r="M3" s="9" t="n"/>
     </row>
-    <row r="4" ht="15" customHeight="1" s="197">
+    <row r="4" ht="15" customHeight="1" s="181">
       <c r="A4" s="8" t="n">
         <v>0.6736111111111112</v>
       </c>
@@ -6041,7 +6041,7 @@
       <c r="L4" s="9" t="n"/>
       <c r="M4" s="9" t="n"/>
     </row>
-    <row r="5" ht="30" customHeight="1" s="197">
+    <row r="5" ht="30" customHeight="1" s="181">
       <c r="A5" s="8" t="n">
         <v>0.6805555555555556</v>
       </c>
@@ -6062,7 +6062,7 @@
       <c r="L5" s="9" t="n"/>
       <c r="M5" s="9" t="n"/>
     </row>
-    <row r="6" ht="15" customHeight="1" s="197">
+    <row r="6" ht="15" customHeight="1" s="181">
       <c r="A6" s="8" t="n">
         <v>0.6875</v>
       </c>
@@ -6083,7 +6083,7 @@
       <c r="L6" s="9" t="n"/>
       <c r="M6" s="9" t="n"/>
     </row>
-    <row r="7" ht="45" customHeight="1" s="197">
+    <row r="7" ht="45" customHeight="1" s="181">
       <c r="A7" s="8" t="n">
         <v>0.6944444444444444</v>
       </c>
@@ -6104,7 +6104,7 @@
       <c r="L7" s="9" t="n"/>
       <c r="M7" s="9" t="n"/>
     </row>
-    <row r="8" ht="15" customHeight="1" s="197">
+    <row r="8" ht="15" customHeight="1" s="181">
       <c r="A8" s="8" t="n">
         <v>0.7013888888888888</v>
       </c>
@@ -6121,7 +6121,7 @@
       <c r="L8" s="9" t="n"/>
       <c r="M8" s="9" t="n"/>
     </row>
-    <row r="9" ht="15" customHeight="1" s="197">
+    <row r="9" ht="15" customHeight="1" s="181">
       <c r="A9" s="8" t="n">
         <v>0.7083333333333334</v>
       </c>
@@ -6138,7 +6138,7 @@
       <c r="L9" s="9" t="n"/>
       <c r="M9" s="9" t="n"/>
     </row>
-    <row r="10" ht="15" customHeight="1" s="197">
+    <row r="10" ht="15" customHeight="1" s="181">
       <c r="A10" s="8" t="n">
         <v>0.7152777777777778</v>
       </c>
@@ -6155,7 +6155,7 @@
       <c r="L10" s="9" t="n"/>
       <c r="M10" s="9" t="n"/>
     </row>
-    <row r="11" ht="15" customHeight="1" s="197">
+    <row r="11" ht="15" customHeight="1" s="181">
       <c r="A11" s="8" t="n">
         <v>0.7222222222222222</v>
       </c>
@@ -6172,7 +6172,7 @@
       <c r="L11" s="9" t="n"/>
       <c r="M11" s="9" t="n"/>
     </row>
-    <row r="12" ht="15" customHeight="1" s="197">
+    <row r="12" ht="15" customHeight="1" s="181">
       <c r="A12" s="8" t="n">
         <v>0.7291666666666666</v>
       </c>
@@ -6189,7 +6189,7 @@
       <c r="L12" s="9" t="n"/>
       <c r="M12" s="9" t="n"/>
     </row>
-    <row r="13" ht="15" customHeight="1" s="197">
+    <row r="13" ht="15" customHeight="1" s="181">
       <c r="A13" s="8" t="n">
         <v>0.7361111111111112</v>
       </c>
@@ -6206,7 +6206,7 @@
       <c r="L13" s="9" t="n"/>
       <c r="M13" s="9" t="n"/>
     </row>
-    <row r="14" ht="15" customHeight="1" s="197">
+    <row r="14" ht="15" customHeight="1" s="181">
       <c r="A14" s="8" t="n">
         <v>0.7430555555555556</v>
       </c>
@@ -6223,7 +6223,7 @@
       <c r="L14" s="9" t="n"/>
       <c r="M14" s="9" t="n"/>
     </row>
-    <row r="15" ht="15" customHeight="1" s="197">
+    <row r="15" ht="15" customHeight="1" s="181">
       <c r="A15" s="8" t="n">
         <v>0.75</v>
       </c>
@@ -6255,43 +6255,43 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:M15"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="12.75"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="13.2"/>
   <cols>
-    <col width="24.5703125" bestFit="1" customWidth="1" style="197" min="1" max="1"/>
-    <col width="21.140625" bestFit="1" customWidth="1" style="196" min="2" max="2"/>
-    <col width="21.7109375" bestFit="1" customWidth="1" style="197" min="3" max="3"/>
-    <col width="24.5703125" bestFit="1" customWidth="1" style="197" min="4" max="4"/>
-    <col width="22.28515625" bestFit="1" customWidth="1" style="197" min="5" max="5"/>
-    <col width="19.5703125" bestFit="1" customWidth="1" style="197" min="6" max="6"/>
-    <col hidden="1" width="22.140625" customWidth="1" style="197" min="7" max="7"/>
-    <col hidden="1" width="20.7109375" customWidth="1" style="197" min="8" max="8"/>
-    <col width="21" bestFit="1" customWidth="1" style="197" min="9" max="9"/>
-    <col width="21.5703125" bestFit="1" customWidth="1" style="197" min="10" max="10"/>
-    <col width="24.5703125" bestFit="1" customWidth="1" style="197" min="11" max="11"/>
-    <col width="24.28515625" bestFit="1" customWidth="1" style="197" min="12" max="12"/>
-    <col width="21.140625" bestFit="1" customWidth="1" style="197" min="13" max="13"/>
+    <col width="24.5546875" bestFit="1" customWidth="1" style="181" min="1" max="1"/>
+    <col width="21.109375" bestFit="1" customWidth="1" style="180" min="2" max="2"/>
+    <col width="21.6640625" bestFit="1" customWidth="1" style="181" min="3" max="3"/>
+    <col width="24.5546875" bestFit="1" customWidth="1" style="181" min="4" max="4"/>
+    <col width="22.33203125" bestFit="1" customWidth="1" style="181" min="5" max="5"/>
+    <col width="19.5546875" bestFit="1" customWidth="1" style="181" min="6" max="6"/>
+    <col hidden="1" width="22.109375" customWidth="1" style="181" min="7" max="7"/>
+    <col hidden="1" width="20.6640625" customWidth="1" style="181" min="8" max="8"/>
+    <col width="21" bestFit="1" customWidth="1" style="181" min="9" max="9"/>
+    <col width="21.5546875" bestFit="1" customWidth="1" style="181" min="10" max="10"/>
+    <col width="24.5546875" bestFit="1" customWidth="1" style="181" min="11" max="11"/>
+    <col width="24.33203125" bestFit="1" customWidth="1" style="181" min="12" max="12"/>
+    <col width="21.109375" bestFit="1" customWidth="1" style="181" min="13" max="13"/>
   </cols>
   <sheetData>
-    <row r="1" ht="23.25" customHeight="1" s="197">
-      <c r="A1" s="193" t="inlineStr">
+    <row r="1" ht="23.25" customHeight="1" s="181">
+      <c r="A1" s="182" t="inlineStr">
         <is>
           <t>2024 Bechtel Golf League Schedule Tee Time</t>
         </is>
       </c>
-      <c r="B1" s="194" t="n"/>
-      <c r="C1" s="194" t="n"/>
-      <c r="D1" s="194" t="n"/>
-      <c r="E1" s="194" t="n"/>
-      <c r="F1" s="194" t="n"/>
-      <c r="G1" s="194" t="n"/>
-      <c r="H1" s="194" t="n"/>
-      <c r="I1" s="194" t="n"/>
-      <c r="J1" s="194" t="n"/>
-      <c r="K1" s="194" t="n"/>
-      <c r="L1" s="194" t="n"/>
-      <c r="M1" s="194" t="n"/>
-    </row>
-    <row r="2" ht="30" customFormat="1" customHeight="1" s="228">
+      <c r="B1" s="179" t="n"/>
+      <c r="C1" s="179" t="n"/>
+      <c r="D1" s="179" t="n"/>
+      <c r="E1" s="179" t="n"/>
+      <c r="F1" s="179" t="n"/>
+      <c r="G1" s="179" t="n"/>
+      <c r="H1" s="179" t="n"/>
+      <c r="I1" s="179" t="n"/>
+      <c r="J1" s="179" t="n"/>
+      <c r="K1" s="179" t="n"/>
+      <c r="L1" s="179" t="n"/>
+      <c r="M1" s="179" t="n"/>
+    </row>
+    <row r="2" ht="30" customFormat="1" customHeight="1" s="213">
       <c r="A2" s="10" t="inlineStr">
         <is>
           <t>TEE TIME</t>
@@ -6334,7 +6334,7 @@
         <v>45506</v>
       </c>
     </row>
-    <row r="3" ht="30" customHeight="1" s="197">
+    <row r="3" ht="30" customHeight="1" s="181">
       <c r="A3" s="8" t="n">
         <v>0.6666666666666666</v>
       </c>
@@ -6355,7 +6355,7 @@
       <c r="L3" s="9" t="n"/>
       <c r="M3" s="9" t="n"/>
     </row>
-    <row r="4" ht="30" customHeight="1" s="197">
+    <row r="4" ht="30" customHeight="1" s="181">
       <c r="A4" s="8" t="n">
         <v>0.6736111111111112</v>
       </c>
@@ -6372,7 +6372,7 @@
       <c r="L4" s="9" t="n"/>
       <c r="M4" s="9" t="n"/>
     </row>
-    <row r="5" ht="30" customHeight="1" s="197">
+    <row r="5" ht="30" customHeight="1" s="181">
       <c r="A5" s="8" t="n">
         <v>0.6805555555555556</v>
       </c>
@@ -6389,7 +6389,7 @@
       <c r="L5" s="9" t="n"/>
       <c r="M5" s="9" t="n"/>
     </row>
-    <row r="6" ht="30" customHeight="1" s="197">
+    <row r="6" ht="30" customHeight="1" s="181">
       <c r="A6" s="8" t="n">
         <v>0.6875</v>
       </c>
@@ -6414,7 +6414,7 @@
       <c r="L6" s="9" t="n"/>
       <c r="M6" s="9" t="n"/>
     </row>
-    <row r="7" ht="30" customHeight="1" s="197">
+    <row r="7" ht="30" customHeight="1" s="181">
       <c r="A7" s="8" t="n">
         <v>0.6944444444444444</v>
       </c>
@@ -6439,7 +6439,7 @@
       <c r="L7" s="9" t="n"/>
       <c r="M7" s="9" t="n"/>
     </row>
-    <row r="8" ht="30" customHeight="1" s="197">
+    <row r="8" ht="30" customHeight="1" s="181">
       <c r="A8" s="8" t="n">
         <v>0.7013888888888888</v>
       </c>
@@ -6456,7 +6456,7 @@
       <c r="L8" s="9" t="n"/>
       <c r="M8" s="9" t="n"/>
     </row>
-    <row r="9" ht="30" customHeight="1" s="197">
+    <row r="9" ht="30" customHeight="1" s="181">
       <c r="A9" s="8" t="n">
         <v>0.7083333333333334</v>
       </c>
@@ -6473,7 +6473,7 @@
       <c r="L9" s="9" t="n"/>
       <c r="M9" s="9" t="n"/>
     </row>
-    <row r="10" ht="30" customHeight="1" s="197">
+    <row r="10" ht="30" customHeight="1" s="181">
       <c r="A10" s="8" t="n">
         <v>0.7152777777777778</v>
       </c>
@@ -6490,7 +6490,7 @@
       <c r="L10" s="9" t="n"/>
       <c r="M10" s="9" t="n"/>
     </row>
-    <row r="11" ht="30" customHeight="1" s="197">
+    <row r="11" ht="30" customHeight="1" s="181">
       <c r="A11" s="8" t="n">
         <v>0.7222222222222222</v>
       </c>
@@ -6507,7 +6507,7 @@
       <c r="L11" s="9" t="n"/>
       <c r="M11" s="9" t="n"/>
     </row>
-    <row r="12" ht="30" customHeight="1" s="197">
+    <row r="12" ht="30" customHeight="1" s="181">
       <c r="A12" s="8" t="n">
         <v>0.7291666666666666</v>
       </c>
@@ -6524,7 +6524,7 @@
       <c r="L12" s="9" t="n"/>
       <c r="M12" s="9" t="n"/>
     </row>
-    <row r="13" ht="30" customHeight="1" s="197">
+    <row r="13" ht="30" customHeight="1" s="181">
       <c r="A13" s="8" t="n">
         <v>0.7361111111111112</v>
       </c>
@@ -6541,7 +6541,7 @@
       <c r="L13" s="9" t="n"/>
       <c r="M13" s="9" t="n"/>
     </row>
-    <row r="14" ht="30" customHeight="1" s="197">
+    <row r="14" ht="30" customHeight="1" s="181">
       <c r="A14" s="8" t="n">
         <v>0.7430555555555556</v>
       </c>
@@ -6558,7 +6558,7 @@
       <c r="L14" s="9" t="n"/>
       <c r="M14" s="9" t="n"/>
     </row>
-    <row r="15" ht="30" customHeight="1" s="197">
+    <row r="15" ht="30" customHeight="1" s="181">
       <c r="A15" s="8" t="n">
         <v>0.75</v>
       </c>
@@ -6590,33 +6590,33 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:M15"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="12.75"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="13.2"/>
   <cols>
-    <col width="24.5703125" bestFit="1" customWidth="1" style="197" min="1" max="1"/>
-    <col width="25.7109375" customWidth="1" style="196" min="2" max="2"/>
-    <col width="25.7109375" customWidth="1" style="197" min="3" max="13"/>
+    <col width="24.5546875" bestFit="1" customWidth="1" style="181" min="1" max="1"/>
+    <col width="25.6640625" customWidth="1" style="180" min="2" max="2"/>
+    <col width="25.6640625" customWidth="1" style="181" min="3" max="13"/>
   </cols>
   <sheetData>
-    <row r="1" ht="23.25" customHeight="1" s="197">
-      <c r="A1" s="193" t="inlineStr">
+    <row r="1" ht="23.25" customHeight="1" s="181">
+      <c r="A1" s="182" t="inlineStr">
         <is>
           <t>2024 Bechtel Golf League Schedule Tee Time</t>
         </is>
       </c>
-      <c r="B1" s="194" t="n"/>
-      <c r="C1" s="194" t="n"/>
-      <c r="D1" s="194" t="n"/>
-      <c r="E1" s="194" t="n"/>
-      <c r="F1" s="194" t="n"/>
-      <c r="G1" s="194" t="n"/>
-      <c r="H1" s="194" t="n"/>
-      <c r="I1" s="194" t="n"/>
-      <c r="J1" s="194" t="n"/>
-      <c r="K1" s="194" t="n"/>
-      <c r="L1" s="194" t="n"/>
-      <c r="M1" s="194" t="n"/>
-    </row>
-    <row r="2" ht="30" customFormat="1" customHeight="1" s="228">
+      <c r="B1" s="179" t="n"/>
+      <c r="C1" s="179" t="n"/>
+      <c r="D1" s="179" t="n"/>
+      <c r="E1" s="179" t="n"/>
+      <c r="F1" s="179" t="n"/>
+      <c r="G1" s="179" t="n"/>
+      <c r="H1" s="179" t="n"/>
+      <c r="I1" s="179" t="n"/>
+      <c r="J1" s="179" t="n"/>
+      <c r="K1" s="179" t="n"/>
+      <c r="L1" s="179" t="n"/>
+      <c r="M1" s="179" t="n"/>
+    </row>
+    <row r="2" ht="30" customFormat="1" customHeight="1" s="213">
       <c r="A2" s="10" t="inlineStr">
         <is>
           <t>TEE TIME</t>
@@ -6659,7 +6659,7 @@
         <v>45520</v>
       </c>
     </row>
-    <row r="3" ht="30" customHeight="1" s="197">
+    <row r="3" ht="30" customHeight="1" s="181">
       <c r="A3" s="8" t="n">
         <v>0.6666666666666666</v>
       </c>
@@ -6680,7 +6680,7 @@
       <c r="L3" s="9" t="n"/>
       <c r="M3" s="9" t="n"/>
     </row>
-    <row r="4" ht="30" customHeight="1" s="197">
+    <row r="4" ht="30" customHeight="1" s="181">
       <c r="A4" s="8" t="n">
         <v>0.6736111111111112</v>
       </c>
@@ -6697,7 +6697,7 @@
       <c r="L4" s="9" t="n"/>
       <c r="M4" s="9" t="n"/>
     </row>
-    <row r="5" ht="30" customHeight="1" s="197">
+    <row r="5" ht="30" customHeight="1" s="181">
       <c r="A5" s="8" t="n">
         <v>0.6805555555555556</v>
       </c>
@@ -6718,7 +6718,7 @@
       <c r="L5" s="9" t="n"/>
       <c r="M5" s="9" t="n"/>
     </row>
-    <row r="6" ht="30" customHeight="1" s="197">
+    <row r="6" ht="30" customHeight="1" s="181">
       <c r="A6" s="8" t="n">
         <v>0.6875</v>
       </c>
@@ -6740,7 +6740,7 @@
       <c r="L6" s="9" t="n"/>
       <c r="M6" s="9" t="n"/>
     </row>
-    <row r="7" ht="30" customHeight="1" s="197">
+    <row r="7" ht="30" customHeight="1" s="181">
       <c r="A7" s="8" t="n">
         <v>0.6944444444444444</v>
       </c>
@@ -6766,7 +6766,7 @@
       <c r="L7" s="9" t="n"/>
       <c r="M7" s="9" t="n"/>
     </row>
-    <row r="8" ht="30" customHeight="1" s="197">
+    <row r="8" ht="30" customHeight="1" s="181">
       <c r="A8" s="8" t="n">
         <v>0.7013888888888888</v>
       </c>
@@ -6783,7 +6783,7 @@
       <c r="L8" s="9" t="n"/>
       <c r="M8" s="9" t="n"/>
     </row>
-    <row r="9" ht="30" customHeight="1" s="197">
+    <row r="9" ht="30" customHeight="1" s="181">
       <c r="A9" s="8" t="n">
         <v>0.7083333333333334</v>
       </c>
@@ -6800,7 +6800,7 @@
       <c r="L9" s="9" t="n"/>
       <c r="M9" s="9" t="n"/>
     </row>
-    <row r="10" ht="30" customHeight="1" s="197">
+    <row r="10" ht="30" customHeight="1" s="181">
       <c r="A10" s="8" t="n">
         <v>0.7152777777777778</v>
       </c>
@@ -6817,7 +6817,7 @@
       <c r="L10" s="9" t="n"/>
       <c r="M10" s="9" t="n"/>
     </row>
-    <row r="11" ht="30" customHeight="1" s="197">
+    <row r="11" ht="30" customHeight="1" s="181">
       <c r="A11" s="8" t="n">
         <v>0.7222222222222222</v>
       </c>
@@ -6834,7 +6834,7 @@
       <c r="L11" s="9" t="n"/>
       <c r="M11" s="9" t="n"/>
     </row>
-    <row r="12" ht="30" customHeight="1" s="197">
+    <row r="12" ht="30" customHeight="1" s="181">
       <c r="A12" s="8" t="n">
         <v>0.7291666666666666</v>
       </c>
@@ -6851,7 +6851,7 @@
       <c r="L12" s="9" t="n"/>
       <c r="M12" s="9" t="n"/>
     </row>
-    <row r="13" ht="30" customHeight="1" s="197">
+    <row r="13" ht="30" customHeight="1" s="181">
       <c r="A13" s="8" t="n">
         <v>0.7361111111111112</v>
       </c>
@@ -6868,7 +6868,7 @@
       <c r="L13" s="9" t="n"/>
       <c r="M13" s="9" t="n"/>
     </row>
-    <row r="14" ht="30" customHeight="1" s="197">
+    <row r="14" ht="30" customHeight="1" s="181">
       <c r="A14" s="8" t="n">
         <v>0.7430555555555556</v>
       </c>
@@ -6885,7 +6885,7 @@
       <c r="L14" s="9" t="n"/>
       <c r="M14" s="9" t="n"/>
     </row>
-    <row r="15" ht="30" customHeight="1" s="197">
+    <row r="15" ht="30" customHeight="1" s="181">
       <c r="A15" s="8" t="n">
         <v>0.75</v>
       </c>
@@ -6917,43 +6917,43 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:M15"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="12.75"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="13.2"/>
   <cols>
-    <col width="18" bestFit="1" customWidth="1" style="197" min="1" max="1"/>
-    <col width="24" bestFit="1" customWidth="1" style="196" min="2" max="2"/>
-    <col width="24.5703125" bestFit="1" customWidth="1" style="197" min="3" max="3"/>
-    <col width="27.5703125" bestFit="1" customWidth="1" style="197" min="4" max="4"/>
-    <col width="25.42578125" bestFit="1" customWidth="1" style="197" min="5" max="5"/>
-    <col width="22.140625" bestFit="1" customWidth="1" style="197" min="6" max="6"/>
-    <col width="25" bestFit="1" customWidth="1" style="197" min="7" max="7"/>
-    <col width="23.42578125" bestFit="1" customWidth="1" style="197" min="8" max="8"/>
-    <col width="24" bestFit="1" customWidth="1" style="197" min="9" max="9"/>
-    <col width="24.5703125" bestFit="1" customWidth="1" style="197" min="10" max="10"/>
-    <col width="27.5703125" bestFit="1" customWidth="1" style="197" min="11" max="11"/>
-    <col width="25.42578125" bestFit="1" customWidth="1" style="197" min="12" max="12"/>
-    <col width="22.140625" bestFit="1" customWidth="1" style="197" min="13" max="13"/>
+    <col width="18" bestFit="1" customWidth="1" style="181" min="1" max="1"/>
+    <col width="24" bestFit="1" customWidth="1" style="180" min="2" max="2"/>
+    <col width="24.5546875" bestFit="1" customWidth="1" style="181" min="3" max="3"/>
+    <col width="27.5546875" bestFit="1" customWidth="1" style="181" min="4" max="4"/>
+    <col width="25.44140625" bestFit="1" customWidth="1" style="181" min="5" max="5"/>
+    <col width="22.109375" bestFit="1" customWidth="1" style="181" min="6" max="6"/>
+    <col width="25" bestFit="1" customWidth="1" style="181" min="7" max="7"/>
+    <col width="23.44140625" bestFit="1" customWidth="1" style="181" min="8" max="8"/>
+    <col width="24" bestFit="1" customWidth="1" style="181" min="9" max="9"/>
+    <col width="24.5546875" bestFit="1" customWidth="1" style="181" min="10" max="10"/>
+    <col width="27.5546875" bestFit="1" customWidth="1" style="181" min="11" max="11"/>
+    <col width="25.44140625" bestFit="1" customWidth="1" style="181" min="12" max="12"/>
+    <col width="22.109375" bestFit="1" customWidth="1" style="181" min="13" max="13"/>
   </cols>
   <sheetData>
-    <row r="1" ht="23.25" customHeight="1" s="197">
-      <c r="A1" s="193" t="inlineStr">
+    <row r="1" ht="23.25" customHeight="1" s="181">
+      <c r="A1" s="182" t="inlineStr">
         <is>
           <t>2024 Bechtel Golf League Schedule Tee Time</t>
         </is>
       </c>
-      <c r="B1" s="194" t="n"/>
-      <c r="C1" s="194" t="n"/>
-      <c r="D1" s="194" t="n"/>
-      <c r="E1" s="194" t="n"/>
-      <c r="F1" s="194" t="n"/>
-      <c r="G1" s="194" t="n"/>
-      <c r="H1" s="194" t="n"/>
-      <c r="I1" s="194" t="n"/>
-      <c r="J1" s="194" t="n"/>
-      <c r="K1" s="194" t="n"/>
-      <c r="L1" s="194" t="n"/>
-      <c r="M1" s="194" t="n"/>
-    </row>
-    <row r="2" ht="30" customFormat="1" customHeight="1" s="228">
+      <c r="B1" s="179" t="n"/>
+      <c r="C1" s="179" t="n"/>
+      <c r="D1" s="179" t="n"/>
+      <c r="E1" s="179" t="n"/>
+      <c r="F1" s="179" t="n"/>
+      <c r="G1" s="179" t="n"/>
+      <c r="H1" s="179" t="n"/>
+      <c r="I1" s="179" t="n"/>
+      <c r="J1" s="179" t="n"/>
+      <c r="K1" s="179" t="n"/>
+      <c r="L1" s="179" t="n"/>
+      <c r="M1" s="179" t="n"/>
+    </row>
+    <row r="2" ht="30" customFormat="1" customHeight="1" s="213">
       <c r="A2" s="10" t="inlineStr">
         <is>
           <t>TEE TIME</t>
@@ -6996,7 +6996,7 @@
         <v>45534</v>
       </c>
     </row>
-    <row r="3" ht="30" customHeight="1" s="197">
+    <row r="3" ht="30" customHeight="1" s="181">
       <c r="A3" s="8" t="n">
         <v>0.6666666666666666</v>
       </c>
@@ -7013,7 +7013,7 @@
       <c r="L3" s="9" t="n"/>
       <c r="M3" s="9" t="n"/>
     </row>
-    <row r="4" ht="30" customHeight="1" s="197">
+    <row r="4" ht="30" customHeight="1" s="181">
       <c r="A4" s="8" t="n">
         <v>0.6736111111111112</v>
       </c>
@@ -7030,7 +7030,7 @@
       <c r="L4" s="9" t="n"/>
       <c r="M4" s="9" t="n"/>
     </row>
-    <row r="5" ht="30" customHeight="1" s="197">
+    <row r="5" ht="30" customHeight="1" s="181">
       <c r="A5" s="8" t="n">
         <v>0.6805555555555556</v>
       </c>
@@ -7047,7 +7047,7 @@
       <c r="L5" s="9" t="n"/>
       <c r="M5" s="9" t="n"/>
     </row>
-    <row r="6" ht="46.5" customHeight="1" s="197">
+    <row r="6" ht="46.5" customHeight="1" s="181">
       <c r="A6" s="8" t="n">
         <v>0.6875</v>
       </c>
@@ -7075,7 +7075,7 @@
       <c r="L6" s="9" t="n"/>
       <c r="M6" s="9" t="n"/>
     </row>
-    <row r="7" ht="30" customHeight="1" s="197">
+    <row r="7" ht="30" customHeight="1" s="181">
       <c r="A7" s="8" t="n">
         <v>0.6944444444444444</v>
       </c>
@@ -7100,7 +7100,7 @@
       <c r="L7" s="9" t="n"/>
       <c r="M7" s="9" t="n"/>
     </row>
-    <row r="8" ht="30" customHeight="1" s="197">
+    <row r="8" ht="30" customHeight="1" s="181">
       <c r="A8" s="8" t="n">
         <v>0.7013888888888888</v>
       </c>
@@ -7117,7 +7117,7 @@
       <c r="L8" s="9" t="n"/>
       <c r="M8" s="9" t="n"/>
     </row>
-    <row r="9" ht="30" customHeight="1" s="197">
+    <row r="9" ht="30" customHeight="1" s="181">
       <c r="A9" s="8" t="n">
         <v>0.7083333333333334</v>
       </c>
@@ -7134,7 +7134,7 @@
       <c r="L9" s="9" t="n"/>
       <c r="M9" s="9" t="n"/>
     </row>
-    <row r="10" ht="30" customHeight="1" s="197">
+    <row r="10" ht="30" customHeight="1" s="181">
       <c r="A10" s="8" t="n">
         <v>0.7152777777777778</v>
       </c>
@@ -7151,7 +7151,7 @@
       <c r="L10" s="9" t="n"/>
       <c r="M10" s="9" t="n"/>
     </row>
-    <row r="11" ht="30" customHeight="1" s="197">
+    <row r="11" ht="30" customHeight="1" s="181">
       <c r="A11" s="8" t="n">
         <v>0.7222222222222222</v>
       </c>
@@ -7168,7 +7168,7 @@
       <c r="L11" s="9" t="n"/>
       <c r="M11" s="9" t="n"/>
     </row>
-    <row r="12" ht="30" customHeight="1" s="197">
+    <row r="12" ht="30" customHeight="1" s="181">
       <c r="A12" s="8" t="n">
         <v>0.7291666666666666</v>
       </c>
@@ -7185,7 +7185,7 @@
       <c r="L12" s="9" t="n"/>
       <c r="M12" s="9" t="n"/>
     </row>
-    <row r="13" ht="30" customHeight="1" s="197">
+    <row r="13" ht="30" customHeight="1" s="181">
       <c r="A13" s="8" t="n">
         <v>0.7361111111111112</v>
       </c>
@@ -7202,7 +7202,7 @@
       <c r="L13" s="9" t="n"/>
       <c r="M13" s="9" t="n"/>
     </row>
-    <row r="14" ht="30" customHeight="1" s="197">
+    <row r="14" ht="30" customHeight="1" s="181">
       <c r="A14" s="8" t="n">
         <v>0.7430555555555556</v>
       </c>
@@ -7219,7 +7219,7 @@
       <c r="L14" s="9" t="n"/>
       <c r="M14" s="9" t="n"/>
     </row>
-    <row r="15" ht="30" customHeight="1" s="197">
+    <row r="15" ht="30" customHeight="1" s="181">
       <c r="A15" s="8" t="n">
         <v>0.75</v>
       </c>
@@ -7251,33 +7251,33 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:M29"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="12.75"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="13.2"/>
   <cols>
-    <col width="18.28515625" bestFit="1" customWidth="1" style="197" min="2" max="2"/>
-    <col width="18.5703125" customWidth="1" style="197" min="3" max="3"/>
-    <col width="19.42578125" customWidth="1" style="197" min="4" max="4"/>
-    <col width="19" bestFit="1" customWidth="1" style="197" min="5" max="5"/>
-    <col width="20.28515625" customWidth="1" style="197" min="6" max="6"/>
-    <col width="21.28515625" bestFit="1" customWidth="1" style="197" min="7" max="7"/>
-    <col width="19" bestFit="1" customWidth="1" style="197" min="8" max="8"/>
-    <col width="20.42578125" bestFit="1" customWidth="1" style="197" min="9" max="9"/>
-    <col width="19.5703125" bestFit="1" customWidth="1" style="197" min="10" max="10"/>
+    <col width="18.33203125" bestFit="1" customWidth="1" style="181" min="2" max="2"/>
+    <col width="18.5546875" customWidth="1" style="181" min="3" max="3"/>
+    <col width="19.44140625" customWidth="1" style="181" min="4" max="4"/>
+    <col width="19" bestFit="1" customWidth="1" style="181" min="5" max="5"/>
+    <col width="20.33203125" customWidth="1" style="181" min="6" max="6"/>
+    <col width="21.33203125" bestFit="1" customWidth="1" style="181" min="7" max="7"/>
+    <col width="19" bestFit="1" customWidth="1" style="181" min="8" max="8"/>
+    <col width="20.44140625" bestFit="1" customWidth="1" style="181" min="9" max="9"/>
+    <col width="19.5546875" bestFit="1" customWidth="1" style="181" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="23.25" customHeight="1" s="197">
-      <c r="B1" s="195" t="inlineStr">
+    <row r="1" ht="23.25" customHeight="1" s="181">
+      <c r="B1" s="178" t="inlineStr">
         <is>
           <t>2026 iCON Golf League Schedule</t>
         </is>
       </c>
-      <c r="C1" s="194" t="n"/>
-      <c r="D1" s="194" t="n"/>
-      <c r="E1" s="194" t="n"/>
-      <c r="F1" s="194" t="n"/>
-      <c r="G1" s="194" t="n"/>
-      <c r="H1" s="194" t="n"/>
-      <c r="I1" s="194" t="n"/>
-      <c r="J1" s="194" t="n"/>
+      <c r="C1" s="179" t="n"/>
+      <c r="D1" s="179" t="n"/>
+      <c r="E1" s="179" t="n"/>
+      <c r="F1" s="179" t="n"/>
+      <c r="G1" s="179" t="n"/>
+      <c r="H1" s="179" t="n"/>
+      <c r="I1" s="179" t="n"/>
+      <c r="J1" s="179" t="n"/>
     </row>
     <row r="2">
       <c r="B2" s="6" t="inlineStr">
@@ -7749,7 +7749,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="E13" s="196" t="n"/>
+      <c r="E13" s="180" t="n"/>
     </row>
     <row r="14">
       <c r="B14" s="2" t="inlineStr">
@@ -7797,7 +7797,7 @@
       </c>
       <c r="F15" s="3" t="n"/>
     </row>
-    <row r="16" ht="13.5" customHeight="1" s="197">
+    <row r="16" ht="13.5" customHeight="1" s="181">
       <c r="B16" s="5" t="n">
         <v>2</v>
       </c>
@@ -7820,7 +7820,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="13.5" customHeight="1" s="197">
+    <row r="17" ht="13.5" customHeight="1" s="181">
       <c r="B17" s="5">
         <f>B16+1</f>
         <v/>
@@ -7840,7 +7840,7 @@
       </c>
       <c r="F17" s="3" t="n"/>
     </row>
-    <row r="18" ht="13.5" customHeight="1" s="197">
+    <row r="18" ht="13.5" customHeight="1" s="181">
       <c r="B18" s="5">
         <f>B17+1</f>
         <v/>
@@ -7884,7 +7884,7 @@
       </c>
       <c r="F19" s="3" t="n"/>
     </row>
-    <row r="20" ht="13.5" customHeight="1" s="197">
+    <row r="20" ht="13.5" customHeight="1" s="181">
       <c r="B20" s="5">
         <f>B19+1</f>
         <v/>
@@ -7909,7 +7909,7 @@
       </c>
       <c r="G20" s="4" t="n"/>
     </row>
-    <row r="21" ht="13.5" customHeight="1" s="197">
+    <row r="21" ht="13.5" customHeight="1" s="181">
       <c r="B21" s="5">
         <f>B20+1</f>
         <v/>
@@ -7933,7 +7933,7 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="13.5" customHeight="1" s="197">
+    <row r="22" ht="13.5" customHeight="1" s="181">
       <c r="B22" s="5">
         <f>B21+1</f>
         <v/>
@@ -7981,7 +7981,7 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="13.5" customHeight="1" s="197">
+    <row r="24" ht="13.5" customHeight="1" s="181">
       <c r="B24" s="5">
         <f>B23+1</f>
         <v/>
@@ -7992,14 +7992,18 @@
         </is>
       </c>
       <c r="D24" s="105" t="n">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="E24" s="106" t="inlineStr">
         <is>
           <t>Mens</t>
         </is>
       </c>
-      <c r="F24" s="3" t="n"/>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>Yes - Venmo</t>
+        </is>
+      </c>
       <c r="G24" s="4" t="n"/>
     </row>
     <row r="25">
@@ -8026,7 +8030,7 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="13.5" customHeight="1" s="197">
+    <row r="26" ht="13.5" customHeight="1" s="181">
       <c r="B26" s="5">
         <f>B25+1</f>
         <v/>
@@ -8074,7 +8078,7 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="13.5" customHeight="1" s="197">
+    <row r="28" ht="13.5" customHeight="1" s="181">
       <c r="B28" s="5">
         <f>B27+1</f>
         <v/>
@@ -8098,7 +8102,7 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="13.5" customHeight="1" s="197">
+    <row r="29" ht="13.5" customHeight="1" s="181">
       <c r="B29" s="5">
         <f>B28+1</f>
         <v/>
@@ -8119,7 +8123,7 @@
       <c r="F29" s="3" t="n"/>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" algorithmName="SHA-512" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" saltValue="oT9OKE0a6mxXp9lX4avn9Q==" formatRows="1" sort="1" spinCount="100000" hashValue="ufYqSFWQmrwR3tspyCNVwQzCM+2xHEvVEHpnnaCxkigOiT/AKvTKo7lp8cNxe4I9VAA7tv4Evs3NkxT7ROFWSg=="/>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" algorithmName="SHA-512" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" saltValue="ZPV0X8BpwDDvOmyIBVQ1Qg==" formatRows="1" sort="1" spinCount="100000" hashValue="pe3COVHuOEKD5HHAblmDelT9w1i8EQRAgM56tu4ZDnux+YdgWjIMkLB4hT99katjAAvpgJJyC7OafMD+EWGCDg=="/>
   <mergeCells count="2">
     <mergeCell ref="B1:J1"/>
     <mergeCell ref="E13:F13"/>
@@ -8150,131 +8154,131 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="B1:AI46"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="12.75"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="13.2"/>
   <cols>
-    <col width="12" customWidth="1" style="197" min="2" max="2"/>
-    <col width="17" bestFit="1" customWidth="1" style="197" min="3" max="3"/>
-    <col width="11.85546875" customWidth="1" style="197" min="4" max="4"/>
-    <col width="9.140625" customWidth="1" style="197" min="6" max="8"/>
-    <col width="11" bestFit="1" customWidth="1" style="197" min="9" max="9"/>
-    <col width="9.140625" customWidth="1" style="197" min="10" max="10"/>
-    <col width="14" bestFit="1" customWidth="1" style="197" min="11" max="11"/>
-    <col width="15.5703125" bestFit="1" customWidth="1" style="197" min="12" max="12"/>
-    <col width="13.5703125" bestFit="1" customWidth="1" style="197" min="13" max="13"/>
-    <col width="13.5703125" customWidth="1" style="197" min="14" max="15"/>
-    <col width="12.5703125" customWidth="1" style="197" min="16" max="35"/>
+    <col width="12" customWidth="1" style="181" min="2" max="2"/>
+    <col width="17" bestFit="1" customWidth="1" style="181" min="3" max="3"/>
+    <col width="11.88671875" customWidth="1" style="181" min="4" max="4"/>
+    <col width="9.109375" customWidth="1" style="181" min="6" max="8"/>
+    <col width="11" bestFit="1" customWidth="1" style="181" min="9" max="9"/>
+    <col width="9.109375" customWidth="1" style="181" min="10" max="10"/>
+    <col width="14" bestFit="1" customWidth="1" style="181" min="11" max="11"/>
+    <col width="15.5546875" bestFit="1" customWidth="1" style="181" min="12" max="12"/>
+    <col width="13.5546875" bestFit="1" customWidth="1" style="181" min="13" max="13"/>
+    <col width="13.5546875" customWidth="1" style="181" min="14" max="15"/>
+    <col width="12.5546875" customWidth="1" style="181" min="16" max="35"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="P1" s="209" t="inlineStr">
+      <c r="P1" s="194" t="inlineStr">
         <is>
           <t>Reston National</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="13.5" customHeight="1" s="197" thickBot="1">
-      <c r="P2" s="209" t="inlineStr">
+    <row r="2" ht="13.5" customHeight="1" s="181" thickBot="1">
+      <c r="P2" s="194" t="inlineStr">
         <is>
           <t>Round 1</t>
         </is>
       </c>
-      <c r="Q2" s="209" t="inlineStr">
+      <c r="Q2" s="194" t="inlineStr">
         <is>
           <t>Round 2</t>
         </is>
       </c>
-      <c r="R2" s="209" t="inlineStr">
+      <c r="R2" s="194" t="inlineStr">
         <is>
           <t>Round 3</t>
         </is>
       </c>
-      <c r="S2" s="209" t="inlineStr">
+      <c r="S2" s="194" t="inlineStr">
         <is>
           <t>Round 4</t>
         </is>
       </c>
-      <c r="T2" s="209" t="inlineStr">
+      <c r="T2" s="194" t="inlineStr">
         <is>
           <t>Round 5</t>
         </is>
       </c>
-      <c r="U2" s="209" t="inlineStr">
+      <c r="U2" s="194" t="inlineStr">
         <is>
           <t>Round 6</t>
         </is>
       </c>
-      <c r="V2" s="209" t="inlineStr">
+      <c r="V2" s="194" t="inlineStr">
         <is>
           <t>Round 7</t>
         </is>
       </c>
-      <c r="W2" s="209" t="inlineStr">
+      <c r="W2" s="194" t="inlineStr">
         <is>
           <t>Round 8</t>
         </is>
       </c>
-      <c r="X2" s="209" t="inlineStr">
+      <c r="X2" s="194" t="inlineStr">
         <is>
           <t>Round 9</t>
         </is>
       </c>
-      <c r="Y2" s="209" t="inlineStr">
+      <c r="Y2" s="194" t="inlineStr">
         <is>
           <t>Round 10</t>
         </is>
       </c>
-      <c r="Z2" s="209" t="inlineStr">
+      <c r="Z2" s="194" t="inlineStr">
         <is>
           <t>Round 11</t>
         </is>
       </c>
-      <c r="AA2" s="209" t="inlineStr">
+      <c r="AA2" s="194" t="inlineStr">
         <is>
           <t>Round 12</t>
         </is>
       </c>
-      <c r="AB2" s="209" t="inlineStr">
+      <c r="AB2" s="194" t="inlineStr">
         <is>
           <t>Round 13</t>
         </is>
       </c>
-      <c r="AC2" s="209" t="inlineStr">
+      <c r="AC2" s="194" t="inlineStr">
         <is>
           <t>Round 14</t>
         </is>
       </c>
-      <c r="AD2" s="209" t="inlineStr">
+      <c r="AD2" s="194" t="inlineStr">
         <is>
           <t>Round 15</t>
         </is>
       </c>
-      <c r="AE2" s="209" t="inlineStr">
+      <c r="AE2" s="194" t="inlineStr">
         <is>
           <t>Round 16</t>
         </is>
       </c>
-      <c r="AF2" s="209" t="inlineStr">
+      <c r="AF2" s="194" t="inlineStr">
         <is>
           <t>Round 17</t>
         </is>
       </c>
-      <c r="AG2" s="209" t="inlineStr">
+      <c r="AG2" s="194" t="inlineStr">
         <is>
           <t>Round 18</t>
         </is>
       </c>
-      <c r="AH2" s="209" t="inlineStr">
+      <c r="AH2" s="194" t="inlineStr">
         <is>
           <t>Round 19</t>
         </is>
       </c>
-      <c r="AI2" s="209" t="inlineStr">
+      <c r="AI2" s="194" t="inlineStr">
         <is>
           <t>Round 20</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="13.5" customHeight="1" s="197" thickBot="1">
+    <row r="3" ht="13.5" customHeight="1" s="181" thickBot="1">
       <c r="B3" s="2" t="inlineStr">
         <is>
           <t>Mens</t>
@@ -8295,33 +8299,33 @@
           <t>Name</t>
         </is>
       </c>
-      <c r="G3" s="210" t="inlineStr">
+      <c r="G3" s="195" t="inlineStr">
         <is>
           <t>Tees</t>
         </is>
       </c>
-      <c r="H3" s="211" t="n"/>
-      <c r="I3" s="210" t="inlineStr">
+      <c r="H3" s="196" t="n"/>
+      <c r="I3" s="195" t="inlineStr">
         <is>
           <t>USGA Initial</t>
         </is>
       </c>
-      <c r="J3" s="210" t="inlineStr">
+      <c r="J3" s="195" t="inlineStr">
         <is>
           <t>Initial</t>
         </is>
       </c>
-      <c r="K3" s="210" t="inlineStr">
+      <c r="K3" s="195" t="inlineStr">
         <is>
           <t>Initial Handicap</t>
         </is>
       </c>
-      <c r="L3" s="210" t="inlineStr">
+      <c r="L3" s="195" t="inlineStr">
         <is>
           <t>Course Handicap</t>
         </is>
       </c>
-      <c r="M3" s="210" t="inlineStr">
+      <c r="M3" s="195" t="inlineStr">
         <is>
           <t>Live Handicap</t>
         </is>
@@ -8449,42 +8453,42 @@
       <c r="D4" s="43" t="n">
         <v>130</v>
       </c>
-      <c r="F4" s="205" t="inlineStr">
+      <c r="F4" s="190" t="inlineStr">
         <is>
           <t>Ethan</t>
         </is>
       </c>
-      <c r="G4" s="198">
+      <c r="G4" s="183">
         <f>VLOOKUP($F4,Schedule!$C$15:$E$29,3)</f>
         <v/>
       </c>
-      <c r="H4" s="198">
+      <c r="H4" s="183">
         <f>VLOOKUP($F4,Schedule!$C$15:$E$29,4)</f>
         <v/>
       </c>
-      <c r="I4" s="208" t="n">
+      <c r="I4" s="193" t="n">
         <v>13</v>
       </c>
-      <c r="J4" s="198">
+      <c r="J4" s="183">
         <f>I4+36</f>
         <v/>
       </c>
-      <c r="K4" s="201" t="n">
+      <c r="K4" s="186" t="n">
         <v>13</v>
       </c>
-      <c r="L4" s="201">
+      <c r="L4" s="186">
         <f t="array" ref="L4">_xlfn.IFS($G4="Mens",ROUNDUP($K4*(VLOOKUP($H4,$B$4:$D$7,3)/113),0),$G4="Womens",ROUNDUP($K4*(VLOOKUP($H4,$B$10:$D$12,3)/113),0))</f>
         <v/>
       </c>
-      <c r="M4" s="201">
+      <c r="M4" s="186">
         <f t="array" ref="M4">ROUNDUP(_xlfn.IFS(O4&lt;=$B$20,MIN(P6:AI6),AND(O4&gt;=$B$21,O4&lt;=$B$23),AVERAGE(SMALL(P6:AI6,{1,2})),AND(O4&gt;=$B$24,O4&lt;=$B$26),AVERAGE(SMALL(P6:AI6,{1,2,3})),AND(O4&gt;=$B$27,O4&lt;=$B$29),AVERAGE(SMALL(P6:AI6,{1,2,3,4})),AND(O4&gt;=$B$30,O4&lt;=$B$31),AVERAGE(SMALL(P6:AI6,{1,2,3,4,5})),AND(O4&gt;=$B$32,O4&lt;=$B$33),AVERAGE(SMALL(P6:AI6,{1,2,3,4,5,6})),AND(O4=$B$34),AVERAGE(SMALL(P6:AI6,{1,2,3,4,5,6,7})),AND(O4=$B$35),AVERAGE(SMALL(P6:AI6,{1,2,3,4,5,6,7,8})))+VLOOKUP(O4,$B$16:$D$35,3),0)</f>
         <v/>
       </c>
-      <c r="N4" s="201">
+      <c r="N4" s="186">
         <f t="array" ref="N4">ROUNDUP(_xlfn.IFS($G4="Mens",ROUNDUP(M4*(VLOOKUP($H4,$B$4:$D$7,3)/113),1),$G4="Womens",ROUNDUP(M4*(VLOOKUP($H4,$B$10:$D$12,3)/113),1)),0)</f>
         <v/>
       </c>
-      <c r="O4" s="202">
+      <c r="O4" s="187">
         <f>COUNT(P4:AI4)</f>
         <v/>
       </c>
@@ -8537,16 +8541,16 @@
       <c r="D5" s="43" t="n">
         <v>126</v>
       </c>
-      <c r="F5" s="206" t="n"/>
-      <c r="G5" s="199" t="n"/>
-      <c r="H5" s="199" t="n"/>
-      <c r="I5" s="199" t="n"/>
-      <c r="J5" s="199" t="n"/>
-      <c r="K5" s="199" t="n"/>
-      <c r="L5" s="199" t="n"/>
-      <c r="M5" s="199" t="n"/>
-      <c r="N5" s="199" t="n"/>
-      <c r="O5" s="203" t="n"/>
+      <c r="F5" s="191" t="n"/>
+      <c r="G5" s="184" t="n"/>
+      <c r="H5" s="184" t="n"/>
+      <c r="I5" s="184" t="n"/>
+      <c r="J5" s="184" t="n"/>
+      <c r="K5" s="184" t="n"/>
+      <c r="L5" s="184" t="n"/>
+      <c r="M5" s="184" t="n"/>
+      <c r="N5" s="184" t="n"/>
+      <c r="O5" s="188" t="n"/>
       <c r="P5" s="96" t="inlineStr">
         <is>
           <t>USGA Diff.</t>
@@ -8648,7 +8652,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="13.5" customHeight="1" s="197" thickBot="1">
+    <row r="6" ht="13.5" customHeight="1" s="181" thickBot="1">
       <c r="B6" s="42" t="inlineStr">
         <is>
           <t>Blue/White</t>
@@ -8660,16 +8664,16 @@
       <c r="D6" s="43" t="n">
         <v>120</v>
       </c>
-      <c r="F6" s="207" t="n"/>
-      <c r="G6" s="200" t="n"/>
-      <c r="H6" s="200" t="n"/>
-      <c r="I6" s="200" t="n"/>
-      <c r="J6" s="200" t="n"/>
-      <c r="K6" s="200" t="n"/>
-      <c r="L6" s="200" t="n"/>
-      <c r="M6" s="200" t="n"/>
-      <c r="N6" s="200" t="n"/>
-      <c r="O6" s="204" t="n"/>
+      <c r="F6" s="192" t="n"/>
+      <c r="G6" s="185" t="n"/>
+      <c r="H6" s="185" t="n"/>
+      <c r="I6" s="185" t="n"/>
+      <c r="J6" s="185" t="n"/>
+      <c r="K6" s="185" t="n"/>
+      <c r="L6" s="185" t="n"/>
+      <c r="M6" s="185" t="n"/>
+      <c r="N6" s="185" t="n"/>
+      <c r="O6" s="189" t="n"/>
       <c r="P6" s="97">
         <f t="array" ref="P6">IF(P4="","",_xlfn.IFS($G4="Mens",(P4-(VLOOKUP($H4,$B$4:$D$7,2)/2))/VLOOKUP($H4,$B$4:$D$7,3)*113,$G4="Womens",(P4-(VLOOKUP($H4,$B$10:$D$12,2)/2))/VLOOKUP($H4,$B$10:$D$12,3)*113))</f>
         <v/>
@@ -8766,9 +8770,9 @@
       <c r="L7" s="98" t="n"/>
     </row>
     <row r="8">
-      <c r="B8" s="228" t="n"/>
-      <c r="C8" s="228" t="n"/>
-      <c r="D8" s="228" t="n"/>
+      <c r="B8" s="213" t="n"/>
+      <c r="C8" s="213" t="n"/>
+      <c r="D8" s="213" t="n"/>
     </row>
     <row r="9">
       <c r="B9" s="2" t="inlineStr">
@@ -8826,8 +8830,8 @@
         <v>120</v>
       </c>
     </row>
-    <row r="14" ht="13.5" customHeight="1" s="197" thickBot="1"/>
-    <row r="15" ht="25.5" customHeight="1" s="197">
+    <row r="14" ht="13.5" customHeight="1" s="181" thickBot="1"/>
+    <row r="15" ht="25.5" customHeight="1" s="181">
       <c r="B15" s="82" t="inlineStr">
         <is>
           <t># of Score Differentials</t>
@@ -8896,7 +8900,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="20" ht="13.5" customHeight="1" s="197" thickBot="1">
+    <row r="20" ht="13.5" customHeight="1" s="181" thickBot="1">
       <c r="B20" s="39" t="n">
         <v>5</v>
       </c>
@@ -8935,7 +8939,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" ht="13.5" customHeight="1" s="197" thickBot="1">
+    <row r="23" ht="13.5" customHeight="1" s="181" thickBot="1">
       <c r="B23" s="39" t="n">
         <v>8</v>
       </c>
@@ -8975,7 +8979,7 @@
       </c>
       <c r="K25" s="101" t="n"/>
     </row>
-    <row r="26" ht="13.5" customHeight="1" s="197" thickBot="1">
+    <row r="26" ht="13.5" customHeight="1" s="181" thickBot="1">
       <c r="B26" s="39" t="n">
         <v>11</v>
       </c>
@@ -9014,7 +9018,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" ht="13.5" customHeight="1" s="197" thickBot="1">
+    <row r="29" ht="13.5" customHeight="1" s="181" thickBot="1">
       <c r="B29" s="39" t="n">
         <v>14</v>
       </c>
@@ -9040,7 +9044,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" ht="13.5" customHeight="1" s="197" thickBot="1">
+    <row r="31" ht="13.5" customHeight="1" s="181" thickBot="1">
       <c r="B31" s="39" t="n">
         <v>16</v>
       </c>
@@ -9066,7 +9070,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" ht="13.5" customHeight="1" s="197" thickBot="1">
+    <row r="33" ht="13.5" customHeight="1" s="181" thickBot="1">
       <c r="B33" s="39" t="n">
         <v>18</v>
       </c>
@@ -9079,8 +9083,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" ht="13.5" customHeight="1" s="197" thickBot="1">
-      <c r="B34" s="205" t="n">
+    <row r="34" ht="13.5" customHeight="1" s="181" thickBot="1">
+      <c r="B34" s="190" t="n">
         <v>19</v>
       </c>
       <c r="C34" s="92" t="inlineStr">
@@ -9088,15 +9092,15 @@
           <t>Average of lowest 7</t>
         </is>
       </c>
-      <c r="D34" s="202" t="n">
+      <c r="D34" s="187" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="35" ht="13.5" customHeight="1" s="197" thickBot="1">
+    <row r="35" ht="13.5" customHeight="1" s="181" thickBot="1">
       <c r="B35" s="89" t="n">
         <v>20</v>
       </c>
-      <c r="C35" s="200" t="inlineStr">
+      <c r="C35" s="185" t="inlineStr">
         <is>
           <t>Average of lowest 8</t>
         </is>
@@ -9226,29 +9230,29 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:S32"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9.140625" defaultRowHeight="12.75"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9.109375" defaultRowHeight="13.2"/>
   <cols>
-    <col width="3.140625" customWidth="1" style="228" min="1" max="1"/>
-    <col width="18" bestFit="1" customWidth="1" style="228" min="2" max="2"/>
-    <col width="12.140625" bestFit="1" customWidth="1" style="228" min="3" max="3"/>
-    <col width="9.140625" customWidth="1" style="228" min="4" max="12"/>
-    <col width="11.5703125" customWidth="1" style="228" min="13" max="15"/>
-    <col width="9.140625" customWidth="1" style="228" min="16" max="17"/>
-    <col width="14.85546875" customWidth="1" style="228" min="18" max="19"/>
-    <col width="9.140625" customWidth="1" style="228" min="20" max="26"/>
-    <col width="9.140625" customWidth="1" style="228" min="27" max="16384"/>
+    <col width="3.109375" customWidth="1" style="213" min="1" max="1"/>
+    <col width="18" bestFit="1" customWidth="1" style="213" min="2" max="2"/>
+    <col width="12.109375" bestFit="1" customWidth="1" style="213" min="3" max="3"/>
+    <col width="9.109375" customWidth="1" style="213" min="4" max="12"/>
+    <col width="11.5546875" customWidth="1" style="213" min="13" max="15"/>
+    <col width="9.109375" customWidth="1" style="213" min="16" max="17"/>
+    <col width="14.88671875" customWidth="1" style="213" min="18" max="19"/>
+    <col width="9.109375" customWidth="1" style="213" min="20" max="32"/>
+    <col width="9.109375" customWidth="1" style="213" min="33" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1" ht="13.5" customHeight="1" s="197" thickBot="1">
-      <c r="N1" s="229" t="inlineStr">
+    <row r="1" ht="13.5" customHeight="1" s="181" thickBot="1">
+      <c r="N1" s="214" t="inlineStr">
         <is>
           <t>Tiebreakers</t>
         </is>
       </c>
-      <c r="O1" s="191" t="n"/>
+      <c r="O1" s="215" t="n"/>
       <c r="P1" s="21" t="n"/>
     </row>
-    <row r="2" ht="41.45" customHeight="1" s="197" thickBot="1">
+    <row r="2" ht="41.4" customHeight="1" s="181" thickBot="1">
       <c r="B2" s="20" t="inlineStr">
         <is>
           <t>Name</t>
@@ -9316,11 +9320,11 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="12.95" customHeight="1" s="197" thickBot="1">
-      <c r="A3" s="228" t="n">
+    <row r="3" ht="12.9" customHeight="1" s="181" thickBot="1">
+      <c r="A3" s="213" t="n">
         <v>1</v>
       </c>
-      <c r="B3" s="216">
+      <c r="B3" s="201">
         <f>Schedule!C15</f>
         <v/>
       </c>
@@ -9332,35 +9336,35 @@
       <c r="D3" s="158" t="n">
         <v>2</v>
       </c>
-      <c r="E3" s="220" t="n"/>
-      <c r="F3" s="220" t="n"/>
-      <c r="G3" s="220" t="n"/>
-      <c r="H3" s="220" t="n"/>
-      <c r="I3" s="220" t="n"/>
-      <c r="J3" s="220" t="n"/>
-      <c r="K3" s="220" t="n"/>
+      <c r="E3" s="205" t="n"/>
+      <c r="F3" s="205" t="n"/>
+      <c r="G3" s="205" t="n"/>
+      <c r="H3" s="205" t="n"/>
+      <c r="I3" s="205" t="n"/>
+      <c r="J3" s="205" t="n"/>
+      <c r="K3" s="205" t="n"/>
       <c r="L3" s="160" t="n"/>
-      <c r="M3" s="222" t="n">
+      <c r="M3" s="207" t="n">
         <v>2</v>
       </c>
-      <c r="N3" s="220" t="inlineStr">
+      <c r="N3" s="205" t="inlineStr">
         <is>
           <t>0-1-0</t>
         </is>
       </c>
-      <c r="O3" s="230" t="n">
+      <c r="O3" s="216" t="n">
         <v>43</v>
       </c>
-      <c r="Q3" s="231" t="inlineStr">
+      <c r="Q3" s="217" t="inlineStr">
         <is>
           <t>Playoffs</t>
         </is>
       </c>
-      <c r="R3" s="232" t="n"/>
-      <c r="S3" s="179" t="n"/>
-    </row>
-    <row r="4" ht="13.5" customHeight="1" s="197" thickBot="1">
-      <c r="B4" s="217" t="n"/>
+      <c r="R3" s="218" t="n"/>
+      <c r="S3" s="219" t="n"/>
+    </row>
+    <row r="4" ht="13.5" customHeight="1" s="181" thickBot="1">
+      <c r="B4" s="202" t="n"/>
       <c r="C4" s="161" t="inlineStr">
         <is>
           <t>NET Score</t>
@@ -9377,10 +9381,10 @@
       <c r="J4" s="163" t="n"/>
       <c r="K4" s="163" t="n"/>
       <c r="L4" s="164" t="n"/>
-      <c r="M4" s="223" t="n"/>
-      <c r="N4" s="219" t="n"/>
-      <c r="O4" s="213" t="n"/>
-      <c r="Q4" s="224" t="inlineStr">
+      <c r="M4" s="208" t="n"/>
+      <c r="N4" s="204" t="n"/>
+      <c r="O4" s="198" t="n"/>
+      <c r="Q4" s="209" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
@@ -9396,11 +9400,11 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="12.95" customHeight="1" s="197">
-      <c r="A5" s="228" t="n">
+    <row r="5" ht="12.9" customHeight="1" s="181">
+      <c r="A5" s="213" t="n">
         <v>2</v>
       </c>
-      <c r="B5" s="221">
+      <c r="B5" s="206">
         <f>Schedule!C16</f>
         <v/>
       </c>
@@ -9420,15 +9424,15 @@
       <c r="J5" s="166" t="n"/>
       <c r="K5" s="166" t="n"/>
       <c r="L5" s="167" t="n"/>
-      <c r="M5" s="226" t="n">
+      <c r="M5" s="211" t="n">
         <v>6</v>
       </c>
-      <c r="N5" s="218" t="inlineStr">
+      <c r="N5" s="203" t="inlineStr">
         <is>
           <t>1-0-0</t>
         </is>
       </c>
-      <c r="O5" s="212" t="n">
+      <c r="O5" s="197" t="n">
         <v>39</v>
       </c>
       <c r="Q5" s="33" t="n">
@@ -9437,8 +9441,8 @@
       <c r="R5" s="34" t="n"/>
       <c r="S5" s="35" t="n"/>
     </row>
-    <row r="6" ht="13.5" customHeight="1" s="197" thickBot="1">
-      <c r="B6" s="215" t="n"/>
+    <row r="6" ht="13.5" customHeight="1" s="181" thickBot="1">
+      <c r="B6" s="200" t="n"/>
       <c r="C6" s="168" t="inlineStr">
         <is>
           <t>NET Score</t>
@@ -9455,20 +9459,20 @@
       <c r="J6" s="170" t="n"/>
       <c r="K6" s="170" t="n"/>
       <c r="L6" s="171" t="n"/>
-      <c r="M6" s="223" t="n"/>
-      <c r="N6" s="219" t="n"/>
-      <c r="O6" s="213" t="n"/>
+      <c r="M6" s="208" t="n"/>
+      <c r="N6" s="204" t="n"/>
+      <c r="O6" s="198" t="n"/>
       <c r="Q6" s="36" t="n">
         <v>2</v>
       </c>
       <c r="R6" s="37" t="n"/>
       <c r="S6" s="38" t="n"/>
     </row>
-    <row r="7" ht="12.95" customHeight="1" s="197">
-      <c r="A7" s="228" t="n">
+    <row r="7" ht="12.9" customHeight="1" s="181">
+      <c r="A7" s="213" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="214">
+      <c r="B7" s="199">
         <f>Schedule!C17</f>
         <v/>
       </c>
@@ -9480,23 +9484,23 @@
       <c r="D7" s="158" t="n">
         <v>1</v>
       </c>
-      <c r="E7" s="220" t="n"/>
-      <c r="F7" s="220" t="n"/>
-      <c r="G7" s="220" t="n"/>
-      <c r="H7" s="220" t="n"/>
-      <c r="I7" s="220" t="n"/>
-      <c r="J7" s="220" t="n"/>
-      <c r="K7" s="220" t="n"/>
+      <c r="E7" s="205" t="n"/>
+      <c r="F7" s="205" t="n"/>
+      <c r="G7" s="205" t="n"/>
+      <c r="H7" s="205" t="n"/>
+      <c r="I7" s="205" t="n"/>
+      <c r="J7" s="205" t="n"/>
+      <c r="K7" s="205" t="n"/>
       <c r="L7" s="160" t="n"/>
-      <c r="M7" s="222" t="n">
+      <c r="M7" s="207" t="n">
         <v>1</v>
       </c>
-      <c r="N7" s="220" t="inlineStr">
+      <c r="N7" s="205" t="inlineStr">
         <is>
           <t>0-1-0</t>
         </is>
       </c>
-      <c r="O7" s="230" t="n">
+      <c r="O7" s="216" t="n">
         <v>43</v>
       </c>
       <c r="Q7" s="33" t="n">
@@ -9505,8 +9509,8 @@
       <c r="R7" s="34" t="n"/>
       <c r="S7" s="35" t="n"/>
     </row>
-    <row r="8" ht="13.5" customHeight="1" s="197" thickBot="1">
-      <c r="B8" s="215" t="n"/>
+    <row r="8" ht="13.5" customHeight="1" s="181" thickBot="1">
+      <c r="B8" s="200" t="n"/>
       <c r="C8" s="161" t="inlineStr">
         <is>
           <t>NET Score</t>
@@ -9523,20 +9527,20 @@
       <c r="J8" s="163" t="n"/>
       <c r="K8" s="163" t="n"/>
       <c r="L8" s="164" t="n"/>
-      <c r="M8" s="223" t="n"/>
-      <c r="N8" s="219" t="n"/>
-      <c r="O8" s="213" t="n"/>
+      <c r="M8" s="208" t="n"/>
+      <c r="N8" s="204" t="n"/>
+      <c r="O8" s="198" t="n"/>
       <c r="Q8" s="39" t="n">
         <v>4</v>
       </c>
       <c r="R8" s="40" t="n"/>
       <c r="S8" s="41" t="n"/>
     </row>
-    <row r="9" ht="12.95" customHeight="1" s="197" thickBot="1">
-      <c r="A9" s="228" t="n">
+    <row r="9" ht="12.9" customHeight="1" s="181" thickBot="1">
+      <c r="A9" s="213" t="n">
         <v>4</v>
       </c>
-      <c r="B9" s="221">
+      <c r="B9" s="206">
         <f>Schedule!C18</f>
         <v/>
       </c>
@@ -9556,20 +9560,20 @@
       <c r="J9" s="166" t="n"/>
       <c r="K9" s="166" t="n"/>
       <c r="L9" s="167" t="n"/>
-      <c r="M9" s="226" t="n">
+      <c r="M9" s="211" t="n">
         <v>7</v>
       </c>
-      <c r="N9" s="218" t="inlineStr">
+      <c r="N9" s="203" t="inlineStr">
         <is>
           <t>1-0-0</t>
         </is>
       </c>
-      <c r="O9" s="212" t="n">
+      <c r="O9" s="197" t="n">
         <v>38</v>
       </c>
     </row>
-    <row r="10" ht="13.5" customHeight="1" s="197" thickBot="1">
-      <c r="B10" s="215" t="n"/>
+    <row r="10" ht="13.5" customHeight="1" s="181" thickBot="1">
+      <c r="B10" s="200" t="n"/>
       <c r="C10" s="168" t="inlineStr">
         <is>
           <t>NET Score</t>
@@ -9586,21 +9590,21 @@
       <c r="J10" s="170" t="n"/>
       <c r="K10" s="170" t="n"/>
       <c r="L10" s="171" t="n"/>
-      <c r="M10" s="223" t="n"/>
-      <c r="N10" s="219" t="n"/>
-      <c r="O10" s="213" t="n"/>
-      <c r="R10" s="224" t="inlineStr">
+      <c r="M10" s="208" t="n"/>
+      <c r="N10" s="204" t="n"/>
+      <c r="O10" s="198" t="n"/>
+      <c r="R10" s="209" t="inlineStr">
         <is>
           <t>Playoff Matchups</t>
         </is>
       </c>
-      <c r="S10" s="225" t="n"/>
-    </row>
-    <row r="11" ht="12.95" customHeight="1" s="197">
-      <c r="A11" s="228" t="n">
+      <c r="S10" s="210" t="n"/>
+    </row>
+    <row r="11" ht="12.9" customHeight="1" s="181">
+      <c r="A11" s="213" t="n">
         <v>5</v>
       </c>
-      <c r="B11" s="214">
+      <c r="B11" s="199">
         <f>Schedule!C19</f>
         <v/>
       </c>
@@ -9609,18 +9613,28 @@
           <t>Match Points</t>
         </is>
       </c>
-      <c r="D11" s="158" t="n"/>
-      <c r="E11" s="220" t="n"/>
-      <c r="F11" s="220" t="n"/>
-      <c r="G11" s="220" t="n"/>
-      <c r="H11" s="220" t="n"/>
-      <c r="I11" s="220" t="n"/>
-      <c r="J11" s="220" t="n"/>
-      <c r="K11" s="220" t="n"/>
+      <c r="D11" s="158" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="205" t="n"/>
+      <c r="F11" s="205" t="n"/>
+      <c r="G11" s="205" t="n"/>
+      <c r="H11" s="205" t="n"/>
+      <c r="I11" s="205" t="n"/>
+      <c r="J11" s="205" t="n"/>
+      <c r="K11" s="205" t="n"/>
       <c r="L11" s="160" t="n"/>
-      <c r="M11" s="222" t="n"/>
-      <c r="N11" s="220" t="n"/>
-      <c r="O11" s="230" t="n"/>
+      <c r="M11" s="207" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" s="205" t="inlineStr">
+        <is>
+          <t>0-1-0</t>
+        </is>
+      </c>
+      <c r="O11" s="216" t="n">
+        <v>46</v>
+      </c>
       <c r="R11" s="36" t="inlineStr">
         <is>
           <t>Front 9</t>
@@ -9632,14 +9646,16 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="13.5" customHeight="1" s="197" thickBot="1">
-      <c r="B12" s="215" t="n"/>
+    <row r="12" ht="13.5" customHeight="1" s="181" thickBot="1">
+      <c r="B12" s="200" t="n"/>
       <c r="C12" s="161" t="inlineStr">
         <is>
           <t>NET Score</t>
         </is>
       </c>
-      <c r="D12" s="162" t="n"/>
+      <c r="D12" s="162" t="n">
+        <v>46</v>
+      </c>
       <c r="E12" s="163" t="n"/>
       <c r="F12" s="163" t="n"/>
       <c r="G12" s="163" t="n"/>
@@ -9648,9 +9664,9 @@
       <c r="J12" s="163" t="n"/>
       <c r="K12" s="163" t="n"/>
       <c r="L12" s="164" t="n"/>
-      <c r="M12" s="223" t="n"/>
-      <c r="N12" s="219" t="n"/>
-      <c r="O12" s="213" t="n"/>
+      <c r="M12" s="208" t="n"/>
+      <c r="N12" s="204" t="n"/>
+      <c r="O12" s="198" t="n"/>
       <c r="R12" s="36" t="inlineStr">
         <is>
           <t>1 vs 4</t>
@@ -9662,11 +9678,11 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="12.95" customHeight="1" s="197" thickBot="1">
-      <c r="A13" s="228" t="n">
+    <row r="13" ht="12.9" customHeight="1" s="181" thickBot="1">
+      <c r="A13" s="213" t="n">
         <v>6</v>
       </c>
-      <c r="B13" s="221">
+      <c r="B13" s="206">
         <f>Schedule!C20</f>
         <v/>
       </c>
@@ -9675,7 +9691,9 @@
           <t>Match Points</t>
         </is>
       </c>
-      <c r="D13" s="165" t="n"/>
+      <c r="D13" s="165" t="n">
+        <v>8</v>
+      </c>
       <c r="E13" s="166" t="n"/>
       <c r="F13" s="166" t="n"/>
       <c r="G13" s="166" t="n"/>
@@ -9684,9 +9702,17 @@
       <c r="J13" s="166" t="n"/>
       <c r="K13" s="166" t="n"/>
       <c r="L13" s="167" t="n"/>
-      <c r="M13" s="226" t="n"/>
-      <c r="N13" s="218" t="n"/>
-      <c r="O13" s="212" t="n"/>
+      <c r="M13" s="211" t="n">
+        <v>8</v>
+      </c>
+      <c r="N13" s="203" t="inlineStr">
+        <is>
+          <t>1-0-0</t>
+        </is>
+      </c>
+      <c r="O13" s="197" t="n">
+        <v>33</v>
+      </c>
       <c r="R13" s="39" t="inlineStr">
         <is>
           <t>2 vs 3</t>
@@ -9698,14 +9724,16 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="13.5" customHeight="1" s="197" thickBot="1">
-      <c r="B14" s="215" t="n"/>
+    <row r="14" ht="13.5" customHeight="1" s="181" thickBot="1">
+      <c r="B14" s="200" t="n"/>
       <c r="C14" s="168" t="inlineStr">
         <is>
           <t>NET Score</t>
         </is>
       </c>
-      <c r="D14" s="169" t="n"/>
+      <c r="D14" s="169" t="n">
+        <v>33</v>
+      </c>
       <c r="E14" s="170" t="n"/>
       <c r="F14" s="170" t="n"/>
       <c r="G14" s="170" t="n"/>
@@ -9714,15 +9742,15 @@
       <c r="J14" s="170" t="n"/>
       <c r="K14" s="170" t="n"/>
       <c r="L14" s="171" t="n"/>
-      <c r="M14" s="223" t="n"/>
-      <c r="N14" s="219" t="n"/>
-      <c r="O14" s="213" t="n"/>
-    </row>
-    <row r="15" ht="12.95" customHeight="1" s="197">
-      <c r="A15" s="228" t="n">
+      <c r="M14" s="208" t="n"/>
+      <c r="N14" s="204" t="n"/>
+      <c r="O14" s="198" t="n"/>
+    </row>
+    <row r="15" ht="12.9" customHeight="1" s="181">
+      <c r="A15" s="213" t="n">
         <v>7</v>
       </c>
-      <c r="B15" s="214">
+      <c r="B15" s="199">
         <f>Schedule!C21</f>
         <v/>
       </c>
@@ -9731,27 +9759,39 @@
           <t>Match Points</t>
         </is>
       </c>
-      <c r="D15" s="158" t="n"/>
-      <c r="E15" s="220" t="n"/>
-      <c r="F15" s="220" t="n"/>
-      <c r="G15" s="220" t="n"/>
-      <c r="H15" s="220" t="n"/>
-      <c r="I15" s="220" t="n"/>
-      <c r="J15" s="220" t="n"/>
-      <c r="K15" s="220" t="n"/>
+      <c r="D15" s="158" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" s="205" t="n"/>
+      <c r="F15" s="205" t="n"/>
+      <c r="G15" s="205" t="n"/>
+      <c r="H15" s="205" t="n"/>
+      <c r="I15" s="205" t="n"/>
+      <c r="J15" s="205" t="n"/>
+      <c r="K15" s="205" t="n"/>
       <c r="L15" s="160" t="n"/>
-      <c r="M15" s="222" t="n"/>
-      <c r="N15" s="220" t="n"/>
-      <c r="O15" s="230" t="n"/>
-    </row>
-    <row r="16" ht="13.5" customHeight="1" s="197" thickBot="1">
-      <c r="B16" s="215" t="n"/>
+      <c r="M15" s="207" t="n">
+        <v>1</v>
+      </c>
+      <c r="N15" s="205" t="inlineStr">
+        <is>
+          <t>0-1-0</t>
+        </is>
+      </c>
+      <c r="O15" s="216" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="16" ht="13.5" customHeight="1" s="181" thickBot="1">
+      <c r="B16" s="200" t="n"/>
       <c r="C16" s="161" t="inlineStr">
         <is>
           <t>NET Score</t>
         </is>
       </c>
-      <c r="D16" s="162" t="n"/>
+      <c r="D16" s="162" t="n">
+        <v>48</v>
+      </c>
       <c r="E16" s="163" t="n"/>
       <c r="F16" s="163" t="n"/>
       <c r="G16" s="163" t="n"/>
@@ -9760,15 +9800,15 @@
       <c r="J16" s="163" t="n"/>
       <c r="K16" s="163" t="n"/>
       <c r="L16" s="164" t="n"/>
-      <c r="M16" s="223" t="n"/>
-      <c r="N16" s="219" t="n"/>
-      <c r="O16" s="213" t="n"/>
-    </row>
-    <row r="17" ht="12.95" customHeight="1" s="197">
-      <c r="A17" s="228" t="n">
+      <c r="M16" s="208" t="n"/>
+      <c r="N16" s="204" t="n"/>
+      <c r="O16" s="198" t="n"/>
+    </row>
+    <row r="17" ht="12.9" customHeight="1" s="181">
+      <c r="A17" s="213" t="n">
         <v>8</v>
       </c>
-      <c r="B17" s="221">
+      <c r="B17" s="206">
         <f>Schedule!C22</f>
         <v/>
       </c>
@@ -9777,7 +9817,9 @@
           <t>Match Points</t>
         </is>
       </c>
-      <c r="D17" s="165" t="n"/>
+      <c r="D17" s="165" t="n">
+        <v>7</v>
+      </c>
       <c r="E17" s="166" t="n"/>
       <c r="F17" s="166" t="n"/>
       <c r="G17" s="166" t="n"/>
@@ -9786,23 +9828,33 @@
       <c r="J17" s="166" t="n"/>
       <c r="K17" s="166" t="n"/>
       <c r="L17" s="167" t="n"/>
-      <c r="M17" s="226" t="n"/>
-      <c r="N17" s="218" t="n"/>
-      <c r="O17" s="212" t="n"/>
-      <c r="Q17" s="227" t="inlineStr">
+      <c r="M17" s="211" t="n">
+        <v>7</v>
+      </c>
+      <c r="N17" s="203" t="inlineStr">
+        <is>
+          <t>1-0-0</t>
+        </is>
+      </c>
+      <c r="O17" s="197" t="n">
+        <v>37</v>
+      </c>
+      <c r="Q17" s="212" t="inlineStr">
         <is>
           <t>Tiebreaker Rules</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="13.5" customHeight="1" s="197" thickBot="1">
-      <c r="B18" s="215" t="n"/>
+    <row r="18" ht="13.5" customHeight="1" s="181" thickBot="1">
+      <c r="B18" s="200" t="n"/>
       <c r="C18" s="168" t="inlineStr">
         <is>
           <t>NET Score</t>
         </is>
       </c>
-      <c r="D18" s="169" t="n"/>
+      <c r="D18" s="169" t="n">
+        <v>37</v>
+      </c>
       <c r="E18" s="170" t="n"/>
       <c r="F18" s="170" t="n"/>
       <c r="G18" s="170" t="n"/>
@@ -9811,9 +9863,9 @@
       <c r="J18" s="170" t="n"/>
       <c r="K18" s="170" t="n"/>
       <c r="L18" s="171" t="n"/>
-      <c r="M18" s="223" t="n"/>
-      <c r="N18" s="219" t="n"/>
-      <c r="O18" s="213" t="n"/>
+      <c r="M18" s="208" t="n"/>
+      <c r="N18" s="204" t="n"/>
+      <c r="O18" s="198" t="n"/>
       <c r="Q18" s="154" t="inlineStr">
         <is>
           <t>1. Highest overall match wins. A match win means you scored 4.5 points or more against your opponent. 4 points will be considered a draw.</t>
@@ -9821,11 +9873,11 @@
       </c>
       <c r="R18" s="21" t="n"/>
     </row>
-    <row r="19" ht="12.95" customHeight="1" s="197">
-      <c r="A19" s="228" t="n">
+    <row r="19" ht="12.9" customHeight="1" s="181">
+      <c r="A19" s="213" t="n">
         <v>9</v>
       </c>
-      <c r="B19" s="214">
+      <c r="B19" s="199">
         <f>Schedule!C23</f>
         <v/>
       </c>
@@ -9834,32 +9886,44 @@
           <t>Match Points</t>
         </is>
       </c>
-      <c r="D19" s="158" t="n"/>
-      <c r="E19" s="220" t="n"/>
-      <c r="F19" s="220" t="n"/>
-      <c r="G19" s="220" t="n"/>
-      <c r="H19" s="220" t="n"/>
-      <c r="I19" s="220" t="n"/>
-      <c r="J19" s="220" t="n"/>
-      <c r="K19" s="220" t="n"/>
+      <c r="D19" s="158" t="n">
+        <v>2</v>
+      </c>
+      <c r="E19" s="205" t="n"/>
+      <c r="F19" s="205" t="n"/>
+      <c r="G19" s="205" t="n"/>
+      <c r="H19" s="205" t="n"/>
+      <c r="I19" s="205" t="n"/>
+      <c r="J19" s="205" t="n"/>
+      <c r="K19" s="205" t="n"/>
       <c r="L19" s="160" t="n"/>
-      <c r="M19" s="222" t="n"/>
-      <c r="N19" s="220" t="n"/>
-      <c r="O19" s="230" t="n"/>
+      <c r="M19" s="207" t="n">
+        <v>2</v>
+      </c>
+      <c r="N19" s="205" t="inlineStr">
+        <is>
+          <t>0-1-0</t>
+        </is>
+      </c>
+      <c r="O19" s="216" t="n">
+        <v>39</v>
+      </c>
       <c r="Q19" s="154" t="inlineStr">
         <is>
           <t>2. Lowest average NET score for all 8 matches.</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="13.5" customHeight="1" s="197" thickBot="1">
-      <c r="B20" s="215" t="n"/>
+    <row r="20" ht="13.5" customHeight="1" s="181" thickBot="1">
+      <c r="B20" s="200" t="n"/>
       <c r="C20" s="161" t="inlineStr">
         <is>
           <t>NET Score</t>
         </is>
       </c>
-      <c r="D20" s="162" t="n"/>
+      <c r="D20" s="162" t="n">
+        <v>39</v>
+      </c>
       <c r="E20" s="163" t="n"/>
       <c r="F20" s="163" t="n"/>
       <c r="G20" s="163" t="n"/>
@@ -9868,9 +9932,9 @@
       <c r="J20" s="163" t="n"/>
       <c r="K20" s="163" t="n"/>
       <c r="L20" s="164" t="n"/>
-      <c r="M20" s="223" t="n"/>
-      <c r="N20" s="219" t="n"/>
-      <c r="O20" s="213" t="n"/>
+      <c r="M20" s="208" t="n"/>
+      <c r="N20" s="204" t="n"/>
+      <c r="O20" s="198" t="n"/>
       <c r="Q20" s="154" t="inlineStr">
         <is>
           <t>3. Lowest Round 8 NET score.</t>
@@ -9878,11 +9942,11 @@
       </c>
       <c r="R20" s="21" t="n"/>
     </row>
-    <row r="21" ht="12.95" customHeight="1" s="197">
-      <c r="A21" s="228" t="n">
+    <row r="21" ht="12.9" customHeight="1" s="181">
+      <c r="A21" s="213" t="n">
         <v>10</v>
       </c>
-      <c r="B21" s="221">
+      <c r="B21" s="206">
         <f>Schedule!C24</f>
         <v/>
       </c>
@@ -9891,7 +9955,9 @@
           <t>Match Points</t>
         </is>
       </c>
-      <c r="D21" s="165" t="n"/>
+      <c r="D21" s="165" t="n">
+        <v>6</v>
+      </c>
       <c r="E21" s="166" t="n"/>
       <c r="F21" s="166" t="n"/>
       <c r="G21" s="166" t="n"/>
@@ -9900,9 +9966,17 @@
       <c r="J21" s="166" t="n"/>
       <c r="K21" s="166" t="n"/>
       <c r="L21" s="167" t="n"/>
-      <c r="M21" s="226" t="n"/>
-      <c r="N21" s="218" t="n"/>
-      <c r="O21" s="212" t="n"/>
+      <c r="M21" s="211" t="n">
+        <v>6</v>
+      </c>
+      <c r="N21" s="203" t="inlineStr">
+        <is>
+          <t>1-0-0</t>
+        </is>
+      </c>
+      <c r="O21" s="197" t="n">
+        <v>35</v>
+      </c>
       <c r="Q21" s="154" t="inlineStr">
         <is>
           <t>4. Coin Flip or however the two parties wish to settle it.</t>
@@ -9910,14 +9984,16 @@
       </c>
       <c r="R21" s="21" t="n"/>
     </row>
-    <row r="22" ht="13.5" customHeight="1" s="197" thickBot="1">
-      <c r="B22" s="215" t="n"/>
+    <row r="22" ht="13.5" customHeight="1" s="181" thickBot="1">
+      <c r="B22" s="200" t="n"/>
       <c r="C22" s="168" t="inlineStr">
         <is>
           <t>NET Score</t>
         </is>
       </c>
-      <c r="D22" s="169" t="n"/>
+      <c r="D22" s="169" t="n">
+        <v>35</v>
+      </c>
       <c r="E22" s="170" t="n"/>
       <c r="F22" s="170" t="n"/>
       <c r="G22" s="170" t="n"/>
@@ -9926,15 +10002,15 @@
       <c r="J22" s="170" t="n"/>
       <c r="K22" s="170" t="n"/>
       <c r="L22" s="171" t="n"/>
-      <c r="M22" s="223" t="n"/>
-      <c r="N22" s="219" t="n"/>
-      <c r="O22" s="213" t="n"/>
-    </row>
-    <row r="23" ht="12.95" customHeight="1" s="197">
-      <c r="A23" s="228" t="n">
+      <c r="M22" s="208" t="n"/>
+      <c r="N22" s="204" t="n"/>
+      <c r="O22" s="198" t="n"/>
+    </row>
+    <row r="23" ht="12.9" customHeight="1" s="181">
+      <c r="A23" s="213" t="n">
         <v>11</v>
       </c>
-      <c r="B23" s="214">
+      <c r="B23" s="199">
         <f>Schedule!C25</f>
         <v/>
       </c>
@@ -9944,20 +10020,20 @@
         </is>
       </c>
       <c r="D23" s="158" t="n"/>
-      <c r="E23" s="220" t="n"/>
-      <c r="F23" s="220" t="n"/>
-      <c r="G23" s="220" t="n"/>
-      <c r="H23" s="220" t="n"/>
-      <c r="I23" s="220" t="n"/>
-      <c r="J23" s="220" t="n"/>
-      <c r="K23" s="220" t="n"/>
+      <c r="E23" s="205" t="n"/>
+      <c r="F23" s="205" t="n"/>
+      <c r="G23" s="205" t="n"/>
+      <c r="H23" s="205" t="n"/>
+      <c r="I23" s="205" t="n"/>
+      <c r="J23" s="205" t="n"/>
+      <c r="K23" s="205" t="n"/>
       <c r="L23" s="160" t="n"/>
-      <c r="M23" s="222" t="n"/>
-      <c r="N23" s="220" t="n"/>
-      <c r="O23" s="230" t="n"/>
-    </row>
-    <row r="24" ht="13.5" customHeight="1" s="197" thickBot="1">
-      <c r="B24" s="215" t="n"/>
+      <c r="M23" s="207" t="n"/>
+      <c r="N23" s="205" t="n"/>
+      <c r="O23" s="216" t="n"/>
+    </row>
+    <row r="24" ht="13.5" customHeight="1" s="181" thickBot="1">
+      <c r="B24" s="200" t="n"/>
       <c r="C24" s="161" t="inlineStr">
         <is>
           <t>NET Score</t>
@@ -9972,15 +10048,15 @@
       <c r="J24" s="163" t="n"/>
       <c r="K24" s="163" t="n"/>
       <c r="L24" s="164" t="n"/>
-      <c r="M24" s="223" t="n"/>
-      <c r="N24" s="219" t="n"/>
-      <c r="O24" s="213" t="n"/>
-    </row>
-    <row r="25" ht="12.95" customHeight="1" s="197">
-      <c r="A25" s="228" t="n">
+      <c r="M24" s="208" t="n"/>
+      <c r="N24" s="204" t="n"/>
+      <c r="O24" s="198" t="n"/>
+    </row>
+    <row r="25" ht="12.9" customHeight="1" s="181">
+      <c r="A25" s="213" t="n">
         <v>12</v>
       </c>
-      <c r="B25" s="221">
+      <c r="B25" s="206">
         <f>Schedule!C26</f>
         <v/>
       </c>
@@ -10000,20 +10076,20 @@
       <c r="J25" s="166" t="n"/>
       <c r="K25" s="166" t="n"/>
       <c r="L25" s="167" t="n"/>
-      <c r="M25" s="226" t="n">
+      <c r="M25" s="211" t="n">
         <v>4</v>
       </c>
-      <c r="N25" s="218" t="inlineStr">
+      <c r="N25" s="203" t="inlineStr">
         <is>
           <t>0-0-1</t>
         </is>
       </c>
-      <c r="O25" s="212" t="n">
+      <c r="O25" s="197" t="n">
         <v>54</v>
       </c>
     </row>
-    <row r="26" ht="13.5" customHeight="1" s="197" thickBot="1">
-      <c r="B26" s="215" t="n"/>
+    <row r="26" ht="13.5" customHeight="1" s="181" thickBot="1">
+      <c r="B26" s="200" t="n"/>
       <c r="C26" s="168" t="inlineStr">
         <is>
           <t>NET Score</t>
@@ -10030,15 +10106,15 @@
       <c r="J26" s="170" t="n"/>
       <c r="K26" s="170" t="n"/>
       <c r="L26" s="171" t="n"/>
-      <c r="M26" s="223" t="n"/>
-      <c r="N26" s="219" t="n"/>
-      <c r="O26" s="213" t="n"/>
-    </row>
-    <row r="27" ht="12.95" customHeight="1" s="197">
-      <c r="A27" s="228" t="n">
+      <c r="M26" s="208" t="n"/>
+      <c r="N26" s="204" t="n"/>
+      <c r="O26" s="198" t="n"/>
+    </row>
+    <row r="27" ht="12.9" customHeight="1" s="181">
+      <c r="A27" s="213" t="n">
         <v>13</v>
       </c>
-      <c r="B27" s="214">
+      <c r="B27" s="199">
         <f>Schedule!C27</f>
         <v/>
       </c>
@@ -10050,28 +10126,28 @@
       <c r="D27" s="158" t="n">
         <v>4</v>
       </c>
-      <c r="E27" s="220" t="n"/>
-      <c r="F27" s="220" t="n"/>
-      <c r="G27" s="220" t="n"/>
-      <c r="H27" s="220" t="n"/>
-      <c r="I27" s="220" t="n"/>
-      <c r="J27" s="220" t="n"/>
-      <c r="K27" s="220" t="n"/>
+      <c r="E27" s="205" t="n"/>
+      <c r="F27" s="205" t="n"/>
+      <c r="G27" s="205" t="n"/>
+      <c r="H27" s="205" t="n"/>
+      <c r="I27" s="205" t="n"/>
+      <c r="J27" s="205" t="n"/>
+      <c r="K27" s="205" t="n"/>
       <c r="L27" s="160" t="n"/>
-      <c r="M27" s="222" t="n">
+      <c r="M27" s="207" t="n">
         <v>4</v>
       </c>
-      <c r="N27" s="220" t="inlineStr">
+      <c r="N27" s="205" t="inlineStr">
         <is>
           <t>0-0-1</t>
         </is>
       </c>
-      <c r="O27" s="230" t="n">
+      <c r="O27" s="216" t="n">
         <v>54</v>
       </c>
     </row>
-    <row r="28" ht="13.5" customHeight="1" s="197" thickBot="1">
-      <c r="B28" s="215" t="n"/>
+    <row r="28" ht="13.5" customHeight="1" s="181" thickBot="1">
+      <c r="B28" s="200" t="n"/>
       <c r="C28" s="161" t="inlineStr">
         <is>
           <t>NET Score</t>
@@ -10088,15 +10164,15 @@
       <c r="J28" s="163" t="n"/>
       <c r="K28" s="163" t="n"/>
       <c r="L28" s="164" t="n"/>
-      <c r="M28" s="223" t="n"/>
-      <c r="N28" s="219" t="n"/>
-      <c r="O28" s="213" t="n"/>
-    </row>
-    <row r="29" ht="12.95" customHeight="1" s="197">
-      <c r="A29" s="228" t="n">
+      <c r="M28" s="208" t="n"/>
+      <c r="N28" s="204" t="n"/>
+      <c r="O28" s="198" t="n"/>
+    </row>
+    <row r="29" ht="12.9" customHeight="1" s="181">
+      <c r="A29" s="213" t="n">
         <v>14</v>
       </c>
-      <c r="B29" s="221">
+      <c r="B29" s="206">
         <f>Schedule!C28</f>
         <v/>
       </c>
@@ -10105,7 +10181,9 @@
           <t>Match Points</t>
         </is>
       </c>
-      <c r="D29" s="165" t="n"/>
+      <c r="D29" s="165" t="n">
+        <v>7</v>
+      </c>
       <c r="E29" s="166" t="n"/>
       <c r="F29" s="166" t="n"/>
       <c r="G29" s="166" t="n"/>
@@ -10114,18 +10192,28 @@
       <c r="J29" s="166" t="n"/>
       <c r="K29" s="166" t="n"/>
       <c r="L29" s="167" t="n"/>
-      <c r="M29" s="226" t="n"/>
-      <c r="N29" s="218" t="n"/>
-      <c r="O29" s="212" t="n"/>
-    </row>
-    <row r="30" ht="13.5" customHeight="1" s="197" thickBot="1">
-      <c r="B30" s="215" t="n"/>
+      <c r="M29" s="211" t="n">
+        <v>7</v>
+      </c>
+      <c r="N29" s="203" t="inlineStr">
+        <is>
+          <t>1-0-0</t>
+        </is>
+      </c>
+      <c r="O29" s="197" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="30" ht="13.5" customHeight="1" s="181" thickBot="1">
+      <c r="B30" s="200" t="n"/>
       <c r="C30" s="168" t="inlineStr">
         <is>
           <t>NET Score</t>
         </is>
       </c>
-      <c r="D30" s="169" t="n"/>
+      <c r="D30" s="169" t="n">
+        <v>50</v>
+      </c>
       <c r="E30" s="170" t="n"/>
       <c r="F30" s="170" t="n"/>
       <c r="G30" s="170" t="n"/>
@@ -10134,15 +10222,15 @@
       <c r="J30" s="170" t="n"/>
       <c r="K30" s="170" t="n"/>
       <c r="L30" s="171" t="n"/>
-      <c r="M30" s="223" t="n"/>
-      <c r="N30" s="219" t="n"/>
-      <c r="O30" s="213" t="n"/>
-    </row>
-    <row r="31" ht="12.95" customHeight="1" s="197">
-      <c r="A31" s="228" t="n">
+      <c r="M30" s="208" t="n"/>
+      <c r="N30" s="204" t="n"/>
+      <c r="O30" s="198" t="n"/>
+    </row>
+    <row r="31" ht="12.9" customHeight="1" s="181">
+      <c r="A31" s="213" t="n">
         <v>15</v>
       </c>
-      <c r="B31" s="214">
+      <c r="B31" s="199">
         <f>Schedule!C29</f>
         <v/>
       </c>
@@ -10151,27 +10239,39 @@
           <t>Match Points</t>
         </is>
       </c>
-      <c r="D31" s="158" t="n"/>
-      <c r="E31" s="220" t="n"/>
-      <c r="F31" s="220" t="n"/>
-      <c r="G31" s="220" t="n"/>
-      <c r="H31" s="220" t="n"/>
-      <c r="I31" s="220" t="n"/>
-      <c r="J31" s="220" t="n"/>
-      <c r="K31" s="220" t="n"/>
+      <c r="D31" s="158" t="n">
+        <v>1</v>
+      </c>
+      <c r="E31" s="205" t="n"/>
+      <c r="F31" s="205" t="n"/>
+      <c r="G31" s="205" t="n"/>
+      <c r="H31" s="205" t="n"/>
+      <c r="I31" s="205" t="n"/>
+      <c r="J31" s="205" t="n"/>
+      <c r="K31" s="205" t="n"/>
       <c r="L31" s="160" t="n"/>
-      <c r="M31" s="222" t="n"/>
-      <c r="N31" s="220" t="n"/>
-      <c r="O31" s="230" t="n"/>
-    </row>
-    <row r="32" ht="13.5" customHeight="1" s="197" thickBot="1">
-      <c r="B32" s="215" t="n"/>
+      <c r="M31" s="207" t="n">
+        <v>1</v>
+      </c>
+      <c r="N31" s="205" t="inlineStr">
+        <is>
+          <t>0-1-0</t>
+        </is>
+      </c>
+      <c r="O31" s="216" t="n">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="32" ht="13.5" customHeight="1" s="181" thickBot="1">
+      <c r="B32" s="200" t="n"/>
       <c r="C32" s="161" t="inlineStr">
         <is>
           <t>NET Score</t>
         </is>
       </c>
-      <c r="D32" s="162" t="n"/>
+      <c r="D32" s="162" t="n">
+        <v>53</v>
+      </c>
       <c r="E32" s="163" t="n"/>
       <c r="F32" s="163" t="n"/>
       <c r="G32" s="163" t="n"/>
@@ -10180,9 +10280,9 @@
       <c r="J32" s="163" t="n"/>
       <c r="K32" s="163" t="n"/>
       <c r="L32" s="164" t="n"/>
-      <c r="M32" s="223" t="n"/>
-      <c r="N32" s="219" t="n"/>
-      <c r="O32" s="213" t="n"/>
+      <c r="M32" s="208" t="n"/>
+      <c r="N32" s="204" t="n"/>
+      <c r="O32" s="198" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" algorithmName="SHA-512" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" saltValue="kkQ/PatKpMHBAJY782mRBw==" formatRows="1" sort="1" spinCount="100000" password="94CD" hashValue="Y3y62YBPDCQhqKgsSl1/iH5xODfF8lm4IgTCoiweq2jLnTBBsjKN4ZDmcY+ulNgK91riyyuYS5VZZqKHpfKB8g=="/>
@@ -10211,15 +10311,15 @@
     <mergeCell ref="O25:O26"/>
     <mergeCell ref="M3:M4"/>
     <mergeCell ref="Q17:S17"/>
+    <mergeCell ref="N29:N30"/>
     <mergeCell ref="O21:O22"/>
-    <mergeCell ref="N29:N30"/>
     <mergeCell ref="N1:O1"/>
+    <mergeCell ref="B19:B20"/>
+    <mergeCell ref="O31:O32"/>
+    <mergeCell ref="M27:M28"/>
+    <mergeCell ref="N19:N20"/>
+    <mergeCell ref="B15:B16"/>
     <mergeCell ref="N23:N24"/>
-    <mergeCell ref="O31:O32"/>
-    <mergeCell ref="B15:B16"/>
-    <mergeCell ref="N19:N20"/>
-    <mergeCell ref="M27:M28"/>
-    <mergeCell ref="B19:B20"/>
     <mergeCell ref="B9:B10"/>
     <mergeCell ref="N13:N14"/>
     <mergeCell ref="M21:M22"/>
@@ -10264,41 +10364,41 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="B1:AE24"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9.85546875" defaultRowHeight="13.5"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9.88671875" defaultRowHeight="13.8"/>
   <cols>
-    <col width="2.5703125" customWidth="1" style="235" min="1" max="1"/>
-    <col width="27.85546875" customWidth="1" style="235" min="2" max="2"/>
-    <col width="9.85546875" customWidth="1" style="235" min="3" max="8"/>
-    <col width="10.7109375" bestFit="1" customWidth="1" style="235" min="9" max="9"/>
-    <col width="10.5703125" customWidth="1" style="235" min="10" max="11"/>
-    <col width="10.85546875" customWidth="1" style="235" min="12" max="13"/>
-    <col width="5.7109375" customWidth="1" style="235" min="14" max="14"/>
-    <col width="11" bestFit="1" customWidth="1" style="235" min="15" max="15"/>
-    <col width="4.5703125" customWidth="1" style="235" min="16" max="24"/>
-    <col width="7.5703125" customWidth="1" style="235" min="25" max="25"/>
-    <col width="9.85546875" customWidth="1" style="235" min="26" max="27"/>
-    <col width="16.42578125" bestFit="1" customWidth="1" style="235" min="28" max="28"/>
-    <col width="12.7109375" customWidth="1" style="235" min="29" max="30"/>
-    <col width="9.85546875" customWidth="1" style="235" min="31" max="37"/>
-    <col width="9.85546875" customWidth="1" style="235" min="38" max="16384"/>
+    <col width="2.5546875" customWidth="1" style="222" min="1" max="1"/>
+    <col width="27.88671875" customWidth="1" style="222" min="2" max="2"/>
+    <col width="9.88671875" customWidth="1" style="222" min="3" max="8"/>
+    <col width="10.6640625" bestFit="1" customWidth="1" style="222" min="9" max="9"/>
+    <col width="10.5546875" customWidth="1" style="222" min="10" max="11"/>
+    <col width="10.88671875" customWidth="1" style="222" min="12" max="13"/>
+    <col width="5.6640625" customWidth="1" style="222" min="14" max="14"/>
+    <col width="11" bestFit="1" customWidth="1" style="222" min="15" max="15"/>
+    <col width="4.5546875" customWidth="1" style="222" min="16" max="24"/>
+    <col width="7.5546875" customWidth="1" style="222" min="25" max="25"/>
+    <col width="9.88671875" customWidth="1" style="222" min="26" max="27"/>
+    <col width="16.44140625" bestFit="1" customWidth="1" style="222" min="28" max="28"/>
+    <col width="12.6640625" customWidth="1" style="222" min="29" max="30"/>
+    <col width="9.88671875" customWidth="1" style="222" min="31" max="43"/>
+    <col width="9.88671875" customWidth="1" style="222" min="44" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.25" customHeight="1" s="197" thickBot="1">
+    <row r="1" ht="14.25" customHeight="1" s="181" thickBot="1">
       <c r="B1" s="47" t="inlineStr">
         <is>
           <t>Fill in your name, tees, front/back 9, and gross scores in the grey boxes</t>
         </is>
       </c>
-      <c r="J1" s="240" t="inlineStr">
+      <c r="J1" s="231" t="inlineStr">
         <is>
           <t>Points</t>
         </is>
       </c>
-      <c r="K1" s="191" t="n"/>
-      <c r="L1" s="191" t="n"/>
-      <c r="M1" s="191" t="n"/>
-    </row>
-    <row r="2" ht="24.95" customHeight="1" s="197" thickBot="1">
+      <c r="K1" s="215" t="n"/>
+      <c r="L1" s="215" t="n"/>
+      <c r="M1" s="215" t="n"/>
+    </row>
+    <row r="2" ht="24.9" customHeight="1" s="181" thickBot="1">
       <c r="D2" s="49" t="inlineStr">
         <is>
           <t>First 3</t>
@@ -10325,16 +10425,16 @@
         </is>
       </c>
       <c r="I2" s="50" t="n"/>
-      <c r="J2" s="237">
+      <c r="J2" s="229">
         <f>B8</f>
         <v/>
       </c>
-      <c r="K2" s="179" t="n"/>
-      <c r="L2" s="233">
+      <c r="K2" s="219" t="n"/>
+      <c r="L2" s="220">
         <f>B17</f>
         <v/>
       </c>
-      <c r="M2" s="179" t="n"/>
+      <c r="M2" s="219" t="n"/>
       <c r="AA2" s="112" t="inlineStr">
         <is>
           <t>#</t>
@@ -10361,8 +10461,8 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="14.25" customHeight="1" s="197" thickBot="1">
-      <c r="B3" s="238">
+    <row r="3" ht="14.25" customHeight="1" s="181" thickBot="1">
+      <c r="B3" s="230">
         <f>B8</f>
         <v/>
       </c>
@@ -10391,16 +10491,16 @@
         <f>SUM(C14:K14)</f>
         <v/>
       </c>
-      <c r="J3" s="236">
+      <c r="J3" s="223">
         <f>SUM(D4:H4)</f>
         <v/>
       </c>
-      <c r="K3" s="183" t="n"/>
-      <c r="L3" s="239">
+      <c r="K3" s="224" t="n"/>
+      <c r="L3" s="232">
         <f>SUM(D6:H6)</f>
         <v/>
       </c>
-      <c r="M3" s="183" t="n"/>
+      <c r="M3" s="224" t="n"/>
       <c r="AA3" s="110" t="n">
         <v>13</v>
       </c>
@@ -10421,8 +10521,8 @@
         <v>25</v>
       </c>
     </row>
-    <row r="4" ht="14.25" customHeight="1" s="197" thickBot="1">
-      <c r="B4" s="186" t="n"/>
+    <row r="4" ht="14.25" customHeight="1" s="181" thickBot="1">
+      <c r="B4" s="227" t="n"/>
       <c r="C4" s="57" t="inlineStr">
         <is>
           <t>PTS</t>
@@ -10448,9 +10548,9 @@
         <f>IF(H3&lt;H5,1,IF(H3=H5,0.5,0))</f>
         <v/>
       </c>
-      <c r="J4" s="184" t="n"/>
-      <c r="K4" s="185" t="n"/>
-      <c r="M4" s="185" t="n"/>
+      <c r="J4" s="225" t="n"/>
+      <c r="K4" s="226" t="n"/>
+      <c r="M4" s="226" t="n"/>
       <c r="AA4" s="110" t="n">
         <v>17</v>
       </c>
@@ -10471,8 +10571,8 @@
         <v>30</v>
       </c>
     </row>
-    <row r="5" ht="14.25" customHeight="1" s="197" thickBot="1">
-      <c r="B5" s="238">
+    <row r="5" ht="14.25" customHeight="1" s="181" thickBot="1">
+      <c r="B5" s="230">
         <f>B17</f>
         <v/>
       </c>
@@ -10501,10 +10601,10 @@
         <f>SUM(C23:K23)</f>
         <v/>
       </c>
-      <c r="J5" s="186" t="n"/>
-      <c r="K5" s="187" t="n"/>
-      <c r="L5" s="191" t="n"/>
-      <c r="M5" s="187" t="n"/>
+      <c r="J5" s="227" t="n"/>
+      <c r="K5" s="228" t="n"/>
+      <c r="L5" s="215" t="n"/>
+      <c r="M5" s="228" t="n"/>
       <c r="AA5" s="110" t="n">
         <v>4</v>
       </c>
@@ -10525,8 +10625,8 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" ht="14.25" customHeight="1" s="197" thickBot="1">
-      <c r="B6" s="186" t="n"/>
+    <row r="6" ht="14.25" customHeight="1" s="181" thickBot="1">
+      <c r="B6" s="227" t="n"/>
       <c r="C6" s="57" t="inlineStr">
         <is>
           <t>PTS</t>
@@ -10552,10 +10652,10 @@
         <f>IF(H5&lt;H3,1,IF(H5=H3,0.5,0))</f>
         <v/>
       </c>
-      <c r="J6" s="234" t="n"/>
-      <c r="K6" s="234" t="n"/>
-      <c r="L6" s="234" t="n"/>
-      <c r="M6" s="234" t="n"/>
+      <c r="J6" s="221" t="n"/>
+      <c r="K6" s="221" t="n"/>
+      <c r="L6" s="221" t="n"/>
+      <c r="M6" s="221" t="n"/>
       <c r="AA6" s="110" t="n">
         <v>11</v>
       </c>
@@ -10577,16 +10677,16 @@
       </c>
     </row>
     <row r="7">
-      <c r="C7" s="234" t="n"/>
-      <c r="D7" s="234" t="n"/>
-      <c r="E7" s="234" t="n"/>
-      <c r="F7" s="234" t="n"/>
-      <c r="G7" s="234" t="n"/>
-      <c r="H7" s="234" t="n"/>
-      <c r="I7" s="234" t="n"/>
-      <c r="J7" s="234" t="n"/>
-      <c r="K7" s="234" t="n"/>
-      <c r="L7" s="234" t="n"/>
+      <c r="C7" s="221" t="n"/>
+      <c r="D7" s="221" t="n"/>
+      <c r="E7" s="221" t="n"/>
+      <c r="F7" s="221" t="n"/>
+      <c r="G7" s="221" t="n"/>
+      <c r="H7" s="221" t="n"/>
+      <c r="I7" s="221" t="n"/>
+      <c r="J7" s="221" t="n"/>
+      <c r="K7" s="221" t="n"/>
+      <c r="L7" s="221" t="n"/>
       <c r="AA7" s="110" t="n">
         <v>5</v>
       </c>
@@ -10607,7 +10707,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" ht="19.5" customHeight="1" s="197" thickBot="1">
+    <row r="8" ht="19.5" customHeight="1" s="181" thickBot="1">
       <c r="B8" s="109" t="inlineStr">
         <is>
           <t>Ethan High</t>
@@ -10618,12 +10718,12 @@
           <t>Handicap:</t>
         </is>
       </c>
-      <c r="D8" s="234">
+      <c r="D8" s="221">
         <f>IFERROR(VLOOKUP(B8,$AB$3:$AE$21,4,0),0)</f>
         <v/>
       </c>
-      <c r="E8" s="234" t="n"/>
-      <c r="F8" s="234" t="inlineStr">
+      <c r="E8" s="221" t="n"/>
+      <c r="F8" s="221" t="inlineStr">
         <is>
           <t>Tees:</t>
         </is>
@@ -10633,8 +10733,8 @@
           <t>Black</t>
         </is>
       </c>
-      <c r="H8" s="234" t="n"/>
-      <c r="I8" s="234" t="inlineStr">
+      <c r="H8" s="221" t="n"/>
+      <c r="I8" s="221" t="inlineStr">
         <is>
           <t>Holes:</t>
         </is>
@@ -10644,14 +10744,14 @@
           <t>Front 9</t>
         </is>
       </c>
-      <c r="K8" s="234" t="n"/>
-      <c r="L8" s="234" t="n"/>
-      <c r="O8" s="235" t="inlineStr">
+      <c r="K8" s="221" t="n"/>
+      <c r="L8" s="221" t="n"/>
+      <c r="O8" s="222" t="inlineStr">
         <is>
           <t>HC's by Tees</t>
         </is>
       </c>
-      <c r="P8" s="234" t="inlineStr">
+      <c r="P8" s="221" t="inlineStr">
         <is>
           <t>Front 9</t>
         </is>
@@ -10676,7 +10776,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" s="197">
+    <row r="9" ht="15" customHeight="1" s="181">
       <c r="B9" s="64" t="inlineStr">
         <is>
           <t>HOLE</t>
@@ -10709,37 +10809,37 @@
       <c r="K9" s="67" t="n">
         <v>9</v>
       </c>
-      <c r="L9" s="234" t="n"/>
-      <c r="O9" s="235" t="inlineStr">
+      <c r="L9" s="221" t="n"/>
+      <c r="O9" s="222" t="inlineStr">
         <is>
           <t>Black</t>
         </is>
       </c>
-      <c r="P9" s="234" t="n">
+      <c r="P9" s="221" t="n">
         <v>1</v>
       </c>
-      <c r="Q9" s="234" t="n">
+      <c r="Q9" s="221" t="n">
         <v>9</v>
       </c>
-      <c r="R9" s="234" t="n">
+      <c r="R9" s="221" t="n">
         <v>7</v>
       </c>
-      <c r="S9" s="234" t="n">
+      <c r="S9" s="221" t="n">
         <v>13</v>
       </c>
-      <c r="T9" s="234" t="n">
+      <c r="T9" s="221" t="n">
         <v>15</v>
       </c>
-      <c r="U9" s="234" t="n">
+      <c r="U9" s="221" t="n">
         <v>5</v>
       </c>
-      <c r="V9" s="234" t="n">
+      <c r="V9" s="221" t="n">
         <v>11</v>
       </c>
-      <c r="W9" s="234" t="n">
+      <c r="W9" s="221" t="n">
         <v>3</v>
       </c>
-      <c r="X9" s="234" t="n">
+      <c r="X9" s="221" t="n">
         <v>17</v>
       </c>
       <c r="AA9" s="110" t="n">
@@ -10771,7 +10871,7 @@
       <c r="C10" s="69" t="n">
         <v>4</v>
       </c>
-      <c r="D10" s="234" t="n">
+      <c r="D10" s="221" t="n">
         <v>5</v>
       </c>
       <c r="E10" s="70" t="n">
@@ -10780,7 +10880,7 @@
       <c r="F10" s="69" t="n">
         <v>4</v>
       </c>
-      <c r="G10" s="234" t="n">
+      <c r="G10" s="221" t="n">
         <v>5</v>
       </c>
       <c r="H10" s="70" t="n">
@@ -10789,46 +10889,46 @@
       <c r="I10" s="69" t="n">
         <v>4</v>
       </c>
-      <c r="J10" s="234" t="n">
+      <c r="J10" s="221" t="n">
         <v>4</v>
       </c>
       <c r="K10" s="70" t="n">
         <v>4</v>
       </c>
-      <c r="L10" s="234">
+      <c r="L10" s="221">
         <f>SUM(C10:K10)</f>
         <v/>
       </c>
-      <c r="O10" s="235" t="inlineStr">
+      <c r="O10" s="222" t="inlineStr">
         <is>
           <t>Blue</t>
         </is>
       </c>
-      <c r="P10" s="234" t="n">
+      <c r="P10" s="221" t="n">
         <v>1</v>
       </c>
-      <c r="Q10" s="234" t="n">
+      <c r="Q10" s="221" t="n">
         <v>9</v>
       </c>
-      <c r="R10" s="234" t="n">
+      <c r="R10" s="221" t="n">
         <v>7</v>
       </c>
-      <c r="S10" s="234" t="n">
+      <c r="S10" s="221" t="n">
         <v>13</v>
       </c>
-      <c r="T10" s="234" t="n">
+      <c r="T10" s="221" t="n">
         <v>15</v>
       </c>
-      <c r="U10" s="234" t="n">
+      <c r="U10" s="221" t="n">
         <v>5</v>
       </c>
-      <c r="V10" s="234" t="n">
+      <c r="V10" s="221" t="n">
         <v>11</v>
       </c>
-      <c r="W10" s="234" t="n">
+      <c r="W10" s="221" t="n">
         <v>3</v>
       </c>
-      <c r="X10" s="234" t="n">
+      <c r="X10" s="221" t="n">
         <v>17</v>
       </c>
       <c r="AA10" s="110" t="n">
@@ -10861,7 +10961,7 @@
         <f t="array" ref="C11">_xlfn.IFS($J8="Back 9",VLOOKUP($G8,$O$15:$X$18,COLUMN()-1,0),$J8="Front 9",VLOOKUP($G8,$O$9:$X$12,COLUMN()-1,0))</f>
         <v/>
       </c>
-      <c r="D11" s="234">
+      <c r="D11" s="221">
         <f t="array" ref="D11">_xlfn.IFS($J8="Back 9",VLOOKUP($G8,$O$15:$X$18,COLUMN()-1,0),$J8="Front 9",VLOOKUP($G8,$O$9:$X$12,COLUMN()-1,0))</f>
         <v/>
       </c>
@@ -10873,7 +10973,7 @@
         <f t="array" ref="F11">_xlfn.IFS($J8="Back 9",VLOOKUP($G8,$O$15:$X$18,COLUMN()-1,0),$J8="Front 9",VLOOKUP($G8,$O$9:$X$12,COLUMN()-1,0))</f>
         <v/>
       </c>
-      <c r="G11" s="234">
+      <c r="G11" s="221">
         <f t="array" ref="G11">_xlfn.IFS($J8="Back 9",VLOOKUP($G8,$O$15:$X$18,COLUMN()-1,0),$J8="Front 9",VLOOKUP($G8,$O$9:$X$12,COLUMN()-1,0))</f>
         <v/>
       </c>
@@ -10885,7 +10985,7 @@
         <f t="array" ref="I11">_xlfn.IFS($J8="Back 9",VLOOKUP($G8,$O$15:$X$18,COLUMN()-1,0),$J8="Front 9",VLOOKUP($G8,$O$9:$X$12,COLUMN()-1,0))</f>
         <v/>
       </c>
-      <c r="J11" s="234">
+      <c r="J11" s="221">
         <f t="array" ref="J11">_xlfn.IFS($J8="Back 9",VLOOKUP($G8,$O$15:$X$18,COLUMN()-1,0),$J8="Front 9",VLOOKUP($G8,$O$9:$X$12,COLUMN()-1,0))</f>
         <v/>
       </c>
@@ -10893,37 +10993,37 @@
         <f t="array" ref="K11">_xlfn.IFS($J8="Back 9",VLOOKUP($G8,$O$15:$X$18,COLUMN()-1,0),$J8="Front 9",VLOOKUP($G8,$O$9:$X$12,COLUMN()-1,0))</f>
         <v/>
       </c>
-      <c r="L11" s="234" t="n"/>
-      <c r="O11" s="235" t="inlineStr">
+      <c r="L11" s="221" t="n"/>
+      <c r="O11" s="222" t="inlineStr">
         <is>
           <t>Blue / White</t>
         </is>
       </c>
-      <c r="P11" s="234" t="n">
+      <c r="P11" s="221" t="n">
         <v>3</v>
       </c>
-      <c r="Q11" s="234" t="n">
+      <c r="Q11" s="221" t="n">
         <v>7</v>
       </c>
-      <c r="R11" s="234" t="n">
+      <c r="R11" s="221" t="n">
         <v>13</v>
       </c>
-      <c r="S11" s="234" t="n">
+      <c r="S11" s="221" t="n">
         <v>17</v>
       </c>
-      <c r="T11" s="234" t="n">
+      <c r="T11" s="221" t="n">
         <v>15</v>
       </c>
-      <c r="U11" s="234" t="n">
+      <c r="U11" s="221" t="n">
         <v>1</v>
       </c>
-      <c r="V11" s="234" t="n">
+      <c r="V11" s="221" t="n">
         <v>11</v>
       </c>
-      <c r="W11" s="234" t="n">
+      <c r="W11" s="221" t="n">
         <v>5</v>
       </c>
-      <c r="X11" s="234" t="n">
+      <c r="X11" s="221" t="n">
         <v>9</v>
       </c>
       <c r="AA11" s="110" t="n">
@@ -10946,7 +11046,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1" s="197">
+    <row r="12" ht="15" customHeight="1" s="181">
       <c r="B12" s="71" t="inlineStr">
         <is>
           <t>GROSS</t>
@@ -10979,7 +11079,7 @@
       <c r="K12" s="115" t="n">
         <v>5</v>
       </c>
-      <c r="L12" s="234">
+      <c r="L12" s="221">
         <f>SUM(C12:K12)</f>
         <v/>
       </c>
@@ -10987,36 +11087,36 @@
         <f>SUM(C12:K12)-SUM(C$10:K$10)</f>
         <v/>
       </c>
-      <c r="O12" s="235" t="inlineStr">
+      <c r="O12" s="222" t="inlineStr">
         <is>
           <t>White</t>
         </is>
       </c>
-      <c r="P12" s="234" t="n">
+      <c r="P12" s="221" t="n">
         <v>1</v>
       </c>
-      <c r="Q12" s="234" t="n">
+      <c r="Q12" s="221" t="n">
         <v>7</v>
       </c>
-      <c r="R12" s="234" t="n">
+      <c r="R12" s="221" t="n">
         <v>11</v>
       </c>
-      <c r="S12" s="234" t="n">
+      <c r="S12" s="221" t="n">
         <v>13</v>
       </c>
-      <c r="T12" s="234" t="n">
+      <c r="T12" s="221" t="n">
         <v>15</v>
       </c>
-      <c r="U12" s="234" t="n">
+      <c r="U12" s="221" t="n">
         <v>9</v>
       </c>
-      <c r="V12" s="234" t="n">
+      <c r="V12" s="221" t="n">
         <v>17</v>
       </c>
-      <c r="W12" s="234" t="n">
+      <c r="W12" s="221" t="n">
         <v>3</v>
       </c>
-      <c r="X12" s="234" t="n">
+      <c r="X12" s="221" t="n">
         <v>5</v>
       </c>
       <c r="AA12" s="110" t="n">
@@ -11048,7 +11148,7 @@
       <c r="C13" s="69" t="n">
         <v>5</v>
       </c>
-      <c r="D13" s="234" t="n">
+      <c r="D13" s="221" t="n">
         <v>6</v>
       </c>
       <c r="E13" s="70" t="n">
@@ -11057,7 +11157,7 @@
       <c r="F13" s="69" t="n">
         <v>5</v>
       </c>
-      <c r="G13" s="234" t="n">
+      <c r="G13" s="221" t="n">
         <v>6</v>
       </c>
       <c r="H13" s="70" t="n">
@@ -11066,7 +11166,7 @@
       <c r="I13" s="69" t="n">
         <v>5</v>
       </c>
-      <c r="J13" s="234" t="n">
+      <c r="J13" s="221" t="n">
         <v>5</v>
       </c>
       <c r="K13" s="70" t="n">
@@ -11103,7 +11203,7 @@
         <f>C12-C13</f>
         <v/>
       </c>
-      <c r="D14" s="234">
+      <c r="D14" s="221">
         <f>D12-INT($D$8/18)-IF(D11&lt;=MOD($D$8,18),1,0)</f>
         <v/>
       </c>
@@ -11115,7 +11215,7 @@
         <f>F12-INT($D$8/18)-IF(F11&lt;=MOD($D$8,18),1,0)</f>
         <v/>
       </c>
-      <c r="G14" s="234">
+      <c r="G14" s="221">
         <f>G12-INT($D$8/18)-IF(G11&lt;=MOD($D$8,18),1,0)</f>
         <v/>
       </c>
@@ -11127,7 +11227,7 @@
         <f>I12-INT($D$8/18)-IF(I11&lt;=MOD($D$8,18),1,0)</f>
         <v/>
       </c>
-      <c r="J14" s="234">
+      <c r="J14" s="221">
         <f>J12-INT($D$8/18)-IF(J11&lt;=MOD($D$8,18),1,0)</f>
         <v/>
       </c>
@@ -11135,7 +11235,7 @@
         <f>K12-INT($D$8/18)-IF(K11&lt;=MOD($D$8,18),1,0)</f>
         <v/>
       </c>
-      <c r="L14" s="234">
+      <c r="L14" s="221">
         <f>SUM(C14:K14)</f>
         <v/>
       </c>
@@ -11143,7 +11243,7 @@
         <f>SUM(C14:K14)-SUM(C$10:K$10)</f>
         <v/>
       </c>
-      <c r="O14" s="234" t="inlineStr">
+      <c r="O14" s="221" t="inlineStr">
         <is>
           <t>Back 9</t>
         </is>
@@ -11168,7 +11268,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="15" ht="14.25" customHeight="1" s="197" thickBot="1">
+    <row r="15" ht="14.25" customHeight="1" s="181" thickBot="1">
       <c r="B15" s="74" t="inlineStr">
         <is>
           <t>Wins Hole</t>
@@ -11210,37 +11310,37 @@
         <f>IF(K14&lt;K23,1,0)</f>
         <v/>
       </c>
-      <c r="L15" s="234" t="n"/>
-      <c r="O15" s="235" t="inlineStr">
+      <c r="L15" s="221" t="n"/>
+      <c r="O15" s="222" t="inlineStr">
         <is>
           <t>Black</t>
         </is>
       </c>
-      <c r="P15" s="234" t="n">
+      <c r="P15" s="221" t="n">
         <v>12</v>
       </c>
-      <c r="Q15" s="234" t="n">
+      <c r="Q15" s="221" t="n">
         <v>2</v>
       </c>
-      <c r="R15" s="234" t="n">
+      <c r="R15" s="221" t="n">
         <v>8</v>
       </c>
-      <c r="S15" s="234" t="n">
+      <c r="S15" s="221" t="n">
         <v>6</v>
       </c>
-      <c r="T15" s="234" t="n">
+      <c r="T15" s="221" t="n">
         <v>18</v>
       </c>
-      <c r="U15" s="234" t="n">
+      <c r="U15" s="221" t="n">
         <v>14</v>
       </c>
-      <c r="V15" s="234" t="n">
+      <c r="V15" s="221" t="n">
         <v>16</v>
       </c>
-      <c r="W15" s="234" t="n">
+      <c r="W15" s="221" t="n">
         <v>10</v>
       </c>
-      <c r="X15" s="234" t="n">
+      <c r="X15" s="221" t="n">
         <v>4</v>
       </c>
       <c r="AA15" s="110" t="n">
@@ -11264,46 +11364,46 @@
       </c>
     </row>
     <row r="16">
-      <c r="C16" s="234" t="n"/>
-      <c r="D16" s="234" t="n"/>
-      <c r="E16" s="234" t="n"/>
-      <c r="F16" s="234" t="n"/>
-      <c r="G16" s="234" t="n"/>
-      <c r="H16" s="234" t="n"/>
-      <c r="I16" s="234" t="n"/>
-      <c r="J16" s="234" t="n"/>
-      <c r="K16" s="234" t="n"/>
-      <c r="L16" s="234" t="n"/>
-      <c r="O16" s="235" t="inlineStr">
+      <c r="C16" s="221" t="n"/>
+      <c r="D16" s="221" t="n"/>
+      <c r="E16" s="221" t="n"/>
+      <c r="F16" s="221" t="n"/>
+      <c r="G16" s="221" t="n"/>
+      <c r="H16" s="221" t="n"/>
+      <c r="I16" s="221" t="n"/>
+      <c r="J16" s="221" t="n"/>
+      <c r="K16" s="221" t="n"/>
+      <c r="L16" s="221" t="n"/>
+      <c r="O16" s="222" t="inlineStr">
         <is>
           <t>Blue</t>
         </is>
       </c>
-      <c r="P16" s="234" t="n">
+      <c r="P16" s="221" t="n">
         <v>12</v>
       </c>
-      <c r="Q16" s="234" t="n">
+      <c r="Q16" s="221" t="n">
         <v>2</v>
       </c>
-      <c r="R16" s="234" t="n">
+      <c r="R16" s="221" t="n">
         <v>8</v>
       </c>
-      <c r="S16" s="234" t="n">
+      <c r="S16" s="221" t="n">
         <v>6</v>
       </c>
-      <c r="T16" s="234" t="n">
+      <c r="T16" s="221" t="n">
         <v>18</v>
       </c>
-      <c r="U16" s="234" t="n">
+      <c r="U16" s="221" t="n">
         <v>14</v>
       </c>
-      <c r="V16" s="234" t="n">
+      <c r="V16" s="221" t="n">
         <v>16</v>
       </c>
-      <c r="W16" s="234" t="n">
+      <c r="W16" s="221" t="n">
         <v>10</v>
       </c>
-      <c r="X16" s="234" t="n">
+      <c r="X16" s="221" t="n">
         <v>4</v>
       </c>
       <c r="AA16" s="110" t="n">
@@ -11326,7 +11426,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="17" ht="19.5" customHeight="1" s="197" thickBot="1">
+    <row r="17" ht="19.5" customHeight="1" s="181" thickBot="1">
       <c r="B17" s="109" t="inlineStr">
         <is>
           <t>Bruce Dubovecky</t>
@@ -11337,12 +11437,12 @@
           <t>Handicap:</t>
         </is>
       </c>
-      <c r="D17" s="234">
+      <c r="D17" s="221">
         <f>IFERROR(VLOOKUP(B17,$AB$3:$AE$21,4,0),0)</f>
         <v/>
       </c>
-      <c r="E17" s="234" t="n"/>
-      <c r="F17" s="234" t="inlineStr">
+      <c r="E17" s="221" t="n"/>
+      <c r="F17" s="221" t="inlineStr">
         <is>
           <t>Tees:</t>
         </is>
@@ -11352,8 +11452,8 @@
           <t>Black</t>
         </is>
       </c>
-      <c r="H17" s="234" t="n"/>
-      <c r="I17" s="234" t="inlineStr">
+      <c r="H17" s="221" t="n"/>
+      <c r="I17" s="221" t="inlineStr">
         <is>
           <t>Holes:</t>
         </is>
@@ -11363,38 +11463,38 @@
           <t>Front 9</t>
         </is>
       </c>
-      <c r="K17" s="234" t="n"/>
-      <c r="L17" s="234" t="n"/>
-      <c r="O17" s="235" t="inlineStr">
+      <c r="K17" s="221" t="n"/>
+      <c r="L17" s="221" t="n"/>
+      <c r="O17" s="222" t="inlineStr">
         <is>
           <t>Blue / White</t>
         </is>
       </c>
-      <c r="P17" s="234" t="n">
+      <c r="P17" s="221" t="n">
         <v>12</v>
       </c>
-      <c r="Q17" s="234" t="n">
+      <c r="Q17" s="221" t="n">
         <v>4</v>
       </c>
-      <c r="R17" s="234" t="n">
+      <c r="R17" s="221" t="n">
         <v>10</v>
       </c>
-      <c r="S17" s="234" t="n">
+      <c r="S17" s="221" t="n">
         <v>2</v>
       </c>
-      <c r="T17" s="234" t="n">
+      <c r="T17" s="221" t="n">
         <v>16</v>
       </c>
-      <c r="U17" s="234" t="n">
+      <c r="U17" s="221" t="n">
         <v>14</v>
       </c>
-      <c r="V17" s="234" t="n">
+      <c r="V17" s="221" t="n">
         <v>18</v>
       </c>
-      <c r="W17" s="234" t="n">
+      <c r="W17" s="221" t="n">
         <v>6</v>
       </c>
-      <c r="X17" s="234" t="n">
+      <c r="X17" s="221" t="n">
         <v>8</v>
       </c>
       <c r="AA17" s="110" t="n">
@@ -11417,7 +11517,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="18" ht="15" customHeight="1" s="197">
+    <row r="18" ht="15" customHeight="1" s="181">
       <c r="B18" s="64" t="inlineStr">
         <is>
           <t>HOLE</t>
@@ -11450,38 +11550,38 @@
       <c r="K18" s="67" t="n">
         <v>9</v>
       </c>
-      <c r="L18" s="234" t="n"/>
+      <c r="L18" s="221" t="n"/>
       <c r="M18" s="72" t="n"/>
-      <c r="O18" s="235" t="inlineStr">
+      <c r="O18" s="222" t="inlineStr">
         <is>
           <t>White</t>
         </is>
       </c>
-      <c r="P18" s="234" t="n">
+      <c r="P18" s="221" t="n">
         <v>10</v>
       </c>
-      <c r="Q18" s="234" t="n">
+      <c r="Q18" s="221" t="n">
         <v>4</v>
       </c>
-      <c r="R18" s="234" t="n">
+      <c r="R18" s="221" t="n">
         <v>8</v>
       </c>
-      <c r="S18" s="234" t="n">
+      <c r="S18" s="221" t="n">
         <v>2</v>
       </c>
-      <c r="T18" s="234" t="n">
+      <c r="T18" s="221" t="n">
         <v>16</v>
       </c>
-      <c r="U18" s="234" t="n">
+      <c r="U18" s="221" t="n">
         <v>12</v>
       </c>
-      <c r="V18" s="234" t="n">
+      <c r="V18" s="221" t="n">
         <v>18</v>
       </c>
-      <c r="W18" s="234" t="n">
+      <c r="W18" s="221" t="n">
         <v>14</v>
       </c>
-      <c r="X18" s="234" t="n">
+      <c r="X18" s="221" t="n">
         <v>6</v>
       </c>
       <c r="AA18" s="110" t="n">
@@ -11513,7 +11613,7 @@
       <c r="C19" s="69" t="n">
         <v>4</v>
       </c>
-      <c r="D19" s="234" t="n">
+      <c r="D19" s="221" t="n">
         <v>5</v>
       </c>
       <c r="E19" s="70" t="n">
@@ -11522,7 +11622,7 @@
       <c r="F19" s="69" t="n">
         <v>4</v>
       </c>
-      <c r="G19" s="234" t="n">
+      <c r="G19" s="221" t="n">
         <v>5</v>
       </c>
       <c r="H19" s="70" t="n">
@@ -11531,13 +11631,13 @@
       <c r="I19" s="69" t="n">
         <v>4</v>
       </c>
-      <c r="J19" s="234" t="n">
+      <c r="J19" s="221" t="n">
         <v>4</v>
       </c>
       <c r="K19" s="70" t="n">
         <v>4</v>
       </c>
-      <c r="L19" s="234">
+      <c r="L19" s="221">
         <f>SUM(C19:K19)</f>
         <v/>
       </c>
@@ -11571,7 +11671,7 @@
         <f t="array" ref="C20">_xlfn.IFS($J17="Back 9",VLOOKUP($G17,$O$15:$X$18,COLUMN()-1,0),$J17="Front 9",VLOOKUP($G17,$O$9:$X$12,COLUMN()-1,0))</f>
         <v/>
       </c>
-      <c r="D20" s="234">
+      <c r="D20" s="221">
         <f t="array" ref="D20">_xlfn.IFS($J17="Back 9",VLOOKUP($G17,$O$15:$X$18,COLUMN()-1,0),$J17="Front 9",VLOOKUP($G17,$O$9:$X$12,COLUMN()-1,0))</f>
         <v/>
       </c>
@@ -11583,7 +11683,7 @@
         <f t="array" ref="F20">_xlfn.IFS($J17="Back 9",VLOOKUP($G17,$O$15:$X$18,COLUMN()-1,0),$J17="Front 9",VLOOKUP($G17,$O$9:$X$12,COLUMN()-1,0))</f>
         <v/>
       </c>
-      <c r="G20" s="234">
+      <c r="G20" s="221">
         <f t="array" ref="G20">_xlfn.IFS($J17="Back 9",VLOOKUP($G17,$O$15:$X$18,COLUMN()-1,0),$J17="Front 9",VLOOKUP($G17,$O$9:$X$12,COLUMN()-1,0))</f>
         <v/>
       </c>
@@ -11595,7 +11695,7 @@
         <f t="array" ref="I20">_xlfn.IFS($J17="Back 9",VLOOKUP($G17,$O$15:$X$18,COLUMN()-1,0),$J17="Front 9",VLOOKUP($G17,$O$9:$X$12,COLUMN()-1,0))</f>
         <v/>
       </c>
-      <c r="J20" s="234">
+      <c r="J20" s="221">
         <f t="array" ref="J20">_xlfn.IFS($J17="Back 9",VLOOKUP($G17,$O$15:$X$18,COLUMN()-1,0),$J17="Front 9",VLOOKUP($G17,$O$9:$X$12,COLUMN()-1,0))</f>
         <v/>
       </c>
@@ -11603,7 +11703,7 @@
         <f t="array" ref="K20">_xlfn.IFS($J17="Back 9",VLOOKUP($G17,$O$15:$X$18,COLUMN()-1,0),$J17="Front 9",VLOOKUP($G17,$O$9:$X$12,COLUMN()-1,0))</f>
         <v/>
       </c>
-      <c r="L20" s="234" t="n"/>
+      <c r="L20" s="221" t="n"/>
       <c r="AA20" s="110" t="n">
         <v>16</v>
       </c>
@@ -11624,7 +11724,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="21" ht="15" customHeight="1" s="197">
+    <row r="21" ht="15" customHeight="1" s="181">
       <c r="B21" s="71" t="inlineStr">
         <is>
           <t>GROSS</t>
@@ -11657,7 +11757,7 @@
       <c r="K21" s="115" t="n">
         <v>5</v>
       </c>
-      <c r="L21" s="234">
+      <c r="L21" s="221">
         <f>SUM(C21:K21)</f>
         <v/>
       </c>
@@ -11694,7 +11794,7 @@
       <c r="C22" s="69" t="n">
         <v>5</v>
       </c>
-      <c r="D22" s="234" t="n">
+      <c r="D22" s="221" t="n">
         <v>6</v>
       </c>
       <c r="E22" s="70" t="n">
@@ -11703,7 +11803,7 @@
       <c r="F22" s="69" t="n">
         <v>5</v>
       </c>
-      <c r="G22" s="234" t="n">
+      <c r="G22" s="221" t="n">
         <v>6</v>
       </c>
       <c r="H22" s="70" t="n">
@@ -11712,7 +11812,7 @@
       <c r="I22" s="69" t="n">
         <v>5</v>
       </c>
-      <c r="J22" s="234" t="n">
+      <c r="J22" s="221" t="n">
         <v>5</v>
       </c>
       <c r="K22" s="70" t="n">
@@ -11730,7 +11830,7 @@
         <f>C21-C22</f>
         <v/>
       </c>
-      <c r="D23" s="234">
+      <c r="D23" s="221">
         <f>D21-D22</f>
         <v/>
       </c>
@@ -11742,7 +11842,7 @@
         <f>F21-F22</f>
         <v/>
       </c>
-      <c r="G23" s="234">
+      <c r="G23" s="221">
         <f>G21-G22</f>
         <v/>
       </c>
@@ -11754,7 +11854,7 @@
         <f>I21-I22</f>
         <v/>
       </c>
-      <c r="J23" s="234">
+      <c r="J23" s="221">
         <f>J21-J22</f>
         <v/>
       </c>
@@ -11762,7 +11862,7 @@
         <f>K21-K22</f>
         <v/>
       </c>
-      <c r="L23" s="234">
+      <c r="L23" s="221">
         <f>SUM(C23:K23)</f>
         <v/>
       </c>
@@ -11771,7 +11871,7 @@
         <v/>
       </c>
     </row>
-    <row r="24" ht="14.25" customHeight="1" s="197" thickBot="1">
+    <row r="24" ht="14.25" customHeight="1" s="181" thickBot="1">
       <c r="B24" s="74" t="inlineStr">
         <is>
           <t>Wins Hole</t>
@@ -11813,7 +11913,7 @@
         <f>IF(K23&lt;K14,1,0)</f>
         <v/>
       </c>
-      <c r="L24" s="234" t="n"/>
+      <c r="L24" s="221" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="AA2:AE21">

--- a/2026 IMI Golf League.xlsx
+++ b/2026 IMI Golf League.xlsx
@@ -9336,7 +9336,9 @@
       <c r="D3" s="158" t="n">
         <v>2</v>
       </c>
-      <c r="E3" s="205" t="n"/>
+      <c r="E3" s="205" t="n">
+        <v>4</v>
+      </c>
       <c r="F3" s="205" t="n"/>
       <c r="G3" s="205" t="n"/>
       <c r="H3" s="205" t="n"/>
@@ -9345,15 +9347,15 @@
       <c r="K3" s="205" t="n"/>
       <c r="L3" s="160" t="n"/>
       <c r="M3" s="207" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="N3" s="205" t="inlineStr">
         <is>
-          <t>0-1-0</t>
+          <t>0-1-1</t>
         </is>
       </c>
       <c r="O3" s="216" t="n">
-        <v>43</v>
+        <v>41.5</v>
       </c>
       <c r="Q3" s="217" t="inlineStr">
         <is>
@@ -9373,7 +9375,9 @@
       <c r="D4" s="162" t="n">
         <v>43</v>
       </c>
-      <c r="E4" s="163" t="n"/>
+      <c r="E4" s="163" t="n">
+        <v>40</v>
+      </c>
       <c r="F4" s="163" t="n"/>
       <c r="G4" s="163" t="n"/>
       <c r="H4" s="163" t="n"/>
@@ -9416,7 +9420,9 @@
       <c r="D5" s="165" t="n">
         <v>6</v>
       </c>
-      <c r="E5" s="166" t="n"/>
+      <c r="E5" s="166" t="n">
+        <v>7</v>
+      </c>
       <c r="F5" s="166" t="n"/>
       <c r="G5" s="166" t="n"/>
       <c r="H5" s="166" t="n"/>
@@ -9425,15 +9431,15 @@
       <c r="K5" s="166" t="n"/>
       <c r="L5" s="167" t="n"/>
       <c r="M5" s="211" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="N5" s="203" t="inlineStr">
         <is>
-          <t>1-0-0</t>
+          <t>2-0-0</t>
         </is>
       </c>
       <c r="O5" s="197" t="n">
-        <v>39</v>
+        <v>37.5</v>
       </c>
       <c r="Q5" s="33" t="n">
         <v>1</v>
@@ -9451,7 +9457,9 @@
       <c r="D6" s="169" t="n">
         <v>39</v>
       </c>
-      <c r="E6" s="170" t="n"/>
+      <c r="E6" s="170" t="n">
+        <v>36</v>
+      </c>
       <c r="F6" s="170" t="n"/>
       <c r="G6" s="170" t="n"/>
       <c r="H6" s="170" t="n"/>
@@ -9484,7 +9492,9 @@
       <c r="D7" s="158" t="n">
         <v>1</v>
       </c>
-      <c r="E7" s="205" t="n"/>
+      <c r="E7" s="205" t="n">
+        <v>4</v>
+      </c>
       <c r="F7" s="205" t="n"/>
       <c r="G7" s="205" t="n"/>
       <c r="H7" s="205" t="n"/>
@@ -9493,15 +9503,15 @@
       <c r="K7" s="205" t="n"/>
       <c r="L7" s="160" t="n"/>
       <c r="M7" s="207" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="N7" s="205" t="inlineStr">
         <is>
-          <t>0-1-0</t>
+          <t>0-1-1</t>
         </is>
       </c>
       <c r="O7" s="216" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="Q7" s="33" t="n">
         <v>3</v>
@@ -9519,7 +9529,9 @@
       <c r="D8" s="162" t="n">
         <v>43</v>
       </c>
-      <c r="E8" s="163" t="n"/>
+      <c r="E8" s="163" t="n">
+        <v>39</v>
+      </c>
       <c r="F8" s="163" t="n"/>
       <c r="G8" s="163" t="n"/>
       <c r="H8" s="163" t="n"/>
@@ -9552,7 +9564,9 @@
       <c r="D9" s="165" t="n">
         <v>7</v>
       </c>
-      <c r="E9" s="166" t="n"/>
+      <c r="E9" s="166" t="n">
+        <v>1</v>
+      </c>
       <c r="F9" s="166" t="n"/>
       <c r="G9" s="166" t="n"/>
       <c r="H9" s="166" t="n"/>
@@ -9561,15 +9575,15 @@
       <c r="K9" s="166" t="n"/>
       <c r="L9" s="167" t="n"/>
       <c r="M9" s="211" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N9" s="203" t="inlineStr">
         <is>
-          <t>1-0-0</t>
+          <t>1-1-0</t>
         </is>
       </c>
       <c r="O9" s="197" t="n">
-        <v>38</v>
+        <v>42.5</v>
       </c>
     </row>
     <row r="10" ht="13.5" customHeight="1" s="181" thickBot="1">
@@ -9582,7 +9596,9 @@
       <c r="D10" s="169" t="n">
         <v>38</v>
       </c>
-      <c r="E10" s="170" t="n"/>
+      <c r="E10" s="170" t="n">
+        <v>47</v>
+      </c>
       <c r="F10" s="170" t="n"/>
       <c r="G10" s="170" t="n"/>
       <c r="H10" s="170" t="n"/>

--- a/2026 IMI Golf League.xlsx
+++ b/2026 IMI Golf League.xlsx
@@ -9974,7 +9974,9 @@
       <c r="D21" s="165" t="n">
         <v>6</v>
       </c>
-      <c r="E21" s="166" t="n"/>
+      <c r="E21" s="166" t="n">
+        <v>8</v>
+      </c>
       <c r="F21" s="166" t="n"/>
       <c r="G21" s="166" t="n"/>
       <c r="H21" s="166" t="n"/>
@@ -9983,15 +9985,15 @@
       <c r="K21" s="166" t="n"/>
       <c r="L21" s="167" t="n"/>
       <c r="M21" s="211" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="N21" s="203" t="inlineStr">
         <is>
-          <t>1-0-0</t>
+          <t>2-0-0</t>
         </is>
       </c>
       <c r="O21" s="197" t="n">
-        <v>35</v>
+        <v>38.5</v>
       </c>
       <c r="Q21" s="154" t="inlineStr">
         <is>
@@ -10010,7 +10012,9 @@
       <c r="D22" s="169" t="n">
         <v>35</v>
       </c>
-      <c r="E22" s="170" t="n"/>
+      <c r="E22" s="170" t="n">
+        <v>42</v>
+      </c>
       <c r="F22" s="170" t="n"/>
       <c r="G22" s="170" t="n"/>
       <c r="H22" s="170" t="n"/>
@@ -10142,7 +10146,9 @@
       <c r="D27" s="158" t="n">
         <v>4</v>
       </c>
-      <c r="E27" s="205" t="n"/>
+      <c r="E27" s="205" t="n">
+        <v>0</v>
+      </c>
       <c r="F27" s="205" t="n"/>
       <c r="G27" s="205" t="n"/>
       <c r="H27" s="205" t="n"/>
@@ -10155,11 +10161,11 @@
       </c>
       <c r="N27" s="205" t="inlineStr">
         <is>
-          <t>0-0-1</t>
+          <t>0-1-1</t>
         </is>
       </c>
       <c r="O27" s="216" t="n">
-        <v>54</v>
+        <v>52.5</v>
       </c>
     </row>
     <row r="28" ht="13.5" customHeight="1" s="181" thickBot="1">
@@ -10172,7 +10178,9 @@
       <c r="D28" s="162" t="n">
         <v>54</v>
       </c>
-      <c r="E28" s="163" t="n"/>
+      <c r="E28" s="163" t="n">
+        <v>51</v>
+      </c>
       <c r="F28" s="163" t="n"/>
       <c r="G28" s="163" t="n"/>
       <c r="H28" s="163" t="n"/>

--- a/2026 IMI Golf League.xlsx
+++ b/2026 IMI Golf League.xlsx
@@ -9710,7 +9710,9 @@
       <c r="D13" s="165" t="n">
         <v>8</v>
       </c>
-      <c r="E13" s="166" t="n"/>
+      <c r="E13" s="166" t="n">
+        <v>2</v>
+      </c>
       <c r="F13" s="166" t="n"/>
       <c r="G13" s="166" t="n"/>
       <c r="H13" s="166" t="n"/>
@@ -9719,15 +9721,15 @@
       <c r="K13" s="166" t="n"/>
       <c r="L13" s="167" t="n"/>
       <c r="M13" s="211" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="N13" s="203" t="inlineStr">
         <is>
-          <t>1-0-0</t>
+          <t>1-1-0</t>
         </is>
       </c>
       <c r="O13" s="197" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="R13" s="39" t="inlineStr">
         <is>
@@ -9750,7 +9752,9 @@
       <c r="D14" s="169" t="n">
         <v>33</v>
       </c>
-      <c r="E14" s="170" t="n"/>
+      <c r="E14" s="170" t="n">
+        <v>39</v>
+      </c>
       <c r="F14" s="170" t="n"/>
       <c r="G14" s="170" t="n"/>
       <c r="H14" s="170" t="n"/>
@@ -9836,7 +9840,9 @@
       <c r="D17" s="165" t="n">
         <v>7</v>
       </c>
-      <c r="E17" s="166" t="n"/>
+      <c r="E17" s="166" t="n">
+        <v>6</v>
+      </c>
       <c r="F17" s="166" t="n"/>
       <c r="G17" s="166" t="n"/>
       <c r="H17" s="166" t="n"/>
@@ -9845,15 +9851,15 @@
       <c r="K17" s="166" t="n"/>
       <c r="L17" s="167" t="n"/>
       <c r="M17" s="211" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="N17" s="203" t="inlineStr">
         <is>
-          <t>1-0-0</t>
+          <t>2-0-0</t>
         </is>
       </c>
       <c r="O17" s="197" t="n">
-        <v>37</v>
+        <v>37.5</v>
       </c>
       <c r="Q17" s="212" t="inlineStr">
         <is>
@@ -9871,7 +9877,9 @@
       <c r="D18" s="169" t="n">
         <v>37</v>
       </c>
-      <c r="E18" s="170" t="n"/>
+      <c r="E18" s="170" t="n">
+        <v>38</v>
+      </c>
       <c r="F18" s="170" t="n"/>
       <c r="G18" s="170" t="n"/>
       <c r="H18" s="170" t="n"/>
@@ -10040,7 +10048,9 @@
         </is>
       </c>
       <c r="D23" s="158" t="n"/>
-      <c r="E23" s="205" t="n"/>
+      <c r="E23" s="205" t="n">
+        <v>8</v>
+      </c>
       <c r="F23" s="205" t="n"/>
       <c r="G23" s="205" t="n"/>
       <c r="H23" s="205" t="n"/>
@@ -10048,9 +10058,17 @@
       <c r="J23" s="205" t="n"/>
       <c r="K23" s="205" t="n"/>
       <c r="L23" s="160" t="n"/>
-      <c r="M23" s="207" t="n"/>
-      <c r="N23" s="205" t="n"/>
-      <c r="O23" s="216" t="n"/>
+      <c r="M23" s="207" t="n">
+        <v>8</v>
+      </c>
+      <c r="N23" s="205" t="inlineStr">
+        <is>
+          <t>1-0-0</t>
+        </is>
+      </c>
+      <c r="O23" s="216" t="n">
+        <v>43</v>
+      </c>
     </row>
     <row r="24" ht="13.5" customHeight="1" s="181" thickBot="1">
       <c r="B24" s="200" t="n"/>
@@ -10060,7 +10078,9 @@
         </is>
       </c>
       <c r="D24" s="162" t="n"/>
-      <c r="E24" s="163" t="n"/>
+      <c r="E24" s="163" t="n">
+        <v>43</v>
+      </c>
       <c r="F24" s="163" t="n"/>
       <c r="G24" s="163" t="n"/>
       <c r="H24" s="163" t="n"/>
@@ -10208,7 +10228,9 @@
       <c r="D29" s="165" t="n">
         <v>7</v>
       </c>
-      <c r="E29" s="166" t="n"/>
+      <c r="E29" s="166" t="n">
+        <v>0</v>
+      </c>
       <c r="F29" s="166" t="n"/>
       <c r="G29" s="166" t="n"/>
       <c r="H29" s="166" t="n"/>
@@ -10221,11 +10243,11 @@
       </c>
       <c r="N29" s="203" t="inlineStr">
         <is>
-          <t>1-0-0</t>
+          <t>1-1-0</t>
         </is>
       </c>
       <c r="O29" s="197" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="30" ht="13.5" customHeight="1" s="181" thickBot="1">
@@ -10238,7 +10260,9 @@
       <c r="D30" s="169" t="n">
         <v>50</v>
       </c>
-      <c r="E30" s="170" t="n"/>
+      <c r="E30" s="170" t="n">
+        <v>52</v>
+      </c>
       <c r="F30" s="170" t="n"/>
       <c r="G30" s="170" t="n"/>
       <c r="H30" s="170" t="n"/>

--- a/2026 IMI Golf League.xlsx
+++ b/2026 IMI Golf League.xlsx
@@ -9913,7 +9913,9 @@
       <c r="D19" s="158" t="n">
         <v>2</v>
       </c>
-      <c r="E19" s="205" t="n"/>
+      <c r="E19" s="205" t="n">
+        <v>8</v>
+      </c>
       <c r="F19" s="205" t="n"/>
       <c r="G19" s="205" t="n"/>
       <c r="H19" s="205" t="n"/>
@@ -9922,15 +9924,15 @@
       <c r="K19" s="205" t="n"/>
       <c r="L19" s="160" t="n"/>
       <c r="M19" s="207" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="N19" s="205" t="inlineStr">
         <is>
-          <t>0-1-0</t>
+          <t>1-1-0</t>
         </is>
       </c>
       <c r="O19" s="216" t="n">
-        <v>39</v>
+        <v>37.5</v>
       </c>
       <c r="Q19" s="154" t="inlineStr">
         <is>
@@ -9948,7 +9950,9 @@
       <c r="D20" s="162" t="n">
         <v>39</v>
       </c>
-      <c r="E20" s="163" t="n"/>
+      <c r="E20" s="163" t="n">
+        <v>36</v>
+      </c>
       <c r="F20" s="163" t="n"/>
       <c r="G20" s="163" t="n"/>
       <c r="H20" s="163" t="n"/>
@@ -10108,7 +10112,9 @@
       <c r="D25" s="165" t="n">
         <v>4</v>
       </c>
-      <c r="E25" s="166" t="n"/>
+      <c r="E25" s="166" t="n">
+        <v>0</v>
+      </c>
       <c r="F25" s="166" t="n"/>
       <c r="G25" s="166" t="n"/>
       <c r="H25" s="166" t="n"/>
@@ -10121,7 +10127,7 @@
       </c>
       <c r="N25" s="203" t="inlineStr">
         <is>
-          <t>0-0-1</t>
+          <t>0-1-1</t>
         </is>
       </c>
       <c r="O25" s="197" t="n">
@@ -10138,7 +10144,9 @@
       <c r="D26" s="169" t="n">
         <v>54</v>
       </c>
-      <c r="E26" s="170" t="n"/>
+      <c r="E26" s="170" t="n">
+        <v>54</v>
+      </c>
       <c r="F26" s="170" t="n"/>
       <c r="G26" s="170" t="n"/>
       <c r="H26" s="170" t="n"/>

--- a/2026 IMI Golf League.xlsx
+++ b/2026 IMI Golf League.xlsx
@@ -9632,7 +9632,9 @@
       <c r="D11" s="158" t="n">
         <v>0</v>
       </c>
-      <c r="E11" s="205" t="n"/>
+      <c r="E11" s="205" t="n">
+        <v>6</v>
+      </c>
       <c r="F11" s="205" t="n"/>
       <c r="G11" s="205" t="n"/>
       <c r="H11" s="205" t="n"/>
@@ -9641,15 +9643,15 @@
       <c r="K11" s="205" t="n"/>
       <c r="L11" s="160" t="n"/>
       <c r="M11" s="207" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="N11" s="205" t="inlineStr">
         <is>
-          <t>0-1-0</t>
+          <t>1-1-0</t>
         </is>
       </c>
       <c r="O11" s="216" t="n">
-        <v>46</v>
+        <v>44.5</v>
       </c>
       <c r="R11" s="36" t="inlineStr">
         <is>
@@ -9672,7 +9674,9 @@
       <c r="D12" s="162" t="n">
         <v>46</v>
       </c>
-      <c r="E12" s="163" t="n"/>
+      <c r="E12" s="163" t="n">
+        <v>43</v>
+      </c>
       <c r="F12" s="163" t="n"/>
       <c r="G12" s="163" t="n"/>
       <c r="H12" s="163" t="n"/>
@@ -9782,7 +9786,9 @@
       <c r="D15" s="158" t="n">
         <v>1</v>
       </c>
-      <c r="E15" s="205" t="n"/>
+      <c r="E15" s="205" t="n">
+        <v>2</v>
+      </c>
       <c r="F15" s="205" t="n"/>
       <c r="G15" s="205" t="n"/>
       <c r="H15" s="205" t="n"/>
@@ -9791,15 +9797,15 @@
       <c r="K15" s="205" t="n"/>
       <c r="L15" s="160" t="n"/>
       <c r="M15" s="207" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N15" s="205" t="inlineStr">
         <is>
-          <t>0-1-0</t>
+          <t>0-2-0</t>
         </is>
       </c>
       <c r="O15" s="216" t="n">
-        <v>48</v>
+        <v>48.5</v>
       </c>
     </row>
     <row r="16" ht="13.5" customHeight="1" s="181" thickBot="1">
@@ -9812,7 +9818,9 @@
       <c r="D16" s="162" t="n">
         <v>48</v>
       </c>
-      <c r="E16" s="163" t="n"/>
+      <c r="E16" s="163" t="n">
+        <v>49</v>
+      </c>
       <c r="F16" s="163" t="n"/>
       <c r="G16" s="163" t="n"/>
       <c r="H16" s="163" t="n"/>

--- a/2026 IMI Golf League.xlsx
+++ b/2026 IMI Golf League.xlsx
@@ -9789,7 +9789,9 @@
       <c r="E15" s="205" t="n">
         <v>2</v>
       </c>
-      <c r="F15" s="205" t="n"/>
+      <c r="F15" s="205" t="n">
+        <v>7</v>
+      </c>
       <c r="G15" s="205" t="n"/>
       <c r="H15" s="205" t="n"/>
       <c r="I15" s="205" t="n"/>
@@ -9797,15 +9799,15 @@
       <c r="K15" s="205" t="n"/>
       <c r="L15" s="160" t="n"/>
       <c r="M15" s="207" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="N15" s="205" t="inlineStr">
         <is>
-          <t>0-2-0</t>
+          <t>1-2-0</t>
         </is>
       </c>
       <c r="O15" s="216" t="n">
-        <v>48.5</v>
+        <v>45.3</v>
       </c>
     </row>
     <row r="16" ht="13.5" customHeight="1" s="181" thickBot="1">
@@ -9821,7 +9823,9 @@
       <c r="E16" s="163" t="n">
         <v>49</v>
       </c>
-      <c r="F16" s="163" t="n"/>
+      <c r="F16" s="163" t="n">
+        <v>39</v>
+      </c>
       <c r="G16" s="163" t="n"/>
       <c r="H16" s="163" t="n"/>
       <c r="I16" s="163" t="n"/>
@@ -9851,7 +9855,9 @@
       <c r="E17" s="166" t="n">
         <v>6</v>
       </c>
-      <c r="F17" s="166" t="n"/>
+      <c r="F17" s="166" t="n">
+        <v>8</v>
+      </c>
       <c r="G17" s="166" t="n"/>
       <c r="H17" s="166" t="n"/>
       <c r="I17" s="166" t="n"/>
@@ -9859,15 +9865,15 @@
       <c r="K17" s="166" t="n"/>
       <c r="L17" s="167" t="n"/>
       <c r="M17" s="211" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="N17" s="203" t="inlineStr">
         <is>
-          <t>2-0-0</t>
+          <t>3-0-0</t>
         </is>
       </c>
       <c r="O17" s="197" t="n">
-        <v>37.5</v>
+        <v>37.3</v>
       </c>
       <c r="Q17" s="212" t="inlineStr">
         <is>
@@ -9888,7 +9894,9 @@
       <c r="E18" s="170" t="n">
         <v>38</v>
       </c>
-      <c r="F18" s="170" t="n"/>
+      <c r="F18" s="170" t="n">
+        <v>37</v>
+      </c>
       <c r="G18" s="170" t="n"/>
       <c r="H18" s="170" t="n"/>
       <c r="I18" s="170" t="n"/>
@@ -10185,7 +10193,9 @@
       <c r="E27" s="205" t="n">
         <v>0</v>
       </c>
-      <c r="F27" s="205" t="n"/>
+      <c r="F27" s="205" t="n">
+        <v>1</v>
+      </c>
       <c r="G27" s="205" t="n"/>
       <c r="H27" s="205" t="n"/>
       <c r="I27" s="205" t="n"/>
@@ -10193,15 +10203,15 @@
       <c r="K27" s="205" t="n"/>
       <c r="L27" s="160" t="n"/>
       <c r="M27" s="207" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N27" s="205" t="inlineStr">
         <is>
-          <t>0-1-1</t>
+          <t>0-2-1</t>
         </is>
       </c>
       <c r="O27" s="216" t="n">
-        <v>52.5</v>
+        <v>53</v>
       </c>
     </row>
     <row r="28" ht="13.5" customHeight="1" s="181" thickBot="1">
@@ -10217,7 +10227,9 @@
       <c r="E28" s="163" t="n">
         <v>51</v>
       </c>
-      <c r="F28" s="163" t="n"/>
+      <c r="F28" s="163" t="n">
+        <v>54</v>
+      </c>
       <c r="G28" s="163" t="n"/>
       <c r="H28" s="163" t="n"/>
       <c r="I28" s="163" t="n"/>
@@ -10307,7 +10319,9 @@
         <v>1</v>
       </c>
       <c r="E31" s="205" t="n"/>
-      <c r="F31" s="205" t="n"/>
+      <c r="F31" s="205" t="n">
+        <v>0</v>
+      </c>
       <c r="G31" s="205" t="n"/>
       <c r="H31" s="205" t="n"/>
       <c r="I31" s="205" t="n"/>
@@ -10319,11 +10333,11 @@
       </c>
       <c r="N31" s="205" t="inlineStr">
         <is>
-          <t>0-1-0</t>
+          <t>0-2-0</t>
         </is>
       </c>
       <c r="O31" s="216" t="n">
-        <v>53</v>
+        <v>53.5</v>
       </c>
     </row>
     <row r="32" ht="13.5" customHeight="1" s="181" thickBot="1">
@@ -10337,7 +10351,9 @@
         <v>53</v>
       </c>
       <c r="E32" s="163" t="n"/>
-      <c r="F32" s="163" t="n"/>
+      <c r="F32" s="163" t="n">
+        <v>54</v>
+      </c>
       <c r="G32" s="163" t="n"/>
       <c r="H32" s="163" t="n"/>
       <c r="I32" s="163" t="n"/>

--- a/2026 IMI Golf League.xlsx
+++ b/2026 IMI Golf League.xlsx
@@ -9932,7 +9932,9 @@
       <c r="E19" s="205" t="n">
         <v>8</v>
       </c>
-      <c r="F19" s="205" t="n"/>
+      <c r="F19" s="205" t="n">
+        <v>4.5</v>
+      </c>
       <c r="G19" s="205" t="n"/>
       <c r="H19" s="205" t="n"/>
       <c r="I19" s="205" t="n"/>
@@ -9940,15 +9942,15 @@
       <c r="K19" s="205" t="n"/>
       <c r="L19" s="160" t="n"/>
       <c r="M19" s="207" t="n">
-        <v>10</v>
+        <v>14.5</v>
       </c>
       <c r="N19" s="205" t="inlineStr">
         <is>
-          <t>1-1-0</t>
+          <t>2-1-0</t>
         </is>
       </c>
       <c r="O19" s="216" t="n">
-        <v>37.5</v>
+        <v>39</v>
       </c>
       <c r="Q19" s="154" t="inlineStr">
         <is>
@@ -9969,7 +9971,9 @@
       <c r="E20" s="163" t="n">
         <v>36</v>
       </c>
-      <c r="F20" s="163" t="n"/>
+      <c r="F20" s="163" t="n">
+        <v>42</v>
+      </c>
       <c r="G20" s="163" t="n"/>
       <c r="H20" s="163" t="n"/>
       <c r="I20" s="163" t="n"/>
@@ -10259,7 +10263,9 @@
       <c r="E29" s="166" t="n">
         <v>0</v>
       </c>
-      <c r="F29" s="166" t="n"/>
+      <c r="F29" s="166" t="n">
+        <v>3.5</v>
+      </c>
       <c r="G29" s="166" t="n"/>
       <c r="H29" s="166" t="n"/>
       <c r="I29" s="166" t="n"/>
@@ -10267,15 +10273,15 @@
       <c r="K29" s="166" t="n"/>
       <c r="L29" s="167" t="n"/>
       <c r="M29" s="211" t="n">
-        <v>7</v>
+        <v>10.5</v>
       </c>
       <c r="N29" s="203" t="inlineStr">
         <is>
-          <t>1-1-0</t>
+          <t>1-2-0</t>
         </is>
       </c>
       <c r="O29" s="197" t="n">
-        <v>51</v>
+        <v>48.3</v>
       </c>
     </row>
     <row r="30" ht="13.5" customHeight="1" s="181" thickBot="1">
@@ -10291,7 +10297,9 @@
       <c r="E30" s="170" t="n">
         <v>52</v>
       </c>
-      <c r="F30" s="170" t="n"/>
+      <c r="F30" s="170" t="n">
+        <v>43</v>
+      </c>
       <c r="G30" s="170" t="n"/>
       <c r="H30" s="170" t="n"/>
       <c r="I30" s="170" t="n"/>

--- a/2026 IMI Golf League.xlsx
+++ b/2026 IMI Golf League.xlsx
@@ -10075,7 +10075,9 @@
       <c r="E23" s="205" t="n">
         <v>8</v>
       </c>
-      <c r="F23" s="205" t="n"/>
+      <c r="F23" s="205" t="n">
+        <v>7</v>
+      </c>
       <c r="G23" s="205" t="n"/>
       <c r="H23" s="205" t="n"/>
       <c r="I23" s="205" t="n"/>
@@ -10083,15 +10085,15 @@
       <c r="K23" s="205" t="n"/>
       <c r="L23" s="160" t="n"/>
       <c r="M23" s="207" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="N23" s="205" t="inlineStr">
         <is>
-          <t>1-0-0</t>
+          <t>2-0-0</t>
         </is>
       </c>
       <c r="O23" s="216" t="n">
-        <v>43</v>
+        <v>47.5</v>
       </c>
     </row>
     <row r="24" ht="13.5" customHeight="1" s="181" thickBot="1">
@@ -10105,7 +10107,9 @@
       <c r="E24" s="163" t="n">
         <v>43</v>
       </c>
-      <c r="F24" s="163" t="n"/>
+      <c r="F24" s="163" t="n">
+        <v>52</v>
+      </c>
       <c r="G24" s="163" t="n"/>
       <c r="H24" s="163" t="n"/>
       <c r="I24" s="163" t="n"/>
@@ -10135,7 +10139,9 @@
       <c r="E25" s="166" t="n">
         <v>0</v>
       </c>
-      <c r="F25" s="166" t="n"/>
+      <c r="F25" s="166" t="n">
+        <v>1</v>
+      </c>
       <c r="G25" s="166" t="n"/>
       <c r="H25" s="166" t="n"/>
       <c r="I25" s="166" t="n"/>
@@ -10143,11 +10149,11 @@
       <c r="K25" s="166" t="n"/>
       <c r="L25" s="167" t="n"/>
       <c r="M25" s="211" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N25" s="203" t="inlineStr">
         <is>
-          <t>0-1-1</t>
+          <t>0-2-1</t>
         </is>
       </c>
       <c r="O25" s="197" t="n">
@@ -10167,7 +10173,9 @@
       <c r="E26" s="170" t="n">
         <v>54</v>
       </c>
-      <c r="F26" s="170" t="n"/>
+      <c r="F26" s="170" t="n">
+        <v>54</v>
+      </c>
       <c r="G26" s="170" t="n"/>
       <c r="H26" s="170" t="n"/>
       <c r="I26" s="170" t="n"/>

--- a/2026 IMI Golf League.xlsx
+++ b/2026 IMI Golf League.xlsx
@@ -10078,22 +10078,24 @@
       <c r="F23" s="205" t="n">
         <v>7</v>
       </c>
-      <c r="G23" s="205" t="n"/>
+      <c r="G23" s="205" t="n">
+        <v>4</v>
+      </c>
       <c r="H23" s="205" t="n"/>
       <c r="I23" s="205" t="n"/>
       <c r="J23" s="205" t="n"/>
       <c r="K23" s="205" t="n"/>
       <c r="L23" s="160" t="n"/>
       <c r="M23" s="207" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="N23" s="205" t="inlineStr">
         <is>
-          <t>2-0-0</t>
+          <t>2-0-1</t>
         </is>
       </c>
       <c r="O23" s="216" t="n">
-        <v>47.5</v>
+        <v>46</v>
       </c>
     </row>
     <row r="24" ht="13.5" customHeight="1" s="181" thickBot="1">
@@ -10110,7 +10112,9 @@
       <c r="F24" s="163" t="n">
         <v>52</v>
       </c>
-      <c r="G24" s="163" t="n"/>
+      <c r="G24" s="163" t="n">
+        <v>43</v>
+      </c>
       <c r="H24" s="163" t="n"/>
       <c r="I24" s="163" t="n"/>
       <c r="J24" s="163" t="n"/>
@@ -10338,22 +10342,24 @@
       <c r="F31" s="205" t="n">
         <v>0</v>
       </c>
-      <c r="G31" s="205" t="n"/>
+      <c r="G31" s="205" t="n">
+        <v>4</v>
+      </c>
       <c r="H31" s="205" t="n"/>
       <c r="I31" s="205" t="n"/>
       <c r="J31" s="205" t="n"/>
       <c r="K31" s="205" t="n"/>
       <c r="L31" s="160" t="n"/>
       <c r="M31" s="207" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="N31" s="205" t="inlineStr">
         <is>
-          <t>0-2-0</t>
+          <t>0-2-1</t>
         </is>
       </c>
       <c r="O31" s="216" t="n">
-        <v>53.5</v>
+        <v>50</v>
       </c>
     </row>
     <row r="32" ht="13.5" customHeight="1" s="181" thickBot="1">
@@ -10370,7 +10376,9 @@
       <c r="F32" s="163" t="n">
         <v>54</v>
       </c>
-      <c r="G32" s="163" t="n"/>
+      <c r="G32" s="163" t="n">
+        <v>43</v>
+      </c>
       <c r="H32" s="163" t="n"/>
       <c r="I32" s="163" t="n"/>
       <c r="J32" s="163" t="n"/>

--- a/2026 IMI Golf League.xlsx
+++ b/2026 IMI Golf League.xlsx
@@ -10018,22 +10018,24 @@
         <v>8</v>
       </c>
       <c r="F21" s="166" t="n"/>
-      <c r="G21" s="166" t="n"/>
+      <c r="G21" s="166" t="n">
+        <v>8</v>
+      </c>
       <c r="H21" s="166" t="n"/>
       <c r="I21" s="166" t="n"/>
       <c r="J21" s="166" t="n"/>
       <c r="K21" s="166" t="n"/>
       <c r="L21" s="167" t="n"/>
       <c r="M21" s="226" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="N21" s="218" t="inlineStr">
         <is>
-          <t>2-0-0</t>
+          <t>3-0-0</t>
         </is>
       </c>
       <c r="O21" s="212" t="n">
-        <v>38.5</v>
+        <v>39.3</v>
       </c>
       <c r="Q21" s="154" t="inlineStr">
         <is>
@@ -10056,7 +10058,9 @@
         <v>42</v>
       </c>
       <c r="F22" s="170" t="n"/>
-      <c r="G22" s="170" t="n"/>
+      <c r="G22" s="170" t="n">
+        <v>41</v>
+      </c>
       <c r="H22" s="170" t="n"/>
       <c r="I22" s="170" t="n"/>
       <c r="J22" s="170" t="n"/>
@@ -10286,7 +10290,9 @@
       <c r="F29" s="166" t="n">
         <v>3.5</v>
       </c>
-      <c r="G29" s="166" t="n"/>
+      <c r="G29" s="166" t="n">
+        <v>0</v>
+      </c>
       <c r="H29" s="166" t="n"/>
       <c r="I29" s="166" t="n"/>
       <c r="J29" s="166" t="n"/>
@@ -10297,11 +10303,11 @@
       </c>
       <c r="N29" s="218" t="inlineStr">
         <is>
-          <t>1-2-0</t>
+          <t>1-3-0</t>
         </is>
       </c>
       <c r="O29" s="212" t="n">
-        <v>48.3</v>
+        <v>49.8</v>
       </c>
     </row>
     <row r="30" ht="13.5" customHeight="1" s="197" thickBot="1">
@@ -10320,7 +10326,9 @@
       <c r="F30" s="170" t="n">
         <v>43</v>
       </c>
-      <c r="G30" s="170" t="n"/>
+      <c r="G30" s="170" t="n">
+        <v>54</v>
+      </c>
       <c r="H30" s="170" t="n"/>
       <c r="I30" s="170" t="n"/>
       <c r="J30" s="170" t="n"/>

--- a/2026 IMI Golf League.xlsx
+++ b/2026 IMI Golf League.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="714" firstSheet="5" activeTab="9" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="714" firstSheet="9" activeTab="9" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scores 2024" sheetId="1" state="hidden" r:id="rId1"/>
@@ -26,7 +26,7 @@
     <definedName name="Skybrook">Helper!$C$3:$C$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Calculator (old)'!$AA$2:$AE$21</definedName>
   </definedNames>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <calcPr calcId="191028" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -1385,149 +1385,149 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="2" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="42" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="36" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="48" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="2" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="49" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="31" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="30" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="29" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="33" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1968,24 +1968,24 @@
   <dimension ref="A1:N20"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.140625" defaultRowHeight="12.75"/>
   <cols>
-    <col width="3.140625" customWidth="1" style="217" min="1" max="1"/>
-    <col width="18" bestFit="1" customWidth="1" style="217" min="2" max="2"/>
-    <col width="12.140625" bestFit="1" customWidth="1" style="217" min="3" max="3"/>
-    <col width="9.140625" customWidth="1" style="217" min="4" max="11"/>
-    <col width="11.5703125" customWidth="1" style="217" min="12" max="13"/>
-    <col width="9.140625" customWidth="1" style="217" min="14" max="28"/>
-    <col width="9.140625" customWidth="1" style="217" min="29" max="16384"/>
+    <col width="3.140625" customWidth="1" style="206" min="1" max="1"/>
+    <col width="18" bestFit="1" customWidth="1" style="206" min="2" max="2"/>
+    <col width="12.140625" bestFit="1" customWidth="1" style="206" min="3" max="3"/>
+    <col width="9.140625" customWidth="1" style="206" min="4" max="11"/>
+    <col width="11.5703125" customWidth="1" style="206" min="12" max="13"/>
+    <col width="9.140625" customWidth="1" style="206" min="14" max="29"/>
+    <col width="9.140625" customWidth="1" style="206" min="30" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1" ht="13.5" customHeight="1" s="181" thickBot="1">
-      <c r="M1" s="205" t="inlineStr">
+    <row r="1" ht="13.5" customHeight="1" s="219" thickBot="1">
+      <c r="M1" s="207" t="inlineStr">
         <is>
           <t>Tiebreaker</t>
         </is>
       </c>
       <c r="N1" s="21" t="n"/>
     </row>
-    <row r="2" ht="41.45" customHeight="1" s="181" thickBot="1">
+    <row r="2" ht="41.45" customHeight="1" s="219" thickBot="1">
       <c r="B2" s="20" t="inlineStr">
         <is>
           <t>Name</t>
@@ -2043,8 +2043,8 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="12.95" customHeight="1" s="181" thickBot="1">
-      <c r="A3" s="217" t="n">
+    <row r="3" ht="12.95" customHeight="1" s="219" thickBot="1">
+      <c r="A3" s="206" t="n">
         <v>1</v>
       </c>
       <c r="B3" s="25" t="inlineStr">
@@ -2084,8 +2084,8 @@
         <v/>
       </c>
     </row>
-    <row r="4" ht="12.95" customHeight="1" s="181" thickBot="1">
-      <c r="A4" s="217" t="n">
+    <row r="4" ht="12.95" customHeight="1" s="219" thickBot="1">
+      <c r="A4" s="206" t="n">
         <v>2</v>
       </c>
       <c r="B4" s="25" t="inlineStr">
@@ -2125,8 +2125,8 @@
         <v/>
       </c>
     </row>
-    <row r="5" ht="12.95" customHeight="1" s="181" thickBot="1">
-      <c r="A5" s="217" t="n">
+    <row r="5" ht="12.95" customHeight="1" s="219" thickBot="1">
+      <c r="A5" s="206" t="n">
         <v>3</v>
       </c>
       <c r="B5" s="25" t="inlineStr">
@@ -2166,8 +2166,8 @@
         <v/>
       </c>
     </row>
-    <row r="6" ht="12.95" customHeight="1" s="181" thickBot="1">
-      <c r="A6" s="217" t="n">
+    <row r="6" ht="12.95" customHeight="1" s="219" thickBot="1">
+      <c r="A6" s="206" t="n">
         <v>4</v>
       </c>
       <c r="B6" s="25" t="inlineStr">
@@ -2205,8 +2205,8 @@
         <v/>
       </c>
     </row>
-    <row r="7" ht="12.95" customHeight="1" s="181" thickBot="1">
-      <c r="A7" s="217" t="n">
+    <row r="7" ht="12.95" customHeight="1" s="219" thickBot="1">
+      <c r="A7" s="206" t="n">
         <v>5</v>
       </c>
       <c r="B7" s="25" t="inlineStr">
@@ -2248,8 +2248,8 @@
         <v/>
       </c>
     </row>
-    <row r="8" ht="12.95" customHeight="1" s="181" thickBot="1">
-      <c r="A8" s="217" t="n">
+    <row r="8" ht="12.95" customHeight="1" s="219" thickBot="1">
+      <c r="A8" s="206" t="n">
         <v>6</v>
       </c>
       <c r="B8" s="25" t="inlineStr">
@@ -2289,8 +2289,8 @@
         <v/>
       </c>
     </row>
-    <row r="9" ht="12.95" customHeight="1" s="181" thickBot="1">
-      <c r="A9" s="217" t="n">
+    <row r="9" ht="12.95" customHeight="1" s="219" thickBot="1">
+      <c r="A9" s="206" t="n">
         <v>7</v>
       </c>
       <c r="B9" s="25" t="inlineStr">
@@ -2328,8 +2328,8 @@
         <v/>
       </c>
     </row>
-    <row r="10" ht="12.95" customHeight="1" s="181" thickBot="1">
-      <c r="A10" s="217" t="n">
+    <row r="10" ht="12.95" customHeight="1" s="219" thickBot="1">
+      <c r="A10" s="206" t="n">
         <v>8</v>
       </c>
       <c r="B10" s="25" t="inlineStr">
@@ -2369,8 +2369,8 @@
         <v/>
       </c>
     </row>
-    <row r="11" ht="12.95" customHeight="1" s="181" thickBot="1">
-      <c r="A11" s="217" t="n">
+    <row r="11" ht="12.95" customHeight="1" s="219" thickBot="1">
+      <c r="A11" s="206" t="n">
         <v>9</v>
       </c>
       <c r="B11" s="25" t="inlineStr">
@@ -2410,8 +2410,8 @@
         <v/>
       </c>
     </row>
-    <row r="12" ht="12.95" customHeight="1" s="181" thickBot="1">
-      <c r="A12" s="217" t="n">
+    <row r="12" ht="12.95" customHeight="1" s="219" thickBot="1">
+      <c r="A12" s="206" t="n">
         <v>10</v>
       </c>
       <c r="B12" s="25" t="inlineStr">
@@ -2453,8 +2453,8 @@
         <v/>
       </c>
     </row>
-    <row r="13" ht="12.95" customHeight="1" s="181" thickBot="1">
-      <c r="A13" s="217" t="n">
+    <row r="13" ht="12.95" customHeight="1" s="219" thickBot="1">
+      <c r="A13" s="206" t="n">
         <v>11</v>
       </c>
       <c r="B13" s="25" t="inlineStr">
@@ -2492,8 +2492,8 @@
         <v/>
       </c>
     </row>
-    <row r="14" ht="12.95" customHeight="1" s="181" thickBot="1">
-      <c r="A14" s="217" t="n">
+    <row r="14" ht="12.95" customHeight="1" s="219" thickBot="1">
+      <c r="A14" s="206" t="n">
         <v>12</v>
       </c>
       <c r="B14" s="25" t="inlineStr">
@@ -2533,8 +2533,8 @@
         <v/>
       </c>
     </row>
-    <row r="15" ht="12.95" customHeight="1" s="181" thickBot="1">
-      <c r="A15" s="217" t="n">
+    <row r="15" ht="12.95" customHeight="1" s="219" thickBot="1">
+      <c r="A15" s="206" t="n">
         <v>13</v>
       </c>
       <c r="B15" s="25" t="inlineStr">
@@ -2574,8 +2574,8 @@
         <v/>
       </c>
     </row>
-    <row r="16" ht="12.95" customHeight="1" s="181" thickBot="1">
-      <c r="A16" s="217" t="n">
+    <row r="16" ht="12.95" customHeight="1" s="219" thickBot="1">
+      <c r="A16" s="206" t="n">
         <v>14</v>
       </c>
       <c r="B16" s="25" t="inlineStr">
@@ -2615,8 +2615,8 @@
         <v/>
       </c>
     </row>
-    <row r="17" ht="12.95" customHeight="1" s="181" thickBot="1">
-      <c r="A17" s="217" t="n">
+    <row r="17" ht="12.95" customHeight="1" s="219" thickBot="1">
+      <c r="A17" s="206" t="n">
         <v>15</v>
       </c>
       <c r="B17" s="25" t="inlineStr">
@@ -2654,8 +2654,8 @@
         <v/>
       </c>
     </row>
-    <row r="18" ht="12.95" customHeight="1" s="181" thickBot="1">
-      <c r="A18" s="217" t="n">
+    <row r="18" ht="12.95" customHeight="1" s="219" thickBot="1">
+      <c r="A18" s="206" t="n">
         <v>16</v>
       </c>
       <c r="B18" s="25" t="inlineStr">
@@ -2697,8 +2697,8 @@
         <v/>
       </c>
     </row>
-    <row r="19" ht="12.95" customHeight="1" s="181" thickBot="1">
-      <c r="A19" s="217" t="n">
+    <row r="19" ht="12.95" customHeight="1" s="219" thickBot="1">
+      <c r="A19" s="206" t="n">
         <v>17</v>
       </c>
       <c r="B19" s="25" t="inlineStr">
@@ -2738,8 +2738,8 @@
         <v/>
       </c>
     </row>
-    <row r="20" ht="12.95" customHeight="1" s="181">
-      <c r="A20" s="217" t="n">
+    <row r="20" ht="12.95" customHeight="1" s="219">
+      <c r="A20" s="206" t="n">
         <v>18</v>
       </c>
       <c r="B20" s="25" t="inlineStr">
@@ -2793,48 +2793,48 @@
   <dimension ref="B1:BG24"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.85546875" defaultRowHeight="13.5"/>
   <cols>
-    <col width="2.5703125" customWidth="1" style="235" min="1" max="1"/>
-    <col width="20.7109375" customWidth="1" style="235" min="2" max="2"/>
-    <col width="9.85546875" customWidth="1" style="235" min="3" max="8"/>
-    <col width="10.7109375" bestFit="1" customWidth="1" style="235" min="9" max="9"/>
-    <col width="10.5703125" customWidth="1" style="235" min="10" max="11"/>
-    <col width="10.85546875" customWidth="1" style="235" min="12" max="13"/>
-    <col width="5.7109375" customWidth="1" style="235" min="14" max="14"/>
-    <col width="11" bestFit="1" customWidth="1" style="235" min="15" max="15"/>
-    <col width="16.5703125" bestFit="1" customWidth="1" style="235" min="16" max="16"/>
-    <col width="8.85546875" bestFit="1" customWidth="1" style="235" min="17" max="17"/>
-    <col width="4.5703125" customWidth="1" style="235" min="18" max="19"/>
-    <col width="11" bestFit="1" customWidth="1" style="235" min="20" max="20"/>
-    <col width="4" customWidth="1" style="235" min="21" max="29"/>
-    <col width="10.42578125" bestFit="1" customWidth="1" style="235" min="30" max="30"/>
-    <col width="4" customWidth="1" style="235" min="31" max="39"/>
-    <col width="11" bestFit="1" customWidth="1" style="235" min="40" max="40"/>
-    <col width="4" customWidth="1" style="235" min="41" max="49"/>
-    <col width="10.42578125" bestFit="1" customWidth="1" style="235" min="50" max="50"/>
-    <col width="4" customWidth="1" style="235" min="51" max="59"/>
-    <col width="9.85546875" customWidth="1" style="235" min="60" max="74"/>
-    <col width="9.85546875" customWidth="1" style="235" min="75" max="16384"/>
+    <col width="2.5703125" customWidth="1" style="180" min="1" max="1"/>
+    <col width="20.7109375" customWidth="1" style="180" min="2" max="2"/>
+    <col width="9.85546875" customWidth="1" style="180" min="3" max="8"/>
+    <col width="10.7109375" bestFit="1" customWidth="1" style="180" min="9" max="9"/>
+    <col width="10.5703125" customWidth="1" style="180" min="10" max="11"/>
+    <col width="10.85546875" customWidth="1" style="180" min="12" max="13"/>
+    <col width="5.7109375" customWidth="1" style="180" min="14" max="14"/>
+    <col width="11" bestFit="1" customWidth="1" style="180" min="15" max="15"/>
+    <col width="16.5703125" bestFit="1" customWidth="1" style="180" min="16" max="16"/>
+    <col width="8.85546875" bestFit="1" customWidth="1" style="180" min="17" max="17"/>
+    <col width="4.5703125" customWidth="1" style="180" min="18" max="19"/>
+    <col width="11" bestFit="1" customWidth="1" style="180" min="20" max="20"/>
+    <col width="4" customWidth="1" style="180" min="21" max="29"/>
+    <col width="10.42578125" bestFit="1" customWidth="1" style="180" min="30" max="30"/>
+    <col width="4" customWidth="1" style="180" min="31" max="39"/>
+    <col width="11" bestFit="1" customWidth="1" style="180" min="40" max="40"/>
+    <col width="4" customWidth="1" style="180" min="41" max="49"/>
+    <col width="10.42578125" bestFit="1" customWidth="1" style="180" min="50" max="50"/>
+    <col width="4" customWidth="1" style="180" min="51" max="59"/>
+    <col width="9.85546875" customWidth="1" style="180" min="60" max="75"/>
+    <col width="9.85546875" customWidth="1" style="180" min="76" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.25" customHeight="1" s="181" thickBot="1">
+    <row r="1" ht="14.25" customHeight="1" s="219" thickBot="1">
       <c r="B1" s="116" t="inlineStr">
         <is>
           <t>Fill in the course, your name, tees, front/back and gross scores in the grey boxes</t>
         </is>
       </c>
-      <c r="J1" s="233" t="inlineStr">
+      <c r="J1" s="184" t="inlineStr">
         <is>
           <t>Points</t>
         </is>
       </c>
-      <c r="K1" s="206" t="n"/>
-      <c r="L1" s="206" t="n"/>
-      <c r="M1" s="206" t="n"/>
-    </row>
-    <row r="2" ht="24.95" customHeight="1" s="181" thickBot="1">
+      <c r="K1" s="227" t="n"/>
+      <c r="L1" s="227" t="n"/>
+      <c r="M1" s="227" t="n"/>
+    </row>
+    <row r="2" ht="24.95" customHeight="1" s="219" thickBot="1">
       <c r="B2" s="172" t="inlineStr">
         <is>
-          <t>Skybrook</t>
+          <t>Highland Creek</t>
         </is>
       </c>
       <c r="D2" s="118" t="inlineStr">
@@ -2863,19 +2863,19 @@
         </is>
       </c>
       <c r="I2" s="119" t="n"/>
-      <c r="J2" s="239">
+      <c r="J2" s="182">
         <f>B8</f>
         <v/>
       </c>
-      <c r="K2" s="199" t="n"/>
-      <c r="L2" s="237">
+      <c r="K2" s="229" t="n"/>
+      <c r="L2" s="178">
         <f>B17</f>
         <v/>
       </c>
-      <c r="M2" s="199" t="n"/>
-    </row>
-    <row r="3" ht="14.25" customHeight="1" s="181" thickBot="1">
-      <c r="B3" s="240">
+      <c r="M2" s="229" t="n"/>
+    </row>
+    <row r="3" ht="14.25" customHeight="1" s="219" thickBot="1">
+      <c r="B3" s="183">
         <f>J2</f>
         <v/>
       </c>
@@ -2904,19 +2904,19 @@
         <f>SUM(C14:K14)</f>
         <v/>
       </c>
-      <c r="J3" s="238">
+      <c r="J3" s="181">
         <f>SUM(D4:H4)</f>
         <v/>
       </c>
-      <c r="K3" s="224" t="n"/>
-      <c r="L3" s="236">
+      <c r="K3" s="236" t="n"/>
+      <c r="L3" s="185">
         <f>SUM(D6:H6)</f>
         <v/>
       </c>
-      <c r="M3" s="224" t="n"/>
-    </row>
-    <row r="4" ht="14.25" customHeight="1" s="181" thickBot="1">
-      <c r="B4" s="221" t="n"/>
+      <c r="M3" s="236" t="n"/>
+    </row>
+    <row r="4" ht="14.25" customHeight="1" s="219" thickBot="1">
+      <c r="B4" s="237" t="n"/>
       <c r="C4" s="125" t="inlineStr">
         <is>
           <t>PTS</t>
@@ -2942,12 +2942,12 @@
         <f>IF(H3&lt;H5,1,IF(H3=H5,0.5,0))</f>
         <v/>
       </c>
-      <c r="J4" s="231" t="n"/>
-      <c r="K4" s="226" t="n"/>
-      <c r="M4" s="226" t="n"/>
-    </row>
-    <row r="5" ht="14.25" customHeight="1" s="181" thickBot="1">
-      <c r="B5" s="240">
+      <c r="J4" s="238" t="n"/>
+      <c r="K4" s="239" t="n"/>
+      <c r="M4" s="239" t="n"/>
+    </row>
+    <row r="5" ht="14.25" customHeight="1" s="219" thickBot="1">
+      <c r="B5" s="183">
         <f>L2</f>
         <v/>
       </c>
@@ -2976,13 +2976,13 @@
         <f>SUM(C23:K23)</f>
         <v/>
       </c>
-      <c r="J5" s="221" t="n"/>
-      <c r="K5" s="227" t="n"/>
-      <c r="L5" s="206" t="n"/>
-      <c r="M5" s="227" t="n"/>
-    </row>
-    <row r="6" ht="14.25" customHeight="1" s="181" thickBot="1">
-      <c r="B6" s="221" t="n"/>
+      <c r="J5" s="237" t="n"/>
+      <c r="K5" s="240" t="n"/>
+      <c r="L5" s="227" t="n"/>
+      <c r="M5" s="240" t="n"/>
+    </row>
+    <row r="6" ht="14.25" customHeight="1" s="219" thickBot="1">
+      <c r="B6" s="237" t="n"/>
       <c r="C6" s="125" t="inlineStr">
         <is>
           <t>PTS</t>
@@ -3008,34 +3008,34 @@
         <f>IF(H5&lt;H3,1,IF(H5=H3,0.5,0))</f>
         <v/>
       </c>
-      <c r="J6" s="234" t="n"/>
-      <c r="K6" s="234" t="n"/>
-      <c r="L6" s="234" t="n"/>
-      <c r="M6" s="234" t="n"/>
+      <c r="J6" s="179" t="n"/>
+      <c r="K6" s="179" t="n"/>
+      <c r="L6" s="179" t="n"/>
+      <c r="M6" s="179" t="n"/>
     </row>
     <row r="7">
-      <c r="C7" s="234" t="n"/>
-      <c r="D7" s="234" t="n"/>
-      <c r="E7" s="234" t="n"/>
-      <c r="F7" s="234" t="n"/>
-      <c r="G7" s="234" t="n"/>
-      <c r="H7" s="234" t="n"/>
-      <c r="I7" s="234" t="n"/>
-      <c r="J7" s="234" t="n"/>
-      <c r="K7" s="234" t="n"/>
-      <c r="L7" s="234" t="n"/>
-      <c r="T7" s="234" t="inlineStr">
+      <c r="C7" s="179" t="n"/>
+      <c r="D7" s="179" t="n"/>
+      <c r="E7" s="179" t="n"/>
+      <c r="F7" s="179" t="n"/>
+      <c r="G7" s="179" t="n"/>
+      <c r="H7" s="179" t="n"/>
+      <c r="I7" s="179" t="n"/>
+      <c r="J7" s="179" t="n"/>
+      <c r="K7" s="179" t="n"/>
+      <c r="L7" s="179" t="n"/>
+      <c r="T7" s="179" t="inlineStr">
         <is>
           <t>Skybrook</t>
         </is>
       </c>
-      <c r="AN7" s="234" t="inlineStr">
+      <c r="AN7" s="179" t="inlineStr">
         <is>
           <t>Highland Creek</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="16.5" customHeight="1" s="181" thickBot="1">
+    <row r="8" ht="16.5" customHeight="1" s="219" thickBot="1">
       <c r="B8" s="145" t="inlineStr">
         <is>
           <t>Preston Stoner</t>
@@ -3046,12 +3046,12 @@
           <t>Handicap:</t>
         </is>
       </c>
-      <c r="D8" s="234">
+      <c r="D8" s="179">
         <f>_xlfn.XLOOKUP(B8,$P$9:$P$23,$Q$9:$Q$23)</f>
         <v/>
       </c>
-      <c r="E8" s="234" t="n"/>
-      <c r="F8" s="234" t="inlineStr">
+      <c r="E8" s="179" t="n"/>
+      <c r="F8" s="179" t="inlineStr">
         <is>
           <t>Tees:</t>
         </is>
@@ -3061,8 +3061,8 @@
           <t>Blue</t>
         </is>
       </c>
-      <c r="H8" s="234" t="n"/>
-      <c r="I8" s="234" t="inlineStr">
+      <c r="H8" s="179" t="n"/>
+      <c r="I8" s="179" t="inlineStr">
         <is>
           <t>Holes:</t>
         </is>
@@ -3072,8 +3072,8 @@
           <t>Front 9</t>
         </is>
       </c>
-      <c r="K8" s="234" t="n"/>
-      <c r="L8" s="234" t="n"/>
+      <c r="K8" s="179" t="n"/>
+      <c r="L8" s="179" t="n"/>
       <c r="O8" s="143" t="inlineStr">
         <is>
           <t>#</t>
@@ -3089,38 +3089,38 @@
           <t>Handicap</t>
         </is>
       </c>
-      <c r="T8" s="235" t="inlineStr">
+      <c r="T8" s="180" t="inlineStr">
         <is>
           <t>HC's by Tees</t>
         </is>
       </c>
-      <c r="U8" s="234" t="inlineStr">
+      <c r="U8" s="179" t="inlineStr">
         <is>
           <t>Front 9</t>
         </is>
       </c>
-      <c r="AD8" s="234" t="inlineStr">
+      <c r="AD8" s="179" t="inlineStr">
         <is>
           <t>Back 9</t>
         </is>
       </c>
-      <c r="AN8" s="235" t="inlineStr">
+      <c r="AN8" s="180" t="inlineStr">
         <is>
           <t>HC's by Tees</t>
         </is>
       </c>
-      <c r="AO8" s="234" t="inlineStr">
+      <c r="AO8" s="179" t="inlineStr">
         <is>
           <t>Front 9</t>
         </is>
       </c>
-      <c r="AX8" s="234" t="inlineStr">
+      <c r="AX8" s="179" t="inlineStr">
         <is>
           <t>Back 9</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" s="181">
+    <row r="9" ht="15" customHeight="1" s="219">
       <c r="B9" s="131" t="inlineStr">
         <is>
           <t>HOLE</t>
@@ -3153,7 +3153,7 @@
       <c r="K9" s="134" t="n">
         <v>9</v>
       </c>
-      <c r="L9" s="234" t="n"/>
+      <c r="L9" s="179" t="n"/>
       <c r="O9" s="122" t="n">
         <v>1</v>
       </c>
@@ -3166,132 +3166,132 @@
         <f>Schedule!D15</f>
         <v/>
       </c>
-      <c r="T9" s="235" t="inlineStr">
+      <c r="T9" s="180" t="inlineStr">
         <is>
           <t>Blue</t>
         </is>
       </c>
-      <c r="U9" s="234" t="n">
+      <c r="U9" s="179" t="n">
         <v>7</v>
       </c>
-      <c r="V9" s="234" t="n">
+      <c r="V9" s="179" t="n">
         <v>15</v>
       </c>
-      <c r="W9" s="234" t="n">
+      <c r="W9" s="179" t="n">
         <v>5</v>
       </c>
-      <c r="X9" s="234" t="n">
+      <c r="X9" s="179" t="n">
         <v>13</v>
       </c>
-      <c r="Y9" s="234" t="n">
+      <c r="Y9" s="179" t="n">
         <v>3</v>
       </c>
-      <c r="Z9" s="234" t="n">
+      <c r="Z9" s="179" t="n">
         <v>11</v>
       </c>
-      <c r="AA9" s="234" t="n">
+      <c r="AA9" s="179" t="n">
         <v>17</v>
       </c>
-      <c r="AB9" s="234" t="n">
+      <c r="AB9" s="179" t="n">
         <v>9</v>
       </c>
-      <c r="AC9" s="234" t="n">
+      <c r="AC9" s="179" t="n">
         <v>1</v>
       </c>
-      <c r="AD9" s="235" t="inlineStr">
+      <c r="AD9" s="180" t="inlineStr">
         <is>
           <t>Blue</t>
         </is>
       </c>
-      <c r="AE9" s="234" t="n">
+      <c r="AE9" s="179" t="n">
         <v>4</v>
       </c>
-      <c r="AF9" s="234" t="n">
+      <c r="AF9" s="179" t="n">
         <v>12</v>
       </c>
-      <c r="AG9" s="234" t="n">
+      <c r="AG9" s="179" t="n">
         <v>14</v>
       </c>
-      <c r="AH9" s="234" t="n">
+      <c r="AH9" s="179" t="n">
         <v>6</v>
       </c>
-      <c r="AI9" s="234" t="n">
+      <c r="AI9" s="179" t="n">
         <v>16</v>
       </c>
-      <c r="AJ9" s="234" t="n">
+      <c r="AJ9" s="179" t="n">
         <v>8</v>
       </c>
-      <c r="AK9" s="234" t="n">
+      <c r="AK9" s="179" t="n">
         <v>18</v>
       </c>
-      <c r="AL9" s="234" t="n">
+      <c r="AL9" s="179" t="n">
         <v>2</v>
       </c>
-      <c r="AM9" s="234" t="n">
+      <c r="AM9" s="179" t="n">
         <v>10</v>
       </c>
-      <c r="AN9" s="235" t="inlineStr">
+      <c r="AN9" s="180" t="inlineStr">
         <is>
           <t>Blue</t>
         </is>
       </c>
-      <c r="AO9" s="234" t="n">
+      <c r="AO9" s="179" t="n">
         <v>7</v>
       </c>
-      <c r="AP9" s="234" t="n">
+      <c r="AP9" s="179" t="n">
         <v>17</v>
       </c>
-      <c r="AQ9" s="234" t="n">
+      <c r="AQ9" s="179" t="n">
         <v>15</v>
       </c>
-      <c r="AR9" s="234" t="n">
+      <c r="AR9" s="179" t="n">
         <v>1</v>
       </c>
-      <c r="AS9" s="234" t="n">
+      <c r="AS9" s="179" t="n">
         <v>11</v>
       </c>
-      <c r="AT9" s="234" t="n">
+      <c r="AT9" s="179" t="n">
         <v>9</v>
       </c>
-      <c r="AU9" s="234" t="n">
+      <c r="AU9" s="179" t="n">
         <v>13</v>
       </c>
-      <c r="AV9" s="234" t="n">
+      <c r="AV9" s="179" t="n">
         <v>5</v>
       </c>
-      <c r="AW9" s="234" t="n">
+      <c r="AW9" s="179" t="n">
         <v>3</v>
       </c>
-      <c r="AX9" s="235" t="inlineStr">
+      <c r="AX9" s="180" t="inlineStr">
         <is>
           <t>Blue</t>
         </is>
       </c>
-      <c r="AY9" s="234" t="n">
+      <c r="AY9" s="179" t="n">
         <v>14</v>
       </c>
-      <c r="AZ9" s="234" t="n">
+      <c r="AZ9" s="179" t="n">
         <v>8</v>
       </c>
-      <c r="BA9" s="234" t="n">
+      <c r="BA9" s="179" t="n">
         <v>6</v>
       </c>
-      <c r="BB9" s="234" t="n">
+      <c r="BB9" s="179" t="n">
         <v>4</v>
       </c>
-      <c r="BC9" s="234" t="n">
+      <c r="BC9" s="179" t="n">
         <v>16</v>
       </c>
-      <c r="BD9" s="234" t="n">
+      <c r="BD9" s="179" t="n">
         <v>2</v>
       </c>
-      <c r="BE9" s="234" t="n">
+      <c r="BE9" s="179" t="n">
         <v>10</v>
       </c>
-      <c r="BF9" s="234" t="n">
+      <c r="BF9" s="179" t="n">
         <v>12</v>
       </c>
-      <c r="BG9" s="234" t="n">
+      <c r="BG9" s="179" t="n">
         <v>18</v>
       </c>
     </row>
@@ -3301,7 +3301,7 @@
           <t>PAR</t>
         </is>
       </c>
-      <c r="C10" s="234">
+      <c r="C10" s="179">
         <f t="array" ref="C10">IF($B$2="Skybrook",
    _xlfn.IFS(
       $J8="Back 9",INDEX($AE$12:$AM$12,1,C9),
@@ -3314,7 +3314,7 @@
 )</f>
         <v/>
       </c>
-      <c r="D10" s="234">
+      <c r="D10" s="179">
         <f t="array" ref="D10">IF($B$2="Skybrook",
    _xlfn.IFS(
       $J8="Back 9",INDEX($AE$12:$AM$12,1,D9),
@@ -3353,7 +3353,7 @@
 )</f>
         <v/>
       </c>
-      <c r="G10" s="234">
+      <c r="G10" s="179">
         <f t="array" ref="G10">IF($B$2="Skybrook",
    _xlfn.IFS(
       $J8="Back 9",INDEX($AE$12:$AM$12,1,G9),
@@ -3392,7 +3392,7 @@
 )</f>
         <v/>
       </c>
-      <c r="J10" s="234">
+      <c r="J10" s="179">
         <f t="array" ref="J10">IF($B$2="Skybrook",
    _xlfn.IFS(
       $J8="Back 9",INDEX($AE$12:$AM$12,1,J9),
@@ -3418,7 +3418,7 @@
 )</f>
         <v/>
       </c>
-      <c r="L10" s="234">
+      <c r="L10" s="179">
         <f>SUM(C10:K10)</f>
         <v/>
       </c>
@@ -3434,132 +3434,132 @@
         <f>Schedule!D16</f>
         <v/>
       </c>
-      <c r="T10" s="235" t="inlineStr">
+      <c r="T10" s="180" t="inlineStr">
         <is>
           <t>Green</t>
         </is>
       </c>
-      <c r="U10" s="234" t="n">
+      <c r="U10" s="179" t="n">
         <v>7</v>
       </c>
-      <c r="V10" s="234" t="n">
+      <c r="V10" s="179" t="n">
         <v>15</v>
       </c>
-      <c r="W10" s="234" t="n">
+      <c r="W10" s="179" t="n">
         <v>5</v>
       </c>
-      <c r="X10" s="234" t="n">
+      <c r="X10" s="179" t="n">
         <v>13</v>
       </c>
-      <c r="Y10" s="234" t="n">
+      <c r="Y10" s="179" t="n">
         <v>3</v>
       </c>
-      <c r="Z10" s="234" t="n">
+      <c r="Z10" s="179" t="n">
         <v>11</v>
       </c>
-      <c r="AA10" s="234" t="n">
+      <c r="AA10" s="179" t="n">
         <v>17</v>
       </c>
-      <c r="AB10" s="234" t="n">
+      <c r="AB10" s="179" t="n">
         <v>9</v>
       </c>
-      <c r="AC10" s="234" t="n">
+      <c r="AC10" s="179" t="n">
         <v>1</v>
       </c>
-      <c r="AD10" s="235" t="inlineStr">
+      <c r="AD10" s="180" t="inlineStr">
         <is>
           <t>Green</t>
         </is>
       </c>
-      <c r="AE10" s="234" t="n">
+      <c r="AE10" s="179" t="n">
         <v>4</v>
       </c>
-      <c r="AF10" s="234" t="n">
+      <c r="AF10" s="179" t="n">
         <v>12</v>
       </c>
-      <c r="AG10" s="234" t="n">
+      <c r="AG10" s="179" t="n">
         <v>14</v>
       </c>
-      <c r="AH10" s="234" t="n">
+      <c r="AH10" s="179" t="n">
         <v>6</v>
       </c>
-      <c r="AI10" s="234" t="n">
+      <c r="AI10" s="179" t="n">
         <v>16</v>
       </c>
-      <c r="AJ10" s="234" t="n">
+      <c r="AJ10" s="179" t="n">
         <v>8</v>
       </c>
-      <c r="AK10" s="234" t="n">
+      <c r="AK10" s="179" t="n">
         <v>18</v>
       </c>
-      <c r="AL10" s="234" t="n">
+      <c r="AL10" s="179" t="n">
         <v>2</v>
       </c>
-      <c r="AM10" s="234" t="n">
+      <c r="AM10" s="179" t="n">
         <v>10</v>
       </c>
-      <c r="AN10" s="235" t="inlineStr">
+      <c r="AN10" s="180" t="inlineStr">
         <is>
           <t>White</t>
         </is>
       </c>
-      <c r="AO10" s="234" t="n">
+      <c r="AO10" s="179" t="n">
         <v>7</v>
       </c>
-      <c r="AP10" s="234" t="n">
+      <c r="AP10" s="179" t="n">
         <v>17</v>
       </c>
-      <c r="AQ10" s="234" t="n">
+      <c r="AQ10" s="179" t="n">
         <v>15</v>
       </c>
-      <c r="AR10" s="234" t="n">
+      <c r="AR10" s="179" t="n">
         <v>1</v>
       </c>
-      <c r="AS10" s="234" t="n">
+      <c r="AS10" s="179" t="n">
         <v>11</v>
       </c>
-      <c r="AT10" s="234" t="n">
+      <c r="AT10" s="179" t="n">
         <v>9</v>
       </c>
-      <c r="AU10" s="234" t="n">
+      <c r="AU10" s="179" t="n">
         <v>13</v>
       </c>
-      <c r="AV10" s="234" t="n">
+      <c r="AV10" s="179" t="n">
         <v>5</v>
       </c>
-      <c r="AW10" s="234" t="n">
+      <c r="AW10" s="179" t="n">
         <v>3</v>
       </c>
-      <c r="AX10" s="235" t="inlineStr">
+      <c r="AX10" s="180" t="inlineStr">
         <is>
           <t>White</t>
         </is>
       </c>
-      <c r="AY10" s="234" t="n">
+      <c r="AY10" s="179" t="n">
         <v>14</v>
       </c>
-      <c r="AZ10" s="234" t="n">
+      <c r="AZ10" s="179" t="n">
         <v>8</v>
       </c>
-      <c r="BA10" s="234" t="n">
+      <c r="BA10" s="179" t="n">
         <v>6</v>
       </c>
-      <c r="BB10" s="234" t="n">
+      <c r="BB10" s="179" t="n">
         <v>4</v>
       </c>
-      <c r="BC10" s="234" t="n">
+      <c r="BC10" s="179" t="n">
         <v>16</v>
       </c>
-      <c r="BD10" s="234" t="n">
+      <c r="BD10" s="179" t="n">
         <v>2</v>
       </c>
-      <c r="BE10" s="234" t="n">
+      <c r="BE10" s="179" t="n">
         <v>10</v>
       </c>
-      <c r="BF10" s="234" t="n">
+      <c r="BF10" s="179" t="n">
         <v>12</v>
       </c>
-      <c r="BG10" s="234" t="n">
+      <c r="BG10" s="179" t="n">
         <v>18</v>
       </c>
     </row>
@@ -3569,7 +3569,7 @@
           <t>HC</t>
         </is>
       </c>
-      <c r="C11" s="234">
+      <c r="C11" s="179">
         <f t="array" ref="C11">IF($B$2="Skybrook",
    _xlfn.IFS(
       $J8="Back 9",VLOOKUP($G8,$AD$9:$AM$11,COLUMN()-1,0),
@@ -3582,7 +3582,7 @@
 )</f>
         <v/>
       </c>
-      <c r="D11" s="234">
+      <c r="D11" s="179">
         <f t="array" ref="D11">IF($B$2="Skybrook",
    _xlfn.IFS(
       $J8="Back 9",VLOOKUP($G8,$AD$9:$AM$11,COLUMN()-1,0),
@@ -3621,7 +3621,7 @@
 )</f>
         <v/>
       </c>
-      <c r="G11" s="234">
+      <c r="G11" s="179">
         <f t="array" ref="G11">IF($B$2="Skybrook",
    _xlfn.IFS(
       $J8="Back 9",VLOOKUP($G8,$AD$9:$AM$11,COLUMN()-1,0),
@@ -3660,7 +3660,7 @@
 )</f>
         <v/>
       </c>
-      <c r="J11" s="234">
+      <c r="J11" s="179">
         <f t="array" ref="J11">IF($B$2="Skybrook",
    _xlfn.IFS(
       $J8="Back 9",VLOOKUP($G8,$AD$9:$AM$11,COLUMN()-1,0),
@@ -3686,7 +3686,7 @@
 )</f>
         <v/>
       </c>
-      <c r="L11" s="234" t="n"/>
+      <c r="L11" s="179" t="n"/>
       <c r="O11" s="122">
         <f>O10+1</f>
         <v/>
@@ -3700,136 +3700,136 @@
         <f>Schedule!D17</f>
         <v/>
       </c>
-      <c r="T11" s="235" t="inlineStr">
+      <c r="T11" s="180" t="inlineStr">
         <is>
           <t>Red</t>
         </is>
       </c>
-      <c r="U11" s="234" t="n">
+      <c r="U11" s="179" t="n">
         <v>17</v>
       </c>
-      <c r="V11" s="234" t="n">
+      <c r="V11" s="179" t="n">
         <v>9</v>
       </c>
-      <c r="W11" s="234" t="n">
+      <c r="W11" s="179" t="n">
         <v>5</v>
       </c>
-      <c r="X11" s="234" t="n">
+      <c r="X11" s="179" t="n">
         <v>7</v>
       </c>
-      <c r="Y11" s="234" t="n">
+      <c r="Y11" s="179" t="n">
         <v>3</v>
       </c>
-      <c r="Z11" s="234" t="n">
+      <c r="Z11" s="179" t="n">
         <v>15</v>
       </c>
-      <c r="AA11" s="234" t="n">
+      <c r="AA11" s="179" t="n">
         <v>11</v>
       </c>
-      <c r="AB11" s="234" t="n">
+      <c r="AB11" s="179" t="n">
         <v>13</v>
       </c>
-      <c r="AC11" s="234" t="n">
+      <c r="AC11" s="179" t="n">
         <v>1</v>
       </c>
-      <c r="AD11" s="235" t="inlineStr">
+      <c r="AD11" s="180" t="inlineStr">
         <is>
           <t>Red</t>
         </is>
       </c>
-      <c r="AE11" s="234" t="n">
+      <c r="AE11" s="179" t="n">
         <v>4</v>
       </c>
-      <c r="AF11" s="234" t="n">
+      <c r="AF11" s="179" t="n">
         <v>10</v>
       </c>
-      <c r="AG11" s="234" t="n">
+      <c r="AG11" s="179" t="n">
         <v>14</v>
       </c>
-      <c r="AH11" s="234" t="n">
+      <c r="AH11" s="179" t="n">
         <v>6</v>
       </c>
-      <c r="AI11" s="234" t="n">
+      <c r="AI11" s="179" t="n">
         <v>16</v>
       </c>
-      <c r="AJ11" s="234" t="n">
+      <c r="AJ11" s="179" t="n">
         <v>12</v>
       </c>
-      <c r="AK11" s="234" t="n">
+      <c r="AK11" s="179" t="n">
         <v>18</v>
       </c>
-      <c r="AL11" s="234" t="n">
+      <c r="AL11" s="179" t="n">
         <v>2</v>
       </c>
-      <c r="AM11" s="234" t="n">
+      <c r="AM11" s="179" t="n">
         <v>8</v>
       </c>
-      <c r="AN11" s="235" t="inlineStr">
+      <c r="AN11" s="180" t="inlineStr">
         <is>
           <t>Red</t>
         </is>
       </c>
-      <c r="AO11" s="234" t="n">
+      <c r="AO11" s="179" t="n">
         <v>7</v>
       </c>
-      <c r="AP11" s="234" t="n">
+      <c r="AP11" s="179" t="n">
         <v>17</v>
       </c>
-      <c r="AQ11" s="234" t="n">
+      <c r="AQ11" s="179" t="n">
         <v>15</v>
       </c>
-      <c r="AR11" s="234" t="n">
+      <c r="AR11" s="179" t="n">
         <v>1</v>
       </c>
-      <c r="AS11" s="234" t="n">
+      <c r="AS11" s="179" t="n">
         <v>11</v>
       </c>
-      <c r="AT11" s="234" t="n">
+      <c r="AT11" s="179" t="n">
         <v>9</v>
       </c>
-      <c r="AU11" s="234" t="n">
+      <c r="AU11" s="179" t="n">
         <v>13</v>
       </c>
-      <c r="AV11" s="234" t="n">
+      <c r="AV11" s="179" t="n">
         <v>5</v>
       </c>
-      <c r="AW11" s="234" t="n">
+      <c r="AW11" s="179" t="n">
         <v>3</v>
       </c>
-      <c r="AX11" s="235" t="inlineStr">
+      <c r="AX11" s="180" t="inlineStr">
         <is>
           <t>Red</t>
         </is>
       </c>
-      <c r="AY11" s="234" t="n">
+      <c r="AY11" s="179" t="n">
         <v>14</v>
       </c>
-      <c r="AZ11" s="234" t="n">
+      <c r="AZ11" s="179" t="n">
         <v>8</v>
       </c>
-      <c r="BA11" s="234" t="n">
+      <c r="BA11" s="179" t="n">
         <v>6</v>
       </c>
-      <c r="BB11" s="234" t="n">
+      <c r="BB11" s="179" t="n">
         <v>4</v>
       </c>
-      <c r="BC11" s="234" t="n">
+      <c r="BC11" s="179" t="n">
         <v>16</v>
       </c>
-      <c r="BD11" s="234" t="n">
+      <c r="BD11" s="179" t="n">
         <v>2</v>
       </c>
-      <c r="BE11" s="234" t="n">
+      <c r="BE11" s="179" t="n">
         <v>10</v>
       </c>
-      <c r="BF11" s="234" t="n">
+      <c r="BF11" s="179" t="n">
         <v>12</v>
       </c>
-      <c r="BG11" s="234" t="n">
+      <c r="BG11" s="179" t="n">
         <v>18</v>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1" s="181">
+    <row r="12" ht="15" customHeight="1" s="219">
       <c r="B12" s="138" t="inlineStr">
         <is>
           <t>GROSS</t>
@@ -3839,22 +3839,22 @@
         <v>7</v>
       </c>
       <c r="D12" s="147" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E12" s="148" t="n">
         <v>5</v>
       </c>
       <c r="F12" s="146" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G12" s="147" t="n">
         <v>6</v>
       </c>
       <c r="H12" s="148" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I12" s="146" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J12" s="147" t="n">
         <v>5</v>
@@ -3862,7 +3862,7 @@
       <c r="K12" s="148" t="n">
         <v>6</v>
       </c>
-      <c r="L12" s="234">
+      <c r="L12" s="179">
         <f>SUM(C12:K12)</f>
         <v/>
       </c>
@@ -3882,7 +3882,7 @@
         <f>Schedule!D18</f>
         <v/>
       </c>
-      <c r="T12" s="235" t="inlineStr">
+      <c r="T12" s="180" t="inlineStr">
         <is>
           <t>Par</t>
         </is>
@@ -3914,7 +3914,7 @@
       <c r="AC12" s="144" t="n">
         <v>4</v>
       </c>
-      <c r="AD12" s="235" t="inlineStr">
+      <c r="AD12" s="180" t="inlineStr">
         <is>
           <t>Par</t>
         </is>
@@ -3946,7 +3946,7 @@
       <c r="AM12" s="144" t="n">
         <v>5</v>
       </c>
-      <c r="AN12" s="235" t="inlineStr">
+      <c r="AN12" s="180" t="inlineStr">
         <is>
           <t>Par</t>
         </is>
@@ -3978,7 +3978,7 @@
       <c r="AW12" s="144" t="n">
         <v>4</v>
       </c>
-      <c r="AX12" s="235" t="inlineStr">
+      <c r="AX12" s="180" t="inlineStr">
         <is>
           <t>Par</t>
         </is>
@@ -4021,7 +4021,7 @@
         <f>INT($D$8/18)+IF(C11&lt;=MOD($D$8,18),1,0)</f>
         <v/>
       </c>
-      <c r="D13" s="234">
+      <c r="D13" s="179">
         <f>INT($D$8/18)+IF(D11&lt;=MOD($D$8,18),1,0)</f>
         <v/>
       </c>
@@ -4033,7 +4033,7 @@
         <f>INT($D$8/18)+IF(F11&lt;=MOD($D$8,18),1,0)</f>
         <v/>
       </c>
-      <c r="G13" s="234">
+      <c r="G13" s="179">
         <f>INT($D$8/18)+IF(G11&lt;=MOD($D$8,18),1,0)</f>
         <v/>
       </c>
@@ -4045,7 +4045,7 @@
         <f>INT($D$8/18)+IF(I11&lt;=MOD($D$8,18),1,0)</f>
         <v/>
       </c>
-      <c r="J13" s="234">
+      <c r="J13" s="179">
         <f>INT($D$8/18)+IF(J11&lt;=MOD($D$8,18),1,0)</f>
         <v/>
       </c>
@@ -4077,7 +4077,7 @@
         <f>C12-C13</f>
         <v/>
       </c>
-      <c r="D14" s="234">
+      <c r="D14" s="179">
         <f>D12-INT($D$8/18)-IF(D11&lt;=MOD($D$8,18),1,0)</f>
         <v/>
       </c>
@@ -4089,7 +4089,7 @@
         <f>F12-INT($D$8/18)-IF(F11&lt;=MOD($D$8,18),1,0)</f>
         <v/>
       </c>
-      <c r="G14" s="234">
+      <c r="G14" s="179">
         <f>G12-INT($D$8/18)-IF(G11&lt;=MOD($D$8,18),1,0)</f>
         <v/>
       </c>
@@ -4101,7 +4101,7 @@
         <f>I12-INT($D$8/18)-IF(I11&lt;=MOD($D$8,18),1,0)</f>
         <v/>
       </c>
-      <c r="J14" s="234">
+      <c r="J14" s="179">
         <f>J12-INT($D$8/18)-IF(J11&lt;=MOD($D$8,18),1,0)</f>
         <v/>
       </c>
@@ -4130,7 +4130,7 @@
         <v/>
       </c>
     </row>
-    <row r="15" ht="14.25" customHeight="1" s="181" thickBot="1">
+    <row r="15" ht="14.25" customHeight="1" s="219" thickBot="1">
       <c r="B15" s="140" t="inlineStr">
         <is>
           <t>Wins Hole</t>
@@ -4172,7 +4172,7 @@
         <f>IF(K14&lt;K23,1,0)</f>
         <v/>
       </c>
-      <c r="L15" s="234" t="n"/>
+      <c r="L15" s="179" t="n"/>
       <c r="O15" s="122">
         <f>O14+1</f>
         <v/>
@@ -4188,16 +4188,16 @@
       </c>
     </row>
     <row r="16">
-      <c r="C16" s="234" t="n"/>
-      <c r="D16" s="234" t="n"/>
-      <c r="E16" s="234" t="n"/>
-      <c r="F16" s="234" t="n"/>
-      <c r="G16" s="234" t="n"/>
-      <c r="H16" s="234" t="n"/>
-      <c r="I16" s="234" t="n"/>
-      <c r="J16" s="234" t="n"/>
-      <c r="K16" s="234" t="n"/>
-      <c r="L16" s="234" t="n"/>
+      <c r="C16" s="179" t="n"/>
+      <c r="D16" s="179" t="n"/>
+      <c r="E16" s="179" t="n"/>
+      <c r="F16" s="179" t="n"/>
+      <c r="G16" s="179" t="n"/>
+      <c r="H16" s="179" t="n"/>
+      <c r="I16" s="179" t="n"/>
+      <c r="J16" s="179" t="n"/>
+      <c r="K16" s="179" t="n"/>
+      <c r="L16" s="179" t="n"/>
       <c r="O16" s="122" t="n">
         <v>8</v>
       </c>
@@ -4211,7 +4211,7 @@
         <v/>
       </c>
     </row>
-    <row r="17" ht="16.5" customHeight="1" s="181" thickBot="1">
+    <row r="17" ht="16.5" customHeight="1" s="219" thickBot="1">
       <c r="B17" s="145" t="inlineStr">
         <is>
           <t>Charlotte Hayes</t>
@@ -4222,12 +4222,12 @@
           <t>Handicap:</t>
         </is>
       </c>
-      <c r="D17" s="234">
+      <c r="D17" s="179">
         <f>_xlfn.XLOOKUP(B17,$P$9:$P$23,$Q$9:$Q$23)</f>
         <v/>
       </c>
-      <c r="E17" s="234" t="n"/>
-      <c r="F17" s="234" t="inlineStr">
+      <c r="E17" s="179" t="n"/>
+      <c r="F17" s="179" t="inlineStr">
         <is>
           <t>Tees:</t>
         </is>
@@ -4237,18 +4237,18 @@
           <t>Blue</t>
         </is>
       </c>
-      <c r="H17" s="234" t="n"/>
-      <c r="I17" s="234" t="inlineStr">
+      <c r="H17" s="179" t="n"/>
+      <c r="I17" s="179" t="inlineStr">
         <is>
           <t>Holes:</t>
         </is>
       </c>
-      <c r="J17" s="234">
+      <c r="J17" s="179">
         <f>J8</f>
         <v/>
       </c>
-      <c r="K17" s="234" t="n"/>
-      <c r="L17" s="234" t="n"/>
+      <c r="K17" s="179" t="n"/>
+      <c r="L17" s="179" t="n"/>
       <c r="O17" s="122" t="n">
         <v>9</v>
       </c>
@@ -4262,7 +4262,7 @@
         <v/>
       </c>
     </row>
-    <row r="18" ht="15" customHeight="1" s="181">
+    <row r="18" ht="15" customHeight="1" s="219">
       <c r="B18" s="131" t="inlineStr">
         <is>
           <t>HOLE</t>
@@ -4295,7 +4295,7 @@
       <c r="K18" s="134" t="n">
         <v>9</v>
       </c>
-      <c r="L18" s="234" t="n"/>
+      <c r="L18" s="179" t="n"/>
       <c r="M18" s="139" t="n"/>
       <c r="O18" s="122" t="n">
         <v>10</v>
@@ -4316,7 +4316,7 @@
           <t>PAR</t>
         </is>
       </c>
-      <c r="C19" s="234">
+      <c r="C19" s="179">
         <f t="array" ref="C19">IF($B$2="Skybrook",
    _xlfn.IFS(
       $J17="Back 9",INDEX($AE$12:$AM$12,1,C18),
@@ -4329,7 +4329,7 @@
 )</f>
         <v/>
       </c>
-      <c r="D19" s="234">
+      <c r="D19" s="179">
         <f t="array" ref="D19">IF($B$2="Skybrook",
    _xlfn.IFS(
       $J17="Back 9",INDEX($AE$12:$AM$12,1,D18),
@@ -4368,7 +4368,7 @@
 )</f>
         <v/>
       </c>
-      <c r="G19" s="234">
+      <c r="G19" s="179">
         <f t="array" ref="G19">IF($B$2="Skybrook",
    _xlfn.IFS(
       $J17="Back 9",INDEX($AE$12:$AM$12,1,G18),
@@ -4407,7 +4407,7 @@
 )</f>
         <v/>
       </c>
-      <c r="J19" s="234">
+      <c r="J19" s="179">
         <f t="array" ref="J19">IF($B$2="Skybrook",
    _xlfn.IFS(
       $J17="Back 9",INDEX($AE$12:$AM$12,1,J18),
@@ -4433,7 +4433,7 @@
 )</f>
         <v/>
       </c>
-      <c r="L19" s="234">
+      <c r="L19" s="179">
         <f>SUM(C19:K19)</f>
         <v/>
       </c>
@@ -4457,7 +4457,7 @@
           <t>HC</t>
         </is>
       </c>
-      <c r="C20" s="234">
+      <c r="C20" s="179">
         <f t="array" ref="C20">IF($B$2="Skybrook",
    _xlfn.IFS(
       $J17="Back 9",VLOOKUP($G17,$AD$9:$AM$11,COLUMN()-1,0),
@@ -4470,7 +4470,7 @@
 )</f>
         <v/>
       </c>
-      <c r="D20" s="234">
+      <c r="D20" s="179">
         <f t="array" ref="D20">IF($B$2="Skybrook",
    _xlfn.IFS(
       $J17="Back 9",VLOOKUP($G17,$AD$9:$AM$11,COLUMN()-1,0),
@@ -4509,7 +4509,7 @@
 )</f>
         <v/>
       </c>
-      <c r="G20" s="234">
+      <c r="G20" s="179">
         <f t="array" ref="G20">IF($B$2="Skybrook",
    _xlfn.IFS(
       $J17="Back 9",VLOOKUP($G17,$AD$9:$AM$11,COLUMN()-1,0),
@@ -4548,7 +4548,7 @@
 )</f>
         <v/>
       </c>
-      <c r="J20" s="234">
+      <c r="J20" s="179">
         <f t="array" ref="J20">IF($B$2="Skybrook",
    _xlfn.IFS(
       $J17="Back 9",VLOOKUP($G17,$AD$9:$AM$11,COLUMN()-1,0),
@@ -4574,7 +4574,7 @@
 )</f>
         <v/>
       </c>
-      <c r="L20" s="234" t="n"/>
+      <c r="L20" s="179" t="n"/>
       <c r="O20" s="122" t="n">
         <v>12</v>
       </c>
@@ -4588,40 +4588,40 @@
         <v/>
       </c>
     </row>
-    <row r="21" ht="15" customHeight="1" s="181">
+    <row r="21" ht="15" customHeight="1" s="219">
       <c r="B21" s="138" t="inlineStr">
         <is>
           <t>GROSS</t>
         </is>
       </c>
       <c r="C21" s="146" t="n">
+        <v>8</v>
+      </c>
+      <c r="D21" s="147" t="n">
+        <v>8</v>
+      </c>
+      <c r="E21" s="148" t="n">
         <v>5</v>
       </c>
-      <c r="D21" s="147" t="n">
+      <c r="F21" s="146" t="n">
+        <v>8</v>
+      </c>
+      <c r="G21" s="147" t="n">
+        <v>8</v>
+      </c>
+      <c r="H21" s="148" t="n">
         <v>6</v>
       </c>
-      <c r="E21" s="148" t="n">
-        <v>4</v>
-      </c>
-      <c r="F21" s="146" t="n">
-        <v>6</v>
-      </c>
-      <c r="G21" s="147" t="n">
-        <v>4</v>
-      </c>
-      <c r="H21" s="148" t="n">
-        <v>5</v>
-      </c>
       <c r="I21" s="146" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="J21" s="147" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="K21" s="148" t="n">
-        <v>7</v>
-      </c>
-      <c r="L21" s="234">
+        <v>8</v>
+      </c>
+      <c r="L21" s="179">
         <f>SUM(C21:K21)</f>
         <v/>
       </c>
@@ -4652,7 +4652,7 @@
         <f>INT($D$17/18)+IF(C20&lt;=MOD($D$17,18),1,0)</f>
         <v/>
       </c>
-      <c r="D22" s="234">
+      <c r="D22" s="179">
         <f>INT($D$17/18)+IF(D20&lt;=MOD($D$17,18),1,0)</f>
         <v/>
       </c>
@@ -4664,7 +4664,7 @@
         <f>INT($D$17/18)+IF(F20&lt;=MOD($D$17,18),1,0)</f>
         <v/>
       </c>
-      <c r="G22" s="234">
+      <c r="G22" s="179">
         <f>INT($D$17/18)+IF(G20&lt;=MOD($D$17,18),1,0)</f>
         <v/>
       </c>
@@ -4676,7 +4676,7 @@
         <f>INT($D$17/18)+IF(I20&lt;=MOD($D$17,18),1,0)</f>
         <v/>
       </c>
-      <c r="J22" s="234">
+      <c r="J22" s="179">
         <f>INT($D$17/18)+IF(J20&lt;=MOD($D$17,18),1,0)</f>
         <v/>
       </c>
@@ -4708,7 +4708,7 @@
         <f>C21-C22</f>
         <v/>
       </c>
-      <c r="D23" s="234">
+      <c r="D23" s="179">
         <f>D21-D22</f>
         <v/>
       </c>
@@ -4720,7 +4720,7 @@
         <f>F21-F22</f>
         <v/>
       </c>
-      <c r="G23" s="234">
+      <c r="G23" s="179">
         <f>G21-G22</f>
         <v/>
       </c>
@@ -4732,7 +4732,7 @@
         <f>I21-I22</f>
         <v/>
       </c>
-      <c r="J23" s="234">
+      <c r="J23" s="179">
         <f>J21-J22</f>
         <v/>
       </c>
@@ -4761,7 +4761,7 @@
         <v/>
       </c>
     </row>
-    <row r="24" ht="14.25" customHeight="1" s="181" thickBot="1">
+    <row r="24" ht="14.25" customHeight="1" s="219" thickBot="1">
       <c r="B24" s="140" t="inlineStr">
         <is>
           <t>Wins Hole</t>
@@ -4803,7 +4803,7 @@
         <f>IF(K23&lt;K14,1,0)</f>
         <v/>
       </c>
-      <c r="L24" s="234" t="n"/>
+      <c r="L24" s="179" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="13">
@@ -4853,8 +4853,8 @@
   <dimension ref="C2:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="12.75"/>
   <cols>
-    <col width="8.85546875" bestFit="1" customWidth="1" style="181" min="3" max="3"/>
-    <col width="14.140625" bestFit="1" customWidth="1" style="181" min="4" max="4"/>
+    <col width="8.85546875" bestFit="1" customWidth="1" style="219" min="3" max="3"/>
+    <col width="14.140625" bestFit="1" customWidth="1" style="219" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="2">
@@ -4919,41 +4919,41 @@
   <dimension ref="A1:M15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="12.75"/>
   <cols>
-    <col width="18" bestFit="1" customWidth="1" style="181" min="1" max="1"/>
-    <col width="28" bestFit="1" customWidth="1" style="180" min="2" max="2"/>
-    <col width="28.5703125" bestFit="1" customWidth="1" style="181" min="3" max="3"/>
-    <col width="31.7109375" bestFit="1" customWidth="1" style="181" min="4" max="4"/>
-    <col width="29.42578125" bestFit="1" customWidth="1" style="181" min="5" max="5"/>
-    <col width="26.42578125" bestFit="1" customWidth="1" style="181" min="6" max="6"/>
-    <col width="28.85546875" bestFit="1" customWidth="1" style="181" min="7" max="7"/>
-    <col width="27.7109375" bestFit="1" customWidth="1" style="181" min="8" max="8"/>
-    <col width="28" bestFit="1" customWidth="1" style="181" min="9" max="9"/>
-    <col width="28.5703125" bestFit="1" customWidth="1" style="181" min="10" max="10"/>
-    <col width="31.7109375" bestFit="1" customWidth="1" style="181" min="11" max="11"/>
-    <col width="29.42578125" bestFit="1" customWidth="1" style="181" min="12" max="12"/>
-    <col width="26.42578125" bestFit="1" customWidth="1" style="181" min="13" max="13"/>
+    <col width="18" bestFit="1" customWidth="1" style="219" min="1" max="1"/>
+    <col width="28" bestFit="1" customWidth="1" style="188" min="2" max="2"/>
+    <col width="28.5703125" bestFit="1" customWidth="1" style="219" min="3" max="3"/>
+    <col width="31.7109375" bestFit="1" customWidth="1" style="219" min="4" max="4"/>
+    <col width="29.42578125" bestFit="1" customWidth="1" style="219" min="5" max="5"/>
+    <col width="26.42578125" bestFit="1" customWidth="1" style="219" min="6" max="6"/>
+    <col width="28.85546875" bestFit="1" customWidth="1" style="219" min="7" max="7"/>
+    <col width="27.7109375" bestFit="1" customWidth="1" style="219" min="8" max="8"/>
+    <col width="28" bestFit="1" customWidth="1" style="219" min="9" max="9"/>
+    <col width="28.5703125" bestFit="1" customWidth="1" style="219" min="10" max="10"/>
+    <col width="31.7109375" bestFit="1" customWidth="1" style="219" min="11" max="11"/>
+    <col width="29.42578125" bestFit="1" customWidth="1" style="219" min="12" max="12"/>
+    <col width="26.42578125" bestFit="1" customWidth="1" style="219" min="13" max="13"/>
   </cols>
   <sheetData>
-    <row r="1" ht="23.25" customHeight="1" s="181">
-      <c r="A1" s="182" t="inlineStr">
+    <row r="1" ht="23.25" customHeight="1" s="219">
+      <c r="A1" s="186" t="inlineStr">
         <is>
           <t>2024 Bechtel Golf League Schedule Tee Time</t>
         </is>
       </c>
-      <c r="B1" s="179" t="n"/>
-      <c r="C1" s="179" t="n"/>
-      <c r="D1" s="179" t="n"/>
-      <c r="E1" s="179" t="n"/>
-      <c r="F1" s="179" t="n"/>
-      <c r="G1" s="179" t="n"/>
-      <c r="H1" s="179" t="n"/>
-      <c r="I1" s="179" t="n"/>
-      <c r="J1" s="179" t="n"/>
-      <c r="K1" s="179" t="n"/>
-      <c r="L1" s="179" t="n"/>
-      <c r="M1" s="179" t="n"/>
-    </row>
-    <row r="2" ht="30" customFormat="1" customHeight="1" s="217">
+      <c r="B1" s="218" t="n"/>
+      <c r="C1" s="218" t="n"/>
+      <c r="D1" s="218" t="n"/>
+      <c r="E1" s="218" t="n"/>
+      <c r="F1" s="218" t="n"/>
+      <c r="G1" s="218" t="n"/>
+      <c r="H1" s="218" t="n"/>
+      <c r="I1" s="218" t="n"/>
+      <c r="J1" s="218" t="n"/>
+      <c r="K1" s="218" t="n"/>
+      <c r="L1" s="218" t="n"/>
+      <c r="M1" s="218" t="n"/>
+    </row>
+    <row r="2" ht="30" customFormat="1" customHeight="1" s="206">
       <c r="A2" s="10" t="inlineStr">
         <is>
           <t>TEE TIME</t>
@@ -4996,7 +4996,7 @@
         <v>45562</v>
       </c>
     </row>
-    <row r="3" ht="30" customHeight="1" s="181">
+    <row r="3" ht="30" customHeight="1" s="219">
       <c r="A3" s="8" t="n">
         <v>0.6666666666666666</v>
       </c>
@@ -5013,7 +5013,7 @@
       <c r="L3" s="9" t="n"/>
       <c r="M3" s="9" t="n"/>
     </row>
-    <row r="4" ht="30" customHeight="1" s="181">
+    <row r="4" ht="30" customHeight="1" s="219">
       <c r="A4" s="8" t="n">
         <v>0.6736111111111112</v>
       </c>
@@ -5030,7 +5030,7 @@
       <c r="L4" s="9" t="n"/>
       <c r="M4" s="9" t="n"/>
     </row>
-    <row r="5" ht="30" customHeight="1" s="181">
+    <row r="5" ht="30" customHeight="1" s="219">
       <c r="A5" s="8" t="n">
         <v>0.6805555555555556</v>
       </c>
@@ -5055,7 +5055,7 @@
       <c r="L5" s="9" t="n"/>
       <c r="M5" s="9" t="n"/>
     </row>
-    <row r="6" ht="30" customHeight="1" s="181">
+    <row r="6" ht="30" customHeight="1" s="219">
       <c r="A6" s="8" t="n">
         <v>0.6875</v>
       </c>
@@ -5076,7 +5076,7 @@
       <c r="L6" s="9" t="n"/>
       <c r="M6" s="9" t="n"/>
     </row>
-    <row r="7" ht="30" customHeight="1" s="181">
+    <row r="7" ht="30" customHeight="1" s="219">
       <c r="A7" s="8" t="n">
         <v>0.6944444444444444</v>
       </c>
@@ -5093,7 +5093,7 @@
       <c r="L7" s="9" t="n"/>
       <c r="M7" s="9" t="n"/>
     </row>
-    <row r="8" ht="30" customHeight="1" s="181">
+    <row r="8" ht="30" customHeight="1" s="219">
       <c r="A8" s="8" t="n">
         <v>0.7013888888888888</v>
       </c>
@@ -5110,7 +5110,7 @@
       <c r="L8" s="9" t="n"/>
       <c r="M8" s="9" t="n"/>
     </row>
-    <row r="9" ht="30" customHeight="1" s="181">
+    <row r="9" ht="30" customHeight="1" s="219">
       <c r="A9" s="8" t="n">
         <v>0.7083333333333334</v>
       </c>
@@ -5127,7 +5127,7 @@
       <c r="L9" s="9" t="n"/>
       <c r="M9" s="9" t="n"/>
     </row>
-    <row r="10" ht="30" customHeight="1" s="181">
+    <row r="10" ht="30" customHeight="1" s="219">
       <c r="A10" s="8" t="n">
         <v>0.7152777777777778</v>
       </c>
@@ -5144,7 +5144,7 @@
       <c r="L10" s="9" t="n"/>
       <c r="M10" s="9" t="n"/>
     </row>
-    <row r="11" ht="30" customHeight="1" s="181">
+    <row r="11" ht="30" customHeight="1" s="219">
       <c r="A11" s="8" t="n">
         <v>0.7222222222222222</v>
       </c>
@@ -5161,7 +5161,7 @@
       <c r="L11" s="9" t="n"/>
       <c r="M11" s="9" t="n"/>
     </row>
-    <row r="12" ht="30" customHeight="1" s="181">
+    <row r="12" ht="30" customHeight="1" s="219">
       <c r="A12" s="8" t="n">
         <v>0.7291666666666666</v>
       </c>
@@ -5178,7 +5178,7 @@
       <c r="L12" s="9" t="n"/>
       <c r="M12" s="9" t="n"/>
     </row>
-    <row r="13" ht="30" customHeight="1" s="181">
+    <row r="13" ht="30" customHeight="1" s="219">
       <c r="A13" s="8" t="n">
         <v>0.7361111111111112</v>
       </c>
@@ -5195,7 +5195,7 @@
       <c r="L13" s="9" t="n"/>
       <c r="M13" s="9" t="n"/>
     </row>
-    <row r="14" ht="30" customHeight="1" s="181">
+    <row r="14" ht="30" customHeight="1" s="219">
       <c r="A14" s="8" t="n">
         <v>0.7430555555555556</v>
       </c>
@@ -5212,7 +5212,7 @@
       <c r="L14" s="9" t="n"/>
       <c r="M14" s="9" t="n"/>
     </row>
-    <row r="15" ht="30" customHeight="1" s="181">
+    <row r="15" ht="30" customHeight="1" s="219">
       <c r="A15" s="8" t="n">
         <v>0.75</v>
       </c>
@@ -5246,41 +5246,41 @@
   <dimension ref="A1:M16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="12.75"/>
   <cols>
-    <col width="24.5703125" bestFit="1" customWidth="1" style="181" min="1" max="1"/>
-    <col width="26.28515625" bestFit="1" customWidth="1" style="180" min="2" max="2"/>
-    <col width="27.140625" bestFit="1" customWidth="1" style="181" min="3" max="3"/>
-    <col width="30" bestFit="1" customWidth="1" style="181" min="4" max="4"/>
-    <col width="27.85546875" bestFit="1" customWidth="1" style="181" min="5" max="5"/>
-    <col width="24.85546875" bestFit="1" customWidth="1" style="181" min="6" max="6"/>
-    <col hidden="1" width="26.28515625" customWidth="1" style="181" min="7" max="7"/>
-    <col hidden="1" width="24.85546875" customWidth="1" style="181" min="8" max="8"/>
-    <col width="26.28515625" bestFit="1" customWidth="1" style="181" min="9" max="9"/>
-    <col width="27.140625" bestFit="1" customWidth="1" style="181" min="10" max="10"/>
-    <col width="30" bestFit="1" customWidth="1" style="181" min="11" max="11"/>
-    <col width="27.85546875" bestFit="1" customWidth="1" style="181" min="12" max="12"/>
-    <col width="24.85546875" bestFit="1" customWidth="1" style="181" min="13" max="13"/>
+    <col width="24.5703125" bestFit="1" customWidth="1" style="219" min="1" max="1"/>
+    <col width="26.28515625" bestFit="1" customWidth="1" style="188" min="2" max="2"/>
+    <col width="27.140625" bestFit="1" customWidth="1" style="219" min="3" max="3"/>
+    <col width="30" bestFit="1" customWidth="1" style="219" min="4" max="4"/>
+    <col width="27.85546875" bestFit="1" customWidth="1" style="219" min="5" max="5"/>
+    <col width="24.85546875" bestFit="1" customWidth="1" style="219" min="6" max="6"/>
+    <col hidden="1" width="26.28515625" customWidth="1" style="219" min="7" max="7"/>
+    <col hidden="1" width="24.85546875" customWidth="1" style="219" min="8" max="8"/>
+    <col width="26.28515625" bestFit="1" customWidth="1" style="219" min="9" max="9"/>
+    <col width="27.140625" bestFit="1" customWidth="1" style="219" min="10" max="10"/>
+    <col width="30" bestFit="1" customWidth="1" style="219" min="11" max="11"/>
+    <col width="27.85546875" bestFit="1" customWidth="1" style="219" min="12" max="12"/>
+    <col width="24.85546875" bestFit="1" customWidth="1" style="219" min="13" max="13"/>
   </cols>
   <sheetData>
-    <row r="1" ht="23.25" customHeight="1" s="181">
-      <c r="A1" s="182" t="inlineStr">
+    <row r="1" ht="23.25" customHeight="1" s="219">
+      <c r="A1" s="186" t="inlineStr">
         <is>
           <t>2024 Bechtel Golf League Schedule Tee Time</t>
         </is>
       </c>
-      <c r="B1" s="179" t="n"/>
-      <c r="C1" s="179" t="n"/>
-      <c r="D1" s="179" t="n"/>
-      <c r="E1" s="179" t="n"/>
-      <c r="F1" s="179" t="n"/>
-      <c r="G1" s="179" t="n"/>
-      <c r="H1" s="179" t="n"/>
-      <c r="I1" s="179" t="n"/>
-      <c r="J1" s="179" t="n"/>
-      <c r="K1" s="179" t="n"/>
-      <c r="L1" s="179" t="n"/>
-      <c r="M1" s="179" t="n"/>
-    </row>
-    <row r="2" ht="30" customFormat="1" customHeight="1" s="217">
+      <c r="B1" s="218" t="n"/>
+      <c r="C1" s="218" t="n"/>
+      <c r="D1" s="218" t="n"/>
+      <c r="E1" s="218" t="n"/>
+      <c r="F1" s="218" t="n"/>
+      <c r="G1" s="218" t="n"/>
+      <c r="H1" s="218" t="n"/>
+      <c r="I1" s="218" t="n"/>
+      <c r="J1" s="218" t="n"/>
+      <c r="K1" s="218" t="n"/>
+      <c r="L1" s="218" t="n"/>
+      <c r="M1" s="218" t="n"/>
+    </row>
+    <row r="2" ht="30" customFormat="1" customHeight="1" s="206">
       <c r="A2" s="10" t="inlineStr">
         <is>
           <t>TEE TIME</t>
@@ -5323,7 +5323,7 @@
         <v>45576</v>
       </c>
     </row>
-    <row r="3" ht="30" customHeight="1" s="181">
+    <row r="3" ht="30" customHeight="1" s="219">
       <c r="A3" s="8" t="n">
         <v>0.6597222222222222</v>
       </c>
@@ -5344,7 +5344,7 @@
       </c>
       <c r="M3" s="9" t="n"/>
     </row>
-    <row r="4" ht="30" customHeight="1" s="181">
+    <row r="4" ht="30" customHeight="1" s="219">
       <c r="A4" s="8" t="n">
         <v>0.6666666666666666</v>
       </c>
@@ -5361,7 +5361,7 @@
       <c r="L4" s="9" t="n"/>
       <c r="M4" s="9" t="n"/>
     </row>
-    <row r="5" ht="30" customHeight="1" s="181">
+    <row r="5" ht="30" customHeight="1" s="219">
       <c r="A5" s="8" t="n">
         <v>0.6736111111111112</v>
       </c>
@@ -5378,7 +5378,7 @@
       <c r="L5" s="9" t="n"/>
       <c r="M5" s="9" t="n"/>
     </row>
-    <row r="6" ht="30" customHeight="1" s="181">
+    <row r="6" ht="30" customHeight="1" s="219">
       <c r="A6" s="8" t="n">
         <v>0.6805555555555556</v>
       </c>
@@ -5395,7 +5395,7 @@
       <c r="L6" s="9" t="n"/>
       <c r="M6" s="9" t="n"/>
     </row>
-    <row r="7" ht="30" customHeight="1" s="181">
+    <row r="7" ht="30" customHeight="1" s="219">
       <c r="A7" s="8" t="n">
         <v>0.6875</v>
       </c>
@@ -5412,7 +5412,7 @@
       <c r="L7" s="9" t="n"/>
       <c r="M7" s="9" t="n"/>
     </row>
-    <row r="8" ht="30" customHeight="1" s="181">
+    <row r="8" ht="30" customHeight="1" s="219">
       <c r="A8" s="8" t="n">
         <v>0.6944444444444444</v>
       </c>
@@ -5429,7 +5429,7 @@
       <c r="L8" s="9" t="n"/>
       <c r="M8" s="9" t="n"/>
     </row>
-    <row r="9" ht="30" customHeight="1" s="181">
+    <row r="9" ht="30" customHeight="1" s="219">
       <c r="A9" s="8" t="n">
         <v>0.7013888888888888</v>
       </c>
@@ -5446,7 +5446,7 @@
       <c r="L9" s="9" t="n"/>
       <c r="M9" s="9" t="n"/>
     </row>
-    <row r="10" ht="30" customHeight="1" s="181">
+    <row r="10" ht="30" customHeight="1" s="219">
       <c r="A10" s="8" t="n">
         <v>0.7083333333333334</v>
       </c>
@@ -5463,7 +5463,7 @@
       <c r="L10" s="9" t="n"/>
       <c r="M10" s="9" t="n"/>
     </row>
-    <row r="11" ht="30" customHeight="1" s="181">
+    <row r="11" ht="30" customHeight="1" s="219">
       <c r="A11" s="8" t="n">
         <v>0.7152777777777778</v>
       </c>
@@ -5480,7 +5480,7 @@
       <c r="L11" s="9" t="n"/>
       <c r="M11" s="9" t="n"/>
     </row>
-    <row r="12" ht="30" customHeight="1" s="181">
+    <row r="12" ht="30" customHeight="1" s="219">
       <c r="A12" s="8" t="n">
         <v>0.7222222222222222</v>
       </c>
@@ -5497,7 +5497,7 @@
       <c r="L12" s="9" t="n"/>
       <c r="M12" s="9" t="n"/>
     </row>
-    <row r="13" ht="30" customHeight="1" s="181">
+    <row r="13" ht="30" customHeight="1" s="219">
       <c r="A13" s="8" t="n">
         <v>0.7291666666666666</v>
       </c>
@@ -5514,7 +5514,7 @@
       <c r="L13" s="9" t="n"/>
       <c r="M13" s="9" t="n"/>
     </row>
-    <row r="14" ht="30" customHeight="1" s="181">
+    <row r="14" ht="30" customHeight="1" s="219">
       <c r="A14" s="8" t="n">
         <v>0.7361111111111112</v>
       </c>
@@ -5531,7 +5531,7 @@
       <c r="L14" s="9" t="n"/>
       <c r="M14" s="9" t="n"/>
     </row>
-    <row r="15" ht="30" customHeight="1" s="181">
+    <row r="15" ht="30" customHeight="1" s="219">
       <c r="A15" s="8" t="n">
         <v>0.7430555555555556</v>
       </c>
@@ -5548,7 +5548,7 @@
       <c r="L15" s="9" t="n"/>
       <c r="M15" s="9" t="n"/>
     </row>
-    <row r="16" ht="30" customHeight="1" s="181">
+    <row r="16" ht="30" customHeight="1" s="219">
       <c r="A16" s="8" t="n">
         <v>0.75</v>
       </c>
@@ -5582,41 +5582,41 @@
   <dimension ref="A1:M16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="12.75"/>
   <cols>
-    <col width="24.5703125" bestFit="1" customWidth="1" style="181" min="1" max="1"/>
-    <col width="26.28515625" bestFit="1" customWidth="1" style="180" min="2" max="2"/>
-    <col width="27.140625" bestFit="1" customWidth="1" style="181" min="3" max="3"/>
-    <col width="30" bestFit="1" customWidth="1" style="181" min="4" max="4"/>
-    <col width="27.85546875" bestFit="1" customWidth="1" style="181" min="5" max="5"/>
-    <col width="24.85546875" bestFit="1" customWidth="1" style="181" min="6" max="6"/>
-    <col hidden="1" width="26.28515625" customWidth="1" style="181" min="7" max="7"/>
-    <col hidden="1" width="24.85546875" customWidth="1" style="181" min="8" max="8"/>
-    <col width="26.28515625" bestFit="1" customWidth="1" style="181" min="9" max="9"/>
-    <col width="27.140625" bestFit="1" customWidth="1" style="181" min="10" max="10"/>
-    <col width="30" bestFit="1" customWidth="1" style="181" min="11" max="11"/>
-    <col width="27.85546875" customWidth="1" style="181" min="12" max="12"/>
-    <col width="24.85546875" bestFit="1" customWidth="1" style="181" min="13" max="13"/>
+    <col width="24.5703125" bestFit="1" customWidth="1" style="219" min="1" max="1"/>
+    <col width="26.28515625" bestFit="1" customWidth="1" style="188" min="2" max="2"/>
+    <col width="27.140625" bestFit="1" customWidth="1" style="219" min="3" max="3"/>
+    <col width="30" bestFit="1" customWidth="1" style="219" min="4" max="4"/>
+    <col width="27.85546875" bestFit="1" customWidth="1" style="219" min="5" max="5"/>
+    <col width="24.85546875" bestFit="1" customWidth="1" style="219" min="6" max="6"/>
+    <col hidden="1" width="26.28515625" customWidth="1" style="219" min="7" max="7"/>
+    <col hidden="1" width="24.85546875" customWidth="1" style="219" min="8" max="8"/>
+    <col width="26.28515625" bestFit="1" customWidth="1" style="219" min="9" max="9"/>
+    <col width="27.140625" bestFit="1" customWidth="1" style="219" min="10" max="10"/>
+    <col width="30" bestFit="1" customWidth="1" style="219" min="11" max="11"/>
+    <col width="27.85546875" customWidth="1" style="219" min="12" max="12"/>
+    <col width="24.85546875" bestFit="1" customWidth="1" style="219" min="13" max="13"/>
   </cols>
   <sheetData>
-    <row r="1" ht="23.25" customHeight="1" s="181">
-      <c r="A1" s="182" t="inlineStr">
+    <row r="1" ht="23.25" customHeight="1" s="219">
+      <c r="A1" s="186" t="inlineStr">
         <is>
           <t>2024 Bechtel Golf League Schedule Tee Time</t>
         </is>
       </c>
-      <c r="B1" s="179" t="n"/>
-      <c r="C1" s="179" t="n"/>
-      <c r="D1" s="179" t="n"/>
-      <c r="E1" s="179" t="n"/>
-      <c r="F1" s="179" t="n"/>
-      <c r="G1" s="179" t="n"/>
-      <c r="H1" s="179" t="n"/>
-      <c r="I1" s="179" t="n"/>
-      <c r="J1" s="179" t="n"/>
-      <c r="K1" s="179" t="n"/>
-      <c r="L1" s="179" t="n"/>
-      <c r="M1" s="179" t="n"/>
-    </row>
-    <row r="2" ht="30" customFormat="1" customHeight="1" s="217">
+      <c r="B1" s="218" t="n"/>
+      <c r="C1" s="218" t="n"/>
+      <c r="D1" s="218" t="n"/>
+      <c r="E1" s="218" t="n"/>
+      <c r="F1" s="218" t="n"/>
+      <c r="G1" s="218" t="n"/>
+      <c r="H1" s="218" t="n"/>
+      <c r="I1" s="218" t="n"/>
+      <c r="J1" s="218" t="n"/>
+      <c r="K1" s="218" t="n"/>
+      <c r="L1" s="218" t="n"/>
+      <c r="M1" s="218" t="n"/>
+    </row>
+    <row r="2" ht="30" customFormat="1" customHeight="1" s="206">
       <c r="A2" s="10" t="inlineStr">
         <is>
           <t>TEE TIME</t>
@@ -5659,7 +5659,7 @@
         <v>45590</v>
       </c>
     </row>
-    <row r="3" ht="30" customFormat="1" customHeight="1" s="217">
+    <row r="3" ht="30" customFormat="1" customHeight="1" s="206">
       <c r="A3" s="8" t="n">
         <v>0.6597222222222222</v>
       </c>
@@ -5688,7 +5688,7 @@
       <c r="L3" s="30" t="n"/>
       <c r="M3" s="30" t="n"/>
     </row>
-    <row r="4" ht="30" customHeight="1" s="181">
+    <row r="4" ht="30" customHeight="1" s="219">
       <c r="A4" s="8" t="n">
         <v>0.6666666666666666</v>
       </c>
@@ -5705,7 +5705,7 @@
       <c r="L4" s="9" t="n"/>
       <c r="M4" s="9" t="n"/>
     </row>
-    <row r="5" ht="30" customHeight="1" s="181">
+    <row r="5" ht="30" customHeight="1" s="219">
       <c r="A5" s="8" t="n">
         <v>0.6736111111111112</v>
       </c>
@@ -5722,7 +5722,7 @@
       <c r="L5" s="9" t="n"/>
       <c r="M5" s="9" t="n"/>
     </row>
-    <row r="6" ht="30" customHeight="1" s="181">
+    <row r="6" ht="30" customHeight="1" s="219">
       <c r="A6" s="8" t="n">
         <v>0.6805555555555556</v>
       </c>
@@ -5739,7 +5739,7 @@
       <c r="L6" s="9" t="n"/>
       <c r="M6" s="9" t="n"/>
     </row>
-    <row r="7" ht="30" customHeight="1" s="181">
+    <row r="7" ht="30" customHeight="1" s="219">
       <c r="A7" s="8" t="n">
         <v>0.6875</v>
       </c>
@@ -5756,7 +5756,7 @@
       <c r="L7" s="9" t="n"/>
       <c r="M7" s="9" t="n"/>
     </row>
-    <row r="8" ht="30" customHeight="1" s="181">
+    <row r="8" ht="30" customHeight="1" s="219">
       <c r="A8" s="8" t="n">
         <v>0.6944444444444444</v>
       </c>
@@ -5773,7 +5773,7 @@
       <c r="L8" s="9" t="n"/>
       <c r="M8" s="9" t="n"/>
     </row>
-    <row r="9" ht="30" customHeight="1" s="181">
+    <row r="9" ht="30" customHeight="1" s="219">
       <c r="A9" s="8" t="n">
         <v>0.7013888888888888</v>
       </c>
@@ -5790,7 +5790,7 @@
       <c r="L9" s="9" t="n"/>
       <c r="M9" s="9" t="n"/>
     </row>
-    <row r="10" ht="30" customHeight="1" s="181">
+    <row r="10" ht="30" customHeight="1" s="219">
       <c r="A10" s="8" t="n">
         <v>0.7083333333333334</v>
       </c>
@@ -5807,7 +5807,7 @@
       <c r="L10" s="9" t="n"/>
       <c r="M10" s="9" t="n"/>
     </row>
-    <row r="11" ht="30" customHeight="1" s="181">
+    <row r="11" ht="30" customHeight="1" s="219">
       <c r="A11" s="8" t="n">
         <v>0.7152777777777778</v>
       </c>
@@ -5824,7 +5824,7 @@
       <c r="L11" s="9" t="n"/>
       <c r="M11" s="9" t="n"/>
     </row>
-    <row r="12" ht="30" customHeight="1" s="181">
+    <row r="12" ht="30" customHeight="1" s="219">
       <c r="A12" s="8" t="n">
         <v>0.7222222222222222</v>
       </c>
@@ -5841,7 +5841,7 @@
       <c r="L12" s="9" t="n"/>
       <c r="M12" s="9" t="n"/>
     </row>
-    <row r="13" ht="30" customHeight="1" s="181">
+    <row r="13" ht="30" customHeight="1" s="219">
       <c r="A13" s="8" t="n">
         <v>0.7291666666666666</v>
       </c>
@@ -5858,7 +5858,7 @@
       <c r="L13" s="9" t="n"/>
       <c r="M13" s="9" t="n"/>
     </row>
-    <row r="14" ht="30" customHeight="1" s="181">
+    <row r="14" ht="30" customHeight="1" s="219">
       <c r="A14" s="8" t="n">
         <v>0.7361111111111112</v>
       </c>
@@ -5875,7 +5875,7 @@
       <c r="L14" s="9" t="n"/>
       <c r="M14" s="9" t="n"/>
     </row>
-    <row r="15" ht="30" customHeight="1" s="181">
+    <row r="15" ht="30" customHeight="1" s="219">
       <c r="A15" s="8" t="n">
         <v>0.7430555555555556</v>
       </c>
@@ -5892,7 +5892,7 @@
       <c r="L15" s="9" t="n"/>
       <c r="M15" s="9" t="n"/>
     </row>
-    <row r="16" ht="30" customHeight="1" s="181">
+    <row r="16" ht="30" customHeight="1" s="219">
       <c r="A16" s="8" t="n">
         <v>0.75</v>
       </c>
@@ -5926,41 +5926,41 @@
   <dimension ref="A1:M15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="12.75"/>
   <cols>
-    <col width="18" bestFit="1" customWidth="1" style="181" min="1" max="1"/>
-    <col width="27" bestFit="1" customWidth="1" style="180" min="2" max="2"/>
-    <col width="27.7109375" bestFit="1" customWidth="1" style="181" min="3" max="3"/>
-    <col width="30.7109375" bestFit="1" customWidth="1" style="181" min="4" max="4"/>
-    <col width="28.5703125" bestFit="1" customWidth="1" style="181" min="5" max="5"/>
-    <col width="25.140625" bestFit="1" customWidth="1" style="181" min="6" max="6"/>
-    <col width="27.85546875" bestFit="1" customWidth="1" style="181" min="7" max="7"/>
-    <col width="26.5703125" bestFit="1" customWidth="1" style="181" min="8" max="8"/>
-    <col width="27" bestFit="1" customWidth="1" style="181" min="9" max="9"/>
-    <col width="28.7109375" bestFit="1" customWidth="1" style="181" min="10" max="10"/>
-    <col width="31.7109375" bestFit="1" customWidth="1" style="181" min="11" max="11"/>
-    <col width="29.5703125" bestFit="1" customWidth="1" style="181" min="12" max="12"/>
-    <col width="26.42578125" bestFit="1" customWidth="1" style="181" min="13" max="13"/>
+    <col width="18" bestFit="1" customWidth="1" style="219" min="1" max="1"/>
+    <col width="27" bestFit="1" customWidth="1" style="188" min="2" max="2"/>
+    <col width="27.7109375" bestFit="1" customWidth="1" style="219" min="3" max="3"/>
+    <col width="30.7109375" bestFit="1" customWidth="1" style="219" min="4" max="4"/>
+    <col width="28.5703125" bestFit="1" customWidth="1" style="219" min="5" max="5"/>
+    <col width="25.140625" bestFit="1" customWidth="1" style="219" min="6" max="6"/>
+    <col width="27.85546875" bestFit="1" customWidth="1" style="219" min="7" max="7"/>
+    <col width="26.5703125" bestFit="1" customWidth="1" style="219" min="8" max="8"/>
+    <col width="27" bestFit="1" customWidth="1" style="219" min="9" max="9"/>
+    <col width="28.7109375" bestFit="1" customWidth="1" style="219" min="10" max="10"/>
+    <col width="31.7109375" bestFit="1" customWidth="1" style="219" min="11" max="11"/>
+    <col width="29.5703125" bestFit="1" customWidth="1" style="219" min="12" max="12"/>
+    <col width="26.42578125" bestFit="1" customWidth="1" style="219" min="13" max="13"/>
   </cols>
   <sheetData>
-    <row r="1" ht="23.25" customHeight="1" s="181">
-      <c r="A1" s="182" t="inlineStr">
+    <row r="1" ht="23.25" customHeight="1" s="219">
+      <c r="A1" s="186" t="inlineStr">
         <is>
           <t>2024 Bechtel Golf League Schedule Tee Time</t>
         </is>
       </c>
-      <c r="B1" s="179" t="n"/>
-      <c r="C1" s="179" t="n"/>
-      <c r="D1" s="179" t="n"/>
-      <c r="E1" s="179" t="n"/>
-      <c r="F1" s="179" t="n"/>
-      <c r="G1" s="179" t="n"/>
-      <c r="H1" s="179" t="n"/>
-      <c r="I1" s="179" t="n"/>
-      <c r="J1" s="179" t="n"/>
-      <c r="K1" s="179" t="n"/>
-      <c r="L1" s="179" t="n"/>
-      <c r="M1" s="179" t="n"/>
-    </row>
-    <row r="2" ht="30" customFormat="1" customHeight="1" s="217">
+      <c r="B1" s="218" t="n"/>
+      <c r="C1" s="218" t="n"/>
+      <c r="D1" s="218" t="n"/>
+      <c r="E1" s="218" t="n"/>
+      <c r="F1" s="218" t="n"/>
+      <c r="G1" s="218" t="n"/>
+      <c r="H1" s="218" t="n"/>
+      <c r="I1" s="218" t="n"/>
+      <c r="J1" s="218" t="n"/>
+      <c r="K1" s="218" t="n"/>
+      <c r="L1" s="218" t="n"/>
+      <c r="M1" s="218" t="n"/>
+    </row>
+    <row r="2" ht="30" customFormat="1" customHeight="1" s="206">
       <c r="A2" s="10" t="inlineStr">
         <is>
           <t>TEE TIME</t>
@@ -6003,7 +6003,7 @@
         <v>45548</v>
       </c>
     </row>
-    <row r="3" ht="15" customHeight="1" s="181">
+    <row r="3" ht="15" customHeight="1" s="219">
       <c r="A3" s="8" t="n">
         <v>0.6666666666666666</v>
       </c>
@@ -6024,7 +6024,7 @@
       <c r="L3" s="9" t="n"/>
       <c r="M3" s="9" t="n"/>
     </row>
-    <row r="4" ht="15" customHeight="1" s="181">
+    <row r="4" ht="15" customHeight="1" s="219">
       <c r="A4" s="8" t="n">
         <v>0.6736111111111112</v>
       </c>
@@ -6041,7 +6041,7 @@
       <c r="L4" s="9" t="n"/>
       <c r="M4" s="9" t="n"/>
     </row>
-    <row r="5" ht="30" customHeight="1" s="181">
+    <row r="5" ht="30" customHeight="1" s="219">
       <c r="A5" s="8" t="n">
         <v>0.6805555555555556</v>
       </c>
@@ -6062,7 +6062,7 @@
       <c r="L5" s="9" t="n"/>
       <c r="M5" s="9" t="n"/>
     </row>
-    <row r="6" ht="15" customHeight="1" s="181">
+    <row r="6" ht="15" customHeight="1" s="219">
       <c r="A6" s="8" t="n">
         <v>0.6875</v>
       </c>
@@ -6083,7 +6083,7 @@
       <c r="L6" s="9" t="n"/>
       <c r="M6" s="9" t="n"/>
     </row>
-    <row r="7" ht="45" customHeight="1" s="181">
+    <row r="7" ht="45" customHeight="1" s="219">
       <c r="A7" s="8" t="n">
         <v>0.6944444444444444</v>
       </c>
@@ -6104,7 +6104,7 @@
       <c r="L7" s="9" t="n"/>
       <c r="M7" s="9" t="n"/>
     </row>
-    <row r="8" ht="15" customHeight="1" s="181">
+    <row r="8" ht="15" customHeight="1" s="219">
       <c r="A8" s="8" t="n">
         <v>0.7013888888888888</v>
       </c>
@@ -6121,7 +6121,7 @@
       <c r="L8" s="9" t="n"/>
       <c r="M8" s="9" t="n"/>
     </row>
-    <row r="9" ht="15" customHeight="1" s="181">
+    <row r="9" ht="15" customHeight="1" s="219">
       <c r="A9" s="8" t="n">
         <v>0.7083333333333334</v>
       </c>
@@ -6138,7 +6138,7 @@
       <c r="L9" s="9" t="n"/>
       <c r="M9" s="9" t="n"/>
     </row>
-    <row r="10" ht="15" customHeight="1" s="181">
+    <row r="10" ht="15" customHeight="1" s="219">
       <c r="A10" s="8" t="n">
         <v>0.7152777777777778</v>
       </c>
@@ -6155,7 +6155,7 @@
       <c r="L10" s="9" t="n"/>
       <c r="M10" s="9" t="n"/>
     </row>
-    <row r="11" ht="15" customHeight="1" s="181">
+    <row r="11" ht="15" customHeight="1" s="219">
       <c r="A11" s="8" t="n">
         <v>0.7222222222222222</v>
       </c>
@@ -6172,7 +6172,7 @@
       <c r="L11" s="9" t="n"/>
       <c r="M11" s="9" t="n"/>
     </row>
-    <row r="12" ht="15" customHeight="1" s="181">
+    <row r="12" ht="15" customHeight="1" s="219">
       <c r="A12" s="8" t="n">
         <v>0.7291666666666666</v>
       </c>
@@ -6189,7 +6189,7 @@
       <c r="L12" s="9" t="n"/>
       <c r="M12" s="9" t="n"/>
     </row>
-    <row r="13" ht="15" customHeight="1" s="181">
+    <row r="13" ht="15" customHeight="1" s="219">
       <c r="A13" s="8" t="n">
         <v>0.7361111111111112</v>
       </c>
@@ -6206,7 +6206,7 @@
       <c r="L13" s="9" t="n"/>
       <c r="M13" s="9" t="n"/>
     </row>
-    <row r="14" ht="15" customHeight="1" s="181">
+    <row r="14" ht="15" customHeight="1" s="219">
       <c r="A14" s="8" t="n">
         <v>0.7430555555555556</v>
       </c>
@@ -6223,7 +6223,7 @@
       <c r="L14" s="9" t="n"/>
       <c r="M14" s="9" t="n"/>
     </row>
-    <row r="15" ht="15" customHeight="1" s="181">
+    <row r="15" ht="15" customHeight="1" s="219">
       <c r="A15" s="8" t="n">
         <v>0.75</v>
       </c>
@@ -6257,41 +6257,41 @@
   <dimension ref="A1:M15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="12.75"/>
   <cols>
-    <col width="24.5703125" bestFit="1" customWidth="1" style="181" min="1" max="1"/>
-    <col width="21.140625" bestFit="1" customWidth="1" style="180" min="2" max="2"/>
-    <col width="21.7109375" bestFit="1" customWidth="1" style="181" min="3" max="3"/>
-    <col width="24.5703125" bestFit="1" customWidth="1" style="181" min="4" max="4"/>
-    <col width="22.28515625" bestFit="1" customWidth="1" style="181" min="5" max="5"/>
-    <col width="19.5703125" bestFit="1" customWidth="1" style="181" min="6" max="6"/>
-    <col hidden="1" width="22.140625" customWidth="1" style="181" min="7" max="7"/>
-    <col hidden="1" width="20.7109375" customWidth="1" style="181" min="8" max="8"/>
-    <col width="21" bestFit="1" customWidth="1" style="181" min="9" max="9"/>
-    <col width="21.5703125" bestFit="1" customWidth="1" style="181" min="10" max="10"/>
-    <col width="24.5703125" bestFit="1" customWidth="1" style="181" min="11" max="11"/>
-    <col width="24.28515625" bestFit="1" customWidth="1" style="181" min="12" max="12"/>
-    <col width="21.140625" bestFit="1" customWidth="1" style="181" min="13" max="13"/>
+    <col width="24.5703125" bestFit="1" customWidth="1" style="219" min="1" max="1"/>
+    <col width="21.140625" bestFit="1" customWidth="1" style="188" min="2" max="2"/>
+    <col width="21.7109375" bestFit="1" customWidth="1" style="219" min="3" max="3"/>
+    <col width="24.5703125" bestFit="1" customWidth="1" style="219" min="4" max="4"/>
+    <col width="22.28515625" bestFit="1" customWidth="1" style="219" min="5" max="5"/>
+    <col width="19.5703125" bestFit="1" customWidth="1" style="219" min="6" max="6"/>
+    <col hidden="1" width="22.140625" customWidth="1" style="219" min="7" max="7"/>
+    <col hidden="1" width="20.7109375" customWidth="1" style="219" min="8" max="8"/>
+    <col width="21" bestFit="1" customWidth="1" style="219" min="9" max="9"/>
+    <col width="21.5703125" bestFit="1" customWidth="1" style="219" min="10" max="10"/>
+    <col width="24.5703125" bestFit="1" customWidth="1" style="219" min="11" max="11"/>
+    <col width="24.28515625" bestFit="1" customWidth="1" style="219" min="12" max="12"/>
+    <col width="21.140625" bestFit="1" customWidth="1" style="219" min="13" max="13"/>
   </cols>
   <sheetData>
-    <row r="1" ht="23.25" customHeight="1" s="181">
-      <c r="A1" s="182" t="inlineStr">
+    <row r="1" ht="23.25" customHeight="1" s="219">
+      <c r="A1" s="186" t="inlineStr">
         <is>
           <t>2024 Bechtel Golf League Schedule Tee Time</t>
         </is>
       </c>
-      <c r="B1" s="179" t="n"/>
-      <c r="C1" s="179" t="n"/>
-      <c r="D1" s="179" t="n"/>
-      <c r="E1" s="179" t="n"/>
-      <c r="F1" s="179" t="n"/>
-      <c r="G1" s="179" t="n"/>
-      <c r="H1" s="179" t="n"/>
-      <c r="I1" s="179" t="n"/>
-      <c r="J1" s="179" t="n"/>
-      <c r="K1" s="179" t="n"/>
-      <c r="L1" s="179" t="n"/>
-      <c r="M1" s="179" t="n"/>
-    </row>
-    <row r="2" ht="30" customFormat="1" customHeight="1" s="217">
+      <c r="B1" s="218" t="n"/>
+      <c r="C1" s="218" t="n"/>
+      <c r="D1" s="218" t="n"/>
+      <c r="E1" s="218" t="n"/>
+      <c r="F1" s="218" t="n"/>
+      <c r="G1" s="218" t="n"/>
+      <c r="H1" s="218" t="n"/>
+      <c r="I1" s="218" t="n"/>
+      <c r="J1" s="218" t="n"/>
+      <c r="K1" s="218" t="n"/>
+      <c r="L1" s="218" t="n"/>
+      <c r="M1" s="218" t="n"/>
+    </row>
+    <row r="2" ht="30" customFormat="1" customHeight="1" s="206">
       <c r="A2" s="10" t="inlineStr">
         <is>
           <t>TEE TIME</t>
@@ -6334,7 +6334,7 @@
         <v>45506</v>
       </c>
     </row>
-    <row r="3" ht="30" customHeight="1" s="181">
+    <row r="3" ht="30" customHeight="1" s="219">
       <c r="A3" s="8" t="n">
         <v>0.6666666666666666</v>
       </c>
@@ -6355,7 +6355,7 @@
       <c r="L3" s="9" t="n"/>
       <c r="M3" s="9" t="n"/>
     </row>
-    <row r="4" ht="30" customHeight="1" s="181">
+    <row r="4" ht="30" customHeight="1" s="219">
       <c r="A4" s="8" t="n">
         <v>0.6736111111111112</v>
       </c>
@@ -6372,7 +6372,7 @@
       <c r="L4" s="9" t="n"/>
       <c r="M4" s="9" t="n"/>
     </row>
-    <row r="5" ht="30" customHeight="1" s="181">
+    <row r="5" ht="30" customHeight="1" s="219">
       <c r="A5" s="8" t="n">
         <v>0.6805555555555556</v>
       </c>
@@ -6389,7 +6389,7 @@
       <c r="L5" s="9" t="n"/>
       <c r="M5" s="9" t="n"/>
     </row>
-    <row r="6" ht="30" customHeight="1" s="181">
+    <row r="6" ht="30" customHeight="1" s="219">
       <c r="A6" s="8" t="n">
         <v>0.6875</v>
       </c>
@@ -6414,7 +6414,7 @@
       <c r="L6" s="9" t="n"/>
       <c r="M6" s="9" t="n"/>
     </row>
-    <row r="7" ht="30" customHeight="1" s="181">
+    <row r="7" ht="30" customHeight="1" s="219">
       <c r="A7" s="8" t="n">
         <v>0.6944444444444444</v>
       </c>
@@ -6439,7 +6439,7 @@
       <c r="L7" s="9" t="n"/>
       <c r="M7" s="9" t="n"/>
     </row>
-    <row r="8" ht="30" customHeight="1" s="181">
+    <row r="8" ht="30" customHeight="1" s="219">
       <c r="A8" s="8" t="n">
         <v>0.7013888888888888</v>
       </c>
@@ -6456,7 +6456,7 @@
       <c r="L8" s="9" t="n"/>
       <c r="M8" s="9" t="n"/>
     </row>
-    <row r="9" ht="30" customHeight="1" s="181">
+    <row r="9" ht="30" customHeight="1" s="219">
       <c r="A9" s="8" t="n">
         <v>0.7083333333333334</v>
       </c>
@@ -6473,7 +6473,7 @@
       <c r="L9" s="9" t="n"/>
       <c r="M9" s="9" t="n"/>
     </row>
-    <row r="10" ht="30" customHeight="1" s="181">
+    <row r="10" ht="30" customHeight="1" s="219">
       <c r="A10" s="8" t="n">
         <v>0.7152777777777778</v>
       </c>
@@ -6490,7 +6490,7 @@
       <c r="L10" s="9" t="n"/>
       <c r="M10" s="9" t="n"/>
     </row>
-    <row r="11" ht="30" customHeight="1" s="181">
+    <row r="11" ht="30" customHeight="1" s="219">
       <c r="A11" s="8" t="n">
         <v>0.7222222222222222</v>
       </c>
@@ -6507,7 +6507,7 @@
       <c r="L11" s="9" t="n"/>
       <c r="M11" s="9" t="n"/>
     </row>
-    <row r="12" ht="30" customHeight="1" s="181">
+    <row r="12" ht="30" customHeight="1" s="219">
       <c r="A12" s="8" t="n">
         <v>0.7291666666666666</v>
       </c>
@@ -6524,7 +6524,7 @@
       <c r="L12" s="9" t="n"/>
       <c r="M12" s="9" t="n"/>
     </row>
-    <row r="13" ht="30" customHeight="1" s="181">
+    <row r="13" ht="30" customHeight="1" s="219">
       <c r="A13" s="8" t="n">
         <v>0.7361111111111112</v>
       </c>
@@ -6541,7 +6541,7 @@
       <c r="L13" s="9" t="n"/>
       <c r="M13" s="9" t="n"/>
     </row>
-    <row r="14" ht="30" customHeight="1" s="181">
+    <row r="14" ht="30" customHeight="1" s="219">
       <c r="A14" s="8" t="n">
         <v>0.7430555555555556</v>
       </c>
@@ -6558,7 +6558,7 @@
       <c r="L14" s="9" t="n"/>
       <c r="M14" s="9" t="n"/>
     </row>
-    <row r="15" ht="30" customHeight="1" s="181">
+    <row r="15" ht="30" customHeight="1" s="219">
       <c r="A15" s="8" t="n">
         <v>0.75</v>
       </c>
@@ -6592,31 +6592,31 @@
   <dimension ref="A1:M15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="12.75"/>
   <cols>
-    <col width="24.5703125" bestFit="1" customWidth="1" style="181" min="1" max="1"/>
-    <col width="25.7109375" customWidth="1" style="180" min="2" max="2"/>
-    <col width="25.7109375" customWidth="1" style="181" min="3" max="13"/>
+    <col width="24.5703125" bestFit="1" customWidth="1" style="219" min="1" max="1"/>
+    <col width="25.7109375" customWidth="1" style="188" min="2" max="2"/>
+    <col width="25.7109375" customWidth="1" style="219" min="3" max="13"/>
   </cols>
   <sheetData>
-    <row r="1" ht="23.25" customHeight="1" s="181">
-      <c r="A1" s="182" t="inlineStr">
+    <row r="1" ht="23.25" customHeight="1" s="219">
+      <c r="A1" s="186" t="inlineStr">
         <is>
           <t>2024 Bechtel Golf League Schedule Tee Time</t>
         </is>
       </c>
-      <c r="B1" s="179" t="n"/>
-      <c r="C1" s="179" t="n"/>
-      <c r="D1" s="179" t="n"/>
-      <c r="E1" s="179" t="n"/>
-      <c r="F1" s="179" t="n"/>
-      <c r="G1" s="179" t="n"/>
-      <c r="H1" s="179" t="n"/>
-      <c r="I1" s="179" t="n"/>
-      <c r="J1" s="179" t="n"/>
-      <c r="K1" s="179" t="n"/>
-      <c r="L1" s="179" t="n"/>
-      <c r="M1" s="179" t="n"/>
-    </row>
-    <row r="2" ht="30" customFormat="1" customHeight="1" s="217">
+      <c r="B1" s="218" t="n"/>
+      <c r="C1" s="218" t="n"/>
+      <c r="D1" s="218" t="n"/>
+      <c r="E1" s="218" t="n"/>
+      <c r="F1" s="218" t="n"/>
+      <c r="G1" s="218" t="n"/>
+      <c r="H1" s="218" t="n"/>
+      <c r="I1" s="218" t="n"/>
+      <c r="J1" s="218" t="n"/>
+      <c r="K1" s="218" t="n"/>
+      <c r="L1" s="218" t="n"/>
+      <c r="M1" s="218" t="n"/>
+    </row>
+    <row r="2" ht="30" customFormat="1" customHeight="1" s="206">
       <c r="A2" s="10" t="inlineStr">
         <is>
           <t>TEE TIME</t>
@@ -6659,7 +6659,7 @@
         <v>45520</v>
       </c>
     </row>
-    <row r="3" ht="30" customHeight="1" s="181">
+    <row r="3" ht="30" customHeight="1" s="219">
       <c r="A3" s="8" t="n">
         <v>0.6666666666666666</v>
       </c>
@@ -6680,7 +6680,7 @@
       <c r="L3" s="9" t="n"/>
       <c r="M3" s="9" t="n"/>
     </row>
-    <row r="4" ht="30" customHeight="1" s="181">
+    <row r="4" ht="30" customHeight="1" s="219">
       <c r="A4" s="8" t="n">
         <v>0.6736111111111112</v>
       </c>
@@ -6697,7 +6697,7 @@
       <c r="L4" s="9" t="n"/>
       <c r="M4" s="9" t="n"/>
     </row>
-    <row r="5" ht="30" customHeight="1" s="181">
+    <row r="5" ht="30" customHeight="1" s="219">
       <c r="A5" s="8" t="n">
         <v>0.6805555555555556</v>
       </c>
@@ -6718,7 +6718,7 @@
       <c r="L5" s="9" t="n"/>
       <c r="M5" s="9" t="n"/>
     </row>
-    <row r="6" ht="30" customHeight="1" s="181">
+    <row r="6" ht="30" customHeight="1" s="219">
       <c r="A6" s="8" t="n">
         <v>0.6875</v>
       </c>
@@ -6740,7 +6740,7 @@
       <c r="L6" s="9" t="n"/>
       <c r="M6" s="9" t="n"/>
     </row>
-    <row r="7" ht="30" customHeight="1" s="181">
+    <row r="7" ht="30" customHeight="1" s="219">
       <c r="A7" s="8" t="n">
         <v>0.6944444444444444</v>
       </c>
@@ -6766,7 +6766,7 @@
       <c r="L7" s="9" t="n"/>
       <c r="M7" s="9" t="n"/>
     </row>
-    <row r="8" ht="30" customHeight="1" s="181">
+    <row r="8" ht="30" customHeight="1" s="219">
       <c r="A8" s="8" t="n">
         <v>0.7013888888888888</v>
       </c>
@@ -6783,7 +6783,7 @@
       <c r="L8" s="9" t="n"/>
       <c r="M8" s="9" t="n"/>
     </row>
-    <row r="9" ht="30" customHeight="1" s="181">
+    <row r="9" ht="30" customHeight="1" s="219">
       <c r="A9" s="8" t="n">
         <v>0.7083333333333334</v>
       </c>
@@ -6800,7 +6800,7 @@
       <c r="L9" s="9" t="n"/>
       <c r="M9" s="9" t="n"/>
     </row>
-    <row r="10" ht="30" customHeight="1" s="181">
+    <row r="10" ht="30" customHeight="1" s="219">
       <c r="A10" s="8" t="n">
         <v>0.7152777777777778</v>
       </c>
@@ -6817,7 +6817,7 @@
       <c r="L10" s="9" t="n"/>
       <c r="M10" s="9" t="n"/>
     </row>
-    <row r="11" ht="30" customHeight="1" s="181">
+    <row r="11" ht="30" customHeight="1" s="219">
       <c r="A11" s="8" t="n">
         <v>0.7222222222222222</v>
       </c>
@@ -6834,7 +6834,7 @@
       <c r="L11" s="9" t="n"/>
       <c r="M11" s="9" t="n"/>
     </row>
-    <row r="12" ht="30" customHeight="1" s="181">
+    <row r="12" ht="30" customHeight="1" s="219">
       <c r="A12" s="8" t="n">
         <v>0.7291666666666666</v>
       </c>
@@ -6851,7 +6851,7 @@
       <c r="L12" s="9" t="n"/>
       <c r="M12" s="9" t="n"/>
     </row>
-    <row r="13" ht="30" customHeight="1" s="181">
+    <row r="13" ht="30" customHeight="1" s="219">
       <c r="A13" s="8" t="n">
         <v>0.7361111111111112</v>
       </c>
@@ -6868,7 +6868,7 @@
       <c r="L13" s="9" t="n"/>
       <c r="M13" s="9" t="n"/>
     </row>
-    <row r="14" ht="30" customHeight="1" s="181">
+    <row r="14" ht="30" customHeight="1" s="219">
       <c r="A14" s="8" t="n">
         <v>0.7430555555555556</v>
       </c>
@@ -6885,7 +6885,7 @@
       <c r="L14" s="9" t="n"/>
       <c r="M14" s="9" t="n"/>
     </row>
-    <row r="15" ht="30" customHeight="1" s="181">
+    <row r="15" ht="30" customHeight="1" s="219">
       <c r="A15" s="8" t="n">
         <v>0.75</v>
       </c>
@@ -6919,41 +6919,41 @@
   <dimension ref="A1:M15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="12.75"/>
   <cols>
-    <col width="18" bestFit="1" customWidth="1" style="181" min="1" max="1"/>
-    <col width="24" bestFit="1" customWidth="1" style="180" min="2" max="2"/>
-    <col width="24.5703125" bestFit="1" customWidth="1" style="181" min="3" max="3"/>
-    <col width="27.5703125" bestFit="1" customWidth="1" style="181" min="4" max="4"/>
-    <col width="25.42578125" bestFit="1" customWidth="1" style="181" min="5" max="5"/>
-    <col width="22.140625" bestFit="1" customWidth="1" style="181" min="6" max="6"/>
-    <col width="25" bestFit="1" customWidth="1" style="181" min="7" max="7"/>
-    <col width="23.42578125" bestFit="1" customWidth="1" style="181" min="8" max="8"/>
-    <col width="24" bestFit="1" customWidth="1" style="181" min="9" max="9"/>
-    <col width="24.5703125" bestFit="1" customWidth="1" style="181" min="10" max="10"/>
-    <col width="27.5703125" bestFit="1" customWidth="1" style="181" min="11" max="11"/>
-    <col width="25.42578125" bestFit="1" customWidth="1" style="181" min="12" max="12"/>
-    <col width="22.140625" bestFit="1" customWidth="1" style="181" min="13" max="13"/>
+    <col width="18" bestFit="1" customWidth="1" style="219" min="1" max="1"/>
+    <col width="24" bestFit="1" customWidth="1" style="188" min="2" max="2"/>
+    <col width="24.5703125" bestFit="1" customWidth="1" style="219" min="3" max="3"/>
+    <col width="27.5703125" bestFit="1" customWidth="1" style="219" min="4" max="4"/>
+    <col width="25.42578125" bestFit="1" customWidth="1" style="219" min="5" max="5"/>
+    <col width="22.140625" bestFit="1" customWidth="1" style="219" min="6" max="6"/>
+    <col width="25" bestFit="1" customWidth="1" style="219" min="7" max="7"/>
+    <col width="23.42578125" bestFit="1" customWidth="1" style="219" min="8" max="8"/>
+    <col width="24" bestFit="1" customWidth="1" style="219" min="9" max="9"/>
+    <col width="24.5703125" bestFit="1" customWidth="1" style="219" min="10" max="10"/>
+    <col width="27.5703125" bestFit="1" customWidth="1" style="219" min="11" max="11"/>
+    <col width="25.42578125" bestFit="1" customWidth="1" style="219" min="12" max="12"/>
+    <col width="22.140625" bestFit="1" customWidth="1" style="219" min="13" max="13"/>
   </cols>
   <sheetData>
-    <row r="1" ht="23.25" customHeight="1" s="181">
-      <c r="A1" s="182" t="inlineStr">
+    <row r="1" ht="23.25" customHeight="1" s="219">
+      <c r="A1" s="186" t="inlineStr">
         <is>
           <t>2024 Bechtel Golf League Schedule Tee Time</t>
         </is>
       </c>
-      <c r="B1" s="179" t="n"/>
-      <c r="C1" s="179" t="n"/>
-      <c r="D1" s="179" t="n"/>
-      <c r="E1" s="179" t="n"/>
-      <c r="F1" s="179" t="n"/>
-      <c r="G1" s="179" t="n"/>
-      <c r="H1" s="179" t="n"/>
-      <c r="I1" s="179" t="n"/>
-      <c r="J1" s="179" t="n"/>
-      <c r="K1" s="179" t="n"/>
-      <c r="L1" s="179" t="n"/>
-      <c r="M1" s="179" t="n"/>
-    </row>
-    <row r="2" ht="30" customFormat="1" customHeight="1" s="217">
+      <c r="B1" s="218" t="n"/>
+      <c r="C1" s="218" t="n"/>
+      <c r="D1" s="218" t="n"/>
+      <c r="E1" s="218" t="n"/>
+      <c r="F1" s="218" t="n"/>
+      <c r="G1" s="218" t="n"/>
+      <c r="H1" s="218" t="n"/>
+      <c r="I1" s="218" t="n"/>
+      <c r="J1" s="218" t="n"/>
+      <c r="K1" s="218" t="n"/>
+      <c r="L1" s="218" t="n"/>
+      <c r="M1" s="218" t="n"/>
+    </row>
+    <row r="2" ht="30" customFormat="1" customHeight="1" s="206">
       <c r="A2" s="10" t="inlineStr">
         <is>
           <t>TEE TIME</t>
@@ -6996,7 +6996,7 @@
         <v>45534</v>
       </c>
     </row>
-    <row r="3" ht="30" customHeight="1" s="181">
+    <row r="3" ht="30" customHeight="1" s="219">
       <c r="A3" s="8" t="n">
         <v>0.6666666666666666</v>
       </c>
@@ -7013,7 +7013,7 @@
       <c r="L3" s="9" t="n"/>
       <c r="M3" s="9" t="n"/>
     </row>
-    <row r="4" ht="30" customHeight="1" s="181">
+    <row r="4" ht="30" customHeight="1" s="219">
       <c r="A4" s="8" t="n">
         <v>0.6736111111111112</v>
       </c>
@@ -7030,7 +7030,7 @@
       <c r="L4" s="9" t="n"/>
       <c r="M4" s="9" t="n"/>
     </row>
-    <row r="5" ht="30" customHeight="1" s="181">
+    <row r="5" ht="30" customHeight="1" s="219">
       <c r="A5" s="8" t="n">
         <v>0.6805555555555556</v>
       </c>
@@ -7047,7 +7047,7 @@
       <c r="L5" s="9" t="n"/>
       <c r="M5" s="9" t="n"/>
     </row>
-    <row r="6" ht="46.5" customHeight="1" s="181">
+    <row r="6" ht="46.5" customHeight="1" s="219">
       <c r="A6" s="8" t="n">
         <v>0.6875</v>
       </c>
@@ -7075,7 +7075,7 @@
       <c r="L6" s="9" t="n"/>
       <c r="M6" s="9" t="n"/>
     </row>
-    <row r="7" ht="30" customHeight="1" s="181">
+    <row r="7" ht="30" customHeight="1" s="219">
       <c r="A7" s="8" t="n">
         <v>0.6944444444444444</v>
       </c>
@@ -7100,7 +7100,7 @@
       <c r="L7" s="9" t="n"/>
       <c r="M7" s="9" t="n"/>
     </row>
-    <row r="8" ht="30" customHeight="1" s="181">
+    <row r="8" ht="30" customHeight="1" s="219">
       <c r="A8" s="8" t="n">
         <v>0.7013888888888888</v>
       </c>
@@ -7117,7 +7117,7 @@
       <c r="L8" s="9" t="n"/>
       <c r="M8" s="9" t="n"/>
     </row>
-    <row r="9" ht="30" customHeight="1" s="181">
+    <row r="9" ht="30" customHeight="1" s="219">
       <c r="A9" s="8" t="n">
         <v>0.7083333333333334</v>
       </c>
@@ -7134,7 +7134,7 @@
       <c r="L9" s="9" t="n"/>
       <c r="M9" s="9" t="n"/>
     </row>
-    <row r="10" ht="30" customHeight="1" s="181">
+    <row r="10" ht="30" customHeight="1" s="219">
       <c r="A10" s="8" t="n">
         <v>0.7152777777777778</v>
       </c>
@@ -7151,7 +7151,7 @@
       <c r="L10" s="9" t="n"/>
       <c r="M10" s="9" t="n"/>
     </row>
-    <row r="11" ht="30" customHeight="1" s="181">
+    <row r="11" ht="30" customHeight="1" s="219">
       <c r="A11" s="8" t="n">
         <v>0.7222222222222222</v>
       </c>
@@ -7168,7 +7168,7 @@
       <c r="L11" s="9" t="n"/>
       <c r="M11" s="9" t="n"/>
     </row>
-    <row r="12" ht="30" customHeight="1" s="181">
+    <row r="12" ht="30" customHeight="1" s="219">
       <c r="A12" s="8" t="n">
         <v>0.7291666666666666</v>
       </c>
@@ -7185,7 +7185,7 @@
       <c r="L12" s="9" t="n"/>
       <c r="M12" s="9" t="n"/>
     </row>
-    <row r="13" ht="30" customHeight="1" s="181">
+    <row r="13" ht="30" customHeight="1" s="219">
       <c r="A13" s="8" t="n">
         <v>0.7361111111111112</v>
       </c>
@@ -7202,7 +7202,7 @@
       <c r="L13" s="9" t="n"/>
       <c r="M13" s="9" t="n"/>
     </row>
-    <row r="14" ht="30" customHeight="1" s="181">
+    <row r="14" ht="30" customHeight="1" s="219">
       <c r="A14" s="8" t="n">
         <v>0.7430555555555556</v>
       </c>
@@ -7219,7 +7219,7 @@
       <c r="L14" s="9" t="n"/>
       <c r="M14" s="9" t="n"/>
     </row>
-    <row r="15" ht="30" customHeight="1" s="181">
+    <row r="15" ht="30" customHeight="1" s="219">
       <c r="A15" s="8" t="n">
         <v>0.75</v>
       </c>
@@ -7253,31 +7253,31 @@
   <dimension ref="A1:M29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="12.75"/>
   <cols>
-    <col width="18.28515625" bestFit="1" customWidth="1" style="181" min="2" max="2"/>
-    <col width="18.5703125" customWidth="1" style="181" min="3" max="3"/>
-    <col width="19.42578125" customWidth="1" style="181" min="4" max="4"/>
-    <col width="19" bestFit="1" customWidth="1" style="181" min="5" max="5"/>
-    <col width="20.28515625" customWidth="1" style="181" min="6" max="6"/>
-    <col width="21.28515625" bestFit="1" customWidth="1" style="181" min="7" max="7"/>
-    <col width="19" bestFit="1" customWidth="1" style="181" min="8" max="8"/>
-    <col width="20.42578125" bestFit="1" customWidth="1" style="181" min="9" max="9"/>
-    <col width="19.5703125" bestFit="1" customWidth="1" style="181" min="10" max="10"/>
+    <col width="18.28515625" bestFit="1" customWidth="1" style="219" min="2" max="2"/>
+    <col width="18.5703125" customWidth="1" style="219" min="3" max="3"/>
+    <col width="19.42578125" customWidth="1" style="219" min="4" max="4"/>
+    <col width="19" bestFit="1" customWidth="1" style="219" min="5" max="5"/>
+    <col width="20.28515625" customWidth="1" style="219" min="6" max="6"/>
+    <col width="21.28515625" bestFit="1" customWidth="1" style="219" min="7" max="7"/>
+    <col width="19" bestFit="1" customWidth="1" style="219" min="8" max="8"/>
+    <col width="20.42578125" bestFit="1" customWidth="1" style="219" min="9" max="9"/>
+    <col width="19.5703125" bestFit="1" customWidth="1" style="219" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="23.25" customHeight="1" s="181">
-      <c r="B1" s="178" t="inlineStr">
+    <row r="1" ht="23.25" customHeight="1" s="219">
+      <c r="B1" s="187" t="inlineStr">
         <is>
           <t>2026 iCON Golf League Schedule</t>
         </is>
       </c>
-      <c r="C1" s="179" t="n"/>
-      <c r="D1" s="179" t="n"/>
-      <c r="E1" s="179" t="n"/>
-      <c r="F1" s="179" t="n"/>
-      <c r="G1" s="179" t="n"/>
-      <c r="H1" s="179" t="n"/>
-      <c r="I1" s="179" t="n"/>
-      <c r="J1" s="179" t="n"/>
+      <c r="C1" s="218" t="n"/>
+      <c r="D1" s="218" t="n"/>
+      <c r="E1" s="218" t="n"/>
+      <c r="F1" s="218" t="n"/>
+      <c r="G1" s="218" t="n"/>
+      <c r="H1" s="218" t="n"/>
+      <c r="I1" s="218" t="n"/>
+      <c r="J1" s="218" t="n"/>
     </row>
     <row r="2">
       <c r="B2" s="6" t="inlineStr">
@@ -7749,7 +7749,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="E13" s="180" t="n"/>
+      <c r="E13" s="188" t="n"/>
     </row>
     <row r="14">
       <c r="B14" s="2" t="inlineStr">
@@ -7797,7 +7797,7 @@
       </c>
       <c r="F15" s="3" t="n"/>
     </row>
-    <row r="16" ht="13.5" customHeight="1" s="181">
+    <row r="16" ht="13.5" customHeight="1" s="219">
       <c r="B16" s="5" t="n">
         <v>2</v>
       </c>
@@ -7820,7 +7820,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="13.5" customHeight="1" s="181">
+    <row r="17" ht="13.5" customHeight="1" s="219">
       <c r="B17" s="5">
         <f>B16+1</f>
         <v/>
@@ -7844,7 +7844,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="13.5" customHeight="1" s="181">
+    <row r="18" ht="13.5" customHeight="1" s="219">
       <c r="B18" s="5">
         <f>B17+1</f>
         <v/>
@@ -7888,7 +7888,7 @@
       </c>
       <c r="F19" s="3" t="n"/>
     </row>
-    <row r="20" ht="13.5" customHeight="1" s="181">
+    <row r="20" ht="13.5" customHeight="1" s="219">
       <c r="B20" s="5">
         <f>B19+1</f>
         <v/>
@@ -7913,7 +7913,7 @@
       </c>
       <c r="G20" s="4" t="n"/>
     </row>
-    <row r="21" ht="13.5" customHeight="1" s="181">
+    <row r="21" ht="13.5" customHeight="1" s="219">
       <c r="B21" s="5">
         <f>B20+1</f>
         <v/>
@@ -7937,7 +7937,7 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="13.5" customHeight="1" s="181">
+    <row r="22" ht="13.5" customHeight="1" s="219">
       <c r="B22" s="5">
         <f>B21+1</f>
         <v/>
@@ -7985,7 +7985,7 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="13.5" customHeight="1" s="181">
+    <row r="24" ht="13.5" customHeight="1" s="219">
       <c r="B24" s="5">
         <f>B23+1</f>
         <v/>
@@ -8034,7 +8034,7 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="13.5" customHeight="1" s="181">
+    <row r="26" ht="13.5" customHeight="1" s="219">
       <c r="B26" s="5">
         <f>B25+1</f>
         <v/>
@@ -8082,7 +8082,7 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="13.5" customHeight="1" s="181">
+    <row r="28" ht="13.5" customHeight="1" s="219">
       <c r="B28" s="5">
         <f>B27+1</f>
         <v/>
@@ -8106,7 +8106,7 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="13.5" customHeight="1" s="181">
+    <row r="29" ht="13.5" customHeight="1" s="219">
       <c r="B29" s="5">
         <f>B28+1</f>
         <v/>
@@ -8159,129 +8159,129 @@
   <dimension ref="B1:AI46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="12.75"/>
   <cols>
-    <col width="12" customWidth="1" style="181" min="2" max="2"/>
-    <col width="17" bestFit="1" customWidth="1" style="181" min="3" max="3"/>
-    <col width="11.85546875" customWidth="1" style="181" min="4" max="4"/>
-    <col width="9.140625" customWidth="1" style="181" min="6" max="8"/>
-    <col width="11" bestFit="1" customWidth="1" style="181" min="9" max="9"/>
-    <col width="9.140625" customWidth="1" style="181" min="10" max="10"/>
-    <col width="14" bestFit="1" customWidth="1" style="181" min="11" max="11"/>
-    <col width="15.5703125" bestFit="1" customWidth="1" style="181" min="12" max="12"/>
-    <col width="13.5703125" bestFit="1" customWidth="1" style="181" min="13" max="13"/>
-    <col width="13.5703125" customWidth="1" style="181" min="14" max="15"/>
-    <col width="12.5703125" customWidth="1" style="181" min="16" max="35"/>
+    <col width="12" customWidth="1" style="219" min="2" max="2"/>
+    <col width="17" bestFit="1" customWidth="1" style="219" min="3" max="3"/>
+    <col width="11.85546875" customWidth="1" style="219" min="4" max="4"/>
+    <col width="9.140625" customWidth="1" style="219" min="6" max="8"/>
+    <col width="11" bestFit="1" customWidth="1" style="219" min="9" max="9"/>
+    <col width="9.140625" customWidth="1" style="219" min="10" max="10"/>
+    <col width="14" bestFit="1" customWidth="1" style="219" min="11" max="11"/>
+    <col width="15.5703125" bestFit="1" customWidth="1" style="219" min="12" max="12"/>
+    <col width="13.5703125" bestFit="1" customWidth="1" style="219" min="13" max="13"/>
+    <col width="13.5703125" customWidth="1" style="219" min="14" max="15"/>
+    <col width="12.5703125" customWidth="1" style="219" min="16" max="35"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="P1" s="193" t="inlineStr">
+      <c r="P1" s="194" t="inlineStr">
         <is>
           <t>Reston National</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="13.5" customHeight="1" s="181" thickBot="1">
-      <c r="P2" s="193" t="inlineStr">
+    <row r="2" ht="13.5" customHeight="1" s="219" thickBot="1">
+      <c r="P2" s="194" t="inlineStr">
         <is>
           <t>Round 1</t>
         </is>
       </c>
-      <c r="Q2" s="193" t="inlineStr">
+      <c r="Q2" s="194" t="inlineStr">
         <is>
           <t>Round 2</t>
         </is>
       </c>
-      <c r="R2" s="193" t="inlineStr">
+      <c r="R2" s="194" t="inlineStr">
         <is>
           <t>Round 3</t>
         </is>
       </c>
-      <c r="S2" s="193" t="inlineStr">
+      <c r="S2" s="194" t="inlineStr">
         <is>
           <t>Round 4</t>
         </is>
       </c>
-      <c r="T2" s="193" t="inlineStr">
+      <c r="T2" s="194" t="inlineStr">
         <is>
           <t>Round 5</t>
         </is>
       </c>
-      <c r="U2" s="193" t="inlineStr">
+      <c r="U2" s="194" t="inlineStr">
         <is>
           <t>Round 6</t>
         </is>
       </c>
-      <c r="V2" s="193" t="inlineStr">
+      <c r="V2" s="194" t="inlineStr">
         <is>
           <t>Round 7</t>
         </is>
       </c>
-      <c r="W2" s="193" t="inlineStr">
+      <c r="W2" s="194" t="inlineStr">
         <is>
           <t>Round 8</t>
         </is>
       </c>
-      <c r="X2" s="193" t="inlineStr">
+      <c r="X2" s="194" t="inlineStr">
         <is>
           <t>Round 9</t>
         </is>
       </c>
-      <c r="Y2" s="193" t="inlineStr">
+      <c r="Y2" s="194" t="inlineStr">
         <is>
           <t>Round 10</t>
         </is>
       </c>
-      <c r="Z2" s="193" t="inlineStr">
+      <c r="Z2" s="194" t="inlineStr">
         <is>
           <t>Round 11</t>
         </is>
       </c>
-      <c r="AA2" s="193" t="inlineStr">
+      <c r="AA2" s="194" t="inlineStr">
         <is>
           <t>Round 12</t>
         </is>
       </c>
-      <c r="AB2" s="193" t="inlineStr">
+      <c r="AB2" s="194" t="inlineStr">
         <is>
           <t>Round 13</t>
         </is>
       </c>
-      <c r="AC2" s="193" t="inlineStr">
+      <c r="AC2" s="194" t="inlineStr">
         <is>
           <t>Round 14</t>
         </is>
       </c>
-      <c r="AD2" s="193" t="inlineStr">
+      <c r="AD2" s="194" t="inlineStr">
         <is>
           <t>Round 15</t>
         </is>
       </c>
-      <c r="AE2" s="193" t="inlineStr">
+      <c r="AE2" s="194" t="inlineStr">
         <is>
           <t>Round 16</t>
         </is>
       </c>
-      <c r="AF2" s="193" t="inlineStr">
+      <c r="AF2" s="194" t="inlineStr">
         <is>
           <t>Round 17</t>
         </is>
       </c>
-      <c r="AG2" s="193" t="inlineStr">
+      <c r="AG2" s="194" t="inlineStr">
         <is>
           <t>Round 18</t>
         </is>
       </c>
-      <c r="AH2" s="193" t="inlineStr">
+      <c r="AH2" s="194" t="inlineStr">
         <is>
           <t>Round 19</t>
         </is>
       </c>
-      <c r="AI2" s="193" t="inlineStr">
+      <c r="AI2" s="194" t="inlineStr">
         <is>
           <t>Round 20</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="13.5" customHeight="1" s="181" thickBot="1">
+    <row r="3" ht="13.5" customHeight="1" s="219" thickBot="1">
       <c r="B3" s="2" t="inlineStr">
         <is>
           <t>Mens</t>
@@ -8302,33 +8302,33 @@
           <t>Name</t>
         </is>
       </c>
-      <c r="G3" s="194" t="inlineStr">
+      <c r="G3" s="195" t="inlineStr">
         <is>
           <t>Tees</t>
         </is>
       </c>
-      <c r="H3" s="195" t="n"/>
-      <c r="I3" s="194" t="inlineStr">
+      <c r="H3" s="220" t="n"/>
+      <c r="I3" s="195" t="inlineStr">
         <is>
           <t>USGA Initial</t>
         </is>
       </c>
-      <c r="J3" s="194" t="inlineStr">
+      <c r="J3" s="195" t="inlineStr">
         <is>
           <t>Initial</t>
         </is>
       </c>
-      <c r="K3" s="194" t="inlineStr">
+      <c r="K3" s="195" t="inlineStr">
         <is>
           <t>Initial Handicap</t>
         </is>
       </c>
-      <c r="L3" s="194" t="inlineStr">
+      <c r="L3" s="195" t="inlineStr">
         <is>
           <t>Course Handicap</t>
         </is>
       </c>
-      <c r="M3" s="194" t="inlineStr">
+      <c r="M3" s="195" t="inlineStr">
         <is>
           <t>Live Handicap</t>
         </is>
@@ -8456,42 +8456,42 @@
       <c r="D4" s="43" t="n">
         <v>130</v>
       </c>
-      <c r="F4" s="189" t="inlineStr">
+      <c r="F4" s="192" t="inlineStr">
         <is>
           <t>Ethan</t>
         </is>
       </c>
-      <c r="G4" s="196">
+      <c r="G4" s="189">
         <f>VLOOKUP($F4,Schedule!$C$15:$E$29,3)</f>
         <v/>
       </c>
-      <c r="H4" s="196">
+      <c r="H4" s="189">
         <f>VLOOKUP($F4,Schedule!$C$15:$E$29,4)</f>
         <v/>
       </c>
-      <c r="I4" s="192" t="n">
+      <c r="I4" s="193" t="n">
         <v>13</v>
       </c>
-      <c r="J4" s="196">
+      <c r="J4" s="189">
         <f>I4+36</f>
         <v/>
       </c>
-      <c r="K4" s="186" t="n">
+      <c r="K4" s="190" t="n">
         <v>13</v>
       </c>
-      <c r="L4" s="186">
+      <c r="L4" s="190">
         <f t="array" ref="L4">_xlfn.IFS($G4="Mens",ROUNDUP($K4*(VLOOKUP($H4,$B$4:$D$7,3)/113),0),$G4="Womens",ROUNDUP($K4*(VLOOKUP($H4,$B$10:$D$12,3)/113),0))</f>
         <v/>
       </c>
-      <c r="M4" s="186">
+      <c r="M4" s="190">
         <f t="array" ref="M4">ROUNDUP(_xlfn.IFS(O4&lt;=$B$20,MIN(P6:AI6),AND(O4&gt;=$B$21,O4&lt;=$B$23),AVERAGE(SMALL(P6:AI6,{1,2})),AND(O4&gt;=$B$24,O4&lt;=$B$26),AVERAGE(SMALL(P6:AI6,{1,2,3})),AND(O4&gt;=$B$27,O4&lt;=$B$29),AVERAGE(SMALL(P6:AI6,{1,2,3,4})),AND(O4&gt;=$B$30,O4&lt;=$B$31),AVERAGE(SMALL(P6:AI6,{1,2,3,4,5})),AND(O4&gt;=$B$32,O4&lt;=$B$33),AVERAGE(SMALL(P6:AI6,{1,2,3,4,5,6})),AND(O4=$B$34),AVERAGE(SMALL(P6:AI6,{1,2,3,4,5,6,7})),AND(O4=$B$35),AVERAGE(SMALL(P6:AI6,{1,2,3,4,5,6,7,8})))+VLOOKUP(O4,$B$16:$D$35,3),0)</f>
         <v/>
       </c>
-      <c r="N4" s="186">
+      <c r="N4" s="190">
         <f t="array" ref="N4">ROUNDUP(_xlfn.IFS($G4="Mens",ROUNDUP(M4*(VLOOKUP($H4,$B$4:$D$7,3)/113),1),$G4="Womens",ROUNDUP(M4*(VLOOKUP($H4,$B$10:$D$12,3)/113),1)),0)</f>
         <v/>
       </c>
-      <c r="O4" s="183">
+      <c r="O4" s="191">
         <f>COUNT(P4:AI4)</f>
         <v/>
       </c>
@@ -8544,16 +8544,16 @@
       <c r="D5" s="43" t="n">
         <v>126</v>
       </c>
-      <c r="F5" s="190" t="n"/>
-      <c r="G5" s="187" t="n"/>
-      <c r="H5" s="187" t="n"/>
-      <c r="I5" s="187" t="n"/>
-      <c r="J5" s="187" t="n"/>
-      <c r="K5" s="187" t="n"/>
-      <c r="L5" s="187" t="n"/>
-      <c r="M5" s="187" t="n"/>
-      <c r="N5" s="187" t="n"/>
-      <c r="O5" s="184" t="n"/>
+      <c r="F5" s="221" t="n"/>
+      <c r="G5" s="222" t="n"/>
+      <c r="H5" s="222" t="n"/>
+      <c r="I5" s="222" t="n"/>
+      <c r="J5" s="222" t="n"/>
+      <c r="K5" s="222" t="n"/>
+      <c r="L5" s="222" t="n"/>
+      <c r="M5" s="222" t="n"/>
+      <c r="N5" s="222" t="n"/>
+      <c r="O5" s="223" t="n"/>
       <c r="P5" s="96" t="inlineStr">
         <is>
           <t>USGA Diff.</t>
@@ -8655,7 +8655,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="13.5" customHeight="1" s="181" thickBot="1">
+    <row r="6" ht="13.5" customHeight="1" s="219" thickBot="1">
       <c r="B6" s="42" t="inlineStr">
         <is>
           <t>Blue/White</t>
@@ -8667,16 +8667,16 @@
       <c r="D6" s="43" t="n">
         <v>120</v>
       </c>
-      <c r="F6" s="191" t="n"/>
-      <c r="G6" s="188" t="n"/>
-      <c r="H6" s="188" t="n"/>
-      <c r="I6" s="188" t="n"/>
-      <c r="J6" s="188" t="n"/>
-      <c r="K6" s="188" t="n"/>
-      <c r="L6" s="188" t="n"/>
-      <c r="M6" s="188" t="n"/>
-      <c r="N6" s="188" t="n"/>
-      <c r="O6" s="185" t="n"/>
+      <c r="F6" s="224" t="n"/>
+      <c r="G6" s="225" t="n"/>
+      <c r="H6" s="225" t="n"/>
+      <c r="I6" s="225" t="n"/>
+      <c r="J6" s="225" t="n"/>
+      <c r="K6" s="225" t="n"/>
+      <c r="L6" s="225" t="n"/>
+      <c r="M6" s="225" t="n"/>
+      <c r="N6" s="225" t="n"/>
+      <c r="O6" s="226" t="n"/>
       <c r="P6" s="97">
         <f t="array" ref="P6">IF(P4="","",_xlfn.IFS($G4="Mens",(P4-(VLOOKUP($H4,$B$4:$D$7,2)/2))/VLOOKUP($H4,$B$4:$D$7,3)*113,$G4="Womens",(P4-(VLOOKUP($H4,$B$10:$D$12,2)/2))/VLOOKUP($H4,$B$10:$D$12,3)*113))</f>
         <v/>
@@ -8773,9 +8773,9 @@
       <c r="L7" s="98" t="n"/>
     </row>
     <row r="8">
-      <c r="B8" s="217" t="n"/>
-      <c r="C8" s="217" t="n"/>
-      <c r="D8" s="217" t="n"/>
+      <c r="B8" s="206" t="n"/>
+      <c r="C8" s="206" t="n"/>
+      <c r="D8" s="206" t="n"/>
     </row>
     <row r="9">
       <c r="B9" s="2" t="inlineStr">
@@ -8833,8 +8833,8 @@
         <v>120</v>
       </c>
     </row>
-    <row r="14" ht="13.5" customHeight="1" s="181" thickBot="1"/>
-    <row r="15" ht="25.5" customHeight="1" s="181">
+    <row r="14" ht="13.5" customHeight="1" s="219" thickBot="1"/>
+    <row r="15" ht="25.5" customHeight="1" s="219">
       <c r="B15" s="82" t="inlineStr">
         <is>
           <t># of Score Differentials</t>
@@ -8903,7 +8903,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="20" ht="13.5" customHeight="1" s="181" thickBot="1">
+    <row r="20" ht="13.5" customHeight="1" s="219" thickBot="1">
       <c r="B20" s="39" t="n">
         <v>5</v>
       </c>
@@ -8942,7 +8942,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" ht="13.5" customHeight="1" s="181" thickBot="1">
+    <row r="23" ht="13.5" customHeight="1" s="219" thickBot="1">
       <c r="B23" s="39" t="n">
         <v>8</v>
       </c>
@@ -8982,7 +8982,7 @@
       </c>
       <c r="K25" s="101" t="n"/>
     </row>
-    <row r="26" ht="13.5" customHeight="1" s="181" thickBot="1">
+    <row r="26" ht="13.5" customHeight="1" s="219" thickBot="1">
       <c r="B26" s="39" t="n">
         <v>11</v>
       </c>
@@ -9021,7 +9021,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" ht="13.5" customHeight="1" s="181" thickBot="1">
+    <row r="29" ht="13.5" customHeight="1" s="219" thickBot="1">
       <c r="B29" s="39" t="n">
         <v>14</v>
       </c>
@@ -9047,7 +9047,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" ht="13.5" customHeight="1" s="181" thickBot="1">
+    <row r="31" ht="13.5" customHeight="1" s="219" thickBot="1">
       <c r="B31" s="39" t="n">
         <v>16</v>
       </c>
@@ -9073,7 +9073,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" ht="13.5" customHeight="1" s="181" thickBot="1">
+    <row r="33" ht="13.5" customHeight="1" s="219" thickBot="1">
       <c r="B33" s="39" t="n">
         <v>18</v>
       </c>
@@ -9086,8 +9086,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" ht="13.5" customHeight="1" s="181" thickBot="1">
-      <c r="B34" s="189" t="n">
+    <row r="34" ht="13.5" customHeight="1" s="219" thickBot="1">
+      <c r="B34" s="192" t="n">
         <v>19</v>
       </c>
       <c r="C34" s="92" t="inlineStr">
@@ -9095,15 +9095,15 @@
           <t>Average of lowest 7</t>
         </is>
       </c>
-      <c r="D34" s="183" t="n">
+      <c r="D34" s="191" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="35" ht="13.5" customHeight="1" s="181" thickBot="1">
+    <row r="35" ht="13.5" customHeight="1" s="219" thickBot="1">
       <c r="B35" s="89" t="n">
         <v>20</v>
       </c>
-      <c r="C35" s="188" t="inlineStr">
+      <c r="C35" s="225" t="inlineStr">
         <is>
           <t>Average of lowest 8</t>
         </is>
@@ -9235,27 +9235,27 @@
   <dimension ref="A1:S32"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.140625" defaultRowHeight="12.75"/>
   <cols>
-    <col width="3.140625" customWidth="1" style="217" min="1" max="1"/>
-    <col width="18" bestFit="1" customWidth="1" style="217" min="2" max="2"/>
-    <col width="12.140625" bestFit="1" customWidth="1" style="217" min="3" max="3"/>
-    <col width="9.140625" customWidth="1" style="217" min="4" max="12"/>
-    <col width="11.5703125" customWidth="1" style="217" min="13" max="15"/>
-    <col width="9.140625" customWidth="1" style="217" min="16" max="17"/>
-    <col width="14.85546875" customWidth="1" style="217" min="18" max="19"/>
-    <col width="9.140625" customWidth="1" style="217" min="20" max="34"/>
-    <col width="9.140625" customWidth="1" style="217" min="35" max="16384"/>
+    <col width="3.140625" customWidth="1" style="206" min="1" max="1"/>
+    <col width="18" bestFit="1" customWidth="1" style="206" min="2" max="2"/>
+    <col width="12.140625" bestFit="1" customWidth="1" style="206" min="3" max="3"/>
+    <col width="9.140625" customWidth="1" style="206" min="4" max="12"/>
+    <col width="11.5703125" customWidth="1" style="206" min="13" max="15"/>
+    <col width="9.140625" customWidth="1" style="206" min="16" max="17"/>
+    <col width="14.85546875" customWidth="1" style="206" min="18" max="19"/>
+    <col width="9.140625" customWidth="1" style="206" min="20" max="35"/>
+    <col width="9.140625" customWidth="1" style="206" min="36" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1" ht="13.5" customHeight="1" s="181" thickBot="1">
-      <c r="N1" s="205" t="inlineStr">
+    <row r="1" ht="13.5" customHeight="1" s="219" thickBot="1">
+      <c r="N1" s="207" t="inlineStr">
         <is>
           <t>Tiebreakers</t>
         </is>
       </c>
-      <c r="O1" s="206" t="n"/>
+      <c r="O1" s="227" t="n"/>
       <c r="P1" s="21" t="n"/>
     </row>
-    <row r="2" ht="41.45" customHeight="1" s="181" thickBot="1">
+    <row r="2" ht="41.45" customHeight="1" s="219" thickBot="1">
       <c r="B2" s="20" t="inlineStr">
         <is>
           <t>Name</t>
@@ -9323,11 +9323,11 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="12.95" customHeight="1" s="181" thickBot="1">
-      <c r="A3" s="217" t="n">
+    <row r="3" ht="12.95" customHeight="1" s="219" thickBot="1">
+      <c r="A3" s="206" t="n">
         <v>1</v>
       </c>
-      <c r="B3" s="218">
+      <c r="B3" s="198">
         <f>Schedule!C15</f>
         <v/>
       </c>
@@ -9349,7 +9349,7 @@
       <c r="J3" s="200" t="n"/>
       <c r="K3" s="200" t="n"/>
       <c r="L3" s="160" t="n"/>
-      <c r="M3" s="209" t="n">
+      <c r="M3" s="202" t="n">
         <v>6</v>
       </c>
       <c r="N3" s="200" t="inlineStr">
@@ -9357,19 +9357,19 @@
           <t>0-1-1</t>
         </is>
       </c>
-      <c r="O3" s="202" t="n">
+      <c r="O3" s="208" t="n">
         <v>41.5</v>
       </c>
-      <c r="Q3" s="197" t="inlineStr">
+      <c r="Q3" s="209" t="inlineStr">
         <is>
           <t>Playoffs</t>
         </is>
       </c>
-      <c r="R3" s="198" t="n"/>
-      <c r="S3" s="199" t="n"/>
-    </row>
-    <row r="4" ht="13.5" customHeight="1" s="181" thickBot="1">
-      <c r="B4" s="219" t="n"/>
+      <c r="R3" s="228" t="n"/>
+      <c r="S3" s="229" t="n"/>
+    </row>
+    <row r="4" ht="13.5" customHeight="1" s="219" thickBot="1">
+      <c r="B4" s="230" t="n"/>
       <c r="C4" s="161" t="inlineStr">
         <is>
           <t>NET Score</t>
@@ -9388,10 +9388,10 @@
       <c r="J4" s="163" t="n"/>
       <c r="K4" s="163" t="n"/>
       <c r="L4" s="164" t="n"/>
-      <c r="M4" s="210" t="n"/>
-      <c r="N4" s="201" t="n"/>
-      <c r="O4" s="203" t="n"/>
-      <c r="Q4" s="214" t="inlineStr">
+      <c r="M4" s="231" t="n"/>
+      <c r="N4" s="232" t="n"/>
+      <c r="O4" s="233" t="n"/>
+      <c r="Q4" s="203" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
@@ -9407,11 +9407,11 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="12.95" customHeight="1" s="181">
-      <c r="A5" s="217" t="n">
+    <row r="5" ht="12.95" customHeight="1" s="219">
+      <c r="A5" s="206" t="n">
         <v>2</v>
       </c>
-      <c r="B5" s="211">
+      <c r="B5" s="201">
         <f>Schedule!C16</f>
         <v/>
       </c>
@@ -9426,7 +9426,9 @@
       <c r="E5" s="166" t="n">
         <v>7</v>
       </c>
-      <c r="F5" s="166" t="n"/>
+      <c r="F5" s="166" t="n">
+        <v>7</v>
+      </c>
       <c r="G5" s="166" t="n">
         <v>7</v>
       </c>
@@ -9435,16 +9437,16 @@
       <c r="J5" s="166" t="n"/>
       <c r="K5" s="166" t="n"/>
       <c r="L5" s="167" t="n"/>
-      <c r="M5" s="213" t="n">
-        <v>20</v>
-      </c>
-      <c r="N5" s="212" t="inlineStr">
-        <is>
-          <t>3-0-0</t>
-        </is>
-      </c>
-      <c r="O5" s="204" t="n">
-        <v>39</v>
+      <c r="M5" s="204" t="n">
+        <v>27</v>
+      </c>
+      <c r="N5" s="199" t="inlineStr">
+        <is>
+          <t>4-0-0</t>
+        </is>
+      </c>
+      <c r="O5" s="196" t="n">
+        <v>38</v>
       </c>
       <c r="Q5" s="33" t="n">
         <v>1</v>
@@ -9452,8 +9454,8 @@
       <c r="R5" s="34" t="n"/>
       <c r="S5" s="35" t="n"/>
     </row>
-    <row r="6" ht="13.5" customHeight="1" s="181" thickBot="1">
-      <c r="B6" s="208" t="n"/>
+    <row r="6" ht="13.5" customHeight="1" s="219" thickBot="1">
+      <c r="B6" s="234" t="n"/>
       <c r="C6" s="168" t="inlineStr">
         <is>
           <t>NET Score</t>
@@ -9465,7 +9467,9 @@
       <c r="E6" s="170" t="n">
         <v>36</v>
       </c>
-      <c r="F6" s="170" t="n"/>
+      <c r="F6" s="170" t="n">
+        <v>35</v>
+      </c>
       <c r="G6" s="170" t="n">
         <v>42</v>
       </c>
@@ -9474,20 +9478,20 @@
       <c r="J6" s="170" t="n"/>
       <c r="K6" s="170" t="n"/>
       <c r="L6" s="171" t="n"/>
-      <c r="M6" s="210" t="n"/>
-      <c r="N6" s="201" t="n"/>
-      <c r="O6" s="203" t="n"/>
+      <c r="M6" s="231" t="n"/>
+      <c r="N6" s="232" t="n"/>
+      <c r="O6" s="233" t="n"/>
       <c r="Q6" s="36" t="n">
         <v>2</v>
       </c>
       <c r="R6" s="37" t="n"/>
       <c r="S6" s="38" t="n"/>
     </row>
-    <row r="7" ht="12.95" customHeight="1" s="181">
-      <c r="A7" s="217" t="n">
+    <row r="7" ht="12.95" customHeight="1" s="219">
+      <c r="A7" s="206" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="207">
+      <c r="B7" s="197">
         <f>Schedule!C17</f>
         <v/>
       </c>
@@ -9509,7 +9513,7 @@
       <c r="J7" s="200" t="n"/>
       <c r="K7" s="200" t="n"/>
       <c r="L7" s="160" t="n"/>
-      <c r="M7" s="209" t="n">
+      <c r="M7" s="202" t="n">
         <v>5</v>
       </c>
       <c r="N7" s="200" t="inlineStr">
@@ -9517,7 +9521,7 @@
           <t>0-1-1</t>
         </is>
       </c>
-      <c r="O7" s="202" t="n">
+      <c r="O7" s="208" t="n">
         <v>41</v>
       </c>
       <c r="Q7" s="33" t="n">
@@ -9526,8 +9530,8 @@
       <c r="R7" s="34" t="n"/>
       <c r="S7" s="35" t="n"/>
     </row>
-    <row r="8" ht="13.5" customHeight="1" s="181" thickBot="1">
-      <c r="B8" s="208" t="n"/>
+    <row r="8" ht="13.5" customHeight="1" s="219" thickBot="1">
+      <c r="B8" s="234" t="n"/>
       <c r="C8" s="161" t="inlineStr">
         <is>
           <t>NET Score</t>
@@ -9546,20 +9550,20 @@
       <c r="J8" s="163" t="n"/>
       <c r="K8" s="163" t="n"/>
       <c r="L8" s="164" t="n"/>
-      <c r="M8" s="210" t="n"/>
-      <c r="N8" s="201" t="n"/>
-      <c r="O8" s="203" t="n"/>
+      <c r="M8" s="231" t="n"/>
+      <c r="N8" s="232" t="n"/>
+      <c r="O8" s="233" t="n"/>
       <c r="Q8" s="39" t="n">
         <v>4</v>
       </c>
       <c r="R8" s="40" t="n"/>
       <c r="S8" s="41" t="n"/>
     </row>
-    <row r="9" ht="12.95" customHeight="1" s="181" thickBot="1">
-      <c r="A9" s="217" t="n">
+    <row r="9" ht="12.95" customHeight="1" s="219" thickBot="1">
+      <c r="A9" s="206" t="n">
         <v>4</v>
       </c>
-      <c r="B9" s="211">
+      <c r="B9" s="201">
         <f>Schedule!C18</f>
         <v/>
       </c>
@@ -9581,20 +9585,20 @@
       <c r="J9" s="166" t="n"/>
       <c r="K9" s="166" t="n"/>
       <c r="L9" s="167" t="n"/>
-      <c r="M9" s="213" t="n">
+      <c r="M9" s="204" t="n">
         <v>8</v>
       </c>
-      <c r="N9" s="212" t="inlineStr">
+      <c r="N9" s="199" t="inlineStr">
         <is>
           <t>1-1-0</t>
         </is>
       </c>
-      <c r="O9" s="204" t="n">
+      <c r="O9" s="196" t="n">
         <v>42.5</v>
       </c>
     </row>
-    <row r="10" ht="13.5" customHeight="1" s="181" thickBot="1">
-      <c r="B10" s="208" t="n"/>
+    <row r="10" ht="13.5" customHeight="1" s="219" thickBot="1">
+      <c r="B10" s="234" t="n"/>
       <c r="C10" s="168" t="inlineStr">
         <is>
           <t>NET Score</t>
@@ -9613,21 +9617,21 @@
       <c r="J10" s="170" t="n"/>
       <c r="K10" s="170" t="n"/>
       <c r="L10" s="171" t="n"/>
-      <c r="M10" s="210" t="n"/>
-      <c r="N10" s="201" t="n"/>
-      <c r="O10" s="203" t="n"/>
-      <c r="R10" s="214" t="inlineStr">
+      <c r="M10" s="231" t="n"/>
+      <c r="N10" s="232" t="n"/>
+      <c r="O10" s="233" t="n"/>
+      <c r="R10" s="203" t="inlineStr">
         <is>
           <t>Playoff Matchups</t>
         </is>
       </c>
-      <c r="S10" s="215" t="n"/>
-    </row>
-    <row r="11" ht="12.95" customHeight="1" s="181">
-      <c r="A11" s="217" t="n">
+      <c r="S10" s="235" t="n"/>
+    </row>
+    <row r="11" ht="12.95" customHeight="1" s="219">
+      <c r="A11" s="206" t="n">
         <v>5</v>
       </c>
-      <c r="B11" s="207">
+      <c r="B11" s="197">
         <f>Schedule!C19</f>
         <v/>
       </c>
@@ -9642,23 +9646,25 @@
       <c r="E11" s="200" t="n">
         <v>6</v>
       </c>
-      <c r="F11" s="200" t="n"/>
+      <c r="F11" s="200" t="n">
+        <v>1</v>
+      </c>
       <c r="G11" s="200" t="n"/>
       <c r="H11" s="200" t="n"/>
       <c r="I11" s="200" t="n"/>
       <c r="J11" s="200" t="n"/>
       <c r="K11" s="200" t="n"/>
       <c r="L11" s="160" t="n"/>
-      <c r="M11" s="209" t="n">
-        <v>6</v>
+      <c r="M11" s="202" t="n">
+        <v>7</v>
       </c>
       <c r="N11" s="200" t="inlineStr">
         <is>
-          <t>1-1-0</t>
-        </is>
-      </c>
-      <c r="O11" s="202" t="n">
-        <v>44.5</v>
+          <t>1-2-0</t>
+        </is>
+      </c>
+      <c r="O11" s="208" t="n">
+        <v>44</v>
       </c>
       <c r="R11" s="36" t="inlineStr">
         <is>
@@ -9671,8 +9677,8 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="13.5" customHeight="1" s="181" thickBot="1">
-      <c r="B12" s="208" t="n"/>
+    <row r="12" ht="13.5" customHeight="1" s="219" thickBot="1">
+      <c r="B12" s="234" t="n"/>
       <c r="C12" s="161" t="inlineStr">
         <is>
           <t>NET Score</t>
@@ -9684,16 +9690,18 @@
       <c r="E12" s="163" t="n">
         <v>43</v>
       </c>
-      <c r="F12" s="163" t="n"/>
+      <c r="F12" s="163" t="n">
+        <v>43</v>
+      </c>
       <c r="G12" s="163" t="n"/>
       <c r="H12" s="163" t="n"/>
       <c r="I12" s="163" t="n"/>
       <c r="J12" s="163" t="n"/>
       <c r="K12" s="163" t="n"/>
       <c r="L12" s="164" t="n"/>
-      <c r="M12" s="210" t="n"/>
-      <c r="N12" s="201" t="n"/>
-      <c r="O12" s="203" t="n"/>
+      <c r="M12" s="231" t="n"/>
+      <c r="N12" s="232" t="n"/>
+      <c r="O12" s="233" t="n"/>
       <c r="R12" s="36" t="inlineStr">
         <is>
           <t>1 vs 4</t>
@@ -9705,11 +9713,11 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="12.95" customHeight="1" s="181" thickBot="1">
-      <c r="A13" s="217" t="n">
+    <row r="13" ht="12.95" customHeight="1" s="219" thickBot="1">
+      <c r="A13" s="206" t="n">
         <v>6</v>
       </c>
-      <c r="B13" s="211">
+      <c r="B13" s="201">
         <f>Schedule!C20</f>
         <v/>
       </c>
@@ -9731,15 +9739,15 @@
       <c r="J13" s="166" t="n"/>
       <c r="K13" s="166" t="n"/>
       <c r="L13" s="167" t="n"/>
-      <c r="M13" s="213" t="n">
+      <c r="M13" s="204" t="n">
         <v>10</v>
       </c>
-      <c r="N13" s="212" t="inlineStr">
+      <c r="N13" s="199" t="inlineStr">
         <is>
           <t>1-1-0</t>
         </is>
       </c>
-      <c r="O13" s="204" t="n">
+      <c r="O13" s="196" t="n">
         <v>36</v>
       </c>
       <c r="R13" s="39" t="inlineStr">
@@ -9753,8 +9761,8 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="13.5" customHeight="1" s="181" thickBot="1">
-      <c r="B14" s="208" t="n"/>
+    <row r="14" ht="13.5" customHeight="1" s="219" thickBot="1">
+      <c r="B14" s="234" t="n"/>
       <c r="C14" s="168" t="inlineStr">
         <is>
           <t>NET Score</t>
@@ -9773,15 +9781,15 @@
       <c r="J14" s="170" t="n"/>
       <c r="K14" s="170" t="n"/>
       <c r="L14" s="171" t="n"/>
-      <c r="M14" s="210" t="n"/>
-      <c r="N14" s="201" t="n"/>
-      <c r="O14" s="203" t="n"/>
-    </row>
-    <row r="15" ht="12.95" customHeight="1" s="181">
-      <c r="A15" s="217" t="n">
+      <c r="M14" s="231" t="n"/>
+      <c r="N14" s="232" t="n"/>
+      <c r="O14" s="233" t="n"/>
+    </row>
+    <row r="15" ht="12.95" customHeight="1" s="219">
+      <c r="A15" s="206" t="n">
         <v>7</v>
       </c>
-      <c r="B15" s="207">
+      <c r="B15" s="197">
         <f>Schedule!C21</f>
         <v/>
       </c>
@@ -9807,7 +9815,7 @@
       <c r="J15" s="200" t="n"/>
       <c r="K15" s="200" t="n"/>
       <c r="L15" s="160" t="n"/>
-      <c r="M15" s="209" t="n">
+      <c r="M15" s="202" t="n">
         <v>11</v>
       </c>
       <c r="N15" s="200" t="inlineStr">
@@ -9815,12 +9823,12 @@
           <t>1-3-0</t>
         </is>
       </c>
-      <c r="O15" s="202" t="n">
+      <c r="O15" s="208" t="n">
         <v>46.2</v>
       </c>
     </row>
-    <row r="16" ht="13.5" customHeight="1" s="181" thickBot="1">
-      <c r="B16" s="208" t="n"/>
+    <row r="16" ht="13.5" customHeight="1" s="219" thickBot="1">
+      <c r="B16" s="234" t="n"/>
       <c r="C16" s="161" t="inlineStr">
         <is>
           <t>NET Score</t>
@@ -9843,15 +9851,15 @@
       <c r="J16" s="163" t="n"/>
       <c r="K16" s="163" t="n"/>
       <c r="L16" s="164" t="n"/>
-      <c r="M16" s="210" t="n"/>
-      <c r="N16" s="201" t="n"/>
-      <c r="O16" s="203" t="n"/>
-    </row>
-    <row r="17" ht="12.95" customHeight="1" s="181">
-      <c r="A17" s="217" t="n">
+      <c r="M16" s="231" t="n"/>
+      <c r="N16" s="232" t="n"/>
+      <c r="O16" s="233" t="n"/>
+    </row>
+    <row r="17" ht="12.95" customHeight="1" s="219">
+      <c r="A17" s="206" t="n">
         <v>8</v>
       </c>
-      <c r="B17" s="211">
+      <c r="B17" s="201">
         <f>Schedule!C22</f>
         <v/>
       </c>
@@ -9875,25 +9883,25 @@
       <c r="J17" s="166" t="n"/>
       <c r="K17" s="166" t="n"/>
       <c r="L17" s="167" t="n"/>
-      <c r="M17" s="213" t="n">
+      <c r="M17" s="204" t="n">
         <v>21</v>
       </c>
-      <c r="N17" s="212" t="inlineStr">
+      <c r="N17" s="199" t="inlineStr">
         <is>
           <t>3-0-0</t>
         </is>
       </c>
-      <c r="O17" s="204" t="n">
+      <c r="O17" s="196" t="n">
         <v>37.3</v>
       </c>
-      <c r="Q17" s="216" t="inlineStr">
+      <c r="Q17" s="205" t="inlineStr">
         <is>
           <t>Tiebreaker Rules</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="13.5" customHeight="1" s="181" thickBot="1">
-      <c r="B18" s="208" t="n"/>
+    <row r="18" ht="13.5" customHeight="1" s="219" thickBot="1">
+      <c r="B18" s="234" t="n"/>
       <c r="C18" s="168" t="inlineStr">
         <is>
           <t>NET Score</t>
@@ -9914,9 +9922,9 @@
       <c r="J18" s="170" t="n"/>
       <c r="K18" s="170" t="n"/>
       <c r="L18" s="171" t="n"/>
-      <c r="M18" s="210" t="n"/>
-      <c r="N18" s="201" t="n"/>
-      <c r="O18" s="203" t="n"/>
+      <c r="M18" s="231" t="n"/>
+      <c r="N18" s="232" t="n"/>
+      <c r="O18" s="233" t="n"/>
       <c r="Q18" s="154" t="inlineStr">
         <is>
           <t>1. Highest overall match wins. A match win means you scored 4.5 points or more against your opponent. 4 points will be considered a draw.</t>
@@ -9924,11 +9932,11 @@
       </c>
       <c r="R18" s="21" t="n"/>
     </row>
-    <row r="19" ht="12.95" customHeight="1" s="181">
-      <c r="A19" s="217" t="n">
+    <row r="19" ht="12.95" customHeight="1" s="219">
+      <c r="A19" s="206" t="n">
         <v>9</v>
       </c>
-      <c r="B19" s="207">
+      <c r="B19" s="197">
         <f>Schedule!C23</f>
         <v/>
       </c>
@@ -9954,7 +9962,7 @@
       <c r="J19" s="200" t="n"/>
       <c r="K19" s="200" t="n"/>
       <c r="L19" s="160" t="n"/>
-      <c r="M19" s="209" t="n">
+      <c r="M19" s="202" t="n">
         <v>22.5</v>
       </c>
       <c r="N19" s="200" t="inlineStr">
@@ -9962,7 +9970,7 @@
           <t>3-1-0</t>
         </is>
       </c>
-      <c r="O19" s="202" t="n">
+      <c r="O19" s="208" t="n">
         <v>38.8</v>
       </c>
       <c r="Q19" s="154" t="inlineStr">
@@ -9971,8 +9979,8 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="13.5" customHeight="1" s="181" thickBot="1">
-      <c r="B20" s="208" t="n"/>
+    <row r="20" ht="13.5" customHeight="1" s="219" thickBot="1">
+      <c r="B20" s="234" t="n"/>
       <c r="C20" s="161" t="inlineStr">
         <is>
           <t>NET Score</t>
@@ -9995,9 +10003,9 @@
       <c r="J20" s="163" t="n"/>
       <c r="K20" s="163" t="n"/>
       <c r="L20" s="164" t="n"/>
-      <c r="M20" s="210" t="n"/>
-      <c r="N20" s="201" t="n"/>
-      <c r="O20" s="203" t="n"/>
+      <c r="M20" s="231" t="n"/>
+      <c r="N20" s="232" t="n"/>
+      <c r="O20" s="233" t="n"/>
       <c r="Q20" s="154" t="inlineStr">
         <is>
           <t>3. Lowest Round 8 NET score.</t>
@@ -10005,11 +10013,11 @@
       </c>
       <c r="R20" s="21" t="n"/>
     </row>
-    <row r="21" ht="12.95" customHeight="1" s="181">
-      <c r="A21" s="217" t="n">
+    <row r="21" ht="12.95" customHeight="1" s="219">
+      <c r="A21" s="206" t="n">
         <v>10</v>
       </c>
-      <c r="B21" s="211">
+      <c r="B21" s="201">
         <f>Schedule!C24</f>
         <v/>
       </c>
@@ -10033,15 +10041,15 @@
       <c r="J21" s="166" t="n"/>
       <c r="K21" s="166" t="n"/>
       <c r="L21" s="167" t="n"/>
-      <c r="M21" s="213" t="n">
+      <c r="M21" s="204" t="n">
         <v>22</v>
       </c>
-      <c r="N21" s="212" t="inlineStr">
+      <c r="N21" s="199" t="inlineStr">
         <is>
           <t>3-0-0</t>
         </is>
       </c>
-      <c r="O21" s="204" t="n">
+      <c r="O21" s="196" t="n">
         <v>39.3</v>
       </c>
       <c r="Q21" s="154" t="inlineStr">
@@ -10051,8 +10059,8 @@
       </c>
       <c r="R21" s="21" t="n"/>
     </row>
-    <row r="22" ht="13.5" customHeight="1" s="181" thickBot="1">
-      <c r="B22" s="208" t="n"/>
+    <row r="22" ht="13.5" customHeight="1" s="219" thickBot="1">
+      <c r="B22" s="234" t="n"/>
       <c r="C22" s="168" t="inlineStr">
         <is>
           <t>NET Score</t>
@@ -10073,15 +10081,15 @@
       <c r="J22" s="170" t="n"/>
       <c r="K22" s="170" t="n"/>
       <c r="L22" s="171" t="n"/>
-      <c r="M22" s="210" t="n"/>
-      <c r="N22" s="201" t="n"/>
-      <c r="O22" s="203" t="n"/>
-    </row>
-    <row r="23" ht="12.95" customHeight="1" s="181">
-      <c r="A23" s="217" t="n">
+      <c r="M22" s="231" t="n"/>
+      <c r="N22" s="232" t="n"/>
+      <c r="O22" s="233" t="n"/>
+    </row>
+    <row r="23" ht="12.95" customHeight="1" s="219">
+      <c r="A23" s="206" t="n">
         <v>11</v>
       </c>
-      <c r="B23" s="207">
+      <c r="B23" s="197">
         <f>Schedule!C25</f>
         <v/>
       </c>
@@ -10105,7 +10113,7 @@
       <c r="J23" s="200" t="n"/>
       <c r="K23" s="200" t="n"/>
       <c r="L23" s="160" t="n"/>
-      <c r="M23" s="209" t="n">
+      <c r="M23" s="202" t="n">
         <v>19</v>
       </c>
       <c r="N23" s="200" t="inlineStr">
@@ -10113,12 +10121,12 @@
           <t>2-0-1</t>
         </is>
       </c>
-      <c r="O23" s="202" t="n">
+      <c r="O23" s="208" t="n">
         <v>46</v>
       </c>
     </row>
-    <row r="24" ht="13.5" customHeight="1" s="181" thickBot="1">
-      <c r="B24" s="208" t="n"/>
+    <row r="24" ht="13.5" customHeight="1" s="219" thickBot="1">
+      <c r="B24" s="234" t="n"/>
       <c r="C24" s="161" t="inlineStr">
         <is>
           <t>NET Score</t>
@@ -10139,15 +10147,15 @@
       <c r="J24" s="163" t="n"/>
       <c r="K24" s="163" t="n"/>
       <c r="L24" s="164" t="n"/>
-      <c r="M24" s="210" t="n"/>
-      <c r="N24" s="201" t="n"/>
-      <c r="O24" s="203" t="n"/>
-    </row>
-    <row r="25" ht="12.95" customHeight="1" s="181">
-      <c r="A25" s="217" t="n">
+      <c r="M24" s="231" t="n"/>
+      <c r="N24" s="232" t="n"/>
+      <c r="O24" s="233" t="n"/>
+    </row>
+    <row r="25" ht="12.95" customHeight="1" s="219">
+      <c r="A25" s="206" t="n">
         <v>12</v>
       </c>
-      <c r="B25" s="211">
+      <c r="B25" s="201">
         <f>Schedule!C26</f>
         <v/>
       </c>
@@ -10166,25 +10174,27 @@
         <v>1</v>
       </c>
       <c r="G25" s="166" t="n"/>
-      <c r="H25" s="166" t="n"/>
+      <c r="H25" s="166" t="n">
+        <v>6</v>
+      </c>
       <c r="I25" s="166" t="n"/>
       <c r="J25" s="166" t="n"/>
       <c r="K25" s="166" t="n"/>
       <c r="L25" s="167" t="n"/>
-      <c r="M25" s="213" t="n">
-        <v>5</v>
-      </c>
-      <c r="N25" s="212" t="inlineStr">
-        <is>
-          <t>0-2-1</t>
-        </is>
-      </c>
-      <c r="O25" s="204" t="n">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="26" ht="13.5" customHeight="1" s="181" thickBot="1">
-      <c r="B26" s="208" t="n"/>
+      <c r="M25" s="204" t="n">
+        <v>11</v>
+      </c>
+      <c r="N25" s="199" t="inlineStr">
+        <is>
+          <t>1-2-1</t>
+        </is>
+      </c>
+      <c r="O25" s="196" t="n">
+        <v>53.5</v>
+      </c>
+    </row>
+    <row r="26" ht="13.5" customHeight="1" s="219" thickBot="1">
+      <c r="B26" s="234" t="n"/>
       <c r="C26" s="168" t="inlineStr">
         <is>
           <t>NET Score</t>
@@ -10200,20 +10210,22 @@
         <v>54</v>
       </c>
       <c r="G26" s="170" t="n"/>
-      <c r="H26" s="170" t="n"/>
+      <c r="H26" s="170" t="n">
+        <v>52</v>
+      </c>
       <c r="I26" s="170" t="n"/>
       <c r="J26" s="170" t="n"/>
       <c r="K26" s="170" t="n"/>
       <c r="L26" s="171" t="n"/>
-      <c r="M26" s="210" t="n"/>
-      <c r="N26" s="201" t="n"/>
-      <c r="O26" s="203" t="n"/>
-    </row>
-    <row r="27" ht="12.95" customHeight="1" s="181">
-      <c r="A27" s="217" t="n">
+      <c r="M26" s="231" t="n"/>
+      <c r="N26" s="232" t="n"/>
+      <c r="O26" s="233" t="n"/>
+    </row>
+    <row r="27" ht="12.95" customHeight="1" s="219">
+      <c r="A27" s="206" t="n">
         <v>13</v>
       </c>
-      <c r="B27" s="207">
+      <c r="B27" s="197">
         <f>Schedule!C27</f>
         <v/>
       </c>
@@ -10241,7 +10253,7 @@
       <c r="J27" s="200" t="n"/>
       <c r="K27" s="200" t="n"/>
       <c r="L27" s="160" t="n"/>
-      <c r="M27" s="209" t="n">
+      <c r="M27" s="202" t="n">
         <v>12</v>
       </c>
       <c r="N27" s="200" t="inlineStr">
@@ -10249,12 +10261,12 @@
           <t>1-3-1</t>
         </is>
       </c>
-      <c r="O27" s="202" t="n">
+      <c r="O27" s="208" t="n">
         <v>51.4</v>
       </c>
     </row>
-    <row r="28" ht="13.5" customHeight="1" s="181" thickBot="1">
-      <c r="B28" s="208" t="n"/>
+    <row r="28" ht="13.5" customHeight="1" s="219" thickBot="1">
+      <c r="B28" s="234" t="n"/>
       <c r="C28" s="161" t="inlineStr">
         <is>
           <t>NET Score</t>
@@ -10279,15 +10291,15 @@
       <c r="J28" s="163" t="n"/>
       <c r="K28" s="163" t="n"/>
       <c r="L28" s="164" t="n"/>
-      <c r="M28" s="210" t="n"/>
-      <c r="N28" s="201" t="n"/>
-      <c r="O28" s="203" t="n"/>
-    </row>
-    <row r="29" ht="12.95" customHeight="1" s="181">
-      <c r="A29" s="217" t="n">
+      <c r="M28" s="231" t="n"/>
+      <c r="N28" s="232" t="n"/>
+      <c r="O28" s="233" t="n"/>
+    </row>
+    <row r="29" ht="12.95" customHeight="1" s="219">
+      <c r="A29" s="206" t="n">
         <v>14</v>
       </c>
-      <c r="B29" s="211">
+      <c r="B29" s="201">
         <f>Schedule!C28</f>
         <v/>
       </c>
@@ -10315,20 +10327,20 @@
       <c r="J29" s="166" t="n"/>
       <c r="K29" s="166" t="n"/>
       <c r="L29" s="167" t="n"/>
-      <c r="M29" s="213" t="n">
+      <c r="M29" s="204" t="n">
         <v>11.5</v>
       </c>
-      <c r="N29" s="212" t="inlineStr">
+      <c r="N29" s="199" t="inlineStr">
         <is>
           <t>1-4-0</t>
         </is>
       </c>
-      <c r="O29" s="204" t="n">
+      <c r="O29" s="196" t="n">
         <v>50.2</v>
       </c>
     </row>
-    <row r="30" ht="13.5" customHeight="1" s="181" thickBot="1">
-      <c r="B30" s="208" t="n"/>
+    <row r="30" ht="13.5" customHeight="1" s="219" thickBot="1">
+      <c r="B30" s="234" t="n"/>
       <c r="C30" s="168" t="inlineStr">
         <is>
           <t>NET Score</t>
@@ -10353,15 +10365,15 @@
       <c r="J30" s="170" t="n"/>
       <c r="K30" s="170" t="n"/>
       <c r="L30" s="171" t="n"/>
-      <c r="M30" s="210" t="n"/>
-      <c r="N30" s="201" t="n"/>
-      <c r="O30" s="203" t="n"/>
-    </row>
-    <row r="31" ht="12.95" customHeight="1" s="181">
-      <c r="A31" s="217" t="n">
+      <c r="M30" s="231" t="n"/>
+      <c r="N30" s="232" t="n"/>
+      <c r="O30" s="233" t="n"/>
+    </row>
+    <row r="31" ht="12.95" customHeight="1" s="219">
+      <c r="A31" s="206" t="n">
         <v>15</v>
       </c>
-      <c r="B31" s="207">
+      <c r="B31" s="197">
         <f>Schedule!C29</f>
         <v/>
       </c>
@@ -10380,25 +10392,27 @@
       <c r="G31" s="200" t="n">
         <v>4</v>
       </c>
-      <c r="H31" s="200" t="n"/>
+      <c r="H31" s="200" t="n">
+        <v>2</v>
+      </c>
       <c r="I31" s="200" t="n"/>
       <c r="J31" s="200" t="n"/>
       <c r="K31" s="200" t="n"/>
       <c r="L31" s="160" t="n"/>
-      <c r="M31" s="209" t="n">
-        <v>5</v>
+      <c r="M31" s="202" t="n">
+        <v>7</v>
       </c>
       <c r="N31" s="200" t="inlineStr">
         <is>
-          <t>0-2-1</t>
-        </is>
-      </c>
-      <c r="O31" s="202" t="n">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="32" ht="13.5" customHeight="1" s="181" thickBot="1">
-      <c r="B32" s="208" t="n"/>
+          <t>0-3-1</t>
+        </is>
+      </c>
+      <c r="O31" s="208" t="n">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="32" ht="13.5" customHeight="1" s="219" thickBot="1">
+      <c r="B32" s="234" t="n"/>
       <c r="C32" s="161" t="inlineStr">
         <is>
           <t>NET Score</t>
@@ -10414,14 +10428,16 @@
       <c r="G32" s="163" t="n">
         <v>43</v>
       </c>
-      <c r="H32" s="163" t="n"/>
+      <c r="H32" s="163" t="n">
+        <v>54</v>
+      </c>
       <c r="I32" s="163" t="n"/>
       <c r="J32" s="163" t="n"/>
       <c r="K32" s="163" t="n"/>
       <c r="L32" s="164" t="n"/>
-      <c r="M32" s="210" t="n"/>
-      <c r="N32" s="201" t="n"/>
-      <c r="O32" s="203" t="n"/>
+      <c r="M32" s="231" t="n"/>
+      <c r="N32" s="232" t="n"/>
+      <c r="O32" s="233" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" algorithmName="SHA-512" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" saltValue="kkQ/PatKpMHBAJY782mRBw==" formatRows="1" sort="1" spinCount="100000" password="94CD" hashValue="Y3y62YBPDCQhqKgsSl1/iH5xODfF8lm4IgTCoiweq2jLnTBBsjKN4ZDmcY+ulNgK91riyyuYS5VZZqKHpfKB8g=="/>
@@ -10433,33 +10449,32 @@
     <mergeCell ref="N3:N4"/>
     <mergeCell ref="B17:B18"/>
     <mergeCell ref="M11:M12"/>
+    <mergeCell ref="R10:S10"/>
     <mergeCell ref="B11:B12"/>
-    <mergeCell ref="R10:S10"/>
     <mergeCell ref="N21:N22"/>
     <mergeCell ref="M7:M8"/>
     <mergeCell ref="B29:B30"/>
     <mergeCell ref="B23:B24"/>
     <mergeCell ref="N5:N6"/>
     <mergeCell ref="M15:M16"/>
-    <mergeCell ref="O29:O30"/>
+    <mergeCell ref="M13:M14"/>
     <mergeCell ref="M31:M32"/>
     <mergeCell ref="B13:B14"/>
     <mergeCell ref="N17:N18"/>
     <mergeCell ref="M25:M26"/>
     <mergeCell ref="M3:M4"/>
+    <mergeCell ref="O29:O30"/>
     <mergeCell ref="O25:O26"/>
-    <mergeCell ref="M13:M14"/>
-    <mergeCell ref="M5:M6"/>
     <mergeCell ref="Q17:S17"/>
+    <mergeCell ref="N29:N30"/>
     <mergeCell ref="O21:O22"/>
-    <mergeCell ref="N29:N30"/>
+    <mergeCell ref="N23:N24"/>
+    <mergeCell ref="B19:B20"/>
     <mergeCell ref="N1:O1"/>
-    <mergeCell ref="B19:B20"/>
+    <mergeCell ref="N19:N20"/>
+    <mergeCell ref="B15:B16"/>
     <mergeCell ref="O31:O32"/>
     <mergeCell ref="M27:M28"/>
-    <mergeCell ref="N19:N20"/>
-    <mergeCell ref="B15:B16"/>
-    <mergeCell ref="N23:N24"/>
     <mergeCell ref="B9:B10"/>
     <mergeCell ref="N13:N14"/>
     <mergeCell ref="M21:M22"/>
@@ -10469,15 +10484,16 @@
     <mergeCell ref="N31:N32"/>
     <mergeCell ref="O11:O12"/>
     <mergeCell ref="O27:O28"/>
+    <mergeCell ref="N15:N16"/>
     <mergeCell ref="O7:O8"/>
-    <mergeCell ref="N15:N16"/>
     <mergeCell ref="M23:M24"/>
     <mergeCell ref="B5:B6"/>
     <mergeCell ref="O23:O24"/>
+    <mergeCell ref="N11:N12"/>
     <mergeCell ref="Q3:S3"/>
-    <mergeCell ref="N11:N12"/>
     <mergeCell ref="O19:O20"/>
     <mergeCell ref="N27:N28"/>
+    <mergeCell ref="B31:B32"/>
     <mergeCell ref="O13:O14"/>
     <mergeCell ref="M29:M30"/>
     <mergeCell ref="M9:M10"/>
@@ -10489,7 +10505,7 @@
     <mergeCell ref="N7:N8"/>
     <mergeCell ref="B21:B22"/>
     <mergeCell ref="O15:O16"/>
-    <mergeCell ref="B31:B32"/>
+    <mergeCell ref="M5:M6"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="3" horizontalDpi="300" verticalDpi="300"/>
@@ -10505,39 +10521,39 @@
   <dimension ref="B1:AE24"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.85546875" defaultRowHeight="13.5"/>
   <cols>
-    <col width="2.5703125" customWidth="1" style="225" min="1" max="1"/>
-    <col width="27.85546875" customWidth="1" style="225" min="2" max="2"/>
-    <col width="9.85546875" customWidth="1" style="225" min="3" max="8"/>
-    <col width="10.7109375" bestFit="1" customWidth="1" style="225" min="9" max="9"/>
-    <col width="10.5703125" customWidth="1" style="225" min="10" max="11"/>
-    <col width="10.85546875" customWidth="1" style="225" min="12" max="13"/>
-    <col width="5.7109375" customWidth="1" style="225" min="14" max="14"/>
-    <col width="11" bestFit="1" customWidth="1" style="225" min="15" max="15"/>
-    <col width="4.5703125" customWidth="1" style="225" min="16" max="24"/>
-    <col width="7.5703125" customWidth="1" style="225" min="25" max="25"/>
-    <col width="9.85546875" customWidth="1" style="225" min="26" max="27"/>
-    <col width="16.42578125" bestFit="1" customWidth="1" style="225" min="28" max="28"/>
-    <col width="12.7109375" customWidth="1" style="225" min="29" max="30"/>
-    <col width="9.85546875" customWidth="1" style="225" min="31" max="45"/>
-    <col width="9.85546875" customWidth="1" style="225" min="46" max="16384"/>
+    <col width="2.5703125" customWidth="1" style="212" min="1" max="1"/>
+    <col width="27.85546875" customWidth="1" style="212" min="2" max="2"/>
+    <col width="9.85546875" customWidth="1" style="212" min="3" max="8"/>
+    <col width="10.7109375" bestFit="1" customWidth="1" style="212" min="9" max="9"/>
+    <col width="10.5703125" customWidth="1" style="212" min="10" max="11"/>
+    <col width="10.85546875" customWidth="1" style="212" min="12" max="13"/>
+    <col width="5.7109375" customWidth="1" style="212" min="14" max="14"/>
+    <col width="11" bestFit="1" customWidth="1" style="212" min="15" max="15"/>
+    <col width="4.5703125" customWidth="1" style="212" min="16" max="24"/>
+    <col width="7.5703125" customWidth="1" style="212" min="25" max="25"/>
+    <col width="9.85546875" customWidth="1" style="212" min="26" max="27"/>
+    <col width="16.42578125" bestFit="1" customWidth="1" style="212" min="28" max="28"/>
+    <col width="12.7109375" customWidth="1" style="212" min="29" max="30"/>
+    <col width="9.85546875" customWidth="1" style="212" min="31" max="46"/>
+    <col width="9.85546875" customWidth="1" style="212" min="47" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.25" customHeight="1" s="181" thickBot="1">
+    <row r="1" ht="14.25" customHeight="1" s="219" thickBot="1">
       <c r="B1" s="47" t="inlineStr">
         <is>
           <t>Fill in your name, tees, front/back 9, and gross scores in the grey boxes</t>
         </is>
       </c>
-      <c r="J1" s="222" t="inlineStr">
+      <c r="J1" s="216" t="inlineStr">
         <is>
           <t>Points</t>
         </is>
       </c>
-      <c r="K1" s="206" t="n"/>
-      <c r="L1" s="206" t="n"/>
-      <c r="M1" s="206" t="n"/>
-    </row>
-    <row r="2" ht="24.95" customHeight="1" s="181" thickBot="1">
+      <c r="K1" s="227" t="n"/>
+      <c r="L1" s="227" t="n"/>
+      <c r="M1" s="227" t="n"/>
+    </row>
+    <row r="2" ht="24.95" customHeight="1" s="219" thickBot="1">
       <c r="D2" s="49" t="inlineStr">
         <is>
           <t>First 3</t>
@@ -10564,16 +10580,16 @@
         </is>
       </c>
       <c r="I2" s="50" t="n"/>
-      <c r="J2" s="232">
+      <c r="J2" s="214">
         <f>B8</f>
         <v/>
       </c>
-      <c r="K2" s="199" t="n"/>
-      <c r="L2" s="228">
+      <c r="K2" s="229" t="n"/>
+      <c r="L2" s="210">
         <f>B17</f>
         <v/>
       </c>
-      <c r="M2" s="199" t="n"/>
+      <c r="M2" s="229" t="n"/>
       <c r="AA2" s="112" t="inlineStr">
         <is>
           <t>#</t>
@@ -10600,8 +10616,8 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="14.25" customHeight="1" s="181" thickBot="1">
-      <c r="B3" s="220">
+    <row r="3" ht="14.25" customHeight="1" s="219" thickBot="1">
+      <c r="B3" s="215">
         <f>B8</f>
         <v/>
       </c>
@@ -10630,16 +10646,16 @@
         <f>SUM(C14:K14)</f>
         <v/>
       </c>
-      <c r="J3" s="230">
+      <c r="J3" s="213">
         <f>SUM(D4:H4)</f>
         <v/>
       </c>
-      <c r="K3" s="224" t="n"/>
-      <c r="L3" s="223">
+      <c r="K3" s="236" t="n"/>
+      <c r="L3" s="217">
         <f>SUM(D6:H6)</f>
         <v/>
       </c>
-      <c r="M3" s="224" t="n"/>
+      <c r="M3" s="236" t="n"/>
       <c r="AA3" s="110" t="n">
         <v>13</v>
       </c>
@@ -10660,8 +10676,8 @@
         <v>25</v>
       </c>
     </row>
-    <row r="4" ht="14.25" customHeight="1" s="181" thickBot="1">
-      <c r="B4" s="221" t="n"/>
+    <row r="4" ht="14.25" customHeight="1" s="219" thickBot="1">
+      <c r="B4" s="237" t="n"/>
       <c r="C4" s="57" t="inlineStr">
         <is>
           <t>PTS</t>
@@ -10687,9 +10703,9 @@
         <f>IF(H3&lt;H5,1,IF(H3=H5,0.5,0))</f>
         <v/>
       </c>
-      <c r="J4" s="231" t="n"/>
-      <c r="K4" s="226" t="n"/>
-      <c r="M4" s="226" t="n"/>
+      <c r="J4" s="238" t="n"/>
+      <c r="K4" s="239" t="n"/>
+      <c r="M4" s="239" t="n"/>
       <c r="AA4" s="110" t="n">
         <v>17</v>
       </c>
@@ -10710,8 +10726,8 @@
         <v>30</v>
       </c>
     </row>
-    <row r="5" ht="14.25" customHeight="1" s="181" thickBot="1">
-      <c r="B5" s="220">
+    <row r="5" ht="14.25" customHeight="1" s="219" thickBot="1">
+      <c r="B5" s="215">
         <f>B17</f>
         <v/>
       </c>
@@ -10740,10 +10756,10 @@
         <f>SUM(C23:K23)</f>
         <v/>
       </c>
-      <c r="J5" s="221" t="n"/>
-      <c r="K5" s="227" t="n"/>
-      <c r="L5" s="206" t="n"/>
-      <c r="M5" s="227" t="n"/>
+      <c r="J5" s="237" t="n"/>
+      <c r="K5" s="240" t="n"/>
+      <c r="L5" s="227" t="n"/>
+      <c r="M5" s="240" t="n"/>
       <c r="AA5" s="110" t="n">
         <v>4</v>
       </c>
@@ -10764,8 +10780,8 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" ht="14.25" customHeight="1" s="181" thickBot="1">
-      <c r="B6" s="221" t="n"/>
+    <row r="6" ht="14.25" customHeight="1" s="219" thickBot="1">
+      <c r="B6" s="237" t="n"/>
       <c r="C6" s="57" t="inlineStr">
         <is>
           <t>PTS</t>
@@ -10791,10 +10807,10 @@
         <f>IF(H5&lt;H3,1,IF(H5=H3,0.5,0))</f>
         <v/>
       </c>
-      <c r="J6" s="229" t="n"/>
-      <c r="K6" s="229" t="n"/>
-      <c r="L6" s="229" t="n"/>
-      <c r="M6" s="229" t="n"/>
+      <c r="J6" s="211" t="n"/>
+      <c r="K6" s="211" t="n"/>
+      <c r="L6" s="211" t="n"/>
+      <c r="M6" s="211" t="n"/>
       <c r="AA6" s="110" t="n">
         <v>11</v>
       </c>
@@ -10816,16 +10832,16 @@
       </c>
     </row>
     <row r="7">
-      <c r="C7" s="229" t="n"/>
-      <c r="D7" s="229" t="n"/>
-      <c r="E7" s="229" t="n"/>
-      <c r="F7" s="229" t="n"/>
-      <c r="G7" s="229" t="n"/>
-      <c r="H7" s="229" t="n"/>
-      <c r="I7" s="229" t="n"/>
-      <c r="J7" s="229" t="n"/>
-      <c r="K7" s="229" t="n"/>
-      <c r="L7" s="229" t="n"/>
+      <c r="C7" s="211" t="n"/>
+      <c r="D7" s="211" t="n"/>
+      <c r="E7" s="211" t="n"/>
+      <c r="F7" s="211" t="n"/>
+      <c r="G7" s="211" t="n"/>
+      <c r="H7" s="211" t="n"/>
+      <c r="I7" s="211" t="n"/>
+      <c r="J7" s="211" t="n"/>
+      <c r="K7" s="211" t="n"/>
+      <c r="L7" s="211" t="n"/>
       <c r="AA7" s="110" t="n">
         <v>5</v>
       </c>
@@ -10846,7 +10862,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" ht="19.5" customHeight="1" s="181" thickBot="1">
+    <row r="8" ht="19.5" customHeight="1" s="219" thickBot="1">
       <c r="B8" s="109" t="inlineStr">
         <is>
           <t>Ethan High</t>
@@ -10857,12 +10873,12 @@
           <t>Handicap:</t>
         </is>
       </c>
-      <c r="D8" s="229">
+      <c r="D8" s="211">
         <f>IFERROR(VLOOKUP(B8,$AB$3:$AE$21,4,0),0)</f>
         <v/>
       </c>
-      <c r="E8" s="229" t="n"/>
-      <c r="F8" s="229" t="inlineStr">
+      <c r="E8" s="211" t="n"/>
+      <c r="F8" s="211" t="inlineStr">
         <is>
           <t>Tees:</t>
         </is>
@@ -10872,8 +10888,8 @@
           <t>Black</t>
         </is>
       </c>
-      <c r="H8" s="229" t="n"/>
-      <c r="I8" s="229" t="inlineStr">
+      <c r="H8" s="211" t="n"/>
+      <c r="I8" s="211" t="inlineStr">
         <is>
           <t>Holes:</t>
         </is>
@@ -10883,14 +10899,14 @@
           <t>Front 9</t>
         </is>
       </c>
-      <c r="K8" s="229" t="n"/>
-      <c r="L8" s="229" t="n"/>
-      <c r="O8" s="225" t="inlineStr">
+      <c r="K8" s="211" t="n"/>
+      <c r="L8" s="211" t="n"/>
+      <c r="O8" s="212" t="inlineStr">
         <is>
           <t>HC's by Tees</t>
         </is>
       </c>
-      <c r="P8" s="229" t="inlineStr">
+      <c r="P8" s="211" t="inlineStr">
         <is>
           <t>Front 9</t>
         </is>
@@ -10915,7 +10931,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" s="181">
+    <row r="9" ht="15" customHeight="1" s="219">
       <c r="B9" s="64" t="inlineStr">
         <is>
           <t>HOLE</t>
@@ -10948,37 +10964,37 @@
       <c r="K9" s="67" t="n">
         <v>9</v>
       </c>
-      <c r="L9" s="229" t="n"/>
-      <c r="O9" s="225" t="inlineStr">
+      <c r="L9" s="211" t="n"/>
+      <c r="O9" s="212" t="inlineStr">
         <is>
           <t>Black</t>
         </is>
       </c>
-      <c r="P9" s="229" t="n">
+      <c r="P9" s="211" t="n">
         <v>1</v>
       </c>
-      <c r="Q9" s="229" t="n">
+      <c r="Q9" s="211" t="n">
         <v>9</v>
       </c>
-      <c r="R9" s="229" t="n">
+      <c r="R9" s="211" t="n">
         <v>7</v>
       </c>
-      <c r="S9" s="229" t="n">
+      <c r="S9" s="211" t="n">
         <v>13</v>
       </c>
-      <c r="T9" s="229" t="n">
+      <c r="T9" s="211" t="n">
         <v>15</v>
       </c>
-      <c r="U9" s="229" t="n">
+      <c r="U9" s="211" t="n">
         <v>5</v>
       </c>
-      <c r="V9" s="229" t="n">
+      <c r="V9" s="211" t="n">
         <v>11</v>
       </c>
-      <c r="W9" s="229" t="n">
+      <c r="W9" s="211" t="n">
         <v>3</v>
       </c>
-      <c r="X9" s="229" t="n">
+      <c r="X9" s="211" t="n">
         <v>17</v>
       </c>
       <c r="AA9" s="110" t="n">
@@ -11010,7 +11026,7 @@
       <c r="C10" s="69" t="n">
         <v>4</v>
       </c>
-      <c r="D10" s="229" t="n">
+      <c r="D10" s="211" t="n">
         <v>5</v>
       </c>
       <c r="E10" s="70" t="n">
@@ -11019,7 +11035,7 @@
       <c r="F10" s="69" t="n">
         <v>4</v>
       </c>
-      <c r="G10" s="229" t="n">
+      <c r="G10" s="211" t="n">
         <v>5</v>
       </c>
       <c r="H10" s="70" t="n">
@@ -11028,46 +11044,46 @@
       <c r="I10" s="69" t="n">
         <v>4</v>
       </c>
-      <c r="J10" s="229" t="n">
+      <c r="J10" s="211" t="n">
         <v>4</v>
       </c>
       <c r="K10" s="70" t="n">
         <v>4</v>
       </c>
-      <c r="L10" s="229">
+      <c r="L10" s="211">
         <f>SUM(C10:K10)</f>
         <v/>
       </c>
-      <c r="O10" s="225" t="inlineStr">
+      <c r="O10" s="212" t="inlineStr">
         <is>
           <t>Blue</t>
         </is>
       </c>
-      <c r="P10" s="229" t="n">
+      <c r="P10" s="211" t="n">
         <v>1</v>
       </c>
-      <c r="Q10" s="229" t="n">
+      <c r="Q10" s="211" t="n">
         <v>9</v>
       </c>
-      <c r="R10" s="229" t="n">
+      <c r="R10" s="211" t="n">
         <v>7</v>
       </c>
-      <c r="S10" s="229" t="n">
+      <c r="S10" s="211" t="n">
         <v>13</v>
       </c>
-      <c r="T10" s="229" t="n">
+      <c r="T10" s="211" t="n">
         <v>15</v>
       </c>
-      <c r="U10" s="229" t="n">
+      <c r="U10" s="211" t="n">
         <v>5</v>
       </c>
-      <c r="V10" s="229" t="n">
+      <c r="V10" s="211" t="n">
         <v>11</v>
       </c>
-      <c r="W10" s="229" t="n">
+      <c r="W10" s="211" t="n">
         <v>3</v>
       </c>
-      <c r="X10" s="229" t="n">
+      <c r="X10" s="211" t="n">
         <v>17</v>
       </c>
       <c r="AA10" s="110" t="n">
@@ -11100,7 +11116,7 @@
         <f t="array" ref="C11">_xlfn.IFS($J8="Back 9",VLOOKUP($G8,$O$15:$X$18,COLUMN()-1,0),$J8="Front 9",VLOOKUP($G8,$O$9:$X$12,COLUMN()-1,0))</f>
         <v/>
       </c>
-      <c r="D11" s="229">
+      <c r="D11" s="211">
         <f t="array" ref="D11">_xlfn.IFS($J8="Back 9",VLOOKUP($G8,$O$15:$X$18,COLUMN()-1,0),$J8="Front 9",VLOOKUP($G8,$O$9:$X$12,COLUMN()-1,0))</f>
         <v/>
       </c>
@@ -11112,7 +11128,7 @@
         <f t="array" ref="F11">_xlfn.IFS($J8="Back 9",VLOOKUP($G8,$O$15:$X$18,COLUMN()-1,0),$J8="Front 9",VLOOKUP($G8,$O$9:$X$12,COLUMN()-1,0))</f>
         <v/>
       </c>
-      <c r="G11" s="229">
+      <c r="G11" s="211">
         <f t="array" ref="G11">_xlfn.IFS($J8="Back 9",VLOOKUP($G8,$O$15:$X$18,COLUMN()-1,0),$J8="Front 9",VLOOKUP($G8,$O$9:$X$12,COLUMN()-1,0))</f>
         <v/>
       </c>
@@ -11124,7 +11140,7 @@
         <f t="array" ref="I11">_xlfn.IFS($J8="Back 9",VLOOKUP($G8,$O$15:$X$18,COLUMN()-1,0),$J8="Front 9",VLOOKUP($G8,$O$9:$X$12,COLUMN()-1,0))</f>
         <v/>
       </c>
-      <c r="J11" s="229">
+      <c r="J11" s="211">
         <f t="array" ref="J11">_xlfn.IFS($J8="Back 9",VLOOKUP($G8,$O$15:$X$18,COLUMN()-1,0),$J8="Front 9",VLOOKUP($G8,$O$9:$X$12,COLUMN()-1,0))</f>
         <v/>
       </c>
@@ -11132,37 +11148,37 @@
         <f t="array" ref="K11">_xlfn.IFS($J8="Back 9",VLOOKUP($G8,$O$15:$X$18,COLUMN()-1,0),$J8="Front 9",VLOOKUP($G8,$O$9:$X$12,COLUMN()-1,0))</f>
         <v/>
       </c>
-      <c r="L11" s="229" t="n"/>
-      <c r="O11" s="225" t="inlineStr">
+      <c r="L11" s="211" t="n"/>
+      <c r="O11" s="212" t="inlineStr">
         <is>
           <t>Blue / White</t>
         </is>
       </c>
-      <c r="P11" s="229" t="n">
+      <c r="P11" s="211" t="n">
         <v>3</v>
       </c>
-      <c r="Q11" s="229" t="n">
+      <c r="Q11" s="211" t="n">
         <v>7</v>
       </c>
-      <c r="R11" s="229" t="n">
+      <c r="R11" s="211" t="n">
         <v>13</v>
       </c>
-      <c r="S11" s="229" t="n">
+      <c r="S11" s="211" t="n">
         <v>17</v>
       </c>
-      <c r="T11" s="229" t="n">
+      <c r="T11" s="211" t="n">
         <v>15</v>
       </c>
-      <c r="U11" s="229" t="n">
+      <c r="U11" s="211" t="n">
         <v>1</v>
       </c>
-      <c r="V11" s="229" t="n">
+      <c r="V11" s="211" t="n">
         <v>11</v>
       </c>
-      <c r="W11" s="229" t="n">
+      <c r="W11" s="211" t="n">
         <v>5</v>
       </c>
-      <c r="X11" s="229" t="n">
+      <c r="X11" s="211" t="n">
         <v>9</v>
       </c>
       <c r="AA11" s="110" t="n">
@@ -11185,7 +11201,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1" s="181">
+    <row r="12" ht="15" customHeight="1" s="219">
       <c r="B12" s="71" t="inlineStr">
         <is>
           <t>GROSS</t>
@@ -11218,7 +11234,7 @@
       <c r="K12" s="115" t="n">
         <v>5</v>
       </c>
-      <c r="L12" s="229">
+      <c r="L12" s="211">
         <f>SUM(C12:K12)</f>
         <v/>
       </c>
@@ -11226,36 +11242,36 @@
         <f>SUM(C12:K12)-SUM(C$10:K$10)</f>
         <v/>
       </c>
-      <c r="O12" s="225" t="inlineStr">
+      <c r="O12" s="212" t="inlineStr">
         <is>
           <t>White</t>
         </is>
       </c>
-      <c r="P12" s="229" t="n">
+      <c r="P12" s="211" t="n">
         <v>1</v>
       </c>
-      <c r="Q12" s="229" t="n">
+      <c r="Q12" s="211" t="n">
         <v>7</v>
       </c>
-      <c r="R12" s="229" t="n">
+      <c r="R12" s="211" t="n">
         <v>11</v>
       </c>
-      <c r="S12" s="229" t="n">
+      <c r="S12" s="211" t="n">
         <v>13</v>
       </c>
-      <c r="T12" s="229" t="n">
+      <c r="T12" s="211" t="n">
         <v>15</v>
       </c>
-      <c r="U12" s="229" t="n">
+      <c r="U12" s="211" t="n">
         <v>9</v>
       </c>
-      <c r="V12" s="229" t="n">
+      <c r="V12" s="211" t="n">
         <v>17</v>
       </c>
-      <c r="W12" s="229" t="n">
+      <c r="W12" s="211" t="n">
         <v>3</v>
       </c>
-      <c r="X12" s="229" t="n">
+      <c r="X12" s="211" t="n">
         <v>5</v>
       </c>
       <c r="AA12" s="110" t="n">
@@ -11287,7 +11303,7 @@
       <c r="C13" s="69" t="n">
         <v>5</v>
       </c>
-      <c r="D13" s="229" t="n">
+      <c r="D13" s="211" t="n">
         <v>6</v>
       </c>
       <c r="E13" s="70" t="n">
@@ -11296,7 +11312,7 @@
       <c r="F13" s="69" t="n">
         <v>5</v>
       </c>
-      <c r="G13" s="229" t="n">
+      <c r="G13" s="211" t="n">
         <v>6</v>
       </c>
       <c r="H13" s="70" t="n">
@@ -11305,7 +11321,7 @@
       <c r="I13" s="69" t="n">
         <v>5</v>
       </c>
-      <c r="J13" s="229" t="n">
+      <c r="J13" s="211" t="n">
         <v>5</v>
       </c>
       <c r="K13" s="70" t="n">
@@ -11342,7 +11358,7 @@
         <f>C12-C13</f>
         <v/>
       </c>
-      <c r="D14" s="229">
+      <c r="D14" s="211">
         <f>D12-INT($D$8/18)-IF(D11&lt;=MOD($D$8,18),1,0)</f>
         <v/>
       </c>
@@ -11354,7 +11370,7 @@
         <f>F12-INT($D$8/18)-IF(F11&lt;=MOD($D$8,18),1,0)</f>
         <v/>
       </c>
-      <c r="G14" s="229">
+      <c r="G14" s="211">
         <f>G12-INT($D$8/18)-IF(G11&lt;=MOD($D$8,18),1,0)</f>
         <v/>
       </c>
@@ -11366,7 +11382,7 @@
         <f>I12-INT($D$8/18)-IF(I11&lt;=MOD($D$8,18),1,0)</f>
         <v/>
       </c>
-      <c r="J14" s="229">
+      <c r="J14" s="211">
         <f>J12-INT($D$8/18)-IF(J11&lt;=MOD($D$8,18),1,0)</f>
         <v/>
       </c>
@@ -11374,7 +11390,7 @@
         <f>K12-INT($D$8/18)-IF(K11&lt;=MOD($D$8,18),1,0)</f>
         <v/>
       </c>
-      <c r="L14" s="229">
+      <c r="L14" s="211">
         <f>SUM(C14:K14)</f>
         <v/>
       </c>
@@ -11382,7 +11398,7 @@
         <f>SUM(C14:K14)-SUM(C$10:K$10)</f>
         <v/>
       </c>
-      <c r="O14" s="229" t="inlineStr">
+      <c r="O14" s="211" t="inlineStr">
         <is>
           <t>Back 9</t>
         </is>
@@ -11407,7 +11423,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="15" ht="14.25" customHeight="1" s="181" thickBot="1">
+    <row r="15" ht="14.25" customHeight="1" s="219" thickBot="1">
       <c r="B15" s="74" t="inlineStr">
         <is>
           <t>Wins Hole</t>
@@ -11449,37 +11465,37 @@
         <f>IF(K14&lt;K23,1,0)</f>
         <v/>
       </c>
-      <c r="L15" s="229" t="n"/>
-      <c r="O15" s="225" t="inlineStr">
+      <c r="L15" s="211" t="n"/>
+      <c r="O15" s="212" t="inlineStr">
         <is>
           <t>Black</t>
         </is>
       </c>
-      <c r="P15" s="229" t="n">
+      <c r="P15" s="211" t="n">
         <v>12</v>
       </c>
-      <c r="Q15" s="229" t="n">
+      <c r="Q15" s="211" t="n">
         <v>2</v>
       </c>
-      <c r="R15" s="229" t="n">
+      <c r="R15" s="211" t="n">
         <v>8</v>
       </c>
-      <c r="S15" s="229" t="n">
+      <c r="S15" s="211" t="n">
         <v>6</v>
       </c>
-      <c r="T15" s="229" t="n">
+      <c r="T15" s="211" t="n">
         <v>18</v>
       </c>
-      <c r="U15" s="229" t="n">
+      <c r="U15" s="211" t="n">
         <v>14</v>
       </c>
-      <c r="V15" s="229" t="n">
+      <c r="V15" s="211" t="n">
         <v>16</v>
       </c>
-      <c r="W15" s="229" t="n">
+      <c r="W15" s="211" t="n">
         <v>10</v>
       </c>
-      <c r="X15" s="229" t="n">
+      <c r="X15" s="211" t="n">
         <v>4</v>
       </c>
       <c r="AA15" s="110" t="n">
@@ -11503,46 +11519,46 @@
       </c>
     </row>
     <row r="16">
-      <c r="C16" s="229" t="n"/>
-      <c r="D16" s="229" t="n"/>
-      <c r="E16" s="229" t="n"/>
-      <c r="F16" s="229" t="n"/>
-      <c r="G16" s="229" t="n"/>
-      <c r="H16" s="229" t="n"/>
-      <c r="I16" s="229" t="n"/>
-      <c r="J16" s="229" t="n"/>
-      <c r="K16" s="229" t="n"/>
-      <c r="L16" s="229" t="n"/>
-      <c r="O16" s="225" t="inlineStr">
+      <c r="C16" s="211" t="n"/>
+      <c r="D16" s="211" t="n"/>
+      <c r="E16" s="211" t="n"/>
+      <c r="F16" s="211" t="n"/>
+      <c r="G16" s="211" t="n"/>
+      <c r="H16" s="211" t="n"/>
+      <c r="I16" s="211" t="n"/>
+      <c r="J16" s="211" t="n"/>
+      <c r="K16" s="211" t="n"/>
+      <c r="L16" s="211" t="n"/>
+      <c r="O16" s="212" t="inlineStr">
         <is>
           <t>Blue</t>
         </is>
       </c>
-      <c r="P16" s="229" t="n">
+      <c r="P16" s="211" t="n">
         <v>12</v>
       </c>
-      <c r="Q16" s="229" t="n">
+      <c r="Q16" s="211" t="n">
         <v>2</v>
       </c>
-      <c r="R16" s="229" t="n">
+      <c r="R16" s="211" t="n">
         <v>8</v>
       </c>
-      <c r="S16" s="229" t="n">
+      <c r="S16" s="211" t="n">
         <v>6</v>
       </c>
-      <c r="T16" s="229" t="n">
+      <c r="T16" s="211" t="n">
         <v>18</v>
       </c>
-      <c r="U16" s="229" t="n">
+      <c r="U16" s="211" t="n">
         <v>14</v>
       </c>
-      <c r="V16" s="229" t="n">
+      <c r="V16" s="211" t="n">
         <v>16</v>
       </c>
-      <c r="W16" s="229" t="n">
+      <c r="W16" s="211" t="n">
         <v>10</v>
       </c>
-      <c r="X16" s="229" t="n">
+      <c r="X16" s="211" t="n">
         <v>4</v>
       </c>
       <c r="AA16" s="110" t="n">
@@ -11565,7 +11581,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="17" ht="19.5" customHeight="1" s="181" thickBot="1">
+    <row r="17" ht="19.5" customHeight="1" s="219" thickBot="1">
       <c r="B17" s="109" t="inlineStr">
         <is>
           <t>Bruce Dubovecky</t>
@@ -11576,12 +11592,12 @@
           <t>Handicap:</t>
         </is>
       </c>
-      <c r="D17" s="229">
+      <c r="D17" s="211">
         <f>IFERROR(VLOOKUP(B17,$AB$3:$AE$21,4,0),0)</f>
         <v/>
       </c>
-      <c r="E17" s="229" t="n"/>
-      <c r="F17" s="229" t="inlineStr">
+      <c r="E17" s="211" t="n"/>
+      <c r="F17" s="211" t="inlineStr">
         <is>
           <t>Tees:</t>
         </is>
@@ -11591,8 +11607,8 @@
           <t>Black</t>
         </is>
       </c>
-      <c r="H17" s="229" t="n"/>
-      <c r="I17" s="229" t="inlineStr">
+      <c r="H17" s="211" t="n"/>
+      <c r="I17" s="211" t="inlineStr">
         <is>
           <t>Holes:</t>
         </is>
@@ -11602,38 +11618,38 @@
           <t>Front 9</t>
         </is>
       </c>
-      <c r="K17" s="229" t="n"/>
-      <c r="L17" s="229" t="n"/>
-      <c r="O17" s="225" t="inlineStr">
+      <c r="K17" s="211" t="n"/>
+      <c r="L17" s="211" t="n"/>
+      <c r="O17" s="212" t="inlineStr">
         <is>
           <t>Blue / White</t>
         </is>
       </c>
-      <c r="P17" s="229" t="n">
+      <c r="P17" s="211" t="n">
         <v>12</v>
       </c>
-      <c r="Q17" s="229" t="n">
+      <c r="Q17" s="211" t="n">
         <v>4</v>
       </c>
-      <c r="R17" s="229" t="n">
+      <c r="R17" s="211" t="n">
         <v>10</v>
       </c>
-      <c r="S17" s="229" t="n">
+      <c r="S17" s="211" t="n">
         <v>2</v>
       </c>
-      <c r="T17" s="229" t="n">
+      <c r="T17" s="211" t="n">
         <v>16</v>
       </c>
-      <c r="U17" s="229" t="n">
+      <c r="U17" s="211" t="n">
         <v>14</v>
       </c>
-      <c r="V17" s="229" t="n">
+      <c r="V17" s="211" t="n">
         <v>18</v>
       </c>
-      <c r="W17" s="229" t="n">
+      <c r="W17" s="211" t="n">
         <v>6</v>
       </c>
-      <c r="X17" s="229" t="n">
+      <c r="X17" s="211" t="n">
         <v>8</v>
       </c>
       <c r="AA17" s="110" t="n">
@@ -11656,7 +11672,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="18" ht="15" customHeight="1" s="181">
+    <row r="18" ht="15" customHeight="1" s="219">
       <c r="B18" s="64" t="inlineStr">
         <is>
           <t>HOLE</t>
@@ -11689,38 +11705,38 @@
       <c r="K18" s="67" t="n">
         <v>9</v>
       </c>
-      <c r="L18" s="229" t="n"/>
+      <c r="L18" s="211" t="n"/>
       <c r="M18" s="72" t="n"/>
-      <c r="O18" s="225" t="inlineStr">
+      <c r="O18" s="212" t="inlineStr">
         <is>
           <t>White</t>
         </is>
       </c>
-      <c r="P18" s="229" t="n">
+      <c r="P18" s="211" t="n">
         <v>10</v>
       </c>
-      <c r="Q18" s="229" t="n">
+      <c r="Q18" s="211" t="n">
         <v>4</v>
       </c>
-      <c r="R18" s="229" t="n">
+      <c r="R18" s="211" t="n">
         <v>8</v>
       </c>
-      <c r="S18" s="229" t="n">
+      <c r="S18" s="211" t="n">
         <v>2</v>
       </c>
-      <c r="T18" s="229" t="n">
+      <c r="T18" s="211" t="n">
         <v>16</v>
       </c>
-      <c r="U18" s="229" t="n">
+      <c r="U18" s="211" t="n">
         <v>12</v>
       </c>
-      <c r="V18" s="229" t="n">
+      <c r="V18" s="211" t="n">
         <v>18</v>
       </c>
-      <c r="W18" s="229" t="n">
+      <c r="W18" s="211" t="n">
         <v>14</v>
       </c>
-      <c r="X18" s="229" t="n">
+      <c r="X18" s="211" t="n">
         <v>6</v>
       </c>
       <c r="AA18" s="110" t="n">
@@ -11752,7 +11768,7 @@
       <c r="C19" s="69" t="n">
         <v>4</v>
       </c>
-      <c r="D19" s="229" t="n">
+      <c r="D19" s="211" t="n">
         <v>5</v>
       </c>
       <c r="E19" s="70" t="n">
@@ -11761,7 +11777,7 @@
       <c r="F19" s="69" t="n">
         <v>4</v>
       </c>
-      <c r="G19" s="229" t="n">
+      <c r="G19" s="211" t="n">
         <v>5</v>
       </c>
       <c r="H19" s="70" t="n">
@@ -11770,13 +11786,13 @@
       <c r="I19" s="69" t="n">
         <v>4</v>
       </c>
-      <c r="J19" s="229" t="n">
+      <c r="J19" s="211" t="n">
         <v>4</v>
       </c>
       <c r="K19" s="70" t="n">
         <v>4</v>
       </c>
-      <c r="L19" s="229">
+      <c r="L19" s="211">
         <f>SUM(C19:K19)</f>
         <v/>
       </c>
@@ -11810,7 +11826,7 @@
         <f t="array" ref="C20">_xlfn.IFS($J17="Back 9",VLOOKUP($G17,$O$15:$X$18,COLUMN()-1,0),$J17="Front 9",VLOOKUP($G17,$O$9:$X$12,COLUMN()-1,0))</f>
         <v/>
       </c>
-      <c r="D20" s="229">
+      <c r="D20" s="211">
         <f t="array" ref="D20">_xlfn.IFS($J17="Back 9",VLOOKUP($G17,$O$15:$X$18,COLUMN()-1,0),$J17="Front 9",VLOOKUP($G17,$O$9:$X$12,COLUMN()-1,0))</f>
         <v/>
       </c>
@@ -11822,7 +11838,7 @@
         <f t="array" ref="F20">_xlfn.IFS($J17="Back 9",VLOOKUP($G17,$O$15:$X$18,COLUMN()-1,0),$J17="Front 9",VLOOKUP($G17,$O$9:$X$12,COLUMN()-1,0))</f>
         <v/>
       </c>
-      <c r="G20" s="229">
+      <c r="G20" s="211">
         <f t="array" ref="G20">_xlfn.IFS($J17="Back 9",VLOOKUP($G17,$O$15:$X$18,COLUMN()-1,0),$J17="Front 9",VLOOKUP($G17,$O$9:$X$12,COLUMN()-1,0))</f>
         <v/>
       </c>
@@ -11834,7 +11850,7 @@
         <f t="array" ref="I20">_xlfn.IFS($J17="Back 9",VLOOKUP($G17,$O$15:$X$18,COLUMN()-1,0),$J17="Front 9",VLOOKUP($G17,$O$9:$X$12,COLUMN()-1,0))</f>
         <v/>
       </c>
-      <c r="J20" s="229">
+      <c r="J20" s="211">
         <f t="array" ref="J20">_xlfn.IFS($J17="Back 9",VLOOKUP($G17,$O$15:$X$18,COLUMN()-1,0),$J17="Front 9",VLOOKUP($G17,$O$9:$X$12,COLUMN()-1,0))</f>
         <v/>
       </c>
@@ -11842,7 +11858,7 @@
         <f t="array" ref="K20">_xlfn.IFS($J17="Back 9",VLOOKUP($G17,$O$15:$X$18,COLUMN()-1,0),$J17="Front 9",VLOOKUP($G17,$O$9:$X$12,COLUMN()-1,0))</f>
         <v/>
       </c>
-      <c r="L20" s="229" t="n"/>
+      <c r="L20" s="211" t="n"/>
       <c r="AA20" s="110" t="n">
         <v>16</v>
       </c>
@@ -11863,7 +11879,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="21" ht="15" customHeight="1" s="181">
+    <row r="21" ht="15" customHeight="1" s="219">
       <c r="B21" s="71" t="inlineStr">
         <is>
           <t>GROSS</t>
@@ -11896,7 +11912,7 @@
       <c r="K21" s="115" t="n">
         <v>5</v>
       </c>
-      <c r="L21" s="229">
+      <c r="L21" s="211">
         <f>SUM(C21:K21)</f>
         <v/>
       </c>
@@ -11933,7 +11949,7 @@
       <c r="C22" s="69" t="n">
         <v>5</v>
       </c>
-      <c r="D22" s="229" t="n">
+      <c r="D22" s="211" t="n">
         <v>6</v>
       </c>
       <c r="E22" s="70" t="n">
@@ -11942,7 +11958,7 @@
       <c r="F22" s="69" t="n">
         <v>5</v>
       </c>
-      <c r="G22" s="229" t="n">
+      <c r="G22" s="211" t="n">
         <v>6</v>
       </c>
       <c r="H22" s="70" t="n">
@@ -11951,7 +11967,7 @@
       <c r="I22" s="69" t="n">
         <v>5</v>
       </c>
-      <c r="J22" s="229" t="n">
+      <c r="J22" s="211" t="n">
         <v>5</v>
       </c>
       <c r="K22" s="70" t="n">
@@ -11969,7 +11985,7 @@
         <f>C21-C22</f>
         <v/>
       </c>
-      <c r="D23" s="229">
+      <c r="D23" s="211">
         <f>D21-D22</f>
         <v/>
       </c>
@@ -11981,7 +11997,7 @@
         <f>F21-F22</f>
         <v/>
       </c>
-      <c r="G23" s="229">
+      <c r="G23" s="211">
         <f>G21-G22</f>
         <v/>
       </c>
@@ -11993,7 +12009,7 @@
         <f>I21-I22</f>
         <v/>
       </c>
-      <c r="J23" s="229">
+      <c r="J23" s="211">
         <f>J21-J22</f>
         <v/>
       </c>
@@ -12001,7 +12017,7 @@
         <f>K21-K22</f>
         <v/>
       </c>
-      <c r="L23" s="229">
+      <c r="L23" s="211">
         <f>SUM(C23:K23)</f>
         <v/>
       </c>
@@ -12010,7 +12026,7 @@
         <v/>
       </c>
     </row>
-    <row r="24" ht="14.25" customHeight="1" s="181" thickBot="1">
+    <row r="24" ht="14.25" customHeight="1" s="219" thickBot="1">
       <c r="B24" s="74" t="inlineStr">
         <is>
           <t>Wins Hole</t>
@@ -12052,7 +12068,7 @@
         <f>IF(K23&lt;K14,1,0)</f>
         <v/>
       </c>
-      <c r="L24" s="229" t="n"/>
+      <c r="L24" s="211" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="AA2:AE21">
@@ -12063,8 +12079,8 @@
   <mergeCells count="9">
     <mergeCell ref="L2:M2"/>
     <mergeCell ref="O14:X14"/>
+    <mergeCell ref="P8:X8"/>
     <mergeCell ref="J3:K5"/>
-    <mergeCell ref="P8:X8"/>
     <mergeCell ref="J2:K2"/>
     <mergeCell ref="B3:B4"/>
     <mergeCell ref="J1:M1"/>

--- a/2026 IMI Golf League.xlsx
+++ b/2026 IMI Golf League.xlsx
@@ -9342,7 +9342,9 @@
       <c r="E3" s="200" t="n">
         <v>4</v>
       </c>
-      <c r="F3" s="200" t="n"/>
+      <c r="F3" s="200" t="n">
+        <v>8</v>
+      </c>
       <c r="G3" s="200" t="n"/>
       <c r="H3" s="200" t="n"/>
       <c r="I3" s="200" t="n"/>
@@ -9350,15 +9352,15 @@
       <c r="K3" s="200" t="n"/>
       <c r="L3" s="160" t="n"/>
       <c r="M3" s="202" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="N3" s="200" t="inlineStr">
         <is>
-          <t>0-1-1</t>
+          <t>1-1-1</t>
         </is>
       </c>
       <c r="O3" s="208" t="n">
-        <v>41.5</v>
+        <v>39</v>
       </c>
       <c r="Q3" s="209" t="inlineStr">
         <is>
@@ -9381,7 +9383,9 @@
       <c r="E4" s="163" t="n">
         <v>40</v>
       </c>
-      <c r="F4" s="163" t="n"/>
+      <c r="F4" s="163" t="n">
+        <v>34</v>
+      </c>
       <c r="G4" s="163" t="n"/>
       <c r="H4" s="163" t="n"/>
       <c r="I4" s="163" t="n"/>
@@ -9578,7 +9582,9 @@
       <c r="E9" s="166" t="n">
         <v>1</v>
       </c>
-      <c r="F9" s="166" t="n"/>
+      <c r="F9" s="166" t="n">
+        <v>0</v>
+      </c>
       <c r="G9" s="166" t="n"/>
       <c r="H9" s="166" t="n"/>
       <c r="I9" s="166" t="n"/>
@@ -9590,11 +9596,11 @@
       </c>
       <c r="N9" s="199" t="inlineStr">
         <is>
-          <t>1-1-0</t>
+          <t>1-2-0</t>
         </is>
       </c>
       <c r="O9" s="196" t="n">
-        <v>42.5</v>
+        <v>44</v>
       </c>
     </row>
     <row r="10" ht="13.5" customHeight="1" s="219" thickBot="1">
@@ -9610,7 +9616,9 @@
       <c r="E10" s="170" t="n">
         <v>47</v>
       </c>
-      <c r="F10" s="170" t="n"/>
+      <c r="F10" s="170" t="n">
+        <v>47</v>
+      </c>
       <c r="G10" s="170" t="n"/>
       <c r="H10" s="170" t="n"/>
       <c r="I10" s="170" t="n"/>

--- a/2026 IMI Golf League.xlsx
+++ b/2026 IMI Golf League.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="714" firstSheet="9" activeTab="9" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="39900" yWindow="1470" windowWidth="28800" windowHeight="15345" tabRatio="714" firstSheet="5" activeTab="5" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scores 2024" sheetId="1" state="hidden" r:id="rId1"/>
@@ -15,7 +15,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Course Info" sheetId="7" state="hidden" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scores 2026" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Calculator (old)" sheetId="9" state="hidden" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Calculator" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Calculator" sheetId="10" state="hidden" r:id="rId10"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Helper" sheetId="11" state="hidden" r:id="rId11"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sep 16 - 27th" sheetId="12" state="hidden" r:id="rId12"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sep 30 - Oct 11" sheetId="13" state="hidden" r:id="rId13"/>
@@ -26,7 +26,7 @@
     <definedName name="Skybrook">Helper!$C$3:$C$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Calculator (old)'!$AA$2:$AE$21</definedName>
   </definedNames>
-  <calcPr calcId="191028" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -1388,6 +1388,7 @@
     <xf numFmtId="0" fontId="17" fillId="5" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1397,6 +1398,11 @@
     <xf numFmtId="0" fontId="13" fillId="5" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="17" fillId="5" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1406,30 +1412,39 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="13" fillId="5" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="39" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="37" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1439,18 +1454,23 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="49" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="48" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1460,9 +1480,11 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1481,6 +1503,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="17" fillId="5" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1505,29 +1528,6 @@
     <xf numFmtId="0" fontId="13" fillId="5" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="48" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="49" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1968,24 +1968,24 @@
   <dimension ref="A1:N20"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.140625" defaultRowHeight="12.75"/>
   <cols>
-    <col width="3.140625" customWidth="1" style="206" min="1" max="1"/>
-    <col width="18" bestFit="1" customWidth="1" style="206" min="2" max="2"/>
-    <col width="12.140625" bestFit="1" customWidth="1" style="206" min="3" max="3"/>
-    <col width="9.140625" customWidth="1" style="206" min="4" max="11"/>
-    <col width="11.5703125" customWidth="1" style="206" min="12" max="13"/>
-    <col width="9.140625" customWidth="1" style="206" min="14" max="29"/>
-    <col width="9.140625" customWidth="1" style="206" min="30" max="16384"/>
+    <col width="3.140625" customWidth="1" style="228" min="1" max="1"/>
+    <col width="18" bestFit="1" customWidth="1" style="228" min="2" max="2"/>
+    <col width="12.140625" bestFit="1" customWidth="1" style="228" min="3" max="3"/>
+    <col width="9.140625" customWidth="1" style="228" min="4" max="11"/>
+    <col width="11.5703125" customWidth="1" style="228" min="12" max="13"/>
+    <col width="9.140625" customWidth="1" style="228" min="14" max="30"/>
+    <col width="9.140625" customWidth="1" style="228" min="31" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1" ht="13.5" customHeight="1" s="219" thickBot="1">
-      <c r="M1" s="207" t="inlineStr">
+    <row r="1" ht="13.5" customHeight="1" s="197" thickBot="1">
+      <c r="M1" s="229" t="inlineStr">
         <is>
           <t>Tiebreaker</t>
         </is>
       </c>
       <c r="N1" s="21" t="n"/>
     </row>
-    <row r="2" ht="41.45" customHeight="1" s="219" thickBot="1">
+    <row r="2" ht="41.45" customHeight="1" s="197" thickBot="1">
       <c r="B2" s="20" t="inlineStr">
         <is>
           <t>Name</t>
@@ -2043,8 +2043,8 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="12.95" customHeight="1" s="219" thickBot="1">
-      <c r="A3" s="206" t="n">
+    <row r="3" ht="12.95" customHeight="1" s="197" thickBot="1">
+      <c r="A3" s="228" t="n">
         <v>1</v>
       </c>
       <c r="B3" s="25" t="inlineStr">
@@ -2084,8 +2084,8 @@
         <v/>
       </c>
     </row>
-    <row r="4" ht="12.95" customHeight="1" s="219" thickBot="1">
-      <c r="A4" s="206" t="n">
+    <row r="4" ht="12.95" customHeight="1" s="197" thickBot="1">
+      <c r="A4" s="228" t="n">
         <v>2</v>
       </c>
       <c r="B4" s="25" t="inlineStr">
@@ -2125,8 +2125,8 @@
         <v/>
       </c>
     </row>
-    <row r="5" ht="12.95" customHeight="1" s="219" thickBot="1">
-      <c r="A5" s="206" t="n">
+    <row r="5" ht="12.95" customHeight="1" s="197" thickBot="1">
+      <c r="A5" s="228" t="n">
         <v>3</v>
       </c>
       <c r="B5" s="25" t="inlineStr">
@@ -2166,8 +2166,8 @@
         <v/>
       </c>
     </row>
-    <row r="6" ht="12.95" customHeight="1" s="219" thickBot="1">
-      <c r="A6" s="206" t="n">
+    <row r="6" ht="12.95" customHeight="1" s="197" thickBot="1">
+      <c r="A6" s="228" t="n">
         <v>4</v>
       </c>
       <c r="B6" s="25" t="inlineStr">
@@ -2205,8 +2205,8 @@
         <v/>
       </c>
     </row>
-    <row r="7" ht="12.95" customHeight="1" s="219" thickBot="1">
-      <c r="A7" s="206" t="n">
+    <row r="7" ht="12.95" customHeight="1" s="197" thickBot="1">
+      <c r="A7" s="228" t="n">
         <v>5</v>
       </c>
       <c r="B7" s="25" t="inlineStr">
@@ -2248,8 +2248,8 @@
         <v/>
       </c>
     </row>
-    <row r="8" ht="12.95" customHeight="1" s="219" thickBot="1">
-      <c r="A8" s="206" t="n">
+    <row r="8" ht="12.95" customHeight="1" s="197" thickBot="1">
+      <c r="A8" s="228" t="n">
         <v>6</v>
       </c>
       <c r="B8" s="25" t="inlineStr">
@@ -2289,8 +2289,8 @@
         <v/>
       </c>
     </row>
-    <row r="9" ht="12.95" customHeight="1" s="219" thickBot="1">
-      <c r="A9" s="206" t="n">
+    <row r="9" ht="12.95" customHeight="1" s="197" thickBot="1">
+      <c r="A9" s="228" t="n">
         <v>7</v>
       </c>
       <c r="B9" s="25" t="inlineStr">
@@ -2328,8 +2328,8 @@
         <v/>
       </c>
     </row>
-    <row r="10" ht="12.95" customHeight="1" s="219" thickBot="1">
-      <c r="A10" s="206" t="n">
+    <row r="10" ht="12.95" customHeight="1" s="197" thickBot="1">
+      <c r="A10" s="228" t="n">
         <v>8</v>
       </c>
       <c r="B10" s="25" t="inlineStr">
@@ -2369,8 +2369,8 @@
         <v/>
       </c>
     </row>
-    <row r="11" ht="12.95" customHeight="1" s="219" thickBot="1">
-      <c r="A11" s="206" t="n">
+    <row r="11" ht="12.95" customHeight="1" s="197" thickBot="1">
+      <c r="A11" s="228" t="n">
         <v>9</v>
       </c>
       <c r="B11" s="25" t="inlineStr">
@@ -2410,8 +2410,8 @@
         <v/>
       </c>
     </row>
-    <row r="12" ht="12.95" customHeight="1" s="219" thickBot="1">
-      <c r="A12" s="206" t="n">
+    <row r="12" ht="12.95" customHeight="1" s="197" thickBot="1">
+      <c r="A12" s="228" t="n">
         <v>10</v>
       </c>
       <c r="B12" s="25" t="inlineStr">
@@ -2453,8 +2453,8 @@
         <v/>
       </c>
     </row>
-    <row r="13" ht="12.95" customHeight="1" s="219" thickBot="1">
-      <c r="A13" s="206" t="n">
+    <row r="13" ht="12.95" customHeight="1" s="197" thickBot="1">
+      <c r="A13" s="228" t="n">
         <v>11</v>
       </c>
       <c r="B13" s="25" t="inlineStr">
@@ -2492,8 +2492,8 @@
         <v/>
       </c>
     </row>
-    <row r="14" ht="12.95" customHeight="1" s="219" thickBot="1">
-      <c r="A14" s="206" t="n">
+    <row r="14" ht="12.95" customHeight="1" s="197" thickBot="1">
+      <c r="A14" s="228" t="n">
         <v>12</v>
       </c>
       <c r="B14" s="25" t="inlineStr">
@@ -2533,8 +2533,8 @@
         <v/>
       </c>
     </row>
-    <row r="15" ht="12.95" customHeight="1" s="219" thickBot="1">
-      <c r="A15" s="206" t="n">
+    <row r="15" ht="12.95" customHeight="1" s="197" thickBot="1">
+      <c r="A15" s="228" t="n">
         <v>13</v>
       </c>
       <c r="B15" s="25" t="inlineStr">
@@ -2574,8 +2574,8 @@
         <v/>
       </c>
     </row>
-    <row r="16" ht="12.95" customHeight="1" s="219" thickBot="1">
-      <c r="A16" s="206" t="n">
+    <row r="16" ht="12.95" customHeight="1" s="197" thickBot="1">
+      <c r="A16" s="228" t="n">
         <v>14</v>
       </c>
       <c r="B16" s="25" t="inlineStr">
@@ -2615,8 +2615,8 @@
         <v/>
       </c>
     </row>
-    <row r="17" ht="12.95" customHeight="1" s="219" thickBot="1">
-      <c r="A17" s="206" t="n">
+    <row r="17" ht="12.95" customHeight="1" s="197" thickBot="1">
+      <c r="A17" s="228" t="n">
         <v>15</v>
       </c>
       <c r="B17" s="25" t="inlineStr">
@@ -2654,8 +2654,8 @@
         <v/>
       </c>
     </row>
-    <row r="18" ht="12.95" customHeight="1" s="219" thickBot="1">
-      <c r="A18" s="206" t="n">
+    <row r="18" ht="12.95" customHeight="1" s="197" thickBot="1">
+      <c r="A18" s="228" t="n">
         <v>16</v>
       </c>
       <c r="B18" s="25" t="inlineStr">
@@ -2697,8 +2697,8 @@
         <v/>
       </c>
     </row>
-    <row r="19" ht="12.95" customHeight="1" s="219" thickBot="1">
-      <c r="A19" s="206" t="n">
+    <row r="19" ht="12.95" customHeight="1" s="197" thickBot="1">
+      <c r="A19" s="228" t="n">
         <v>17</v>
       </c>
       <c r="B19" s="25" t="inlineStr">
@@ -2738,8 +2738,8 @@
         <v/>
       </c>
     </row>
-    <row r="20" ht="12.95" customHeight="1" s="219">
-      <c r="A20" s="206" t="n">
+    <row r="20" ht="12.95" customHeight="1" s="197">
+      <c r="A20" s="228" t="n">
         <v>18</v>
       </c>
       <c r="B20" s="25" t="inlineStr">
@@ -2793,45 +2793,45 @@
   <dimension ref="B1:BG24"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.85546875" defaultRowHeight="13.5"/>
   <cols>
-    <col width="2.5703125" customWidth="1" style="180" min="1" max="1"/>
-    <col width="20.7109375" customWidth="1" style="180" min="2" max="2"/>
-    <col width="9.85546875" customWidth="1" style="180" min="3" max="8"/>
-    <col width="10.7109375" bestFit="1" customWidth="1" style="180" min="9" max="9"/>
-    <col width="10.5703125" customWidth="1" style="180" min="10" max="11"/>
-    <col width="10.85546875" customWidth="1" style="180" min="12" max="13"/>
-    <col width="5.7109375" customWidth="1" style="180" min="14" max="14"/>
-    <col width="11" bestFit="1" customWidth="1" style="180" min="15" max="15"/>
-    <col width="16.5703125" bestFit="1" customWidth="1" style="180" min="16" max="16"/>
-    <col width="8.85546875" bestFit="1" customWidth="1" style="180" min="17" max="17"/>
-    <col width="4.5703125" customWidth="1" style="180" min="18" max="19"/>
-    <col width="11" bestFit="1" customWidth="1" style="180" min="20" max="20"/>
-    <col width="4" customWidth="1" style="180" min="21" max="29"/>
-    <col width="10.42578125" bestFit="1" customWidth="1" style="180" min="30" max="30"/>
-    <col width="4" customWidth="1" style="180" min="31" max="39"/>
-    <col width="11" bestFit="1" customWidth="1" style="180" min="40" max="40"/>
-    <col width="4" customWidth="1" style="180" min="41" max="49"/>
-    <col width="10.42578125" bestFit="1" customWidth="1" style="180" min="50" max="50"/>
-    <col width="4" customWidth="1" style="180" min="51" max="59"/>
-    <col width="9.85546875" customWidth="1" style="180" min="60" max="75"/>
-    <col width="9.85546875" customWidth="1" style="180" min="76" max="16384"/>
+    <col width="2.5703125" customWidth="1" style="181" min="1" max="1"/>
+    <col width="20.7109375" customWidth="1" style="181" min="2" max="2"/>
+    <col width="9.85546875" customWidth="1" style="181" min="3" max="8"/>
+    <col width="10.7109375" bestFit="1" customWidth="1" style="181" min="9" max="9"/>
+    <col width="10.5703125" customWidth="1" style="181" min="10" max="11"/>
+    <col width="10.85546875" customWidth="1" style="181" min="12" max="13"/>
+    <col width="5.7109375" customWidth="1" style="181" min="14" max="14"/>
+    <col width="11" bestFit="1" customWidth="1" style="181" min="15" max="15"/>
+    <col width="16.5703125" bestFit="1" customWidth="1" style="181" min="16" max="16"/>
+    <col width="8.85546875" bestFit="1" customWidth="1" style="181" min="17" max="17"/>
+    <col width="4.5703125" customWidth="1" style="181" min="18" max="19"/>
+    <col width="11" bestFit="1" customWidth="1" style="181" min="20" max="20"/>
+    <col width="4" customWidth="1" style="181" min="21" max="29"/>
+    <col width="10.42578125" bestFit="1" customWidth="1" style="181" min="30" max="30"/>
+    <col width="4" customWidth="1" style="181" min="31" max="39"/>
+    <col width="11" bestFit="1" customWidth="1" style="181" min="40" max="40"/>
+    <col width="4" customWidth="1" style="181" min="41" max="49"/>
+    <col width="10.42578125" bestFit="1" customWidth="1" style="181" min="50" max="50"/>
+    <col width="4" customWidth="1" style="181" min="51" max="59"/>
+    <col width="9.85546875" customWidth="1" style="181" min="60" max="76"/>
+    <col width="9.85546875" customWidth="1" style="181" min="77" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.25" customHeight="1" s="219" thickBot="1">
+    <row r="1" ht="14.25" customHeight="1" s="197" thickBot="1">
       <c r="B1" s="116" t="inlineStr">
         <is>
           <t>Fill in the course, your name, tees, front/back and gross scores in the grey boxes</t>
         </is>
       </c>
-      <c r="J1" s="184" t="inlineStr">
+      <c r="J1" s="190" t="inlineStr">
         <is>
           <t>Points</t>
         </is>
       </c>
-      <c r="K1" s="227" t="n"/>
-      <c r="L1" s="227" t="n"/>
-      <c r="M1" s="227" t="n"/>
-    </row>
-    <row r="2" ht="24.95" customHeight="1" s="219" thickBot="1">
+      <c r="K1" s="191" t="n"/>
+      <c r="L1" s="191" t="n"/>
+      <c r="M1" s="191" t="n"/>
+    </row>
+    <row r="2" ht="24.95" customHeight="1" s="197" thickBot="1">
       <c r="B2" s="172" t="inlineStr">
         <is>
           <t>Highland Creek</t>
@@ -2863,19 +2863,19 @@
         </is>
       </c>
       <c r="I2" s="119" t="n"/>
-      <c r="J2" s="182">
+      <c r="J2" s="188">
         <f>B8</f>
         <v/>
       </c>
-      <c r="K2" s="229" t="n"/>
+      <c r="K2" s="179" t="n"/>
       <c r="L2" s="178">
         <f>B17</f>
         <v/>
       </c>
-      <c r="M2" s="229" t="n"/>
-    </row>
-    <row r="3" ht="14.25" customHeight="1" s="219" thickBot="1">
-      <c r="B3" s="183">
+      <c r="M2" s="179" t="n"/>
+    </row>
+    <row r="3" ht="14.25" customHeight="1" s="197" thickBot="1">
+      <c r="B3" s="189">
         <f>J2</f>
         <v/>
       </c>
@@ -2904,19 +2904,19 @@
         <f>SUM(C14:K14)</f>
         <v/>
       </c>
-      <c r="J3" s="181">
+      <c r="J3" s="182">
         <f>SUM(D4:H4)</f>
         <v/>
       </c>
-      <c r="K3" s="236" t="n"/>
-      <c r="L3" s="185">
+      <c r="K3" s="183" t="n"/>
+      <c r="L3" s="192">
         <f>SUM(D6:H6)</f>
         <v/>
       </c>
-      <c r="M3" s="236" t="n"/>
-    </row>
-    <row r="4" ht="14.25" customHeight="1" s="219" thickBot="1">
-      <c r="B4" s="237" t="n"/>
+      <c r="M3" s="183" t="n"/>
+    </row>
+    <row r="4" ht="14.25" customHeight="1" s="197" thickBot="1">
+      <c r="B4" s="186" t="n"/>
       <c r="C4" s="125" t="inlineStr">
         <is>
           <t>PTS</t>
@@ -2942,12 +2942,12 @@
         <f>IF(H3&lt;H5,1,IF(H3=H5,0.5,0))</f>
         <v/>
       </c>
-      <c r="J4" s="238" t="n"/>
-      <c r="K4" s="239" t="n"/>
-      <c r="M4" s="239" t="n"/>
-    </row>
-    <row r="5" ht="14.25" customHeight="1" s="219" thickBot="1">
-      <c r="B5" s="183">
+      <c r="J4" s="184" t="n"/>
+      <c r="K4" s="185" t="n"/>
+      <c r="M4" s="185" t="n"/>
+    </row>
+    <row r="5" ht="14.25" customHeight="1" s="197" thickBot="1">
+      <c r="B5" s="189">
         <f>L2</f>
         <v/>
       </c>
@@ -2976,13 +2976,13 @@
         <f>SUM(C23:K23)</f>
         <v/>
       </c>
-      <c r="J5" s="237" t="n"/>
-      <c r="K5" s="240" t="n"/>
-      <c r="L5" s="227" t="n"/>
-      <c r="M5" s="240" t="n"/>
-    </row>
-    <row r="6" ht="14.25" customHeight="1" s="219" thickBot="1">
-      <c r="B6" s="237" t="n"/>
+      <c r="J5" s="186" t="n"/>
+      <c r="K5" s="187" t="n"/>
+      <c r="L5" s="191" t="n"/>
+      <c r="M5" s="187" t="n"/>
+    </row>
+    <row r="6" ht="14.25" customHeight="1" s="197" thickBot="1">
+      <c r="B6" s="186" t="n"/>
       <c r="C6" s="125" t="inlineStr">
         <is>
           <t>PTS</t>
@@ -3008,34 +3008,34 @@
         <f>IF(H5&lt;H3,1,IF(H5=H3,0.5,0))</f>
         <v/>
       </c>
-      <c r="J6" s="179" t="n"/>
-      <c r="K6" s="179" t="n"/>
-      <c r="L6" s="179" t="n"/>
-      <c r="M6" s="179" t="n"/>
+      <c r="J6" s="180" t="n"/>
+      <c r="K6" s="180" t="n"/>
+      <c r="L6" s="180" t="n"/>
+      <c r="M6" s="180" t="n"/>
     </row>
     <row r="7">
-      <c r="C7" s="179" t="n"/>
-      <c r="D7" s="179" t="n"/>
-      <c r="E7" s="179" t="n"/>
-      <c r="F7" s="179" t="n"/>
-      <c r="G7" s="179" t="n"/>
-      <c r="H7" s="179" t="n"/>
-      <c r="I7" s="179" t="n"/>
-      <c r="J7" s="179" t="n"/>
-      <c r="K7" s="179" t="n"/>
-      <c r="L7" s="179" t="n"/>
-      <c r="T7" s="179" t="inlineStr">
+      <c r="C7" s="180" t="n"/>
+      <c r="D7" s="180" t="n"/>
+      <c r="E7" s="180" t="n"/>
+      <c r="F7" s="180" t="n"/>
+      <c r="G7" s="180" t="n"/>
+      <c r="H7" s="180" t="n"/>
+      <c r="I7" s="180" t="n"/>
+      <c r="J7" s="180" t="n"/>
+      <c r="K7" s="180" t="n"/>
+      <c r="L7" s="180" t="n"/>
+      <c r="T7" s="180" t="inlineStr">
         <is>
           <t>Skybrook</t>
         </is>
       </c>
-      <c r="AN7" s="179" t="inlineStr">
+      <c r="AN7" s="180" t="inlineStr">
         <is>
           <t>Highland Creek</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="16.5" customHeight="1" s="219" thickBot="1">
+    <row r="8" ht="16.5" customHeight="1" s="197" thickBot="1">
       <c r="B8" s="145" t="inlineStr">
         <is>
           <t>Preston Stoner</t>
@@ -3046,12 +3046,12 @@
           <t>Handicap:</t>
         </is>
       </c>
-      <c r="D8" s="179">
+      <c r="D8" s="180">
         <f>_xlfn.XLOOKUP(B8,$P$9:$P$23,$Q$9:$Q$23)</f>
         <v/>
       </c>
-      <c r="E8" s="179" t="n"/>
-      <c r="F8" s="179" t="inlineStr">
+      <c r="E8" s="180" t="n"/>
+      <c r="F8" s="180" t="inlineStr">
         <is>
           <t>Tees:</t>
         </is>
@@ -3061,8 +3061,8 @@
           <t>Blue</t>
         </is>
       </c>
-      <c r="H8" s="179" t="n"/>
-      <c r="I8" s="179" t="inlineStr">
+      <c r="H8" s="180" t="n"/>
+      <c r="I8" s="180" t="inlineStr">
         <is>
           <t>Holes:</t>
         </is>
@@ -3072,8 +3072,8 @@
           <t>Front 9</t>
         </is>
       </c>
-      <c r="K8" s="179" t="n"/>
-      <c r="L8" s="179" t="n"/>
+      <c r="K8" s="180" t="n"/>
+      <c r="L8" s="180" t="n"/>
       <c r="O8" s="143" t="inlineStr">
         <is>
           <t>#</t>
@@ -3089,38 +3089,38 @@
           <t>Handicap</t>
         </is>
       </c>
-      <c r="T8" s="180" t="inlineStr">
+      <c r="T8" s="181" t="inlineStr">
         <is>
           <t>HC's by Tees</t>
         </is>
       </c>
-      <c r="U8" s="179" t="inlineStr">
+      <c r="U8" s="180" t="inlineStr">
         <is>
           <t>Front 9</t>
         </is>
       </c>
-      <c r="AD8" s="179" t="inlineStr">
+      <c r="AD8" s="180" t="inlineStr">
         <is>
           <t>Back 9</t>
         </is>
       </c>
-      <c r="AN8" s="180" t="inlineStr">
+      <c r="AN8" s="181" t="inlineStr">
         <is>
           <t>HC's by Tees</t>
         </is>
       </c>
-      <c r="AO8" s="179" t="inlineStr">
+      <c r="AO8" s="180" t="inlineStr">
         <is>
           <t>Front 9</t>
         </is>
       </c>
-      <c r="AX8" s="179" t="inlineStr">
+      <c r="AX8" s="180" t="inlineStr">
         <is>
           <t>Back 9</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" s="219">
+    <row r="9" ht="15" customHeight="1" s="197">
       <c r="B9" s="131" t="inlineStr">
         <is>
           <t>HOLE</t>
@@ -3153,7 +3153,7 @@
       <c r="K9" s="134" t="n">
         <v>9</v>
       </c>
-      <c r="L9" s="179" t="n"/>
+      <c r="L9" s="180" t="n"/>
       <c r="O9" s="122" t="n">
         <v>1</v>
       </c>
@@ -3166,132 +3166,132 @@
         <f>Schedule!D15</f>
         <v/>
       </c>
-      <c r="T9" s="180" t="inlineStr">
+      <c r="T9" s="181" t="inlineStr">
         <is>
           <t>Blue</t>
         </is>
       </c>
-      <c r="U9" s="179" t="n">
+      <c r="U9" s="180" t="n">
         <v>7</v>
       </c>
-      <c r="V9" s="179" t="n">
+      <c r="V9" s="180" t="n">
         <v>15</v>
       </c>
-      <c r="W9" s="179" t="n">
+      <c r="W9" s="180" t="n">
         <v>5</v>
       </c>
-      <c r="X9" s="179" t="n">
+      <c r="X9" s="180" t="n">
         <v>13</v>
       </c>
-      <c r="Y9" s="179" t="n">
+      <c r="Y9" s="180" t="n">
         <v>3</v>
       </c>
-      <c r="Z9" s="179" t="n">
+      <c r="Z9" s="180" t="n">
         <v>11</v>
       </c>
-      <c r="AA9" s="179" t="n">
+      <c r="AA9" s="180" t="n">
         <v>17</v>
       </c>
-      <c r="AB9" s="179" t="n">
+      <c r="AB9" s="180" t="n">
         <v>9</v>
       </c>
-      <c r="AC9" s="179" t="n">
+      <c r="AC9" s="180" t="n">
         <v>1</v>
       </c>
-      <c r="AD9" s="180" t="inlineStr">
+      <c r="AD9" s="181" t="inlineStr">
         <is>
           <t>Blue</t>
         </is>
       </c>
-      <c r="AE9" s="179" t="n">
+      <c r="AE9" s="180" t="n">
         <v>4</v>
       </c>
-      <c r="AF9" s="179" t="n">
+      <c r="AF9" s="180" t="n">
         <v>12</v>
       </c>
-      <c r="AG9" s="179" t="n">
+      <c r="AG9" s="180" t="n">
         <v>14</v>
       </c>
-      <c r="AH9" s="179" t="n">
+      <c r="AH9" s="180" t="n">
         <v>6</v>
       </c>
-      <c r="AI9" s="179" t="n">
+      <c r="AI9" s="180" t="n">
         <v>16</v>
       </c>
-      <c r="AJ9" s="179" t="n">
+      <c r="AJ9" s="180" t="n">
         <v>8</v>
       </c>
-      <c r="AK9" s="179" t="n">
+      <c r="AK9" s="180" t="n">
         <v>18</v>
       </c>
-      <c r="AL9" s="179" t="n">
+      <c r="AL9" s="180" t="n">
         <v>2</v>
       </c>
-      <c r="AM9" s="179" t="n">
+      <c r="AM9" s="180" t="n">
         <v>10</v>
       </c>
-      <c r="AN9" s="180" t="inlineStr">
+      <c r="AN9" s="181" t="inlineStr">
         <is>
           <t>Blue</t>
         </is>
       </c>
-      <c r="AO9" s="179" t="n">
+      <c r="AO9" s="180" t="n">
         <v>7</v>
       </c>
-      <c r="AP9" s="179" t="n">
+      <c r="AP9" s="180" t="n">
         <v>17</v>
       </c>
-      <c r="AQ9" s="179" t="n">
+      <c r="AQ9" s="180" t="n">
         <v>15</v>
       </c>
-      <c r="AR9" s="179" t="n">
+      <c r="AR9" s="180" t="n">
         <v>1</v>
       </c>
-      <c r="AS9" s="179" t="n">
+      <c r="AS9" s="180" t="n">
         <v>11</v>
       </c>
-      <c r="AT9" s="179" t="n">
+      <c r="AT9" s="180" t="n">
         <v>9</v>
       </c>
-      <c r="AU9" s="179" t="n">
+      <c r="AU9" s="180" t="n">
         <v>13</v>
       </c>
-      <c r="AV9" s="179" t="n">
+      <c r="AV9" s="180" t="n">
         <v>5</v>
       </c>
-      <c r="AW9" s="179" t="n">
+      <c r="AW9" s="180" t="n">
         <v>3</v>
       </c>
-      <c r="AX9" s="180" t="inlineStr">
+      <c r="AX9" s="181" t="inlineStr">
         <is>
           <t>Blue</t>
         </is>
       </c>
-      <c r="AY9" s="179" t="n">
+      <c r="AY9" s="180" t="n">
         <v>14</v>
       </c>
-      <c r="AZ9" s="179" t="n">
+      <c r="AZ9" s="180" t="n">
         <v>8</v>
       </c>
-      <c r="BA9" s="179" t="n">
+      <c r="BA9" s="180" t="n">
         <v>6</v>
       </c>
-      <c r="BB9" s="179" t="n">
+      <c r="BB9" s="180" t="n">
         <v>4</v>
       </c>
-      <c r="BC9" s="179" t="n">
+      <c r="BC9" s="180" t="n">
         <v>16</v>
       </c>
-      <c r="BD9" s="179" t="n">
+      <c r="BD9" s="180" t="n">
         <v>2</v>
       </c>
-      <c r="BE9" s="179" t="n">
+      <c r="BE9" s="180" t="n">
         <v>10</v>
       </c>
-      <c r="BF9" s="179" t="n">
+      <c r="BF9" s="180" t="n">
         <v>12</v>
       </c>
-      <c r="BG9" s="179" t="n">
+      <c r="BG9" s="180" t="n">
         <v>18</v>
       </c>
     </row>
@@ -3301,7 +3301,7 @@
           <t>PAR</t>
         </is>
       </c>
-      <c r="C10" s="179">
+      <c r="C10" s="180">
         <f t="array" ref="C10">IF($B$2="Skybrook",
    _xlfn.IFS(
       $J8="Back 9",INDEX($AE$12:$AM$12,1,C9),
@@ -3314,7 +3314,7 @@
 )</f>
         <v/>
       </c>
-      <c r="D10" s="179">
+      <c r="D10" s="180">
         <f t="array" ref="D10">IF($B$2="Skybrook",
    _xlfn.IFS(
       $J8="Back 9",INDEX($AE$12:$AM$12,1,D9),
@@ -3353,7 +3353,7 @@
 )</f>
         <v/>
       </c>
-      <c r="G10" s="179">
+      <c r="G10" s="180">
         <f t="array" ref="G10">IF($B$2="Skybrook",
    _xlfn.IFS(
       $J8="Back 9",INDEX($AE$12:$AM$12,1,G9),
@@ -3392,7 +3392,7 @@
 )</f>
         <v/>
       </c>
-      <c r="J10" s="179">
+      <c r="J10" s="180">
         <f t="array" ref="J10">IF($B$2="Skybrook",
    _xlfn.IFS(
       $J8="Back 9",INDEX($AE$12:$AM$12,1,J9),
@@ -3418,7 +3418,7 @@
 )</f>
         <v/>
       </c>
-      <c r="L10" s="179">
+      <c r="L10" s="180">
         <f>SUM(C10:K10)</f>
         <v/>
       </c>
@@ -3434,132 +3434,132 @@
         <f>Schedule!D16</f>
         <v/>
       </c>
-      <c r="T10" s="180" t="inlineStr">
+      <c r="T10" s="181" t="inlineStr">
         <is>
           <t>Green</t>
         </is>
       </c>
-      <c r="U10" s="179" t="n">
+      <c r="U10" s="180" t="n">
         <v>7</v>
       </c>
-      <c r="V10" s="179" t="n">
+      <c r="V10" s="180" t="n">
         <v>15</v>
       </c>
-      <c r="W10" s="179" t="n">
+      <c r="W10" s="180" t="n">
         <v>5</v>
       </c>
-      <c r="X10" s="179" t="n">
+      <c r="X10" s="180" t="n">
         <v>13</v>
       </c>
-      <c r="Y10" s="179" t="n">
+      <c r="Y10" s="180" t="n">
         <v>3</v>
       </c>
-      <c r="Z10" s="179" t="n">
+      <c r="Z10" s="180" t="n">
         <v>11</v>
       </c>
-      <c r="AA10" s="179" t="n">
+      <c r="AA10" s="180" t="n">
         <v>17</v>
       </c>
-      <c r="AB10" s="179" t="n">
+      <c r="AB10" s="180" t="n">
         <v>9</v>
       </c>
-      <c r="AC10" s="179" t="n">
+      <c r="AC10" s="180" t="n">
         <v>1</v>
       </c>
-      <c r="AD10" s="180" t="inlineStr">
+      <c r="AD10" s="181" t="inlineStr">
         <is>
           <t>Green</t>
         </is>
       </c>
-      <c r="AE10" s="179" t="n">
+      <c r="AE10" s="180" t="n">
         <v>4</v>
       </c>
-      <c r="AF10" s="179" t="n">
+      <c r="AF10" s="180" t="n">
         <v>12</v>
       </c>
-      <c r="AG10" s="179" t="n">
+      <c r="AG10" s="180" t="n">
         <v>14</v>
       </c>
-      <c r="AH10" s="179" t="n">
+      <c r="AH10" s="180" t="n">
         <v>6</v>
       </c>
-      <c r="AI10" s="179" t="n">
+      <c r="AI10" s="180" t="n">
         <v>16</v>
       </c>
-      <c r="AJ10" s="179" t="n">
+      <c r="AJ10" s="180" t="n">
         <v>8</v>
       </c>
-      <c r="AK10" s="179" t="n">
+      <c r="AK10" s="180" t="n">
         <v>18</v>
       </c>
-      <c r="AL10" s="179" t="n">
+      <c r="AL10" s="180" t="n">
         <v>2</v>
       </c>
-      <c r="AM10" s="179" t="n">
+      <c r="AM10" s="180" t="n">
         <v>10</v>
       </c>
-      <c r="AN10" s="180" t="inlineStr">
+      <c r="AN10" s="181" t="inlineStr">
         <is>
           <t>White</t>
         </is>
       </c>
-      <c r="AO10" s="179" t="n">
+      <c r="AO10" s="180" t="n">
         <v>7</v>
       </c>
-      <c r="AP10" s="179" t="n">
+      <c r="AP10" s="180" t="n">
         <v>17</v>
       </c>
-      <c r="AQ10" s="179" t="n">
+      <c r="AQ10" s="180" t="n">
         <v>15</v>
       </c>
-      <c r="AR10" s="179" t="n">
+      <c r="AR10" s="180" t="n">
         <v>1</v>
       </c>
-      <c r="AS10" s="179" t="n">
+      <c r="AS10" s="180" t="n">
         <v>11</v>
       </c>
-      <c r="AT10" s="179" t="n">
+      <c r="AT10" s="180" t="n">
         <v>9</v>
       </c>
-      <c r="AU10" s="179" t="n">
+      <c r="AU10" s="180" t="n">
         <v>13</v>
       </c>
-      <c r="AV10" s="179" t="n">
+      <c r="AV10" s="180" t="n">
         <v>5</v>
       </c>
-      <c r="AW10" s="179" t="n">
+      <c r="AW10" s="180" t="n">
         <v>3</v>
       </c>
-      <c r="AX10" s="180" t="inlineStr">
+      <c r="AX10" s="181" t="inlineStr">
         <is>
           <t>White</t>
         </is>
       </c>
-      <c r="AY10" s="179" t="n">
+      <c r="AY10" s="180" t="n">
         <v>14</v>
       </c>
-      <c r="AZ10" s="179" t="n">
+      <c r="AZ10" s="180" t="n">
         <v>8</v>
       </c>
-      <c r="BA10" s="179" t="n">
+      <c r="BA10" s="180" t="n">
         <v>6</v>
       </c>
-      <c r="BB10" s="179" t="n">
+      <c r="BB10" s="180" t="n">
         <v>4</v>
       </c>
-      <c r="BC10" s="179" t="n">
+      <c r="BC10" s="180" t="n">
         <v>16</v>
       </c>
-      <c r="BD10" s="179" t="n">
+      <c r="BD10" s="180" t="n">
         <v>2</v>
       </c>
-      <c r="BE10" s="179" t="n">
+      <c r="BE10" s="180" t="n">
         <v>10</v>
       </c>
-      <c r="BF10" s="179" t="n">
+      <c r="BF10" s="180" t="n">
         <v>12</v>
       </c>
-      <c r="BG10" s="179" t="n">
+      <c r="BG10" s="180" t="n">
         <v>18</v>
       </c>
     </row>
@@ -3569,7 +3569,7 @@
           <t>HC</t>
         </is>
       </c>
-      <c r="C11" s="179">
+      <c r="C11" s="180">
         <f t="array" ref="C11">IF($B$2="Skybrook",
    _xlfn.IFS(
       $J8="Back 9",VLOOKUP($G8,$AD$9:$AM$11,COLUMN()-1,0),
@@ -3582,7 +3582,7 @@
 )</f>
         <v/>
       </c>
-      <c r="D11" s="179">
+      <c r="D11" s="180">
         <f t="array" ref="D11">IF($B$2="Skybrook",
    _xlfn.IFS(
       $J8="Back 9",VLOOKUP($G8,$AD$9:$AM$11,COLUMN()-1,0),
@@ -3621,7 +3621,7 @@
 )</f>
         <v/>
       </c>
-      <c r="G11" s="179">
+      <c r="G11" s="180">
         <f t="array" ref="G11">IF($B$2="Skybrook",
    _xlfn.IFS(
       $J8="Back 9",VLOOKUP($G8,$AD$9:$AM$11,COLUMN()-1,0),
@@ -3660,7 +3660,7 @@
 )</f>
         <v/>
       </c>
-      <c r="J11" s="179">
+      <c r="J11" s="180">
         <f t="array" ref="J11">IF($B$2="Skybrook",
    _xlfn.IFS(
       $J8="Back 9",VLOOKUP($G8,$AD$9:$AM$11,COLUMN()-1,0),
@@ -3686,7 +3686,7 @@
 )</f>
         <v/>
       </c>
-      <c r="L11" s="179" t="n"/>
+      <c r="L11" s="180" t="n"/>
       <c r="O11" s="122">
         <f>O10+1</f>
         <v/>
@@ -3700,136 +3700,136 @@
         <f>Schedule!D17</f>
         <v/>
       </c>
-      <c r="T11" s="180" t="inlineStr">
+      <c r="T11" s="181" t="inlineStr">
         <is>
           <t>Red</t>
         </is>
       </c>
-      <c r="U11" s="179" t="n">
+      <c r="U11" s="180" t="n">
         <v>17</v>
       </c>
-      <c r="V11" s="179" t="n">
+      <c r="V11" s="180" t="n">
         <v>9</v>
       </c>
-      <c r="W11" s="179" t="n">
+      <c r="W11" s="180" t="n">
         <v>5</v>
       </c>
-      <c r="X11" s="179" t="n">
+      <c r="X11" s="180" t="n">
         <v>7</v>
       </c>
-      <c r="Y11" s="179" t="n">
+      <c r="Y11" s="180" t="n">
         <v>3</v>
       </c>
-      <c r="Z11" s="179" t="n">
+      <c r="Z11" s="180" t="n">
         <v>15</v>
       </c>
-      <c r="AA11" s="179" t="n">
+      <c r="AA11" s="180" t="n">
         <v>11</v>
       </c>
-      <c r="AB11" s="179" t="n">
+      <c r="AB11" s="180" t="n">
         <v>13</v>
       </c>
-      <c r="AC11" s="179" t="n">
+      <c r="AC11" s="180" t="n">
         <v>1</v>
       </c>
-      <c r="AD11" s="180" t="inlineStr">
+      <c r="AD11" s="181" t="inlineStr">
         <is>
           <t>Red</t>
         </is>
       </c>
-      <c r="AE11" s="179" t="n">
+      <c r="AE11" s="180" t="n">
         <v>4</v>
       </c>
-      <c r="AF11" s="179" t="n">
+      <c r="AF11" s="180" t="n">
         <v>10</v>
       </c>
-      <c r="AG11" s="179" t="n">
+      <c r="AG11" s="180" t="n">
         <v>14</v>
       </c>
-      <c r="AH11" s="179" t="n">
+      <c r="AH11" s="180" t="n">
         <v>6</v>
       </c>
-      <c r="AI11" s="179" t="n">
+      <c r="AI11" s="180" t="n">
         <v>16</v>
       </c>
-      <c r="AJ11" s="179" t="n">
+      <c r="AJ11" s="180" t="n">
         <v>12</v>
       </c>
-      <c r="AK11" s="179" t="n">
+      <c r="AK11" s="180" t="n">
         <v>18</v>
       </c>
-      <c r="AL11" s="179" t="n">
+      <c r="AL11" s="180" t="n">
         <v>2</v>
       </c>
-      <c r="AM11" s="179" t="n">
+      <c r="AM11" s="180" t="n">
         <v>8</v>
       </c>
-      <c r="AN11" s="180" t="inlineStr">
+      <c r="AN11" s="181" t="inlineStr">
         <is>
           <t>Red</t>
         </is>
       </c>
-      <c r="AO11" s="179" t="n">
+      <c r="AO11" s="180" t="n">
         <v>7</v>
       </c>
-      <c r="AP11" s="179" t="n">
+      <c r="AP11" s="180" t="n">
         <v>17</v>
       </c>
-      <c r="AQ11" s="179" t="n">
+      <c r="AQ11" s="180" t="n">
         <v>15</v>
       </c>
-      <c r="AR11" s="179" t="n">
+      <c r="AR11" s="180" t="n">
         <v>1</v>
       </c>
-      <c r="AS11" s="179" t="n">
+      <c r="AS11" s="180" t="n">
         <v>11</v>
       </c>
-      <c r="AT11" s="179" t="n">
+      <c r="AT11" s="180" t="n">
         <v>9</v>
       </c>
-      <c r="AU11" s="179" t="n">
+      <c r="AU11" s="180" t="n">
         <v>13</v>
       </c>
-      <c r="AV11" s="179" t="n">
+      <c r="AV11" s="180" t="n">
         <v>5</v>
       </c>
-      <c r="AW11" s="179" t="n">
+      <c r="AW11" s="180" t="n">
         <v>3</v>
       </c>
-      <c r="AX11" s="180" t="inlineStr">
+      <c r="AX11" s="181" t="inlineStr">
         <is>
           <t>Red</t>
         </is>
       </c>
-      <c r="AY11" s="179" t="n">
+      <c r="AY11" s="180" t="n">
         <v>14</v>
       </c>
-      <c r="AZ11" s="179" t="n">
+      <c r="AZ11" s="180" t="n">
         <v>8</v>
       </c>
-      <c r="BA11" s="179" t="n">
+      <c r="BA11" s="180" t="n">
         <v>6</v>
       </c>
-      <c r="BB11" s="179" t="n">
+      <c r="BB11" s="180" t="n">
         <v>4</v>
       </c>
-      <c r="BC11" s="179" t="n">
+      <c r="BC11" s="180" t="n">
         <v>16</v>
       </c>
-      <c r="BD11" s="179" t="n">
+      <c r="BD11" s="180" t="n">
         <v>2</v>
       </c>
-      <c r="BE11" s="179" t="n">
+      <c r="BE11" s="180" t="n">
         <v>10</v>
       </c>
-      <c r="BF11" s="179" t="n">
+      <c r="BF11" s="180" t="n">
         <v>12</v>
       </c>
-      <c r="BG11" s="179" t="n">
+      <c r="BG11" s="180" t="n">
         <v>18</v>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1" s="219">
+    <row r="12" ht="15" customHeight="1" s="197">
       <c r="B12" s="138" t="inlineStr">
         <is>
           <t>GROSS</t>
@@ -3862,7 +3862,7 @@
       <c r="K12" s="148" t="n">
         <v>6</v>
       </c>
-      <c r="L12" s="179">
+      <c r="L12" s="180">
         <f>SUM(C12:K12)</f>
         <v/>
       </c>
@@ -3882,7 +3882,7 @@
         <f>Schedule!D18</f>
         <v/>
       </c>
-      <c r="T12" s="180" t="inlineStr">
+      <c r="T12" s="181" t="inlineStr">
         <is>
           <t>Par</t>
         </is>
@@ -3914,7 +3914,7 @@
       <c r="AC12" s="144" t="n">
         <v>4</v>
       </c>
-      <c r="AD12" s="180" t="inlineStr">
+      <c r="AD12" s="181" t="inlineStr">
         <is>
           <t>Par</t>
         </is>
@@ -3946,7 +3946,7 @@
       <c r="AM12" s="144" t="n">
         <v>5</v>
       </c>
-      <c r="AN12" s="180" t="inlineStr">
+      <c r="AN12" s="181" t="inlineStr">
         <is>
           <t>Par</t>
         </is>
@@ -3978,7 +3978,7 @@
       <c r="AW12" s="144" t="n">
         <v>4</v>
       </c>
-      <c r="AX12" s="180" t="inlineStr">
+      <c r="AX12" s="181" t="inlineStr">
         <is>
           <t>Par</t>
         </is>
@@ -4021,7 +4021,7 @@
         <f>INT($D$8/18)+IF(C11&lt;=MOD($D$8,18),1,0)</f>
         <v/>
       </c>
-      <c r="D13" s="179">
+      <c r="D13" s="180">
         <f>INT($D$8/18)+IF(D11&lt;=MOD($D$8,18),1,0)</f>
         <v/>
       </c>
@@ -4033,7 +4033,7 @@
         <f>INT($D$8/18)+IF(F11&lt;=MOD($D$8,18),1,0)</f>
         <v/>
       </c>
-      <c r="G13" s="179">
+      <c r="G13" s="180">
         <f>INT($D$8/18)+IF(G11&lt;=MOD($D$8,18),1,0)</f>
         <v/>
       </c>
@@ -4045,7 +4045,7 @@
         <f>INT($D$8/18)+IF(I11&lt;=MOD($D$8,18),1,0)</f>
         <v/>
       </c>
-      <c r="J13" s="179">
+      <c r="J13" s="180">
         <f>INT($D$8/18)+IF(J11&lt;=MOD($D$8,18),1,0)</f>
         <v/>
       </c>
@@ -4077,7 +4077,7 @@
         <f>C12-C13</f>
         <v/>
       </c>
-      <c r="D14" s="179">
+      <c r="D14" s="180">
         <f>D12-INT($D$8/18)-IF(D11&lt;=MOD($D$8,18),1,0)</f>
         <v/>
       </c>
@@ -4089,7 +4089,7 @@
         <f>F12-INT($D$8/18)-IF(F11&lt;=MOD($D$8,18),1,0)</f>
         <v/>
       </c>
-      <c r="G14" s="179">
+      <c r="G14" s="180">
         <f>G12-INT($D$8/18)-IF(G11&lt;=MOD($D$8,18),1,0)</f>
         <v/>
       </c>
@@ -4101,7 +4101,7 @@
         <f>I12-INT($D$8/18)-IF(I11&lt;=MOD($D$8,18),1,0)</f>
         <v/>
       </c>
-      <c r="J14" s="179">
+      <c r="J14" s="180">
         <f>J12-INT($D$8/18)-IF(J11&lt;=MOD($D$8,18),1,0)</f>
         <v/>
       </c>
@@ -4130,7 +4130,7 @@
         <v/>
       </c>
     </row>
-    <row r="15" ht="14.25" customHeight="1" s="219" thickBot="1">
+    <row r="15" ht="14.25" customHeight="1" s="197" thickBot="1">
       <c r="B15" s="140" t="inlineStr">
         <is>
           <t>Wins Hole</t>
@@ -4172,7 +4172,7 @@
         <f>IF(K14&lt;K23,1,0)</f>
         <v/>
       </c>
-      <c r="L15" s="179" t="n"/>
+      <c r="L15" s="180" t="n"/>
       <c r="O15" s="122">
         <f>O14+1</f>
         <v/>
@@ -4188,16 +4188,16 @@
       </c>
     </row>
     <row r="16">
-      <c r="C16" s="179" t="n"/>
-      <c r="D16" s="179" t="n"/>
-      <c r="E16" s="179" t="n"/>
-      <c r="F16" s="179" t="n"/>
-      <c r="G16" s="179" t="n"/>
-      <c r="H16" s="179" t="n"/>
-      <c r="I16" s="179" t="n"/>
-      <c r="J16" s="179" t="n"/>
-      <c r="K16" s="179" t="n"/>
-      <c r="L16" s="179" t="n"/>
+      <c r="C16" s="180" t="n"/>
+      <c r="D16" s="180" t="n"/>
+      <c r="E16" s="180" t="n"/>
+      <c r="F16" s="180" t="n"/>
+      <c r="G16" s="180" t="n"/>
+      <c r="H16" s="180" t="n"/>
+      <c r="I16" s="180" t="n"/>
+      <c r="J16" s="180" t="n"/>
+      <c r="K16" s="180" t="n"/>
+      <c r="L16" s="180" t="n"/>
       <c r="O16" s="122" t="n">
         <v>8</v>
       </c>
@@ -4211,7 +4211,7 @@
         <v/>
       </c>
     </row>
-    <row r="17" ht="16.5" customHeight="1" s="219" thickBot="1">
+    <row r="17" ht="16.5" customHeight="1" s="197" thickBot="1">
       <c r="B17" s="145" t="inlineStr">
         <is>
           <t>Charlotte Hayes</t>
@@ -4222,12 +4222,12 @@
           <t>Handicap:</t>
         </is>
       </c>
-      <c r="D17" s="179">
+      <c r="D17" s="180">
         <f>_xlfn.XLOOKUP(B17,$P$9:$P$23,$Q$9:$Q$23)</f>
         <v/>
       </c>
-      <c r="E17" s="179" t="n"/>
-      <c r="F17" s="179" t="inlineStr">
+      <c r="E17" s="180" t="n"/>
+      <c r="F17" s="180" t="inlineStr">
         <is>
           <t>Tees:</t>
         </is>
@@ -4237,18 +4237,18 @@
           <t>Blue</t>
         </is>
       </c>
-      <c r="H17" s="179" t="n"/>
-      <c r="I17" s="179" t="inlineStr">
+      <c r="H17" s="180" t="n"/>
+      <c r="I17" s="180" t="inlineStr">
         <is>
           <t>Holes:</t>
         </is>
       </c>
-      <c r="J17" s="179">
+      <c r="J17" s="180">
         <f>J8</f>
         <v/>
       </c>
-      <c r="K17" s="179" t="n"/>
-      <c r="L17" s="179" t="n"/>
+      <c r="K17" s="180" t="n"/>
+      <c r="L17" s="180" t="n"/>
       <c r="O17" s="122" t="n">
         <v>9</v>
       </c>
@@ -4262,7 +4262,7 @@
         <v/>
       </c>
     </row>
-    <row r="18" ht="15" customHeight="1" s="219">
+    <row r="18" ht="15" customHeight="1" s="197">
       <c r="B18" s="131" t="inlineStr">
         <is>
           <t>HOLE</t>
@@ -4295,7 +4295,7 @@
       <c r="K18" s="134" t="n">
         <v>9</v>
       </c>
-      <c r="L18" s="179" t="n"/>
+      <c r="L18" s="180" t="n"/>
       <c r="M18" s="139" t="n"/>
       <c r="O18" s="122" t="n">
         <v>10</v>
@@ -4316,7 +4316,7 @@
           <t>PAR</t>
         </is>
       </c>
-      <c r="C19" s="179">
+      <c r="C19" s="180">
         <f t="array" ref="C19">IF($B$2="Skybrook",
    _xlfn.IFS(
       $J17="Back 9",INDEX($AE$12:$AM$12,1,C18),
@@ -4329,7 +4329,7 @@
 )</f>
         <v/>
       </c>
-      <c r="D19" s="179">
+      <c r="D19" s="180">
         <f t="array" ref="D19">IF($B$2="Skybrook",
    _xlfn.IFS(
       $J17="Back 9",INDEX($AE$12:$AM$12,1,D18),
@@ -4368,7 +4368,7 @@
 )</f>
         <v/>
       </c>
-      <c r="G19" s="179">
+      <c r="G19" s="180">
         <f t="array" ref="G19">IF($B$2="Skybrook",
    _xlfn.IFS(
       $J17="Back 9",INDEX($AE$12:$AM$12,1,G18),
@@ -4407,7 +4407,7 @@
 )</f>
         <v/>
       </c>
-      <c r="J19" s="179">
+      <c r="J19" s="180">
         <f t="array" ref="J19">IF($B$2="Skybrook",
    _xlfn.IFS(
       $J17="Back 9",INDEX($AE$12:$AM$12,1,J18),
@@ -4433,7 +4433,7 @@
 )</f>
         <v/>
       </c>
-      <c r="L19" s="179">
+      <c r="L19" s="180">
         <f>SUM(C19:K19)</f>
         <v/>
       </c>
@@ -4457,7 +4457,7 @@
           <t>HC</t>
         </is>
       </c>
-      <c r="C20" s="179">
+      <c r="C20" s="180">
         <f t="array" ref="C20">IF($B$2="Skybrook",
    _xlfn.IFS(
       $J17="Back 9",VLOOKUP($G17,$AD$9:$AM$11,COLUMN()-1,0),
@@ -4470,7 +4470,7 @@
 )</f>
         <v/>
       </c>
-      <c r="D20" s="179">
+      <c r="D20" s="180">
         <f t="array" ref="D20">IF($B$2="Skybrook",
    _xlfn.IFS(
       $J17="Back 9",VLOOKUP($G17,$AD$9:$AM$11,COLUMN()-1,0),
@@ -4509,7 +4509,7 @@
 )</f>
         <v/>
       </c>
-      <c r="G20" s="179">
+      <c r="G20" s="180">
         <f t="array" ref="G20">IF($B$2="Skybrook",
    _xlfn.IFS(
       $J17="Back 9",VLOOKUP($G17,$AD$9:$AM$11,COLUMN()-1,0),
@@ -4548,7 +4548,7 @@
 )</f>
         <v/>
       </c>
-      <c r="J20" s="179">
+      <c r="J20" s="180">
         <f t="array" ref="J20">IF($B$2="Skybrook",
    _xlfn.IFS(
       $J17="Back 9",VLOOKUP($G17,$AD$9:$AM$11,COLUMN()-1,0),
@@ -4574,7 +4574,7 @@
 )</f>
         <v/>
       </c>
-      <c r="L20" s="179" t="n"/>
+      <c r="L20" s="180" t="n"/>
       <c r="O20" s="122" t="n">
         <v>12</v>
       </c>
@@ -4588,7 +4588,7 @@
         <v/>
       </c>
     </row>
-    <row r="21" ht="15" customHeight="1" s="219">
+    <row r="21" ht="15" customHeight="1" s="197">
       <c r="B21" s="138" t="inlineStr">
         <is>
           <t>GROSS</t>
@@ -4621,7 +4621,7 @@
       <c r="K21" s="148" t="n">
         <v>8</v>
       </c>
-      <c r="L21" s="179">
+      <c r="L21" s="180">
         <f>SUM(C21:K21)</f>
         <v/>
       </c>
@@ -4652,7 +4652,7 @@
         <f>INT($D$17/18)+IF(C20&lt;=MOD($D$17,18),1,0)</f>
         <v/>
       </c>
-      <c r="D22" s="179">
+      <c r="D22" s="180">
         <f>INT($D$17/18)+IF(D20&lt;=MOD($D$17,18),1,0)</f>
         <v/>
       </c>
@@ -4664,7 +4664,7 @@
         <f>INT($D$17/18)+IF(F20&lt;=MOD($D$17,18),1,0)</f>
         <v/>
       </c>
-      <c r="G22" s="179">
+      <c r="G22" s="180">
         <f>INT($D$17/18)+IF(G20&lt;=MOD($D$17,18),1,0)</f>
         <v/>
       </c>
@@ -4676,7 +4676,7 @@
         <f>INT($D$17/18)+IF(I20&lt;=MOD($D$17,18),1,0)</f>
         <v/>
       </c>
-      <c r="J22" s="179">
+      <c r="J22" s="180">
         <f>INT($D$17/18)+IF(J20&lt;=MOD($D$17,18),1,0)</f>
         <v/>
       </c>
@@ -4708,7 +4708,7 @@
         <f>C21-C22</f>
         <v/>
       </c>
-      <c r="D23" s="179">
+      <c r="D23" s="180">
         <f>D21-D22</f>
         <v/>
       </c>
@@ -4720,7 +4720,7 @@
         <f>F21-F22</f>
         <v/>
       </c>
-      <c r="G23" s="179">
+      <c r="G23" s="180">
         <f>G21-G22</f>
         <v/>
       </c>
@@ -4732,7 +4732,7 @@
         <f>I21-I22</f>
         <v/>
       </c>
-      <c r="J23" s="179">
+      <c r="J23" s="180">
         <f>J21-J22</f>
         <v/>
       </c>
@@ -4761,7 +4761,7 @@
         <v/>
       </c>
     </row>
-    <row r="24" ht="14.25" customHeight="1" s="219" thickBot="1">
+    <row r="24" ht="14.25" customHeight="1" s="197" thickBot="1">
       <c r="B24" s="140" t="inlineStr">
         <is>
           <t>Wins Hole</t>
@@ -4803,7 +4803,7 @@
         <f>IF(K23&lt;K14,1,0)</f>
         <v/>
       </c>
-      <c r="L24" s="179" t="n"/>
+      <c r="L24" s="180" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="13">
@@ -4853,8 +4853,8 @@
   <dimension ref="C2:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="12.75"/>
   <cols>
-    <col width="8.85546875" bestFit="1" customWidth="1" style="219" min="3" max="3"/>
-    <col width="14.140625" bestFit="1" customWidth="1" style="219" min="4" max="4"/>
+    <col width="8.85546875" bestFit="1" customWidth="1" style="197" min="3" max="3"/>
+    <col width="14.140625" bestFit="1" customWidth="1" style="197" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="2">
@@ -4919,41 +4919,41 @@
   <dimension ref="A1:M15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="12.75"/>
   <cols>
-    <col width="18" bestFit="1" customWidth="1" style="219" min="1" max="1"/>
-    <col width="28" bestFit="1" customWidth="1" style="188" min="2" max="2"/>
-    <col width="28.5703125" bestFit="1" customWidth="1" style="219" min="3" max="3"/>
-    <col width="31.7109375" bestFit="1" customWidth="1" style="219" min="4" max="4"/>
-    <col width="29.42578125" bestFit="1" customWidth="1" style="219" min="5" max="5"/>
-    <col width="26.42578125" bestFit="1" customWidth="1" style="219" min="6" max="6"/>
-    <col width="28.85546875" bestFit="1" customWidth="1" style="219" min="7" max="7"/>
-    <col width="27.7109375" bestFit="1" customWidth="1" style="219" min="8" max="8"/>
-    <col width="28" bestFit="1" customWidth="1" style="219" min="9" max="9"/>
-    <col width="28.5703125" bestFit="1" customWidth="1" style="219" min="10" max="10"/>
-    <col width="31.7109375" bestFit="1" customWidth="1" style="219" min="11" max="11"/>
-    <col width="29.42578125" bestFit="1" customWidth="1" style="219" min="12" max="12"/>
-    <col width="26.42578125" bestFit="1" customWidth="1" style="219" min="13" max="13"/>
+    <col width="18" bestFit="1" customWidth="1" style="197" min="1" max="1"/>
+    <col width="28" bestFit="1" customWidth="1" style="196" min="2" max="2"/>
+    <col width="28.5703125" bestFit="1" customWidth="1" style="197" min="3" max="3"/>
+    <col width="31.7109375" bestFit="1" customWidth="1" style="197" min="4" max="4"/>
+    <col width="29.42578125" bestFit="1" customWidth="1" style="197" min="5" max="5"/>
+    <col width="26.42578125" bestFit="1" customWidth="1" style="197" min="6" max="6"/>
+    <col width="28.85546875" bestFit="1" customWidth="1" style="197" min="7" max="7"/>
+    <col width="27.7109375" bestFit="1" customWidth="1" style="197" min="8" max="8"/>
+    <col width="28" bestFit="1" customWidth="1" style="197" min="9" max="9"/>
+    <col width="28.5703125" bestFit="1" customWidth="1" style="197" min="10" max="10"/>
+    <col width="31.7109375" bestFit="1" customWidth="1" style="197" min="11" max="11"/>
+    <col width="29.42578125" bestFit="1" customWidth="1" style="197" min="12" max="12"/>
+    <col width="26.42578125" bestFit="1" customWidth="1" style="197" min="13" max="13"/>
   </cols>
   <sheetData>
-    <row r="1" ht="23.25" customHeight="1" s="219">
-      <c r="A1" s="186" t="inlineStr">
+    <row r="1" ht="23.25" customHeight="1" s="197">
+      <c r="A1" s="193" t="inlineStr">
         <is>
           <t>2024 Bechtel Golf League Schedule Tee Time</t>
         </is>
       </c>
-      <c r="B1" s="218" t="n"/>
-      <c r="C1" s="218" t="n"/>
-      <c r="D1" s="218" t="n"/>
-      <c r="E1" s="218" t="n"/>
-      <c r="F1" s="218" t="n"/>
-      <c r="G1" s="218" t="n"/>
-      <c r="H1" s="218" t="n"/>
-      <c r="I1" s="218" t="n"/>
-      <c r="J1" s="218" t="n"/>
-      <c r="K1" s="218" t="n"/>
-      <c r="L1" s="218" t="n"/>
-      <c r="M1" s="218" t="n"/>
-    </row>
-    <row r="2" ht="30" customFormat="1" customHeight="1" s="206">
+      <c r="B1" s="194" t="n"/>
+      <c r="C1" s="194" t="n"/>
+      <c r="D1" s="194" t="n"/>
+      <c r="E1" s="194" t="n"/>
+      <c r="F1" s="194" t="n"/>
+      <c r="G1" s="194" t="n"/>
+      <c r="H1" s="194" t="n"/>
+      <c r="I1" s="194" t="n"/>
+      <c r="J1" s="194" t="n"/>
+      <c r="K1" s="194" t="n"/>
+      <c r="L1" s="194" t="n"/>
+      <c r="M1" s="194" t="n"/>
+    </row>
+    <row r="2" ht="30" customFormat="1" customHeight="1" s="228">
       <c r="A2" s="10" t="inlineStr">
         <is>
           <t>TEE TIME</t>
@@ -4996,7 +4996,7 @@
         <v>45562</v>
       </c>
     </row>
-    <row r="3" ht="30" customHeight="1" s="219">
+    <row r="3" ht="30" customHeight="1" s="197">
       <c r="A3" s="8" t="n">
         <v>0.6666666666666666</v>
       </c>
@@ -5013,7 +5013,7 @@
       <c r="L3" s="9" t="n"/>
       <c r="M3" s="9" t="n"/>
     </row>
-    <row r="4" ht="30" customHeight="1" s="219">
+    <row r="4" ht="30" customHeight="1" s="197">
       <c r="A4" s="8" t="n">
         <v>0.6736111111111112</v>
       </c>
@@ -5030,7 +5030,7 @@
       <c r="L4" s="9" t="n"/>
       <c r="M4" s="9" t="n"/>
     </row>
-    <row r="5" ht="30" customHeight="1" s="219">
+    <row r="5" ht="30" customHeight="1" s="197">
       <c r="A5" s="8" t="n">
         <v>0.6805555555555556</v>
       </c>
@@ -5055,7 +5055,7 @@
       <c r="L5" s="9" t="n"/>
       <c r="M5" s="9" t="n"/>
     </row>
-    <row r="6" ht="30" customHeight="1" s="219">
+    <row r="6" ht="30" customHeight="1" s="197">
       <c r="A6" s="8" t="n">
         <v>0.6875</v>
       </c>
@@ -5076,7 +5076,7 @@
       <c r="L6" s="9" t="n"/>
       <c r="M6" s="9" t="n"/>
     </row>
-    <row r="7" ht="30" customHeight="1" s="219">
+    <row r="7" ht="30" customHeight="1" s="197">
       <c r="A7" s="8" t="n">
         <v>0.6944444444444444</v>
       </c>
@@ -5093,7 +5093,7 @@
       <c r="L7" s="9" t="n"/>
       <c r="M7" s="9" t="n"/>
     </row>
-    <row r="8" ht="30" customHeight="1" s="219">
+    <row r="8" ht="30" customHeight="1" s="197">
       <c r="A8" s="8" t="n">
         <v>0.7013888888888888</v>
       </c>
@@ -5110,7 +5110,7 @@
       <c r="L8" s="9" t="n"/>
       <c r="M8" s="9" t="n"/>
     </row>
-    <row r="9" ht="30" customHeight="1" s="219">
+    <row r="9" ht="30" customHeight="1" s="197">
       <c r="A9" s="8" t="n">
         <v>0.7083333333333334</v>
       </c>
@@ -5127,7 +5127,7 @@
       <c r="L9" s="9" t="n"/>
       <c r="M9" s="9" t="n"/>
     </row>
-    <row r="10" ht="30" customHeight="1" s="219">
+    <row r="10" ht="30" customHeight="1" s="197">
       <c r="A10" s="8" t="n">
         <v>0.7152777777777778</v>
       </c>
@@ -5144,7 +5144,7 @@
       <c r="L10" s="9" t="n"/>
       <c r="M10" s="9" t="n"/>
     </row>
-    <row r="11" ht="30" customHeight="1" s="219">
+    <row r="11" ht="30" customHeight="1" s="197">
       <c r="A11" s="8" t="n">
         <v>0.7222222222222222</v>
       </c>
@@ -5161,7 +5161,7 @@
       <c r="L11" s="9" t="n"/>
       <c r="M11" s="9" t="n"/>
     </row>
-    <row r="12" ht="30" customHeight="1" s="219">
+    <row r="12" ht="30" customHeight="1" s="197">
       <c r="A12" s="8" t="n">
         <v>0.7291666666666666</v>
       </c>
@@ -5178,7 +5178,7 @@
       <c r="L12" s="9" t="n"/>
       <c r="M12" s="9" t="n"/>
     </row>
-    <row r="13" ht="30" customHeight="1" s="219">
+    <row r="13" ht="30" customHeight="1" s="197">
       <c r="A13" s="8" t="n">
         <v>0.7361111111111112</v>
       </c>
@@ -5195,7 +5195,7 @@
       <c r="L13" s="9" t="n"/>
       <c r="M13" s="9" t="n"/>
     </row>
-    <row r="14" ht="30" customHeight="1" s="219">
+    <row r="14" ht="30" customHeight="1" s="197">
       <c r="A14" s="8" t="n">
         <v>0.7430555555555556</v>
       </c>
@@ -5212,7 +5212,7 @@
       <c r="L14" s="9" t="n"/>
       <c r="M14" s="9" t="n"/>
     </row>
-    <row r="15" ht="30" customHeight="1" s="219">
+    <row r="15" ht="30" customHeight="1" s="197">
       <c r="A15" s="8" t="n">
         <v>0.75</v>
       </c>
@@ -5246,41 +5246,41 @@
   <dimension ref="A1:M16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="12.75"/>
   <cols>
-    <col width="24.5703125" bestFit="1" customWidth="1" style="219" min="1" max="1"/>
-    <col width="26.28515625" bestFit="1" customWidth="1" style="188" min="2" max="2"/>
-    <col width="27.140625" bestFit="1" customWidth="1" style="219" min="3" max="3"/>
-    <col width="30" bestFit="1" customWidth="1" style="219" min="4" max="4"/>
-    <col width="27.85546875" bestFit="1" customWidth="1" style="219" min="5" max="5"/>
-    <col width="24.85546875" bestFit="1" customWidth="1" style="219" min="6" max="6"/>
-    <col hidden="1" width="26.28515625" customWidth="1" style="219" min="7" max="7"/>
-    <col hidden="1" width="24.85546875" customWidth="1" style="219" min="8" max="8"/>
-    <col width="26.28515625" bestFit="1" customWidth="1" style="219" min="9" max="9"/>
-    <col width="27.140625" bestFit="1" customWidth="1" style="219" min="10" max="10"/>
-    <col width="30" bestFit="1" customWidth="1" style="219" min="11" max="11"/>
-    <col width="27.85546875" bestFit="1" customWidth="1" style="219" min="12" max="12"/>
-    <col width="24.85546875" bestFit="1" customWidth="1" style="219" min="13" max="13"/>
+    <col width="24.5703125" bestFit="1" customWidth="1" style="197" min="1" max="1"/>
+    <col width="26.28515625" bestFit="1" customWidth="1" style="196" min="2" max="2"/>
+    <col width="27.140625" bestFit="1" customWidth="1" style="197" min="3" max="3"/>
+    <col width="30" bestFit="1" customWidth="1" style="197" min="4" max="4"/>
+    <col width="27.85546875" bestFit="1" customWidth="1" style="197" min="5" max="5"/>
+    <col width="24.85546875" bestFit="1" customWidth="1" style="197" min="6" max="6"/>
+    <col hidden="1" width="26.28515625" customWidth="1" style="197" min="7" max="7"/>
+    <col hidden="1" width="24.85546875" customWidth="1" style="197" min="8" max="8"/>
+    <col width="26.28515625" bestFit="1" customWidth="1" style="197" min="9" max="9"/>
+    <col width="27.140625" bestFit="1" customWidth="1" style="197" min="10" max="10"/>
+    <col width="30" bestFit="1" customWidth="1" style="197" min="11" max="11"/>
+    <col width="27.85546875" bestFit="1" customWidth="1" style="197" min="12" max="12"/>
+    <col width="24.85546875" bestFit="1" customWidth="1" style="197" min="13" max="13"/>
   </cols>
   <sheetData>
-    <row r="1" ht="23.25" customHeight="1" s="219">
-      <c r="A1" s="186" t="inlineStr">
+    <row r="1" ht="23.25" customHeight="1" s="197">
+      <c r="A1" s="193" t="inlineStr">
         <is>
           <t>2024 Bechtel Golf League Schedule Tee Time</t>
         </is>
       </c>
-      <c r="B1" s="218" t="n"/>
-      <c r="C1" s="218" t="n"/>
-      <c r="D1" s="218" t="n"/>
-      <c r="E1" s="218" t="n"/>
-      <c r="F1" s="218" t="n"/>
-      <c r="G1" s="218" t="n"/>
-      <c r="H1" s="218" t="n"/>
-      <c r="I1" s="218" t="n"/>
-      <c r="J1" s="218" t="n"/>
-      <c r="K1" s="218" t="n"/>
-      <c r="L1" s="218" t="n"/>
-      <c r="M1" s="218" t="n"/>
-    </row>
-    <row r="2" ht="30" customFormat="1" customHeight="1" s="206">
+      <c r="B1" s="194" t="n"/>
+      <c r="C1" s="194" t="n"/>
+      <c r="D1" s="194" t="n"/>
+      <c r="E1" s="194" t="n"/>
+      <c r="F1" s="194" t="n"/>
+      <c r="G1" s="194" t="n"/>
+      <c r="H1" s="194" t="n"/>
+      <c r="I1" s="194" t="n"/>
+      <c r="J1" s="194" t="n"/>
+      <c r="K1" s="194" t="n"/>
+      <c r="L1" s="194" t="n"/>
+      <c r="M1" s="194" t="n"/>
+    </row>
+    <row r="2" ht="30" customFormat="1" customHeight="1" s="228">
       <c r="A2" s="10" t="inlineStr">
         <is>
           <t>TEE TIME</t>
@@ -5323,7 +5323,7 @@
         <v>45576</v>
       </c>
     </row>
-    <row r="3" ht="30" customHeight="1" s="219">
+    <row r="3" ht="30" customHeight="1" s="197">
       <c r="A3" s="8" t="n">
         <v>0.6597222222222222</v>
       </c>
@@ -5344,7 +5344,7 @@
       </c>
       <c r="M3" s="9" t="n"/>
     </row>
-    <row r="4" ht="30" customHeight="1" s="219">
+    <row r="4" ht="30" customHeight="1" s="197">
       <c r="A4" s="8" t="n">
         <v>0.6666666666666666</v>
       </c>
@@ -5361,7 +5361,7 @@
       <c r="L4" s="9" t="n"/>
       <c r="M4" s="9" t="n"/>
     </row>
-    <row r="5" ht="30" customHeight="1" s="219">
+    <row r="5" ht="30" customHeight="1" s="197">
       <c r="A5" s="8" t="n">
         <v>0.6736111111111112</v>
       </c>
@@ -5378,7 +5378,7 @@
       <c r="L5" s="9" t="n"/>
       <c r="M5" s="9" t="n"/>
     </row>
-    <row r="6" ht="30" customHeight="1" s="219">
+    <row r="6" ht="30" customHeight="1" s="197">
       <c r="A6" s="8" t="n">
         <v>0.6805555555555556</v>
       </c>
@@ -5395,7 +5395,7 @@
       <c r="L6" s="9" t="n"/>
       <c r="M6" s="9" t="n"/>
     </row>
-    <row r="7" ht="30" customHeight="1" s="219">
+    <row r="7" ht="30" customHeight="1" s="197">
       <c r="A7" s="8" t="n">
         <v>0.6875</v>
       </c>
@@ -5412,7 +5412,7 @@
       <c r="L7" s="9" t="n"/>
       <c r="M7" s="9" t="n"/>
     </row>
-    <row r="8" ht="30" customHeight="1" s="219">
+    <row r="8" ht="30" customHeight="1" s="197">
       <c r="A8" s="8" t="n">
         <v>0.6944444444444444</v>
       </c>
@@ -5429,7 +5429,7 @@
       <c r="L8" s="9" t="n"/>
       <c r="M8" s="9" t="n"/>
     </row>
-    <row r="9" ht="30" customHeight="1" s="219">
+    <row r="9" ht="30" customHeight="1" s="197">
       <c r="A9" s="8" t="n">
         <v>0.7013888888888888</v>
       </c>
@@ -5446,7 +5446,7 @@
       <c r="L9" s="9" t="n"/>
       <c r="M9" s="9" t="n"/>
     </row>
-    <row r="10" ht="30" customHeight="1" s="219">
+    <row r="10" ht="30" customHeight="1" s="197">
       <c r="A10" s="8" t="n">
         <v>0.7083333333333334</v>
       </c>
@@ -5463,7 +5463,7 @@
       <c r="L10" s="9" t="n"/>
       <c r="M10" s="9" t="n"/>
     </row>
-    <row r="11" ht="30" customHeight="1" s="219">
+    <row r="11" ht="30" customHeight="1" s="197">
       <c r="A11" s="8" t="n">
         <v>0.7152777777777778</v>
       </c>
@@ -5480,7 +5480,7 @@
       <c r="L11" s="9" t="n"/>
       <c r="M11" s="9" t="n"/>
     </row>
-    <row r="12" ht="30" customHeight="1" s="219">
+    <row r="12" ht="30" customHeight="1" s="197">
       <c r="A12" s="8" t="n">
         <v>0.7222222222222222</v>
       </c>
@@ -5497,7 +5497,7 @@
       <c r="L12" s="9" t="n"/>
       <c r="M12" s="9" t="n"/>
     </row>
-    <row r="13" ht="30" customHeight="1" s="219">
+    <row r="13" ht="30" customHeight="1" s="197">
       <c r="A13" s="8" t="n">
         <v>0.7291666666666666</v>
       </c>
@@ -5514,7 +5514,7 @@
       <c r="L13" s="9" t="n"/>
       <c r="M13" s="9" t="n"/>
     </row>
-    <row r="14" ht="30" customHeight="1" s="219">
+    <row r="14" ht="30" customHeight="1" s="197">
       <c r="A14" s="8" t="n">
         <v>0.7361111111111112</v>
       </c>
@@ -5531,7 +5531,7 @@
       <c r="L14" s="9" t="n"/>
       <c r="M14" s="9" t="n"/>
     </row>
-    <row r="15" ht="30" customHeight="1" s="219">
+    <row r="15" ht="30" customHeight="1" s="197">
       <c r="A15" s="8" t="n">
         <v>0.7430555555555556</v>
       </c>
@@ -5548,7 +5548,7 @@
       <c r="L15" s="9" t="n"/>
       <c r="M15" s="9" t="n"/>
     </row>
-    <row r="16" ht="30" customHeight="1" s="219">
+    <row r="16" ht="30" customHeight="1" s="197">
       <c r="A16" s="8" t="n">
         <v>0.75</v>
       </c>
@@ -5582,41 +5582,41 @@
   <dimension ref="A1:M16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="12.75"/>
   <cols>
-    <col width="24.5703125" bestFit="1" customWidth="1" style="219" min="1" max="1"/>
-    <col width="26.28515625" bestFit="1" customWidth="1" style="188" min="2" max="2"/>
-    <col width="27.140625" bestFit="1" customWidth="1" style="219" min="3" max="3"/>
-    <col width="30" bestFit="1" customWidth="1" style="219" min="4" max="4"/>
-    <col width="27.85546875" bestFit="1" customWidth="1" style="219" min="5" max="5"/>
-    <col width="24.85546875" bestFit="1" customWidth="1" style="219" min="6" max="6"/>
-    <col hidden="1" width="26.28515625" customWidth="1" style="219" min="7" max="7"/>
-    <col hidden="1" width="24.85546875" customWidth="1" style="219" min="8" max="8"/>
-    <col width="26.28515625" bestFit="1" customWidth="1" style="219" min="9" max="9"/>
-    <col width="27.140625" bestFit="1" customWidth="1" style="219" min="10" max="10"/>
-    <col width="30" bestFit="1" customWidth="1" style="219" min="11" max="11"/>
-    <col width="27.85546875" customWidth="1" style="219" min="12" max="12"/>
-    <col width="24.85546875" bestFit="1" customWidth="1" style="219" min="13" max="13"/>
+    <col width="24.5703125" bestFit="1" customWidth="1" style="197" min="1" max="1"/>
+    <col width="26.28515625" bestFit="1" customWidth="1" style="196" min="2" max="2"/>
+    <col width="27.140625" bestFit="1" customWidth="1" style="197" min="3" max="3"/>
+    <col width="30" bestFit="1" customWidth="1" style="197" min="4" max="4"/>
+    <col width="27.85546875" bestFit="1" customWidth="1" style="197" min="5" max="5"/>
+    <col width="24.85546875" bestFit="1" customWidth="1" style="197" min="6" max="6"/>
+    <col hidden="1" width="26.28515625" customWidth="1" style="197" min="7" max="7"/>
+    <col hidden="1" width="24.85546875" customWidth="1" style="197" min="8" max="8"/>
+    <col width="26.28515625" bestFit="1" customWidth="1" style="197" min="9" max="9"/>
+    <col width="27.140625" bestFit="1" customWidth="1" style="197" min="10" max="10"/>
+    <col width="30" bestFit="1" customWidth="1" style="197" min="11" max="11"/>
+    <col width="27.85546875" customWidth="1" style="197" min="12" max="12"/>
+    <col width="24.85546875" bestFit="1" customWidth="1" style="197" min="13" max="13"/>
   </cols>
   <sheetData>
-    <row r="1" ht="23.25" customHeight="1" s="219">
-      <c r="A1" s="186" t="inlineStr">
+    <row r="1" ht="23.25" customHeight="1" s="197">
+      <c r="A1" s="193" t="inlineStr">
         <is>
           <t>2024 Bechtel Golf League Schedule Tee Time</t>
         </is>
       </c>
-      <c r="B1" s="218" t="n"/>
-      <c r="C1" s="218" t="n"/>
-      <c r="D1" s="218" t="n"/>
-      <c r="E1" s="218" t="n"/>
-      <c r="F1" s="218" t="n"/>
-      <c r="G1" s="218" t="n"/>
-      <c r="H1" s="218" t="n"/>
-      <c r="I1" s="218" t="n"/>
-      <c r="J1" s="218" t="n"/>
-      <c r="K1" s="218" t="n"/>
-      <c r="L1" s="218" t="n"/>
-      <c r="M1" s="218" t="n"/>
-    </row>
-    <row r="2" ht="30" customFormat="1" customHeight="1" s="206">
+      <c r="B1" s="194" t="n"/>
+      <c r="C1" s="194" t="n"/>
+      <c r="D1" s="194" t="n"/>
+      <c r="E1" s="194" t="n"/>
+      <c r="F1" s="194" t="n"/>
+      <c r="G1" s="194" t="n"/>
+      <c r="H1" s="194" t="n"/>
+      <c r="I1" s="194" t="n"/>
+      <c r="J1" s="194" t="n"/>
+      <c r="K1" s="194" t="n"/>
+      <c r="L1" s="194" t="n"/>
+      <c r="M1" s="194" t="n"/>
+    </row>
+    <row r="2" ht="30" customFormat="1" customHeight="1" s="228">
       <c r="A2" s="10" t="inlineStr">
         <is>
           <t>TEE TIME</t>
@@ -5659,7 +5659,7 @@
         <v>45590</v>
       </c>
     </row>
-    <row r="3" ht="30" customFormat="1" customHeight="1" s="206">
+    <row r="3" ht="30" customFormat="1" customHeight="1" s="228">
       <c r="A3" s="8" t="n">
         <v>0.6597222222222222</v>
       </c>
@@ -5688,7 +5688,7 @@
       <c r="L3" s="30" t="n"/>
       <c r="M3" s="30" t="n"/>
     </row>
-    <row r="4" ht="30" customHeight="1" s="219">
+    <row r="4" ht="30" customHeight="1" s="197">
       <c r="A4" s="8" t="n">
         <v>0.6666666666666666</v>
       </c>
@@ -5705,7 +5705,7 @@
       <c r="L4" s="9" t="n"/>
       <c r="M4" s="9" t="n"/>
     </row>
-    <row r="5" ht="30" customHeight="1" s="219">
+    <row r="5" ht="30" customHeight="1" s="197">
       <c r="A5" s="8" t="n">
         <v>0.6736111111111112</v>
       </c>
@@ -5722,7 +5722,7 @@
       <c r="L5" s="9" t="n"/>
       <c r="M5" s="9" t="n"/>
     </row>
-    <row r="6" ht="30" customHeight="1" s="219">
+    <row r="6" ht="30" customHeight="1" s="197">
       <c r="A6" s="8" t="n">
         <v>0.6805555555555556</v>
       </c>
@@ -5739,7 +5739,7 @@
       <c r="L6" s="9" t="n"/>
       <c r="M6" s="9" t="n"/>
     </row>
-    <row r="7" ht="30" customHeight="1" s="219">
+    <row r="7" ht="30" customHeight="1" s="197">
       <c r="A7" s="8" t="n">
         <v>0.6875</v>
       </c>
@@ -5756,7 +5756,7 @@
       <c r="L7" s="9" t="n"/>
       <c r="M7" s="9" t="n"/>
     </row>
-    <row r="8" ht="30" customHeight="1" s="219">
+    <row r="8" ht="30" customHeight="1" s="197">
       <c r="A8" s="8" t="n">
         <v>0.6944444444444444</v>
       </c>
@@ -5773,7 +5773,7 @@
       <c r="L8" s="9" t="n"/>
       <c r="M8" s="9" t="n"/>
     </row>
-    <row r="9" ht="30" customHeight="1" s="219">
+    <row r="9" ht="30" customHeight="1" s="197">
       <c r="A9" s="8" t="n">
         <v>0.7013888888888888</v>
       </c>
@@ -5790,7 +5790,7 @@
       <c r="L9" s="9" t="n"/>
       <c r="M9" s="9" t="n"/>
     </row>
-    <row r="10" ht="30" customHeight="1" s="219">
+    <row r="10" ht="30" customHeight="1" s="197">
       <c r="A10" s="8" t="n">
         <v>0.7083333333333334</v>
       </c>
@@ -5807,7 +5807,7 @@
       <c r="L10" s="9" t="n"/>
       <c r="M10" s="9" t="n"/>
     </row>
-    <row r="11" ht="30" customHeight="1" s="219">
+    <row r="11" ht="30" customHeight="1" s="197">
       <c r="A11" s="8" t="n">
         <v>0.7152777777777778</v>
       </c>
@@ -5824,7 +5824,7 @@
       <c r="L11" s="9" t="n"/>
       <c r="M11" s="9" t="n"/>
     </row>
-    <row r="12" ht="30" customHeight="1" s="219">
+    <row r="12" ht="30" customHeight="1" s="197">
       <c r="A12" s="8" t="n">
         <v>0.7222222222222222</v>
       </c>
@@ -5841,7 +5841,7 @@
       <c r="L12" s="9" t="n"/>
       <c r="M12" s="9" t="n"/>
     </row>
-    <row r="13" ht="30" customHeight="1" s="219">
+    <row r="13" ht="30" customHeight="1" s="197">
       <c r="A13" s="8" t="n">
         <v>0.7291666666666666</v>
       </c>
@@ -5858,7 +5858,7 @@
       <c r="L13" s="9" t="n"/>
       <c r="M13" s="9" t="n"/>
     </row>
-    <row r="14" ht="30" customHeight="1" s="219">
+    <row r="14" ht="30" customHeight="1" s="197">
       <c r="A14" s="8" t="n">
         <v>0.7361111111111112</v>
       </c>
@@ -5875,7 +5875,7 @@
       <c r="L14" s="9" t="n"/>
       <c r="M14" s="9" t="n"/>
     </row>
-    <row r="15" ht="30" customHeight="1" s="219">
+    <row r="15" ht="30" customHeight="1" s="197">
       <c r="A15" s="8" t="n">
         <v>0.7430555555555556</v>
       </c>
@@ -5892,7 +5892,7 @@
       <c r="L15" s="9" t="n"/>
       <c r="M15" s="9" t="n"/>
     </row>
-    <row r="16" ht="30" customHeight="1" s="219">
+    <row r="16" ht="30" customHeight="1" s="197">
       <c r="A16" s="8" t="n">
         <v>0.75</v>
       </c>
@@ -5926,41 +5926,41 @@
   <dimension ref="A1:M15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="12.75"/>
   <cols>
-    <col width="18" bestFit="1" customWidth="1" style="219" min="1" max="1"/>
-    <col width="27" bestFit="1" customWidth="1" style="188" min="2" max="2"/>
-    <col width="27.7109375" bestFit="1" customWidth="1" style="219" min="3" max="3"/>
-    <col width="30.7109375" bestFit="1" customWidth="1" style="219" min="4" max="4"/>
-    <col width="28.5703125" bestFit="1" customWidth="1" style="219" min="5" max="5"/>
-    <col width="25.140625" bestFit="1" customWidth="1" style="219" min="6" max="6"/>
-    <col width="27.85546875" bestFit="1" customWidth="1" style="219" min="7" max="7"/>
-    <col width="26.5703125" bestFit="1" customWidth="1" style="219" min="8" max="8"/>
-    <col width="27" bestFit="1" customWidth="1" style="219" min="9" max="9"/>
-    <col width="28.7109375" bestFit="1" customWidth="1" style="219" min="10" max="10"/>
-    <col width="31.7109375" bestFit="1" customWidth="1" style="219" min="11" max="11"/>
-    <col width="29.5703125" bestFit="1" customWidth="1" style="219" min="12" max="12"/>
-    <col width="26.42578125" bestFit="1" customWidth="1" style="219" min="13" max="13"/>
+    <col width="18" bestFit="1" customWidth="1" style="197" min="1" max="1"/>
+    <col width="27" bestFit="1" customWidth="1" style="196" min="2" max="2"/>
+    <col width="27.7109375" bestFit="1" customWidth="1" style="197" min="3" max="3"/>
+    <col width="30.7109375" bestFit="1" customWidth="1" style="197" min="4" max="4"/>
+    <col width="28.5703125" bestFit="1" customWidth="1" style="197" min="5" max="5"/>
+    <col width="25.140625" bestFit="1" customWidth="1" style="197" min="6" max="6"/>
+    <col width="27.85546875" bestFit="1" customWidth="1" style="197" min="7" max="7"/>
+    <col width="26.5703125" bestFit="1" customWidth="1" style="197" min="8" max="8"/>
+    <col width="27" bestFit="1" customWidth="1" style="197" min="9" max="9"/>
+    <col width="28.7109375" bestFit="1" customWidth="1" style="197" min="10" max="10"/>
+    <col width="31.7109375" bestFit="1" customWidth="1" style="197" min="11" max="11"/>
+    <col width="29.5703125" bestFit="1" customWidth="1" style="197" min="12" max="12"/>
+    <col width="26.42578125" bestFit="1" customWidth="1" style="197" min="13" max="13"/>
   </cols>
   <sheetData>
-    <row r="1" ht="23.25" customHeight="1" s="219">
-      <c r="A1" s="186" t="inlineStr">
+    <row r="1" ht="23.25" customHeight="1" s="197">
+      <c r="A1" s="193" t="inlineStr">
         <is>
           <t>2024 Bechtel Golf League Schedule Tee Time</t>
         </is>
       </c>
-      <c r="B1" s="218" t="n"/>
-      <c r="C1" s="218" t="n"/>
-      <c r="D1" s="218" t="n"/>
-      <c r="E1" s="218" t="n"/>
-      <c r="F1" s="218" t="n"/>
-      <c r="G1" s="218" t="n"/>
-      <c r="H1" s="218" t="n"/>
-      <c r="I1" s="218" t="n"/>
-      <c r="J1" s="218" t="n"/>
-      <c r="K1" s="218" t="n"/>
-      <c r="L1" s="218" t="n"/>
-      <c r="M1" s="218" t="n"/>
-    </row>
-    <row r="2" ht="30" customFormat="1" customHeight="1" s="206">
+      <c r="B1" s="194" t="n"/>
+      <c r="C1" s="194" t="n"/>
+      <c r="D1" s="194" t="n"/>
+      <c r="E1" s="194" t="n"/>
+      <c r="F1" s="194" t="n"/>
+      <c r="G1" s="194" t="n"/>
+      <c r="H1" s="194" t="n"/>
+      <c r="I1" s="194" t="n"/>
+      <c r="J1" s="194" t="n"/>
+      <c r="K1" s="194" t="n"/>
+      <c r="L1" s="194" t="n"/>
+      <c r="M1" s="194" t="n"/>
+    </row>
+    <row r="2" ht="30" customFormat="1" customHeight="1" s="228">
       <c r="A2" s="10" t="inlineStr">
         <is>
           <t>TEE TIME</t>
@@ -6003,7 +6003,7 @@
         <v>45548</v>
       </c>
     </row>
-    <row r="3" ht="15" customHeight="1" s="219">
+    <row r="3" ht="15" customHeight="1" s="197">
       <c r="A3" s="8" t="n">
         <v>0.6666666666666666</v>
       </c>
@@ -6024,7 +6024,7 @@
       <c r="L3" s="9" t="n"/>
       <c r="M3" s="9" t="n"/>
     </row>
-    <row r="4" ht="15" customHeight="1" s="219">
+    <row r="4" ht="15" customHeight="1" s="197">
       <c r="A4" s="8" t="n">
         <v>0.6736111111111112</v>
       </c>
@@ -6041,7 +6041,7 @@
       <c r="L4" s="9" t="n"/>
       <c r="M4" s="9" t="n"/>
     </row>
-    <row r="5" ht="30" customHeight="1" s="219">
+    <row r="5" ht="30" customHeight="1" s="197">
       <c r="A5" s="8" t="n">
         <v>0.6805555555555556</v>
       </c>
@@ -6062,7 +6062,7 @@
       <c r="L5" s="9" t="n"/>
       <c r="M5" s="9" t="n"/>
     </row>
-    <row r="6" ht="15" customHeight="1" s="219">
+    <row r="6" ht="15" customHeight="1" s="197">
       <c r="A6" s="8" t="n">
         <v>0.6875</v>
       </c>
@@ -6083,7 +6083,7 @@
       <c r="L6" s="9" t="n"/>
       <c r="M6" s="9" t="n"/>
     </row>
-    <row r="7" ht="45" customHeight="1" s="219">
+    <row r="7" ht="45" customHeight="1" s="197">
       <c r="A7" s="8" t="n">
         <v>0.6944444444444444</v>
       </c>
@@ -6104,7 +6104,7 @@
       <c r="L7" s="9" t="n"/>
       <c r="M7" s="9" t="n"/>
     </row>
-    <row r="8" ht="15" customHeight="1" s="219">
+    <row r="8" ht="15" customHeight="1" s="197">
       <c r="A8" s="8" t="n">
         <v>0.7013888888888888</v>
       </c>
@@ -6121,7 +6121,7 @@
       <c r="L8" s="9" t="n"/>
       <c r="M8" s="9" t="n"/>
     </row>
-    <row r="9" ht="15" customHeight="1" s="219">
+    <row r="9" ht="15" customHeight="1" s="197">
       <c r="A9" s="8" t="n">
         <v>0.7083333333333334</v>
       </c>
@@ -6138,7 +6138,7 @@
       <c r="L9" s="9" t="n"/>
       <c r="M9" s="9" t="n"/>
     </row>
-    <row r="10" ht="15" customHeight="1" s="219">
+    <row r="10" ht="15" customHeight="1" s="197">
       <c r="A10" s="8" t="n">
         <v>0.7152777777777778</v>
       </c>
@@ -6155,7 +6155,7 @@
       <c r="L10" s="9" t="n"/>
       <c r="M10" s="9" t="n"/>
     </row>
-    <row r="11" ht="15" customHeight="1" s="219">
+    <row r="11" ht="15" customHeight="1" s="197">
       <c r="A11" s="8" t="n">
         <v>0.7222222222222222</v>
       </c>
@@ -6172,7 +6172,7 @@
       <c r="L11" s="9" t="n"/>
       <c r="M11" s="9" t="n"/>
     </row>
-    <row r="12" ht="15" customHeight="1" s="219">
+    <row r="12" ht="15" customHeight="1" s="197">
       <c r="A12" s="8" t="n">
         <v>0.7291666666666666</v>
       </c>
@@ -6189,7 +6189,7 @@
       <c r="L12" s="9" t="n"/>
       <c r="M12" s="9" t="n"/>
     </row>
-    <row r="13" ht="15" customHeight="1" s="219">
+    <row r="13" ht="15" customHeight="1" s="197">
       <c r="A13" s="8" t="n">
         <v>0.7361111111111112</v>
       </c>
@@ -6206,7 +6206,7 @@
       <c r="L13" s="9" t="n"/>
       <c r="M13" s="9" t="n"/>
     </row>
-    <row r="14" ht="15" customHeight="1" s="219">
+    <row r="14" ht="15" customHeight="1" s="197">
       <c r="A14" s="8" t="n">
         <v>0.7430555555555556</v>
       </c>
@@ -6223,7 +6223,7 @@
       <c r="L14" s="9" t="n"/>
       <c r="M14" s="9" t="n"/>
     </row>
-    <row r="15" ht="15" customHeight="1" s="219">
+    <row r="15" ht="15" customHeight="1" s="197">
       <c r="A15" s="8" t="n">
         <v>0.75</v>
       </c>
@@ -6257,41 +6257,41 @@
   <dimension ref="A1:M15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="12.75"/>
   <cols>
-    <col width="24.5703125" bestFit="1" customWidth="1" style="219" min="1" max="1"/>
-    <col width="21.140625" bestFit="1" customWidth="1" style="188" min="2" max="2"/>
-    <col width="21.7109375" bestFit="1" customWidth="1" style="219" min="3" max="3"/>
-    <col width="24.5703125" bestFit="1" customWidth="1" style="219" min="4" max="4"/>
-    <col width="22.28515625" bestFit="1" customWidth="1" style="219" min="5" max="5"/>
-    <col width="19.5703125" bestFit="1" customWidth="1" style="219" min="6" max="6"/>
-    <col hidden="1" width="22.140625" customWidth="1" style="219" min="7" max="7"/>
-    <col hidden="1" width="20.7109375" customWidth="1" style="219" min="8" max="8"/>
-    <col width="21" bestFit="1" customWidth="1" style="219" min="9" max="9"/>
-    <col width="21.5703125" bestFit="1" customWidth="1" style="219" min="10" max="10"/>
-    <col width="24.5703125" bestFit="1" customWidth="1" style="219" min="11" max="11"/>
-    <col width="24.28515625" bestFit="1" customWidth="1" style="219" min="12" max="12"/>
-    <col width="21.140625" bestFit="1" customWidth="1" style="219" min="13" max="13"/>
+    <col width="24.5703125" bestFit="1" customWidth="1" style="197" min="1" max="1"/>
+    <col width="21.140625" bestFit="1" customWidth="1" style="196" min="2" max="2"/>
+    <col width="21.7109375" bestFit="1" customWidth="1" style="197" min="3" max="3"/>
+    <col width="24.5703125" bestFit="1" customWidth="1" style="197" min="4" max="4"/>
+    <col width="22.28515625" bestFit="1" customWidth="1" style="197" min="5" max="5"/>
+    <col width="19.5703125" bestFit="1" customWidth="1" style="197" min="6" max="6"/>
+    <col hidden="1" width="22.140625" customWidth="1" style="197" min="7" max="7"/>
+    <col hidden="1" width="20.7109375" customWidth="1" style="197" min="8" max="8"/>
+    <col width="21" bestFit="1" customWidth="1" style="197" min="9" max="9"/>
+    <col width="21.5703125" bestFit="1" customWidth="1" style="197" min="10" max="10"/>
+    <col width="24.5703125" bestFit="1" customWidth="1" style="197" min="11" max="11"/>
+    <col width="24.28515625" bestFit="1" customWidth="1" style="197" min="12" max="12"/>
+    <col width="21.140625" bestFit="1" customWidth="1" style="197" min="13" max="13"/>
   </cols>
   <sheetData>
-    <row r="1" ht="23.25" customHeight="1" s="219">
-      <c r="A1" s="186" t="inlineStr">
+    <row r="1" ht="23.25" customHeight="1" s="197">
+      <c r="A1" s="193" t="inlineStr">
         <is>
           <t>2024 Bechtel Golf League Schedule Tee Time</t>
         </is>
       </c>
-      <c r="B1" s="218" t="n"/>
-      <c r="C1" s="218" t="n"/>
-      <c r="D1" s="218" t="n"/>
-      <c r="E1" s="218" t="n"/>
-      <c r="F1" s="218" t="n"/>
-      <c r="G1" s="218" t="n"/>
-      <c r="H1" s="218" t="n"/>
-      <c r="I1" s="218" t="n"/>
-      <c r="J1" s="218" t="n"/>
-      <c r="K1" s="218" t="n"/>
-      <c r="L1" s="218" t="n"/>
-      <c r="M1" s="218" t="n"/>
-    </row>
-    <row r="2" ht="30" customFormat="1" customHeight="1" s="206">
+      <c r="B1" s="194" t="n"/>
+      <c r="C1" s="194" t="n"/>
+      <c r="D1" s="194" t="n"/>
+      <c r="E1" s="194" t="n"/>
+      <c r="F1" s="194" t="n"/>
+      <c r="G1" s="194" t="n"/>
+      <c r="H1" s="194" t="n"/>
+      <c r="I1" s="194" t="n"/>
+      <c r="J1" s="194" t="n"/>
+      <c r="K1" s="194" t="n"/>
+      <c r="L1" s="194" t="n"/>
+      <c r="M1" s="194" t="n"/>
+    </row>
+    <row r="2" ht="30" customFormat="1" customHeight="1" s="228">
       <c r="A2" s="10" t="inlineStr">
         <is>
           <t>TEE TIME</t>
@@ -6334,7 +6334,7 @@
         <v>45506</v>
       </c>
     </row>
-    <row r="3" ht="30" customHeight="1" s="219">
+    <row r="3" ht="30" customHeight="1" s="197">
       <c r="A3" s="8" t="n">
         <v>0.6666666666666666</v>
       </c>
@@ -6355,7 +6355,7 @@
       <c r="L3" s="9" t="n"/>
       <c r="M3" s="9" t="n"/>
     </row>
-    <row r="4" ht="30" customHeight="1" s="219">
+    <row r="4" ht="30" customHeight="1" s="197">
       <c r="A4" s="8" t="n">
         <v>0.6736111111111112</v>
       </c>
@@ -6372,7 +6372,7 @@
       <c r="L4" s="9" t="n"/>
       <c r="M4" s="9" t="n"/>
     </row>
-    <row r="5" ht="30" customHeight="1" s="219">
+    <row r="5" ht="30" customHeight="1" s="197">
       <c r="A5" s="8" t="n">
         <v>0.6805555555555556</v>
       </c>
@@ -6389,7 +6389,7 @@
       <c r="L5" s="9" t="n"/>
       <c r="M5" s="9" t="n"/>
     </row>
-    <row r="6" ht="30" customHeight="1" s="219">
+    <row r="6" ht="30" customHeight="1" s="197">
       <c r="A6" s="8" t="n">
         <v>0.6875</v>
       </c>
@@ -6414,7 +6414,7 @@
       <c r="L6" s="9" t="n"/>
       <c r="M6" s="9" t="n"/>
     </row>
-    <row r="7" ht="30" customHeight="1" s="219">
+    <row r="7" ht="30" customHeight="1" s="197">
       <c r="A7" s="8" t="n">
         <v>0.6944444444444444</v>
       </c>
@@ -6439,7 +6439,7 @@
       <c r="L7" s="9" t="n"/>
       <c r="M7" s="9" t="n"/>
     </row>
-    <row r="8" ht="30" customHeight="1" s="219">
+    <row r="8" ht="30" customHeight="1" s="197">
       <c r="A8" s="8" t="n">
         <v>0.7013888888888888</v>
       </c>
@@ -6456,7 +6456,7 @@
       <c r="L8" s="9" t="n"/>
       <c r="M8" s="9" t="n"/>
     </row>
-    <row r="9" ht="30" customHeight="1" s="219">
+    <row r="9" ht="30" customHeight="1" s="197">
       <c r="A9" s="8" t="n">
         <v>0.7083333333333334</v>
       </c>
@@ -6473,7 +6473,7 @@
       <c r="L9" s="9" t="n"/>
       <c r="M9" s="9" t="n"/>
     </row>
-    <row r="10" ht="30" customHeight="1" s="219">
+    <row r="10" ht="30" customHeight="1" s="197">
       <c r="A10" s="8" t="n">
         <v>0.7152777777777778</v>
       </c>
@@ -6490,7 +6490,7 @@
       <c r="L10" s="9" t="n"/>
       <c r="M10" s="9" t="n"/>
     </row>
-    <row r="11" ht="30" customHeight="1" s="219">
+    <row r="11" ht="30" customHeight="1" s="197">
       <c r="A11" s="8" t="n">
         <v>0.7222222222222222</v>
       </c>
@@ -6507,7 +6507,7 @@
       <c r="L11" s="9" t="n"/>
       <c r="M11" s="9" t="n"/>
     </row>
-    <row r="12" ht="30" customHeight="1" s="219">
+    <row r="12" ht="30" customHeight="1" s="197">
       <c r="A12" s="8" t="n">
         <v>0.7291666666666666</v>
       </c>
@@ -6524,7 +6524,7 @@
       <c r="L12" s="9" t="n"/>
       <c r="M12" s="9" t="n"/>
     </row>
-    <row r="13" ht="30" customHeight="1" s="219">
+    <row r="13" ht="30" customHeight="1" s="197">
       <c r="A13" s="8" t="n">
         <v>0.7361111111111112</v>
       </c>
@@ -6541,7 +6541,7 @@
       <c r="L13" s="9" t="n"/>
       <c r="M13" s="9" t="n"/>
     </row>
-    <row r="14" ht="30" customHeight="1" s="219">
+    <row r="14" ht="30" customHeight="1" s="197">
       <c r="A14" s="8" t="n">
         <v>0.7430555555555556</v>
       </c>
@@ -6558,7 +6558,7 @@
       <c r="L14" s="9" t="n"/>
       <c r="M14" s="9" t="n"/>
     </row>
-    <row r="15" ht="30" customHeight="1" s="219">
+    <row r="15" ht="30" customHeight="1" s="197">
       <c r="A15" s="8" t="n">
         <v>0.75</v>
       </c>
@@ -6592,31 +6592,31 @@
   <dimension ref="A1:M15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="12.75"/>
   <cols>
-    <col width="24.5703125" bestFit="1" customWidth="1" style="219" min="1" max="1"/>
-    <col width="25.7109375" customWidth="1" style="188" min="2" max="2"/>
-    <col width="25.7109375" customWidth="1" style="219" min="3" max="13"/>
+    <col width="24.5703125" bestFit="1" customWidth="1" style="197" min="1" max="1"/>
+    <col width="25.7109375" customWidth="1" style="196" min="2" max="2"/>
+    <col width="25.7109375" customWidth="1" style="197" min="3" max="13"/>
   </cols>
   <sheetData>
-    <row r="1" ht="23.25" customHeight="1" s="219">
-      <c r="A1" s="186" t="inlineStr">
+    <row r="1" ht="23.25" customHeight="1" s="197">
+      <c r="A1" s="193" t="inlineStr">
         <is>
           <t>2024 Bechtel Golf League Schedule Tee Time</t>
         </is>
       </c>
-      <c r="B1" s="218" t="n"/>
-      <c r="C1" s="218" t="n"/>
-      <c r="D1" s="218" t="n"/>
-      <c r="E1" s="218" t="n"/>
-      <c r="F1" s="218" t="n"/>
-      <c r="G1" s="218" t="n"/>
-      <c r="H1" s="218" t="n"/>
-      <c r="I1" s="218" t="n"/>
-      <c r="J1" s="218" t="n"/>
-      <c r="K1" s="218" t="n"/>
-      <c r="L1" s="218" t="n"/>
-      <c r="M1" s="218" t="n"/>
-    </row>
-    <row r="2" ht="30" customFormat="1" customHeight="1" s="206">
+      <c r="B1" s="194" t="n"/>
+      <c r="C1" s="194" t="n"/>
+      <c r="D1" s="194" t="n"/>
+      <c r="E1" s="194" t="n"/>
+      <c r="F1" s="194" t="n"/>
+      <c r="G1" s="194" t="n"/>
+      <c r="H1" s="194" t="n"/>
+      <c r="I1" s="194" t="n"/>
+      <c r="J1" s="194" t="n"/>
+      <c r="K1" s="194" t="n"/>
+      <c r="L1" s="194" t="n"/>
+      <c r="M1" s="194" t="n"/>
+    </row>
+    <row r="2" ht="30" customFormat="1" customHeight="1" s="228">
       <c r="A2" s="10" t="inlineStr">
         <is>
           <t>TEE TIME</t>
@@ -6659,7 +6659,7 @@
         <v>45520</v>
       </c>
     </row>
-    <row r="3" ht="30" customHeight="1" s="219">
+    <row r="3" ht="30" customHeight="1" s="197">
       <c r="A3" s="8" t="n">
         <v>0.6666666666666666</v>
       </c>
@@ -6680,7 +6680,7 @@
       <c r="L3" s="9" t="n"/>
       <c r="M3" s="9" t="n"/>
     </row>
-    <row r="4" ht="30" customHeight="1" s="219">
+    <row r="4" ht="30" customHeight="1" s="197">
       <c r="A4" s="8" t="n">
         <v>0.6736111111111112</v>
       </c>
@@ -6697,7 +6697,7 @@
       <c r="L4" s="9" t="n"/>
       <c r="M4" s="9" t="n"/>
     </row>
-    <row r="5" ht="30" customHeight="1" s="219">
+    <row r="5" ht="30" customHeight="1" s="197">
       <c r="A5" s="8" t="n">
         <v>0.6805555555555556</v>
       </c>
@@ -6718,7 +6718,7 @@
       <c r="L5" s="9" t="n"/>
       <c r="M5" s="9" t="n"/>
     </row>
-    <row r="6" ht="30" customHeight="1" s="219">
+    <row r="6" ht="30" customHeight="1" s="197">
       <c r="A6" s="8" t="n">
         <v>0.6875</v>
       </c>
@@ -6740,7 +6740,7 @@
       <c r="L6" s="9" t="n"/>
       <c r="M6" s="9" t="n"/>
     </row>
-    <row r="7" ht="30" customHeight="1" s="219">
+    <row r="7" ht="30" customHeight="1" s="197">
       <c r="A7" s="8" t="n">
         <v>0.6944444444444444</v>
       </c>
@@ -6766,7 +6766,7 @@
       <c r="L7" s="9" t="n"/>
       <c r="M7" s="9" t="n"/>
     </row>
-    <row r="8" ht="30" customHeight="1" s="219">
+    <row r="8" ht="30" customHeight="1" s="197">
       <c r="A8" s="8" t="n">
         <v>0.7013888888888888</v>
       </c>
@@ -6783,7 +6783,7 @@
       <c r="L8" s="9" t="n"/>
       <c r="M8" s="9" t="n"/>
     </row>
-    <row r="9" ht="30" customHeight="1" s="219">
+    <row r="9" ht="30" customHeight="1" s="197">
       <c r="A9" s="8" t="n">
         <v>0.7083333333333334</v>
       </c>
@@ -6800,7 +6800,7 @@
       <c r="L9" s="9" t="n"/>
       <c r="M9" s="9" t="n"/>
     </row>
-    <row r="10" ht="30" customHeight="1" s="219">
+    <row r="10" ht="30" customHeight="1" s="197">
       <c r="A10" s="8" t="n">
         <v>0.7152777777777778</v>
       </c>
@@ -6817,7 +6817,7 @@
       <c r="L10" s="9" t="n"/>
       <c r="M10" s="9" t="n"/>
     </row>
-    <row r="11" ht="30" customHeight="1" s="219">
+    <row r="11" ht="30" customHeight="1" s="197">
       <c r="A11" s="8" t="n">
         <v>0.7222222222222222</v>
       </c>
@@ -6834,7 +6834,7 @@
       <c r="L11" s="9" t="n"/>
       <c r="M11" s="9" t="n"/>
     </row>
-    <row r="12" ht="30" customHeight="1" s="219">
+    <row r="12" ht="30" customHeight="1" s="197">
       <c r="A12" s="8" t="n">
         <v>0.7291666666666666</v>
       </c>
@@ -6851,7 +6851,7 @@
       <c r="L12" s="9" t="n"/>
       <c r="M12" s="9" t="n"/>
     </row>
-    <row r="13" ht="30" customHeight="1" s="219">
+    <row r="13" ht="30" customHeight="1" s="197">
       <c r="A13" s="8" t="n">
         <v>0.7361111111111112</v>
       </c>
@@ -6868,7 +6868,7 @@
       <c r="L13" s="9" t="n"/>
       <c r="M13" s="9" t="n"/>
     </row>
-    <row r="14" ht="30" customHeight="1" s="219">
+    <row r="14" ht="30" customHeight="1" s="197">
       <c r="A14" s="8" t="n">
         <v>0.7430555555555556</v>
       </c>
@@ -6885,7 +6885,7 @@
       <c r="L14" s="9" t="n"/>
       <c r="M14" s="9" t="n"/>
     </row>
-    <row r="15" ht="30" customHeight="1" s="219">
+    <row r="15" ht="30" customHeight="1" s="197">
       <c r="A15" s="8" t="n">
         <v>0.75</v>
       </c>
@@ -6919,41 +6919,41 @@
   <dimension ref="A1:M15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="12.75"/>
   <cols>
-    <col width="18" bestFit="1" customWidth="1" style="219" min="1" max="1"/>
-    <col width="24" bestFit="1" customWidth="1" style="188" min="2" max="2"/>
-    <col width="24.5703125" bestFit="1" customWidth="1" style="219" min="3" max="3"/>
-    <col width="27.5703125" bestFit="1" customWidth="1" style="219" min="4" max="4"/>
-    <col width="25.42578125" bestFit="1" customWidth="1" style="219" min="5" max="5"/>
-    <col width="22.140625" bestFit="1" customWidth="1" style="219" min="6" max="6"/>
-    <col width="25" bestFit="1" customWidth="1" style="219" min="7" max="7"/>
-    <col width="23.42578125" bestFit="1" customWidth="1" style="219" min="8" max="8"/>
-    <col width="24" bestFit="1" customWidth="1" style="219" min="9" max="9"/>
-    <col width="24.5703125" bestFit="1" customWidth="1" style="219" min="10" max="10"/>
-    <col width="27.5703125" bestFit="1" customWidth="1" style="219" min="11" max="11"/>
-    <col width="25.42578125" bestFit="1" customWidth="1" style="219" min="12" max="12"/>
-    <col width="22.140625" bestFit="1" customWidth="1" style="219" min="13" max="13"/>
+    <col width="18" bestFit="1" customWidth="1" style="197" min="1" max="1"/>
+    <col width="24" bestFit="1" customWidth="1" style="196" min="2" max="2"/>
+    <col width="24.5703125" bestFit="1" customWidth="1" style="197" min="3" max="3"/>
+    <col width="27.5703125" bestFit="1" customWidth="1" style="197" min="4" max="4"/>
+    <col width="25.42578125" bestFit="1" customWidth="1" style="197" min="5" max="5"/>
+    <col width="22.140625" bestFit="1" customWidth="1" style="197" min="6" max="6"/>
+    <col width="25" bestFit="1" customWidth="1" style="197" min="7" max="7"/>
+    <col width="23.42578125" bestFit="1" customWidth="1" style="197" min="8" max="8"/>
+    <col width="24" bestFit="1" customWidth="1" style="197" min="9" max="9"/>
+    <col width="24.5703125" bestFit="1" customWidth="1" style="197" min="10" max="10"/>
+    <col width="27.5703125" bestFit="1" customWidth="1" style="197" min="11" max="11"/>
+    <col width="25.42578125" bestFit="1" customWidth="1" style="197" min="12" max="12"/>
+    <col width="22.140625" bestFit="1" customWidth="1" style="197" min="13" max="13"/>
   </cols>
   <sheetData>
-    <row r="1" ht="23.25" customHeight="1" s="219">
-      <c r="A1" s="186" t="inlineStr">
+    <row r="1" ht="23.25" customHeight="1" s="197">
+      <c r="A1" s="193" t="inlineStr">
         <is>
           <t>2024 Bechtel Golf League Schedule Tee Time</t>
         </is>
       </c>
-      <c r="B1" s="218" t="n"/>
-      <c r="C1" s="218" t="n"/>
-      <c r="D1" s="218" t="n"/>
-      <c r="E1" s="218" t="n"/>
-      <c r="F1" s="218" t="n"/>
-      <c r="G1" s="218" t="n"/>
-      <c r="H1" s="218" t="n"/>
-      <c r="I1" s="218" t="n"/>
-      <c r="J1" s="218" t="n"/>
-      <c r="K1" s="218" t="n"/>
-      <c r="L1" s="218" t="n"/>
-      <c r="M1" s="218" t="n"/>
-    </row>
-    <row r="2" ht="30" customFormat="1" customHeight="1" s="206">
+      <c r="B1" s="194" t="n"/>
+      <c r="C1" s="194" t="n"/>
+      <c r="D1" s="194" t="n"/>
+      <c r="E1" s="194" t="n"/>
+      <c r="F1" s="194" t="n"/>
+      <c r="G1" s="194" t="n"/>
+      <c r="H1" s="194" t="n"/>
+      <c r="I1" s="194" t="n"/>
+      <c r="J1" s="194" t="n"/>
+      <c r="K1" s="194" t="n"/>
+      <c r="L1" s="194" t="n"/>
+      <c r="M1" s="194" t="n"/>
+    </row>
+    <row r="2" ht="30" customFormat="1" customHeight="1" s="228">
       <c r="A2" s="10" t="inlineStr">
         <is>
           <t>TEE TIME</t>
@@ -6996,7 +6996,7 @@
         <v>45534</v>
       </c>
     </row>
-    <row r="3" ht="30" customHeight="1" s="219">
+    <row r="3" ht="30" customHeight="1" s="197">
       <c r="A3" s="8" t="n">
         <v>0.6666666666666666</v>
       </c>
@@ -7013,7 +7013,7 @@
       <c r="L3" s="9" t="n"/>
       <c r="M3" s="9" t="n"/>
     </row>
-    <row r="4" ht="30" customHeight="1" s="219">
+    <row r="4" ht="30" customHeight="1" s="197">
       <c r="A4" s="8" t="n">
         <v>0.6736111111111112</v>
       </c>
@@ -7030,7 +7030,7 @@
       <c r="L4" s="9" t="n"/>
       <c r="M4" s="9" t="n"/>
     </row>
-    <row r="5" ht="30" customHeight="1" s="219">
+    <row r="5" ht="30" customHeight="1" s="197">
       <c r="A5" s="8" t="n">
         <v>0.6805555555555556</v>
       </c>
@@ -7047,7 +7047,7 @@
       <c r="L5" s="9" t="n"/>
       <c r="M5" s="9" t="n"/>
     </row>
-    <row r="6" ht="46.5" customHeight="1" s="219">
+    <row r="6" ht="46.5" customHeight="1" s="197">
       <c r="A6" s="8" t="n">
         <v>0.6875</v>
       </c>
@@ -7075,7 +7075,7 @@
       <c r="L6" s="9" t="n"/>
       <c r="M6" s="9" t="n"/>
     </row>
-    <row r="7" ht="30" customHeight="1" s="219">
+    <row r="7" ht="30" customHeight="1" s="197">
       <c r="A7" s="8" t="n">
         <v>0.6944444444444444</v>
       </c>
@@ -7100,7 +7100,7 @@
       <c r="L7" s="9" t="n"/>
       <c r="M7" s="9" t="n"/>
     </row>
-    <row r="8" ht="30" customHeight="1" s="219">
+    <row r="8" ht="30" customHeight="1" s="197">
       <c r="A8" s="8" t="n">
         <v>0.7013888888888888</v>
       </c>
@@ -7117,7 +7117,7 @@
       <c r="L8" s="9" t="n"/>
       <c r="M8" s="9" t="n"/>
     </row>
-    <row r="9" ht="30" customHeight="1" s="219">
+    <row r="9" ht="30" customHeight="1" s="197">
       <c r="A9" s="8" t="n">
         <v>0.7083333333333334</v>
       </c>
@@ -7134,7 +7134,7 @@
       <c r="L9" s="9" t="n"/>
       <c r="M9" s="9" t="n"/>
     </row>
-    <row r="10" ht="30" customHeight="1" s="219">
+    <row r="10" ht="30" customHeight="1" s="197">
       <c r="A10" s="8" t="n">
         <v>0.7152777777777778</v>
       </c>
@@ -7151,7 +7151,7 @@
       <c r="L10" s="9" t="n"/>
       <c r="M10" s="9" t="n"/>
     </row>
-    <row r="11" ht="30" customHeight="1" s="219">
+    <row r="11" ht="30" customHeight="1" s="197">
       <c r="A11" s="8" t="n">
         <v>0.7222222222222222</v>
       </c>
@@ -7168,7 +7168,7 @@
       <c r="L11" s="9" t="n"/>
       <c r="M11" s="9" t="n"/>
     </row>
-    <row r="12" ht="30" customHeight="1" s="219">
+    <row r="12" ht="30" customHeight="1" s="197">
       <c r="A12" s="8" t="n">
         <v>0.7291666666666666</v>
       </c>
@@ -7185,7 +7185,7 @@
       <c r="L12" s="9" t="n"/>
       <c r="M12" s="9" t="n"/>
     </row>
-    <row r="13" ht="30" customHeight="1" s="219">
+    <row r="13" ht="30" customHeight="1" s="197">
       <c r="A13" s="8" t="n">
         <v>0.7361111111111112</v>
       </c>
@@ -7202,7 +7202,7 @@
       <c r="L13" s="9" t="n"/>
       <c r="M13" s="9" t="n"/>
     </row>
-    <row r="14" ht="30" customHeight="1" s="219">
+    <row r="14" ht="30" customHeight="1" s="197">
       <c r="A14" s="8" t="n">
         <v>0.7430555555555556</v>
       </c>
@@ -7219,7 +7219,7 @@
       <c r="L14" s="9" t="n"/>
       <c r="M14" s="9" t="n"/>
     </row>
-    <row r="15" ht="30" customHeight="1" s="219">
+    <row r="15" ht="30" customHeight="1" s="197">
       <c r="A15" s="8" t="n">
         <v>0.75</v>
       </c>
@@ -7253,31 +7253,31 @@
   <dimension ref="A1:M29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="12.75"/>
   <cols>
-    <col width="18.28515625" bestFit="1" customWidth="1" style="219" min="2" max="2"/>
-    <col width="18.5703125" customWidth="1" style="219" min="3" max="3"/>
-    <col width="19.42578125" customWidth="1" style="219" min="4" max="4"/>
-    <col width="19" bestFit="1" customWidth="1" style="219" min="5" max="5"/>
-    <col width="20.28515625" customWidth="1" style="219" min="6" max="6"/>
-    <col width="21.28515625" bestFit="1" customWidth="1" style="219" min="7" max="7"/>
-    <col width="19" bestFit="1" customWidth="1" style="219" min="8" max="8"/>
-    <col width="20.42578125" bestFit="1" customWidth="1" style="219" min="9" max="9"/>
-    <col width="19.5703125" bestFit="1" customWidth="1" style="219" min="10" max="10"/>
+    <col width="18.28515625" bestFit="1" customWidth="1" style="197" min="2" max="2"/>
+    <col width="18.5703125" customWidth="1" style="197" min="3" max="3"/>
+    <col width="19.42578125" customWidth="1" style="197" min="4" max="4"/>
+    <col width="19" bestFit="1" customWidth="1" style="197" min="5" max="5"/>
+    <col width="20.28515625" customWidth="1" style="197" min="6" max="6"/>
+    <col width="21.28515625" bestFit="1" customWidth="1" style="197" min="7" max="7"/>
+    <col width="19" bestFit="1" customWidth="1" style="197" min="8" max="8"/>
+    <col width="20.42578125" bestFit="1" customWidth="1" style="197" min="9" max="9"/>
+    <col width="19.5703125" bestFit="1" customWidth="1" style="197" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="23.25" customHeight="1" s="219">
-      <c r="B1" s="187" t="inlineStr">
+    <row r="1" ht="23.25" customHeight="1" s="197">
+      <c r="B1" s="195" t="inlineStr">
         <is>
           <t>2026 iCON Golf League Schedule</t>
         </is>
       </c>
-      <c r="C1" s="218" t="n"/>
-      <c r="D1" s="218" t="n"/>
-      <c r="E1" s="218" t="n"/>
-      <c r="F1" s="218" t="n"/>
-      <c r="G1" s="218" t="n"/>
-      <c r="H1" s="218" t="n"/>
-      <c r="I1" s="218" t="n"/>
-      <c r="J1" s="218" t="n"/>
+      <c r="C1" s="194" t="n"/>
+      <c r="D1" s="194" t="n"/>
+      <c r="E1" s="194" t="n"/>
+      <c r="F1" s="194" t="n"/>
+      <c r="G1" s="194" t="n"/>
+      <c r="H1" s="194" t="n"/>
+      <c r="I1" s="194" t="n"/>
+      <c r="J1" s="194" t="n"/>
     </row>
     <row r="2">
       <c r="B2" s="6" t="inlineStr">
@@ -7749,7 +7749,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="E13" s="188" t="n"/>
+      <c r="E13" s="196" t="n"/>
     </row>
     <row r="14">
       <c r="B14" s="2" t="inlineStr">
@@ -7797,7 +7797,7 @@
       </c>
       <c r="F15" s="3" t="n"/>
     </row>
-    <row r="16" ht="13.5" customHeight="1" s="219">
+    <row r="16" ht="13.5" customHeight="1" s="197">
       <c r="B16" s="5" t="n">
         <v>2</v>
       </c>
@@ -7820,7 +7820,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="13.5" customHeight="1" s="219">
+    <row r="17" ht="13.5" customHeight="1" s="197">
       <c r="B17" s="5">
         <f>B16+1</f>
         <v/>
@@ -7844,7 +7844,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="13.5" customHeight="1" s="219">
+    <row r="18" ht="13.5" customHeight="1" s="197">
       <c r="B18" s="5">
         <f>B17+1</f>
         <v/>
@@ -7855,7 +7855,7 @@
         </is>
       </c>
       <c r="D18" s="105" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="E18" s="106" t="inlineStr">
         <is>
@@ -7879,7 +7879,7 @@
         </is>
       </c>
       <c r="D19" s="108" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E19" s="106" t="inlineStr">
         <is>
@@ -7888,7 +7888,7 @@
       </c>
       <c r="F19" s="3" t="n"/>
     </row>
-    <row r="20" ht="13.5" customHeight="1" s="219">
+    <row r="20" ht="13.5" customHeight="1" s="197">
       <c r="B20" s="5">
         <f>B19+1</f>
         <v/>
@@ -7913,7 +7913,7 @@
       </c>
       <c r="G20" s="4" t="n"/>
     </row>
-    <row r="21" ht="13.5" customHeight="1" s="219">
+    <row r="21" ht="13.5" customHeight="1" s="197">
       <c r="B21" s="5">
         <f>B20+1</f>
         <v/>
@@ -7937,7 +7937,7 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="13.5" customHeight="1" s="219">
+    <row r="22" ht="13.5" customHeight="1" s="197">
       <c r="B22" s="5">
         <f>B21+1</f>
         <v/>
@@ -7985,7 +7985,7 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="13.5" customHeight="1" s="219">
+    <row r="24" ht="13.5" customHeight="1" s="197">
       <c r="B24" s="5">
         <f>B23+1</f>
         <v/>
@@ -8034,7 +8034,7 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="13.5" customHeight="1" s="219">
+    <row r="26" ht="13.5" customHeight="1" s="197">
       <c r="B26" s="5">
         <f>B25+1</f>
         <v/>
@@ -8082,7 +8082,7 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="13.5" customHeight="1" s="219">
+    <row r="28" ht="13.5" customHeight="1" s="197">
       <c r="B28" s="5">
         <f>B27+1</f>
         <v/>
@@ -8106,7 +8106,7 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="13.5" customHeight="1" s="219">
+    <row r="29" ht="13.5" customHeight="1" s="197">
       <c r="B29" s="5">
         <f>B28+1</f>
         <v/>
@@ -8159,129 +8159,129 @@
   <dimension ref="B1:AI46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="12.75"/>
   <cols>
-    <col width="12" customWidth="1" style="219" min="2" max="2"/>
-    <col width="17" bestFit="1" customWidth="1" style="219" min="3" max="3"/>
-    <col width="11.85546875" customWidth="1" style="219" min="4" max="4"/>
-    <col width="9.140625" customWidth="1" style="219" min="6" max="8"/>
-    <col width="11" bestFit="1" customWidth="1" style="219" min="9" max="9"/>
-    <col width="9.140625" customWidth="1" style="219" min="10" max="10"/>
-    <col width="14" bestFit="1" customWidth="1" style="219" min="11" max="11"/>
-    <col width="15.5703125" bestFit="1" customWidth="1" style="219" min="12" max="12"/>
-    <col width="13.5703125" bestFit="1" customWidth="1" style="219" min="13" max="13"/>
-    <col width="13.5703125" customWidth="1" style="219" min="14" max="15"/>
-    <col width="12.5703125" customWidth="1" style="219" min="16" max="35"/>
+    <col width="12" customWidth="1" style="197" min="2" max="2"/>
+    <col width="17" bestFit="1" customWidth="1" style="197" min="3" max="3"/>
+    <col width="11.85546875" customWidth="1" style="197" min="4" max="4"/>
+    <col width="9.140625" customWidth="1" style="197" min="6" max="8"/>
+    <col width="11" bestFit="1" customWidth="1" style="197" min="9" max="9"/>
+    <col width="9.140625" customWidth="1" style="197" min="10" max="10"/>
+    <col width="14" bestFit="1" customWidth="1" style="197" min="11" max="11"/>
+    <col width="15.5703125" bestFit="1" customWidth="1" style="197" min="12" max="12"/>
+    <col width="13.5703125" bestFit="1" customWidth="1" style="197" min="13" max="13"/>
+    <col width="13.5703125" customWidth="1" style="197" min="14" max="15"/>
+    <col width="12.5703125" customWidth="1" style="197" min="16" max="35"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="P1" s="194" t="inlineStr">
+      <c r="P1" s="209" t="inlineStr">
         <is>
           <t>Reston National</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="13.5" customHeight="1" s="219" thickBot="1">
-      <c r="P2" s="194" t="inlineStr">
+    <row r="2" ht="13.5" customHeight="1" s="197" thickBot="1">
+      <c r="P2" s="209" t="inlineStr">
         <is>
           <t>Round 1</t>
         </is>
       </c>
-      <c r="Q2" s="194" t="inlineStr">
+      <c r="Q2" s="209" t="inlineStr">
         <is>
           <t>Round 2</t>
         </is>
       </c>
-      <c r="R2" s="194" t="inlineStr">
+      <c r="R2" s="209" t="inlineStr">
         <is>
           <t>Round 3</t>
         </is>
       </c>
-      <c r="S2" s="194" t="inlineStr">
+      <c r="S2" s="209" t="inlineStr">
         <is>
           <t>Round 4</t>
         </is>
       </c>
-      <c r="T2" s="194" t="inlineStr">
+      <c r="T2" s="209" t="inlineStr">
         <is>
           <t>Round 5</t>
         </is>
       </c>
-      <c r="U2" s="194" t="inlineStr">
+      <c r="U2" s="209" t="inlineStr">
         <is>
           <t>Round 6</t>
         </is>
       </c>
-      <c r="V2" s="194" t="inlineStr">
+      <c r="V2" s="209" t="inlineStr">
         <is>
           <t>Round 7</t>
         </is>
       </c>
-      <c r="W2" s="194" t="inlineStr">
+      <c r="W2" s="209" t="inlineStr">
         <is>
           <t>Round 8</t>
         </is>
       </c>
-      <c r="X2" s="194" t="inlineStr">
+      <c r="X2" s="209" t="inlineStr">
         <is>
           <t>Round 9</t>
         </is>
       </c>
-      <c r="Y2" s="194" t="inlineStr">
+      <c r="Y2" s="209" t="inlineStr">
         <is>
           <t>Round 10</t>
         </is>
       </c>
-      <c r="Z2" s="194" t="inlineStr">
+      <c r="Z2" s="209" t="inlineStr">
         <is>
           <t>Round 11</t>
         </is>
       </c>
-      <c r="AA2" s="194" t="inlineStr">
+      <c r="AA2" s="209" t="inlineStr">
         <is>
           <t>Round 12</t>
         </is>
       </c>
-      <c r="AB2" s="194" t="inlineStr">
+      <c r="AB2" s="209" t="inlineStr">
         <is>
           <t>Round 13</t>
         </is>
       </c>
-      <c r="AC2" s="194" t="inlineStr">
+      <c r="AC2" s="209" t="inlineStr">
         <is>
           <t>Round 14</t>
         </is>
       </c>
-      <c r="AD2" s="194" t="inlineStr">
+      <c r="AD2" s="209" t="inlineStr">
         <is>
           <t>Round 15</t>
         </is>
       </c>
-      <c r="AE2" s="194" t="inlineStr">
+      <c r="AE2" s="209" t="inlineStr">
         <is>
           <t>Round 16</t>
         </is>
       </c>
-      <c r="AF2" s="194" t="inlineStr">
+      <c r="AF2" s="209" t="inlineStr">
         <is>
           <t>Round 17</t>
         </is>
       </c>
-      <c r="AG2" s="194" t="inlineStr">
+      <c r="AG2" s="209" t="inlineStr">
         <is>
           <t>Round 18</t>
         </is>
       </c>
-      <c r="AH2" s="194" t="inlineStr">
+      <c r="AH2" s="209" t="inlineStr">
         <is>
           <t>Round 19</t>
         </is>
       </c>
-      <c r="AI2" s="194" t="inlineStr">
+      <c r="AI2" s="209" t="inlineStr">
         <is>
           <t>Round 20</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="13.5" customHeight="1" s="219" thickBot="1">
+    <row r="3" ht="13.5" customHeight="1" s="197" thickBot="1">
       <c r="B3" s="2" t="inlineStr">
         <is>
           <t>Mens</t>
@@ -8302,33 +8302,33 @@
           <t>Name</t>
         </is>
       </c>
-      <c r="G3" s="195" t="inlineStr">
+      <c r="G3" s="210" t="inlineStr">
         <is>
           <t>Tees</t>
         </is>
       </c>
-      <c r="H3" s="220" t="n"/>
-      <c r="I3" s="195" t="inlineStr">
+      <c r="H3" s="211" t="n"/>
+      <c r="I3" s="210" t="inlineStr">
         <is>
           <t>USGA Initial</t>
         </is>
       </c>
-      <c r="J3" s="195" t="inlineStr">
+      <c r="J3" s="210" t="inlineStr">
         <is>
           <t>Initial</t>
         </is>
       </c>
-      <c r="K3" s="195" t="inlineStr">
+      <c r="K3" s="210" t="inlineStr">
         <is>
           <t>Initial Handicap</t>
         </is>
       </c>
-      <c r="L3" s="195" t="inlineStr">
+      <c r="L3" s="210" t="inlineStr">
         <is>
           <t>Course Handicap</t>
         </is>
       </c>
-      <c r="M3" s="195" t="inlineStr">
+      <c r="M3" s="210" t="inlineStr">
         <is>
           <t>Live Handicap</t>
         </is>
@@ -8456,42 +8456,42 @@
       <c r="D4" s="43" t="n">
         <v>130</v>
       </c>
-      <c r="F4" s="192" t="inlineStr">
+      <c r="F4" s="205" t="inlineStr">
         <is>
           <t>Ethan</t>
         </is>
       </c>
-      <c r="G4" s="189">
+      <c r="G4" s="198">
         <f>VLOOKUP($F4,Schedule!$C$15:$E$29,3)</f>
         <v/>
       </c>
-      <c r="H4" s="189">
+      <c r="H4" s="198">
         <f>VLOOKUP($F4,Schedule!$C$15:$E$29,4)</f>
         <v/>
       </c>
-      <c r="I4" s="193" t="n">
+      <c r="I4" s="208" t="n">
         <v>13</v>
       </c>
-      <c r="J4" s="189">
+      <c r="J4" s="198">
         <f>I4+36</f>
         <v/>
       </c>
-      <c r="K4" s="190" t="n">
+      <c r="K4" s="201" t="n">
         <v>13</v>
       </c>
-      <c r="L4" s="190">
+      <c r="L4" s="201">
         <f t="array" ref="L4">_xlfn.IFS($G4="Mens",ROUNDUP($K4*(VLOOKUP($H4,$B$4:$D$7,3)/113),0),$G4="Womens",ROUNDUP($K4*(VLOOKUP($H4,$B$10:$D$12,3)/113),0))</f>
         <v/>
       </c>
-      <c r="M4" s="190">
+      <c r="M4" s="201">
         <f t="array" ref="M4">ROUNDUP(_xlfn.IFS(O4&lt;=$B$20,MIN(P6:AI6),AND(O4&gt;=$B$21,O4&lt;=$B$23),AVERAGE(SMALL(P6:AI6,{1,2})),AND(O4&gt;=$B$24,O4&lt;=$B$26),AVERAGE(SMALL(P6:AI6,{1,2,3})),AND(O4&gt;=$B$27,O4&lt;=$B$29),AVERAGE(SMALL(P6:AI6,{1,2,3,4})),AND(O4&gt;=$B$30,O4&lt;=$B$31),AVERAGE(SMALL(P6:AI6,{1,2,3,4,5})),AND(O4&gt;=$B$32,O4&lt;=$B$33),AVERAGE(SMALL(P6:AI6,{1,2,3,4,5,6})),AND(O4=$B$34),AVERAGE(SMALL(P6:AI6,{1,2,3,4,5,6,7})),AND(O4=$B$35),AVERAGE(SMALL(P6:AI6,{1,2,3,4,5,6,7,8})))+VLOOKUP(O4,$B$16:$D$35,3),0)</f>
         <v/>
       </c>
-      <c r="N4" s="190">
+      <c r="N4" s="201">
         <f t="array" ref="N4">ROUNDUP(_xlfn.IFS($G4="Mens",ROUNDUP(M4*(VLOOKUP($H4,$B$4:$D$7,3)/113),1),$G4="Womens",ROUNDUP(M4*(VLOOKUP($H4,$B$10:$D$12,3)/113),1)),0)</f>
         <v/>
       </c>
-      <c r="O4" s="191">
+      <c r="O4" s="202">
         <f>COUNT(P4:AI4)</f>
         <v/>
       </c>
@@ -8544,16 +8544,16 @@
       <c r="D5" s="43" t="n">
         <v>126</v>
       </c>
-      <c r="F5" s="221" t="n"/>
-      <c r="G5" s="222" t="n"/>
-      <c r="H5" s="222" t="n"/>
-      <c r="I5" s="222" t="n"/>
-      <c r="J5" s="222" t="n"/>
-      <c r="K5" s="222" t="n"/>
-      <c r="L5" s="222" t="n"/>
-      <c r="M5" s="222" t="n"/>
-      <c r="N5" s="222" t="n"/>
-      <c r="O5" s="223" t="n"/>
+      <c r="F5" s="206" t="n"/>
+      <c r="G5" s="199" t="n"/>
+      <c r="H5" s="199" t="n"/>
+      <c r="I5" s="199" t="n"/>
+      <c r="J5" s="199" t="n"/>
+      <c r="K5" s="199" t="n"/>
+      <c r="L5" s="199" t="n"/>
+      <c r="M5" s="199" t="n"/>
+      <c r="N5" s="199" t="n"/>
+      <c r="O5" s="203" t="n"/>
       <c r="P5" s="96" t="inlineStr">
         <is>
           <t>USGA Diff.</t>
@@ -8655,7 +8655,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="13.5" customHeight="1" s="219" thickBot="1">
+    <row r="6" ht="13.5" customHeight="1" s="197" thickBot="1">
       <c r="B6" s="42" t="inlineStr">
         <is>
           <t>Blue/White</t>
@@ -8667,16 +8667,16 @@
       <c r="D6" s="43" t="n">
         <v>120</v>
       </c>
-      <c r="F6" s="224" t="n"/>
-      <c r="G6" s="225" t="n"/>
-      <c r="H6" s="225" t="n"/>
-      <c r="I6" s="225" t="n"/>
-      <c r="J6" s="225" t="n"/>
-      <c r="K6" s="225" t="n"/>
-      <c r="L6" s="225" t="n"/>
-      <c r="M6" s="225" t="n"/>
-      <c r="N6" s="225" t="n"/>
-      <c r="O6" s="226" t="n"/>
+      <c r="F6" s="207" t="n"/>
+      <c r="G6" s="200" t="n"/>
+      <c r="H6" s="200" t="n"/>
+      <c r="I6" s="200" t="n"/>
+      <c r="J6" s="200" t="n"/>
+      <c r="K6" s="200" t="n"/>
+      <c r="L6" s="200" t="n"/>
+      <c r="M6" s="200" t="n"/>
+      <c r="N6" s="200" t="n"/>
+      <c r="O6" s="204" t="n"/>
       <c r="P6" s="97">
         <f t="array" ref="P6">IF(P4="","",_xlfn.IFS($G4="Mens",(P4-(VLOOKUP($H4,$B$4:$D$7,2)/2))/VLOOKUP($H4,$B$4:$D$7,3)*113,$G4="Womens",(P4-(VLOOKUP($H4,$B$10:$D$12,2)/2))/VLOOKUP($H4,$B$10:$D$12,3)*113))</f>
         <v/>
@@ -8773,9 +8773,9 @@
       <c r="L7" s="98" t="n"/>
     </row>
     <row r="8">
-      <c r="B8" s="206" t="n"/>
-      <c r="C8" s="206" t="n"/>
-      <c r="D8" s="206" t="n"/>
+      <c r="B8" s="228" t="n"/>
+      <c r="C8" s="228" t="n"/>
+      <c r="D8" s="228" t="n"/>
     </row>
     <row r="9">
       <c r="B9" s="2" t="inlineStr">
@@ -8833,8 +8833,8 @@
         <v>120</v>
       </c>
     </row>
-    <row r="14" ht="13.5" customHeight="1" s="219" thickBot="1"/>
-    <row r="15" ht="25.5" customHeight="1" s="219">
+    <row r="14" ht="13.5" customHeight="1" s="197" thickBot="1"/>
+    <row r="15" ht="25.5" customHeight="1" s="197">
       <c r="B15" s="82" t="inlineStr">
         <is>
           <t># of Score Differentials</t>
@@ -8903,7 +8903,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="20" ht="13.5" customHeight="1" s="219" thickBot="1">
+    <row r="20" ht="13.5" customHeight="1" s="197" thickBot="1">
       <c r="B20" s="39" t="n">
         <v>5</v>
       </c>
@@ -8942,7 +8942,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" ht="13.5" customHeight="1" s="219" thickBot="1">
+    <row r="23" ht="13.5" customHeight="1" s="197" thickBot="1">
       <c r="B23" s="39" t="n">
         <v>8</v>
       </c>
@@ -8982,7 +8982,7 @@
       </c>
       <c r="K25" s="101" t="n"/>
     </row>
-    <row r="26" ht="13.5" customHeight="1" s="219" thickBot="1">
+    <row r="26" ht="13.5" customHeight="1" s="197" thickBot="1">
       <c r="B26" s="39" t="n">
         <v>11</v>
       </c>
@@ -9021,7 +9021,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" ht="13.5" customHeight="1" s="219" thickBot="1">
+    <row r="29" ht="13.5" customHeight="1" s="197" thickBot="1">
       <c r="B29" s="39" t="n">
         <v>14</v>
       </c>
@@ -9047,7 +9047,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" ht="13.5" customHeight="1" s="219" thickBot="1">
+    <row r="31" ht="13.5" customHeight="1" s="197" thickBot="1">
       <c r="B31" s="39" t="n">
         <v>16</v>
       </c>
@@ -9073,7 +9073,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" ht="13.5" customHeight="1" s="219" thickBot="1">
+    <row r="33" ht="13.5" customHeight="1" s="197" thickBot="1">
       <c r="B33" s="39" t="n">
         <v>18</v>
       </c>
@@ -9086,8 +9086,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" ht="13.5" customHeight="1" s="219" thickBot="1">
-      <c r="B34" s="192" t="n">
+    <row r="34" ht="13.5" customHeight="1" s="197" thickBot="1">
+      <c r="B34" s="205" t="n">
         <v>19</v>
       </c>
       <c r="C34" s="92" t="inlineStr">
@@ -9095,15 +9095,15 @@
           <t>Average of lowest 7</t>
         </is>
       </c>
-      <c r="D34" s="191" t="n">
+      <c r="D34" s="202" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="35" ht="13.5" customHeight="1" s="219" thickBot="1">
+    <row r="35" ht="13.5" customHeight="1" s="197" thickBot="1">
       <c r="B35" s="89" t="n">
         <v>20</v>
       </c>
-      <c r="C35" s="225" t="inlineStr">
+      <c r="C35" s="200" t="inlineStr">
         <is>
           <t>Average of lowest 8</t>
         </is>
@@ -9235,27 +9235,27 @@
   <dimension ref="A1:S32"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.140625" defaultRowHeight="12.75"/>
   <cols>
-    <col width="3.140625" customWidth="1" style="206" min="1" max="1"/>
-    <col width="18" bestFit="1" customWidth="1" style="206" min="2" max="2"/>
-    <col width="12.140625" bestFit="1" customWidth="1" style="206" min="3" max="3"/>
-    <col width="9.140625" customWidth="1" style="206" min="4" max="12"/>
-    <col width="11.5703125" customWidth="1" style="206" min="13" max="15"/>
-    <col width="9.140625" customWidth="1" style="206" min="16" max="17"/>
-    <col width="14.85546875" customWidth="1" style="206" min="18" max="19"/>
-    <col width="9.140625" customWidth="1" style="206" min="20" max="35"/>
-    <col width="9.140625" customWidth="1" style="206" min="36" max="16384"/>
+    <col width="3.140625" customWidth="1" style="228" min="1" max="1"/>
+    <col width="18" bestFit="1" customWidth="1" style="228" min="2" max="2"/>
+    <col width="12.140625" bestFit="1" customWidth="1" style="228" min="3" max="3"/>
+    <col width="9.140625" customWidth="1" style="228" min="4" max="12"/>
+    <col width="11.5703125" customWidth="1" style="228" min="13" max="15"/>
+    <col width="9.140625" customWidth="1" style="228" min="16" max="17"/>
+    <col width="14.85546875" customWidth="1" style="228" min="18" max="19"/>
+    <col width="9.140625" customWidth="1" style="228" min="20" max="36"/>
+    <col width="9.140625" customWidth="1" style="228" min="37" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1" ht="13.5" customHeight="1" s="219" thickBot="1">
-      <c r="N1" s="207" t="inlineStr">
+    <row r="1" ht="13.5" customHeight="1" s="197" thickBot="1">
+      <c r="N1" s="229" t="inlineStr">
         <is>
           <t>Tiebreakers</t>
         </is>
       </c>
-      <c r="O1" s="227" t="n"/>
+      <c r="O1" s="191" t="n"/>
       <c r="P1" s="21" t="n"/>
     </row>
-    <row r="2" ht="41.45" customHeight="1" s="219" thickBot="1">
+    <row r="2" ht="41.45" customHeight="1" s="197" thickBot="1">
       <c r="B2" s="20" t="inlineStr">
         <is>
           <t>Name</t>
@@ -9323,11 +9323,11 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="12.95" customHeight="1" s="219" thickBot="1">
-      <c r="A3" s="206" t="n">
+    <row r="3" ht="12.95" customHeight="1" s="197" thickBot="1">
+      <c r="A3" s="228" t="n">
         <v>1</v>
       </c>
-      <c r="B3" s="198">
+      <c r="B3" s="216">
         <f>Schedule!C15</f>
         <v/>
       </c>
@@ -9339,39 +9339,41 @@
       <c r="D3" s="158" t="n">
         <v>2</v>
       </c>
-      <c r="E3" s="200" t="n">
+      <c r="E3" s="220" t="n">
         <v>4</v>
       </c>
-      <c r="F3" s="200" t="n">
+      <c r="F3" s="220" t="n">
         <v>8</v>
       </c>
-      <c r="G3" s="200" t="n"/>
-      <c r="H3" s="200" t="n"/>
-      <c r="I3" s="200" t="n"/>
-      <c r="J3" s="200" t="n"/>
-      <c r="K3" s="200" t="n"/>
+      <c r="G3" s="220" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H3" s="220" t="n"/>
+      <c r="I3" s="220" t="n"/>
+      <c r="J3" s="220" t="n"/>
+      <c r="K3" s="220" t="n"/>
       <c r="L3" s="160" t="n"/>
-      <c r="M3" s="202" t="n">
-        <v>14</v>
-      </c>
-      <c r="N3" s="200" t="inlineStr">
-        <is>
-          <t>1-1-1</t>
-        </is>
-      </c>
-      <c r="O3" s="208" t="n">
+      <c r="M3" s="222" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="N3" s="220" t="inlineStr">
+        <is>
+          <t>1-2-1</t>
+        </is>
+      </c>
+      <c r="O3" s="230" t="n">
         <v>39</v>
       </c>
-      <c r="Q3" s="209" t="inlineStr">
+      <c r="Q3" s="231" t="inlineStr">
         <is>
           <t>Playoffs</t>
         </is>
       </c>
-      <c r="R3" s="228" t="n"/>
-      <c r="S3" s="229" t="n"/>
-    </row>
-    <row r="4" ht="13.5" customHeight="1" s="219" thickBot="1">
-      <c r="B4" s="230" t="n"/>
+      <c r="R3" s="232" t="n"/>
+      <c r="S3" s="179" t="n"/>
+    </row>
+    <row r="4" ht="13.5" customHeight="1" s="197" thickBot="1">
+      <c r="B4" s="217" t="n"/>
       <c r="C4" s="161" t="inlineStr">
         <is>
           <t>NET Score</t>
@@ -9386,16 +9388,18 @@
       <c r="F4" s="163" t="n">
         <v>34</v>
       </c>
-      <c r="G4" s="163" t="n"/>
+      <c r="G4" s="163" t="n">
+        <v>39</v>
+      </c>
       <c r="H4" s="163" t="n"/>
       <c r="I4" s="163" t="n"/>
       <c r="J4" s="163" t="n"/>
       <c r="K4" s="163" t="n"/>
       <c r="L4" s="164" t="n"/>
-      <c r="M4" s="231" t="n"/>
-      <c r="N4" s="232" t="n"/>
-      <c r="O4" s="233" t="n"/>
-      <c r="Q4" s="203" t="inlineStr">
+      <c r="M4" s="223" t="n"/>
+      <c r="N4" s="219" t="n"/>
+      <c r="O4" s="213" t="n"/>
+      <c r="Q4" s="224" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
@@ -9411,11 +9415,11 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="12.95" customHeight="1" s="219">
-      <c r="A5" s="206" t="n">
+    <row r="5" ht="12.95" customHeight="1" s="197">
+      <c r="A5" s="228" t="n">
         <v>2</v>
       </c>
-      <c r="B5" s="201">
+      <c r="B5" s="221">
         <f>Schedule!C16</f>
         <v/>
       </c>
@@ -9441,15 +9445,15 @@
       <c r="J5" s="166" t="n"/>
       <c r="K5" s="166" t="n"/>
       <c r="L5" s="167" t="n"/>
-      <c r="M5" s="204" t="n">
+      <c r="M5" s="226" t="n">
         <v>27</v>
       </c>
-      <c r="N5" s="199" t="inlineStr">
+      <c r="N5" s="218" t="inlineStr">
         <is>
           <t>4-0-0</t>
         </is>
       </c>
-      <c r="O5" s="196" t="n">
+      <c r="O5" s="212" t="n">
         <v>38</v>
       </c>
       <c r="Q5" s="33" t="n">
@@ -9458,8 +9462,8 @@
       <c r="R5" s="34" t="n"/>
       <c r="S5" s="35" t="n"/>
     </row>
-    <row r="6" ht="13.5" customHeight="1" s="219" thickBot="1">
-      <c r="B6" s="234" t="n"/>
+    <row r="6" ht="13.5" customHeight="1" s="197" thickBot="1">
+      <c r="B6" s="215" t="n"/>
       <c r="C6" s="168" t="inlineStr">
         <is>
           <t>NET Score</t>
@@ -9482,20 +9486,20 @@
       <c r="J6" s="170" t="n"/>
       <c r="K6" s="170" t="n"/>
       <c r="L6" s="171" t="n"/>
-      <c r="M6" s="231" t="n"/>
-      <c r="N6" s="232" t="n"/>
-      <c r="O6" s="233" t="n"/>
+      <c r="M6" s="223" t="n"/>
+      <c r="N6" s="219" t="n"/>
+      <c r="O6" s="213" t="n"/>
       <c r="Q6" s="36" t="n">
         <v>2</v>
       </c>
       <c r="R6" s="37" t="n"/>
       <c r="S6" s="38" t="n"/>
     </row>
-    <row r="7" ht="12.95" customHeight="1" s="219">
-      <c r="A7" s="206" t="n">
+    <row r="7" ht="12.95" customHeight="1" s="197">
+      <c r="A7" s="228" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="197">
+      <c r="B7" s="214">
         <f>Schedule!C17</f>
         <v/>
       </c>
@@ -9507,25 +9511,25 @@
       <c r="D7" s="158" t="n">
         <v>1</v>
       </c>
-      <c r="E7" s="200" t="n">
+      <c r="E7" s="220" t="n">
         <v>4</v>
       </c>
-      <c r="F7" s="200" t="n"/>
-      <c r="G7" s="200" t="n"/>
-      <c r="H7" s="200" t="n"/>
-      <c r="I7" s="200" t="n"/>
-      <c r="J7" s="200" t="n"/>
-      <c r="K7" s="200" t="n"/>
+      <c r="F7" s="220" t="n"/>
+      <c r="G7" s="220" t="n"/>
+      <c r="H7" s="220" t="n"/>
+      <c r="I7" s="220" t="n"/>
+      <c r="J7" s="220" t="n"/>
+      <c r="K7" s="220" t="n"/>
       <c r="L7" s="160" t="n"/>
-      <c r="M7" s="202" t="n">
+      <c r="M7" s="222" t="n">
         <v>5</v>
       </c>
-      <c r="N7" s="200" t="inlineStr">
+      <c r="N7" s="220" t="inlineStr">
         <is>
           <t>0-1-1</t>
         </is>
       </c>
-      <c r="O7" s="208" t="n">
+      <c r="O7" s="230" t="n">
         <v>41</v>
       </c>
       <c r="Q7" s="33" t="n">
@@ -9534,8 +9538,8 @@
       <c r="R7" s="34" t="n"/>
       <c r="S7" s="35" t="n"/>
     </row>
-    <row r="8" ht="13.5" customHeight="1" s="219" thickBot="1">
-      <c r="B8" s="234" t="n"/>
+    <row r="8" ht="13.5" customHeight="1" s="197" thickBot="1">
+      <c r="B8" s="215" t="n"/>
       <c r="C8" s="161" t="inlineStr">
         <is>
           <t>NET Score</t>
@@ -9554,20 +9558,20 @@
       <c r="J8" s="163" t="n"/>
       <c r="K8" s="163" t="n"/>
       <c r="L8" s="164" t="n"/>
-      <c r="M8" s="231" t="n"/>
-      <c r="N8" s="232" t="n"/>
-      <c r="O8" s="233" t="n"/>
+      <c r="M8" s="223" t="n"/>
+      <c r="N8" s="219" t="n"/>
+      <c r="O8" s="213" t="n"/>
       <c r="Q8" s="39" t="n">
         <v>4</v>
       </c>
       <c r="R8" s="40" t="n"/>
       <c r="S8" s="41" t="n"/>
     </row>
-    <row r="9" ht="12.95" customHeight="1" s="219" thickBot="1">
-      <c r="A9" s="206" t="n">
+    <row r="9" ht="12.95" customHeight="1" s="197" thickBot="1">
+      <c r="A9" s="228" t="n">
         <v>4</v>
       </c>
-      <c r="B9" s="201">
+      <c r="B9" s="221">
         <f>Schedule!C18</f>
         <v/>
       </c>
@@ -9585,26 +9589,28 @@
       <c r="F9" s="166" t="n">
         <v>0</v>
       </c>
-      <c r="G9" s="166" t="n"/>
+      <c r="G9" s="166" t="n">
+        <v>5</v>
+      </c>
       <c r="H9" s="166" t="n"/>
       <c r="I9" s="166" t="n"/>
       <c r="J9" s="166" t="n"/>
       <c r="K9" s="166" t="n"/>
       <c r="L9" s="167" t="n"/>
-      <c r="M9" s="204" t="n">
-        <v>8</v>
-      </c>
-      <c r="N9" s="199" t="inlineStr">
-        <is>
-          <t>1-2-0</t>
-        </is>
-      </c>
-      <c r="O9" s="196" t="n">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="10" ht="13.5" customHeight="1" s="219" thickBot="1">
-      <c r="B10" s="234" t="n"/>
+      <c r="M9" s="226" t="n">
+        <v>13</v>
+      </c>
+      <c r="N9" s="218" t="inlineStr">
+        <is>
+          <t>2-2-0</t>
+        </is>
+      </c>
+      <c r="O9" s="212" t="n">
+        <v>41.5</v>
+      </c>
+    </row>
+    <row r="10" ht="13.5" customHeight="1" s="197" thickBot="1">
+      <c r="B10" s="215" t="n"/>
       <c r="C10" s="168" t="inlineStr">
         <is>
           <t>NET Score</t>
@@ -9619,27 +9625,29 @@
       <c r="F10" s="170" t="n">
         <v>47</v>
       </c>
-      <c r="G10" s="170" t="n"/>
+      <c r="G10" s="170" t="n">
+        <v>34</v>
+      </c>
       <c r="H10" s="170" t="n"/>
       <c r="I10" s="170" t="n"/>
       <c r="J10" s="170" t="n"/>
       <c r="K10" s="170" t="n"/>
       <c r="L10" s="171" t="n"/>
-      <c r="M10" s="231" t="n"/>
-      <c r="N10" s="232" t="n"/>
-      <c r="O10" s="233" t="n"/>
-      <c r="R10" s="203" t="inlineStr">
+      <c r="M10" s="223" t="n"/>
+      <c r="N10" s="219" t="n"/>
+      <c r="O10" s="213" t="n"/>
+      <c r="R10" s="224" t="inlineStr">
         <is>
           <t>Playoff Matchups</t>
         </is>
       </c>
-      <c r="S10" s="235" t="n"/>
-    </row>
-    <row r="11" ht="12.95" customHeight="1" s="219">
-      <c r="A11" s="206" t="n">
+      <c r="S10" s="225" t="n"/>
+    </row>
+    <row r="11" ht="12.95" customHeight="1" s="197">
+      <c r="A11" s="228" t="n">
         <v>5</v>
       </c>
-      <c r="B11" s="197">
+      <c r="B11" s="214">
         <f>Schedule!C19</f>
         <v/>
       </c>
@@ -9651,28 +9659,30 @@
       <c r="D11" s="158" t="n">
         <v>0</v>
       </c>
-      <c r="E11" s="200" t="n">
+      <c r="E11" s="220" t="n">
         <v>6</v>
       </c>
-      <c r="F11" s="200" t="n">
+      <c r="F11" s="220" t="n">
         <v>1</v>
       </c>
-      <c r="G11" s="200" t="n"/>
-      <c r="H11" s="200" t="n"/>
-      <c r="I11" s="200" t="n"/>
-      <c r="J11" s="200" t="n"/>
-      <c r="K11" s="200" t="n"/>
+      <c r="G11" s="220" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H11" s="220" t="n"/>
+      <c r="I11" s="220" t="n"/>
+      <c r="J11" s="220" t="n"/>
+      <c r="K11" s="220" t="n"/>
       <c r="L11" s="160" t="n"/>
-      <c r="M11" s="202" t="n">
-        <v>7</v>
-      </c>
-      <c r="N11" s="200" t="inlineStr">
-        <is>
-          <t>1-2-0</t>
-        </is>
-      </c>
-      <c r="O11" s="208" t="n">
-        <v>44</v>
+      <c r="M11" s="222" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="N11" s="220" t="inlineStr">
+        <is>
+          <t>2-2-0</t>
+        </is>
+      </c>
+      <c r="O11" s="230" t="n">
+        <v>43</v>
       </c>
       <c r="R11" s="36" t="inlineStr">
         <is>
@@ -9685,8 +9695,8 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="13.5" customHeight="1" s="219" thickBot="1">
-      <c r="B12" s="234" t="n"/>
+    <row r="12" ht="13.5" customHeight="1" s="197" thickBot="1">
+      <c r="B12" s="215" t="n"/>
       <c r="C12" s="161" t="inlineStr">
         <is>
           <t>NET Score</t>
@@ -9701,15 +9711,17 @@
       <c r="F12" s="163" t="n">
         <v>43</v>
       </c>
-      <c r="G12" s="163" t="n"/>
+      <c r="G12" s="163" t="n">
+        <v>40</v>
+      </c>
       <c r="H12" s="163" t="n"/>
       <c r="I12" s="163" t="n"/>
       <c r="J12" s="163" t="n"/>
       <c r="K12" s="163" t="n"/>
       <c r="L12" s="164" t="n"/>
-      <c r="M12" s="231" t="n"/>
-      <c r="N12" s="232" t="n"/>
-      <c r="O12" s="233" t="n"/>
+      <c r="M12" s="223" t="n"/>
+      <c r="N12" s="219" t="n"/>
+      <c r="O12" s="213" t="n"/>
       <c r="R12" s="36" t="inlineStr">
         <is>
           <t>1 vs 4</t>
@@ -9721,11 +9733,11 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="12.95" customHeight="1" s="219" thickBot="1">
-      <c r="A13" s="206" t="n">
+    <row r="13" ht="12.95" customHeight="1" s="197" thickBot="1">
+      <c r="A13" s="228" t="n">
         <v>6</v>
       </c>
-      <c r="B13" s="201">
+      <c r="B13" s="221">
         <f>Schedule!C20</f>
         <v/>
       </c>
@@ -9747,15 +9759,15 @@
       <c r="J13" s="166" t="n"/>
       <c r="K13" s="166" t="n"/>
       <c r="L13" s="167" t="n"/>
-      <c r="M13" s="204" t="n">
+      <c r="M13" s="226" t="n">
         <v>10</v>
       </c>
-      <c r="N13" s="199" t="inlineStr">
+      <c r="N13" s="218" t="inlineStr">
         <is>
           <t>1-1-0</t>
         </is>
       </c>
-      <c r="O13" s="196" t="n">
+      <c r="O13" s="212" t="n">
         <v>36</v>
       </c>
       <c r="R13" s="39" t="inlineStr">
@@ -9769,8 +9781,8 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="13.5" customHeight="1" s="219" thickBot="1">
-      <c r="B14" s="234" t="n"/>
+    <row r="14" ht="13.5" customHeight="1" s="197" thickBot="1">
+      <c r="B14" s="215" t="n"/>
       <c r="C14" s="168" t="inlineStr">
         <is>
           <t>NET Score</t>
@@ -9789,15 +9801,15 @@
       <c r="J14" s="170" t="n"/>
       <c r="K14" s="170" t="n"/>
       <c r="L14" s="171" t="n"/>
-      <c r="M14" s="231" t="n"/>
-      <c r="N14" s="232" t="n"/>
-      <c r="O14" s="233" t="n"/>
-    </row>
-    <row r="15" ht="12.95" customHeight="1" s="219">
-      <c r="A15" s="206" t="n">
+      <c r="M14" s="223" t="n"/>
+      <c r="N14" s="219" t="n"/>
+      <c r="O14" s="213" t="n"/>
+    </row>
+    <row r="15" ht="12.95" customHeight="1" s="197">
+      <c r="A15" s="228" t="n">
         <v>7</v>
       </c>
-      <c r="B15" s="197">
+      <c r="B15" s="214">
         <f>Schedule!C21</f>
         <v/>
       </c>
@@ -9809,34 +9821,34 @@
       <c r="D15" s="158" t="n">
         <v>1</v>
       </c>
-      <c r="E15" s="200" t="n">
+      <c r="E15" s="220" t="n">
         <v>2</v>
       </c>
-      <c r="F15" s="200" t="n">
+      <c r="F15" s="220" t="n">
         <v>7</v>
       </c>
-      <c r="G15" s="200" t="n">
+      <c r="G15" s="220" t="n">
         <v>1</v>
       </c>
-      <c r="H15" s="200" t="n"/>
-      <c r="I15" s="200" t="n"/>
-      <c r="J15" s="200" t="n"/>
-      <c r="K15" s="200" t="n"/>
+      <c r="H15" s="220" t="n"/>
+      <c r="I15" s="220" t="n"/>
+      <c r="J15" s="220" t="n"/>
+      <c r="K15" s="220" t="n"/>
       <c r="L15" s="160" t="n"/>
-      <c r="M15" s="202" t="n">
+      <c r="M15" s="222" t="n">
         <v>11</v>
       </c>
-      <c r="N15" s="200" t="inlineStr">
+      <c r="N15" s="220" t="inlineStr">
         <is>
           <t>1-3-0</t>
         </is>
       </c>
-      <c r="O15" s="208" t="n">
+      <c r="O15" s="230" t="n">
         <v>46.2</v>
       </c>
     </row>
-    <row r="16" ht="13.5" customHeight="1" s="219" thickBot="1">
-      <c r="B16" s="234" t="n"/>
+    <row r="16" ht="13.5" customHeight="1" s="197" thickBot="1">
+      <c r="B16" s="215" t="n"/>
       <c r="C16" s="161" t="inlineStr">
         <is>
           <t>NET Score</t>
@@ -9859,15 +9871,15 @@
       <c r="J16" s="163" t="n"/>
       <c r="K16" s="163" t="n"/>
       <c r="L16" s="164" t="n"/>
-      <c r="M16" s="231" t="n"/>
-      <c r="N16" s="232" t="n"/>
-      <c r="O16" s="233" t="n"/>
-    </row>
-    <row r="17" ht="12.95" customHeight="1" s="219">
-      <c r="A17" s="206" t="n">
+      <c r="M16" s="223" t="n"/>
+      <c r="N16" s="219" t="n"/>
+      <c r="O16" s="213" t="n"/>
+    </row>
+    <row r="17" ht="12.95" customHeight="1" s="197">
+      <c r="A17" s="228" t="n">
         <v>8</v>
       </c>
-      <c r="B17" s="201">
+      <c r="B17" s="221">
         <f>Schedule!C22</f>
         <v/>
       </c>
@@ -9891,25 +9903,25 @@
       <c r="J17" s="166" t="n"/>
       <c r="K17" s="166" t="n"/>
       <c r="L17" s="167" t="n"/>
-      <c r="M17" s="204" t="n">
+      <c r="M17" s="226" t="n">
         <v>21</v>
       </c>
-      <c r="N17" s="199" t="inlineStr">
+      <c r="N17" s="218" t="inlineStr">
         <is>
           <t>3-0-0</t>
         </is>
       </c>
-      <c r="O17" s="196" t="n">
+      <c r="O17" s="212" t="n">
         <v>37.3</v>
       </c>
-      <c r="Q17" s="205" t="inlineStr">
+      <c r="Q17" s="227" t="inlineStr">
         <is>
           <t>Tiebreaker Rules</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="13.5" customHeight="1" s="219" thickBot="1">
-      <c r="B18" s="234" t="n"/>
+    <row r="18" ht="13.5" customHeight="1" s="197" thickBot="1">
+      <c r="B18" s="215" t="n"/>
       <c r="C18" s="168" t="inlineStr">
         <is>
           <t>NET Score</t>
@@ -9930,9 +9942,9 @@
       <c r="J18" s="170" t="n"/>
       <c r="K18" s="170" t="n"/>
       <c r="L18" s="171" t="n"/>
-      <c r="M18" s="231" t="n"/>
-      <c r="N18" s="232" t="n"/>
-      <c r="O18" s="233" t="n"/>
+      <c r="M18" s="223" t="n"/>
+      <c r="N18" s="219" t="n"/>
+      <c r="O18" s="213" t="n"/>
       <c r="Q18" s="154" t="inlineStr">
         <is>
           <t>1. Highest overall match wins. A match win means you scored 4.5 points or more against your opponent. 4 points will be considered a draw.</t>
@@ -9940,11 +9952,11 @@
       </c>
       <c r="R18" s="21" t="n"/>
     </row>
-    <row r="19" ht="12.95" customHeight="1" s="219">
-      <c r="A19" s="206" t="n">
+    <row r="19" ht="12.95" customHeight="1" s="197">
+      <c r="A19" s="228" t="n">
         <v>9</v>
       </c>
-      <c r="B19" s="197">
+      <c r="B19" s="214">
         <f>Schedule!C23</f>
         <v/>
       </c>
@@ -9956,29 +9968,29 @@
       <c r="D19" s="158" t="n">
         <v>2</v>
       </c>
-      <c r="E19" s="200" t="n">
+      <c r="E19" s="220" t="n">
         <v>8</v>
       </c>
-      <c r="F19" s="200" t="n">
+      <c r="F19" s="220" t="n">
         <v>4.5</v>
       </c>
-      <c r="G19" s="200" t="n">
+      <c r="G19" s="220" t="n">
         <v>8</v>
       </c>
-      <c r="H19" s="200" t="n"/>
-      <c r="I19" s="200" t="n"/>
-      <c r="J19" s="200" t="n"/>
-      <c r="K19" s="200" t="n"/>
+      <c r="H19" s="220" t="n"/>
+      <c r="I19" s="220" t="n"/>
+      <c r="J19" s="220" t="n"/>
+      <c r="K19" s="220" t="n"/>
       <c r="L19" s="160" t="n"/>
-      <c r="M19" s="202" t="n">
+      <c r="M19" s="222" t="n">
         <v>22.5</v>
       </c>
-      <c r="N19" s="200" t="inlineStr">
+      <c r="N19" s="220" t="inlineStr">
         <is>
           <t>3-1-0</t>
         </is>
       </c>
-      <c r="O19" s="208" t="n">
+      <c r="O19" s="230" t="n">
         <v>38.8</v>
       </c>
       <c r="Q19" s="154" t="inlineStr">
@@ -9987,8 +9999,8 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="13.5" customHeight="1" s="219" thickBot="1">
-      <c r="B20" s="234" t="n"/>
+    <row r="20" ht="13.5" customHeight="1" s="197" thickBot="1">
+      <c r="B20" s="215" t="n"/>
       <c r="C20" s="161" t="inlineStr">
         <is>
           <t>NET Score</t>
@@ -10011,9 +10023,9 @@
       <c r="J20" s="163" t="n"/>
       <c r="K20" s="163" t="n"/>
       <c r="L20" s="164" t="n"/>
-      <c r="M20" s="231" t="n"/>
-      <c r="N20" s="232" t="n"/>
-      <c r="O20" s="233" t="n"/>
+      <c r="M20" s="223" t="n"/>
+      <c r="N20" s="219" t="n"/>
+      <c r="O20" s="213" t="n"/>
       <c r="Q20" s="154" t="inlineStr">
         <is>
           <t>3. Lowest Round 8 NET score.</t>
@@ -10021,11 +10033,11 @@
       </c>
       <c r="R20" s="21" t="n"/>
     </row>
-    <row r="21" ht="12.95" customHeight="1" s="219">
-      <c r="A21" s="206" t="n">
+    <row r="21" ht="12.95" customHeight="1" s="197">
+      <c r="A21" s="228" t="n">
         <v>10</v>
       </c>
-      <c r="B21" s="201">
+      <c r="B21" s="221">
         <f>Schedule!C24</f>
         <v/>
       </c>
@@ -10049,15 +10061,15 @@
       <c r="J21" s="166" t="n"/>
       <c r="K21" s="166" t="n"/>
       <c r="L21" s="167" t="n"/>
-      <c r="M21" s="204" t="n">
+      <c r="M21" s="226" t="n">
         <v>22</v>
       </c>
-      <c r="N21" s="199" t="inlineStr">
+      <c r="N21" s="218" t="inlineStr">
         <is>
           <t>3-0-0</t>
         </is>
       </c>
-      <c r="O21" s="196" t="n">
+      <c r="O21" s="212" t="n">
         <v>39.3</v>
       </c>
       <c r="Q21" s="154" t="inlineStr">
@@ -10067,8 +10079,8 @@
       </c>
       <c r="R21" s="21" t="n"/>
     </row>
-    <row r="22" ht="13.5" customHeight="1" s="219" thickBot="1">
-      <c r="B22" s="234" t="n"/>
+    <row r="22" ht="13.5" customHeight="1" s="197" thickBot="1">
+      <c r="B22" s="215" t="n"/>
       <c r="C22" s="168" t="inlineStr">
         <is>
           <t>NET Score</t>
@@ -10089,15 +10101,15 @@
       <c r="J22" s="170" t="n"/>
       <c r="K22" s="170" t="n"/>
       <c r="L22" s="171" t="n"/>
-      <c r="M22" s="231" t="n"/>
-      <c r="N22" s="232" t="n"/>
-      <c r="O22" s="233" t="n"/>
-    </row>
-    <row r="23" ht="12.95" customHeight="1" s="219">
-      <c r="A23" s="206" t="n">
+      <c r="M22" s="223" t="n"/>
+      <c r="N22" s="219" t="n"/>
+      <c r="O22" s="213" t="n"/>
+    </row>
+    <row r="23" ht="12.95" customHeight="1" s="197">
+      <c r="A23" s="228" t="n">
         <v>11</v>
       </c>
-      <c r="B23" s="197">
+      <c r="B23" s="214">
         <f>Schedule!C25</f>
         <v/>
       </c>
@@ -10107,34 +10119,34 @@
         </is>
       </c>
       <c r="D23" s="158" t="n"/>
-      <c r="E23" s="200" t="n">
+      <c r="E23" s="220" t="n">
         <v>8</v>
       </c>
-      <c r="F23" s="200" t="n">
+      <c r="F23" s="220" t="n">
         <v>7</v>
       </c>
-      <c r="G23" s="200" t="n">
+      <c r="G23" s="220" t="n">
         <v>4</v>
       </c>
-      <c r="H23" s="200" t="n"/>
-      <c r="I23" s="200" t="n"/>
-      <c r="J23" s="200" t="n"/>
-      <c r="K23" s="200" t="n"/>
+      <c r="H23" s="220" t="n"/>
+      <c r="I23" s="220" t="n"/>
+      <c r="J23" s="220" t="n"/>
+      <c r="K23" s="220" t="n"/>
       <c r="L23" s="160" t="n"/>
-      <c r="M23" s="202" t="n">
+      <c r="M23" s="222" t="n">
         <v>19</v>
       </c>
-      <c r="N23" s="200" t="inlineStr">
+      <c r="N23" s="220" t="inlineStr">
         <is>
           <t>2-0-1</t>
         </is>
       </c>
-      <c r="O23" s="208" t="n">
+      <c r="O23" s="230" t="n">
         <v>46</v>
       </c>
     </row>
-    <row r="24" ht="13.5" customHeight="1" s="219" thickBot="1">
-      <c r="B24" s="234" t="n"/>
+    <row r="24" ht="13.5" customHeight="1" s="197" thickBot="1">
+      <c r="B24" s="215" t="n"/>
       <c r="C24" s="161" t="inlineStr">
         <is>
           <t>NET Score</t>
@@ -10155,15 +10167,15 @@
       <c r="J24" s="163" t="n"/>
       <c r="K24" s="163" t="n"/>
       <c r="L24" s="164" t="n"/>
-      <c r="M24" s="231" t="n"/>
-      <c r="N24" s="232" t="n"/>
-      <c r="O24" s="233" t="n"/>
-    </row>
-    <row r="25" ht="12.95" customHeight="1" s="219">
-      <c r="A25" s="206" t="n">
+      <c r="M24" s="223" t="n"/>
+      <c r="N24" s="219" t="n"/>
+      <c r="O24" s="213" t="n"/>
+    </row>
+    <row r="25" ht="12.95" customHeight="1" s="197">
+      <c r="A25" s="228" t="n">
         <v>12</v>
       </c>
-      <c r="B25" s="201">
+      <c r="B25" s="221">
         <f>Schedule!C26</f>
         <v/>
       </c>
@@ -10189,20 +10201,20 @@
       <c r="J25" s="166" t="n"/>
       <c r="K25" s="166" t="n"/>
       <c r="L25" s="167" t="n"/>
-      <c r="M25" s="204" t="n">
+      <c r="M25" s="226" t="n">
         <v>11</v>
       </c>
-      <c r="N25" s="199" t="inlineStr">
+      <c r="N25" s="218" t="inlineStr">
         <is>
           <t>1-2-1</t>
         </is>
       </c>
-      <c r="O25" s="196" t="n">
+      <c r="O25" s="212" t="n">
         <v>53.5</v>
       </c>
     </row>
-    <row r="26" ht="13.5" customHeight="1" s="219" thickBot="1">
-      <c r="B26" s="234" t="n"/>
+    <row r="26" ht="13.5" customHeight="1" s="197" thickBot="1">
+      <c r="B26" s="215" t="n"/>
       <c r="C26" s="168" t="inlineStr">
         <is>
           <t>NET Score</t>
@@ -10225,15 +10237,15 @@
       <c r="J26" s="170" t="n"/>
       <c r="K26" s="170" t="n"/>
       <c r="L26" s="171" t="n"/>
-      <c r="M26" s="231" t="n"/>
-      <c r="N26" s="232" t="n"/>
-      <c r="O26" s="233" t="n"/>
-    </row>
-    <row r="27" ht="12.95" customHeight="1" s="219">
-      <c r="A27" s="206" t="n">
+      <c r="M26" s="223" t="n"/>
+      <c r="N26" s="219" t="n"/>
+      <c r="O26" s="213" t="n"/>
+    </row>
+    <row r="27" ht="12.95" customHeight="1" s="197">
+      <c r="A27" s="228" t="n">
         <v>13</v>
       </c>
-      <c r="B27" s="197">
+      <c r="B27" s="214">
         <f>Schedule!C27</f>
         <v/>
       </c>
@@ -10245,36 +10257,36 @@
       <c r="D27" s="158" t="n">
         <v>4</v>
       </c>
-      <c r="E27" s="200" t="n">
+      <c r="E27" s="220" t="n">
         <v>0</v>
       </c>
-      <c r="F27" s="200" t="n">
+      <c r="F27" s="220" t="n">
         <v>1</v>
       </c>
-      <c r="G27" s="200" t="n">
+      <c r="G27" s="220" t="n">
         <v>0</v>
       </c>
-      <c r="H27" s="200" t="n">
+      <c r="H27" s="220" t="n">
         <v>7</v>
       </c>
-      <c r="I27" s="200" t="n"/>
-      <c r="J27" s="200" t="n"/>
-      <c r="K27" s="200" t="n"/>
+      <c r="I27" s="220" t="n"/>
+      <c r="J27" s="220" t="n"/>
+      <c r="K27" s="220" t="n"/>
       <c r="L27" s="160" t="n"/>
-      <c r="M27" s="202" t="n">
+      <c r="M27" s="222" t="n">
         <v>12</v>
       </c>
-      <c r="N27" s="200" t="inlineStr">
+      <c r="N27" s="220" t="inlineStr">
         <is>
           <t>1-3-1</t>
         </is>
       </c>
-      <c r="O27" s="208" t="n">
+      <c r="O27" s="230" t="n">
         <v>51.4</v>
       </c>
     </row>
-    <row r="28" ht="13.5" customHeight="1" s="219" thickBot="1">
-      <c r="B28" s="234" t="n"/>
+    <row r="28" ht="13.5" customHeight="1" s="197" thickBot="1">
+      <c r="B28" s="215" t="n"/>
       <c r="C28" s="161" t="inlineStr">
         <is>
           <t>NET Score</t>
@@ -10299,15 +10311,15 @@
       <c r="J28" s="163" t="n"/>
       <c r="K28" s="163" t="n"/>
       <c r="L28" s="164" t="n"/>
-      <c r="M28" s="231" t="n"/>
-      <c r="N28" s="232" t="n"/>
-      <c r="O28" s="233" t="n"/>
-    </row>
-    <row r="29" ht="12.95" customHeight="1" s="219">
-      <c r="A29" s="206" t="n">
+      <c r="M28" s="223" t="n"/>
+      <c r="N28" s="219" t="n"/>
+      <c r="O28" s="213" t="n"/>
+    </row>
+    <row r="29" ht="12.95" customHeight="1" s="197">
+      <c r="A29" s="228" t="n">
         <v>14</v>
       </c>
-      <c r="B29" s="201">
+      <c r="B29" s="221">
         <f>Schedule!C28</f>
         <v/>
       </c>
@@ -10335,20 +10347,20 @@
       <c r="J29" s="166" t="n"/>
       <c r="K29" s="166" t="n"/>
       <c r="L29" s="167" t="n"/>
-      <c r="M29" s="204" t="n">
+      <c r="M29" s="226" t="n">
         <v>11.5</v>
       </c>
-      <c r="N29" s="199" t="inlineStr">
+      <c r="N29" s="218" t="inlineStr">
         <is>
           <t>1-4-0</t>
         </is>
       </c>
-      <c r="O29" s="196" t="n">
+      <c r="O29" s="212" t="n">
         <v>50.2</v>
       </c>
     </row>
-    <row r="30" ht="13.5" customHeight="1" s="219" thickBot="1">
-      <c r="B30" s="234" t="n"/>
+    <row r="30" ht="13.5" customHeight="1" s="197" thickBot="1">
+      <c r="B30" s="215" t="n"/>
       <c r="C30" s="168" t="inlineStr">
         <is>
           <t>NET Score</t>
@@ -10373,15 +10385,15 @@
       <c r="J30" s="170" t="n"/>
       <c r="K30" s="170" t="n"/>
       <c r="L30" s="171" t="n"/>
-      <c r="M30" s="231" t="n"/>
-      <c r="N30" s="232" t="n"/>
-      <c r="O30" s="233" t="n"/>
-    </row>
-    <row r="31" ht="12.95" customHeight="1" s="219">
-      <c r="A31" s="206" t="n">
+      <c r="M30" s="223" t="n"/>
+      <c r="N30" s="219" t="n"/>
+      <c r="O30" s="213" t="n"/>
+    </row>
+    <row r="31" ht="12.95" customHeight="1" s="197">
+      <c r="A31" s="228" t="n">
         <v>15</v>
       </c>
-      <c r="B31" s="197">
+      <c r="B31" s="214">
         <f>Schedule!C29</f>
         <v/>
       </c>
@@ -10393,34 +10405,34 @@
       <c r="D31" s="158" t="n">
         <v>1</v>
       </c>
-      <c r="E31" s="200" t="n"/>
-      <c r="F31" s="200" t="n">
+      <c r="E31" s="220" t="n"/>
+      <c r="F31" s="220" t="n">
         <v>0</v>
       </c>
-      <c r="G31" s="200" t="n">
+      <c r="G31" s="220" t="n">
         <v>4</v>
       </c>
-      <c r="H31" s="200" t="n">
+      <c r="H31" s="220" t="n">
         <v>2</v>
       </c>
-      <c r="I31" s="200" t="n"/>
-      <c r="J31" s="200" t="n"/>
-      <c r="K31" s="200" t="n"/>
+      <c r="I31" s="220" t="n"/>
+      <c r="J31" s="220" t="n"/>
+      <c r="K31" s="220" t="n"/>
       <c r="L31" s="160" t="n"/>
-      <c r="M31" s="202" t="n">
+      <c r="M31" s="222" t="n">
         <v>7</v>
       </c>
-      <c r="N31" s="200" t="inlineStr">
+      <c r="N31" s="220" t="inlineStr">
         <is>
           <t>0-3-1</t>
         </is>
       </c>
-      <c r="O31" s="208" t="n">
+      <c r="O31" s="230" t="n">
         <v>51</v>
       </c>
     </row>
-    <row r="32" ht="13.5" customHeight="1" s="219" thickBot="1">
-      <c r="B32" s="234" t="n"/>
+    <row r="32" ht="13.5" customHeight="1" s="197" thickBot="1">
+      <c r="B32" s="215" t="n"/>
       <c r="C32" s="161" t="inlineStr">
         <is>
           <t>NET Score</t>
@@ -10443,9 +10455,9 @@
       <c r="J32" s="163" t="n"/>
       <c r="K32" s="163" t="n"/>
       <c r="L32" s="164" t="n"/>
-      <c r="M32" s="231" t="n"/>
-      <c r="N32" s="232" t="n"/>
-      <c r="O32" s="233" t="n"/>
+      <c r="M32" s="223" t="n"/>
+      <c r="N32" s="219" t="n"/>
+      <c r="O32" s="213" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" algorithmName="SHA-512" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" saltValue="kkQ/PatKpMHBAJY782mRBw==" formatRows="1" sort="1" spinCount="100000" password="94CD" hashValue="Y3y62YBPDCQhqKgsSl1/iH5xODfF8lm4IgTCoiweq2jLnTBBsjKN4ZDmcY+ulNgK91riyyuYS5VZZqKHpfKB8g=="/>
@@ -10473,16 +10485,17 @@
     <mergeCell ref="M3:M4"/>
     <mergeCell ref="O29:O30"/>
     <mergeCell ref="O25:O26"/>
+    <mergeCell ref="M5:M6"/>
     <mergeCell ref="Q17:S17"/>
     <mergeCell ref="N29:N30"/>
     <mergeCell ref="O21:O22"/>
+    <mergeCell ref="N1:O1"/>
     <mergeCell ref="N23:N24"/>
+    <mergeCell ref="O31:O32"/>
+    <mergeCell ref="B15:B16"/>
+    <mergeCell ref="N19:N20"/>
+    <mergeCell ref="M27:M28"/>
     <mergeCell ref="B19:B20"/>
-    <mergeCell ref="N1:O1"/>
-    <mergeCell ref="N19:N20"/>
-    <mergeCell ref="B15:B16"/>
-    <mergeCell ref="O31:O32"/>
-    <mergeCell ref="M27:M28"/>
     <mergeCell ref="B9:B10"/>
     <mergeCell ref="N13:N14"/>
     <mergeCell ref="M21:M22"/>
@@ -10497,11 +10510,10 @@
     <mergeCell ref="M23:M24"/>
     <mergeCell ref="B5:B6"/>
     <mergeCell ref="O23:O24"/>
+    <mergeCell ref="Q3:S3"/>
     <mergeCell ref="N11:N12"/>
-    <mergeCell ref="Q3:S3"/>
     <mergeCell ref="O19:O20"/>
     <mergeCell ref="N27:N28"/>
-    <mergeCell ref="B31:B32"/>
     <mergeCell ref="O13:O14"/>
     <mergeCell ref="M29:M30"/>
     <mergeCell ref="M9:M10"/>
@@ -10513,7 +10525,7 @@
     <mergeCell ref="N7:N8"/>
     <mergeCell ref="B21:B22"/>
     <mergeCell ref="O15:O16"/>
-    <mergeCell ref="M5:M6"/>
+    <mergeCell ref="B31:B32"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="3" horizontalDpi="300" verticalDpi="300"/>
@@ -10529,39 +10541,39 @@
   <dimension ref="B1:AE24"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.85546875" defaultRowHeight="13.5"/>
   <cols>
-    <col width="2.5703125" customWidth="1" style="212" min="1" max="1"/>
-    <col width="27.85546875" customWidth="1" style="212" min="2" max="2"/>
-    <col width="9.85546875" customWidth="1" style="212" min="3" max="8"/>
-    <col width="10.7109375" bestFit="1" customWidth="1" style="212" min="9" max="9"/>
-    <col width="10.5703125" customWidth="1" style="212" min="10" max="11"/>
-    <col width="10.85546875" customWidth="1" style="212" min="12" max="13"/>
-    <col width="5.7109375" customWidth="1" style="212" min="14" max="14"/>
-    <col width="11" bestFit="1" customWidth="1" style="212" min="15" max="15"/>
-    <col width="4.5703125" customWidth="1" style="212" min="16" max="24"/>
-    <col width="7.5703125" customWidth="1" style="212" min="25" max="25"/>
-    <col width="9.85546875" customWidth="1" style="212" min="26" max="27"/>
-    <col width="16.42578125" bestFit="1" customWidth="1" style="212" min="28" max="28"/>
-    <col width="12.7109375" customWidth="1" style="212" min="29" max="30"/>
-    <col width="9.85546875" customWidth="1" style="212" min="31" max="46"/>
-    <col width="9.85546875" customWidth="1" style="212" min="47" max="16384"/>
+    <col width="2.5703125" customWidth="1" style="235" min="1" max="1"/>
+    <col width="27.85546875" customWidth="1" style="235" min="2" max="2"/>
+    <col width="9.85546875" customWidth="1" style="235" min="3" max="8"/>
+    <col width="10.7109375" bestFit="1" customWidth="1" style="235" min="9" max="9"/>
+    <col width="10.5703125" customWidth="1" style="235" min="10" max="11"/>
+    <col width="10.85546875" customWidth="1" style="235" min="12" max="13"/>
+    <col width="5.7109375" customWidth="1" style="235" min="14" max="14"/>
+    <col width="11" bestFit="1" customWidth="1" style="235" min="15" max="15"/>
+    <col width="4.5703125" customWidth="1" style="235" min="16" max="24"/>
+    <col width="7.5703125" customWidth="1" style="235" min="25" max="25"/>
+    <col width="9.85546875" customWidth="1" style="235" min="26" max="27"/>
+    <col width="16.42578125" bestFit="1" customWidth="1" style="235" min="28" max="28"/>
+    <col width="12.7109375" customWidth="1" style="235" min="29" max="30"/>
+    <col width="9.85546875" customWidth="1" style="235" min="31" max="47"/>
+    <col width="9.85546875" customWidth="1" style="235" min="48" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.25" customHeight="1" s="219" thickBot="1">
+    <row r="1" ht="14.25" customHeight="1" s="197" thickBot="1">
       <c r="B1" s="47" t="inlineStr">
         <is>
           <t>Fill in your name, tees, front/back 9, and gross scores in the grey boxes</t>
         </is>
       </c>
-      <c r="J1" s="216" t="inlineStr">
+      <c r="J1" s="239" t="inlineStr">
         <is>
           <t>Points</t>
         </is>
       </c>
-      <c r="K1" s="227" t="n"/>
-      <c r="L1" s="227" t="n"/>
-      <c r="M1" s="227" t="n"/>
-    </row>
-    <row r="2" ht="24.95" customHeight="1" s="219" thickBot="1">
+      <c r="K1" s="191" t="n"/>
+      <c r="L1" s="191" t="n"/>
+      <c r="M1" s="191" t="n"/>
+    </row>
+    <row r="2" ht="24.95" customHeight="1" s="197" thickBot="1">
       <c r="D2" s="49" t="inlineStr">
         <is>
           <t>First 3</t>
@@ -10588,16 +10600,16 @@
         </is>
       </c>
       <c r="I2" s="50" t="n"/>
-      <c r="J2" s="214">
+      <c r="J2" s="237">
         <f>B8</f>
         <v/>
       </c>
-      <c r="K2" s="229" t="n"/>
-      <c r="L2" s="210">
+      <c r="K2" s="179" t="n"/>
+      <c r="L2" s="233">
         <f>B17</f>
         <v/>
       </c>
-      <c r="M2" s="229" t="n"/>
+      <c r="M2" s="179" t="n"/>
       <c r="AA2" s="112" t="inlineStr">
         <is>
           <t>#</t>
@@ -10624,8 +10636,8 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="14.25" customHeight="1" s="219" thickBot="1">
-      <c r="B3" s="215">
+    <row r="3" ht="14.25" customHeight="1" s="197" thickBot="1">
+      <c r="B3" s="238">
         <f>B8</f>
         <v/>
       </c>
@@ -10654,16 +10666,16 @@
         <f>SUM(C14:K14)</f>
         <v/>
       </c>
-      <c r="J3" s="213">
+      <c r="J3" s="236">
         <f>SUM(D4:H4)</f>
         <v/>
       </c>
-      <c r="K3" s="236" t="n"/>
-      <c r="L3" s="217">
+      <c r="K3" s="183" t="n"/>
+      <c r="L3" s="240">
         <f>SUM(D6:H6)</f>
         <v/>
       </c>
-      <c r="M3" s="236" t="n"/>
+      <c r="M3" s="183" t="n"/>
       <c r="AA3" s="110" t="n">
         <v>13</v>
       </c>
@@ -10684,8 +10696,8 @@
         <v>25</v>
       </c>
     </row>
-    <row r="4" ht="14.25" customHeight="1" s="219" thickBot="1">
-      <c r="B4" s="237" t="n"/>
+    <row r="4" ht="14.25" customHeight="1" s="197" thickBot="1">
+      <c r="B4" s="186" t="n"/>
       <c r="C4" s="57" t="inlineStr">
         <is>
           <t>PTS</t>
@@ -10711,9 +10723,9 @@
         <f>IF(H3&lt;H5,1,IF(H3=H5,0.5,0))</f>
         <v/>
       </c>
-      <c r="J4" s="238" t="n"/>
-      <c r="K4" s="239" t="n"/>
-      <c r="M4" s="239" t="n"/>
+      <c r="J4" s="184" t="n"/>
+      <c r="K4" s="185" t="n"/>
+      <c r="M4" s="185" t="n"/>
       <c r="AA4" s="110" t="n">
         <v>17</v>
       </c>
@@ -10734,8 +10746,8 @@
         <v>30</v>
       </c>
     </row>
-    <row r="5" ht="14.25" customHeight="1" s="219" thickBot="1">
-      <c r="B5" s="215">
+    <row r="5" ht="14.25" customHeight="1" s="197" thickBot="1">
+      <c r="B5" s="238">
         <f>B17</f>
         <v/>
       </c>
@@ -10764,10 +10776,10 @@
         <f>SUM(C23:K23)</f>
         <v/>
       </c>
-      <c r="J5" s="237" t="n"/>
-      <c r="K5" s="240" t="n"/>
-      <c r="L5" s="227" t="n"/>
-      <c r="M5" s="240" t="n"/>
+      <c r="J5" s="186" t="n"/>
+      <c r="K5" s="187" t="n"/>
+      <c r="L5" s="191" t="n"/>
+      <c r="M5" s="187" t="n"/>
       <c r="AA5" s="110" t="n">
         <v>4</v>
       </c>
@@ -10788,8 +10800,8 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" ht="14.25" customHeight="1" s="219" thickBot="1">
-      <c r="B6" s="237" t="n"/>
+    <row r="6" ht="14.25" customHeight="1" s="197" thickBot="1">
+      <c r="B6" s="186" t="n"/>
       <c r="C6" s="57" t="inlineStr">
         <is>
           <t>PTS</t>
@@ -10815,10 +10827,10 @@
         <f>IF(H5&lt;H3,1,IF(H5=H3,0.5,0))</f>
         <v/>
       </c>
-      <c r="J6" s="211" t="n"/>
-      <c r="K6" s="211" t="n"/>
-      <c r="L6" s="211" t="n"/>
-      <c r="M6" s="211" t="n"/>
+      <c r="J6" s="234" t="n"/>
+      <c r="K6" s="234" t="n"/>
+      <c r="L6" s="234" t="n"/>
+      <c r="M6" s="234" t="n"/>
       <c r="AA6" s="110" t="n">
         <v>11</v>
       </c>
@@ -10840,16 +10852,16 @@
       </c>
     </row>
     <row r="7">
-      <c r="C7" s="211" t="n"/>
-      <c r="D7" s="211" t="n"/>
-      <c r="E7" s="211" t="n"/>
-      <c r="F7" s="211" t="n"/>
-      <c r="G7" s="211" t="n"/>
-      <c r="H7" s="211" t="n"/>
-      <c r="I7" s="211" t="n"/>
-      <c r="J7" s="211" t="n"/>
-      <c r="K7" s="211" t="n"/>
-      <c r="L7" s="211" t="n"/>
+      <c r="C7" s="234" t="n"/>
+      <c r="D7" s="234" t="n"/>
+      <c r="E7" s="234" t="n"/>
+      <c r="F7" s="234" t="n"/>
+      <c r="G7" s="234" t="n"/>
+      <c r="H7" s="234" t="n"/>
+      <c r="I7" s="234" t="n"/>
+      <c r="J7" s="234" t="n"/>
+      <c r="K7" s="234" t="n"/>
+      <c r="L7" s="234" t="n"/>
       <c r="AA7" s="110" t="n">
         <v>5</v>
       </c>
@@ -10870,7 +10882,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" ht="19.5" customHeight="1" s="219" thickBot="1">
+    <row r="8" ht="19.5" customHeight="1" s="197" thickBot="1">
       <c r="B8" s="109" t="inlineStr">
         <is>
           <t>Ethan High</t>
@@ -10881,12 +10893,12 @@
           <t>Handicap:</t>
         </is>
       </c>
-      <c r="D8" s="211">
+      <c r="D8" s="234">
         <f>IFERROR(VLOOKUP(B8,$AB$3:$AE$21,4,0),0)</f>
         <v/>
       </c>
-      <c r="E8" s="211" t="n"/>
-      <c r="F8" s="211" t="inlineStr">
+      <c r="E8" s="234" t="n"/>
+      <c r="F8" s="234" t="inlineStr">
         <is>
           <t>Tees:</t>
         </is>
@@ -10896,8 +10908,8 @@
           <t>Black</t>
         </is>
       </c>
-      <c r="H8" s="211" t="n"/>
-      <c r="I8" s="211" t="inlineStr">
+      <c r="H8" s="234" t="n"/>
+      <c r="I8" s="234" t="inlineStr">
         <is>
           <t>Holes:</t>
         </is>
@@ -10907,14 +10919,14 @@
           <t>Front 9</t>
         </is>
       </c>
-      <c r="K8" s="211" t="n"/>
-      <c r="L8" s="211" t="n"/>
-      <c r="O8" s="212" t="inlineStr">
+      <c r="K8" s="234" t="n"/>
+      <c r="L8" s="234" t="n"/>
+      <c r="O8" s="235" t="inlineStr">
         <is>
           <t>HC's by Tees</t>
         </is>
       </c>
-      <c r="P8" s="211" t="inlineStr">
+      <c r="P8" s="234" t="inlineStr">
         <is>
           <t>Front 9</t>
         </is>
@@ -10939,7 +10951,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" s="219">
+    <row r="9" ht="15" customHeight="1" s="197">
       <c r="B9" s="64" t="inlineStr">
         <is>
           <t>HOLE</t>
@@ -10972,37 +10984,37 @@
       <c r="K9" s="67" t="n">
         <v>9</v>
       </c>
-      <c r="L9" s="211" t="n"/>
-      <c r="O9" s="212" t="inlineStr">
+      <c r="L9" s="234" t="n"/>
+      <c r="O9" s="235" t="inlineStr">
         <is>
           <t>Black</t>
         </is>
       </c>
-      <c r="P9" s="211" t="n">
+      <c r="P9" s="234" t="n">
         <v>1</v>
       </c>
-      <c r="Q9" s="211" t="n">
+      <c r="Q9" s="234" t="n">
         <v>9</v>
       </c>
-      <c r="R9" s="211" t="n">
+      <c r="R9" s="234" t="n">
         <v>7</v>
       </c>
-      <c r="S9" s="211" t="n">
+      <c r="S9" s="234" t="n">
         <v>13</v>
       </c>
-      <c r="T9" s="211" t="n">
+      <c r="T9" s="234" t="n">
         <v>15</v>
       </c>
-      <c r="U9" s="211" t="n">
+      <c r="U9" s="234" t="n">
         <v>5</v>
       </c>
-      <c r="V9" s="211" t="n">
+      <c r="V9" s="234" t="n">
         <v>11</v>
       </c>
-      <c r="W9" s="211" t="n">
+      <c r="W9" s="234" t="n">
         <v>3</v>
       </c>
-      <c r="X9" s="211" t="n">
+      <c r="X9" s="234" t="n">
         <v>17</v>
       </c>
       <c r="AA9" s="110" t="n">
@@ -11034,7 +11046,7 @@
       <c r="C10" s="69" t="n">
         <v>4</v>
       </c>
-      <c r="D10" s="211" t="n">
+      <c r="D10" s="234" t="n">
         <v>5</v>
       </c>
       <c r="E10" s="70" t="n">
@@ -11043,7 +11055,7 @@
       <c r="F10" s="69" t="n">
         <v>4</v>
       </c>
-      <c r="G10" s="211" t="n">
+      <c r="G10" s="234" t="n">
         <v>5</v>
       </c>
       <c r="H10" s="70" t="n">
@@ -11052,46 +11064,46 @@
       <c r="I10" s="69" t="n">
         <v>4</v>
       </c>
-      <c r="J10" s="211" t="n">
+      <c r="J10" s="234" t="n">
         <v>4</v>
       </c>
       <c r="K10" s="70" t="n">
         <v>4</v>
       </c>
-      <c r="L10" s="211">
+      <c r="L10" s="234">
         <f>SUM(C10:K10)</f>
         <v/>
       </c>
-      <c r="O10" s="212" t="inlineStr">
+      <c r="O10" s="235" t="inlineStr">
         <is>
           <t>Blue</t>
         </is>
       </c>
-      <c r="P10" s="211" t="n">
+      <c r="P10" s="234" t="n">
         <v>1</v>
       </c>
-      <c r="Q10" s="211" t="n">
+      <c r="Q10" s="234" t="n">
         <v>9</v>
       </c>
-      <c r="R10" s="211" t="n">
+      <c r="R10" s="234" t="n">
         <v>7</v>
       </c>
-      <c r="S10" s="211" t="n">
+      <c r="S10" s="234" t="n">
         <v>13</v>
       </c>
-      <c r="T10" s="211" t="n">
+      <c r="T10" s="234" t="n">
         <v>15</v>
       </c>
-      <c r="U10" s="211" t="n">
+      <c r="U10" s="234" t="n">
         <v>5</v>
       </c>
-      <c r="V10" s="211" t="n">
+      <c r="V10" s="234" t="n">
         <v>11</v>
       </c>
-      <c r="W10" s="211" t="n">
+      <c r="W10" s="234" t="n">
         <v>3</v>
       </c>
-      <c r="X10" s="211" t="n">
+      <c r="X10" s="234" t="n">
         <v>17</v>
       </c>
       <c r="AA10" s="110" t="n">
@@ -11124,7 +11136,7 @@
         <f t="array" ref="C11">_xlfn.IFS($J8="Back 9",VLOOKUP($G8,$O$15:$X$18,COLUMN()-1,0),$J8="Front 9",VLOOKUP($G8,$O$9:$X$12,COLUMN()-1,0))</f>
         <v/>
       </c>
-      <c r="D11" s="211">
+      <c r="D11" s="234">
         <f t="array" ref="D11">_xlfn.IFS($J8="Back 9",VLOOKUP($G8,$O$15:$X$18,COLUMN()-1,0),$J8="Front 9",VLOOKUP($G8,$O$9:$X$12,COLUMN()-1,0))</f>
         <v/>
       </c>
@@ -11136,7 +11148,7 @@
         <f t="array" ref="F11">_xlfn.IFS($J8="Back 9",VLOOKUP($G8,$O$15:$X$18,COLUMN()-1,0),$J8="Front 9",VLOOKUP($G8,$O$9:$X$12,COLUMN()-1,0))</f>
         <v/>
       </c>
-      <c r="G11" s="211">
+      <c r="G11" s="234">
         <f t="array" ref="G11">_xlfn.IFS($J8="Back 9",VLOOKUP($G8,$O$15:$X$18,COLUMN()-1,0),$J8="Front 9",VLOOKUP($G8,$O$9:$X$12,COLUMN()-1,0))</f>
         <v/>
       </c>
@@ -11148,7 +11160,7 @@
         <f t="array" ref="I11">_xlfn.IFS($J8="Back 9",VLOOKUP($G8,$O$15:$X$18,COLUMN()-1,0),$J8="Front 9",VLOOKUP($G8,$O$9:$X$12,COLUMN()-1,0))</f>
         <v/>
       </c>
-      <c r="J11" s="211">
+      <c r="J11" s="234">
         <f t="array" ref="J11">_xlfn.IFS($J8="Back 9",VLOOKUP($G8,$O$15:$X$18,COLUMN()-1,0),$J8="Front 9",VLOOKUP($G8,$O$9:$X$12,COLUMN()-1,0))</f>
         <v/>
       </c>
@@ -11156,37 +11168,37 @@
         <f t="array" ref="K11">_xlfn.IFS($J8="Back 9",VLOOKUP($G8,$O$15:$X$18,COLUMN()-1,0),$J8="Front 9",VLOOKUP($G8,$O$9:$X$12,COLUMN()-1,0))</f>
         <v/>
       </c>
-      <c r="L11" s="211" t="n"/>
-      <c r="O11" s="212" t="inlineStr">
+      <c r="L11" s="234" t="n"/>
+      <c r="O11" s="235" t="inlineStr">
         <is>
           <t>Blue / White</t>
         </is>
       </c>
-      <c r="P11" s="211" t="n">
+      <c r="P11" s="234" t="n">
         <v>3</v>
       </c>
-      <c r="Q11" s="211" t="n">
+      <c r="Q11" s="234" t="n">
         <v>7</v>
       </c>
-      <c r="R11" s="211" t="n">
+      <c r="R11" s="234" t="n">
         <v>13</v>
       </c>
-      <c r="S11" s="211" t="n">
+      <c r="S11" s="234" t="n">
         <v>17</v>
       </c>
-      <c r="T11" s="211" t="n">
+      <c r="T11" s="234" t="n">
         <v>15</v>
       </c>
-      <c r="U11" s="211" t="n">
+      <c r="U11" s="234" t="n">
         <v>1</v>
       </c>
-      <c r="V11" s="211" t="n">
+      <c r="V11" s="234" t="n">
         <v>11</v>
       </c>
-      <c r="W11" s="211" t="n">
+      <c r="W11" s="234" t="n">
         <v>5</v>
       </c>
-      <c r="X11" s="211" t="n">
+      <c r="X11" s="234" t="n">
         <v>9</v>
       </c>
       <c r="AA11" s="110" t="n">
@@ -11209,7 +11221,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1" s="219">
+    <row r="12" ht="15" customHeight="1" s="197">
       <c r="B12" s="71" t="inlineStr">
         <is>
           <t>GROSS</t>
@@ -11242,7 +11254,7 @@
       <c r="K12" s="115" t="n">
         <v>5</v>
       </c>
-      <c r="L12" s="211">
+      <c r="L12" s="234">
         <f>SUM(C12:K12)</f>
         <v/>
       </c>
@@ -11250,36 +11262,36 @@
         <f>SUM(C12:K12)-SUM(C$10:K$10)</f>
         <v/>
       </c>
-      <c r="O12" s="212" t="inlineStr">
+      <c r="O12" s="235" t="inlineStr">
         <is>
           <t>White</t>
         </is>
       </c>
-      <c r="P12" s="211" t="n">
+      <c r="P12" s="234" t="n">
         <v>1</v>
       </c>
-      <c r="Q12" s="211" t="n">
+      <c r="Q12" s="234" t="n">
         <v>7</v>
       </c>
-      <c r="R12" s="211" t="n">
+      <c r="R12" s="234" t="n">
         <v>11</v>
       </c>
-      <c r="S12" s="211" t="n">
+      <c r="S12" s="234" t="n">
         <v>13</v>
       </c>
-      <c r="T12" s="211" t="n">
+      <c r="T12" s="234" t="n">
         <v>15</v>
       </c>
-      <c r="U12" s="211" t="n">
+      <c r="U12" s="234" t="n">
         <v>9</v>
       </c>
-      <c r="V12" s="211" t="n">
+      <c r="V12" s="234" t="n">
         <v>17</v>
       </c>
-      <c r="W12" s="211" t="n">
+      <c r="W12" s="234" t="n">
         <v>3</v>
       </c>
-      <c r="X12" s="211" t="n">
+      <c r="X12" s="234" t="n">
         <v>5</v>
       </c>
       <c r="AA12" s="110" t="n">
@@ -11311,7 +11323,7 @@
       <c r="C13" s="69" t="n">
         <v>5</v>
       </c>
-      <c r="D13" s="211" t="n">
+      <c r="D13" s="234" t="n">
         <v>6</v>
       </c>
       <c r="E13" s="70" t="n">
@@ -11320,7 +11332,7 @@
       <c r="F13" s="69" t="n">
         <v>5</v>
       </c>
-      <c r="G13" s="211" t="n">
+      <c r="G13" s="234" t="n">
         <v>6</v>
       </c>
       <c r="H13" s="70" t="n">
@@ -11329,7 +11341,7 @@
       <c r="I13" s="69" t="n">
         <v>5</v>
       </c>
-      <c r="J13" s="211" t="n">
+      <c r="J13" s="234" t="n">
         <v>5</v>
       </c>
       <c r="K13" s="70" t="n">
@@ -11366,7 +11378,7 @@
         <f>C12-C13</f>
         <v/>
       </c>
-      <c r="D14" s="211">
+      <c r="D14" s="234">
         <f>D12-INT($D$8/18)-IF(D11&lt;=MOD($D$8,18),1,0)</f>
         <v/>
       </c>
@@ -11378,7 +11390,7 @@
         <f>F12-INT($D$8/18)-IF(F11&lt;=MOD($D$8,18),1,0)</f>
         <v/>
       </c>
-      <c r="G14" s="211">
+      <c r="G14" s="234">
         <f>G12-INT($D$8/18)-IF(G11&lt;=MOD($D$8,18),1,0)</f>
         <v/>
       </c>
@@ -11390,7 +11402,7 @@
         <f>I12-INT($D$8/18)-IF(I11&lt;=MOD($D$8,18),1,0)</f>
         <v/>
       </c>
-      <c r="J14" s="211">
+      <c r="J14" s="234">
         <f>J12-INT($D$8/18)-IF(J11&lt;=MOD($D$8,18),1,0)</f>
         <v/>
       </c>
@@ -11398,7 +11410,7 @@
         <f>K12-INT($D$8/18)-IF(K11&lt;=MOD($D$8,18),1,0)</f>
         <v/>
       </c>
-      <c r="L14" s="211">
+      <c r="L14" s="234">
         <f>SUM(C14:K14)</f>
         <v/>
       </c>
@@ -11406,7 +11418,7 @@
         <f>SUM(C14:K14)-SUM(C$10:K$10)</f>
         <v/>
       </c>
-      <c r="O14" s="211" t="inlineStr">
+      <c r="O14" s="234" t="inlineStr">
         <is>
           <t>Back 9</t>
         </is>
@@ -11431,7 +11443,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="15" ht="14.25" customHeight="1" s="219" thickBot="1">
+    <row r="15" ht="14.25" customHeight="1" s="197" thickBot="1">
       <c r="B15" s="74" t="inlineStr">
         <is>
           <t>Wins Hole</t>
@@ -11473,37 +11485,37 @@
         <f>IF(K14&lt;K23,1,0)</f>
         <v/>
       </c>
-      <c r="L15" s="211" t="n"/>
-      <c r="O15" s="212" t="inlineStr">
+      <c r="L15" s="234" t="n"/>
+      <c r="O15" s="235" t="inlineStr">
         <is>
           <t>Black</t>
         </is>
       </c>
-      <c r="P15" s="211" t="n">
+      <c r="P15" s="234" t="n">
         <v>12</v>
       </c>
-      <c r="Q15" s="211" t="n">
+      <c r="Q15" s="234" t="n">
         <v>2</v>
       </c>
-      <c r="R15" s="211" t="n">
+      <c r="R15" s="234" t="n">
         <v>8</v>
       </c>
-      <c r="S15" s="211" t="n">
+      <c r="S15" s="234" t="n">
         <v>6</v>
       </c>
-      <c r="T15" s="211" t="n">
+      <c r="T15" s="234" t="n">
         <v>18</v>
       </c>
-      <c r="U15" s="211" t="n">
+      <c r="U15" s="234" t="n">
         <v>14</v>
       </c>
-      <c r="V15" s="211" t="n">
+      <c r="V15" s="234" t="n">
         <v>16</v>
       </c>
-      <c r="W15" s="211" t="n">
+      <c r="W15" s="234" t="n">
         <v>10</v>
       </c>
-      <c r="X15" s="211" t="n">
+      <c r="X15" s="234" t="n">
         <v>4</v>
       </c>
       <c r="AA15" s="110" t="n">
@@ -11527,46 +11539,46 @@
       </c>
     </row>
     <row r="16">
-      <c r="C16" s="211" t="n"/>
-      <c r="D16" s="211" t="n"/>
-      <c r="E16" s="211" t="n"/>
-      <c r="F16" s="211" t="n"/>
-      <c r="G16" s="211" t="n"/>
-      <c r="H16" s="211" t="n"/>
-      <c r="I16" s="211" t="n"/>
-      <c r="J16" s="211" t="n"/>
-      <c r="K16" s="211" t="n"/>
-      <c r="L16" s="211" t="n"/>
-      <c r="O16" s="212" t="inlineStr">
+      <c r="C16" s="234" t="n"/>
+      <c r="D16" s="234" t="n"/>
+      <c r="E16" s="234" t="n"/>
+      <c r="F16" s="234" t="n"/>
+      <c r="G16" s="234" t="n"/>
+      <c r="H16" s="234" t="n"/>
+      <c r="I16" s="234" t="n"/>
+      <c r="J16" s="234" t="n"/>
+      <c r="K16" s="234" t="n"/>
+      <c r="L16" s="234" t="n"/>
+      <c r="O16" s="235" t="inlineStr">
         <is>
           <t>Blue</t>
         </is>
       </c>
-      <c r="P16" s="211" t="n">
+      <c r="P16" s="234" t="n">
         <v>12</v>
       </c>
-      <c r="Q16" s="211" t="n">
+      <c r="Q16" s="234" t="n">
         <v>2</v>
       </c>
-      <c r="R16" s="211" t="n">
+      <c r="R16" s="234" t="n">
         <v>8</v>
       </c>
-      <c r="S16" s="211" t="n">
+      <c r="S16" s="234" t="n">
         <v>6</v>
       </c>
-      <c r="T16" s="211" t="n">
+      <c r="T16" s="234" t="n">
         <v>18</v>
       </c>
-      <c r="U16" s="211" t="n">
+      <c r="U16" s="234" t="n">
         <v>14</v>
       </c>
-      <c r="V16" s="211" t="n">
+      <c r="V16" s="234" t="n">
         <v>16</v>
       </c>
-      <c r="W16" s="211" t="n">
+      <c r="W16" s="234" t="n">
         <v>10</v>
       </c>
-      <c r="X16" s="211" t="n">
+      <c r="X16" s="234" t="n">
         <v>4</v>
       </c>
       <c r="AA16" s="110" t="n">
@@ -11589,7 +11601,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="17" ht="19.5" customHeight="1" s="219" thickBot="1">
+    <row r="17" ht="19.5" customHeight="1" s="197" thickBot="1">
       <c r="B17" s="109" t="inlineStr">
         <is>
           <t>Bruce Dubovecky</t>
@@ -11600,12 +11612,12 @@
           <t>Handicap:</t>
         </is>
       </c>
-      <c r="D17" s="211">
+      <c r="D17" s="234">
         <f>IFERROR(VLOOKUP(B17,$AB$3:$AE$21,4,0),0)</f>
         <v/>
       </c>
-      <c r="E17" s="211" t="n"/>
-      <c r="F17" s="211" t="inlineStr">
+      <c r="E17" s="234" t="n"/>
+      <c r="F17" s="234" t="inlineStr">
         <is>
           <t>Tees:</t>
         </is>
@@ -11615,8 +11627,8 @@
           <t>Black</t>
         </is>
       </c>
-      <c r="H17" s="211" t="n"/>
-      <c r="I17" s="211" t="inlineStr">
+      <c r="H17" s="234" t="n"/>
+      <c r="I17" s="234" t="inlineStr">
         <is>
           <t>Holes:</t>
         </is>
@@ -11626,38 +11638,38 @@
           <t>Front 9</t>
         </is>
       </c>
-      <c r="K17" s="211" t="n"/>
-      <c r="L17" s="211" t="n"/>
-      <c r="O17" s="212" t="inlineStr">
+      <c r="K17" s="234" t="n"/>
+      <c r="L17" s="234" t="n"/>
+      <c r="O17" s="235" t="inlineStr">
         <is>
           <t>Blue / White</t>
         </is>
       </c>
-      <c r="P17" s="211" t="n">
+      <c r="P17" s="234" t="n">
         <v>12</v>
       </c>
-      <c r="Q17" s="211" t="n">
+      <c r="Q17" s="234" t="n">
         <v>4</v>
       </c>
-      <c r="R17" s="211" t="n">
+      <c r="R17" s="234" t="n">
         <v>10</v>
       </c>
-      <c r="S17" s="211" t="n">
+      <c r="S17" s="234" t="n">
         <v>2</v>
       </c>
-      <c r="T17" s="211" t="n">
+      <c r="T17" s="234" t="n">
         <v>16</v>
       </c>
-      <c r="U17" s="211" t="n">
+      <c r="U17" s="234" t="n">
         <v>14</v>
       </c>
-      <c r="V17" s="211" t="n">
+      <c r="V17" s="234" t="n">
         <v>18</v>
       </c>
-      <c r="W17" s="211" t="n">
+      <c r="W17" s="234" t="n">
         <v>6</v>
       </c>
-      <c r="X17" s="211" t="n">
+      <c r="X17" s="234" t="n">
         <v>8</v>
       </c>
       <c r="AA17" s="110" t="n">
@@ -11680,7 +11692,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="18" ht="15" customHeight="1" s="219">
+    <row r="18" ht="15" customHeight="1" s="197">
       <c r="B18" s="64" t="inlineStr">
         <is>
           <t>HOLE</t>
@@ -11713,38 +11725,38 @@
       <c r="K18" s="67" t="n">
         <v>9</v>
       </c>
-      <c r="L18" s="211" t="n"/>
+      <c r="L18" s="234" t="n"/>
       <c r="M18" s="72" t="n"/>
-      <c r="O18" s="212" t="inlineStr">
+      <c r="O18" s="235" t="inlineStr">
         <is>
           <t>White</t>
         </is>
       </c>
-      <c r="P18" s="211" t="n">
+      <c r="P18" s="234" t="n">
         <v>10</v>
       </c>
-      <c r="Q18" s="211" t="n">
+      <c r="Q18" s="234" t="n">
         <v>4</v>
       </c>
-      <c r="R18" s="211" t="n">
+      <c r="R18" s="234" t="n">
         <v>8</v>
       </c>
-      <c r="S18" s="211" t="n">
+      <c r="S18" s="234" t="n">
         <v>2</v>
       </c>
-      <c r="T18" s="211" t="n">
+      <c r="T18" s="234" t="n">
         <v>16</v>
       </c>
-      <c r="U18" s="211" t="n">
+      <c r="U18" s="234" t="n">
         <v>12</v>
       </c>
-      <c r="V18" s="211" t="n">
+      <c r="V18" s="234" t="n">
         <v>18</v>
       </c>
-      <c r="W18" s="211" t="n">
+      <c r="W18" s="234" t="n">
         <v>14</v>
       </c>
-      <c r="X18" s="211" t="n">
+      <c r="X18" s="234" t="n">
         <v>6</v>
       </c>
       <c r="AA18" s="110" t="n">
@@ -11776,7 +11788,7 @@
       <c r="C19" s="69" t="n">
         <v>4</v>
       </c>
-      <c r="D19" s="211" t="n">
+      <c r="D19" s="234" t="n">
         <v>5</v>
       </c>
       <c r="E19" s="70" t="n">
@@ -11785,7 +11797,7 @@
       <c r="F19" s="69" t="n">
         <v>4</v>
       </c>
-      <c r="G19" s="211" t="n">
+      <c r="G19" s="234" t="n">
         <v>5</v>
       </c>
       <c r="H19" s="70" t="n">
@@ -11794,13 +11806,13 @@
       <c r="I19" s="69" t="n">
         <v>4</v>
       </c>
-      <c r="J19" s="211" t="n">
+      <c r="J19" s="234" t="n">
         <v>4</v>
       </c>
       <c r="K19" s="70" t="n">
         <v>4</v>
       </c>
-      <c r="L19" s="211">
+      <c r="L19" s="234">
         <f>SUM(C19:K19)</f>
         <v/>
       </c>
@@ -11834,7 +11846,7 @@
         <f t="array" ref="C20">_xlfn.IFS($J17="Back 9",VLOOKUP($G17,$O$15:$X$18,COLUMN()-1,0),$J17="Front 9",VLOOKUP($G17,$O$9:$X$12,COLUMN()-1,0))</f>
         <v/>
       </c>
-      <c r="D20" s="211">
+      <c r="D20" s="234">
         <f t="array" ref="D20">_xlfn.IFS($J17="Back 9",VLOOKUP($G17,$O$15:$X$18,COLUMN()-1,0),$J17="Front 9",VLOOKUP($G17,$O$9:$X$12,COLUMN()-1,0))</f>
         <v/>
       </c>
@@ -11846,7 +11858,7 @@
         <f t="array" ref="F20">_xlfn.IFS($J17="Back 9",VLOOKUP($G17,$O$15:$X$18,COLUMN()-1,0),$J17="Front 9",VLOOKUP($G17,$O$9:$X$12,COLUMN()-1,0))</f>
         <v/>
       </c>
-      <c r="G20" s="211">
+      <c r="G20" s="234">
         <f t="array" ref="G20">_xlfn.IFS($J17="Back 9",VLOOKUP($G17,$O$15:$X$18,COLUMN()-1,0),$J17="Front 9",VLOOKUP($G17,$O$9:$X$12,COLUMN()-1,0))</f>
         <v/>
       </c>
@@ -11858,7 +11870,7 @@
         <f t="array" ref="I20">_xlfn.IFS($J17="Back 9",VLOOKUP($G17,$O$15:$X$18,COLUMN()-1,0),$J17="Front 9",VLOOKUP($G17,$O$9:$X$12,COLUMN()-1,0))</f>
         <v/>
       </c>
-      <c r="J20" s="211">
+      <c r="J20" s="234">
         <f t="array" ref="J20">_xlfn.IFS($J17="Back 9",VLOOKUP($G17,$O$15:$X$18,COLUMN()-1,0),$J17="Front 9",VLOOKUP($G17,$O$9:$X$12,COLUMN()-1,0))</f>
         <v/>
       </c>
@@ -11866,7 +11878,7 @@
         <f t="array" ref="K20">_xlfn.IFS($J17="Back 9",VLOOKUP($G17,$O$15:$X$18,COLUMN()-1,0),$J17="Front 9",VLOOKUP($G17,$O$9:$X$12,COLUMN()-1,0))</f>
         <v/>
       </c>
-      <c r="L20" s="211" t="n"/>
+      <c r="L20" s="234" t="n"/>
       <c r="AA20" s="110" t="n">
         <v>16</v>
       </c>
@@ -11887,7 +11899,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="21" ht="15" customHeight="1" s="219">
+    <row r="21" ht="15" customHeight="1" s="197">
       <c r="B21" s="71" t="inlineStr">
         <is>
           <t>GROSS</t>
@@ -11920,7 +11932,7 @@
       <c r="K21" s="115" t="n">
         <v>5</v>
       </c>
-      <c r="L21" s="211">
+      <c r="L21" s="234">
         <f>SUM(C21:K21)</f>
         <v/>
       </c>
@@ -11957,7 +11969,7 @@
       <c r="C22" s="69" t="n">
         <v>5</v>
       </c>
-      <c r="D22" s="211" t="n">
+      <c r="D22" s="234" t="n">
         <v>6</v>
       </c>
       <c r="E22" s="70" t="n">
@@ -11966,7 +11978,7 @@
       <c r="F22" s="69" t="n">
         <v>5</v>
       </c>
-      <c r="G22" s="211" t="n">
+      <c r="G22" s="234" t="n">
         <v>6</v>
       </c>
       <c r="H22" s="70" t="n">
@@ -11975,7 +11987,7 @@
       <c r="I22" s="69" t="n">
         <v>5</v>
       </c>
-      <c r="J22" s="211" t="n">
+      <c r="J22" s="234" t="n">
         <v>5</v>
       </c>
       <c r="K22" s="70" t="n">
@@ -11993,7 +12005,7 @@
         <f>C21-C22</f>
         <v/>
       </c>
-      <c r="D23" s="211">
+      <c r="D23" s="234">
         <f>D21-D22</f>
         <v/>
       </c>
@@ -12005,7 +12017,7 @@
         <f>F21-F22</f>
         <v/>
       </c>
-      <c r="G23" s="211">
+      <c r="G23" s="234">
         <f>G21-G22</f>
         <v/>
       </c>
@@ -12017,7 +12029,7 @@
         <f>I21-I22</f>
         <v/>
       </c>
-      <c r="J23" s="211">
+      <c r="J23" s="234">
         <f>J21-J22</f>
         <v/>
       </c>
@@ -12025,7 +12037,7 @@
         <f>K21-K22</f>
         <v/>
       </c>
-      <c r="L23" s="211">
+      <c r="L23" s="234">
         <f>SUM(C23:K23)</f>
         <v/>
       </c>
@@ -12034,7 +12046,7 @@
         <v/>
       </c>
     </row>
-    <row r="24" ht="14.25" customHeight="1" s="219" thickBot="1">
+    <row r="24" ht="14.25" customHeight="1" s="197" thickBot="1">
       <c r="B24" s="74" t="inlineStr">
         <is>
           <t>Wins Hole</t>
@@ -12076,7 +12088,7 @@
         <f>IF(K23&lt;K14,1,0)</f>
         <v/>
       </c>
-      <c r="L24" s="211" t="n"/>
+      <c r="L24" s="234" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="AA2:AE21">
@@ -12087,8 +12099,8 @@
   <mergeCells count="9">
     <mergeCell ref="L2:M2"/>
     <mergeCell ref="O14:X14"/>
+    <mergeCell ref="J3:K5"/>
     <mergeCell ref="P8:X8"/>
-    <mergeCell ref="J3:K5"/>
     <mergeCell ref="J2:K2"/>
     <mergeCell ref="B3:B4"/>
     <mergeCell ref="J1:M1"/>

--- a/2026 IMI Golf League.xlsx
+++ b/2026 IMI Golf League.xlsx
@@ -9898,21 +9898,23 @@
         <v>8</v>
       </c>
       <c r="G17" s="166" t="n"/>
-      <c r="H17" s="166" t="n"/>
+      <c r="H17" s="166" t="n">
+        <v>8</v>
+      </c>
       <c r="I17" s="166" t="n"/>
       <c r="J17" s="166" t="n"/>
       <c r="K17" s="166" t="n"/>
       <c r="L17" s="167" t="n"/>
       <c r="M17" s="226" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="N17" s="218" t="inlineStr">
         <is>
-          <t>3-0-0</t>
+          <t>4-0-0</t>
         </is>
       </c>
       <c r="O17" s="212" t="n">
-        <v>37.3</v>
+        <v>36.8</v>
       </c>
       <c r="Q17" s="227" t="inlineStr">
         <is>
@@ -9937,7 +9939,9 @@
         <v>37</v>
       </c>
       <c r="G18" s="170" t="n"/>
-      <c r="H18" s="170" t="n"/>
+      <c r="H18" s="170" t="n">
+        <v>35</v>
+      </c>
       <c r="I18" s="170" t="n"/>
       <c r="J18" s="170" t="n"/>
       <c r="K18" s="170" t="n"/>
@@ -9977,7 +9981,9 @@
       <c r="G19" s="220" t="n">
         <v>8</v>
       </c>
-      <c r="H19" s="220" t="n"/>
+      <c r="H19" s="220" t="n">
+        <v>0</v>
+      </c>
       <c r="I19" s="220" t="n"/>
       <c r="J19" s="220" t="n"/>
       <c r="K19" s="220" t="n"/>
@@ -9987,11 +9993,11 @@
       </c>
       <c r="N19" s="220" t="inlineStr">
         <is>
-          <t>3-1-0</t>
+          <t>3-2-0</t>
         </is>
       </c>
       <c r="O19" s="230" t="n">
-        <v>38.8</v>
+        <v>39.8</v>
       </c>
       <c r="Q19" s="154" t="inlineStr">
         <is>
@@ -10018,7 +10024,9 @@
       <c r="G20" s="163" t="n">
         <v>38</v>
       </c>
-      <c r="H20" s="163" t="n"/>
+      <c r="H20" s="163" t="n">
+        <v>44</v>
+      </c>
       <c r="I20" s="163" t="n"/>
       <c r="J20" s="163" t="n"/>
       <c r="K20" s="163" t="n"/>

--- a/2026 IMI Golf League.xlsx
+++ b/2026 IMI Golf League.xlsx
@@ -10277,20 +10277,22 @@
       <c r="H27" s="220" t="n">
         <v>7</v>
       </c>
-      <c r="I27" s="220" t="n"/>
+      <c r="I27" s="220" t="n">
+        <v>2</v>
+      </c>
       <c r="J27" s="220" t="n"/>
       <c r="K27" s="220" t="n"/>
       <c r="L27" s="160" t="n"/>
       <c r="M27" s="222" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="N27" s="220" t="inlineStr">
         <is>
-          <t>1-3-1</t>
+          <t>1-4-1</t>
         </is>
       </c>
       <c r="O27" s="230" t="n">
-        <v>51.4</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="28" ht="13.5" customHeight="1" s="197" thickBot="1">
@@ -10315,7 +10317,9 @@
       <c r="H28" s="163" t="n">
         <v>48</v>
       </c>
-      <c r="I28" s="163" t="n"/>
+      <c r="I28" s="163" t="n">
+        <v>50</v>
+      </c>
       <c r="J28" s="163" t="n"/>
       <c r="K28" s="163" t="n"/>
       <c r="L28" s="164" t="n"/>
@@ -10423,20 +10427,22 @@
       <c r="H31" s="220" t="n">
         <v>2</v>
       </c>
-      <c r="I31" s="220" t="n"/>
+      <c r="I31" s="220" t="n">
+        <v>6</v>
+      </c>
       <c r="J31" s="220" t="n"/>
       <c r="K31" s="220" t="n"/>
       <c r="L31" s="160" t="n"/>
       <c r="M31" s="222" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="N31" s="220" t="inlineStr">
         <is>
-          <t>0-3-1</t>
+          <t>1-3-1</t>
         </is>
       </c>
       <c r="O31" s="230" t="n">
-        <v>51</v>
+        <v>49.8</v>
       </c>
     </row>
     <row r="32" ht="13.5" customHeight="1" s="197" thickBot="1">
@@ -10459,7 +10465,9 @@
       <c r="H32" s="163" t="n">
         <v>54</v>
       </c>
-      <c r="I32" s="163" t="n"/>
+      <c r="I32" s="163" t="n">
+        <v>45</v>
+      </c>
       <c r="J32" s="163" t="n"/>
       <c r="K32" s="163" t="n"/>
       <c r="L32" s="164" t="n"/>

--- a/2026 IMI Golf League.xlsx
+++ b/2026 IMI Golf League.xlsx
@@ -9441,20 +9441,24 @@
         <v>7</v>
       </c>
       <c r="H5" s="166" t="n"/>
-      <c r="I5" s="166" t="n"/>
+      <c r="I5" s="166" t="n">
+        <v>5</v>
+      </c>
       <c r="J5" s="166" t="n"/>
-      <c r="K5" s="166" t="n"/>
+      <c r="K5" s="166" t="n">
+        <v>7</v>
+      </c>
       <c r="L5" s="167" t="n"/>
       <c r="M5" s="226" t="n">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="N5" s="218" t="inlineStr">
         <is>
-          <t>4-0-0</t>
+          <t>6-0-0</t>
         </is>
       </c>
       <c r="O5" s="212" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="Q5" s="33" t="n">
         <v>1</v>
@@ -9482,9 +9486,13 @@
         <v>42</v>
       </c>
       <c r="H6" s="170" t="n"/>
-      <c r="I6" s="170" t="n"/>
+      <c r="I6" s="170" t="n">
+        <v>37</v>
+      </c>
       <c r="J6" s="170" t="n"/>
-      <c r="K6" s="170" t="n"/>
+      <c r="K6" s="170" t="n">
+        <v>33</v>
+      </c>
       <c r="L6" s="171" t="n"/>
       <c r="M6" s="223" t="n"/>
       <c r="N6" s="219" t="n"/>
@@ -9517,20 +9525,22 @@
       <c r="F7" s="220" t="n"/>
       <c r="G7" s="220" t="n"/>
       <c r="H7" s="220" t="n"/>
-      <c r="I7" s="220" t="n"/>
+      <c r="I7" s="220" t="n">
+        <v>3</v>
+      </c>
       <c r="J7" s="220" t="n"/>
       <c r="K7" s="220" t="n"/>
       <c r="L7" s="160" t="n"/>
       <c r="M7" s="222" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="N7" s="220" t="inlineStr">
         <is>
-          <t>0-1-1</t>
+          <t>0-2-1</t>
         </is>
       </c>
       <c r="O7" s="230" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q7" s="33" t="n">
         <v>3</v>
@@ -9554,7 +9564,9 @@
       <c r="F8" s="163" t="n"/>
       <c r="G8" s="163" t="n"/>
       <c r="H8" s="163" t="n"/>
-      <c r="I8" s="163" t="n"/>
+      <c r="I8" s="163" t="n">
+        <v>38</v>
+      </c>
       <c r="J8" s="163" t="n"/>
       <c r="K8" s="163" t="n"/>
       <c r="L8" s="164" t="n"/>
@@ -9903,18 +9915,20 @@
       </c>
       <c r="I17" s="166" t="n"/>
       <c r="J17" s="166" t="n"/>
-      <c r="K17" s="166" t="n"/>
+      <c r="K17" s="166" t="n">
+        <v>1</v>
+      </c>
       <c r="L17" s="167" t="n"/>
       <c r="M17" s="226" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="N17" s="218" t="inlineStr">
         <is>
-          <t>4-0-0</t>
+          <t>4-1-0</t>
         </is>
       </c>
       <c r="O17" s="212" t="n">
-        <v>36.8</v>
+        <v>37.4</v>
       </c>
       <c r="Q17" s="227" t="inlineStr">
         <is>
@@ -9944,7 +9958,9 @@
       </c>
       <c r="I18" s="170" t="n"/>
       <c r="J18" s="170" t="n"/>
-      <c r="K18" s="170" t="n"/>
+      <c r="K18" s="170" t="n">
+        <v>40</v>
+      </c>
       <c r="L18" s="171" t="n"/>
       <c r="M18" s="223" t="n"/>
       <c r="N18" s="219" t="n"/>

--- a/2026 IMI Golf League.xlsx
+++ b/2026 IMI Golf League.xlsx
@@ -10083,18 +10083,20 @@
       <c r="H21" s="166" t="n"/>
       <c r="I21" s="166" t="n"/>
       <c r="J21" s="166" t="n"/>
-      <c r="K21" s="166" t="n"/>
+      <c r="K21" s="166" t="n">
+        <v>6</v>
+      </c>
       <c r="L21" s="167" t="n"/>
       <c r="M21" s="226" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="N21" s="218" t="inlineStr">
         <is>
-          <t>3-0-0</t>
+          <t>4-0-0</t>
         </is>
       </c>
       <c r="O21" s="212" t="n">
-        <v>39.3</v>
+        <v>39.2</v>
       </c>
       <c r="Q21" s="154" t="inlineStr">
         <is>
@@ -10123,7 +10125,9 @@
       <c r="H22" s="170" t="n"/>
       <c r="I22" s="170" t="n"/>
       <c r="J22" s="170" t="n"/>
-      <c r="K22" s="170" t="n"/>
+      <c r="K22" s="170" t="n">
+        <v>39</v>
+      </c>
       <c r="L22" s="171" t="n"/>
       <c r="M22" s="223" t="n"/>
       <c r="N22" s="219" t="n"/>
@@ -10223,18 +10227,20 @@
       </c>
       <c r="I25" s="166" t="n"/>
       <c r="J25" s="166" t="n"/>
-      <c r="K25" s="166" t="n"/>
+      <c r="K25" s="166" t="n">
+        <v>2</v>
+      </c>
       <c r="L25" s="167" t="n"/>
       <c r="M25" s="226" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="N25" s="218" t="inlineStr">
         <is>
-          <t>1-2-1</t>
+          <t>1-3-1</t>
         </is>
       </c>
       <c r="O25" s="212" t="n">
-        <v>53.5</v>
+        <v>52.8</v>
       </c>
     </row>
     <row r="26" ht="13.5" customHeight="1" s="197" thickBot="1">
@@ -10259,7 +10265,9 @@
       </c>
       <c r="I26" s="170" t="n"/>
       <c r="J26" s="170" t="n"/>
-      <c r="K26" s="170" t="n"/>
+      <c r="K26" s="170" t="n">
+        <v>50</v>
+      </c>
       <c r="L26" s="171" t="n"/>
       <c r="M26" s="223" t="n"/>
       <c r="N26" s="219" t="n"/>
